--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -37,10 +37,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -291,6 +287,10 @@
   </si>
   <si>
     <t>strawberry</t>
+  </si>
+  <si>
+    <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -685,19 +685,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>0</v>
@@ -709,16 +709,16 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>1</v>
@@ -726,63 +726,63 @@
     </row>
     <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="L3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="P3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
         <v>1001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1">
         <v>5</v>
@@ -813,18 +813,18 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3">
         <v>1002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
@@ -855,18 +855,18 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -893,18 +893,18 @@
         <v>165</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3">
         <v>1004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -931,18 +931,18 @@
         <v>220</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3">
         <v>1005</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
@@ -969,18 +969,18 @@
         <v>165</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3">
         <v>1006</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -1007,18 +1007,18 @@
         <v>181</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>1007</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -1045,18 +1045,18 @@
         <v>208</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3">
         <v>1008</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -1083,18 +1083,18 @@
         <v>195</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3">
         <v>1009</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -1121,18 +1121,18 @@
         <v>73</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="3">
         <v>1010</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
@@ -1159,18 +1159,18 @@
         <v>146</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3">
         <v>1011</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
@@ -1197,18 +1197,18 @@
         <v>101</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="3">
         <v>1012</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1">
         <v>5</v>
@@ -1235,18 +1235,18 @@
         <v>101</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="3">
         <v>1013</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" s="1">
         <v>5</v>
@@ -1273,18 +1273,18 @@
         <v>208</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3">
         <v>1014</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" s="1">
         <v>5</v>
@@ -1311,18 +1311,18 @@
         <v>208</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="3">
         <v>1015</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -1349,18 +1349,18 @@
         <v>146</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3">
         <v>1016</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -1387,18 +1387,18 @@
         <v>125</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="3">
         <v>1017</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D20" s="1">
         <v>5</v>
@@ -1425,7 +1425,7 @@
         <v>208</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -12,11 +12,11 @@
     <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380"/>
   </bookViews>
   <sheets>
-    <sheet name="item" sheetId="1" r:id="rId1"/>
+    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">item!$A$3:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$C$3</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -290,6 +290,62 @@
   </si>
   <si>
     <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉米种子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉米的种子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锄头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洒水壶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斧头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>镰刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平整田地使用的工具。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浇灌农作物的工具。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>砍伐树木的工具。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收割农作物种子的工具。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hoe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Waterpot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sickle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corn_seed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -660,7 +716,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P20"/>
+  <dimension ref="A2:P25"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -797,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -839,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -881,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -919,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -957,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -995,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
@@ -1033,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -1071,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
@@ -1109,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
@@ -1147,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
@@ -1185,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
@@ -1223,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
@@ -1261,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
@@ -1299,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
@@ -1337,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
@@ -1375,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
@@ -1413,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
@@ -1426,6 +1482,193 @@
       </c>
       <c r="P20" s="5" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>8000</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>49</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>100</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="1">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>100</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="1">
+        <v>6</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>100</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2002</v>
+      </c>
+      <c r="D24" s="1">
+        <v>6</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>100</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="1">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>100</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -347,6 +347,9 @@
   <si>
     <t>corn_seed</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemValue</t>
   </si>
 </sst>
 </file>
@@ -716,21 +719,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P25"/>
+  <dimension ref="A2:Q25"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.75" style="1" customWidth="1"/>
-    <col min="4" max="7" width="8.875" style="1" customWidth="1"/>
-    <col min="8" max="11" width="11.875" style="1" customWidth="1"/>
-    <col min="12" max="15" width="11" style="2" customWidth="1"/>
-    <col min="16" max="16" width="37" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="7.75" style="1"/>
+    <col min="4" max="8" width="8.875" style="1" customWidth="1"/>
+    <col min="9" max="12" width="11.875" style="1" customWidth="1"/>
+    <col min="13" max="16" width="11" style="2" customWidth="1"/>
+    <col min="17" max="17" width="37" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -750,22 +753,22 @@
         <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>11</v>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>11</v>
@@ -776,11 +779,14 @@
       <c r="O2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="P2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -800,37 +806,40 @@
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
@@ -852,27 +861,30 @@
       <c r="G4" s="1">
         <v>0</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
         <v>29</v>
       </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
       <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
         <v>292</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>73</v>
       </c>
-      <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4"/>
+      <c r="Q4" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
@@ -894,27 +906,30 @@
       <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
         <v>29</v>
       </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
       <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
         <v>724</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>181</v>
       </c>
-      <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>24</v>
       </c>
@@ -936,23 +951,26 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
         <v>29</v>
       </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
       <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
         <v>660</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>165</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
@@ -974,23 +992,26 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
         <v>29</v>
       </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
       <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
         <v>880</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>220</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="Q7" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
@@ -1012,23 +1033,26 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>29</v>
       </c>
-      <c r="I8" s="3">
-        <v>1</v>
-      </c>
       <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3">
         <v>660</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>165</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -1050,23 +1074,26 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>29</v>
       </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
       <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
         <v>724</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>181</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="Q9" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>28</v>
       </c>
@@ -1088,23 +1115,26 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>29</v>
       </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
       <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
         <v>832</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>208</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="Q10" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>29</v>
       </c>
@@ -1126,23 +1156,26 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
         <v>29</v>
       </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
       <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
         <v>780</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>195</v>
       </c>
-      <c r="P11" s="5" t="s">
+      <c r="Q11" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
@@ -1164,23 +1197,26 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
         <v>29</v>
       </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
       <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
         <v>292</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>73</v>
       </c>
-      <c r="P12" s="5" t="s">
+      <c r="Q12" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>30</v>
       </c>
@@ -1202,23 +1238,26 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
         <v>29</v>
       </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
       <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
         <v>584</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>146</v>
       </c>
-      <c r="P13" s="5" t="s">
+      <c r="Q13" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>31</v>
       </c>
@@ -1240,23 +1279,26 @@
       <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>29</v>
       </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
       <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
         <v>404</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>101</v>
       </c>
-      <c r="P14" s="5" t="s">
+      <c r="Q14" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>32</v>
       </c>
@@ -1278,23 +1320,26 @@
       <c r="G15" s="1">
         <v>0</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>29</v>
       </c>
-      <c r="I15" s="1">
-        <v>1</v>
-      </c>
       <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
         <v>404</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>101</v>
       </c>
-      <c r="P15" s="5" t="s">
+      <c r="Q15" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
         <v>33</v>
       </c>
@@ -1316,23 +1361,26 @@
       <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
         <v>29</v>
       </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
       <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
         <v>832</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>208</v>
       </c>
-      <c r="P16" s="5" t="s">
+      <c r="Q16" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>34</v>
       </c>
@@ -1354,23 +1402,26 @@
       <c r="G17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>29</v>
       </c>
-      <c r="I17" s="1">
-        <v>1</v>
-      </c>
       <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
         <v>832</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>208</v>
       </c>
-      <c r="P17" s="5" t="s">
+      <c r="Q17" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>35</v>
       </c>
@@ -1392,23 +1443,26 @@
       <c r="G18" s="1">
         <v>0</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>29</v>
       </c>
-      <c r="I18" s="1">
-        <v>1</v>
-      </c>
       <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
         <v>584</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>146</v>
       </c>
-      <c r="P18" s="5" t="s">
+      <c r="Q18" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>36</v>
       </c>
@@ -1430,23 +1484,26 @@
       <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
         <v>29</v>
       </c>
-      <c r="I19" s="1">
-        <v>1</v>
-      </c>
       <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
         <v>500</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>125</v>
       </c>
-      <c r="P19" s="5" t="s">
+      <c r="Q19" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
@@ -1468,23 +1525,26 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>29</v>
       </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
       <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
         <v>832</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>208</v>
       </c>
-      <c r="P20" s="5" t="s">
+      <c r="Q20" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>74</v>
       </c>
@@ -1506,23 +1566,26 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>49</v>
       </c>
-      <c r="I21" s="1">
-        <v>1</v>
-      </c>
       <c r="J21" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>76</v>
       </c>
@@ -1545,22 +1608,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="J22" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>77</v>
       </c>
@@ -1580,25 +1646,28 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
       </c>
       <c r="J23" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>78</v>
       </c>
@@ -1618,22 +1687,25 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="J24" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>79</v>
       </c>
@@ -1656,18 +1728,21 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="J25" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="1" t="s">
         <v>83</v>
       </c>
     </row>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,200 +107,25 @@
     <t>sellPrice</t>
   </si>
   <si>
-    <t>卷心菜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>南瓜</t>
   </si>
   <si>
-    <t>黄瓜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玉米</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>番茄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>茄子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马铃薯</t>
-  </si>
-  <si>
     <t>胡萝卜</t>
   </si>
   <si>
-    <t>萝卜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大葱</t>
   </si>
   <si>
-    <t>紫甘蓝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>葡萄</t>
   </si>
   <si>
-    <t>蓝莓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辣椒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大蒜</t>
-  </si>
-  <si>
-    <t>草莓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>芜菁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各地普遍培植的常见叶菜。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能结出巨大果实的蔬菜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生吃和料理都是非常美味哦。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>富含糖分的粮食作物。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能够结出可爱的红色果实。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以制作成各种料理的万能蔬菜。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>富含能量的根茎作物。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>营养丰富的根。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>适合制作腌菜的作物。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辛辣与甘甜完美结合的蔬菜。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>万能的调味剂。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>好看又好吃的蔬菜。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏季代表性水果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>美味的灌木小浆果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重要的料理佐料。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>常见的调味佐料。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高营养价值的浆果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cabbage</t>
-  </si>
-  <si>
-    <t>pumpkin</t>
-  </si>
-  <si>
-    <t>cucumber</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>corn</t>
-  </si>
-  <si>
-    <t>tomato</t>
-  </si>
-  <si>
-    <t>eggplant</t>
-  </si>
-  <si>
-    <t>potato</t>
-  </si>
-  <si>
-    <t>carrot</t>
-  </si>
-  <si>
-    <t>turnip</t>
-  </si>
-  <si>
-    <t>daikon</t>
-  </si>
-  <si>
-    <t>leek</t>
-  </si>
-  <si>
-    <t>redCabbage</t>
-  </si>
-  <si>
-    <t>grape</t>
-  </si>
-  <si>
-    <t>blueberry</t>
-  </si>
-  <si>
-    <t>chilli</t>
-  </si>
-  <si>
-    <t>garlic</t>
-  </si>
-  <si>
-    <t>strawberry</t>
   </si>
   <si>
     <t>iconName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>玉米种子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玉米的种子。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>锄头</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -345,11 +170,160 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>corn_seed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>itemValue</t>
+  </si>
+  <si>
+    <t>芜菁</t>
+  </si>
+  <si>
+    <t>卷心菜</t>
+  </si>
+  <si>
+    <t>萝卜</t>
+  </si>
+  <si>
+    <t>紫甘蓝</t>
+  </si>
+  <si>
+    <t>黄瓜</t>
+  </si>
+  <si>
+    <t>西兰花</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>辣椒</t>
+  </si>
+  <si>
+    <t>奇异果</t>
+  </si>
+  <si>
+    <t>玉米</t>
+  </si>
+  <si>
+    <t>大麦</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>芦笋</t>
+  </si>
+  <si>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>蓝莓</t>
+  </si>
+  <si>
+    <t>红薯</t>
+  </si>
+  <si>
+    <t>甜菜</t>
+  </si>
+  <si>
+    <t>啤酒花</t>
+  </si>
+  <si>
+    <t>菠萝</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>豌豆</t>
+  </si>
+  <si>
+    <t>芜菁种子</t>
+  </si>
+  <si>
+    <t>卷心菜种子</t>
+  </si>
+  <si>
+    <t>大葱种子</t>
+  </si>
+  <si>
+    <t>萝卜种子</t>
+  </si>
+  <si>
+    <t>紫甘蓝种子</t>
+  </si>
+  <si>
+    <t>黄瓜种子</t>
+  </si>
+  <si>
+    <t>西兰花种子</t>
+  </si>
+  <si>
+    <t>番茄种子</t>
+  </si>
+  <si>
+    <t>胡萝卜种子</t>
+  </si>
+  <si>
+    <t>西瓜种子</t>
+  </si>
+  <si>
+    <t>辣椒种子</t>
+  </si>
+  <si>
+    <t>奇异果种子</t>
+  </si>
+  <si>
+    <t>茄子种子</t>
+  </si>
+  <si>
+    <t>豌豆种子</t>
+  </si>
+  <si>
+    <t>土豆种子</t>
+  </si>
+  <si>
+    <t>大蒜种子</t>
+  </si>
+  <si>
+    <t>芦笋种子</t>
+  </si>
+  <si>
+    <t>南瓜种子</t>
+  </si>
+  <si>
+    <t>玉米种子</t>
+  </si>
+  <si>
+    <t>大麦种子</t>
+  </si>
+  <si>
+    <t>啤酒花种子</t>
+  </si>
+  <si>
+    <t>葡萄种子</t>
+  </si>
+  <si>
+    <t>菠萝种子</t>
+  </si>
+  <si>
+    <t>咖啡种子</t>
+  </si>
+  <si>
+    <t>草莓种子</t>
+  </si>
+  <si>
+    <t>蓝莓种子</t>
+  </si>
+  <si>
+    <t>红薯种子</t>
+  </si>
+  <si>
+    <t>甜菜种子</t>
   </si>
 </sst>
 </file>
@@ -719,7 +693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q25"/>
+  <dimension ref="A2:Q63"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -794,7 +768,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>13</v>
@@ -806,7 +780,7 @@
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
@@ -841,13 +815,14 @@
     </row>
     <row r="4" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3">
         <v>1001</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>56</v>
+      <c r="C4" s="3" t="str">
+        <f>A4&amp;"_01"</f>
+        <v>芜菁_01</v>
       </c>
       <c r="D4" s="1">
         <v>5</v>
@@ -870,29 +845,28 @@
       <c r="J4" s="3">
         <v>1</v>
       </c>
-      <c r="K4" s="3">
-        <v>292</v>
-      </c>
-      <c r="L4" s="3">
-        <v>73</v>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>100</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3">
         <v>1002</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>57</v>
+      <c r="C5" s="3" t="str">
+        <f t="shared" ref="C5:C31" si="0">A5&amp;"_01"</f>
+        <v>卷心菜_01</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
@@ -915,19 +889,17 @@
       <c r="J5" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="3">
-        <v>724</v>
-      </c>
-      <c r="L5" s="3">
-        <v>181</v>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
+        <v>100</v>
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
-      <c r="Q5" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
@@ -936,8 +908,9 @@
       <c r="B6" s="3">
         <v>1003</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>58</v>
+      <c r="C6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>大葱_01</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -960,25 +933,24 @@
       <c r="J6" s="3">
         <v>1</v>
       </c>
-      <c r="K6" s="3">
-        <v>660</v>
-      </c>
-      <c r="L6" s="3">
-        <v>165</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3">
         <v>1004</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>59</v>
+      <c r="C7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>萝卜_01</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -1001,25 +973,24 @@
       <c r="J7" s="3">
         <v>1</v>
       </c>
-      <c r="K7" s="3">
-        <v>880</v>
-      </c>
-      <c r="L7" s="3">
-        <v>220</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>42</v>
-      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3">
         <v>1005</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>60</v>
+      <c r="C8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>紫甘蓝_01</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
@@ -1042,25 +1013,24 @@
       <c r="J8" s="3">
         <v>1</v>
       </c>
-      <c r="K8" s="3">
-        <v>660</v>
-      </c>
-      <c r="L8" s="3">
-        <v>165</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3">
         <v>1006</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>61</v>
+      <c r="C9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>黄瓜_01</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -1084,24 +1054,23 @@
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>724</v>
+        <v>100</v>
       </c>
       <c r="L9" s="1">
-        <v>181</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>44</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q9" s="5"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B10" s="3">
         <v>1007</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>62</v>
+      <c r="C10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>西兰花_01</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -1125,24 +1094,23 @@
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>832</v>
+        <v>100</v>
       </c>
       <c r="L10" s="1">
-        <v>208</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3">
         <v>1008</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>63</v>
+      <c r="C11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>番茄_01</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -1166,24 +1134,23 @@
         <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>780</v>
+        <v>100</v>
       </c>
       <c r="L11" s="1">
-        <v>195</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3">
         <v>1009</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>64</v>
+      <c r="C12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>胡萝卜_01</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -1207,24 +1174,23 @@
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>292</v>
+        <v>100</v>
       </c>
       <c r="L12" s="1">
-        <v>73</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B13" s="3">
         <v>1010</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>65</v>
+      <c r="C13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>西瓜_01</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
@@ -1248,24 +1214,23 @@
         <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>584</v>
+        <v>100</v>
       </c>
       <c r="L13" s="1">
-        <v>146</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q13" s="5"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3">
         <v>1011</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>66</v>
+      <c r="C14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>辣椒_01</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
@@ -1289,24 +1254,23 @@
         <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>404</v>
+        <v>100</v>
       </c>
       <c r="L14" s="1">
-        <v>101</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q14" s="5"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B15" s="3">
         <v>1012</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>67</v>
+      <c r="C15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>奇异果_01</v>
       </c>
       <c r="D15" s="1">
         <v>5</v>
@@ -1330,24 +1294,23 @@
         <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>404</v>
+        <v>100</v>
       </c>
       <c r="L15" s="1">
-        <v>101</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>50</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B16" s="3">
         <v>1013</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>68</v>
+      <c r="C16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>茄子_01</v>
       </c>
       <c r="D16" s="1">
         <v>5</v>
@@ -1371,24 +1334,23 @@
         <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>832</v>
+        <v>100</v>
       </c>
       <c r="L16" s="1">
-        <v>208</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q16" s="5"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B17" s="3">
         <v>1014</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>69</v>
+      <c r="C17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>豌豆_01</v>
       </c>
       <c r="D17" s="1">
         <v>5</v>
@@ -1412,24 +1374,23 @@
         <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>832</v>
+        <v>100</v>
       </c>
       <c r="L17" s="1">
-        <v>208</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>52</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q17" s="5"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B18" s="3">
         <v>1015</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>70</v>
+      <c r="C18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>土豆_01</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -1453,24 +1414,23 @@
         <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>584</v>
+        <v>100</v>
       </c>
       <c r="L18" s="1">
-        <v>146</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>53</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q18" s="5"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B19" s="3">
         <v>1016</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>71</v>
+      <c r="C19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>大蒜_01</v>
       </c>
       <c r="D19" s="1">
         <v>5</v>
@@ -1494,24 +1454,23 @@
         <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L19" s="1">
-        <v>125</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q19" s="5"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3">
         <v>1017</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>72</v>
+      <c r="C20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>芦笋_01</v>
       </c>
       <c r="D20" s="1">
         <v>5</v>
@@ -1535,215 +1494,1693 @@
         <v>1</v>
       </c>
       <c r="K20" s="1">
-        <v>832</v>
+        <v>100</v>
       </c>
       <c r="L20" s="1">
-        <v>208</v>
-      </c>
-      <c r="Q20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1018</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>南瓜_01</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>29</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1019</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>玉米_01</v>
+      </c>
+      <c r="D22" s="1">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>29</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1020</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>大麦_01</v>
+      </c>
+      <c r="D23" s="1">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>29</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1021</v>
+      </c>
+      <c r="C24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>啤酒花_01</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>29</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1022</v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>葡萄_01</v>
+      </c>
+      <c r="D25" s="1">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>29</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1023</v>
+      </c>
+      <c r="C26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>菠萝_01</v>
+      </c>
+      <c r="D26" s="1">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>29</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1024</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>咖啡_01</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>29</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1025</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>草莓_01</v>
+      </c>
+      <c r="D28" s="1">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>29</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
+      <c r="B29" s="3">
+        <v>1026</v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>蓝莓_01</v>
+      </c>
+      <c r="D29" s="1">
+        <v>5</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>29</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1027</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>红薯_01</v>
+      </c>
+      <c r="D30" s="1">
+        <v>5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>29</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1028</v>
+      </c>
+      <c r="C31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>甜菜_01</v>
+      </c>
+      <c r="D31" s="1">
+        <v>5</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>29</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="3">
+        <f>B4+100</f>
+        <v>1101</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8001</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>29</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="3">
+        <f t="shared" ref="B33:B59" si="1">B5+100</f>
+        <v>1102</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8002</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>29</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="3">
+        <f t="shared" si="1"/>
+        <v>1103</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8003</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>29</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="3">
+        <f t="shared" si="1"/>
+        <v>1104</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8004</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>29</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="3">
+        <f t="shared" si="1"/>
+        <v>1105</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1">
+        <v>8005</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <v>29</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="3">
+        <f t="shared" si="1"/>
+        <v>1106</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8006</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>29</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="3">
+        <f t="shared" si="1"/>
+        <v>1107</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>8007</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>29</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="3">
+        <f t="shared" si="1"/>
+        <v>1108</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>8008</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>29</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="3">
+        <f t="shared" si="1"/>
+        <v>1109</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8009</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>29</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="3">
+        <f t="shared" si="1"/>
+        <v>1110</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>8010</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>29</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="3">
+        <f t="shared" si="1"/>
+        <v>1111</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>8011</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>29</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="B43" s="3">
+        <f t="shared" si="1"/>
+        <v>1112</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8012</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>29</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="3">
+        <f t="shared" si="1"/>
+        <v>1113</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>8013</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>29</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="3">
+        <f t="shared" si="1"/>
+        <v>1114</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>8014</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>29</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100</v>
+      </c>
+      <c r="L45" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="3">
+        <f t="shared" si="1"/>
+        <v>1115</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
+        <v>8015</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <v>29</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>100</v>
+      </c>
+      <c r="L46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="3">
+        <f t="shared" si="1"/>
+        <v>1116</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>8016</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>29</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+      <c r="L47" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="3">
+        <f t="shared" si="1"/>
+        <v>1117</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>8017</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>29</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+      <c r="L48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="3">
+        <f t="shared" si="1"/>
+        <v>1118</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
+        <v>8018</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>29</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="3">
+        <f t="shared" si="1"/>
+        <v>1119</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>8019</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <v>29</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A51" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="3">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
+        <v>8020</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <v>29</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+      <c r="L51" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" s="3">
+        <f t="shared" si="1"/>
+        <v>1121</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>8021</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>29</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>100</v>
+      </c>
+      <c r="L52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="3">
+        <f t="shared" si="1"/>
+        <v>1122</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
+        <v>8022</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <v>29</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1">
+        <v>100</v>
+      </c>
+      <c r="L53" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="3">
+        <f t="shared" si="1"/>
+        <v>1123</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <v>8023</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>29</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>100</v>
+      </c>
+      <c r="L54" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="3">
+        <f t="shared" si="1"/>
+        <v>1124</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>8024</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
+        <v>29</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>100</v>
+      </c>
+      <c r="L55" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>8000</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>49</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="B56" s="3">
+        <f t="shared" si="1"/>
+        <v>1125</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
+        <v>8025</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <v>29</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="1">
+        <v>100</v>
+      </c>
+      <c r="L56" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="3">
+        <f t="shared" si="1"/>
+        <v>1126</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>8026</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>29</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="1">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" s="3">
+        <f t="shared" si="1"/>
+        <v>1127</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
+        <v>8027</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>29</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" s="3">
+        <f t="shared" si="1"/>
+        <v>1128</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
+        <v>8028</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>29</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" s="1">
         <v>2000</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="1">
+      <c r="C60" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="1">
         <v>6</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="1">
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="1">
+        <v>100</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="1">
         <v>2001</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="C61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="1">
         <v>6</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-      <c r="L23" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="1">
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="1">
+        <v>100</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" s="1">
         <v>2002</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D62" s="1">
         <v>6</v>
       </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="1">
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="1">
+        <v>100</v>
+      </c>
+      <c r="L62" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="1">
         <v>2003</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="1">
+      <c r="C63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="1">
         <v>6</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>83</v>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="1">
+        <v>100</v>
+      </c>
+      <c r="L63" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="130">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -324,6 +324,161 @@
   </si>
   <si>
     <t>甜菜种子</t>
+  </si>
+  <si>
+    <t>纺织机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锻造炉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷餐台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酿造桶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绘写台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双人床</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物箱(木)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物箱(银)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物箱(金)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服饰架</t>
+  </si>
+  <si>
+    <t>服饰架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤炉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炖煮锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烘烤炉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作衣物，布匹的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作武器的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来烘烤食物的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作炖煮食物的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作冷餐的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来酿造酒水饮料的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来绘写卷轴的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来保存新鲜物品的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木质的储物箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银质的储物箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金质的储物箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用的柜台，可放置一般商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置武器的柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置服饰的架子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柔软舒适的座位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供给夫妇两人休息的床</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -693,7 +848,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q63"/>
+  <dimension ref="A2:Q79"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -3181,6 +3336,662 @@
       </c>
       <c r="Q63" s="1" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2100</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="1">
+        <v>10</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2100</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>1</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="1">
+        <v>100</v>
+      </c>
+      <c r="L64" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="1">
+        <v>2101</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" s="1">
+        <v>10</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2101</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="1">
+        <v>100</v>
+      </c>
+      <c r="L65" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A66" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2102</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="1">
+        <v>10</v>
+      </c>
+      <c r="E66" s="1">
+        <v>2102</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1">
+        <v>100</v>
+      </c>
+      <c r="L66" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A67" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2103</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" s="1">
+        <v>10</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2103</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="1">
+        <v>100</v>
+      </c>
+      <c r="L67" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2104</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" s="1">
+        <v>10</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2104</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="1">
+        <v>100</v>
+      </c>
+      <c r="L68" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A69" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2105</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="1">
+        <v>10</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2105</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+      <c r="K69" s="1">
+        <v>100</v>
+      </c>
+      <c r="L69" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A70" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2106</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D70" s="1">
+        <v>10</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2106</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>100</v>
+      </c>
+      <c r="L70" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2107</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71" s="1">
+        <v>10</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2107</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1</v>
+      </c>
+      <c r="K71" s="1">
+        <v>100</v>
+      </c>
+      <c r="L71" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2108</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D72" s="1">
+        <v>10</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2108</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1</v>
+      </c>
+      <c r="J72" s="1">
+        <v>1</v>
+      </c>
+      <c r="K72" s="1">
+        <v>100</v>
+      </c>
+      <c r="L72" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="1">
+        <v>2109</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="1">
+        <v>10</v>
+      </c>
+      <c r="E73" s="1">
+        <v>2109</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1</v>
+      </c>
+      <c r="K73" s="1">
+        <v>100</v>
+      </c>
+      <c r="L73" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A74" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2110</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D74" s="1">
+        <v>10</v>
+      </c>
+      <c r="E74" s="1">
+        <v>2110</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1">
+        <v>1</v>
+      </c>
+      <c r="K74" s="1">
+        <v>100</v>
+      </c>
+      <c r="L74" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A75" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" s="1">
+        <v>2111</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="1">
+        <v>10</v>
+      </c>
+      <c r="E75" s="1">
+        <v>2111</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1</v>
+      </c>
+      <c r="J75" s="1">
+        <v>1</v>
+      </c>
+      <c r="K75" s="1">
+        <v>100</v>
+      </c>
+      <c r="L75" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A76" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2112</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="1">
+        <v>10</v>
+      </c>
+      <c r="E76" s="1">
+        <v>2112</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1</v>
+      </c>
+      <c r="K76" s="1">
+        <v>100</v>
+      </c>
+      <c r="L76" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B77" s="1">
+        <v>2113</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D77" s="1">
+        <v>10</v>
+      </c>
+      <c r="E77" s="1">
+        <v>2113</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>1</v>
+      </c>
+      <c r="J77" s="1">
+        <v>1</v>
+      </c>
+      <c r="K77" s="1">
+        <v>100</v>
+      </c>
+      <c r="L77" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A78" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2200</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D78" s="1">
+        <v>10</v>
+      </c>
+      <c r="E78" s="1">
+        <v>2200</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+      <c r="I78" s="1">
+        <v>1</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1</v>
+      </c>
+      <c r="K78" s="1">
+        <v>100</v>
+      </c>
+      <c r="L78" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A79" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B79" s="1">
+        <v>2201</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D79" s="1">
+        <v>10</v>
+      </c>
+      <c r="E79" s="1">
+        <v>2201</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1</v>
+      </c>
+      <c r="K79" s="1">
+        <v>100</v>
+      </c>
+      <c r="L79" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -22,8 +22,46 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>flyer</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  Default=-1, 种子 = 0, 武器 = 1, 防具 = 2,
+ 食材 = 3,食物 = 4, 收集物 = 5,  工具=6,
+ 家具 = 10, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -478,6 +516,30 @@
   </si>
   <si>
     <t>提供给夫妇两人休息的床</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未知的物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>????????</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失败的料理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看起来不像是能吃的样子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>food0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,7 +547,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,6 +562,21 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -846,9 +923,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q79"/>
+  <dimension ref="A2:Q81"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -968,1181 +1045,1185 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="1">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B6" s="3">
         <v>1001</v>
       </c>
-      <c r="C4" s="3" t="str">
-        <f>A4&amp;"_01"</f>
+      <c r="C6" s="3" t="str">
+        <f>A6&amp;"_01"</f>
         <v>芜菁_01</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>29</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>100</v>
-      </c>
-      <c r="L4" s="1">
-        <v>100</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="5" t="s">
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>29</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>100</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B7" s="3">
         <v>1002</v>
       </c>
-      <c r="C5" s="3" t="str">
-        <f t="shared" ref="C5:C31" si="0">A5&amp;"_01"</f>
+      <c r="C7" s="3" t="str">
+        <f t="shared" ref="C7:C33" si="0">A7&amp;"_01"</f>
         <v>卷心菜_01</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D7" s="1">
         <v>5</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>29</v>
-      </c>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>100</v>
-      </c>
-      <c r="L5" s="1">
-        <v>100</v>
-      </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A6" s="5" t="s">
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>29</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B8" s="3">
         <v>1003</v>
       </c>
-      <c r="C6" s="3" t="str">
+      <c r="C8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大葱_01</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D8" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>29</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>100</v>
-      </c>
-      <c r="L6" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="5"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A7" s="5" t="s">
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>29</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B9" s="3">
         <v>1004</v>
       </c>
-      <c r="C7" s="3" t="str">
+      <c r="C9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>萝卜_01</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D9" s="1">
         <v>5</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>29</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-      <c r="L7" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A8" s="5" t="s">
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>29</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B10" s="3">
         <v>1005</v>
       </c>
-      <c r="C8" s="3" t="str">
+      <c r="C10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>紫甘蓝_01</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D10" s="1">
         <v>5</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>29</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>100</v>
-      </c>
-      <c r="L8" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A9" s="5" t="s">
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>29</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B11" s="3">
         <v>1006</v>
       </c>
-      <c r="C9" s="3" t="str">
+      <c r="C11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>黄瓜_01</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>29</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>100</v>
-      </c>
-      <c r="L9" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A10" s="5" t="s">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>29</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B12" s="3">
         <v>1007</v>
       </c>
-      <c r="C10" s="3" t="str">
+      <c r="C12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西兰花_01</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>29</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>100</v>
-      </c>
-      <c r="L10" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A11" s="5" t="s">
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>29</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B13" s="3">
         <v>1008</v>
       </c>
-      <c r="C11" s="3" t="str">
+      <c r="C13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>番茄_01</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D13" s="1">
         <v>5</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>29</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>100</v>
-      </c>
-      <c r="L11" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B14" s="3">
         <v>1009</v>
       </c>
-      <c r="C12" s="3" t="str">
+      <c r="C14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>胡萝卜_01</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D14" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>29</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>100</v>
-      </c>
-      <c r="L12" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>29</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B15" s="3">
         <v>1010</v>
       </c>
-      <c r="C13" s="3" t="str">
+      <c r="C15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西瓜_01</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D15" s="1">
         <v>5</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>29</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>100</v>
-      </c>
-      <c r="L13" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>29</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B16" s="3">
         <v>1011</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>辣椒_01</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D16" s="1">
         <v>5</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>29</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>100</v>
-      </c>
-      <c r="L14" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>29</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B17" s="3">
         <v>1012</v>
       </c>
-      <c r="C15" s="3" t="str">
+      <c r="C17" s="3" t="str">
         <f t="shared" si="0"/>
         <v>奇异果_01</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>29</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-      <c r="L15" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>29</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B18" s="3">
         <v>1013</v>
       </c>
-      <c r="C16" s="3" t="str">
+      <c r="C18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>茄子_01</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D18" s="1">
         <v>5</v>
       </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>29</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-      <c r="L16" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A17" s="5" t="s">
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>29</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B19" s="3">
         <v>1014</v>
       </c>
-      <c r="C17" s="3" t="str">
+      <c r="C19" s="3" t="str">
         <f t="shared" si="0"/>
         <v>豌豆_01</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D19" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>29</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-      <c r="L17" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>29</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B20" s="3">
         <v>1015</v>
       </c>
-      <c r="C18" s="3" t="str">
+      <c r="C20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>土豆_01</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D20" s="1">
         <v>5</v>
       </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>29</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
-      </c>
-      <c r="L18" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A19" s="5" t="s">
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>29</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B21" s="3">
         <v>1016</v>
       </c>
-      <c r="C19" s="3" t="str">
+      <c r="C21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大蒜_01</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D21" s="1">
         <v>5</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>29</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>29</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B22" s="3">
         <v>1017</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>芦笋_01</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>29</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>29</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B23" s="3">
         <v>1018</v>
       </c>
-      <c r="C21" s="3" t="str">
+      <c r="C23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>南瓜_01</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D23" s="1">
         <v>5</v>
       </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>29</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>29</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B24" s="3">
         <v>1019</v>
       </c>
-      <c r="C22" s="3" t="str">
+      <c r="C24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>玉米_01</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>29</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="s">
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>29</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B25" s="3">
         <v>1020</v>
       </c>
-      <c r="C23" s="3" t="str">
+      <c r="C25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大麦_01</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D25" s="1">
         <v>5</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>29</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-      <c r="L23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>29</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B26" s="3">
         <v>1021</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C26" s="3" t="str">
         <f t="shared" si="0"/>
         <v>啤酒花_01</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D26" s="1">
         <v>5</v>
       </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>29</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A25" s="5" t="s">
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>29</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B27" s="3">
         <v>1022</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>葡萄_01</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D27" s="1">
         <v>5</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <v>29</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>29</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B28" s="3">
         <v>1023</v>
       </c>
-      <c r="C26" s="3" t="str">
+      <c r="C28" s="3" t="str">
         <f t="shared" si="0"/>
         <v>菠萝_01</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D28" s="1">
         <v>5</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>29</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>100</v>
-      </c>
-      <c r="L26" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A27" s="5" t="s">
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>29</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B29" s="3">
         <v>1024</v>
       </c>
-      <c r="C27" s="3" t="str">
+      <c r="C29" s="3" t="str">
         <f t="shared" si="0"/>
         <v>咖啡_01</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D29" s="1">
         <v>5</v>
       </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>29</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>100</v>
-      </c>
-      <c r="L27" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>29</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B30" s="3">
         <v>1025</v>
       </c>
-      <c r="C28" s="3" t="str">
+      <c r="C30" s="3" t="str">
         <f t="shared" si="0"/>
         <v>草莓_01</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D30" s="1">
         <v>5</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <v>29</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>100</v>
-      </c>
-      <c r="L28" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>29</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B31" s="3">
         <v>1026</v>
       </c>
-      <c r="C29" s="3" t="str">
+      <c r="C31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>蓝莓_01</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D31" s="1">
         <v>5</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>29</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>100</v>
-      </c>
-      <c r="L29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>29</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B32" s="3">
         <v>1027</v>
       </c>
-      <c r="C30" s="3" t="str">
+      <c r="C32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>红薯_01</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D32" s="1">
         <v>5</v>
       </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
-        <v>29</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>100</v>
-      </c>
-      <c r="L30" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>29</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B33" s="3">
         <v>1028</v>
       </c>
-      <c r="C31" s="3" t="str">
+      <c r="C33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>甜菜_01</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D33" s="1">
         <v>5</v>
       </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
-        <v>29</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>100</v>
-      </c>
-      <c r="L31" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="3">
-        <f>B4+100</f>
-        <v>1101</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>8001</v>
-      </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>29</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>100</v>
-      </c>
-      <c r="L32" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A33" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="3">
-        <f t="shared" ref="B33:B59" si="1">B5+100</f>
-        <v>1102</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
       <c r="E33" s="1">
-        <v>8002</v>
+        <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -2165,1086 +2246,1085 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="3">
+        <f>B6+100</f>
+        <v>1101</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8001</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>29</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="3">
+        <f t="shared" ref="B35:B61" si="1">B7+100</f>
+        <v>1102</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8002</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>29</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B36" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="1">
-        <v>0</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1">
         <v>8003</v>
       </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
-        <v>29</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>100</v>
-      </c>
-      <c r="L34" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A35" s="5" t="s">
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <v>29</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B37" s="3">
         <f t="shared" si="1"/>
         <v>1104</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
         <v>8004</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>29</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>100</v>
-      </c>
-      <c r="L35" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A36" s="5" t="s">
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>29</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B38" s="3">
         <f t="shared" si="1"/>
         <v>1105</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
         <v>8005</v>
       </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3">
-        <v>29</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>100</v>
-      </c>
-      <c r="L36" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A37" s="5" t="s">
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>29</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B39" s="3">
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
         <v>8006</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="3">
-        <v>29</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>100</v>
-      </c>
-      <c r="L37" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A38" s="5" t="s">
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>29</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B40" s="3">
         <f t="shared" si="1"/>
         <v>1107</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
         <v>8007</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3">
-        <v>29</v>
-      </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>100</v>
-      </c>
-      <c r="L38" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A39" s="5" t="s">
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>29</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B41" s="3">
         <f t="shared" si="1"/>
         <v>1108</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
         <v>8008</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3">
-        <v>29</v>
-      </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>100</v>
-      </c>
-      <c r="L39" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A40" s="5" t="s">
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>29</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B42" s="3">
         <f t="shared" si="1"/>
         <v>1109</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
         <v>8009</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
-        <v>29</v>
-      </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>100</v>
-      </c>
-      <c r="L40" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A41" s="5" t="s">
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>29</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B43" s="3">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
         <v>8010</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>29</v>
-      </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A42" s="5" t="s">
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>29</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B44" s="3">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="1">
-        <v>0</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
         <v>8011</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>29</v>
-      </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>100</v>
-      </c>
-      <c r="L42" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A43" s="5" t="s">
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>29</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B45" s="3">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D43" s="1">
-        <v>0</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
         <v>8012</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>29</v>
-      </c>
-      <c r="J43" s="1">
-        <v>1</v>
-      </c>
-      <c r="K43" s="1">
-        <v>100</v>
-      </c>
-      <c r="L43" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A44" s="5" t="s">
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>29</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100</v>
+      </c>
+      <c r="L45" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B46" s="3">
         <f t="shared" si="1"/>
         <v>1113</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
         <v>8013</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>29</v>
-      </c>
-      <c r="J44" s="1">
-        <v>1</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A45" s="5" t="s">
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <v>29</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>100</v>
+      </c>
+      <c r="L46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B47" s="3">
         <f t="shared" si="1"/>
         <v>1114</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
         <v>8014</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>29</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1">
-        <v>100</v>
-      </c>
-      <c r="L45" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A46" s="5" t="s">
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>29</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+      <c r="L47" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B48" s="3">
         <f t="shared" si="1"/>
         <v>1115</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="1">
-        <v>0</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
         <v>8015</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
-        <v>29</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1">
-        <v>100</v>
-      </c>
-      <c r="L46" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A47" s="5" t="s">
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>29</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+      <c r="L48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B49" s="3">
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
         <v>8016</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>29</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>100</v>
-      </c>
-      <c r="L47" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A48" s="5" t="s">
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>29</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B50" s="3">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
         <v>8017</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>29</v>
-      </c>
-      <c r="J48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>100</v>
-      </c>
-      <c r="L48" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A49" s="5" t="s">
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <v>29</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A51" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B51" s="3">
         <f t="shared" si="1"/>
         <v>1118</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
         <v>8018</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>29</v>
-      </c>
-      <c r="J49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1">
-        <v>100</v>
-      </c>
-      <c r="L49" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A50" s="5" t="s">
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <v>29</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+      <c r="L51" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B52" s="3">
         <f t="shared" si="1"/>
         <v>1119</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
         <v>8019</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3">
-        <v>29</v>
-      </c>
-      <c r="J50" s="1">
-        <v>1</v>
-      </c>
-      <c r="K50" s="1">
-        <v>100</v>
-      </c>
-      <c r="L50" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A51" s="5" t="s">
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>29</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>100</v>
+      </c>
+      <c r="L52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B53" s="3">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
         <v>8020</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3">
-        <v>29</v>
-      </c>
-      <c r="J51" s="1">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>100</v>
-      </c>
-      <c r="L51" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A52" s="5" t="s">
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <v>29</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1">
+        <v>100</v>
+      </c>
+      <c r="L53" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B54" s="3">
         <f t="shared" si="1"/>
         <v>1121</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
         <v>8021</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>29</v>
-      </c>
-      <c r="J52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>100</v>
-      </c>
-      <c r="L52" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A53" s="5" t="s">
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>29</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>100</v>
+      </c>
+      <c r="L54" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B55" s="3">
         <f t="shared" si="1"/>
         <v>1122</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
         <v>8022</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3">
-        <v>29</v>
-      </c>
-      <c r="J53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1">
-        <v>100</v>
-      </c>
-      <c r="L53" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A54" s="5" t="s">
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
+        <v>29</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>100</v>
+      </c>
+      <c r="L55" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B56" s="3">
         <f t="shared" si="1"/>
         <v>1123</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
         <v>8023</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3">
-        <v>29</v>
-      </c>
-      <c r="J54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>100</v>
-      </c>
-      <c r="L54" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A55" s="5" t="s">
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <v>29</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="1">
+        <v>100</v>
+      </c>
+      <c r="L56" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B57" s="3">
         <f t="shared" si="1"/>
         <v>1124</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
         <v>8024</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3">
-        <v>29</v>
-      </c>
-      <c r="J55" s="1">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1">
-        <v>100</v>
-      </c>
-      <c r="L55" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A56" s="5" t="s">
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>29</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="1">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B58" s="3">
         <f t="shared" si="1"/>
         <v>1125</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
         <v>8025</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="3">
-        <v>29</v>
-      </c>
-      <c r="J56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>100</v>
-      </c>
-      <c r="L56" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A57" s="5" t="s">
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>29</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B59" s="3">
         <f t="shared" si="1"/>
         <v>1126</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
         <v>8026</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>29</v>
-      </c>
-      <c r="J57" s="1">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1">
-        <v>100</v>
-      </c>
-      <c r="L57" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A58" s="5" t="s">
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>29</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B60" s="3">
         <f t="shared" si="1"/>
         <v>1127</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
         <v>8027</v>
       </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>29</v>
-      </c>
-      <c r="J58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>100</v>
-      </c>
-      <c r="L58" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A59" s="5" t="s">
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>29</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="1">
+        <v>100</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A61" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B61" s="3">
         <f t="shared" si="1"/>
         <v>1128</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
         <v>8028</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>29</v>
-      </c>
-      <c r="J59" s="1">
-        <v>1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>100</v>
-      </c>
-      <c r="L59" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A60" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D60" s="1">
-        <v>6</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1</v>
-      </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
-        <v>1</v>
-      </c>
-      <c r="J60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1">
-        <v>100</v>
-      </c>
-      <c r="L60" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2001</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D61" s="1">
-        <v>6</v>
-      </c>
-      <c r="E61" s="1">
-        <v>1</v>
-      </c>
       <c r="F61" s="1">
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
       </c>
-      <c r="I61" s="1">
-        <v>1</v>
+      <c r="I61" s="3">
+        <v>29</v>
       </c>
       <c r="J61" s="1">
         <v>1</v>
@@ -3254,17 +3334,17 @@
       </c>
       <c r="L61" s="1">
         <v>100</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" s="1">
-        <v>2002</v>
+        <v>2000</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D62" s="1">
         <v>6</v>
@@ -3294,18 +3374,18 @@
         <v>100</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B63" s="1">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D63" s="1">
         <v>6</v>
@@ -3317,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -3335,24 +3415,21 @@
         <v>100</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="B64" s="1">
-        <v>2100</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>91</v>
+        <v>2002</v>
       </c>
       <c r="D64" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E64" s="1">
-        <v>2100</v>
+        <v>1</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3376,24 +3453,24 @@
         <v>100</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B65" s="1">
-        <v>2101</v>
+        <v>2003</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="D65" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E65" s="1">
-        <v>2101</v>
+        <v>1</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3417,24 +3494,24 @@
         <v>100</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B66" s="1">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D66" s="1">
         <v>10</v>
       </c>
       <c r="E66" s="1">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3458,24 +3535,24 @@
         <v>100</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B67" s="1">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="D67" s="1">
         <v>10</v>
       </c>
       <c r="E67" s="1">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3499,24 +3576,24 @@
         <v>100</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="B68" s="1">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D68" s="1">
         <v>10</v>
       </c>
       <c r="E68" s="1">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3540,24 +3617,24 @@
         <v>100</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B69" s="1">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D69" s="1">
         <v>10</v>
       </c>
       <c r="E69" s="1">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3581,24 +3658,24 @@
         <v>100</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B70" s="1">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D70" s="1">
         <v>10</v>
       </c>
       <c r="E70" s="1">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3622,24 +3699,24 @@
         <v>100</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B71" s="1">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D71" s="1">
         <v>10</v>
       </c>
       <c r="E71" s="1">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3663,24 +3740,24 @@
         <v>100</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B72" s="1">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D72" s="1">
         <v>10</v>
       </c>
       <c r="E72" s="1">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3704,24 +3781,24 @@
         <v>100</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B73" s="1">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D73" s="1">
         <v>10</v>
       </c>
       <c r="E73" s="1">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -3745,24 +3822,24 @@
         <v>100</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B74" s="1">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D74" s="1">
         <v>10</v>
       </c>
       <c r="E74" s="1">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3786,24 +3863,24 @@
         <v>100</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B75" s="1">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D75" s="1">
         <v>10</v>
       </c>
       <c r="E75" s="1">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3827,24 +3904,24 @@
         <v>100</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B76" s="1">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76" s="1">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -3868,24 +3945,24 @@
         <v>100</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B77" s="1">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D77" s="1">
         <v>10</v>
       </c>
       <c r="E77" s="1">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -3909,24 +3986,24 @@
         <v>100</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B78" s="1">
-        <v>2200</v>
+        <v>2112</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D78" s="1">
         <v>10</v>
       </c>
       <c r="E78" s="1">
-        <v>2200</v>
+        <v>2112</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -3950,47 +4027,129 @@
         <v>100</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B79" s="1">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D79" s="1">
         <v>10</v>
       </c>
       <c r="E79" s="1">
+        <v>2113</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1</v>
+      </c>
+      <c r="K79" s="1">
+        <v>100</v>
+      </c>
+      <c r="L79" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A80" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2200</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" s="1">
+        <v>10</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2200</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1">
+        <v>1</v>
+      </c>
+      <c r="J80" s="1">
+        <v>1</v>
+      </c>
+      <c r="K80" s="1">
+        <v>100</v>
+      </c>
+      <c r="L80" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A81" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" s="1">
         <v>2201</v>
       </c>
-      <c r="F79" s="1">
-        <v>0</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0</v>
-      </c>
-      <c r="I79" s="1">
-        <v>1</v>
-      </c>
-      <c r="J79" s="1">
-        <v>1</v>
-      </c>
-      <c r="K79" s="1">
-        <v>100</v>
-      </c>
-      <c r="L79" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q79" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D81" s="1">
+        <v>10</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2201</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1</v>
+      </c>
+      <c r="K81" s="1">
+        <v>100</v>
+      </c>
+      <c r="L81" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="1" t="s">
         <v>129</v>
       </c>
     </row>
@@ -4003,6 +4162,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -41,7 +41,7 @@
           </rPr>
           <t xml:space="preserve">  Default=-1, 种子 = 0, 武器 = 1, 防具 = 2,
  食材 = 3,食物 = 4, 收集物 = 5,  工具=6,
- 家具 = 10, </t>
+ 家具 = 10, 动物=11</t>
         </r>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="139">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -540,6 +540,18 @@
   </si>
   <si>
     <t>food0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会生产鸡蛋的动物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -925,7 +937,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q81"/>
+  <dimension ref="A2:Q82"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -4151,6 +4163,47 @@
       </c>
       <c r="Q81" s="1" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A82" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D82" s="1">
+        <v>11</v>
+      </c>
+      <c r="E82" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1">
+        <v>1</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+      <c r="K82" s="1">
+        <v>100</v>
+      </c>
+      <c r="L82" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q82" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="141">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -552,6 +552,14 @@
   </si>
   <si>
     <t>会生产鸡蛋的动物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未成熟的植物制成的鲜嫩可口的饲料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -937,7 +945,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q82"/>
+  <dimension ref="A2:Q83"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -1139,25 +1147,24 @@
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1001</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>A6&amp;"_01"</f>
-        <v>芜菁_01</v>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="1">
+        <v>100</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1165,34 +1172,32 @@
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="3">
-        <v>29</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
+      <c r="I6" s="1">
+        <v>29</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>100</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C7" s="3" t="str">
-        <f t="shared" ref="C7:C33" si="0">A7&amp;"_01"</f>
-        <v>卷心菜_01</v>
+        <f>A7&amp;"_01"</f>
+        <v>芜菁_01</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -1227,1054 +1232,1059 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f t="shared" ref="C8:C34" si="0">A8&amp;"_01"</f>
+        <v>卷心菜_01</v>
+      </c>
+      <c r="D8" s="1">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>29</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>100</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B9" s="3">
         <v>1003</v>
       </c>
-      <c r="C8" s="3" t="str">
+      <c r="C9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大葱_01</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D9" s="1">
         <v>5</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>29</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>100</v>
-      </c>
-      <c r="L8" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A9" s="5" t="s">
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>29</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B10" s="3">
         <v>1004</v>
       </c>
-      <c r="C9" s="3" t="str">
+      <c r="C10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>萝卜_01</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D10" s="1">
         <v>5</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>29</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>100</v>
-      </c>
-      <c r="L9" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A10" s="5" t="s">
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>29</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B11" s="3">
         <v>1005</v>
       </c>
-      <c r="C10" s="3" t="str">
+      <c r="C11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>紫甘蓝_01</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>29</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>100</v>
-      </c>
-      <c r="L10" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A11" s="5" t="s">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>29</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B12" s="3">
         <v>1006</v>
       </c>
-      <c r="C11" s="3" t="str">
+      <c r="C12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>黄瓜_01</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>29</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>100</v>
-      </c>
-      <c r="L11" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>29</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B13" s="3">
         <v>1007</v>
       </c>
-      <c r="C12" s="3" t="str">
+      <c r="C13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西兰花_01</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>29</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>100</v>
-      </c>
-      <c r="L12" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B14" s="3">
         <v>1008</v>
       </c>
-      <c r="C13" s="3" t="str">
+      <c r="C14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>番茄_01</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D14" s="1">
         <v>5</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>29</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>100</v>
-      </c>
-      <c r="L13" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>29</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B15" s="3">
         <v>1009</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>胡萝卜_01</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D15" s="1">
         <v>5</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>29</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>100</v>
-      </c>
-      <c r="L14" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>29</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B16" s="3">
         <v>1010</v>
       </c>
-      <c r="C15" s="3" t="str">
+      <c r="C16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西瓜_01</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D16" s="1">
         <v>5</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>29</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-      <c r="L15" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>29</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B17" s="3">
         <v>1011</v>
       </c>
-      <c r="C16" s="3" t="str">
+      <c r="C17" s="3" t="str">
         <f t="shared" si="0"/>
         <v>辣椒_01</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>29</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-      <c r="L16" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A17" s="5" t="s">
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>29</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B18" s="3">
         <v>1012</v>
       </c>
-      <c r="C17" s="3" t="str">
+      <c r="C18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>奇异果_01</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>29</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-      <c r="L17" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>29</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B19" s="3">
         <v>1013</v>
       </c>
-      <c r="C18" s="3" t="str">
+      <c r="C19" s="3" t="str">
         <f t="shared" si="0"/>
         <v>茄子_01</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D19" s="1">
         <v>5</v>
       </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>29</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
-      </c>
-      <c r="L18" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A19" s="5" t="s">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>29</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>1014</v>
       </c>
-      <c r="C19" s="3" t="str">
+      <c r="C20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>豌豆_01</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>5</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>29</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>29</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B21" s="3">
         <v>1015</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>土豆_01</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>5</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>29</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>29</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B22" s="3">
         <v>1016</v>
       </c>
-      <c r="C21" s="3" t="str">
+      <c r="C22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大蒜_01</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>29</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>29</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B23" s="3">
         <v>1017</v>
       </c>
-      <c r="C22" s="3" t="str">
+      <c r="C23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>芦笋_01</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D23" s="1">
         <v>5</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>29</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="s">
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>29</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B24" s="3">
         <v>1018</v>
       </c>
-      <c r="C23" s="3" t="str">
+      <c r="C24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>南瓜_01</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>29</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-      <c r="L23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>29</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B25" s="3">
         <v>1019</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>玉米_01</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25" s="1">
         <v>5</v>
       </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>29</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A25" s="5" t="s">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>29</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B26" s="3">
         <v>1020</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C26" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大麦_01</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26" s="1">
         <v>5</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <v>29</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>29</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B27" s="3">
         <v>1021</v>
       </c>
-      <c r="C26" s="3" t="str">
+      <c r="C27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>啤酒花_01</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>5</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>29</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>100</v>
-      </c>
-      <c r="L26" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A27" s="5" t="s">
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>29</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>1022</v>
       </c>
-      <c r="C27" s="3" t="str">
+      <c r="C28" s="3" t="str">
         <f t="shared" si="0"/>
         <v>葡萄_01</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28" s="1">
         <v>5</v>
       </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>29</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>100</v>
-      </c>
-      <c r="L27" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>29</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>1023</v>
       </c>
-      <c r="C28" s="3" t="str">
+      <c r="C29" s="3" t="str">
         <f t="shared" si="0"/>
         <v>菠萝_01</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D29" s="1">
         <v>5</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <v>29</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>100</v>
-      </c>
-      <c r="L28" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>29</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>1024</v>
       </c>
-      <c r="C29" s="3" t="str">
+      <c r="C30" s="3" t="str">
         <f t="shared" si="0"/>
         <v>咖啡_01</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30" s="1">
         <v>5</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>29</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>100</v>
-      </c>
-      <c r="L29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>29</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>1025</v>
       </c>
-      <c r="C30" s="3" t="str">
+      <c r="C31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>草莓_01</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="1">
         <v>5</v>
       </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
-        <v>29</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>100</v>
-      </c>
-      <c r="L30" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>29</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <v>1026</v>
       </c>
-      <c r="C31" s="3" t="str">
+      <c r="C32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>蓝莓_01</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>5</v>
       </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
-        <v>29</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>100</v>
-      </c>
-      <c r="L31" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>29</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <v>1027</v>
       </c>
-      <c r="C32" s="3" t="str">
+      <c r="C33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>红薯_01</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D33" s="1">
         <v>5</v>
       </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>29</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>100</v>
-      </c>
-      <c r="L32" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A33" s="5" t="s">
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>29</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B34" s="3">
         <v>1028</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C34" s="3" t="str">
         <f t="shared" si="0"/>
         <v>甜菜_01</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>29</v>
-      </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>100</v>
-      </c>
-      <c r="L33" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="3">
-        <f>B6+100</f>
-        <v>1101</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0</v>
-      </c>
       <c r="E34" s="1">
-        <v>8001</v>
+        <v>1</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -2297,20 +2307,20 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A35" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B35" s="3">
-        <f t="shared" ref="B35:B61" si="1">B7+100</f>
-        <v>1102</v>
+        <f>B7+100</f>
+        <v>1101</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2336,1034 +2346,1035 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="3">
+        <f t="shared" ref="B36:B62" si="1">B8+100</f>
+        <v>1102</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1">
+        <v>8002</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <v>29</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B37" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
         <v>8003</v>
       </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3">
-        <v>29</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>100</v>
-      </c>
-      <c r="L36" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A37" s="5" t="s">
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>29</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B38" s="3">
         <f t="shared" si="1"/>
         <v>1104</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
         <v>8004</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="3">
-        <v>29</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>100</v>
-      </c>
-      <c r="L37" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A38" s="5" t="s">
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>29</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B39" s="3">
         <f t="shared" si="1"/>
         <v>1105</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
         <v>8005</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3">
-        <v>29</v>
-      </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>100</v>
-      </c>
-      <c r="L38" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A39" s="5" t="s">
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>29</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B40" s="3">
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
         <v>8006</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3">
-        <v>29</v>
-      </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>100</v>
-      </c>
-      <c r="L39" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A40" s="5" t="s">
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>29</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B41" s="3">
         <f t="shared" si="1"/>
         <v>1107</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
         <v>8007</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
-        <v>29</v>
-      </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>100</v>
-      </c>
-      <c r="L40" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A41" s="5" t="s">
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>29</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B42" s="3">
         <f t="shared" si="1"/>
         <v>1108</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
         <v>8008</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>29</v>
-      </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A42" s="5" t="s">
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>29</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B43" s="3">
         <f t="shared" si="1"/>
         <v>1109</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="1">
-        <v>0</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
         <v>8009</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>29</v>
-      </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>100</v>
-      </c>
-      <c r="L42" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A43" s="5" t="s">
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>29</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B44" s="3">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="1">
-        <v>0</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
         <v>8010</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>29</v>
-      </c>
-      <c r="J43" s="1">
-        <v>1</v>
-      </c>
-      <c r="K43" s="1">
-        <v>100</v>
-      </c>
-      <c r="L43" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A44" s="5" t="s">
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>29</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B45" s="3">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
         <v>8011</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>29</v>
-      </c>
-      <c r="J44" s="1">
-        <v>1</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A45" s="5" t="s">
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>29</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100</v>
+      </c>
+      <c r="L45" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B46" s="3">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
         <v>8012</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>29</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1">
-        <v>100</v>
-      </c>
-      <c r="L45" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A46" s="5" t="s">
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <v>29</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>100</v>
+      </c>
+      <c r="L46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B47" s="3">
         <f t="shared" si="1"/>
         <v>1113</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="1">
-        <v>0</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
         <v>8013</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
-        <v>29</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1">
-        <v>100</v>
-      </c>
-      <c r="L46" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A47" s="5" t="s">
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>29</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+      <c r="L47" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B48" s="3">
         <f t="shared" si="1"/>
         <v>1114</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
         <v>8014</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>29</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>100</v>
-      </c>
-      <c r="L47" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A48" s="5" t="s">
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>29</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+      <c r="L48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B49" s="3">
         <f t="shared" si="1"/>
         <v>1115</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
         <v>8015</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>29</v>
-      </c>
-      <c r="J48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>100</v>
-      </c>
-      <c r="L48" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A49" s="5" t="s">
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>29</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B50" s="3">
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
         <v>8016</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>29</v>
-      </c>
-      <c r="J49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1">
-        <v>100</v>
-      </c>
-      <c r="L49" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A50" s="5" t="s">
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <v>29</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A51" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B51" s="3">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
         <v>8017</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3">
-        <v>29</v>
-      </c>
-      <c r="J50" s="1">
-        <v>1</v>
-      </c>
-      <c r="K50" s="1">
-        <v>100</v>
-      </c>
-      <c r="L50" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A51" s="5" t="s">
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <v>29</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+      <c r="L51" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B52" s="3">
         <f t="shared" si="1"/>
         <v>1118</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
         <v>8018</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3">
-        <v>29</v>
-      </c>
-      <c r="J51" s="1">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>100</v>
-      </c>
-      <c r="L51" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A52" s="5" t="s">
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>29</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>100</v>
+      </c>
+      <c r="L52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B53" s="3">
         <f t="shared" si="1"/>
         <v>1119</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
         <v>8019</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>29</v>
-      </c>
-      <c r="J52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>100</v>
-      </c>
-      <c r="L52" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A53" s="5" t="s">
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <v>29</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1">
+        <v>100</v>
+      </c>
+      <c r="L53" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B54" s="3">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
         <v>8020</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3">
-        <v>29</v>
-      </c>
-      <c r="J53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1">
-        <v>100</v>
-      </c>
-      <c r="L53" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A54" s="5" t="s">
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>29</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>100</v>
+      </c>
+      <c r="L54" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B55" s="3">
         <f t="shared" si="1"/>
         <v>1121</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
         <v>8021</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3">
-        <v>29</v>
-      </c>
-      <c r="J54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>100</v>
-      </c>
-      <c r="L54" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A55" s="5" t="s">
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
+        <v>29</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>100</v>
+      </c>
+      <c r="L55" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B56" s="3">
         <f t="shared" si="1"/>
         <v>1122</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
         <v>8022</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3">
-        <v>29</v>
-      </c>
-      <c r="J55" s="1">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1">
-        <v>100</v>
-      </c>
-      <c r="L55" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A56" s="5" t="s">
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <v>29</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="1">
+        <v>100</v>
+      </c>
+      <c r="L56" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B57" s="3">
         <f t="shared" si="1"/>
         <v>1123</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
         <v>8023</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="3">
-        <v>29</v>
-      </c>
-      <c r="J56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>100</v>
-      </c>
-      <c r="L56" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A57" s="5" t="s">
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>29</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="1">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B58" s="3">
         <f t="shared" si="1"/>
         <v>1124</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
         <v>8024</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>29</v>
-      </c>
-      <c r="J57" s="1">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1">
-        <v>100</v>
-      </c>
-      <c r="L57" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A58" s="5" t="s">
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>29</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B59" s="3">
         <f t="shared" si="1"/>
         <v>1125</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
         <v>8025</v>
       </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>29</v>
-      </c>
-      <c r="J58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>100</v>
-      </c>
-      <c r="L58" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A59" s="5" t="s">
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>29</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B60" s="3">
         <f t="shared" si="1"/>
         <v>1126</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
         <v>8026</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>29</v>
-      </c>
-      <c r="J59" s="1">
-        <v>1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>100</v>
-      </c>
-      <c r="L59" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A60" s="5" t="s">
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>29</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="1">
+        <v>100</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A61" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B61" s="3">
         <f t="shared" si="1"/>
         <v>1127</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
         <v>8027</v>
       </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>29</v>
-      </c>
-      <c r="J60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1">
-        <v>100</v>
-      </c>
-      <c r="L60" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A61" s="5" t="s">
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>29</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="1">
+        <v>100</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A62" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B62" s="3">
         <f t="shared" si="1"/>
         <v>1128</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
         <v>8028</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>29</v>
-      </c>
-      <c r="J61" s="1">
-        <v>1</v>
-      </c>
-      <c r="K61" s="1">
-        <v>100</v>
-      </c>
-      <c r="L61" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A62" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B62" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="1">
-        <v>6</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
@@ -3373,8 +3384,8 @@
       <c r="H62" s="1">
         <v>0</v>
       </c>
-      <c r="I62" s="1">
-        <v>1</v>
+      <c r="I62" s="3">
+        <v>29</v>
       </c>
       <c r="J62" s="1">
         <v>1</v>
@@ -3384,20 +3395,17 @@
       </c>
       <c r="L62" s="1">
         <v>100</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B63" s="1">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D63" s="1">
         <v>6</v>
@@ -3409,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -3427,15 +3435,18 @@
         <v>100</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B64" s="1">
-        <v>2002</v>
+        <v>2001</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D64" s="1">
         <v>6</v>
@@ -3447,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -3465,18 +3476,15 @@
         <v>100</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B65" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>38</v>
+        <v>2002</v>
       </c>
       <c r="D65" s="1">
         <v>6</v>
@@ -3506,24 +3514,24 @@
         <v>100</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B66" s="1">
-        <v>2100</v>
+        <v>2003</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="D66" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E66" s="1">
-        <v>2100</v>
+        <v>1</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3547,24 +3555,24 @@
         <v>100</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B67" s="1">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D67" s="1">
         <v>10</v>
       </c>
       <c r="E67" s="1">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3588,24 +3596,24 @@
         <v>100</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B68" s="1">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D68" s="1">
         <v>10</v>
       </c>
       <c r="E68" s="1">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3629,24 +3637,24 @@
         <v>100</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B69" s="1">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D69" s="1">
         <v>10</v>
       </c>
       <c r="E69" s="1">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3670,24 +3678,24 @@
         <v>100</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B70" s="1">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D70" s="1">
         <v>10</v>
       </c>
       <c r="E70" s="1">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3711,24 +3719,24 @@
         <v>100</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B71" s="1">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D71" s="1">
         <v>10</v>
       </c>
       <c r="E71" s="1">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3752,24 +3760,24 @@
         <v>100</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B72" s="1">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D72" s="1">
         <v>10</v>
       </c>
       <c r="E72" s="1">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3793,24 +3801,24 @@
         <v>100</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B73" s="1">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D73" s="1">
         <v>10</v>
       </c>
       <c r="E73" s="1">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -3834,24 +3842,24 @@
         <v>100</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B74" s="1">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D74" s="1">
         <v>10</v>
       </c>
       <c r="E74" s="1">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3875,24 +3883,24 @@
         <v>100</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B75" s="1">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D75" s="1">
         <v>10</v>
       </c>
       <c r="E75" s="1">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3916,24 +3924,24 @@
         <v>100</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B76" s="1">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76" s="1">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -3957,24 +3965,24 @@
         <v>100</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B77" s="1">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D77" s="1">
         <v>10</v>
       </c>
       <c r="E77" s="1">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -3998,24 +4006,24 @@
         <v>100</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B78" s="1">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D78" s="1">
         <v>10</v>
       </c>
       <c r="E78" s="1">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4039,24 +4047,24 @@
         <v>100</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B79" s="1">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D79" s="1">
         <v>10</v>
       </c>
       <c r="E79" s="1">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4080,24 +4088,24 @@
         <v>100</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B80" s="1">
-        <v>2200</v>
+        <v>2113</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D80" s="1">
         <v>10</v>
       </c>
       <c r="E80" s="1">
-        <v>2200</v>
+        <v>2113</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4121,24 +4129,24 @@
         <v>100</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B81" s="1">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D81" s="1">
         <v>10</v>
       </c>
       <c r="E81" s="1">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4162,47 +4170,88 @@
         <v>100</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82" s="1">
+        <v>2201</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" s="1">
+        <v>10</v>
+      </c>
+      <c r="E82" s="1">
+        <v>2201</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1">
+        <v>1</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+      <c r="K82" s="1">
+        <v>100</v>
+      </c>
+      <c r="L82" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q82" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A83" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B83" s="1">
         <v>3000</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D83" s="1">
         <v>11</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E83" s="1">
         <v>3000</v>
       </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>0</v>
-      </c>
-      <c r="I82" s="1">
-        <v>1</v>
-      </c>
-      <c r="J82" s="1">
-        <v>1</v>
-      </c>
-      <c r="K82" s="1">
-        <v>100</v>
-      </c>
-      <c r="L82" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q82" s="1" t="s">
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1</v>
+      </c>
+      <c r="K83" s="1">
+        <v>100</v>
+      </c>
+      <c r="L83" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="1" t="s">
         <v>138</v>
       </c>
     </row>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="145">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -560,6 +560,21 @@
   </si>
   <si>
     <t>未成熟的植物制成的鲜嫩可口的饲料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卷轴</t>
+  </si>
+  <si>
+    <t>快速在城镇中移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -945,7 +960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q83"/>
+  <dimension ref="A2:Q84"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -1149,99 +1164,99 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="1">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>19</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="1">
-        <v>100</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B7" s="1">
+        <v>100</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D7" s="1">
         <v>-1</v>
       </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>29</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1" t="s">
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>29</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1001</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>A7&amp;"_01"</f>
-        <v>芜菁_01</v>
-      </c>
-      <c r="D7" s="1">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>29</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-      <c r="L7" s="1">
-        <v>100</v>
-      </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C8" s="3" t="str">
-        <f t="shared" ref="C8:C34" si="0">A8&amp;"_01"</f>
-        <v>卷心菜_01</v>
+        <f>A8&amp;"_01"</f>
+        <v>芜菁_01</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
@@ -1276,1054 +1291,1059 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f t="shared" ref="C9:C35" si="0">A9&amp;"_01"</f>
+        <v>卷心菜_01</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>29</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B10" s="3">
         <v>1003</v>
       </c>
-      <c r="C9" s="3" t="str">
+      <c r="C10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大葱_01</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D10" s="1">
         <v>5</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>29</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>100</v>
-      </c>
-      <c r="L9" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A10" s="5" t="s">
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>29</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B11" s="3">
         <v>1004</v>
       </c>
-      <c r="C10" s="3" t="str">
+      <c r="C11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>萝卜_01</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>29</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>100</v>
-      </c>
-      <c r="L10" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A11" s="5" t="s">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>29</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B12" s="3">
         <v>1005</v>
       </c>
-      <c r="C11" s="3" t="str">
+      <c r="C12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>紫甘蓝_01</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>29</v>
-      </c>
-      <c r="J11" s="3">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>100</v>
-      </c>
-      <c r="L11" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>29</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B13" s="3">
         <v>1006</v>
       </c>
-      <c r="C12" s="3" t="str">
+      <c r="C13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>黄瓜_01</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>29</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>100</v>
-      </c>
-      <c r="L12" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B14" s="3">
         <v>1007</v>
       </c>
-      <c r="C13" s="3" t="str">
+      <c r="C14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西兰花_01</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D14" s="1">
         <v>5</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>29</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>100</v>
-      </c>
-      <c r="L13" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>29</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B15" s="3">
         <v>1008</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>番茄_01</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D15" s="1">
         <v>5</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>29</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>100</v>
-      </c>
-      <c r="L14" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>29</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B16" s="3">
         <v>1009</v>
       </c>
-      <c r="C15" s="3" t="str">
+      <c r="C16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>胡萝卜_01</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D16" s="1">
         <v>5</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>29</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-      <c r="L15" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>29</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B17" s="3">
         <v>1010</v>
       </c>
-      <c r="C16" s="3" t="str">
+      <c r="C17" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西瓜_01</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>29</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-      <c r="L16" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A17" s="5" t="s">
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>29</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B18" s="3">
         <v>1011</v>
       </c>
-      <c r="C17" s="3" t="str">
+      <c r="C18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>辣椒_01</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>29</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-      <c r="L17" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>29</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B19" s="3">
         <v>1012</v>
       </c>
-      <c r="C18" s="3" t="str">
+      <c r="C19" s="3" t="str">
         <f t="shared" si="0"/>
         <v>奇异果_01</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D19" s="1">
         <v>5</v>
       </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>29</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
-      </c>
-      <c r="L18" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A19" s="5" t="s">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>29</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>1013</v>
       </c>
-      <c r="C19" s="3" t="str">
+      <c r="C20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>茄子_01</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>5</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>29</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>29</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B21" s="3">
         <v>1014</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>豌豆_01</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>5</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>29</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>29</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B22" s="3">
         <v>1015</v>
       </c>
-      <c r="C21" s="3" t="str">
+      <c r="C22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>土豆_01</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>29</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>29</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B23" s="3">
         <v>1016</v>
       </c>
-      <c r="C22" s="3" t="str">
+      <c r="C23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大蒜_01</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D23" s="1">
         <v>5</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>29</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="s">
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>29</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B24" s="3">
         <v>1017</v>
       </c>
-      <c r="C23" s="3" t="str">
+      <c r="C24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>芦笋_01</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>29</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-      <c r="L23" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="5"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>29</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B25" s="3">
         <v>1018</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>南瓜_01</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25" s="1">
         <v>5</v>
       </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>29</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A25" s="5" t="s">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>29</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B26" s="3">
         <v>1019</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C26" s="3" t="str">
         <f t="shared" si="0"/>
         <v>玉米_01</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26" s="1">
         <v>5</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <v>29</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>29</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B27" s="3">
         <v>1020</v>
       </c>
-      <c r="C26" s="3" t="str">
+      <c r="C27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大麦_01</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>5</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>29</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>100</v>
-      </c>
-      <c r="L26" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A27" s="5" t="s">
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>29</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>1021</v>
       </c>
-      <c r="C27" s="3" t="str">
+      <c r="C28" s="3" t="str">
         <f t="shared" si="0"/>
         <v>啤酒花_01</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28" s="1">
         <v>5</v>
       </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>29</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>100</v>
-      </c>
-      <c r="L27" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>29</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>1022</v>
       </c>
-      <c r="C28" s="3" t="str">
+      <c r="C29" s="3" t="str">
         <f t="shared" si="0"/>
         <v>葡萄_01</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D29" s="1">
         <v>5</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <v>29</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>100</v>
-      </c>
-      <c r="L28" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>29</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>1023</v>
       </c>
-      <c r="C29" s="3" t="str">
+      <c r="C30" s="3" t="str">
         <f t="shared" si="0"/>
         <v>菠萝_01</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30" s="1">
         <v>5</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>29</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>100</v>
-      </c>
-      <c r="L29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>29</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>1024</v>
       </c>
-      <c r="C30" s="3" t="str">
+      <c r="C31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>咖啡_01</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="1">
         <v>5</v>
       </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
-        <v>29</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>100</v>
-      </c>
-      <c r="L30" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>29</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <v>1025</v>
       </c>
-      <c r="C31" s="3" t="str">
+      <c r="C32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>草莓_01</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>5</v>
       </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
-        <v>29</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>100</v>
-      </c>
-      <c r="L31" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>29</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <v>1026</v>
       </c>
-      <c r="C32" s="3" t="str">
+      <c r="C33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>蓝莓_01</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D33" s="1">
         <v>5</v>
       </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>29</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>100</v>
-      </c>
-      <c r="L32" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A33" s="5" t="s">
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>29</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B34" s="3">
         <v>1027</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C34" s="3" t="str">
         <f t="shared" si="0"/>
         <v>红薯_01</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>29</v>
-      </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>100</v>
-      </c>
-      <c r="L33" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A34" s="5" t="s">
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>29</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B35" s="3">
         <v>1028</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C35" s="3" t="str">
         <f t="shared" si="0"/>
         <v>甜菜_01</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
-        <v>29</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>100</v>
-      </c>
-      <c r="L34" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A35" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="3">
-        <f>B7+100</f>
-        <v>1101</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
       <c r="E35" s="1">
-        <v>8001</v>
+        <v>1</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -2346,20 +2366,20 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" s="3">
-        <f t="shared" ref="B36:B62" si="1">B8+100</f>
-        <v>1102</v>
+        <f>B8+100</f>
+        <v>1101</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2385,1034 +2405,1035 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="3">
+        <f t="shared" ref="B37:B63" si="1">B9+100</f>
+        <v>1102</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8002</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>29</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A38" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B38" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
         <v>8003</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="3">
-        <v>29</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>100</v>
-      </c>
-      <c r="L37" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A38" s="5" t="s">
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>29</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B39" s="3">
         <f t="shared" si="1"/>
         <v>1104</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
         <v>8004</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3">
-        <v>29</v>
-      </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>100</v>
-      </c>
-      <c r="L38" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A39" s="5" t="s">
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>29</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B40" s="3">
         <f t="shared" si="1"/>
         <v>1105</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
         <v>8005</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3">
-        <v>29</v>
-      </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>100</v>
-      </c>
-      <c r="L39" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A40" s="5" t="s">
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>29</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B41" s="3">
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
         <v>8006</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
-        <v>29</v>
-      </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>100</v>
-      </c>
-      <c r="L40" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A41" s="5" t="s">
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>29</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A42" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B42" s="3">
         <f t="shared" si="1"/>
         <v>1107</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
         <v>8007</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>29</v>
-      </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A42" s="5" t="s">
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>29</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A43" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B43" s="3">
         <f t="shared" si="1"/>
         <v>1108</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="1">
-        <v>0</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
         <v>8008</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>29</v>
-      </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>100</v>
-      </c>
-      <c r="L42" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A43" s="5" t="s">
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>29</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A44" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B44" s="3">
         <f t="shared" si="1"/>
         <v>1109</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="1">
-        <v>0</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
         <v>8009</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>29</v>
-      </c>
-      <c r="J43" s="1">
-        <v>1</v>
-      </c>
-      <c r="K43" s="1">
-        <v>100</v>
-      </c>
-      <c r="L43" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A44" s="5" t="s">
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>29</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A45" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B45" s="3">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
         <v>8010</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>29</v>
-      </c>
-      <c r="J44" s="1">
-        <v>1</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A45" s="5" t="s">
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>29</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100</v>
+      </c>
+      <c r="L45" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B46" s="3">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
         <v>8011</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>29</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1">
-        <v>100</v>
-      </c>
-      <c r="L45" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A46" s="5" t="s">
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <v>29</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>100</v>
+      </c>
+      <c r="L46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A47" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B47" s="3">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D46" s="1">
-        <v>0</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
         <v>8012</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
-        <v>29</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1">
-        <v>100</v>
-      </c>
-      <c r="L46" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A47" s="5" t="s">
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>29</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+      <c r="L47" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B48" s="3">
         <f t="shared" si="1"/>
         <v>1113</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
         <v>8013</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>29</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>100</v>
-      </c>
-      <c r="L47" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A48" s="5" t="s">
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>29</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+      <c r="L48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A49" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B49" s="3">
         <f t="shared" si="1"/>
         <v>1114</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
         <v>8014</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>29</v>
-      </c>
-      <c r="J48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>100</v>
-      </c>
-      <c r="L48" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A49" s="5" t="s">
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>29</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B50" s="3">
         <f t="shared" si="1"/>
         <v>1115</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
         <v>8015</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>29</v>
-      </c>
-      <c r="J49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1">
-        <v>100</v>
-      </c>
-      <c r="L49" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A50" s="5" t="s">
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <v>29</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A51" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B51" s="3">
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
         <v>8016</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3">
-        <v>29</v>
-      </c>
-      <c r="J50" s="1">
-        <v>1</v>
-      </c>
-      <c r="K50" s="1">
-        <v>100</v>
-      </c>
-      <c r="L50" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A51" s="5" t="s">
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <v>29</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+      <c r="L51" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B52" s="3">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
         <v>8017</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3">
-        <v>29</v>
-      </c>
-      <c r="J51" s="1">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>100</v>
-      </c>
-      <c r="L51" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A52" s="5" t="s">
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>29</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>100</v>
+      </c>
+      <c r="L52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B53" s="3">
         <f t="shared" si="1"/>
         <v>1118</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
         <v>8018</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>29</v>
-      </c>
-      <c r="J52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>100</v>
-      </c>
-      <c r="L52" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A53" s="5" t="s">
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <v>29</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1">
+        <v>100</v>
+      </c>
+      <c r="L53" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B54" s="3">
         <f t="shared" si="1"/>
         <v>1119</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
         <v>8019</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3">
-        <v>29</v>
-      </c>
-      <c r="J53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1">
-        <v>100</v>
-      </c>
-      <c r="L53" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A54" s="5" t="s">
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>29</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>100</v>
+      </c>
+      <c r="L54" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A55" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B55" s="3">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
         <v>8020</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3">
-        <v>29</v>
-      </c>
-      <c r="J54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>100</v>
-      </c>
-      <c r="L54" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A55" s="5" t="s">
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
+        <v>29</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>100</v>
+      </c>
+      <c r="L55" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B56" s="3">
         <f t="shared" si="1"/>
         <v>1121</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
         <v>8021</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3">
-        <v>29</v>
-      </c>
-      <c r="J55" s="1">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1">
-        <v>100</v>
-      </c>
-      <c r="L55" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A56" s="5" t="s">
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <v>29</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="1">
+        <v>100</v>
+      </c>
+      <c r="L56" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B57" s="3">
         <f t="shared" si="1"/>
         <v>1122</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
         <v>8022</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="3">
-        <v>29</v>
-      </c>
-      <c r="J56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>100</v>
-      </c>
-      <c r="L56" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A57" s="5" t="s">
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>29</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="1">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B58" s="3">
         <f t="shared" si="1"/>
         <v>1123</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
         <v>8023</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>29</v>
-      </c>
-      <c r="J57" s="1">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1">
-        <v>100</v>
-      </c>
-      <c r="L57" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A58" s="5" t="s">
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>29</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B59" s="3">
         <f t="shared" si="1"/>
         <v>1124</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
         <v>8024</v>
       </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>29</v>
-      </c>
-      <c r="J58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>100</v>
-      </c>
-      <c r="L58" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A59" s="5" t="s">
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>29</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B60" s="3">
         <f t="shared" si="1"/>
         <v>1125</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
         <v>8025</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>29</v>
-      </c>
-      <c r="J59" s="1">
-        <v>1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>100</v>
-      </c>
-      <c r="L59" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A60" s="5" t="s">
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>29</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="1">
+        <v>100</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A61" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B61" s="3">
         <f t="shared" si="1"/>
         <v>1126</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
         <v>8026</v>
       </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>29</v>
-      </c>
-      <c r="J60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1">
-        <v>100</v>
-      </c>
-      <c r="L60" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A61" s="5" t="s">
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>29</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="1">
+        <v>100</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A62" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B62" s="3">
         <f t="shared" si="1"/>
         <v>1127</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
         <v>8027</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>29</v>
-      </c>
-      <c r="J61" s="1">
-        <v>1</v>
-      </c>
-      <c r="K61" s="1">
-        <v>100</v>
-      </c>
-      <c r="L61" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A62" s="5" t="s">
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>29</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="1">
+        <v>100</v>
+      </c>
+      <c r="L62" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A63" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B63" s="3">
         <f t="shared" si="1"/>
         <v>1128</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D62" s="1">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1">
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
         <v>8028</v>
       </c>
-      <c r="F62" s="1">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0</v>
-      </c>
-      <c r="H62" s="1">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>29</v>
-      </c>
-      <c r="J62" s="1">
-        <v>1</v>
-      </c>
-      <c r="K62" s="1">
-        <v>100</v>
-      </c>
-      <c r="L62" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A63" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D63" s="1">
-        <v>6</v>
-      </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
       <c r="F63" s="1">
         <v>0</v>
       </c>
@@ -3422,8 +3443,8 @@
       <c r="H63" s="1">
         <v>0</v>
       </c>
-      <c r="I63" s="1">
-        <v>1</v>
+      <c r="I63" s="3">
+        <v>29</v>
       </c>
       <c r="J63" s="1">
         <v>1</v>
@@ -3433,20 +3454,17 @@
       </c>
       <c r="L63" s="1">
         <v>100</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B64" s="1">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D64" s="1">
         <v>6</v>
@@ -3458,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -3476,15 +3494,18 @@
         <v>100</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B65" s="1">
-        <v>2002</v>
+        <v>2001</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D65" s="1">
         <v>6</v>
@@ -3496,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -3514,18 +3535,15 @@
         <v>100</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B66" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>38</v>
+        <v>2002</v>
       </c>
       <c r="D66" s="1">
         <v>6</v>
@@ -3555,24 +3573,24 @@
         <v>100</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B67" s="1">
-        <v>2100</v>
+        <v>2003</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="D67" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E67" s="1">
-        <v>2100</v>
+        <v>1</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3596,24 +3614,24 @@
         <v>100</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B68" s="1">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D68" s="1">
         <v>10</v>
       </c>
       <c r="E68" s="1">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3637,24 +3655,24 @@
         <v>100</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B69" s="1">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D69" s="1">
         <v>10</v>
       </c>
       <c r="E69" s="1">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3678,24 +3696,24 @@
         <v>100</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B70" s="1">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D70" s="1">
         <v>10</v>
       </c>
       <c r="E70" s="1">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3719,24 +3737,24 @@
         <v>100</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B71" s="1">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D71" s="1">
         <v>10</v>
       </c>
       <c r="E71" s="1">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3760,24 +3778,24 @@
         <v>100</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B72" s="1">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D72" s="1">
         <v>10</v>
       </c>
       <c r="E72" s="1">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3801,24 +3819,24 @@
         <v>100</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B73" s="1">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D73" s="1">
         <v>10</v>
       </c>
       <c r="E73" s="1">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -3842,24 +3860,24 @@
         <v>100</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B74" s="1">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D74" s="1">
         <v>10</v>
       </c>
       <c r="E74" s="1">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3883,24 +3901,24 @@
         <v>100</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B75" s="1">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D75" s="1">
         <v>10</v>
       </c>
       <c r="E75" s="1">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3924,24 +3942,24 @@
         <v>100</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B76" s="1">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76" s="1">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -3965,24 +3983,24 @@
         <v>100</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B77" s="1">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D77" s="1">
         <v>10</v>
       </c>
       <c r="E77" s="1">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4006,24 +4024,24 @@
         <v>100</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B78" s="1">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D78" s="1">
         <v>10</v>
       </c>
       <c r="E78" s="1">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4047,24 +4065,24 @@
         <v>100</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B79" s="1">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D79" s="1">
         <v>10</v>
       </c>
       <c r="E79" s="1">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4088,24 +4106,24 @@
         <v>100</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B80" s="1">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D80" s="1">
         <v>10</v>
       </c>
       <c r="E80" s="1">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4129,24 +4147,24 @@
         <v>100</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B81" s="1">
-        <v>2200</v>
+        <v>2113</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D81" s="1">
         <v>10</v>
       </c>
       <c r="E81" s="1">
-        <v>2200</v>
+        <v>2113</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4170,24 +4188,24 @@
         <v>100</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B82" s="1">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D82" s="1">
         <v>10</v>
       </c>
       <c r="E82" s="1">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4211,47 +4229,88 @@
         <v>100</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" s="1">
+        <v>2201</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D83" s="1">
+        <v>10</v>
+      </c>
+      <c r="E83" s="1">
+        <v>2201</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1</v>
+      </c>
+      <c r="K83" s="1">
+        <v>100</v>
+      </c>
+      <c r="L83" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A84" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B84" s="1">
         <v>3000</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D84" s="1">
         <v>11</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E84" s="1">
         <v>3000</v>
       </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0</v>
-      </c>
-      <c r="H83" s="1">
-        <v>0</v>
-      </c>
-      <c r="I83" s="1">
-        <v>1</v>
-      </c>
-      <c r="J83" s="1">
-        <v>1</v>
-      </c>
-      <c r="K83" s="1">
-        <v>100</v>
-      </c>
-      <c r="L83" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q83" s="1" t="s">
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>1</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+      <c r="K84" s="1">
+        <v>100</v>
+      </c>
+      <c r="L84" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q84" s="1" t="s">
         <v>138</v>
       </c>
     </row>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="187">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -576,13 +576,142 @@
   <si>
     <t>41</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>泥鳅</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>小龙虾</t>
+  </si>
+  <si>
+    <t>溪鳟鱼</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>丁鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+  </si>
+  <si>
+    <t>线鱼</t>
+  </si>
+  <si>
+    <t>梭鲈</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+  </si>
+  <si>
+    <t>罗非鱼</t>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+  </si>
+  <si>
+    <t>沙丁鱼</t>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
+  </si>
+  <si>
+    <t>蛤蜊</t>
+  </si>
+  <si>
+    <t>海鳗</t>
+  </si>
+  <si>
+    <t>扇贝</t>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>比目鱼</t>
+  </si>
+  <si>
+    <t>牡蛎</t>
+  </si>
+  <si>
+    <t>𩽾𩾌</t>
+  </si>
+  <si>
+    <t>河豚鱼</t>
+  </si>
+  <si>
+    <t>水母</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+  </si>
+  <si>
+    <t>蓝蟹</t>
+  </si>
+  <si>
+    <t>鲯鳅鱼</t>
+  </si>
+  <si>
+    <t>龙虾</t>
+  </si>
+  <si>
+    <t>金枪鱼</t>
+  </si>
+  <si>
+    <t>斑马狮子鱼</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -613,6 +742,19 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -636,7 +778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -654,6 +796,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q84"/>
+  <dimension ref="A2:Q127"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -4312,6 +4461,1769 @@
       </c>
       <c r="Q84" s="1" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B85" s="1">
+        <v>4000</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" s="1">
+        <v>3</v>
+      </c>
+      <c r="E85" s="7">
+        <v>1000</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1">
+        <v>9</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1</v>
+      </c>
+      <c r="K85" s="1">
+        <v>100</v>
+      </c>
+      <c r="L85" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A86" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D86" s="1">
+        <v>3</v>
+      </c>
+      <c r="E86" s="7">
+        <v>1001</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
+        <v>9</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1</v>
+      </c>
+      <c r="K86" s="1">
+        <v>100</v>
+      </c>
+      <c r="L86" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q86" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A87" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D87" s="1">
+        <v>3</v>
+      </c>
+      <c r="E87" s="7">
+        <v>1002</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1">
+        <v>9</v>
+      </c>
+      <c r="J87" s="1">
+        <v>1</v>
+      </c>
+      <c r="K87" s="1">
+        <v>100</v>
+      </c>
+      <c r="L87" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q87" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A88" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B88" s="1">
+        <v>4003</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D88" s="1">
+        <v>3</v>
+      </c>
+      <c r="E88" s="7">
+        <v>1003</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+      <c r="I88" s="1">
+        <v>9</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1</v>
+      </c>
+      <c r="K88" s="1">
+        <v>100</v>
+      </c>
+      <c r="L88" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q88" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A89" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B89" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89" s="1">
+        <v>3</v>
+      </c>
+      <c r="E89" s="7">
+        <v>1004</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1">
+        <v>9</v>
+      </c>
+      <c r="J89" s="1">
+        <v>1</v>
+      </c>
+      <c r="K89" s="1">
+        <v>100</v>
+      </c>
+      <c r="L89" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q89" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A90" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B90" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D90" s="1">
+        <v>3</v>
+      </c>
+      <c r="E90" s="7">
+        <v>1005</v>
+      </c>
+      <c r="F90" s="1">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1">
+        <v>9</v>
+      </c>
+      <c r="J90" s="1">
+        <v>1</v>
+      </c>
+      <c r="K90" s="1">
+        <v>100</v>
+      </c>
+      <c r="L90" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q90" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A91" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B91" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D91" s="1">
+        <v>3</v>
+      </c>
+      <c r="E91" s="7">
+        <v>1006</v>
+      </c>
+      <c r="F91" s="1">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1">
+        <v>9</v>
+      </c>
+      <c r="J91" s="1">
+        <v>1</v>
+      </c>
+      <c r="K91" s="1">
+        <v>100</v>
+      </c>
+      <c r="L91" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q91" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A92" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" s="1">
+        <v>4007</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92" s="1">
+        <v>3</v>
+      </c>
+      <c r="E92" s="7">
+        <v>1007</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1">
+        <v>9</v>
+      </c>
+      <c r="J92" s="1">
+        <v>1</v>
+      </c>
+      <c r="K92" s="1">
+        <v>100</v>
+      </c>
+      <c r="L92" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q92" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A93" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B93" s="1">
+        <v>4008</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D93" s="1">
+        <v>3</v>
+      </c>
+      <c r="E93" s="7">
+        <v>1008</v>
+      </c>
+      <c r="F93" s="1">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1">
+        <v>9</v>
+      </c>
+      <c r="J93" s="1">
+        <v>1</v>
+      </c>
+      <c r="K93" s="1">
+        <v>100</v>
+      </c>
+      <c r="L93" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q93" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A94" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B94" s="1">
+        <v>4009</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D94" s="1">
+        <v>3</v>
+      </c>
+      <c r="E94" s="7">
+        <v>1009</v>
+      </c>
+      <c r="F94" s="1">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1">
+        <v>9</v>
+      </c>
+      <c r="J94" s="1">
+        <v>1</v>
+      </c>
+      <c r="K94" s="1">
+        <v>100</v>
+      </c>
+      <c r="L94" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q94" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A95" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B95" s="1">
+        <v>4010</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D95" s="1">
+        <v>3</v>
+      </c>
+      <c r="E95" s="7">
+        <v>1010</v>
+      </c>
+      <c r="F95" s="1">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>9</v>
+      </c>
+      <c r="J95" s="1">
+        <v>1</v>
+      </c>
+      <c r="K95" s="1">
+        <v>100</v>
+      </c>
+      <c r="L95" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q95" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A96" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B96" s="1">
+        <v>4011</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D96" s="1">
+        <v>3</v>
+      </c>
+      <c r="E96" s="7">
+        <v>1011</v>
+      </c>
+      <c r="F96" s="1">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1">
+        <v>9</v>
+      </c>
+      <c r="J96" s="1">
+        <v>1</v>
+      </c>
+      <c r="K96" s="1">
+        <v>100</v>
+      </c>
+      <c r="L96" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q96" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A97" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B97" s="1">
+        <v>4012</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D97" s="1">
+        <v>3</v>
+      </c>
+      <c r="E97" s="7">
+        <v>1012</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+      <c r="I97" s="1">
+        <v>9</v>
+      </c>
+      <c r="J97" s="1">
+        <v>1</v>
+      </c>
+      <c r="K97" s="1">
+        <v>100</v>
+      </c>
+      <c r="L97" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q97" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A98" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B98" s="1">
+        <v>4013</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98" s="1">
+        <v>3</v>
+      </c>
+      <c r="E98" s="7">
+        <v>1013</v>
+      </c>
+      <c r="F98" s="1">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1">
+        <v>9</v>
+      </c>
+      <c r="J98" s="1">
+        <v>1</v>
+      </c>
+      <c r="K98" s="1">
+        <v>100</v>
+      </c>
+      <c r="L98" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q98" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A99" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B99" s="1">
+        <v>4014</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99" s="1">
+        <v>3</v>
+      </c>
+      <c r="E99" s="7">
+        <v>1014</v>
+      </c>
+      <c r="F99" s="1">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1">
+        <v>9</v>
+      </c>
+      <c r="J99" s="1">
+        <v>1</v>
+      </c>
+      <c r="K99" s="1">
+        <v>100</v>
+      </c>
+      <c r="L99" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q99" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A100" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B100" s="1">
+        <v>4015</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D100" s="1">
+        <v>3</v>
+      </c>
+      <c r="E100" s="7">
+        <v>1015</v>
+      </c>
+      <c r="F100" s="1">
+        <v>1</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>9</v>
+      </c>
+      <c r="J100" s="1">
+        <v>1</v>
+      </c>
+      <c r="K100" s="1">
+        <v>100</v>
+      </c>
+      <c r="L100" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q100" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A101" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B101" s="1">
+        <v>4016</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D101" s="1">
+        <v>3</v>
+      </c>
+      <c r="E101" s="7">
+        <v>1016</v>
+      </c>
+      <c r="F101" s="1">
+        <v>1</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1">
+        <v>9</v>
+      </c>
+      <c r="J101" s="1">
+        <v>1</v>
+      </c>
+      <c r="K101" s="1">
+        <v>100</v>
+      </c>
+      <c r="L101" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q101" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A102" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B102" s="1">
+        <v>4017</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D102" s="1">
+        <v>3</v>
+      </c>
+      <c r="E102" s="7">
+        <v>1017</v>
+      </c>
+      <c r="F102" s="1">
+        <v>1</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1">
+        <v>9</v>
+      </c>
+      <c r="J102" s="1">
+        <v>1</v>
+      </c>
+      <c r="K102" s="1">
+        <v>100</v>
+      </c>
+      <c r="L102" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q102" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A103" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B103" s="1">
+        <v>4018</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D103" s="1">
+        <v>3</v>
+      </c>
+      <c r="E103" s="7">
+        <v>1018</v>
+      </c>
+      <c r="F103" s="1">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1">
+        <v>9</v>
+      </c>
+      <c r="J103" s="1">
+        <v>1</v>
+      </c>
+      <c r="K103" s="1">
+        <v>100</v>
+      </c>
+      <c r="L103" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q103" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A104" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B104" s="1">
+        <v>4019</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D104" s="1">
+        <v>3</v>
+      </c>
+      <c r="E104" s="7">
+        <v>1019</v>
+      </c>
+      <c r="F104" s="1">
+        <v>1</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1">
+        <v>9</v>
+      </c>
+      <c r="J104" s="1">
+        <v>1</v>
+      </c>
+      <c r="K104" s="1">
+        <v>100</v>
+      </c>
+      <c r="L104" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q104" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A105" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4020</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D105" s="1">
+        <v>3</v>
+      </c>
+      <c r="E105" s="7">
+        <v>1020</v>
+      </c>
+      <c r="F105" s="1">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1">
+        <v>9</v>
+      </c>
+      <c r="J105" s="1">
+        <v>1</v>
+      </c>
+      <c r="K105" s="1">
+        <v>100</v>
+      </c>
+      <c r="L105" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q105" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A106" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B106" s="1">
+        <v>4021</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D106" s="1">
+        <v>3</v>
+      </c>
+      <c r="E106" s="7">
+        <v>1021</v>
+      </c>
+      <c r="F106" s="1">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>9</v>
+      </c>
+      <c r="J106" s="1">
+        <v>1</v>
+      </c>
+      <c r="K106" s="1">
+        <v>100</v>
+      </c>
+      <c r="L106" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q106" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A107" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B107" s="1">
+        <v>4022</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D107" s="1">
+        <v>3</v>
+      </c>
+      <c r="E107" s="7">
+        <v>1022</v>
+      </c>
+      <c r="F107" s="1">
+        <v>1</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1">
+        <v>9</v>
+      </c>
+      <c r="J107" s="1">
+        <v>1</v>
+      </c>
+      <c r="K107" s="1">
+        <v>100</v>
+      </c>
+      <c r="L107" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q107" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A108" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B108" s="1">
+        <v>4023</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D108" s="1">
+        <v>3</v>
+      </c>
+      <c r="E108" s="7">
+        <v>1023</v>
+      </c>
+      <c r="F108" s="1">
+        <v>1</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1">
+        <v>9</v>
+      </c>
+      <c r="J108" s="1">
+        <v>1</v>
+      </c>
+      <c r="K108" s="1">
+        <v>100</v>
+      </c>
+      <c r="L108" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q108" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A109" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B109" s="1">
+        <v>4024</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D109" s="1">
+        <v>3</v>
+      </c>
+      <c r="E109" s="7">
+        <v>1024</v>
+      </c>
+      <c r="F109" s="1">
+        <v>1</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1">
+        <v>9</v>
+      </c>
+      <c r="J109" s="1">
+        <v>1</v>
+      </c>
+      <c r="K109" s="1">
+        <v>100</v>
+      </c>
+      <c r="L109" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q109" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A110" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4100</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D110" s="1">
+        <v>3</v>
+      </c>
+      <c r="E110" s="7">
+        <v>1100</v>
+      </c>
+      <c r="F110" s="1">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1">
+        <v>9</v>
+      </c>
+      <c r="J110" s="1">
+        <v>1</v>
+      </c>
+      <c r="K110" s="1">
+        <v>100</v>
+      </c>
+      <c r="L110" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q110" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A111" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4101</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D111" s="1">
+        <v>3</v>
+      </c>
+      <c r="E111" s="7">
+        <v>1101</v>
+      </c>
+      <c r="F111" s="1">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1">
+        <v>9</v>
+      </c>
+      <c r="J111" s="1">
+        <v>1</v>
+      </c>
+      <c r="K111" s="1">
+        <v>100</v>
+      </c>
+      <c r="L111" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q111" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A112" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4102</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D112" s="1">
+        <v>3</v>
+      </c>
+      <c r="E112" s="7">
+        <v>1102</v>
+      </c>
+      <c r="F112" s="1">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1">
+        <v>9</v>
+      </c>
+      <c r="J112" s="1">
+        <v>1</v>
+      </c>
+      <c r="K112" s="1">
+        <v>100</v>
+      </c>
+      <c r="L112" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q112" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A113" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4103</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D113" s="1">
+        <v>3</v>
+      </c>
+      <c r="E113" s="7">
+        <v>1103</v>
+      </c>
+      <c r="F113" s="1">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+      <c r="I113" s="1">
+        <v>9</v>
+      </c>
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="1">
+        <v>100</v>
+      </c>
+      <c r="L113" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q113" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A114" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B114" s="1">
+        <v>4104</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D114" s="1">
+        <v>3</v>
+      </c>
+      <c r="E114" s="7">
+        <v>1104</v>
+      </c>
+      <c r="F114" s="1">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+      <c r="I114" s="1">
+        <v>9</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+      <c r="K114" s="1">
+        <v>100</v>
+      </c>
+      <c r="L114" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q114" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A115" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B115" s="1">
+        <v>4105</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D115" s="1">
+        <v>3</v>
+      </c>
+      <c r="E115" s="7">
+        <v>1105</v>
+      </c>
+      <c r="F115" s="1">
+        <v>1</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+      <c r="I115" s="1">
+        <v>9</v>
+      </c>
+      <c r="J115" s="1">
+        <v>1</v>
+      </c>
+      <c r="K115" s="1">
+        <v>100</v>
+      </c>
+      <c r="L115" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q115" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A116" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B116" s="1">
+        <v>4106</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D116" s="1">
+        <v>3</v>
+      </c>
+      <c r="E116" s="7">
+        <v>1106</v>
+      </c>
+      <c r="F116" s="1">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+      <c r="I116" s="1">
+        <v>9</v>
+      </c>
+      <c r="J116" s="1">
+        <v>1</v>
+      </c>
+      <c r="K116" s="1">
+        <v>100</v>
+      </c>
+      <c r="L116" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q116" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A117" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B117" s="1">
+        <v>4107</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D117" s="1">
+        <v>3</v>
+      </c>
+      <c r="E117" s="7">
+        <v>1107</v>
+      </c>
+      <c r="F117" s="1">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>9</v>
+      </c>
+      <c r="J117" s="1">
+        <v>1</v>
+      </c>
+      <c r="K117" s="1">
+        <v>100</v>
+      </c>
+      <c r="L117" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q117" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A118" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B118" s="1">
+        <v>4108</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D118" s="1">
+        <v>3</v>
+      </c>
+      <c r="E118" s="7">
+        <v>1108</v>
+      </c>
+      <c r="F118" s="1">
+        <v>1</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1">
+        <v>9</v>
+      </c>
+      <c r="J118" s="1">
+        <v>1</v>
+      </c>
+      <c r="K118" s="1">
+        <v>100</v>
+      </c>
+      <c r="L118" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q118" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A119" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B119" s="1">
+        <v>4109</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D119" s="1">
+        <v>3</v>
+      </c>
+      <c r="E119" s="7">
+        <v>1109</v>
+      </c>
+      <c r="F119" s="1">
+        <v>1</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1">
+        <v>9</v>
+      </c>
+      <c r="J119" s="1">
+        <v>1</v>
+      </c>
+      <c r="K119" s="1">
+        <v>100</v>
+      </c>
+      <c r="L119" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q119" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A120" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4110</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D120" s="1">
+        <v>3</v>
+      </c>
+      <c r="E120" s="7">
+        <v>1110</v>
+      </c>
+      <c r="F120" s="1">
+        <v>1</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+      <c r="H120" s="1">
+        <v>0</v>
+      </c>
+      <c r="I120" s="1">
+        <v>9</v>
+      </c>
+      <c r="J120" s="1">
+        <v>1</v>
+      </c>
+      <c r="K120" s="1">
+        <v>100</v>
+      </c>
+      <c r="L120" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q120" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A121" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B121" s="1">
+        <v>4111</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D121" s="1">
+        <v>3</v>
+      </c>
+      <c r="E121" s="7">
+        <v>1111</v>
+      </c>
+      <c r="F121" s="1">
+        <v>1</v>
+      </c>
+      <c r="G121" s="1">
+        <v>0</v>
+      </c>
+      <c r="H121" s="1">
+        <v>0</v>
+      </c>
+      <c r="I121" s="1">
+        <v>9</v>
+      </c>
+      <c r="J121" s="1">
+        <v>1</v>
+      </c>
+      <c r="K121" s="1">
+        <v>100</v>
+      </c>
+      <c r="L121" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q121" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A122" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B122" s="1">
+        <v>4112</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D122" s="1">
+        <v>3</v>
+      </c>
+      <c r="E122" s="7">
+        <v>1112</v>
+      </c>
+      <c r="F122" s="1">
+        <v>1</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
+      <c r="I122" s="1">
+        <v>9</v>
+      </c>
+      <c r="J122" s="1">
+        <v>1</v>
+      </c>
+      <c r="K122" s="1">
+        <v>100</v>
+      </c>
+      <c r="L122" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q122" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A123" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B123" s="1">
+        <v>4113</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D123" s="1">
+        <v>3</v>
+      </c>
+      <c r="E123" s="7">
+        <v>1113</v>
+      </c>
+      <c r="F123" s="1">
+        <v>1</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+      <c r="I123" s="1">
+        <v>9</v>
+      </c>
+      <c r="J123" s="1">
+        <v>1</v>
+      </c>
+      <c r="K123" s="1">
+        <v>100</v>
+      </c>
+      <c r="L123" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q123" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A124" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B124" s="1">
+        <v>4114</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D124" s="1">
+        <v>3</v>
+      </c>
+      <c r="E124" s="7">
+        <v>1114</v>
+      </c>
+      <c r="F124" s="1">
+        <v>1</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="1">
+        <v>9</v>
+      </c>
+      <c r="J124" s="1">
+        <v>1</v>
+      </c>
+      <c r="K124" s="1">
+        <v>100</v>
+      </c>
+      <c r="L124" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q124" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A125" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B125" s="1">
+        <v>4115</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D125" s="1">
+        <v>3</v>
+      </c>
+      <c r="E125" s="7">
+        <v>1115</v>
+      </c>
+      <c r="F125" s="1">
+        <v>1</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+      <c r="I125" s="1">
+        <v>9</v>
+      </c>
+      <c r="J125" s="1">
+        <v>1</v>
+      </c>
+      <c r="K125" s="1">
+        <v>100</v>
+      </c>
+      <c r="L125" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q125" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A126" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B126" s="1">
+        <v>4116</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D126" s="1">
+        <v>3</v>
+      </c>
+      <c r="E126" s="7">
+        <v>1116</v>
+      </c>
+      <c r="F126" s="1">
+        <v>1</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+      <c r="I126" s="1">
+        <v>9</v>
+      </c>
+      <c r="J126" s="1">
+        <v>1</v>
+      </c>
+      <c r="K126" s="1">
+        <v>100</v>
+      </c>
+      <c r="L126" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q126" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A127" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B127" s="1">
+        <v>4117</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D127" s="1">
+        <v>3</v>
+      </c>
+      <c r="E127" s="7">
+        <v>1117</v>
+      </c>
+      <c r="F127" s="1">
+        <v>1</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+      <c r="I127" s="1">
+        <v>9</v>
+      </c>
+      <c r="J127" s="1">
+        <v>1</v>
+      </c>
+      <c r="K127" s="1">
+        <v>100</v>
+      </c>
+      <c r="L127" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q127" s="8" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -547,10 +547,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>会生产鸡蛋的动物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -705,6 +701,10 @@
   </si>
   <si>
     <t>斑马狮子鱼</t>
+  </si>
+  <si>
+    <t>母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1313,13 +1313,13 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="1">
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -1349,21 +1349,21 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" s="1">
         <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="1">
         <v>-1</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
@@ -4430,7 +4430,7 @@
         <v>3000</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="D84" s="1">
         <v>11</v>
@@ -4460,18 +4460,18 @@
         <v>100</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B85" s="1">
         <v>4000</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D85" s="1">
         <v>3</v>
@@ -4501,18 +4501,18 @@
         <v>100</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A86" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B86" s="1">
         <v>4001</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D86" s="1">
         <v>3</v>
@@ -4542,18 +4542,18 @@
         <v>100</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A87" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B87" s="1">
         <v>4002</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
@@ -4583,18 +4583,18 @@
         <v>100</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A88" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B88" s="1">
         <v>4003</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D88" s="1">
         <v>3</v>
@@ -4624,18 +4624,18 @@
         <v>100</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A89" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B89" s="1">
         <v>4004</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D89" s="1">
         <v>3</v>
@@ -4665,18 +4665,18 @@
         <v>100</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A90" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B90" s="1">
         <v>4005</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D90" s="1">
         <v>3</v>
@@ -4706,18 +4706,18 @@
         <v>100</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A91" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B91" s="1">
         <v>4006</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D91" s="1">
         <v>3</v>
@@ -4747,18 +4747,18 @@
         <v>100</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A92" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B92" s="1">
         <v>4007</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D92" s="1">
         <v>3</v>
@@ -4788,18 +4788,18 @@
         <v>100</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A93" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B93" s="1">
         <v>4008</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D93" s="1">
         <v>3</v>
@@ -4829,18 +4829,18 @@
         <v>100</v>
       </c>
       <c r="Q93" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A94" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B94" s="1">
         <v>4009</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
@@ -4870,18 +4870,18 @@
         <v>100</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A95" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B95" s="1">
         <v>4010</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
@@ -4911,18 +4911,18 @@
         <v>100</v>
       </c>
       <c r="Q95" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A96" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B96" s="1">
         <v>4011</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
@@ -4952,18 +4952,18 @@
         <v>100</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A97" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B97" s="1">
         <v>4012</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
@@ -4993,18 +4993,18 @@
         <v>100</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A98" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B98" s="1">
         <v>4013</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D98" s="1">
         <v>3</v>
@@ -5034,18 +5034,18 @@
         <v>100</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A99" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B99" s="1">
         <v>4014</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D99" s="1">
         <v>3</v>
@@ -5075,18 +5075,18 @@
         <v>100</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A100" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B100" s="1">
         <v>4015</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D100" s="1">
         <v>3</v>
@@ -5116,18 +5116,18 @@
         <v>100</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A101" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B101" s="1">
         <v>4016</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D101" s="1">
         <v>3</v>
@@ -5157,18 +5157,18 @@
         <v>100</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A102" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B102" s="1">
         <v>4017</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D102" s="1">
         <v>3</v>
@@ -5198,18 +5198,18 @@
         <v>100</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A103" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B103" s="1">
         <v>4018</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D103" s="1">
         <v>3</v>
@@ -5239,18 +5239,18 @@
         <v>100</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A104" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B104" s="1">
         <v>4019</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D104" s="1">
         <v>3</v>
@@ -5280,18 +5280,18 @@
         <v>100</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A105" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B105" s="1">
         <v>4020</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D105" s="1">
         <v>3</v>
@@ -5321,18 +5321,18 @@
         <v>100</v>
       </c>
       <c r="Q105" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A106" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B106" s="1">
         <v>4021</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D106" s="1">
         <v>3</v>
@@ -5362,18 +5362,18 @@
         <v>100</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A107" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B107" s="1">
         <v>4022</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D107" s="1">
         <v>3</v>
@@ -5403,18 +5403,18 @@
         <v>100</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A108" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B108" s="1">
         <v>4023</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D108" s="1">
         <v>3</v>
@@ -5444,18 +5444,18 @@
         <v>100</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A109" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B109" s="1">
         <v>4024</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
@@ -5485,18 +5485,18 @@
         <v>100</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A110" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B110" s="1">
         <v>4100</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
@@ -5526,18 +5526,18 @@
         <v>100</v>
       </c>
       <c r="Q110" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A111" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B111" s="1">
         <v>4101</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D111" s="1">
         <v>3</v>
@@ -5567,18 +5567,18 @@
         <v>100</v>
       </c>
       <c r="Q111" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A112" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B112" s="1">
         <v>4102</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D112" s="1">
         <v>3</v>
@@ -5608,18 +5608,18 @@
         <v>100</v>
       </c>
       <c r="Q112" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A113" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B113" s="1">
         <v>4103</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
@@ -5649,18 +5649,18 @@
         <v>100</v>
       </c>
       <c r="Q113" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A114" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B114" s="1">
         <v>4104</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
@@ -5690,18 +5690,18 @@
         <v>100</v>
       </c>
       <c r="Q114" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A115" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B115" s="1">
         <v>4105</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D115" s="1">
         <v>3</v>
@@ -5731,18 +5731,18 @@
         <v>100</v>
       </c>
       <c r="Q115" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A116" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B116" s="1">
         <v>4106</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
@@ -5772,18 +5772,18 @@
         <v>100</v>
       </c>
       <c r="Q116" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A117" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B117" s="1">
         <v>4107</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D117" s="1">
         <v>3</v>
@@ -5813,18 +5813,18 @@
         <v>100</v>
       </c>
       <c r="Q117" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A118" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B118" s="1">
         <v>4108</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D118" s="1">
         <v>3</v>
@@ -5854,18 +5854,18 @@
         <v>100</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A119" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B119" s="1">
         <v>4109</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D119" s="1">
         <v>3</v>
@@ -5895,18 +5895,18 @@
         <v>100</v>
       </c>
       <c r="Q119" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A120" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B120" s="1">
         <v>4110</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
@@ -5936,18 +5936,18 @@
         <v>100</v>
       </c>
       <c r="Q120" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A121" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B121" s="1">
         <v>4111</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D121" s="1">
         <v>3</v>
@@ -5977,18 +5977,18 @@
         <v>100</v>
       </c>
       <c r="Q121" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A122" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B122" s="1">
         <v>4112</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D122" s="1">
         <v>3</v>
@@ -6018,18 +6018,18 @@
         <v>100</v>
       </c>
       <c r="Q122" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A123" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B123" s="1">
         <v>4113</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D123" s="1">
         <v>3</v>
@@ -6059,18 +6059,18 @@
         <v>100</v>
       </c>
       <c r="Q123" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A124" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B124" s="1">
         <v>4114</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D124" s="1">
         <v>3</v>
@@ -6100,18 +6100,18 @@
         <v>100</v>
       </c>
       <c r="Q124" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A125" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B125" s="1">
         <v>4115</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D125" s="1">
         <v>3</v>
@@ -6141,18 +6141,18 @@
         <v>100</v>
       </c>
       <c r="Q125" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A126" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B126" s="1">
         <v>4116</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
@@ -6182,18 +6182,18 @@
         <v>100</v>
       </c>
       <c r="Q126" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A127" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B127" s="1">
         <v>4117</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D127" s="1">
         <v>3</v>
@@ -6223,7 +6223,7 @@
         <v>100</v>
       </c>
       <c r="Q127" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="189">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -151,9 +151,6 @@
     <t>胡萝卜</t>
   </si>
   <si>
-    <t>大葱</t>
-  </si>
-  <si>
     <t>葡萄</t>
   </si>
   <si>
@@ -284,9 +281,6 @@
   </si>
   <si>
     <t>卷心菜种子</t>
-  </si>
-  <si>
-    <t>大葱种子</t>
   </si>
   <si>
     <t>萝卜种子</t>
@@ -704,6 +698,22 @@
   </si>
   <si>
     <t>母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葱种子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套蟹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套蟹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1184,7 +1194,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>13</v>
@@ -1196,7 +1206,7 @@
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
@@ -1231,13 +1241,13 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -1267,18 +1277,18 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -1308,18 +1318,18 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1">
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -1349,21 +1359,21 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B7" s="1">
         <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D7" s="1">
         <v>-1</v>
@@ -1393,12 +1403,12 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="3">
         <v>1001</v>
@@ -1442,7 +1452,7 @@
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="3">
         <v>1002</v>
@@ -1486,14 +1496,14 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="B10" s="3">
         <v>1003</v>
       </c>
       <c r="C10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>大葱_01</v>
+        <v>葱_01</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -1526,7 +1536,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3">
         <v>1004</v>
@@ -1566,7 +1576,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="3">
         <v>1005</v>
@@ -1606,7 +1616,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3">
         <v>1006</v>
@@ -1646,7 +1656,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3">
         <v>1007</v>
@@ -1686,7 +1696,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="3">
         <v>1008</v>
@@ -1766,7 +1776,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3">
         <v>1010</v>
@@ -1806,7 +1816,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="3">
         <v>1011</v>
@@ -1846,7 +1856,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="3">
         <v>1012</v>
@@ -1886,7 +1896,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" s="3">
         <v>1013</v>
@@ -1926,7 +1936,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3">
         <v>1014</v>
@@ -1966,7 +1976,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3">
         <v>1015</v>
@@ -2006,7 +2016,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3">
         <v>1016</v>
@@ -2046,7 +2056,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="3">
         <v>1017</v>
@@ -2125,7 +2135,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" s="3">
         <v>1019</v>
@@ -2164,7 +2174,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="3">
         <v>1020</v>
@@ -2203,7 +2213,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B28" s="3">
         <v>1021</v>
@@ -2242,7 +2252,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="3">
         <v>1022</v>
@@ -2281,7 +2291,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" s="3">
         <v>1023</v>
@@ -2320,7 +2330,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B31" s="3">
         <v>1024</v>
@@ -2359,7 +2369,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A32" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="3">
         <v>1025</v>
@@ -2398,7 +2408,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" s="3">
         <v>1026</v>
@@ -2437,7 +2447,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" s="3">
         <v>1027</v>
@@ -2476,7 +2486,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A35" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="3">
         <v>1028</v>
@@ -2515,14 +2525,14 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B36" s="3">
         <f>B8+100</f>
         <v>1101</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
@@ -2554,14 +2564,14 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" s="3">
         <f t="shared" ref="B37:B63" si="1">B9+100</f>
         <v>1102</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -2593,14 +2603,14 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="B38" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
@@ -2632,14 +2642,14 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B39" s="3">
         <f t="shared" si="1"/>
         <v>1104</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -2671,14 +2681,14 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40" s="3">
         <f t="shared" si="1"/>
         <v>1105</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
@@ -2710,14 +2720,14 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B41" s="3">
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -2749,14 +2759,14 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B42" s="3">
         <f t="shared" si="1"/>
         <v>1107</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -2788,14 +2798,14 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B43" s="3">
         <f t="shared" si="1"/>
         <v>1108</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -2827,14 +2837,14 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B44" s="3">
         <f t="shared" si="1"/>
         <v>1109</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
@@ -2866,14 +2876,14 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B45" s="3">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
@@ -2905,14 +2915,14 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B46" s="3">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
@@ -2944,14 +2954,14 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A47" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B47" s="3">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -2983,14 +2993,14 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A48" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B48" s="3">
         <f t="shared" si="1"/>
         <v>1113</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -3022,14 +3032,14 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A49" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B49" s="3">
         <f t="shared" si="1"/>
         <v>1114</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -3061,14 +3071,14 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A50" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B50" s="3">
         <f t="shared" si="1"/>
         <v>1115</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -3100,14 +3110,14 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A51" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B51" s="3">
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -3139,14 +3149,14 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B52" s="3">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -3178,14 +3188,14 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A53" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B53" s="3">
         <f t="shared" si="1"/>
         <v>1118</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -3217,14 +3227,14 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A54" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B54" s="3">
         <f t="shared" si="1"/>
         <v>1119</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -3256,14 +3266,14 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B55" s="3">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -3295,14 +3305,14 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3">
         <f t="shared" si="1"/>
         <v>1121</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -3334,14 +3344,14 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B57" s="3">
         <f t="shared" si="1"/>
         <v>1122</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
@@ -3373,14 +3383,14 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B58" s="3">
         <f t="shared" si="1"/>
         <v>1123</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
@@ -3412,14 +3422,14 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B59" s="3">
         <f t="shared" si="1"/>
         <v>1124</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
@@ -3451,14 +3461,14 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B60" s="3">
         <f t="shared" si="1"/>
         <v>1125</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
@@ -3490,14 +3500,14 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B61" s="3">
         <f t="shared" si="1"/>
         <v>1126</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
@@ -3529,14 +3539,14 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A62" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B62" s="3">
         <f t="shared" si="1"/>
         <v>1127</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -3568,14 +3578,14 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A63" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B63" s="3">
         <f t="shared" si="1"/>
         <v>1128</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
@@ -3607,13 +3617,13 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B64" s="1">
         <v>2000</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D64" s="1">
         <v>6</v>
@@ -3643,18 +3653,18 @@
         <v>100</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B65" s="1">
         <v>2001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D65" s="1">
         <v>6</v>
@@ -3684,12 +3694,12 @@
         <v>100</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B66" s="1">
         <v>2002</v>
@@ -3722,18 +3732,18 @@
         <v>100</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B67" s="1">
         <v>2003</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D67" s="1">
         <v>6</v>
@@ -3763,18 +3773,18 @@
         <v>100</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B68" s="1">
         <v>2100</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D68" s="1">
         <v>10</v>
@@ -3804,18 +3814,18 @@
         <v>100</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B69" s="1">
         <v>2101</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D69" s="1">
         <v>10</v>
@@ -3845,18 +3855,18 @@
         <v>100</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B70" s="1">
         <v>2102</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D70" s="1">
         <v>10</v>
@@ -3886,18 +3896,18 @@
         <v>100</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B71" s="1">
         <v>2103</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D71" s="1">
         <v>10</v>
@@ -3927,18 +3937,18 @@
         <v>100</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B72" s="1">
         <v>2104</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D72" s="1">
         <v>10</v>
@@ -3968,18 +3978,18 @@
         <v>100</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B73" s="1">
         <v>2105</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D73" s="1">
         <v>10</v>
@@ -4009,18 +4019,18 @@
         <v>100</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B74" s="1">
         <v>2106</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D74" s="1">
         <v>10</v>
@@ -4050,18 +4060,18 @@
         <v>100</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B75" s="1">
         <v>2107</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D75" s="1">
         <v>10</v>
@@ -4091,18 +4101,18 @@
         <v>100</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B76" s="1">
         <v>2108</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D76" s="1">
         <v>10</v>
@@ -4132,18 +4142,18 @@
         <v>100</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B77" s="1">
         <v>2109</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D77" s="1">
         <v>10</v>
@@ -4173,18 +4183,18 @@
         <v>100</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B78" s="1">
         <v>2110</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D78" s="1">
         <v>10</v>
@@ -4214,18 +4224,18 @@
         <v>100</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B79" s="1">
         <v>2111</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D79" s="1">
         <v>10</v>
@@ -4255,18 +4265,18 @@
         <v>100</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B80" s="1">
         <v>2112</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D80" s="1">
         <v>10</v>
@@ -4296,18 +4306,18 @@
         <v>100</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B81" s="1">
         <v>2113</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D81" s="1">
         <v>10</v>
@@ -4337,18 +4347,18 @@
         <v>100</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B82" s="1">
         <v>2200</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D82" s="1">
         <v>10</v>
@@ -4378,18 +4388,18 @@
         <v>100</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B83" s="1">
         <v>2201</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D83" s="1">
         <v>10</v>
@@ -4419,18 +4429,18 @@
         <v>100</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B84" s="1">
         <v>3000</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D84" s="1">
         <v>11</v>
@@ -4460,18 +4470,18 @@
         <v>100</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="85" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B85" s="1">
         <v>4000</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D85" s="1">
         <v>3</v>
@@ -4501,18 +4511,18 @@
         <v>100</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A86" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B86" s="1">
         <v>4001</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D86" s="1">
         <v>3</v>
@@ -4542,18 +4552,18 @@
         <v>100</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A87" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B87" s="1">
         <v>4002</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
@@ -4583,18 +4593,18 @@
         <v>100</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A88" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B88" s="1">
         <v>4003</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D88" s="1">
         <v>3</v>
@@ -4624,18 +4634,18 @@
         <v>100</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A89" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B89" s="1">
         <v>4004</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D89" s="1">
         <v>3</v>
@@ -4665,18 +4675,18 @@
         <v>100</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A90" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B90" s="1">
         <v>4005</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D90" s="1">
         <v>3</v>
@@ -4706,18 +4716,18 @@
         <v>100</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A91" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B91" s="1">
         <v>4006</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D91" s="1">
         <v>3</v>
@@ -4747,18 +4757,18 @@
         <v>100</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A92" s="7" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="B92" s="1">
         <v>4007</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="D92" s="1">
         <v>3</v>
@@ -4788,18 +4798,18 @@
         <v>100</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A93" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B93" s="1">
         <v>4008</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D93" s="1">
         <v>3</v>
@@ -4829,18 +4839,18 @@
         <v>100</v>
       </c>
       <c r="Q93" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A94" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B94" s="1">
         <v>4009</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
@@ -4870,18 +4880,18 @@
         <v>100</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A95" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B95" s="1">
         <v>4010</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
@@ -4911,18 +4921,18 @@
         <v>100</v>
       </c>
       <c r="Q95" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A96" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B96" s="1">
         <v>4011</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
@@ -4952,18 +4962,18 @@
         <v>100</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A97" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B97" s="1">
         <v>4012</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
@@ -4993,18 +5003,18 @@
         <v>100</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A98" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B98" s="1">
         <v>4013</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D98" s="1">
         <v>3</v>
@@ -5034,18 +5044,18 @@
         <v>100</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A99" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B99" s="1">
         <v>4014</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D99" s="1">
         <v>3</v>
@@ -5075,18 +5085,18 @@
         <v>100</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A100" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B100" s="1">
         <v>4015</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D100" s="1">
         <v>3</v>
@@ -5116,18 +5126,18 @@
         <v>100</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A101" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B101" s="1">
         <v>4016</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D101" s="1">
         <v>3</v>
@@ -5157,18 +5167,18 @@
         <v>100</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A102" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B102" s="1">
         <v>4017</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D102" s="1">
         <v>3</v>
@@ -5198,18 +5208,18 @@
         <v>100</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A103" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B103" s="1">
         <v>4018</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D103" s="1">
         <v>3</v>
@@ -5239,18 +5249,18 @@
         <v>100</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A104" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B104" s="1">
         <v>4019</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D104" s="1">
         <v>3</v>
@@ -5280,18 +5290,18 @@
         <v>100</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A105" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B105" s="1">
         <v>4020</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D105" s="1">
         <v>3</v>
@@ -5321,18 +5331,18 @@
         <v>100</v>
       </c>
       <c r="Q105" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A106" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B106" s="1">
         <v>4021</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D106" s="1">
         <v>3</v>
@@ -5362,18 +5372,18 @@
         <v>100</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A107" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B107" s="1">
         <v>4022</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D107" s="1">
         <v>3</v>
@@ -5403,18 +5413,18 @@
         <v>100</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A108" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B108" s="1">
         <v>4023</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D108" s="1">
         <v>3</v>
@@ -5444,18 +5454,18 @@
         <v>100</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A109" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B109" s="1">
         <v>4024</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
@@ -5485,18 +5495,18 @@
         <v>100</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A110" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B110" s="1">
         <v>4100</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
@@ -5526,18 +5536,18 @@
         <v>100</v>
       </c>
       <c r="Q110" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A111" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B111" s="1">
         <v>4101</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D111" s="1">
         <v>3</v>
@@ -5567,18 +5577,18 @@
         <v>100</v>
       </c>
       <c r="Q111" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A112" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B112" s="1">
         <v>4102</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D112" s="1">
         <v>3</v>
@@ -5608,18 +5618,18 @@
         <v>100</v>
       </c>
       <c r="Q112" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A113" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B113" s="1">
         <v>4103</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
@@ -5649,18 +5659,18 @@
         <v>100</v>
       </c>
       <c r="Q113" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A114" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B114" s="1">
         <v>4104</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
@@ -5690,18 +5700,18 @@
         <v>100</v>
       </c>
       <c r="Q114" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A115" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B115" s="1">
         <v>4105</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D115" s="1">
         <v>3</v>
@@ -5731,18 +5741,18 @@
         <v>100</v>
       </c>
       <c r="Q115" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A116" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B116" s="1">
         <v>4106</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
@@ -5772,18 +5782,18 @@
         <v>100</v>
       </c>
       <c r="Q116" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A117" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B117" s="1">
         <v>4107</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D117" s="1">
         <v>3</v>
@@ -5813,18 +5823,18 @@
         <v>100</v>
       </c>
       <c r="Q117" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A118" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B118" s="1">
         <v>4108</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D118" s="1">
         <v>3</v>
@@ -5854,18 +5864,18 @@
         <v>100</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A119" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B119" s="1">
         <v>4109</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D119" s="1">
         <v>3</v>
@@ -5895,18 +5905,18 @@
         <v>100</v>
       </c>
       <c r="Q119" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A120" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B120" s="1">
         <v>4110</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
@@ -5936,18 +5946,18 @@
         <v>100</v>
       </c>
       <c r="Q120" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A121" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B121" s="1">
         <v>4111</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D121" s="1">
         <v>3</v>
@@ -5977,18 +5987,18 @@
         <v>100</v>
       </c>
       <c r="Q121" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A122" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B122" s="1">
         <v>4112</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D122" s="1">
         <v>3</v>
@@ -6018,18 +6028,18 @@
         <v>100</v>
       </c>
       <c r="Q122" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A123" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B123" s="1">
         <v>4113</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D123" s="1">
         <v>3</v>
@@ -6059,18 +6069,18 @@
         <v>100</v>
       </c>
       <c r="Q123" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A124" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B124" s="1">
         <v>4114</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D124" s="1">
         <v>3</v>
@@ -6100,18 +6110,18 @@
         <v>100</v>
       </c>
       <c r="Q124" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A125" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B125" s="1">
         <v>4115</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D125" s="1">
         <v>3</v>
@@ -6141,18 +6151,18 @@
         <v>100</v>
       </c>
       <c r="Q125" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A126" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B126" s="1">
         <v>4116</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
@@ -6182,18 +6192,18 @@
         <v>100</v>
       </c>
       <c r="Q126" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A127" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B127" s="1">
         <v>4117</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D127" s="1">
         <v>3</v>
@@ -6223,7 +6233,7 @@
         <v>100</v>
       </c>
       <c r="Q127" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -766,12 +766,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -788,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -813,6 +819,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2563,7 +2572,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B37" s="3">
@@ -2641,7 +2650,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="9" t="s">
         <v>64</v>
       </c>
       <c r="B39" s="3">
@@ -2719,7 +2728,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B41" s="3">
@@ -2758,7 +2767,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="9" t="s">
         <v>67</v>
       </c>
       <c r="B42" s="3">
@@ -2797,7 +2806,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="9" t="s">
         <v>68</v>
       </c>
       <c r="B43" s="3">
@@ -2836,7 +2845,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="9" t="s">
         <v>69</v>
       </c>
       <c r="B44" s="3">
@@ -2875,7 +2884,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="9" t="s">
         <v>70</v>
       </c>
       <c r="B45" s="3">
@@ -2914,7 +2923,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="9" t="s">
         <v>71</v>
       </c>
       <c r="B46" s="3">
@@ -2992,7 +3001,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B48" s="3">
@@ -3070,7 +3079,7 @@
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="9" t="s">
         <v>75</v>
       </c>
       <c r="B50" s="3">
@@ -3109,7 +3118,7 @@
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="9" t="s">
         <v>76</v>
       </c>
       <c r="B51" s="3">
@@ -3187,7 +3196,7 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B53" s="3">
@@ -3226,7 +3235,7 @@
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="9" t="s">
         <v>79</v>
       </c>
       <c r="B54" s="3">
@@ -3265,7 +3274,7 @@
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="9" t="s">
         <v>80</v>
       </c>
       <c r="B55" s="3">
@@ -3343,7 +3352,7 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="9" t="s">
         <v>82</v>
       </c>
       <c r="B57" s="3">
@@ -3460,7 +3469,7 @@
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="9" t="s">
         <v>85</v>
       </c>
       <c r="B60" s="3">
@@ -3499,7 +3508,7 @@
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B61" s="3">
@@ -3538,7 +3547,7 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="9" t="s">
         <v>87</v>
       </c>
       <c r="B62" s="3">
@@ -3577,7 +3586,7 @@
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B63" s="3">

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="193">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -714,6 +714,22 @@
   </si>
   <si>
     <t>手套蟹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼竿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼饵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来引诱鱼类的饵料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂钓工具</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1128,7 +1144,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q127"/>
+  <dimension ref="A2:Q129"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -1376,99 +1392,96 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="1">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>19</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="1">
-        <v>100</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B8" s="1">
+        <v>100</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D8" s="1">
         <v>-1</v>
       </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
         <v>29</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1" t="s">
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1001</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>A8&amp;"_01"</f>
-        <v>芜菁_01</v>
-      </c>
-      <c r="D8" s="1">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>29</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>100</v>
-      </c>
-      <c r="L8" s="1">
-        <v>100</v>
-      </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C9" s="3" t="str">
-        <f t="shared" ref="C9:C35" si="0">A9&amp;"_01"</f>
-        <v>卷心菜_01</v>
+        <f>A9&amp;"_01"</f>
+        <v>芜菁_01</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -1503,1054 +1516,1059 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <f t="shared" ref="C10:C36" si="0">A10&amp;"_01"</f>
+        <v>卷心菜_01</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>29</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>100</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B11" s="3">
         <v>1003</v>
       </c>
-      <c r="C10" s="3" t="str">
+      <c r="C11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>葱_01</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
         <v>29</v>
       </c>
-      <c r="J10" s="3">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>100</v>
-      </c>
-      <c r="L10" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A11" s="5" t="s">
+      <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B12" s="3">
         <v>1004</v>
       </c>
-      <c r="C11" s="3" t="str">
+      <c r="C12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>萝卜_01</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
         <v>29</v>
       </c>
-      <c r="J11" s="3">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>100</v>
-      </c>
-      <c r="L11" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
+      <c r="J12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B13" s="3">
         <v>1005</v>
       </c>
-      <c r="C12" s="3" t="str">
+      <c r="C13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>紫甘蓝_01</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
         <v>29</v>
       </c>
-      <c r="J12" s="3">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>100</v>
-      </c>
-      <c r="L12" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
+      <c r="J13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B14" s="3">
         <v>1006</v>
       </c>
-      <c r="C13" s="3" t="str">
+      <c r="C14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>黄瓜_01</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D14" s="1">
         <v>5</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>29</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>100</v>
-      </c>
-      <c r="L13" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B15" s="3">
         <v>1007</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西兰花_01</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D15" s="1">
         <v>5</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>29</v>
       </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>100</v>
-      </c>
-      <c r="L14" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B16" s="3">
         <v>1008</v>
       </c>
-      <c r="C15" s="3" t="str">
+      <c r="C16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>番茄_01</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D16" s="1">
         <v>5</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
         <v>29</v>
       </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-      <c r="L15" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B17" s="3">
         <v>1009</v>
       </c>
-      <c r="C16" s="3" t="str">
+      <c r="C17" s="3" t="str">
         <f t="shared" si="0"/>
         <v>胡萝卜_01</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>29</v>
       </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-      <c r="L16" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A17" s="5" t="s">
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B18" s="3">
         <v>1010</v>
       </c>
-      <c r="C17" s="3" t="str">
+      <c r="C18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西瓜_01</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>29</v>
       </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-      <c r="L17" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B19" s="3">
         <v>1011</v>
       </c>
-      <c r="C18" s="3" t="str">
+      <c r="C19" s="3" t="str">
         <f t="shared" si="0"/>
         <v>辣椒_01</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D19" s="1">
         <v>5</v>
       </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
         <v>29</v>
       </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
-      </c>
-      <c r="L18" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A19" s="5" t="s">
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>1012</v>
       </c>
-      <c r="C19" s="3" t="str">
+      <c r="C20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>奇异果_01</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>5</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>29</v>
       </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B21" s="3">
         <v>1013</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>茄子_01</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>5</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>29</v>
       </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B22" s="3">
         <v>1014</v>
       </c>
-      <c r="C21" s="3" t="str">
+      <c r="C22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>豌豆_01</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>29</v>
       </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B23" s="3">
         <v>1015</v>
       </c>
-      <c r="C22" s="3" t="str">
+      <c r="C23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>土豆_01</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D23" s="1">
         <v>5</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>29</v>
       </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="s">
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B24" s="3">
         <v>1016</v>
       </c>
-      <c r="C23" s="3" t="str">
+      <c r="C24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大蒜_01</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>29</v>
       </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-      <c r="L23" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="5"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B25" s="3">
         <v>1017</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>芦笋_01</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25" s="1">
         <v>5</v>
       </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
         <v>29</v>
       </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q24" s="5"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A25" s="5" t="s">
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B26" s="3">
         <v>1018</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C26" s="3" t="str">
         <f t="shared" si="0"/>
         <v>南瓜_01</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26" s="1">
         <v>5</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>29</v>
       </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B27" s="3">
         <v>1019</v>
       </c>
-      <c r="C26" s="3" t="str">
+      <c r="C27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>玉米_01</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>5</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>29</v>
       </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>100</v>
-      </c>
-      <c r="L26" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A27" s="5" t="s">
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>1020</v>
       </c>
-      <c r="C27" s="3" t="str">
+      <c r="C28" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大麦_01</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28" s="1">
         <v>5</v>
       </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
         <v>29</v>
       </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>100</v>
-      </c>
-      <c r="L27" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>1021</v>
       </c>
-      <c r="C28" s="3" t="str">
+      <c r="C29" s="3" t="str">
         <f t="shared" si="0"/>
         <v>啤酒花_01</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D29" s="1">
         <v>5</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>29</v>
       </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>100</v>
-      </c>
-      <c r="L28" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>1022</v>
       </c>
-      <c r="C29" s="3" t="str">
+      <c r="C30" s="3" t="str">
         <f t="shared" si="0"/>
         <v>葡萄_01</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30" s="1">
         <v>5</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
         <v>29</v>
       </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>100</v>
-      </c>
-      <c r="L29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>1023</v>
       </c>
-      <c r="C30" s="3" t="str">
+      <c r="C31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>菠萝_01</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="1">
         <v>5</v>
       </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
         <v>29</v>
       </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>100</v>
-      </c>
-      <c r="L30" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <v>1024</v>
       </c>
-      <c r="C31" s="3" t="str">
+      <c r="C32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>咖啡_01</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>5</v>
       </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>29</v>
       </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>100</v>
-      </c>
-      <c r="L31" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <v>1025</v>
       </c>
-      <c r="C32" s="3" t="str">
+      <c r="C33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>草莓_01</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D33" s="1">
         <v>5</v>
       </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>29</v>
       </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>100</v>
-      </c>
-      <c r="L32" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A33" s="5" t="s">
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B34" s="3">
         <v>1026</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C34" s="3" t="str">
         <f t="shared" si="0"/>
         <v>蓝莓_01</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
         <v>29</v>
       </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>100</v>
-      </c>
-      <c r="L33" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A34" s="5" t="s">
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B35" s="3">
         <v>1027</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C35" s="3" t="str">
         <f t="shared" si="0"/>
         <v>红薯_01</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>29</v>
       </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>100</v>
-      </c>
-      <c r="L34" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A35" s="5" t="s">
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A36" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B36" s="3">
         <v>1028</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C36" s="3" t="str">
         <f t="shared" si="0"/>
         <v>甜菜_01</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D36" s="1">
         <v>5</v>
       </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>29</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>100</v>
-      </c>
-      <c r="L35" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A36" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" s="3">
-        <f>B8+100</f>
-        <v>1101</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
       <c r="E36" s="1">
-        <v>8001</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -2572,21 +2590,21 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A37" s="9" t="s">
-        <v>63</v>
+      <c r="A37" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="B37" s="3">
-        <f t="shared" ref="B37:B63" si="1">B9+100</f>
-        <v>1102</v>
+        <f>B9+100</f>
+        <v>1101</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2611,1047 +2629,1048 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="3">
+        <f t="shared" ref="B38:B64" si="1">B10+100</f>
+        <v>1102</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>8002</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>29</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A39" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B39" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
         <v>8003</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3">
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
         <v>29</v>
       </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>100</v>
-      </c>
-      <c r="L38" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A39" s="9" t="s">
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B40" s="3">
         <f t="shared" si="1"/>
         <v>1104</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
         <v>8004</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3">
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
         <v>29</v>
       </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>100</v>
-      </c>
-      <c r="L39" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A40" s="5" t="s">
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A41" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B41" s="3">
         <f t="shared" si="1"/>
         <v>1105</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
         <v>8005</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>29</v>
       </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>100</v>
-      </c>
-      <c r="L40" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A41" s="9" t="s">
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A42" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B42" s="3">
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
         <v>8006</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>29</v>
       </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A42" s="9" t="s">
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A43" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B43" s="3">
         <f t="shared" si="1"/>
         <v>1107</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="1">
-        <v>0</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
         <v>8007</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>29</v>
       </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>100</v>
-      </c>
-      <c r="L42" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A43" s="9" t="s">
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A44" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B44" s="3">
         <f t="shared" si="1"/>
         <v>1108</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D43" s="1">
-        <v>0</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
         <v>8008</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
         <v>29</v>
       </c>
-      <c r="J43" s="1">
-        <v>1</v>
-      </c>
-      <c r="K43" s="1">
-        <v>100</v>
-      </c>
-      <c r="L43" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A44" s="9" t="s">
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A45" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B45" s="3">
         <f t="shared" si="1"/>
         <v>1109</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
         <v>8009</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>29</v>
       </c>
-      <c r="J44" s="1">
-        <v>1</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A45" s="9" t="s">
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100</v>
+      </c>
+      <c r="L45" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A46" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B46" s="3">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
         <v>8010</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
         <v>29</v>
       </c>
-      <c r="J45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1">
-        <v>100</v>
-      </c>
-      <c r="L45" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A46" s="9" t="s">
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>100</v>
+      </c>
+      <c r="L46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A47" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B47" s="3">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="1">
-        <v>0</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
         <v>8011</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>29</v>
       </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1">
-        <v>100</v>
-      </c>
-      <c r="L46" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A47" s="5" t="s">
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+      <c r="L47" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B48" s="3">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
         <v>8012</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
         <v>29</v>
       </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>100</v>
-      </c>
-      <c r="L47" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A48" s="9" t="s">
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+      <c r="L48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A49" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B49" s="3">
         <f t="shared" si="1"/>
         <v>1113</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
         <v>8013</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>29</v>
       </c>
-      <c r="J48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>100</v>
-      </c>
-      <c r="L48" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A49" s="5" t="s">
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B50" s="3">
         <f t="shared" si="1"/>
         <v>1114</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
         <v>8014</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
         <v>29</v>
       </c>
-      <c r="J49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1">
-        <v>100</v>
-      </c>
-      <c r="L49" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A50" s="9" t="s">
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A51" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B51" s="3">
         <f t="shared" si="1"/>
         <v>1115</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
         <v>8015</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3">
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
         <v>29</v>
       </c>
-      <c r="J50" s="1">
-        <v>1</v>
-      </c>
-      <c r="K50" s="1">
-        <v>100</v>
-      </c>
-      <c r="L50" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A51" s="9" t="s">
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+      <c r="L51" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A52" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B52" s="3">
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
         <v>8016</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3">
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>29</v>
       </c>
-      <c r="J51" s="1">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>100</v>
-      </c>
-      <c r="L51" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A52" s="5" t="s">
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>100</v>
+      </c>
+      <c r="L52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A53" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B53" s="3">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
         <v>8017</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
         <v>29</v>
       </c>
-      <c r="J52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>100</v>
-      </c>
-      <c r="L52" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A53" s="9" t="s">
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1">
+        <v>100</v>
+      </c>
+      <c r="L53" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A54" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B54" s="3">
         <f t="shared" si="1"/>
         <v>1118</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
         <v>8018</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3">
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
         <v>29</v>
       </c>
-      <c r="J53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1">
-        <v>100</v>
-      </c>
-      <c r="L53" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A54" s="9" t="s">
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>100</v>
+      </c>
+      <c r="L54" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A55" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B55" s="3">
         <f t="shared" si="1"/>
         <v>1119</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
         <v>8019</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
         <v>29</v>
       </c>
-      <c r="J54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>100</v>
-      </c>
-      <c r="L54" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A55" s="9" t="s">
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>100</v>
+      </c>
+      <c r="L55" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A56" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B56" s="3">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
         <v>8020</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3">
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
         <v>29</v>
       </c>
-      <c r="J55" s="1">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1">
-        <v>100</v>
-      </c>
-      <c r="L55" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A56" s="5" t="s">
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="1">
+        <v>100</v>
+      </c>
+      <c r="L56" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A57" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B57" s="3">
         <f t="shared" si="1"/>
         <v>1121</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
         <v>8021</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="3">
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>29</v>
       </c>
-      <c r="J56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>100</v>
-      </c>
-      <c r="L56" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A57" s="9" t="s">
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="1">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A58" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B58" s="3">
         <f t="shared" si="1"/>
         <v>1122</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
         <v>8022</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>29</v>
       </c>
-      <c r="J57" s="1">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1">
-        <v>100</v>
-      </c>
-      <c r="L57" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A58" s="5" t="s">
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A59" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B59" s="3">
         <f t="shared" si="1"/>
         <v>1123</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
         <v>8023</v>
       </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>29</v>
       </c>
-      <c r="J58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>100</v>
-      </c>
-      <c r="L58" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A59" s="5" t="s">
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B60" s="3">
         <f t="shared" si="1"/>
         <v>1124</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
         <v>8024</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
         <v>29</v>
       </c>
-      <c r="J59" s="1">
-        <v>1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>100</v>
-      </c>
-      <c r="L59" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A60" s="9" t="s">
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="1">
+        <v>100</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A61" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B61" s="3">
         <f t="shared" si="1"/>
         <v>1125</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
         <v>8025</v>
       </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>29</v>
       </c>
-      <c r="J60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1">
-        <v>100</v>
-      </c>
-      <c r="L60" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A61" s="9" t="s">
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="1">
+        <v>100</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A62" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B62" s="3">
         <f t="shared" si="1"/>
         <v>1126</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
         <v>8026</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>29</v>
       </c>
-      <c r="J61" s="1">
-        <v>1</v>
-      </c>
-      <c r="K61" s="1">
-        <v>100</v>
-      </c>
-      <c r="L61" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A62" s="9" t="s">
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="1">
+        <v>100</v>
+      </c>
+      <c r="L62" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A63" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B63" s="3">
         <f t="shared" si="1"/>
         <v>1127</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="1">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1">
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
         <v>8027</v>
       </c>
-      <c r="F62" s="1">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0</v>
-      </c>
-      <c r="H62" s="1">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
         <v>29</v>
       </c>
-      <c r="J62" s="1">
-        <v>1</v>
-      </c>
-      <c r="K62" s="1">
-        <v>100</v>
-      </c>
-      <c r="L62" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A63" s="9" t="s">
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="1">
+        <v>100</v>
+      </c>
+      <c r="L63" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A64" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B64" s="3">
         <f t="shared" si="1"/>
         <v>1128</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
         <v>8028</v>
       </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0</v>
-      </c>
-      <c r="H63" s="1">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3">
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3">
         <v>29</v>
       </c>
-      <c r="J63" s="1">
-        <v>1</v>
-      </c>
-      <c r="K63" s="1">
-        <v>100</v>
-      </c>
-      <c r="L63" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A64" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B64" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D64" s="1">
-        <v>6</v>
-      </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
-      <c r="F64" s="1">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1">
-        <v>0</v>
-      </c>
-      <c r="I64" s="1">
-        <v>1</v>
-      </c>
       <c r="J64" s="1">
         <v>1</v>
       </c>
@@ -3660,20 +3679,17 @@
       </c>
       <c r="L64" s="1">
         <v>100</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65" s="1">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D65" s="1">
         <v>6</v>
@@ -3685,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -3703,15 +3719,18 @@
         <v>100</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B66" s="1">
-        <v>2002</v>
+        <v>2001</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D66" s="1">
         <v>6</v>
@@ -3723,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -3741,18 +3760,15 @@
         <v>100</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B67" s="1">
-        <v>2003</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>37</v>
+        <v>2002</v>
       </c>
       <c r="D67" s="1">
         <v>6</v>
@@ -3782,24 +3798,24 @@
         <v>100</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="B68" s="1">
-        <v>2100</v>
+        <v>2003</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="D68" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E68" s="1">
-        <v>2100</v>
+        <v>1</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3823,24 +3839,24 @@
         <v>100</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="B69" s="1">
-        <v>2101</v>
+        <v>2004</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="D69" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E69" s="1">
-        <v>2101</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3864,24 +3880,24 @@
         <v>100</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B70" s="1">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D70" s="1">
         <v>10</v>
       </c>
       <c r="E70" s="1">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3905,24 +3921,24 @@
         <v>100</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B71" s="1">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D71" s="1">
         <v>10</v>
       </c>
       <c r="E71" s="1">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3946,24 +3962,24 @@
         <v>100</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B72" s="1">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D72" s="1">
         <v>10</v>
       </c>
       <c r="E72" s="1">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3987,24 +4003,24 @@
         <v>100</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B73" s="1">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D73" s="1">
         <v>10</v>
       </c>
       <c r="E73" s="1">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4028,24 +4044,24 @@
         <v>100</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B74" s="1">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D74" s="1">
         <v>10</v>
       </c>
       <c r="E74" s="1">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4069,24 +4085,24 @@
         <v>100</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B75" s="1">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D75" s="1">
         <v>10</v>
       </c>
       <c r="E75" s="1">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -4110,24 +4126,24 @@
         <v>100</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B76" s="1">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76" s="1">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4151,24 +4167,24 @@
         <v>100</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B77" s="1">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D77" s="1">
         <v>10</v>
       </c>
       <c r="E77" s="1">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4192,24 +4208,24 @@
         <v>100</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B78" s="1">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D78" s="1">
         <v>10</v>
       </c>
       <c r="E78" s="1">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4233,24 +4249,24 @@
         <v>100</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B79" s="1">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D79" s="1">
         <v>10</v>
       </c>
       <c r="E79" s="1">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4274,24 +4290,24 @@
         <v>100</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B80" s="1">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D80" s="1">
         <v>10</v>
       </c>
       <c r="E80" s="1">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4315,24 +4331,24 @@
         <v>100</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B81" s="1">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D81" s="1">
         <v>10</v>
       </c>
       <c r="E81" s="1">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4356,24 +4372,24 @@
         <v>100</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B82" s="1">
-        <v>2200</v>
+        <v>2112</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D82" s="1">
         <v>10</v>
       </c>
       <c r="E82" s="1">
-        <v>2200</v>
+        <v>2112</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4397,24 +4413,24 @@
         <v>100</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B83" s="1">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D83" s="1">
         <v>10</v>
       </c>
       <c r="E83" s="1">
-        <v>2201</v>
+        <v>2113</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4438,147 +4454,147 @@
         <v>100</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="1">
+        <v>2200</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D84" s="1">
+        <v>10</v>
+      </c>
+      <c r="E84" s="1">
+        <v>2200</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>1</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+      <c r="K84" s="1">
+        <v>100</v>
+      </c>
+      <c r="L84" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q84" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A85" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B85" s="1">
+        <v>2201</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D85" s="1">
+        <v>10</v>
+      </c>
+      <c r="E85" s="1">
+        <v>2201</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1">
+        <v>1</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1</v>
+      </c>
+      <c r="K85" s="1">
+        <v>100</v>
+      </c>
+      <c r="L85" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q85" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A86" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B86" s="1">
         <v>3000</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D86" s="1">
         <v>11</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E86" s="1">
         <v>3000</v>
       </c>
-      <c r="F84" s="1">
-        <v>0</v>
-      </c>
-      <c r="G84" s="1">
-        <v>0</v>
-      </c>
-      <c r="H84" s="1">
-        <v>0</v>
-      </c>
-      <c r="I84" s="1">
-        <v>1</v>
-      </c>
-      <c r="J84" s="1">
-        <v>1</v>
-      </c>
-      <c r="K84" s="1">
-        <v>100</v>
-      </c>
-      <c r="L84" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q84" s="1" t="s">
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1</v>
+      </c>
+      <c r="K86" s="1">
+        <v>100</v>
+      </c>
+      <c r="L86" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q86" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
+    <row r="87" spans="1:17" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B87" s="1">
         <v>4000</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C87" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="D85" s="1">
-        <v>3</v>
-      </c>
-      <c r="E85" s="7">
-        <v>1000</v>
-      </c>
-      <c r="F85" s="1">
-        <v>1</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0</v>
-      </c>
-      <c r="H85" s="1">
-        <v>0</v>
-      </c>
-      <c r="I85" s="1">
-        <v>9</v>
-      </c>
-      <c r="J85" s="1">
-        <v>1</v>
-      </c>
-      <c r="K85" s="1">
-        <v>100</v>
-      </c>
-      <c r="L85" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q85" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A86" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B86" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D86" s="1">
-        <v>3</v>
-      </c>
-      <c r="E86" s="7">
-        <v>1001</v>
-      </c>
-      <c r="F86" s="1">
-        <v>1</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0</v>
-      </c>
-      <c r="H86" s="1">
-        <v>0</v>
-      </c>
-      <c r="I86" s="1">
-        <v>9</v>
-      </c>
-      <c r="J86" s="1">
-        <v>1</v>
-      </c>
-      <c r="K86" s="1">
-        <v>100</v>
-      </c>
-      <c r="L86" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q86" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A87" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B87" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
       </c>
       <c r="E87" s="7">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="F87" s="1">
         <v>1</v>
@@ -4601,25 +4617,25 @@
       <c r="L87" s="1">
         <v>100</v>
       </c>
-      <c r="Q87" s="7" t="s">
-        <v>144</v>
+      <c r="Q87" s="6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A88" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B88" s="1">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D88" s="1">
         <v>3</v>
       </c>
       <c r="E88" s="7">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F88" s="1">
         <v>1</v>
@@ -4643,7 +4659,7 @@
         <v>100</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.15">
@@ -4651,7 +4667,7 @@
         <v>144</v>
       </c>
       <c r="B89" s="1">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>144</v>
@@ -4660,7 +4676,7 @@
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="F89" s="1">
         <v>1</v>
@@ -4689,19 +4705,19 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A90" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B90" s="1">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D90" s="1">
         <v>3</v>
       </c>
       <c r="E90" s="7">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
@@ -4725,24 +4741,24 @@
         <v>100</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A91" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B91" s="1">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D91" s="1">
         <v>3</v>
       </c>
       <c r="E91" s="7">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="F91" s="1">
         <v>1</v>
@@ -4766,24 +4782,24 @@
         <v>100</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A92" s="7" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="B92" s="1">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="D92" s="1">
         <v>3</v>
       </c>
       <c r="E92" s="7">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
@@ -4807,24 +4823,24 @@
         <v>100</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A93" s="8" t="s">
-        <v>149</v>
+      <c r="A93" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="B93" s="1">
-        <v>4008</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>149</v>
+        <v>4006</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="D93" s="1">
         <v>3</v>
       </c>
       <c r="E93" s="7">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="F93" s="1">
         <v>1</v>
@@ -4847,25 +4863,25 @@
       <c r="L93" s="1">
         <v>100</v>
       </c>
-      <c r="Q93" s="8" t="s">
-        <v>149</v>
+      <c r="Q93" s="7" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A94" s="7" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="B94" s="1">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
       </c>
       <c r="E94" s="7">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="F94" s="1">
         <v>1</v>
@@ -4889,24 +4905,24 @@
         <v>100</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A95" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B95" s="1">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" s="7">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F95" s="1">
         <v>1</v>
@@ -4930,24 +4946,24 @@
         <v>100</v>
       </c>
       <c r="Q95" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A96" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B96" s="1">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96" s="7">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="F96" s="1">
         <v>1</v>
@@ -4971,24 +4987,24 @@
         <v>100</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A97" s="7" t="s">
-        <v>153</v>
+      <c r="A97" s="8" t="s">
+        <v>151</v>
       </c>
       <c r="B97" s="1">
-        <v>4012</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>153</v>
+        <v>4010</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>151</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
       </c>
       <c r="E97" s="7">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
@@ -5011,25 +5027,25 @@
       <c r="L97" s="1">
         <v>100</v>
       </c>
-      <c r="Q97" s="7" t="s">
-        <v>153</v>
+      <c r="Q97" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A98" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B98" s="1">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D98" s="1">
         <v>3</v>
       </c>
       <c r="E98" s="7">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="F98" s="1">
         <v>1</v>
@@ -5053,24 +5069,24 @@
         <v>100</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A99" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B99" s="1">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D99" s="1">
         <v>3</v>
       </c>
       <c r="E99" s="7">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
@@ -5094,24 +5110,24 @@
         <v>100</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A100" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B100" s="1">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D100" s="1">
         <v>3</v>
       </c>
       <c r="E100" s="7">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -5135,24 +5151,24 @@
         <v>100</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A101" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B101" s="1">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D101" s="1">
         <v>3</v>
       </c>
       <c r="E101" s="7">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
@@ -5176,24 +5192,24 @@
         <v>100</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A102" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B102" s="1">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D102" s="1">
         <v>3</v>
       </c>
       <c r="E102" s="7">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
@@ -5217,24 +5233,24 @@
         <v>100</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A103" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B103" s="1">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D103" s="1">
         <v>3</v>
       </c>
       <c r="E103" s="7">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
@@ -5258,24 +5274,24 @@
         <v>100</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A104" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B104" s="1">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D104" s="1">
         <v>3</v>
       </c>
       <c r="E104" s="7">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -5299,24 +5315,24 @@
         <v>100</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A105" s="8" t="s">
-        <v>161</v>
+      <c r="A105" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="B105" s="1">
-        <v>4020</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>161</v>
+        <v>4018</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="D105" s="1">
         <v>3</v>
       </c>
       <c r="E105" s="7">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -5339,25 +5355,25 @@
       <c r="L105" s="1">
         <v>100</v>
       </c>
-      <c r="Q105" s="8" t="s">
-        <v>161</v>
+      <c r="Q105" s="7" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A106" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B106" s="1">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D106" s="1">
         <v>3</v>
       </c>
       <c r="E106" s="7">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
@@ -5381,24 +5397,24 @@
         <v>100</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A107" s="7" t="s">
-        <v>163</v>
+      <c r="A107" s="8" t="s">
+        <v>161</v>
       </c>
       <c r="B107" s="1">
-        <v>4022</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>163</v>
+        <v>4020</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>161</v>
       </c>
       <c r="D107" s="1">
         <v>3</v>
       </c>
       <c r="E107" s="7">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -5421,25 +5437,25 @@
       <c r="L107" s="1">
         <v>100</v>
       </c>
-      <c r="Q107" s="7" t="s">
-        <v>163</v>
+      <c r="Q107" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A108" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B108" s="1">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D108" s="1">
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
@@ -5463,24 +5479,24 @@
         <v>100</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A109" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B109" s="1">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F109" s="1">
         <v>1</v>
@@ -5504,24 +5520,24 @@
         <v>100</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A110" s="8" t="s">
-        <v>166</v>
+      <c r="A110" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="B110" s="1">
-        <v>4100</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>166</v>
+        <v>4023</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>1100</v>
+        <v>1023</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -5544,25 +5560,25 @@
       <c r="L110" s="1">
         <v>100</v>
       </c>
-      <c r="Q110" s="8" t="s">
-        <v>166</v>
+      <c r="Q110" s="7" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A111" s="8" t="s">
-        <v>167</v>
+      <c r="A111" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="B111" s="1">
-        <v>4101</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>167</v>
+        <v>4024</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="D111" s="1">
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>1101</v>
+        <v>1024</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
@@ -5585,25 +5601,25 @@
       <c r="L111" s="1">
         <v>100</v>
       </c>
-      <c r="Q111" s="8" t="s">
-        <v>167</v>
+      <c r="Q111" s="7" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A112" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B112" s="1">
-        <v>4102</v>
+        <v>4100</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D112" s="1">
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
@@ -5627,24 +5643,24 @@
         <v>100</v>
       </c>
       <c r="Q112" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A113" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B113" s="1">
-        <v>4103</v>
+        <v>4101</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F113" s="1">
         <v>1</v>
@@ -5668,24 +5684,24 @@
         <v>100</v>
       </c>
       <c r="Q113" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A114" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B114" s="1">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
       </c>
       <c r="E114" s="7">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
@@ -5709,24 +5725,24 @@
         <v>100</v>
       </c>
       <c r="Q114" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A115" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B115" s="1">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D115" s="1">
         <v>3</v>
       </c>
       <c r="E115" s="7">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
@@ -5750,24 +5766,24 @@
         <v>100</v>
       </c>
       <c r="Q115" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A116" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B116" s="1">
-        <v>4106</v>
+        <v>4104</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
       </c>
       <c r="E116" s="7">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F116" s="1">
         <v>1</v>
@@ -5791,24 +5807,24 @@
         <v>100</v>
       </c>
       <c r="Q116" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A117" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B117" s="1">
-        <v>4107</v>
+        <v>4105</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D117" s="1">
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
@@ -5832,24 +5848,24 @@
         <v>100</v>
       </c>
       <c r="Q117" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A118" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B118" s="1">
-        <v>4108</v>
+        <v>4106</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D118" s="1">
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="F118" s="1">
         <v>1</v>
@@ -5873,24 +5889,24 @@
         <v>100</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A119" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B119" s="1">
-        <v>4109</v>
+        <v>4107</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D119" s="1">
         <v>3</v>
       </c>
       <c r="E119" s="7">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
@@ -5914,24 +5930,24 @@
         <v>100</v>
       </c>
       <c r="Q119" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A120" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B120" s="1">
-        <v>4110</v>
+        <v>4108</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
       </c>
       <c r="E120" s="7">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -5955,24 +5971,24 @@
         <v>100</v>
       </c>
       <c r="Q120" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A121" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B121" s="1">
-        <v>4111</v>
+        <v>4109</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D121" s="1">
         <v>3</v>
       </c>
       <c r="E121" s="7">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
@@ -5996,24 +6012,24 @@
         <v>100</v>
       </c>
       <c r="Q121" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A122" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B122" s="1">
-        <v>4112</v>
+        <v>4110</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D122" s="1">
         <v>3</v>
       </c>
       <c r="E122" s="7">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="F122" s="1">
         <v>1</v>
@@ -6037,24 +6053,24 @@
         <v>100</v>
       </c>
       <c r="Q122" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A123" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B123" s="1">
-        <v>4113</v>
+        <v>4111</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D123" s="1">
         <v>3</v>
       </c>
       <c r="E123" s="7">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
@@ -6078,24 +6094,24 @@
         <v>100</v>
       </c>
       <c r="Q123" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A124" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B124" s="1">
-        <v>4114</v>
+        <v>4112</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D124" s="1">
         <v>3</v>
       </c>
       <c r="E124" s="7">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
@@ -6119,24 +6135,24 @@
         <v>100</v>
       </c>
       <c r="Q124" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A125" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B125" s="1">
-        <v>4115</v>
+        <v>4113</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D125" s="1">
         <v>3</v>
       </c>
       <c r="E125" s="7">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
@@ -6160,24 +6176,24 @@
         <v>100</v>
       </c>
       <c r="Q125" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A126" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B126" s="1">
-        <v>4116</v>
+        <v>4114</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
       </c>
       <c r="E126" s="7">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
@@ -6201,24 +6217,24 @@
         <v>100</v>
       </c>
       <c r="Q126" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A127" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B127" s="1">
-        <v>4117</v>
+        <v>4115</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D127" s="1">
         <v>3</v>
       </c>
       <c r="E127" s="7">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -6242,6 +6258,88 @@
         <v>100</v>
       </c>
       <c r="Q127" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A128" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B128" s="1">
+        <v>4116</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D128" s="1">
+        <v>3</v>
+      </c>
+      <c r="E128" s="7">
+        <v>1116</v>
+      </c>
+      <c r="F128" s="1">
+        <v>1</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+      <c r="I128" s="1">
+        <v>9</v>
+      </c>
+      <c r="J128" s="1">
+        <v>1</v>
+      </c>
+      <c r="K128" s="1">
+        <v>100</v>
+      </c>
+      <c r="L128" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q128" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A129" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B129" s="1">
+        <v>4117</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D129" s="1">
+        <v>3</v>
+      </c>
+      <c r="E129" s="7">
+        <v>1117</v>
+      </c>
+      <c r="F129" s="1">
+        <v>1</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+      <c r="I129" s="1">
+        <v>9</v>
+      </c>
+      <c r="J129" s="1">
+        <v>1</v>
+      </c>
+      <c r="K129" s="1">
+        <v>100</v>
+      </c>
+      <c r="L129" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q129" s="8" t="s">
         <v>183</v>
       </c>
     </row>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="359">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -537,14 +537,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>会生产鸡蛋的动物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>牧草</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -571,18 +563,12 @@
     <t>鲫鱼</t>
   </si>
   <si>
-    <t>泥鳅</t>
-  </si>
-  <si>
     <t>鲤鱼</t>
   </si>
   <si>
     <t>小龙虾</t>
   </si>
   <si>
-    <t>溪鳟鱼</t>
-  </si>
-  <si>
     <t>鲮鱼</t>
   </si>
   <si>
@@ -620,9 +606,6 @@
   </si>
   <si>
     <t>霓虹脂鲤</t>
-  </si>
-  <si>
-    <t>罗非鱼</t>
   </si>
   <si>
     <t>桃花鱼</t>
@@ -647,13 +630,7 @@
     <t>竹荚鱼</t>
   </si>
   <si>
-    <t>蛤蜊</t>
-  </si>
-  <si>
     <t>海鳗</t>
-  </si>
-  <si>
-    <t>扇贝</t>
   </si>
   <si>
     <t>鱿鱼</t>
@@ -663,12 +640,6 @@
     <t>比目鱼</t>
   </si>
   <si>
-    <t>牡蛎</t>
-  </si>
-  <si>
-    <t>𩽾𩾌</t>
-  </si>
-  <si>
     <t>河豚鱼</t>
   </si>
   <si>
@@ -697,10 +668,6 @@
     <t>斑马狮子鱼</t>
   </si>
   <si>
-    <t>母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>葱种子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -730,6 +697,614 @@
   </si>
   <si>
     <t>垂钓工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭绒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔耳朵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊毛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪肉</t>
+  </si>
+  <si>
+    <t>猪肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛奶</t>
+  </si>
+  <si>
+    <t>牛奶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马尾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火晶石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>象牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰晶石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌芜菁</t>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤肉串</t>
+  </si>
+  <si>
+    <t>烤肉串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌黄瓜</t>
+  </si>
+  <si>
+    <t>腌黄瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌萝卜</t>
+  </si>
+  <si>
+    <t>腌萝卜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤西兰花</t>
+  </si>
+  <si>
+    <t>烤西兰花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混和蔬果汁</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辣椒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咖喱饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇异果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇异果汁</t>
+  </si>
+  <si>
+    <t>奇异果汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茄子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豌豆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豌豆汤</t>
+  </si>
+  <si>
+    <t>土豆泥</t>
+  </si>
+  <si>
+    <t>土豆泥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤肉饼</t>
+  </si>
+  <si>
+    <t>土豆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大蒜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤大蒜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芦笋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芦笋汤</t>
+  </si>
+  <si>
+    <t>蔬菜鸡尾酒</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炖南瓜</t>
+  </si>
+  <si>
+    <t>南瓜面包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤玉米</t>
+  </si>
+  <si>
+    <t>烤玉米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小麦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面粉</t>
+  </si>
+  <si>
+    <t>面粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄汁</t>
+  </si>
+  <si>
+    <t>葡萄汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄酒</t>
+  </si>
+  <si>
+    <t>葡萄酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菠萝汁</t>
+  </si>
+  <si>
+    <t>菠萝汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咖啡粉</t>
+  </si>
+  <si>
+    <t>咖啡粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草莓汁</t>
+  </si>
+  <si>
+    <t>草莓汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝莓汁</t>
+  </si>
+  <si>
+    <t>蓝莓汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤红薯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜菜汁</t>
+  </si>
+  <si>
+    <t>甜菜汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混和蔬果汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拉面</t>
+  </si>
+  <si>
+    <t>拉面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卷心菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饺子</t>
+  </si>
+  <si>
+    <t>紫甘蓝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萝卜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三明治</t>
+  </si>
+  <si>
+    <t>三明治</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜果汁</t>
+  </si>
+  <si>
+    <t>西瓜果汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗姆酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光鸡尾酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伏特加</t>
+  </si>
+  <si>
+    <t>伏特加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>米饭</t>
+  </si>
+  <si>
+    <t>米饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发酵粉</t>
+  </si>
+  <si>
+    <t>发酵粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
+    <t>盐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌黄瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炖南瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咖喱饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤肉饼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酱烤茄子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤玉米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饺子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西式炖菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豌豆汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水母</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>章鱼</t>
+  </si>
+  <si>
+    <t>酸味香料</t>
+  </si>
+  <si>
+    <t>纯净水</t>
+  </si>
+  <si>
+    <t>蜂蜜</t>
+  </si>
+  <si>
+    <t>蜂蜜蛋糕</t>
+  </si>
+  <si>
+    <t>披萨</t>
+  </si>
+  <si>
+    <t>水煮蛋</t>
+  </si>
+  <si>
+    <t>饭团</t>
+  </si>
+  <si>
+    <t>烤面包</t>
+  </si>
+  <si>
+    <t>烤海苔</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>辣蟹堡</t>
+  </si>
+  <si>
+    <t>海鲜饭</t>
+  </si>
+  <si>
+    <t>蔬菜汁</t>
+  </si>
+  <si>
+    <t>玉米汁</t>
+  </si>
+  <si>
+    <t>烤蜜薯</t>
+  </si>
+  <si>
+    <t>黄油</t>
+  </si>
+  <si>
+    <t>奶酪</t>
+  </si>
+  <si>
+    <t>烤茄子</t>
+  </si>
+  <si>
+    <t>炖菜</t>
+  </si>
+  <si>
+    <t>烤芦笋</t>
+  </si>
+  <si>
+    <t>红菜汤</t>
+  </si>
+  <si>
+    <t>草莓牛奶</t>
+  </si>
+  <si>
+    <t>莓莓果汁</t>
+  </si>
+  <si>
+    <t>鲑鱼饭团</t>
+  </si>
+  <si>
+    <t>拿铁</t>
+  </si>
+  <si>
+    <t>黑咖啡</t>
+  </si>
+  <si>
+    <t>朗姆</t>
+  </si>
+  <si>
+    <t>野蜂拉格</t>
+  </si>
+  <si>
+    <t>双莓白兰地</t>
+  </si>
+  <si>
+    <t>绯红之吻</t>
+  </si>
+  <si>
+    <t>盐烤鲮鱼</t>
+  </si>
+  <si>
+    <t>盐烤丁鱼</t>
+  </si>
+  <si>
+    <t>盐烤虹鳟鱼</t>
+  </si>
+  <si>
+    <t>烤鲷鱼</t>
+  </si>
+  <si>
+    <t>盐烤金鳟鱼</t>
+  </si>
+  <si>
+    <t>盐烤鲑鱼</t>
+  </si>
+  <si>
+    <t>烤沙丁鱼串</t>
+  </si>
+  <si>
+    <t>烤竹荚鱼</t>
+  </si>
+  <si>
+    <t>烤海鳗</t>
+  </si>
+  <si>
+    <t>烤比目鱼</t>
+  </si>
+  <si>
+    <t>烤河豚鱼</t>
+  </si>
+  <si>
+    <t>烤条石鲷</t>
+  </si>
+  <si>
+    <t>烤红鲷鱼</t>
+  </si>
+  <si>
+    <t>烤蓝蟹</t>
+  </si>
+  <si>
+    <t>烤龙虾</t>
+  </si>
+  <si>
+    <t>烤金枪鱼</t>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+  </si>
+  <si>
+    <t>海鲜浓汤</t>
+  </si>
+  <si>
+    <t>鳗鱼饭</t>
+  </si>
+  <si>
+    <t>鲫鱼蔬菜汤</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+  </si>
+  <si>
+    <t>鲑鱼刺身</t>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+  </si>
+  <si>
+    <t>炖煮条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷刺身</t>
+  </si>
+  <si>
+    <t>河豚刺身</t>
+  </si>
+  <si>
+    <t>螃蟹煲</t>
+  </si>
+  <si>
+    <t>金枪鱼刺身</t>
+  </si>
+  <si>
+    <t>龙虾鱼子酱</t>
+  </si>
+  <si>
+    <t>黄油</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -737,7 +1312,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -781,8 +1356,29 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -795,13 +1391,34 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -810,7 +1427,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -838,6 +1455,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1144,21 +1779,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q129"/>
-  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A2:Q211"/>
+  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.75" style="1" customWidth="1"/>
     <col min="4" max="8" width="8.875" style="1" customWidth="1"/>
     <col min="9" max="12" width="11.875" style="1" customWidth="1"/>
-    <col min="13" max="16" width="11" style="2" customWidth="1"/>
+    <col min="13" max="16" width="11" style="2" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="37" style="1" customWidth="1"/>
     <col min="18" max="18" width="12.5" style="1" customWidth="1"/>
     <col min="19" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1211,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="27">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1264,7 +1899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
         <v>128</v>
       </c>
@@ -1305,7 +1940,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
         <v>131</v>
       </c>
@@ -1346,15 +1981,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B6" s="1">
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -1384,21 +2019,21 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B7" s="1">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -1428,18 +2063,18 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B8" s="1">
         <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -1469,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="3" customFormat="1">
       <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
@@ -1516,7 +2151,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" s="3" customFormat="1">
       <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
@@ -1560,9 +2195,9 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17">
       <c r="A11" s="5" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B11" s="3">
         <v>1003</v>
@@ -1600,7 +2235,7 @@
       </c>
       <c r="Q11" s="5"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17">
       <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
@@ -1640,7 +2275,7 @@
       </c>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17">
       <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
@@ -1680,7 +2315,7 @@
       </c>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17">
       <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
@@ -1720,7 +2355,7 @@
       </c>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17">
       <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
@@ -1760,7 +2395,7 @@
       </c>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17">
       <c r="A16" s="5" t="s">
         <v>45</v>
       </c>
@@ -1800,7 +2435,7 @@
       </c>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17">
       <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
@@ -1840,7 +2475,7 @@
       </c>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17">
       <c r="A18" s="5" t="s">
         <v>46</v>
       </c>
@@ -1880,7 +2515,7 @@
       </c>
       <c r="Q18" s="5"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17">
       <c r="A19" s="5" t="s">
         <v>47</v>
       </c>
@@ -1920,7 +2555,7 @@
       </c>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17">
       <c r="A20" s="5" t="s">
         <v>48</v>
       </c>
@@ -1960,7 +2595,7 @@
       </c>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:17">
       <c r="A21" s="5" t="s">
         <v>60</v>
       </c>
@@ -2000,7 +2635,7 @@
       </c>
       <c r="Q21" s="5"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17">
       <c r="A22" s="5" t="s">
         <v>61</v>
       </c>
@@ -2040,7 +2675,7 @@
       </c>
       <c r="Q22" s="5"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17">
       <c r="A23" s="5" t="s">
         <v>51</v>
       </c>
@@ -2080,7 +2715,7 @@
       </c>
       <c r="Q23" s="5"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:17">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
@@ -2120,7 +2755,7 @@
       </c>
       <c r="Q24" s="5"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17">
       <c r="A25" s="5" t="s">
         <v>52</v>
       </c>
@@ -2160,7 +2795,7 @@
       </c>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17">
       <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
@@ -2199,7 +2834,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17">
       <c r="A27" s="5" t="s">
         <v>49</v>
       </c>
@@ -2238,7 +2873,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17">
       <c r="A28" s="5" t="s">
         <v>50</v>
       </c>
@@ -2277,7 +2912,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17">
       <c r="A29" s="5" t="s">
         <v>57</v>
       </c>
@@ -2316,7 +2951,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17">
       <c r="A30" s="5" t="s">
         <v>24</v>
       </c>
@@ -2355,7 +2990,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17">
       <c r="A31" s="5" t="s">
         <v>58</v>
       </c>
@@ -2394,7 +3029,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17">
       <c r="A32" s="5" t="s">
         <v>59</v>
       </c>
@@ -2433,7 +3068,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:12">
       <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
@@ -2472,7 +3107,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12">
       <c r="A34" s="5" t="s">
         <v>54</v>
       </c>
@@ -2511,7 +3146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12">
       <c r="A35" s="5" t="s">
         <v>55</v>
       </c>
@@ -2550,7 +3185,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:12">
       <c r="A36" s="5" t="s">
         <v>56</v>
       </c>
@@ -2589,7 +3224,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12">
       <c r="A37" s="5" t="s">
         <v>62</v>
       </c>
@@ -2628,7 +3263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:12">
       <c r="A38" s="9" t="s">
         <v>63</v>
       </c>
@@ -2667,16 +3302,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:12">
       <c r="A39" s="5" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B39" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -2706,7 +3341,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:12">
       <c r="A40" s="9" t="s">
         <v>64</v>
       </c>
@@ -2745,7 +3380,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:12">
       <c r="A41" s="5" t="s">
         <v>65</v>
       </c>
@@ -2784,7 +3419,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:12">
       <c r="A42" s="9" t="s">
         <v>66</v>
       </c>
@@ -2823,7 +3458,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:12">
       <c r="A43" s="9" t="s">
         <v>67</v>
       </c>
@@ -2862,7 +3497,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:12">
       <c r="A44" s="9" t="s">
         <v>68</v>
       </c>
@@ -2901,7 +3536,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:12">
       <c r="A45" s="9" t="s">
         <v>69</v>
       </c>
@@ -2940,7 +3575,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:12">
       <c r="A46" s="9" t="s">
         <v>70</v>
       </c>
@@ -2979,7 +3614,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:12">
       <c r="A47" s="9" t="s">
         <v>71</v>
       </c>
@@ -3018,7 +3653,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:12">
       <c r="A48" s="5" t="s">
         <v>72</v>
       </c>
@@ -3057,7 +3692,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:12">
       <c r="A49" s="9" t="s">
         <v>73</v>
       </c>
@@ -3096,7 +3731,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:12">
       <c r="A50" s="5" t="s">
         <v>74</v>
       </c>
@@ -3135,7 +3770,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:12">
       <c r="A51" s="9" t="s">
         <v>75</v>
       </c>
@@ -3174,7 +3809,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:12">
       <c r="A52" s="9" t="s">
         <v>76</v>
       </c>
@@ -3213,7 +3848,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>77</v>
       </c>
@@ -3252,7 +3887,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:12">
       <c r="A54" s="9" t="s">
         <v>78</v>
       </c>
@@ -3291,7 +3926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:12">
       <c r="A55" s="9" t="s">
         <v>79</v>
       </c>
@@ -3330,7 +3965,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:12">
       <c r="A56" s="9" t="s">
         <v>80</v>
       </c>
@@ -3369,7 +4004,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:12">
       <c r="A57" s="5" t="s">
         <v>81</v>
       </c>
@@ -3408,7 +4043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:12">
       <c r="A58" s="9" t="s">
         <v>82</v>
       </c>
@@ -3447,7 +4082,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:12">
       <c r="A59" s="5" t="s">
         <v>83</v>
       </c>
@@ -3486,7 +4121,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:12">
       <c r="A60" s="5" t="s">
         <v>84</v>
       </c>
@@ -3525,7 +4160,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:12">
       <c r="A61" s="9" t="s">
         <v>85</v>
       </c>
@@ -3564,7 +4199,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:12">
       <c r="A62" s="9" t="s">
         <v>86</v>
       </c>
@@ -3603,7 +4238,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:12">
       <c r="A63" s="9" t="s">
         <v>87</v>
       </c>
@@ -3642,7 +4277,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:12">
       <c r="A64" s="9" t="s">
         <v>88</v>
       </c>
@@ -3681,7 +4316,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17">
       <c r="A65" s="1" t="s">
         <v>27</v>
       </c>
@@ -3722,7 +4357,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17">
       <c r="A66" s="1" t="s">
         <v>28</v>
       </c>
@@ -3763,7 +4398,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17">
       <c r="A67" s="1" t="s">
         <v>29</v>
       </c>
@@ -3801,7 +4436,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17">
       <c r="A68" s="1" t="s">
         <v>30</v>
       </c>
@@ -3842,15 +4477,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17">
       <c r="A69" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B69" s="1">
         <v>2004</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D69" s="1">
         <v>6</v>
@@ -3880,10 +4515,10 @@
         <v>100</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.15">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
       <c r="A70" s="1" t="s">
         <v>89</v>
       </c>
@@ -3924,7 +4559,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17">
       <c r="A71" s="1" t="s">
         <v>90</v>
       </c>
@@ -3965,7 +4600,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17">
       <c r="A72" s="1" t="s">
         <v>111</v>
       </c>
@@ -4006,7 +4641,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17">
       <c r="A73" s="1" t="s">
         <v>110</v>
       </c>
@@ -4047,7 +4682,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17">
       <c r="A74" s="1" t="s">
         <v>91</v>
       </c>
@@ -4088,7 +4723,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17">
       <c r="A75" s="1" t="s">
         <v>92</v>
       </c>
@@ -4129,7 +4764,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17">
       <c r="A76" s="1" t="s">
         <v>93</v>
       </c>
@@ -4170,7 +4805,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17">
       <c r="A77" s="1" t="s">
         <v>94</v>
       </c>
@@ -4211,7 +4846,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17">
       <c r="A78" s="1" t="s">
         <v>99</v>
       </c>
@@ -4252,7 +4887,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17">
       <c r="A79" s="1" t="s">
         <v>100</v>
       </c>
@@ -4293,7 +4928,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17">
       <c r="A80" s="1" t="s">
         <v>101</v>
       </c>
@@ -4334,7 +4969,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17">
       <c r="A81" s="1" t="s">
         <v>97</v>
       </c>
@@ -4375,7 +5010,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17">
       <c r="A82" s="1" t="s">
         <v>98</v>
       </c>
@@ -4416,7 +5051,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17">
       <c r="A83" s="1" t="s">
         <v>107</v>
       </c>
@@ -4457,7 +5092,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17">
       <c r="A84" s="1" t="s">
         <v>95</v>
       </c>
@@ -4498,7 +5133,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17">
       <c r="A85" s="1" t="s">
         <v>96</v>
       </c>
@@ -4539,24 +5174,24 @@
         <v>127</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A86" s="1" t="s">
-        <v>134</v>
+    <row r="86" spans="1:17" ht="15">
+      <c r="A86" s="12" t="s">
+        <v>297</v>
       </c>
       <c r="B86" s="1">
-        <v>3000</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>184</v>
+        <v>4000</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="D86" s="1">
-        <v>11</v>
-      </c>
-      <c r="E86" s="1">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E86" s="7">
+        <v>1000</v>
       </c>
       <c r="F86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="1">
         <v>0</v>
@@ -4565,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J86" s="1">
         <v>1</v>
@@ -4576,25 +5211,25 @@
       <c r="L86" s="1">
         <v>100</v>
       </c>
-      <c r="Q86" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="15" x14ac:dyDescent="0.2">
-      <c r="A87" s="6" t="s">
+      <c r="Q86" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17">
+      <c r="A87" s="7" t="s">
         <v>142</v>
       </c>
       <c r="B87" s="1">
-        <v>4000</v>
-      </c>
-      <c r="C87" s="6" t="s">
+        <v>4003</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>142</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
       </c>
       <c r="E87" s="7">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="F87" s="1">
         <v>1</v>
@@ -4617,25 +5252,25 @@
       <c r="L87" s="1">
         <v>100</v>
       </c>
-      <c r="Q87" s="6" t="s">
+      <c r="Q87" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17">
       <c r="A88" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B88" s="1">
-        <v>4001</v>
+        <v>4004</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D88" s="1">
         <v>3</v>
       </c>
       <c r="E88" s="7">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="F88" s="1">
         <v>1</v>
@@ -4659,24 +5294,24 @@
         <v>100</v>
       </c>
       <c r="Q88" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17">
+      <c r="A89" s="7" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A89" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="B89" s="1">
-        <v>4002</v>
+        <v>4006</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D89" s="1">
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="F89" s="1">
         <v>1</v>
@@ -4700,24 +5335,24 @@
         <v>100</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.15">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17">
       <c r="A90" s="7" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="B90" s="1">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="D90" s="1">
         <v>3</v>
       </c>
       <c r="E90" s="7">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
@@ -4741,24 +5376,24 @@
         <v>100</v>
       </c>
       <c r="Q90" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17">
+      <c r="A91" s="8" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A91" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="B91" s="1">
-        <v>4004</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>144</v>
+        <v>4008</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="D91" s="1">
         <v>3</v>
       </c>
       <c r="E91" s="7">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="F91" s="1">
         <v>1</v>
@@ -4781,16 +5416,16 @@
       <c r="L91" s="1">
         <v>100</v>
       </c>
-      <c r="Q91" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="Q91" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17">
       <c r="A92" s="7" t="s">
         <v>146</v>
       </c>
       <c r="B92" s="1">
-        <v>4005</v>
+        <v>4009</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>146</v>
@@ -4799,7 +5434,7 @@
         <v>3</v>
       </c>
       <c r="E92" s="7">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
@@ -4826,21 +5461,21 @@
         <v>146</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A93" s="7" t="s">
+    <row r="93" spans="1:17">
+      <c r="A93" s="8" t="s">
         <v>147</v>
       </c>
       <c r="B93" s="1">
-        <v>4006</v>
-      </c>
-      <c r="C93" s="7" t="s">
+        <v>4010</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D93" s="1">
         <v>3</v>
       </c>
       <c r="E93" s="7">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="F93" s="1">
         <v>1</v>
@@ -4863,25 +5498,25 @@
       <c r="L93" s="1">
         <v>100</v>
       </c>
-      <c r="Q93" s="7" t="s">
+      <c r="Q93" s="8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17">
       <c r="A94" s="7" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="B94" s="1">
-        <v>4007</v>
+        <v>4011</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
       </c>
       <c r="E94" s="7">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="F94" s="1">
         <v>1</v>
@@ -4908,21 +5543,21 @@
         <v>148</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A95" s="8" t="s">
+    <row r="95" spans="1:17">
+      <c r="A95" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B95" s="1">
-        <v>4008</v>
-      </c>
-      <c r="C95" s="8" t="s">
+        <v>4012</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>149</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" s="7">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="F95" s="1">
         <v>1</v>
@@ -4945,16 +5580,16 @@
       <c r="L95" s="1">
         <v>100</v>
       </c>
-      <c r="Q95" s="8" t="s">
+      <c r="Q95" s="7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17">
       <c r="A96" s="7" t="s">
         <v>150</v>
       </c>
       <c r="B96" s="1">
-        <v>4009</v>
+        <v>4013</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>150</v>
@@ -4963,7 +5598,7 @@
         <v>3</v>
       </c>
       <c r="E96" s="7">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="F96" s="1">
         <v>1</v>
@@ -4990,21 +5625,21 @@
         <v>150</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A97" s="8" t="s">
+    <row r="97" spans="1:17">
+      <c r="A97" s="7" t="s">
         <v>151</v>
       </c>
       <c r="B97" s="1">
-        <v>4010</v>
-      </c>
-      <c r="C97" s="8" t="s">
+        <v>4014</v>
+      </c>
+      <c r="C97" s="7" t="s">
         <v>151</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
       </c>
       <c r="E97" s="7">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
@@ -5027,16 +5662,16 @@
       <c r="L97" s="1">
         <v>100</v>
       </c>
-      <c r="Q97" s="8" t="s">
+      <c r="Q97" s="7" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17">
       <c r="A98" s="7" t="s">
         <v>152</v>
       </c>
       <c r="B98" s="1">
-        <v>4011</v>
+        <v>4015</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>152</v>
@@ -5045,7 +5680,7 @@
         <v>3</v>
       </c>
       <c r="E98" s="7">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="F98" s="1">
         <v>1</v>
@@ -5072,12 +5707,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17">
       <c r="A99" s="7" t="s">
         <v>153</v>
       </c>
       <c r="B99" s="1">
-        <v>4012</v>
+        <v>4016</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>153</v>
@@ -5086,7 +5721,7 @@
         <v>3</v>
       </c>
       <c r="E99" s="7">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
@@ -5113,12 +5748,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17">
       <c r="A100" s="7" t="s">
         <v>154</v>
       </c>
       <c r="B100" s="1">
-        <v>4013</v>
+        <v>4017</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>154</v>
@@ -5127,7 +5762,7 @@
         <v>3</v>
       </c>
       <c r="E100" s="7">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -5154,12 +5789,12 @@
         <v>154</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17">
       <c r="A101" s="7" t="s">
         <v>155</v>
       </c>
       <c r="B101" s="1">
-        <v>4014</v>
+        <v>4018</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>155</v>
@@ -5168,7 +5803,7 @@
         <v>3</v>
       </c>
       <c r="E101" s="7">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
@@ -5195,21 +5830,21 @@
         <v>155</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A102" s="7" t="s">
+    <row r="102" spans="1:17">
+      <c r="A102" s="8" t="s">
         <v>156</v>
       </c>
       <c r="B102" s="1">
-        <v>4015</v>
-      </c>
-      <c r="C102" s="7" t="s">
+        <v>4020</v>
+      </c>
+      <c r="C102" s="8" t="s">
         <v>156</v>
       </c>
       <c r="D102" s="1">
         <v>3</v>
       </c>
       <c r="E102" s="7">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
@@ -5232,16 +5867,16 @@
       <c r="L102" s="1">
         <v>100</v>
       </c>
-      <c r="Q102" s="7" t="s">
+      <c r="Q102" s="8" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17">
       <c r="A103" s="7" t="s">
         <v>157</v>
       </c>
       <c r="B103" s="1">
-        <v>4016</v>
+        <v>4021</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>157</v>
@@ -5250,7 +5885,7 @@
         <v>3</v>
       </c>
       <c r="E103" s="7">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
@@ -5277,12 +5912,12 @@
         <v>157</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17">
       <c r="A104" s="7" t="s">
         <v>158</v>
       </c>
       <c r="B104" s="1">
-        <v>4017</v>
+        <v>4022</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>158</v>
@@ -5291,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="E104" s="7">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -5318,12 +5953,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17">
       <c r="A105" s="7" t="s">
         <v>159</v>
       </c>
       <c r="B105" s="1">
-        <v>4018</v>
+        <v>4023</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>159</v>
@@ -5332,7 +5967,7 @@
         <v>3</v>
       </c>
       <c r="E105" s="7">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -5359,12 +5994,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17">
       <c r="A106" s="7" t="s">
         <v>160</v>
       </c>
       <c r="B106" s="1">
-        <v>4019</v>
+        <v>4024</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>160</v>
@@ -5373,7 +6008,7 @@
         <v>3</v>
       </c>
       <c r="E106" s="7">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
@@ -5400,12 +6035,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17">
       <c r="A107" s="8" t="s">
         <v>161</v>
       </c>
       <c r="B107" s="1">
-        <v>4020</v>
+        <v>4100</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>161</v>
@@ -5414,7 +6049,7 @@
         <v>3</v>
       </c>
       <c r="E107" s="7">
-        <v>1020</v>
+        <v>1100</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -5441,21 +6076,21 @@
         <v>161</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A108" s="7" t="s">
+    <row r="108" spans="1:17">
+      <c r="A108" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B108" s="1">
-        <v>4021</v>
-      </c>
-      <c r="C108" s="7" t="s">
+        <v>4101</v>
+      </c>
+      <c r="C108" s="8" t="s">
         <v>162</v>
       </c>
       <c r="D108" s="1">
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>1021</v>
+        <v>1101</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
@@ -5478,25 +6113,25 @@
       <c r="L108" s="1">
         <v>100</v>
       </c>
-      <c r="Q108" s="7" t="s">
+      <c r="Q108" s="8" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A109" s="7" t="s">
+    <row r="109" spans="1:17">
+      <c r="A109" s="8" t="s">
         <v>163</v>
       </c>
       <c r="B109" s="1">
-        <v>4022</v>
-      </c>
-      <c r="C109" s="7" t="s">
+        <v>4103</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>163</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>1022</v>
+        <v>1103</v>
       </c>
       <c r="F109" s="1">
         <v>1</v>
@@ -5519,25 +6154,25 @@
       <c r="L109" s="1">
         <v>100</v>
       </c>
-      <c r="Q109" s="7" t="s">
+      <c r="Q109" s="8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A110" s="7" t="s">
-        <v>164</v>
+    <row r="110" spans="1:17">
+      <c r="A110" s="8" t="s">
+        <v>298</v>
       </c>
       <c r="B110" s="1">
-        <v>4023</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>164</v>
+        <v>4105</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>298</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>1023</v>
+        <v>1105</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -5560,25 +6195,25 @@
       <c r="L110" s="1">
         <v>100</v>
       </c>
-      <c r="Q110" s="7" t="s">
+      <c r="Q110" s="8" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A111" s="7" t="s">
+    <row r="111" spans="1:17">
+      <c r="A111" s="8" t="s">
         <v>165</v>
       </c>
       <c r="B111" s="1">
-        <v>4024</v>
-      </c>
-      <c r="C111" s="7" t="s">
+        <v>4106</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>165</v>
       </c>
       <c r="D111" s="1">
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>1024</v>
+        <v>1106</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
@@ -5601,16 +6236,16 @@
       <c r="L111" s="1">
         <v>100</v>
       </c>
-      <c r="Q111" s="7" t="s">
+      <c r="Q111" s="8" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17">
       <c r="A112" s="8" t="s">
         <v>166</v>
       </c>
       <c r="B112" s="1">
-        <v>4100</v>
+        <v>4109</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>166</v>
@@ -5619,7 +6254,7 @@
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
@@ -5646,12 +6281,12 @@
         <v>166</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17">
       <c r="A113" s="8" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="B113" s="1">
-        <v>4101</v>
+        <v>4110</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>167</v>
@@ -5660,7 +6295,7 @@
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="F113" s="1">
         <v>1</v>
@@ -5687,12 +6322,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17">
       <c r="A114" s="8" t="s">
         <v>168</v>
       </c>
       <c r="B114" s="1">
-        <v>4102</v>
+        <v>4111</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>168</v>
@@ -5701,7 +6336,7 @@
         <v>3</v>
       </c>
       <c r="E114" s="7">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
@@ -5728,12 +6363,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17">
       <c r="A115" s="8" t="s">
         <v>169</v>
       </c>
       <c r="B115" s="1">
-        <v>4103</v>
+        <v>4112</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>169</v>
@@ -5742,7 +6377,7 @@
         <v>3</v>
       </c>
       <c r="E115" s="7">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
@@ -5769,12 +6404,12 @@
         <v>169</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17">
       <c r="A116" s="8" t="s">
         <v>170</v>
       </c>
       <c r="B116" s="1">
-        <v>4104</v>
+        <v>4113</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>170</v>
@@ -5783,7 +6418,7 @@
         <v>3</v>
       </c>
       <c r="E116" s="7">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="F116" s="1">
         <v>1</v>
@@ -5810,12 +6445,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17">
       <c r="A117" s="8" t="s">
         <v>171</v>
       </c>
       <c r="B117" s="1">
-        <v>4105</v>
+        <v>4114</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>171</v>
@@ -5824,7 +6459,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
@@ -5851,12 +6486,12 @@
         <v>171</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17">
       <c r="A118" s="8" t="s">
         <v>172</v>
       </c>
       <c r="B118" s="1">
-        <v>4106</v>
+        <v>4115</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>172</v>
@@ -5865,7 +6500,7 @@
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="F118" s="1">
         <v>1</v>
@@ -5892,12 +6527,12 @@
         <v>172</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17">
       <c r="A119" s="8" t="s">
         <v>173</v>
       </c>
       <c r="B119" s="1">
-        <v>4107</v>
+        <v>4116</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>173</v>
@@ -5906,7 +6541,7 @@
         <v>3</v>
       </c>
       <c r="E119" s="7">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
@@ -5933,12 +6568,12 @@
         <v>173</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17">
       <c r="A120" s="8" t="s">
         <v>174</v>
       </c>
       <c r="B120" s="1">
-        <v>4108</v>
+        <v>4117</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>174</v>
@@ -5947,7 +6582,7 @@
         <v>3</v>
       </c>
       <c r="E120" s="7">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -5974,21 +6609,21 @@
         <v>174</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A121" s="8" t="s">
-        <v>175</v>
+    <row r="121" spans="1:17">
+      <c r="A121" s="13" t="s">
+        <v>280</v>
       </c>
       <c r="B121" s="1">
-        <v>4109</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>175</v>
+        <v>3000</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="D121" s="1">
         <v>3</v>
       </c>
-      <c r="E121" s="7">
-        <v>1109</v>
+      <c r="E121" s="1">
+        <v>0</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
@@ -6011,28 +6646,25 @@
       <c r="L121" s="1">
         <v>100</v>
       </c>
-      <c r="Q121" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A122" s="8" t="s">
-        <v>176</v>
+    </row>
+    <row r="122" spans="1:17">
+      <c r="A122" s="13" t="s">
+        <v>282</v>
       </c>
       <c r="B122" s="1">
-        <v>4110</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>176</v>
+        <v>3001</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="D122" s="1">
         <v>3</v>
       </c>
-      <c r="E122" s="7">
-        <v>1110</v>
+      <c r="E122" s="1">
+        <v>0</v>
       </c>
       <c r="F122" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
@@ -6041,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J122" s="1">
         <v>1</v>
@@ -6052,28 +6684,25 @@
       <c r="L122" s="1">
         <v>100</v>
       </c>
-      <c r="Q122" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A123" s="8" t="s">
-        <v>177</v>
+    </row>
+    <row r="123" spans="1:17">
+      <c r="A123" s="13" t="s">
+        <v>284</v>
       </c>
       <c r="B123" s="1">
-        <v>4111</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>177</v>
+        <v>3002</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="D123" s="1">
         <v>3</v>
       </c>
-      <c r="E123" s="7">
-        <v>1111</v>
+      <c r="E123" s="1">
+        <v>0</v>
       </c>
       <c r="F123" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" s="1">
         <v>0</v>
@@ -6082,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="I123" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J123" s="1">
         <v>1</v>
@@ -6093,28 +6722,25 @@
       <c r="L123" s="1">
         <v>100</v>
       </c>
-      <c r="Q123" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A124" s="8" t="s">
-        <v>178</v>
+    </row>
+    <row r="124" spans="1:17">
+      <c r="A124" s="13" t="s">
+        <v>299</v>
       </c>
       <c r="B124" s="1">
-        <v>4112</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>178</v>
+        <v>3003</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="D124" s="1">
         <v>3</v>
       </c>
-      <c r="E124" s="7">
-        <v>1112</v>
+      <c r="E124" s="1">
+        <v>0</v>
       </c>
       <c r="F124" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="1">
         <v>0</v>
@@ -6123,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J124" s="1">
         <v>1</v>
@@ -6134,28 +6760,25 @@
       <c r="L124" s="1">
         <v>100</v>
       </c>
-      <c r="Q124" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A125" s="8" t="s">
-        <v>179</v>
+    </row>
+    <row r="125" spans="1:17">
+      <c r="A125" s="13" t="s">
+        <v>300</v>
       </c>
       <c r="B125" s="1">
-        <v>4113</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>179</v>
+        <v>3004</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="D125" s="1">
         <v>3</v>
       </c>
-      <c r="E125" s="7">
-        <v>1113</v>
+      <c r="E125" s="1">
+        <v>0</v>
       </c>
       <c r="F125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="1">
         <v>0</v>
@@ -6164,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J125" s="1">
         <v>1</v>
@@ -6175,28 +6798,25 @@
       <c r="L125" s="1">
         <v>100</v>
       </c>
-      <c r="Q125" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A126" s="8" t="s">
-        <v>180</v>
+    </row>
+    <row r="126" spans="1:17">
+      <c r="A126" s="14" t="s">
+        <v>301</v>
       </c>
       <c r="B126" s="1">
-        <v>4114</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>180</v>
+        <v>3005</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
       </c>
-      <c r="E126" s="7">
-        <v>1114</v>
+      <c r="E126" s="1">
+        <v>0</v>
       </c>
       <c r="F126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="1">
         <v>0</v>
@@ -6205,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="I126" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J126" s="1">
         <v>1</v>
@@ -6216,25 +6836,22 @@
       <c r="L126" s="1">
         <v>100</v>
       </c>
-      <c r="Q126" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A127" s="8" t="s">
-        <v>181</v>
+    </row>
+    <row r="127" spans="1:17">
+      <c r="A127" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="B127" s="1">
-        <v>4115</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>181</v>
+        <v>3006</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D127" s="1">
         <v>3</v>
       </c>
-      <c r="E127" s="7">
-        <v>1115</v>
+      <c r="E127" s="1">
+        <v>0</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -6246,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J127" s="1">
         <v>1</v>
@@ -6257,25 +6874,22 @@
       <c r="L127" s="1">
         <v>100</v>
       </c>
-      <c r="Q127" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A128" s="8" t="s">
-        <v>182</v>
+    </row>
+    <row r="128" spans="1:17">
+      <c r="A128" s="14" t="s">
+        <v>183</v>
       </c>
       <c r="B128" s="1">
-        <v>4116</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>182</v>
+        <v>3007</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="D128" s="1">
         <v>3</v>
       </c>
-      <c r="E128" s="7">
-        <v>1116</v>
+      <c r="E128" s="1">
+        <v>0</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
@@ -6298,25 +6912,22 @@
       <c r="L128" s="1">
         <v>100</v>
       </c>
-      <c r="Q128" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A129" s="8" t="s">
-        <v>183</v>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="B129" s="1">
-        <v>4117</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>183</v>
+        <v>3008</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="D129" s="1">
         <v>3</v>
       </c>
-      <c r="E129" s="7">
-        <v>1117</v>
+      <c r="E129" s="1">
+        <v>0</v>
       </c>
       <c r="F129" s="1">
         <v>1</v>
@@ -6339,8 +6950,3121 @@
       <c r="L129" s="1">
         <v>100</v>
       </c>
-      <c r="Q129" s="8" t="s">
-        <v>183</v>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B130" s="1">
+        <v>3009</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D130" s="1">
+        <v>3</v>
+      </c>
+      <c r="E130" s="1">
+        <v>0</v>
+      </c>
+      <c r="F130" s="1">
+        <v>0</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+      <c r="I130" s="1">
+        <v>29</v>
+      </c>
+      <c r="J130" s="1">
+        <v>1</v>
+      </c>
+      <c r="K130" s="1">
+        <v>100</v>
+      </c>
+      <c r="L130" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B131" s="1">
+        <v>3010</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D131" s="1">
+        <v>3</v>
+      </c>
+      <c r="E131" s="1">
+        <v>0</v>
+      </c>
+      <c r="F131" s="1">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1">
+        <v>29</v>
+      </c>
+      <c r="J131" s="1">
+        <v>1</v>
+      </c>
+      <c r="K131" s="1">
+        <v>100</v>
+      </c>
+      <c r="L131" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="B132" s="1">
+        <v>3011</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D132" s="1">
+        <v>3</v>
+      </c>
+      <c r="E132" s="1">
+        <v>0</v>
+      </c>
+      <c r="F132" s="1">
+        <v>1</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
+      <c r="I132" s="1">
+        <v>29</v>
+      </c>
+      <c r="J132" s="1">
+        <v>1</v>
+      </c>
+      <c r="K132" s="1">
+        <v>100</v>
+      </c>
+      <c r="L132" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B133" s="1">
+        <v>3100</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D133" s="1">
+        <v>4</v>
+      </c>
+      <c r="E133" s="1">
+        <v>0</v>
+      </c>
+      <c r="F133" s="1">
+        <v>1</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+      <c r="I133" s="1">
+        <v>1</v>
+      </c>
+      <c r="J133" s="1">
+        <v>1</v>
+      </c>
+      <c r="K133" s="1">
+        <v>100</v>
+      </c>
+      <c r="L133" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="B134" s="1">
+        <v>3101</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D134" s="1">
+        <v>4</v>
+      </c>
+      <c r="E134" s="1">
+        <v>0</v>
+      </c>
+      <c r="F134" s="1">
+        <v>1</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+      <c r="I134" s="1">
+        <v>1</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1</v>
+      </c>
+      <c r="K134" s="1">
+        <v>100</v>
+      </c>
+      <c r="L134" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B135" s="1">
+        <v>3102</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D135" s="1">
+        <v>4</v>
+      </c>
+      <c r="E135" s="1">
+        <v>0</v>
+      </c>
+      <c r="F135" s="1">
+        <v>1</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+      <c r="I135" s="1">
+        <v>1</v>
+      </c>
+      <c r="J135" s="1">
+        <v>1</v>
+      </c>
+      <c r="K135" s="1">
+        <v>100</v>
+      </c>
+      <c r="L135" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B136" s="1">
+        <v>3103</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D136" s="1">
+        <v>4</v>
+      </c>
+      <c r="E136" s="1">
+        <v>0</v>
+      </c>
+      <c r="F136" s="1">
+        <v>1</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
+      </c>
+      <c r="I136" s="1">
+        <v>1</v>
+      </c>
+      <c r="J136" s="1">
+        <v>1</v>
+      </c>
+      <c r="K136" s="1">
+        <v>100</v>
+      </c>
+      <c r="L136" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B137" s="1">
+        <v>3104</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D137" s="1">
+        <v>4</v>
+      </c>
+      <c r="E137" s="1">
+        <v>0</v>
+      </c>
+      <c r="F137" s="1">
+        <v>1</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+      <c r="I137" s="1">
+        <v>1</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1</v>
+      </c>
+      <c r="K137" s="1">
+        <v>100</v>
+      </c>
+      <c r="L137" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="B138" s="1">
+        <v>3105</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D138" s="1">
+        <v>4</v>
+      </c>
+      <c r="E138" s="1">
+        <v>0</v>
+      </c>
+      <c r="F138" s="1">
+        <v>1</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0</v>
+      </c>
+      <c r="I138" s="1">
+        <v>1</v>
+      </c>
+      <c r="J138" s="1">
+        <v>1</v>
+      </c>
+      <c r="K138" s="1">
+        <v>100</v>
+      </c>
+      <c r="L138" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B139" s="1">
+        <v>3106</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D139" s="1">
+        <v>4</v>
+      </c>
+      <c r="E139" s="1">
+        <v>0</v>
+      </c>
+      <c r="F139" s="1">
+        <v>1</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+      <c r="I139" s="1">
+        <v>1</v>
+      </c>
+      <c r="J139" s="1">
+        <v>1</v>
+      </c>
+      <c r="K139" s="1">
+        <v>100</v>
+      </c>
+      <c r="L139" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B140" s="1">
+        <v>3107</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D140" s="1">
+        <v>4</v>
+      </c>
+      <c r="E140" s="1">
+        <v>0</v>
+      </c>
+      <c r="F140" s="1">
+        <v>1</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+      <c r="I140" s="1">
+        <v>1</v>
+      </c>
+      <c r="J140" s="1">
+        <v>1</v>
+      </c>
+      <c r="K140" s="1">
+        <v>100</v>
+      </c>
+      <c r="L140" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B141" s="1">
+        <v>3108</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D141" s="1">
+        <v>4</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+      <c r="F141" s="1">
+        <v>1</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
+      </c>
+      <c r="I141" s="1">
+        <v>1</v>
+      </c>
+      <c r="J141" s="1">
+        <v>1</v>
+      </c>
+      <c r="K141" s="1">
+        <v>100</v>
+      </c>
+      <c r="L141" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="B142" s="1">
+        <v>3109</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D142" s="1">
+        <v>4</v>
+      </c>
+      <c r="E142" s="1">
+        <v>0</v>
+      </c>
+      <c r="F142" s="1">
+        <v>1</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+      <c r="I142" s="1">
+        <v>1</v>
+      </c>
+      <c r="J142" s="1">
+        <v>1</v>
+      </c>
+      <c r="K142" s="1">
+        <v>100</v>
+      </c>
+      <c r="L142" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B143" s="1">
+        <v>3110</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D143" s="1">
+        <v>4</v>
+      </c>
+      <c r="E143" s="1">
+        <v>0</v>
+      </c>
+      <c r="F143" s="1">
+        <v>1</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0</v>
+      </c>
+      <c r="I143" s="1">
+        <v>1</v>
+      </c>
+      <c r="J143" s="1">
+        <v>1</v>
+      </c>
+      <c r="K143" s="1">
+        <v>100</v>
+      </c>
+      <c r="L143" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B144" s="1">
+        <v>3111</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D144" s="1">
+        <v>4</v>
+      </c>
+      <c r="E144" s="1">
+        <v>0</v>
+      </c>
+      <c r="F144" s="1">
+        <v>1</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>1</v>
+      </c>
+      <c r="J144" s="1">
+        <v>1</v>
+      </c>
+      <c r="K144" s="1">
+        <v>100</v>
+      </c>
+      <c r="L144" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="B145" s="1">
+        <v>3112</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D145" s="1">
+        <v>4</v>
+      </c>
+      <c r="E145" s="1">
+        <v>0</v>
+      </c>
+      <c r="F145" s="1">
+        <v>1</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0</v>
+      </c>
+      <c r="I145" s="1">
+        <v>1</v>
+      </c>
+      <c r="J145" s="1">
+        <v>1</v>
+      </c>
+      <c r="K145" s="1">
+        <v>100</v>
+      </c>
+      <c r="L145" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
+      <c r="A146" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="B146" s="1">
+        <v>3113</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D146" s="1">
+        <v>4</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0</v>
+      </c>
+      <c r="F146" s="1">
+        <v>1</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+      <c r="I146" s="1">
+        <v>1</v>
+      </c>
+      <c r="J146" s="1">
+        <v>1</v>
+      </c>
+      <c r="K146" s="1">
+        <v>100</v>
+      </c>
+      <c r="L146" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12">
+      <c r="A147" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B147" s="1">
+        <v>3114</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D147" s="1">
+        <v>4</v>
+      </c>
+      <c r="E147" s="1">
+        <v>0</v>
+      </c>
+      <c r="F147" s="1">
+        <v>1</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0</v>
+      </c>
+      <c r="I147" s="1">
+        <v>1</v>
+      </c>
+      <c r="J147" s="1">
+        <v>1</v>
+      </c>
+      <c r="K147" s="1">
+        <v>100</v>
+      </c>
+      <c r="L147" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
+      <c r="A148" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="B148" s="1">
+        <v>3115</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D148" s="1">
+        <v>4</v>
+      </c>
+      <c r="E148" s="1">
+        <v>0</v>
+      </c>
+      <c r="F148" s="1">
+        <v>1</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0</v>
+      </c>
+      <c r="I148" s="1">
+        <v>1</v>
+      </c>
+      <c r="J148" s="1">
+        <v>1</v>
+      </c>
+      <c r="K148" s="1">
+        <v>100</v>
+      </c>
+      <c r="L148" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12">
+      <c r="A149" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B149" s="1">
+        <v>3116</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D149" s="1">
+        <v>4</v>
+      </c>
+      <c r="E149" s="1">
+        <v>0</v>
+      </c>
+      <c r="F149" s="1">
+        <v>1</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
+      </c>
+      <c r="I149" s="1">
+        <v>1</v>
+      </c>
+      <c r="J149" s="1">
+        <v>1</v>
+      </c>
+      <c r="K149" s="1">
+        <v>100</v>
+      </c>
+      <c r="L149" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B150" s="1">
+        <v>3117</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D150" s="1">
+        <v>4</v>
+      </c>
+      <c r="E150" s="1">
+        <v>0</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1</v>
+      </c>
+      <c r="G150" s="1">
+        <v>0</v>
+      </c>
+      <c r="H150" s="1">
+        <v>0</v>
+      </c>
+      <c r="I150" s="1">
+        <v>1</v>
+      </c>
+      <c r="J150" s="1">
+        <v>1</v>
+      </c>
+      <c r="K150" s="1">
+        <v>100</v>
+      </c>
+      <c r="L150" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
+      <c r="A151" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B151" s="1">
+        <v>3118</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D151" s="1">
+        <v>4</v>
+      </c>
+      <c r="E151" s="1">
+        <v>0</v>
+      </c>
+      <c r="F151" s="1">
+        <v>1</v>
+      </c>
+      <c r="G151" s="1">
+        <v>0</v>
+      </c>
+      <c r="H151" s="1">
+        <v>0</v>
+      </c>
+      <c r="I151" s="1">
+        <v>1</v>
+      </c>
+      <c r="J151" s="1">
+        <v>1</v>
+      </c>
+      <c r="K151" s="1">
+        <v>100</v>
+      </c>
+      <c r="L151" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B152" s="1">
+        <v>3119</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D152" s="1">
+        <v>4</v>
+      </c>
+      <c r="E152" s="1">
+        <v>0</v>
+      </c>
+      <c r="F152" s="1">
+        <v>1</v>
+      </c>
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+      <c r="H152" s="1">
+        <v>0</v>
+      </c>
+      <c r="I152" s="1">
+        <v>1</v>
+      </c>
+      <c r="J152" s="1">
+        <v>1</v>
+      </c>
+      <c r="K152" s="1">
+        <v>100</v>
+      </c>
+      <c r="L152" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="B153" s="1">
+        <v>3120</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D153" s="1">
+        <v>4</v>
+      </c>
+      <c r="E153" s="1">
+        <v>0</v>
+      </c>
+      <c r="F153" s="1">
+        <v>1</v>
+      </c>
+      <c r="G153" s="1">
+        <v>0</v>
+      </c>
+      <c r="H153" s="1">
+        <v>0</v>
+      </c>
+      <c r="I153" s="1">
+        <v>1</v>
+      </c>
+      <c r="J153" s="1">
+        <v>1</v>
+      </c>
+      <c r="K153" s="1">
+        <v>100</v>
+      </c>
+      <c r="L153" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
+      <c r="A154" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="B154" s="1">
+        <v>3121</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D154" s="1">
+        <v>4</v>
+      </c>
+      <c r="E154" s="1">
+        <v>0</v>
+      </c>
+      <c r="F154" s="1">
+        <v>1</v>
+      </c>
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+      <c r="H154" s="1">
+        <v>0</v>
+      </c>
+      <c r="I154" s="1">
+        <v>1</v>
+      </c>
+      <c r="J154" s="1">
+        <v>1</v>
+      </c>
+      <c r="K154" s="1">
+        <v>100</v>
+      </c>
+      <c r="L154" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B155" s="1">
+        <v>3122</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D155" s="1">
+        <v>4</v>
+      </c>
+      <c r="E155" s="1">
+        <v>0</v>
+      </c>
+      <c r="F155" s="1">
+        <v>1</v>
+      </c>
+      <c r="G155" s="1">
+        <v>0</v>
+      </c>
+      <c r="H155" s="1">
+        <v>0</v>
+      </c>
+      <c r="I155" s="1">
+        <v>1</v>
+      </c>
+      <c r="J155" s="1">
+        <v>1</v>
+      </c>
+      <c r="K155" s="1">
+        <v>100</v>
+      </c>
+      <c r="L155" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
+      <c r="A156" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B156" s="1">
+        <v>3123</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D156" s="1">
+        <v>4</v>
+      </c>
+      <c r="E156" s="1">
+        <v>0</v>
+      </c>
+      <c r="F156" s="1">
+        <v>1</v>
+      </c>
+      <c r="G156" s="1">
+        <v>0</v>
+      </c>
+      <c r="H156" s="1">
+        <v>0</v>
+      </c>
+      <c r="I156" s="1">
+        <v>1</v>
+      </c>
+      <c r="J156" s="1">
+        <v>1</v>
+      </c>
+      <c r="K156" s="1">
+        <v>100</v>
+      </c>
+      <c r="L156" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
+      <c r="A157" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B157" s="1">
+        <v>3124</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D157" s="1">
+        <v>4</v>
+      </c>
+      <c r="E157" s="1">
+        <v>0</v>
+      </c>
+      <c r="F157" s="1">
+        <v>1</v>
+      </c>
+      <c r="G157" s="1">
+        <v>0</v>
+      </c>
+      <c r="H157" s="1">
+        <v>0</v>
+      </c>
+      <c r="I157" s="1">
+        <v>1</v>
+      </c>
+      <c r="J157" s="1">
+        <v>1</v>
+      </c>
+      <c r="K157" s="1">
+        <v>100</v>
+      </c>
+      <c r="L157" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
+      <c r="A158" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B158" s="1">
+        <v>3125</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D158" s="1">
+        <v>4</v>
+      </c>
+      <c r="E158" s="1">
+        <v>0</v>
+      </c>
+      <c r="F158" s="1">
+        <v>1</v>
+      </c>
+      <c r="G158" s="1">
+        <v>0</v>
+      </c>
+      <c r="H158" s="1">
+        <v>0</v>
+      </c>
+      <c r="I158" s="1">
+        <v>1</v>
+      </c>
+      <c r="J158" s="1">
+        <v>1</v>
+      </c>
+      <c r="K158" s="1">
+        <v>100</v>
+      </c>
+      <c r="L158" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
+      <c r="A159" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B159" s="1">
+        <v>3126</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D159" s="1">
+        <v>4</v>
+      </c>
+      <c r="E159" s="1">
+        <v>0</v>
+      </c>
+      <c r="F159" s="1">
+        <v>1</v>
+      </c>
+      <c r="G159" s="1">
+        <v>0</v>
+      </c>
+      <c r="H159" s="1">
+        <v>0</v>
+      </c>
+      <c r="I159" s="1">
+        <v>1</v>
+      </c>
+      <c r="J159" s="1">
+        <v>1</v>
+      </c>
+      <c r="K159" s="1">
+        <v>100</v>
+      </c>
+      <c r="L159" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="B160" s="1">
+        <v>3127</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D160" s="1">
+        <v>4</v>
+      </c>
+      <c r="E160" s="1">
+        <v>0</v>
+      </c>
+      <c r="F160" s="1">
+        <v>1</v>
+      </c>
+      <c r="G160" s="1">
+        <v>0</v>
+      </c>
+      <c r="H160" s="1">
+        <v>0</v>
+      </c>
+      <c r="I160" s="1">
+        <v>1</v>
+      </c>
+      <c r="J160" s="1">
+        <v>1</v>
+      </c>
+      <c r="K160" s="1">
+        <v>100</v>
+      </c>
+      <c r="L160" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="A161" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="B161" s="1">
+        <v>3128</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D161" s="1">
+        <v>4</v>
+      </c>
+      <c r="E161" s="1">
+        <v>0</v>
+      </c>
+      <c r="F161" s="1">
+        <v>1</v>
+      </c>
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+      <c r="H161" s="1">
+        <v>0</v>
+      </c>
+      <c r="I161" s="1">
+        <v>1</v>
+      </c>
+      <c r="J161" s="1">
+        <v>1</v>
+      </c>
+      <c r="K161" s="1">
+        <v>100</v>
+      </c>
+      <c r="L161" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B162" s="1">
+        <v>3129</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D162" s="1">
+        <v>4</v>
+      </c>
+      <c r="E162" s="1">
+        <v>0</v>
+      </c>
+      <c r="F162" s="1">
+        <v>1</v>
+      </c>
+      <c r="G162" s="1">
+        <v>0</v>
+      </c>
+      <c r="H162" s="1">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1">
+        <v>1</v>
+      </c>
+      <c r="J162" s="1">
+        <v>1</v>
+      </c>
+      <c r="K162" s="1">
+        <v>100</v>
+      </c>
+      <c r="L162" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="B163" s="1">
+        <v>3130</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D163" s="1">
+        <v>4</v>
+      </c>
+      <c r="E163" s="1">
+        <v>0</v>
+      </c>
+      <c r="F163" s="1">
+        <v>1</v>
+      </c>
+      <c r="G163" s="1">
+        <v>0</v>
+      </c>
+      <c r="H163" s="1">
+        <v>0</v>
+      </c>
+      <c r="I163" s="1">
+        <v>1</v>
+      </c>
+      <c r="J163" s="1">
+        <v>1</v>
+      </c>
+      <c r="K163" s="1">
+        <v>100</v>
+      </c>
+      <c r="L163" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B164" s="1">
+        <v>3131</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D164" s="1">
+        <v>4</v>
+      </c>
+      <c r="E164" s="1">
+        <v>0</v>
+      </c>
+      <c r="F164" s="1">
+        <v>1</v>
+      </c>
+      <c r="G164" s="1">
+        <v>0</v>
+      </c>
+      <c r="H164" s="1">
+        <v>0</v>
+      </c>
+      <c r="I164" s="1">
+        <v>1</v>
+      </c>
+      <c r="J164" s="1">
+        <v>1</v>
+      </c>
+      <c r="K164" s="1">
+        <v>100</v>
+      </c>
+      <c r="L164" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B165" s="1">
+        <v>3132</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D165" s="1">
+        <v>4</v>
+      </c>
+      <c r="E165" s="1">
+        <v>0</v>
+      </c>
+      <c r="F165" s="1">
+        <v>1</v>
+      </c>
+      <c r="G165" s="1">
+        <v>0</v>
+      </c>
+      <c r="H165" s="1">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1">
+        <v>1</v>
+      </c>
+      <c r="J165" s="1">
+        <v>1</v>
+      </c>
+      <c r="K165" s="1">
+        <v>100</v>
+      </c>
+      <c r="L165" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="B166" s="1">
+        <v>3133</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D166" s="1">
+        <v>4</v>
+      </c>
+      <c r="E166" s="1">
+        <v>0</v>
+      </c>
+      <c r="F166" s="1">
+        <v>1</v>
+      </c>
+      <c r="G166" s="1">
+        <v>0</v>
+      </c>
+      <c r="H166" s="1">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1">
+        <v>1</v>
+      </c>
+      <c r="J166" s="1">
+        <v>1</v>
+      </c>
+      <c r="K166" s="1">
+        <v>100</v>
+      </c>
+      <c r="L166" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B167" s="1">
+        <v>3134</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D167" s="1">
+        <v>4</v>
+      </c>
+      <c r="E167" s="1">
+        <v>0</v>
+      </c>
+      <c r="F167" s="1">
+        <v>1</v>
+      </c>
+      <c r="G167" s="1">
+        <v>0</v>
+      </c>
+      <c r="H167" s="1">
+        <v>0</v>
+      </c>
+      <c r="I167" s="1">
+        <v>1</v>
+      </c>
+      <c r="J167" s="1">
+        <v>1</v>
+      </c>
+      <c r="K167" s="1">
+        <v>100</v>
+      </c>
+      <c r="L167" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="A168" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B168" s="1">
+        <v>3135</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D168" s="1">
+        <v>4</v>
+      </c>
+      <c r="E168" s="1">
+        <v>0</v>
+      </c>
+      <c r="F168" s="1">
+        <v>1</v>
+      </c>
+      <c r="G168" s="1">
+        <v>0</v>
+      </c>
+      <c r="H168" s="1">
+        <v>0</v>
+      </c>
+      <c r="I168" s="1">
+        <v>1</v>
+      </c>
+      <c r="J168" s="1">
+        <v>1</v>
+      </c>
+      <c r="K168" s="1">
+        <v>100</v>
+      </c>
+      <c r="L168" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B169" s="1">
+        <v>3136</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D169" s="1">
+        <v>4</v>
+      </c>
+      <c r="E169" s="1">
+        <v>0</v>
+      </c>
+      <c r="F169" s="1">
+        <v>1</v>
+      </c>
+      <c r="G169" s="1">
+        <v>0</v>
+      </c>
+      <c r="H169" s="1">
+        <v>0</v>
+      </c>
+      <c r="I169" s="1">
+        <v>1</v>
+      </c>
+      <c r="J169" s="1">
+        <v>1</v>
+      </c>
+      <c r="K169" s="1">
+        <v>100</v>
+      </c>
+      <c r="L169" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B170" s="1">
+        <v>3137</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D170" s="1">
+        <v>4</v>
+      </c>
+      <c r="E170" s="1">
+        <v>0</v>
+      </c>
+      <c r="F170" s="1">
+        <v>1</v>
+      </c>
+      <c r="G170" s="1">
+        <v>0</v>
+      </c>
+      <c r="H170" s="1">
+        <v>0</v>
+      </c>
+      <c r="I170" s="1">
+        <v>1</v>
+      </c>
+      <c r="J170" s="1">
+        <v>1</v>
+      </c>
+      <c r="K170" s="1">
+        <v>100</v>
+      </c>
+      <c r="L170" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="A171" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="B171" s="1">
+        <v>3138</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D171" s="1">
+        <v>4</v>
+      </c>
+      <c r="E171" s="1">
+        <v>0</v>
+      </c>
+      <c r="F171" s="1">
+        <v>1</v>
+      </c>
+      <c r="G171" s="1">
+        <v>0</v>
+      </c>
+      <c r="H171" s="1">
+        <v>0</v>
+      </c>
+      <c r="I171" s="1">
+        <v>1</v>
+      </c>
+      <c r="J171" s="1">
+        <v>1</v>
+      </c>
+      <c r="K171" s="1">
+        <v>100</v>
+      </c>
+      <c r="L171" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="A172" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="B172" s="1">
+        <v>3139</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D172" s="1">
+        <v>4</v>
+      </c>
+      <c r="E172" s="1">
+        <v>0</v>
+      </c>
+      <c r="F172" s="1">
+        <v>1</v>
+      </c>
+      <c r="G172" s="1">
+        <v>0</v>
+      </c>
+      <c r="H172" s="1">
+        <v>0</v>
+      </c>
+      <c r="I172" s="1">
+        <v>1</v>
+      </c>
+      <c r="J172" s="1">
+        <v>1</v>
+      </c>
+      <c r="K172" s="1">
+        <v>100</v>
+      </c>
+      <c r="L172" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="A173" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B173" s="1">
+        <v>3140</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D173" s="1">
+        <v>4</v>
+      </c>
+      <c r="E173" s="1">
+        <v>0</v>
+      </c>
+      <c r="F173" s="1">
+        <v>1</v>
+      </c>
+      <c r="G173" s="1">
+        <v>0</v>
+      </c>
+      <c r="H173" s="1">
+        <v>0</v>
+      </c>
+      <c r="I173" s="1">
+        <v>1</v>
+      </c>
+      <c r="J173" s="1">
+        <v>1</v>
+      </c>
+      <c r="K173" s="1">
+        <v>100</v>
+      </c>
+      <c r="L173" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="A174" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="B174" s="1">
+        <v>3141</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D174" s="1">
+        <v>4</v>
+      </c>
+      <c r="E174" s="1">
+        <v>0</v>
+      </c>
+      <c r="F174" s="1">
+        <v>1</v>
+      </c>
+      <c r="G174" s="1">
+        <v>0</v>
+      </c>
+      <c r="H174" s="1">
+        <v>0</v>
+      </c>
+      <c r="I174" s="1">
+        <v>1</v>
+      </c>
+      <c r="J174" s="1">
+        <v>1</v>
+      </c>
+      <c r="K174" s="1">
+        <v>100</v>
+      </c>
+      <c r="L174" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="A175" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="B175" s="1">
+        <v>3142</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D175" s="1">
+        <v>4</v>
+      </c>
+      <c r="E175" s="1">
+        <v>0</v>
+      </c>
+      <c r="F175" s="1">
+        <v>1</v>
+      </c>
+      <c r="G175" s="1">
+        <v>0</v>
+      </c>
+      <c r="H175" s="1">
+        <v>0</v>
+      </c>
+      <c r="I175" s="1">
+        <v>1</v>
+      </c>
+      <c r="J175" s="1">
+        <v>1</v>
+      </c>
+      <c r="K175" s="1">
+        <v>100</v>
+      </c>
+      <c r="L175" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="A176" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="B176" s="1">
+        <v>3143</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D176" s="1">
+        <v>4</v>
+      </c>
+      <c r="E176" s="1">
+        <v>0</v>
+      </c>
+      <c r="F176" s="1">
+        <v>0</v>
+      </c>
+      <c r="G176" s="1">
+        <v>0</v>
+      </c>
+      <c r="H176" s="1">
+        <v>0</v>
+      </c>
+      <c r="I176" s="1">
+        <v>1</v>
+      </c>
+      <c r="J176" s="1">
+        <v>1</v>
+      </c>
+      <c r="K176" s="1">
+        <v>100</v>
+      </c>
+      <c r="L176" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="B177" s="1">
+        <v>3144</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D177" s="1">
+        <v>4</v>
+      </c>
+      <c r="E177" s="1">
+        <v>0</v>
+      </c>
+      <c r="F177" s="1">
+        <v>1</v>
+      </c>
+      <c r="G177" s="1">
+        <v>0</v>
+      </c>
+      <c r="H177" s="1">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>1</v>
+      </c>
+      <c r="J177" s="1">
+        <v>1</v>
+      </c>
+      <c r="K177" s="1">
+        <v>100</v>
+      </c>
+      <c r="L177" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12">
+      <c r="A178" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B178" s="1">
+        <v>3145</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D178" s="1">
+        <v>4</v>
+      </c>
+      <c r="E178" s="1">
+        <v>0</v>
+      </c>
+      <c r="F178" s="1">
+        <v>0</v>
+      </c>
+      <c r="G178" s="1">
+        <v>0</v>
+      </c>
+      <c r="H178" s="1">
+        <v>0</v>
+      </c>
+      <c r="I178" s="1">
+        <v>1</v>
+      </c>
+      <c r="J178" s="1">
+        <v>1</v>
+      </c>
+      <c r="K178" s="1">
+        <v>100</v>
+      </c>
+      <c r="L178" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B179" s="1">
+        <v>3146</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D179" s="1">
+        <v>4</v>
+      </c>
+      <c r="E179" s="1">
+        <v>0</v>
+      </c>
+      <c r="F179" s="1">
+        <v>1</v>
+      </c>
+      <c r="G179" s="1">
+        <v>0</v>
+      </c>
+      <c r="H179" s="1">
+        <v>0</v>
+      </c>
+      <c r="I179" s="1">
+        <v>1</v>
+      </c>
+      <c r="J179" s="1">
+        <v>1</v>
+      </c>
+      <c r="K179" s="1">
+        <v>100</v>
+      </c>
+      <c r="L179" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B180" s="1">
+        <v>3147</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D180" s="1">
+        <v>4</v>
+      </c>
+      <c r="E180" s="1">
+        <v>0</v>
+      </c>
+      <c r="F180" s="1">
+        <v>0</v>
+      </c>
+      <c r="G180" s="1">
+        <v>0</v>
+      </c>
+      <c r="H180" s="1">
+        <v>0</v>
+      </c>
+      <c r="I180" s="1">
+        <v>1</v>
+      </c>
+      <c r="J180" s="1">
+        <v>1</v>
+      </c>
+      <c r="K180" s="1">
+        <v>100</v>
+      </c>
+      <c r="L180" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="B181" s="1">
+        <v>3148</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D181" s="1">
+        <v>4</v>
+      </c>
+      <c r="E181" s="1">
+        <v>0</v>
+      </c>
+      <c r="F181" s="1">
+        <v>1</v>
+      </c>
+      <c r="G181" s="1">
+        <v>0</v>
+      </c>
+      <c r="H181" s="1">
+        <v>0</v>
+      </c>
+      <c r="I181" s="1">
+        <v>1</v>
+      </c>
+      <c r="J181" s="1">
+        <v>1</v>
+      </c>
+      <c r="K181" s="1">
+        <v>100</v>
+      </c>
+      <c r="L181" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="A182" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B182" s="1">
+        <v>3149</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D182" s="1">
+        <v>4</v>
+      </c>
+      <c r="E182" s="1">
+        <v>0</v>
+      </c>
+      <c r="F182" s="1">
+        <v>1</v>
+      </c>
+      <c r="G182" s="1">
+        <v>0</v>
+      </c>
+      <c r="H182" s="1">
+        <v>0</v>
+      </c>
+      <c r="I182" s="1">
+        <v>1</v>
+      </c>
+      <c r="J182" s="1">
+        <v>1</v>
+      </c>
+      <c r="K182" s="1">
+        <v>100</v>
+      </c>
+      <c r="L182" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="A183" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B183" s="1">
+        <v>3150</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D183" s="1">
+        <v>4</v>
+      </c>
+      <c r="E183" s="1">
+        <v>0</v>
+      </c>
+      <c r="F183" s="1">
+        <v>1</v>
+      </c>
+      <c r="G183" s="1">
+        <v>0</v>
+      </c>
+      <c r="H183" s="1">
+        <v>0</v>
+      </c>
+      <c r="I183" s="1">
+        <v>1</v>
+      </c>
+      <c r="J183" s="1">
+        <v>1</v>
+      </c>
+      <c r="K183" s="1">
+        <v>100</v>
+      </c>
+      <c r="L183" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="A184" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B184" s="1">
+        <v>3151</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D184" s="1">
+        <v>4</v>
+      </c>
+      <c r="E184" s="1">
+        <v>0</v>
+      </c>
+      <c r="F184" s="1">
+        <v>1</v>
+      </c>
+      <c r="G184" s="1">
+        <v>0</v>
+      </c>
+      <c r="H184" s="1">
+        <v>0</v>
+      </c>
+      <c r="I184" s="1">
+        <v>1</v>
+      </c>
+      <c r="J184" s="1">
+        <v>1</v>
+      </c>
+      <c r="K184" s="1">
+        <v>100</v>
+      </c>
+      <c r="L184" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="A185" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B185" s="1">
+        <v>3152</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D185" s="1">
+        <v>4</v>
+      </c>
+      <c r="E185" s="1">
+        <v>0</v>
+      </c>
+      <c r="F185" s="1">
+        <v>1</v>
+      </c>
+      <c r="G185" s="1">
+        <v>0</v>
+      </c>
+      <c r="H185" s="1">
+        <v>0</v>
+      </c>
+      <c r="I185" s="1">
+        <v>1</v>
+      </c>
+      <c r="J185" s="1">
+        <v>1</v>
+      </c>
+      <c r="K185" s="1">
+        <v>100</v>
+      </c>
+      <c r="L185" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="A186" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="B186" s="1">
+        <v>3153</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D186" s="1">
+        <v>4</v>
+      </c>
+      <c r="E186" s="1">
+        <v>0</v>
+      </c>
+      <c r="F186" s="1">
+        <v>1</v>
+      </c>
+      <c r="G186" s="1">
+        <v>0</v>
+      </c>
+      <c r="H186" s="1">
+        <v>0</v>
+      </c>
+      <c r="I186" s="1">
+        <v>1</v>
+      </c>
+      <c r="J186" s="1">
+        <v>1</v>
+      </c>
+      <c r="K186" s="1">
+        <v>100</v>
+      </c>
+      <c r="L186" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="A187" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B187" s="1">
+        <v>3154</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D187" s="1">
+        <v>4</v>
+      </c>
+      <c r="E187" s="1">
+        <v>0</v>
+      </c>
+      <c r="F187" s="1">
+        <v>1</v>
+      </c>
+      <c r="G187" s="1">
+        <v>0</v>
+      </c>
+      <c r="H187" s="1">
+        <v>0</v>
+      </c>
+      <c r="I187" s="1">
+        <v>1</v>
+      </c>
+      <c r="J187" s="1">
+        <v>1</v>
+      </c>
+      <c r="K187" s="1">
+        <v>100</v>
+      </c>
+      <c r="L187" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12">
+      <c r="A188" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B188" s="1">
+        <v>3155</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D188" s="1">
+        <v>4</v>
+      </c>
+      <c r="E188" s="1">
+        <v>0</v>
+      </c>
+      <c r="F188" s="1">
+        <v>1</v>
+      </c>
+      <c r="G188" s="1">
+        <v>0</v>
+      </c>
+      <c r="H188" s="1">
+        <v>0</v>
+      </c>
+      <c r="I188" s="1">
+        <v>1</v>
+      </c>
+      <c r="J188" s="1">
+        <v>1</v>
+      </c>
+      <c r="K188" s="1">
+        <v>100</v>
+      </c>
+      <c r="L188" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12">
+      <c r="A189" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="B189" s="1">
+        <v>3156</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D189" s="1">
+        <v>4</v>
+      </c>
+      <c r="E189" s="1">
+        <v>0</v>
+      </c>
+      <c r="F189" s="1">
+        <v>1</v>
+      </c>
+      <c r="G189" s="1">
+        <v>0</v>
+      </c>
+      <c r="H189" s="1">
+        <v>0</v>
+      </c>
+      <c r="I189" s="1">
+        <v>1</v>
+      </c>
+      <c r="J189" s="1">
+        <v>1</v>
+      </c>
+      <c r="K189" s="1">
+        <v>100</v>
+      </c>
+      <c r="L189" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12">
+      <c r="A190" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B190" s="1">
+        <v>3157</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D190" s="1">
+        <v>4</v>
+      </c>
+      <c r="E190" s="1">
+        <v>0</v>
+      </c>
+      <c r="F190" s="1">
+        <v>1</v>
+      </c>
+      <c r="G190" s="1">
+        <v>0</v>
+      </c>
+      <c r="H190" s="1">
+        <v>0</v>
+      </c>
+      <c r="I190" s="1">
+        <v>1</v>
+      </c>
+      <c r="J190" s="1">
+        <v>1</v>
+      </c>
+      <c r="K190" s="1">
+        <v>100</v>
+      </c>
+      <c r="L190" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="B191" s="1">
+        <v>3158</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D191" s="1">
+        <v>4</v>
+      </c>
+      <c r="E191" s="1">
+        <v>0</v>
+      </c>
+      <c r="F191" s="1">
+        <v>1</v>
+      </c>
+      <c r="G191" s="1">
+        <v>0</v>
+      </c>
+      <c r="H191" s="1">
+        <v>0</v>
+      </c>
+      <c r="I191" s="1">
+        <v>1</v>
+      </c>
+      <c r="J191" s="1">
+        <v>1</v>
+      </c>
+      <c r="K191" s="1">
+        <v>100</v>
+      </c>
+      <c r="L191" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12">
+      <c r="A192" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="B192" s="1">
+        <v>3159</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D192" s="1">
+        <v>4</v>
+      </c>
+      <c r="E192" s="1">
+        <v>0</v>
+      </c>
+      <c r="F192" s="1">
+        <v>1</v>
+      </c>
+      <c r="G192" s="1">
+        <v>0</v>
+      </c>
+      <c r="H192" s="1">
+        <v>0</v>
+      </c>
+      <c r="I192" s="1">
+        <v>1</v>
+      </c>
+      <c r="J192" s="1">
+        <v>1</v>
+      </c>
+      <c r="K192" s="1">
+        <v>100</v>
+      </c>
+      <c r="L192" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12">
+      <c r="A193" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="B193" s="1">
+        <v>3160</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D193" s="1">
+        <v>4</v>
+      </c>
+      <c r="E193" s="1">
+        <v>0</v>
+      </c>
+      <c r="F193" s="1">
+        <v>1</v>
+      </c>
+      <c r="G193" s="1">
+        <v>0</v>
+      </c>
+      <c r="H193" s="1">
+        <v>0</v>
+      </c>
+      <c r="I193" s="1">
+        <v>1</v>
+      </c>
+      <c r="J193" s="1">
+        <v>1</v>
+      </c>
+      <c r="K193" s="1">
+        <v>100</v>
+      </c>
+      <c r="L193" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12">
+      <c r="A194" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B194" s="1">
+        <v>3161</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D194" s="1">
+        <v>4</v>
+      </c>
+      <c r="E194" s="1">
+        <v>0</v>
+      </c>
+      <c r="F194" s="1">
+        <v>1</v>
+      </c>
+      <c r="G194" s="1">
+        <v>0</v>
+      </c>
+      <c r="H194" s="1">
+        <v>0</v>
+      </c>
+      <c r="I194" s="1">
+        <v>1</v>
+      </c>
+      <c r="J194" s="1">
+        <v>1</v>
+      </c>
+      <c r="K194" s="1">
+        <v>100</v>
+      </c>
+      <c r="L194" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12">
+      <c r="A195" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="B195" s="1">
+        <v>3162</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D195" s="1">
+        <v>4</v>
+      </c>
+      <c r="E195" s="1">
+        <v>0</v>
+      </c>
+      <c r="F195" s="1">
+        <v>1</v>
+      </c>
+      <c r="G195" s="1">
+        <v>0</v>
+      </c>
+      <c r="H195" s="1">
+        <v>0</v>
+      </c>
+      <c r="I195" s="1">
+        <v>1</v>
+      </c>
+      <c r="J195" s="1">
+        <v>1</v>
+      </c>
+      <c r="K195" s="1">
+        <v>100</v>
+      </c>
+      <c r="L195" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12">
+      <c r="A196" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B196" s="1">
+        <v>3163</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D196" s="1">
+        <v>4</v>
+      </c>
+      <c r="E196" s="1">
+        <v>0</v>
+      </c>
+      <c r="F196" s="1">
+        <v>1</v>
+      </c>
+      <c r="G196" s="1">
+        <v>0</v>
+      </c>
+      <c r="H196" s="1">
+        <v>0</v>
+      </c>
+      <c r="I196" s="1">
+        <v>1</v>
+      </c>
+      <c r="J196" s="1">
+        <v>1</v>
+      </c>
+      <c r="K196" s="1">
+        <v>100</v>
+      </c>
+      <c r="L196" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12">
+      <c r="A197" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="B197" s="1">
+        <v>3164</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D197" s="1">
+        <v>4</v>
+      </c>
+      <c r="E197" s="1">
+        <v>0</v>
+      </c>
+      <c r="F197" s="1">
+        <v>1</v>
+      </c>
+      <c r="G197" s="1">
+        <v>0</v>
+      </c>
+      <c r="H197" s="1">
+        <v>0</v>
+      </c>
+      <c r="I197" s="1">
+        <v>1</v>
+      </c>
+      <c r="J197" s="1">
+        <v>1</v>
+      </c>
+      <c r="K197" s="1">
+        <v>100</v>
+      </c>
+      <c r="L197" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12">
+      <c r="A198" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B198" s="1">
+        <v>3165</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D198" s="1">
+        <v>4</v>
+      </c>
+      <c r="E198" s="1">
+        <v>0</v>
+      </c>
+      <c r="F198" s="1">
+        <v>1</v>
+      </c>
+      <c r="G198" s="1">
+        <v>0</v>
+      </c>
+      <c r="H198" s="1">
+        <v>0</v>
+      </c>
+      <c r="I198" s="1">
+        <v>1</v>
+      </c>
+      <c r="J198" s="1">
+        <v>1</v>
+      </c>
+      <c r="K198" s="1">
+        <v>100</v>
+      </c>
+      <c r="L198" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12">
+      <c r="A199" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B199" s="1">
+        <v>3166</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D199" s="1">
+        <v>4</v>
+      </c>
+      <c r="E199" s="1">
+        <v>0</v>
+      </c>
+      <c r="F199" s="1">
+        <v>1</v>
+      </c>
+      <c r="G199" s="1">
+        <v>0</v>
+      </c>
+      <c r="H199" s="1">
+        <v>0</v>
+      </c>
+      <c r="I199" s="1">
+        <v>1</v>
+      </c>
+      <c r="J199" s="1">
+        <v>1</v>
+      </c>
+      <c r="K199" s="1">
+        <v>100</v>
+      </c>
+      <c r="L199" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12">
+      <c r="A200" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B200" s="1">
+        <v>3167</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D200" s="1">
+        <v>4</v>
+      </c>
+      <c r="E200" s="1">
+        <v>0</v>
+      </c>
+      <c r="F200" s="1">
+        <v>1</v>
+      </c>
+      <c r="G200" s="1">
+        <v>0</v>
+      </c>
+      <c r="H200" s="1">
+        <v>0</v>
+      </c>
+      <c r="I200" s="1">
+        <v>1</v>
+      </c>
+      <c r="J200" s="1">
+        <v>1</v>
+      </c>
+      <c r="K200" s="1">
+        <v>100</v>
+      </c>
+      <c r="L200" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
+      <c r="A201" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="B201" s="1">
+        <v>3168</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D201" s="1">
+        <v>4</v>
+      </c>
+      <c r="E201" s="1">
+        <v>0</v>
+      </c>
+      <c r="F201" s="1">
+        <v>1</v>
+      </c>
+      <c r="G201" s="1">
+        <v>0</v>
+      </c>
+      <c r="H201" s="1">
+        <v>0</v>
+      </c>
+      <c r="I201" s="1">
+        <v>1</v>
+      </c>
+      <c r="J201" s="1">
+        <v>1</v>
+      </c>
+      <c r="K201" s="1">
+        <v>100</v>
+      </c>
+      <c r="L201" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12">
+      <c r="A202" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="B202" s="1">
+        <v>3169</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D202" s="1">
+        <v>4</v>
+      </c>
+      <c r="E202" s="1">
+        <v>0</v>
+      </c>
+      <c r="F202" s="1">
+        <v>1</v>
+      </c>
+      <c r="G202" s="1">
+        <v>0</v>
+      </c>
+      <c r="H202" s="1">
+        <v>0</v>
+      </c>
+      <c r="I202" s="1">
+        <v>1</v>
+      </c>
+      <c r="J202" s="1">
+        <v>1</v>
+      </c>
+      <c r="K202" s="1">
+        <v>100</v>
+      </c>
+      <c r="L202" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12">
+      <c r="A203" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="B203" s="1">
+        <v>3170</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D203" s="1">
+        <v>4</v>
+      </c>
+      <c r="E203" s="1">
+        <v>0</v>
+      </c>
+      <c r="F203" s="1">
+        <v>1</v>
+      </c>
+      <c r="G203" s="1">
+        <v>0</v>
+      </c>
+      <c r="H203" s="1">
+        <v>0</v>
+      </c>
+      <c r="I203" s="1">
+        <v>1</v>
+      </c>
+      <c r="J203" s="1">
+        <v>1</v>
+      </c>
+      <c r="K203" s="1">
+        <v>100</v>
+      </c>
+      <c r="L203" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12">
+      <c r="A204" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B204" s="1">
+        <v>3171</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D204" s="1">
+        <v>4</v>
+      </c>
+      <c r="E204" s="1">
+        <v>0</v>
+      </c>
+      <c r="F204" s="1">
+        <v>1</v>
+      </c>
+      <c r="G204" s="1">
+        <v>0</v>
+      </c>
+      <c r="H204" s="1">
+        <v>0</v>
+      </c>
+      <c r="I204" s="1">
+        <v>1</v>
+      </c>
+      <c r="J204" s="1">
+        <v>1</v>
+      </c>
+      <c r="K204" s="1">
+        <v>100</v>
+      </c>
+      <c r="L204" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12">
+      <c r="A205" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="B205" s="1">
+        <v>3172</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D205" s="1">
+        <v>4</v>
+      </c>
+      <c r="E205" s="1">
+        <v>0</v>
+      </c>
+      <c r="F205" s="1">
+        <v>1</v>
+      </c>
+      <c r="G205" s="1">
+        <v>0</v>
+      </c>
+      <c r="H205" s="1">
+        <v>0</v>
+      </c>
+      <c r="I205" s="1">
+        <v>1</v>
+      </c>
+      <c r="J205" s="1">
+        <v>1</v>
+      </c>
+      <c r="K205" s="1">
+        <v>100</v>
+      </c>
+      <c r="L205" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12">
+      <c r="A206" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="B206" s="1">
+        <v>3173</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D206" s="1">
+        <v>4</v>
+      </c>
+      <c r="E206" s="1">
+        <v>0</v>
+      </c>
+      <c r="F206" s="1">
+        <v>1</v>
+      </c>
+      <c r="G206" s="1">
+        <v>0</v>
+      </c>
+      <c r="H206" s="1">
+        <v>0</v>
+      </c>
+      <c r="I206" s="1">
+        <v>1</v>
+      </c>
+      <c r="J206" s="1">
+        <v>1</v>
+      </c>
+      <c r="K206" s="1">
+        <v>100</v>
+      </c>
+      <c r="L206" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12">
+      <c r="A207" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="B207" s="1">
+        <v>3174</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D207" s="1">
+        <v>4</v>
+      </c>
+      <c r="E207" s="1">
+        <v>0</v>
+      </c>
+      <c r="F207" s="1">
+        <v>1</v>
+      </c>
+      <c r="G207" s="1">
+        <v>0</v>
+      </c>
+      <c r="H207" s="1">
+        <v>0</v>
+      </c>
+      <c r="I207" s="1">
+        <v>1</v>
+      </c>
+      <c r="J207" s="1">
+        <v>1</v>
+      </c>
+      <c r="K207" s="1">
+        <v>100</v>
+      </c>
+      <c r="L207" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12">
+      <c r="A208" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="B208" s="1">
+        <v>3175</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D208" s="1">
+        <v>4</v>
+      </c>
+      <c r="E208" s="1">
+        <v>0</v>
+      </c>
+      <c r="F208" s="1">
+        <v>1</v>
+      </c>
+      <c r="G208" s="1">
+        <v>0</v>
+      </c>
+      <c r="H208" s="1">
+        <v>0</v>
+      </c>
+      <c r="I208" s="1">
+        <v>1</v>
+      </c>
+      <c r="J208" s="1">
+        <v>1</v>
+      </c>
+      <c r="K208" s="1">
+        <v>100</v>
+      </c>
+      <c r="L208" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12">
+      <c r="A209" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="B209" s="1">
+        <v>3176</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D209" s="1">
+        <v>4</v>
+      </c>
+      <c r="E209" s="1">
+        <v>0</v>
+      </c>
+      <c r="F209" s="1">
+        <v>1</v>
+      </c>
+      <c r="G209" s="1">
+        <v>0</v>
+      </c>
+      <c r="H209" s="1">
+        <v>0</v>
+      </c>
+      <c r="I209" s="1">
+        <v>1</v>
+      </c>
+      <c r="J209" s="1">
+        <v>1</v>
+      </c>
+      <c r="K209" s="1">
+        <v>100</v>
+      </c>
+      <c r="L209" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12">
+      <c r="A210" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B210" s="1">
+        <v>3177</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D210" s="1">
+        <v>4</v>
+      </c>
+      <c r="E210" s="1">
+        <v>0</v>
+      </c>
+      <c r="F210" s="1">
+        <v>1</v>
+      </c>
+      <c r="G210" s="1">
+        <v>0</v>
+      </c>
+      <c r="H210" s="1">
+        <v>0</v>
+      </c>
+      <c r="I210" s="1">
+        <v>1</v>
+      </c>
+      <c r="J210" s="1">
+        <v>1</v>
+      </c>
+      <c r="K210" s="1">
+        <v>100</v>
+      </c>
+      <c r="L210" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12">
+      <c r="A211" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B211" s="1">
+        <v>3178</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D211" s="1">
+        <v>4</v>
+      </c>
+      <c r="E211" s="1">
+        <v>0</v>
+      </c>
+      <c r="F211" s="1">
+        <v>1</v>
+      </c>
+      <c r="G211" s="1">
+        <v>0</v>
+      </c>
+      <c r="H211" s="1">
+        <v>0</v>
+      </c>
+      <c r="I211" s="1">
+        <v>1</v>
+      </c>
+      <c r="J211" s="1">
+        <v>1</v>
+      </c>
+      <c r="K211" s="1">
+        <v>100</v>
+      </c>
+      <c r="L211" s="1">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -6359,9 +10083,591 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <dimension ref="A2:J83"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D10" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" t="s">
+        <v>271</v>
+      </c>
+      <c r="E23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F23" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" t="s">
+        <v>264</v>
+      </c>
+      <c r="G24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E25" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D27" t="s">
+        <v>271</v>
+      </c>
+      <c r="E27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>271</v>
+      </c>
+      <c r="I29" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="I30" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G32" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="I33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F35" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="16.5">
+      <c r="A36" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="G37" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E38" t="s">
+        <v>232</v>
+      </c>
+      <c r="I38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="16.5">
+      <c r="A39" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="G39" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G40" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" t="s">
+        <v>244</v>
+      </c>
+      <c r="J41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" t="s">
+        <v>246</v>
+      </c>
+      <c r="J43" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44" t="s">
+        <v>250</v>
+      </c>
+      <c r="J44" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I46" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I49" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="B54" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" t="s">
+        <v>283</v>
+      </c>
+      <c r="D54" t="s">
+        <v>285</v>
+      </c>
+      <c r="F54" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B65" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B70" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16.5">
+      <c r="A73" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B74" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" t="s">
+        <v>246</v>
+      </c>
+      <c r="G77" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" t="s">
+        <v>250</v>
+      </c>
+      <c r="G78" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G79" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B80" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B83" t="s">
+        <v>261</v>
+      </c>
+      <c r="G83" t="s">
+        <v>277</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="428">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -239,9 +239,6 @@
   </si>
   <si>
     <t>玉米</t>
-  </si>
-  <si>
-    <t>大麦</t>
   </si>
   <si>
     <t>土豆</t>
@@ -950,9 +947,6 @@
   </si>
   <si>
     <t>阳光男孩</t>
-  </si>
-  <si>
-    <t>阳光男孩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1148,9 +1142,6 @@
     <t>饭团</t>
   </si>
   <si>
-    <t>烤面包</t>
-  </si>
-  <si>
     <t>烤海苔</t>
   </si>
   <si>
@@ -1305,6 +1296,292 @@
   </si>
   <si>
     <t>黄油</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小麦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海苔</t>
+  </si>
+  <si>
+    <t>河豚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>搅拌机</t>
+  </si>
+  <si>
+    <t>搅拌机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来搅拌食材的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海苔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌芜菁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酸味香料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辣蟹堡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤西兰花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤海苔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤肉饼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆泥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海鲜饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉米汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤玉米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔬菜汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤蜜薯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤茄子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饺子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炖菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤芦笋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莓莓果汁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红菜汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豌豆汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草莓牛奶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼饭团</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿铁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑咖啡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>葡萄酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伏特加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啤酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朗姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野蜂拉格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绯红之吻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双莓白兰地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐烤鲮鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐烤丁鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐烤虹鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤鲷鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐烤金鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐烤鲑鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤沙丁鱼串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤竹荚鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤海鳗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤比目鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤河豚鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤条石鲷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤红鲷鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤蓝蟹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤龙虾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤金枪鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海鲜浓汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳗鱼饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼刺身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炖煮条石鲷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红鲷刺身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河豚刺身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹煲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金枪鱼刺身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙虾鱼子酱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌芜菁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲫鱼蔬菜汤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1378,7 +1655,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1394,6 +1671,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1427,7 +1710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1472,6 +1755,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1779,7 +2068,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q211"/>
+  <dimension ref="A2:Q213"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -1901,13 +2190,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -1937,18 +2226,18 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -1978,18 +2267,18 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B6" s="1">
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -2019,21 +2308,21 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B7" s="1">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -2063,18 +2352,18 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B8" s="1">
         <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -2104,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1">
@@ -2197,7 +2486,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B11" s="3">
         <v>1003</v>
@@ -2597,7 +2886,7 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="3">
         <v>1013</v>
@@ -2637,7 +2926,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" s="3">
         <v>1014</v>
@@ -2677,7 +2966,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3">
         <v>1015</v>
@@ -2757,7 +3046,7 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3">
         <v>1017</v>
@@ -2875,14 +3164,14 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="5" t="s">
-        <v>50</v>
+        <v>356</v>
       </c>
       <c r="B28" s="3">
         <v>1020</v>
       </c>
       <c r="C28" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>大麦_01</v>
+        <v>小麦_01</v>
       </c>
       <c r="D28" s="1">
         <v>5</v>
@@ -2914,7 +3203,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" s="3">
         <v>1021</v>
@@ -2992,7 +3281,7 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="3">
         <v>1023</v>
@@ -3031,7 +3320,7 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" s="3">
         <v>1024</v>
@@ -3070,7 +3359,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" s="3">
         <v>1025</v>
@@ -3109,7 +3398,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" s="3">
         <v>1026</v>
@@ -3148,7 +3437,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" s="3">
         <v>1027</v>
@@ -3187,7 +3476,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" s="3">
         <v>1028</v>
@@ -3226,14 +3515,14 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" s="3">
         <f>B9+100</f>
         <v>1101</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -3265,14 +3554,14 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B38" s="3">
         <f t="shared" ref="B38:B64" si="1">B10+100</f>
         <v>1102</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
@@ -3304,14 +3593,14 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B39" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -3343,14 +3632,14 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" s="3">
         <f t="shared" si="1"/>
         <v>1104</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
@@ -3382,14 +3671,14 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41" s="3">
         <f t="shared" si="1"/>
         <v>1105</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -3421,14 +3710,14 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42" s="3">
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -3460,14 +3749,14 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B43" s="3">
         <f t="shared" si="1"/>
         <v>1107</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -3499,14 +3788,14 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B44" s="3">
         <f t="shared" si="1"/>
         <v>1108</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
@@ -3538,14 +3827,14 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B45" s="3">
         <f t="shared" si="1"/>
         <v>1109</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
@@ -3577,14 +3866,14 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B46" s="3">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
@@ -3616,14 +3905,14 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B47" s="3">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -3655,14 +3944,14 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B48" s="3">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -3694,14 +3983,14 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B49" s="3">
         <f t="shared" si="1"/>
         <v>1113</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -3733,14 +4022,14 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B50" s="3">
         <f t="shared" si="1"/>
         <v>1114</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -3772,14 +4061,14 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B51" s="3">
         <f t="shared" si="1"/>
         <v>1115</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -3811,14 +4100,14 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" s="3">
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -3850,14 +4139,14 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B53" s="3">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -3889,14 +4178,14 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B54" s="3">
         <f t="shared" si="1"/>
         <v>1118</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -3928,14 +4217,14 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B55" s="3">
         <f t="shared" si="1"/>
         <v>1119</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -3967,14 +4256,14 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B56" s="3">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -4006,14 +4295,14 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="3">
         <f t="shared" si="1"/>
         <v>1121</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
@@ -4045,14 +4334,14 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58" s="3">
         <f t="shared" si="1"/>
         <v>1122</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
@@ -4084,14 +4373,14 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B59" s="3">
         <f t="shared" si="1"/>
         <v>1123</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
@@ -4123,14 +4412,14 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B60" s="3">
         <f t="shared" si="1"/>
         <v>1124</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
@@ -4162,14 +4451,14 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B61" s="3">
         <f t="shared" si="1"/>
         <v>1125</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
@@ -4201,14 +4490,14 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B62" s="3">
         <f t="shared" si="1"/>
         <v>1126</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -4240,14 +4529,14 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B63" s="3">
         <f t="shared" si="1"/>
         <v>1127</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
@@ -4279,14 +4568,14 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B64" s="3">
         <f t="shared" si="1"/>
         <v>1128</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
@@ -4479,13 +4768,13 @@
     </row>
     <row r="69" spans="1:17">
       <c r="A69" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B69" s="1">
         <v>2004</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D69" s="1">
         <v>6</v>
@@ -4515,18 +4804,18 @@
         <v>100</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:17">
       <c r="A70" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B70" s="1">
         <v>2100</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D70" s="1">
         <v>10</v>
@@ -4556,18 +4845,18 @@
         <v>100</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:17">
       <c r="A71" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B71" s="1">
         <v>2101</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D71" s="1">
         <v>10</v>
@@ -4597,18 +4886,18 @@
         <v>100</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:17">
       <c r="A72" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B72" s="1">
         <v>2102</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D72" s="1">
         <v>10</v>
@@ -4638,18 +4927,18 @@
         <v>100</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:17">
       <c r="A73" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B73" s="1">
         <v>2103</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D73" s="1">
         <v>10</v>
@@ -4679,18 +4968,18 @@
         <v>100</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:17">
       <c r="A74" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B74" s="1">
         <v>2104</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D74" s="1">
         <v>10</v>
@@ -4720,18 +5009,18 @@
         <v>100</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:17">
       <c r="A75" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B75" s="1">
         <v>2105</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D75" s="1">
         <v>10</v>
@@ -4761,18 +5050,18 @@
         <v>100</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:17">
       <c r="A76" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B76" s="1">
         <v>2106</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D76" s="1">
         <v>10</v>
@@ -4802,18 +5091,18 @@
         <v>100</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:17">
       <c r="A77" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B77" s="1">
         <v>2107</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D77" s="1">
         <v>10</v>
@@ -4843,18 +5132,18 @@
         <v>100</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="1:17">
       <c r="A78" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B78" s="1">
         <v>2108</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D78" s="1">
         <v>10</v>
@@ -4884,18 +5173,18 @@
         <v>100</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:17">
       <c r="A79" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B79" s="1">
         <v>2109</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D79" s="1">
         <v>10</v>
@@ -4925,18 +5214,18 @@
         <v>100</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" spans="1:17">
       <c r="A80" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B80" s="1">
         <v>2110</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D80" s="1">
         <v>10</v>
@@ -4966,18 +5255,18 @@
         <v>100</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:17">
       <c r="A81" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B81" s="1">
         <v>2111</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D81" s="1">
         <v>10</v>
@@ -5007,18 +5296,18 @@
         <v>100</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="82" spans="1:17">
       <c r="A82" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B82" s="1">
         <v>2112</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D82" s="1">
         <v>10</v>
@@ -5048,18 +5337,18 @@
         <v>100</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="1:17">
       <c r="A83" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B83" s="1">
         <v>2113</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D83" s="1">
         <v>10</v>
@@ -5089,18 +5378,18 @@
         <v>100</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="12.75" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B84" s="1">
         <v>2200</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D84" s="1">
         <v>10</v>
@@ -5130,18 +5419,18 @@
         <v>100</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:17">
       <c r="A85" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B85" s="1">
         <v>2201</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D85" s="1">
         <v>10</v>
@@ -5171,65 +5460,65 @@
         <v>100</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="15">
-      <c r="A86" s="12" t="s">
-        <v>297</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17">
+      <c r="A86" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="B86" s="1">
+        <v>2202</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D86" s="1">
+        <v>10</v>
+      </c>
+      <c r="E86" s="1">
+        <v>2202</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1</v>
+      </c>
+      <c r="K86" s="1">
+        <v>100</v>
+      </c>
+      <c r="L86" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q86" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="15">
+      <c r="A87" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B87" s="1">
         <v>4000</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D86" s="1">
-        <v>3</v>
-      </c>
-      <c r="E86" s="7">
-        <v>1000</v>
-      </c>
-      <c r="F86" s="1">
-        <v>1</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0</v>
-      </c>
-      <c r="H86" s="1">
-        <v>0</v>
-      </c>
-      <c r="I86" s="1">
-        <v>9</v>
-      </c>
-      <c r="J86" s="1">
-        <v>1</v>
-      </c>
-      <c r="K86" s="1">
-        <v>100</v>
-      </c>
-      <c r="L86" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q86" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17">
-      <c r="A87" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B87" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>142</v>
+      <c r="C87" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
       </c>
       <c r="E87" s="7">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F87" s="1">
         <v>1</v>
@@ -5252,8 +5541,8 @@
       <c r="L87" s="1">
         <v>100</v>
       </c>
-      <c r="Q87" s="7" t="s">
-        <v>142</v>
+      <c r="Q87" s="6" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:17">
@@ -5261,7 +5550,7 @@
         <v>141</v>
       </c>
       <c r="B88" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>141</v>
@@ -5270,7 +5559,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="7">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F88" s="1">
         <v>1</v>
@@ -5299,19 +5588,19 @@
     </row>
     <row r="89" spans="1:17">
       <c r="A89" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B89" s="1">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D89" s="1">
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="F89" s="1">
         <v>1</v>
@@ -5335,24 +5624,24 @@
         <v>100</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:17">
       <c r="A90" s="7" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="B90" s="1">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="D90" s="1">
         <v>3</v>
       </c>
       <c r="E90" s="7">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
@@ -5376,24 +5665,24 @@
         <v>100</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91" spans="1:17">
-      <c r="A91" s="8" t="s">
-        <v>145</v>
+      <c r="A91" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="B91" s="1">
-        <v>4008</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>145</v>
+        <v>4007</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="D91" s="1">
         <v>3</v>
       </c>
       <c r="E91" s="7">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F91" s="1">
         <v>1</v>
@@ -5416,25 +5705,25 @@
       <c r="L91" s="1">
         <v>100</v>
       </c>
-      <c r="Q91" s="8" t="s">
-        <v>145</v>
+      <c r="Q91" s="7" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="92" spans="1:17">
-      <c r="A92" s="7" t="s">
-        <v>146</v>
+      <c r="A92" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="B92" s="1">
-        <v>4009</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>146</v>
+        <v>4008</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="D92" s="1">
         <v>3</v>
       </c>
       <c r="E92" s="7">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
@@ -5457,25 +5746,25 @@
       <c r="L92" s="1">
         <v>100</v>
       </c>
-      <c r="Q92" s="7" t="s">
-        <v>146</v>
+      <c r="Q92" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:17">
-      <c r="A93" s="8" t="s">
-        <v>147</v>
+      <c r="A93" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="B93" s="1">
-        <v>4010</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>147</v>
+        <v>4009</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="D93" s="1">
         <v>3</v>
       </c>
       <c r="E93" s="7">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F93" s="1">
         <v>1</v>
@@ -5498,25 +5787,25 @@
       <c r="L93" s="1">
         <v>100</v>
       </c>
-      <c r="Q93" s="8" t="s">
-        <v>147</v>
+      <c r="Q93" s="7" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:17">
-      <c r="A94" s="7" t="s">
-        <v>148</v>
+      <c r="A94" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="B94" s="1">
-        <v>4011</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>148</v>
+        <v>4010</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
       </c>
       <c r="E94" s="7">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F94" s="1">
         <v>1</v>
@@ -5539,25 +5828,25 @@
       <c r="L94" s="1">
         <v>100</v>
       </c>
-      <c r="Q94" s="7" t="s">
-        <v>148</v>
+      <c r="Q94" s="8" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:17">
       <c r="A95" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B95" s="1">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" s="7">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F95" s="1">
         <v>1</v>
@@ -5581,24 +5870,24 @@
         <v>100</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="96" spans="1:17">
       <c r="A96" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B96" s="1">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96" s="7">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F96" s="1">
         <v>1</v>
@@ -5622,24 +5911,24 @@
         <v>100</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="97" spans="1:17">
       <c r="A97" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B97" s="1">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
       </c>
       <c r="E97" s="7">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
@@ -5663,24 +5952,24 @@
         <v>100</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:17">
       <c r="A98" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B98" s="1">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D98" s="1">
         <v>3</v>
       </c>
       <c r="E98" s="7">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F98" s="1">
         <v>1</v>
@@ -5704,24 +5993,24 @@
         <v>100</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:17">
       <c r="A99" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B99" s="1">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D99" s="1">
         <v>3</v>
       </c>
       <c r="E99" s="7">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
@@ -5745,24 +6034,24 @@
         <v>100</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" spans="1:17">
       <c r="A100" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B100" s="1">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D100" s="1">
         <v>3</v>
       </c>
       <c r="E100" s="7">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -5786,24 +6075,24 @@
         <v>100</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" spans="1:17">
       <c r="A101" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B101" s="1">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D101" s="1">
         <v>3</v>
       </c>
       <c r="E101" s="7">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
@@ -5827,24 +6116,24 @@
         <v>100</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="102" spans="1:17">
-      <c r="A102" s="8" t="s">
-        <v>156</v>
+      <c r="A102" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="B102" s="1">
-        <v>4020</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>156</v>
+        <v>4018</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="D102" s="1">
         <v>3</v>
       </c>
       <c r="E102" s="7">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
@@ -5867,25 +6156,25 @@
       <c r="L102" s="1">
         <v>100</v>
       </c>
-      <c r="Q102" s="8" t="s">
-        <v>156</v>
+      <c r="Q102" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="103" spans="1:17">
-      <c r="A103" s="7" t="s">
-        <v>157</v>
+      <c r="A103" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="B103" s="1">
-        <v>4021</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>157</v>
+        <v>4020</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="D103" s="1">
         <v>3</v>
       </c>
       <c r="E103" s="7">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
@@ -5908,25 +6197,25 @@
       <c r="L103" s="1">
         <v>100</v>
       </c>
-      <c r="Q103" s="7" t="s">
-        <v>157</v>
+      <c r="Q103" s="8" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="104" spans="1:17">
       <c r="A104" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B104" s="1">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D104" s="1">
         <v>3</v>
       </c>
       <c r="E104" s="7">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -5950,24 +6239,24 @@
         <v>100</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="105" spans="1:17">
       <c r="A105" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B105" s="1">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D105" s="1">
         <v>3</v>
       </c>
       <c r="E105" s="7">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -5991,24 +6280,24 @@
         <v>100</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:17">
       <c r="A106" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B106" s="1">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D106" s="1">
         <v>3</v>
       </c>
       <c r="E106" s="7">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
@@ -6032,24 +6321,24 @@
         <v>100</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="107" spans="1:17">
-      <c r="A107" s="8" t="s">
-        <v>161</v>
+      <c r="A107" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="B107" s="1">
-        <v>4100</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>161</v>
+        <v>4024</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="D107" s="1">
         <v>3</v>
       </c>
       <c r="E107" s="7">
-        <v>1100</v>
+        <v>1024</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -6072,25 +6361,25 @@
       <c r="L107" s="1">
         <v>100</v>
       </c>
-      <c r="Q107" s="8" t="s">
-        <v>161</v>
+      <c r="Q107" s="7" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="108" spans="1:17">
       <c r="A108" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B108" s="1">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D108" s="1">
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
@@ -6114,24 +6403,24 @@
         <v>100</v>
       </c>
       <c r="Q108" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109" spans="1:17">
       <c r="A109" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B109" s="1">
-        <v>4103</v>
+        <v>4101</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F109" s="1">
         <v>1</v>
@@ -6155,24 +6444,24 @@
         <v>100</v>
       </c>
       <c r="Q109" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="110" spans="1:17">
       <c r="A110" s="8" t="s">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="B110" s="1">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -6196,24 +6485,24 @@
         <v>100</v>
       </c>
       <c r="Q110" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:17">
       <c r="A111" s="8" t="s">
-        <v>165</v>
+        <v>296</v>
       </c>
       <c r="B111" s="1">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>165</v>
+        <v>296</v>
       </c>
       <c r="D111" s="1">
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
@@ -6237,24 +6526,24 @@
         <v>100</v>
       </c>
       <c r="Q111" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:17">
       <c r="A112" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B112" s="1">
-        <v>4109</v>
+        <v>4106</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D112" s="1">
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
@@ -6278,24 +6567,24 @@
         <v>100</v>
       </c>
       <c r="Q112" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="113" spans="1:17">
       <c r="A113" s="8" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="B113" s="1">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F113" s="1">
         <v>1</v>
@@ -6319,24 +6608,24 @@
         <v>100</v>
       </c>
       <c r="Q113" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="114" spans="1:17">
       <c r="A114" s="8" t="s">
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="B114" s="1">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
       </c>
       <c r="E114" s="7">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
@@ -6360,24 +6649,24 @@
         <v>100</v>
       </c>
       <c r="Q114" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="115" spans="1:17">
       <c r="A115" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B115" s="1">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D115" s="1">
         <v>3</v>
       </c>
       <c r="E115" s="7">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
@@ -6401,24 +6690,24 @@
         <v>100</v>
       </c>
       <c r="Q115" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="116" spans="1:17">
       <c r="A116" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B116" s="1">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
       </c>
       <c r="E116" s="7">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F116" s="1">
         <v>1</v>
@@ -6442,24 +6731,24 @@
         <v>100</v>
       </c>
       <c r="Q116" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117" spans="1:17">
       <c r="A117" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B117" s="1">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D117" s="1">
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
@@ -6483,24 +6772,24 @@
         <v>100</v>
       </c>
       <c r="Q117" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="118" spans="1:17">
       <c r="A118" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B118" s="1">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D118" s="1">
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F118" s="1">
         <v>1</v>
@@ -6524,24 +6813,24 @@
         <v>100</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119" spans="1:17">
       <c r="A119" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B119" s="1">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D119" s="1">
         <v>3</v>
       </c>
       <c r="E119" s="7">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
@@ -6565,24 +6854,24 @@
         <v>100</v>
       </c>
       <c r="Q119" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="120" spans="1:17">
       <c r="A120" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B120" s="1">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
       </c>
       <c r="E120" s="7">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -6606,24 +6895,24 @@
         <v>100</v>
       </c>
       <c r="Q120" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:17">
-      <c r="A121" s="13" t="s">
-        <v>280</v>
+      <c r="A121" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="B121" s="1">
-        <v>3000</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>280</v>
+        <v>4117</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="D121" s="1">
         <v>3</v>
       </c>
-      <c r="E121" s="1">
-        <v>0</v>
+      <c r="E121" s="7">
+        <v>1117</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
@@ -6646,16 +6935,19 @@
       <c r="L121" s="1">
         <v>100</v>
       </c>
+      <c r="Q121" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="122" spans="1:17">
       <c r="A122" s="13" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B122" s="1">
-        <v>3001</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>282</v>
+        <v>3000</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>278</v>
       </c>
       <c r="D122" s="1">
         <v>3</v>
@@ -6664,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="F122" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
@@ -6673,7 +6965,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="1">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J122" s="1">
         <v>1</v>
@@ -6687,13 +6979,13 @@
     </row>
     <row r="123" spans="1:17">
       <c r="A123" s="13" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B123" s="1">
-        <v>3002</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>284</v>
+        <v>3001</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>280</v>
       </c>
       <c r="D123" s="1">
         <v>3</v>
@@ -6725,13 +7017,13 @@
     </row>
     <row r="124" spans="1:17">
       <c r="A124" s="13" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="B124" s="1">
-        <v>3003</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>299</v>
+        <v>3002</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>282</v>
       </c>
       <c r="D124" s="1">
         <v>3</v>
@@ -6763,13 +7055,13 @@
     </row>
     <row r="125" spans="1:17">
       <c r="A125" s="13" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B125" s="1">
-        <v>3004</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>300</v>
+        <v>3003</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>366</v>
       </c>
       <c r="D125" s="1">
         <v>3</v>
@@ -6800,14 +7092,14 @@
       </c>
     </row>
     <row r="126" spans="1:17">
-      <c r="A126" s="14" t="s">
-        <v>301</v>
+      <c r="A126" s="13" t="s">
+        <v>298</v>
       </c>
       <c r="B126" s="1">
-        <v>3005</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>301</v>
+        <v>3004</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>298</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
@@ -6839,13 +7131,13 @@
     </row>
     <row r="127" spans="1:17">
       <c r="A127" s="14" t="s">
-        <v>190</v>
+        <v>299</v>
       </c>
       <c r="B127" s="1">
-        <v>3006</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>190</v>
+        <v>3005</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>299</v>
       </c>
       <c r="D127" s="1">
         <v>3</v>
@@ -6854,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="1">
         <v>0</v>
@@ -6877,13 +7169,13 @@
     </row>
     <row r="128" spans="1:17">
       <c r="A128" s="14" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B128" s="1">
-        <v>3007</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>183</v>
+        <v>3006</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>189</v>
       </c>
       <c r="D128" s="1">
         <v>3</v>
@@ -6901,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="I128" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J128" s="1">
         <v>1</v>
@@ -6915,13 +7207,13 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" s="14" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B129" s="1">
-        <v>3008</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>188</v>
+        <v>3007</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>182</v>
       </c>
       <c r="D129" s="1">
         <v>3</v>
@@ -6952,14 +7244,14 @@
       </c>
     </row>
     <row r="130" spans="1:12">
-      <c r="A130" s="1" t="s">
-        <v>243</v>
+      <c r="A130" s="14" t="s">
+        <v>187</v>
       </c>
       <c r="B130" s="1">
-        <v>3009</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>243</v>
+        <v>3008</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>187</v>
       </c>
       <c r="D130" s="1">
         <v>3</v>
@@ -6968,7 +7260,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" s="1">
         <v>0</v>
@@ -6977,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="1">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J130" s="1">
         <v>1</v>
@@ -6991,13 +7283,13 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" s="1" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B131" s="1">
-        <v>3010</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>253</v>
+        <v>3009</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>242</v>
       </c>
       <c r="D131" s="1">
         <v>3</v>
@@ -7028,14 +7320,14 @@
       </c>
     </row>
     <row r="132" spans="1:12">
-      <c r="A132" s="15" t="s">
-        <v>358</v>
+      <c r="A132" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="B132" s="1">
-        <v>3011</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>314</v>
+        <v>3010</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="D132" s="1">
         <v>3</v>
@@ -7044,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" s="1">
         <v>0</v>
@@ -7066,23 +7358,23 @@
       </c>
     </row>
     <row r="133" spans="1:12">
-      <c r="A133" s="15" t="s">
-        <v>202</v>
+      <c r="A133" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="B133" s="1">
-        <v>3100</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>202</v>
+        <v>3011</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>358</v>
       </c>
       <c r="D133" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
       </c>
       <c r="F133" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="1">
         <v>0</v>
@@ -7091,7 +7383,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="1">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J133" s="1">
         <v>1</v>
@@ -7105,16 +7397,16 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="15" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="B134" s="1">
-        <v>3101</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>203</v>
+        <v>3011</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>311</v>
       </c>
       <c r="D134" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -7129,7 +7421,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="1">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J134" s="1">
         <v>1</v>
@@ -7143,13 +7435,13 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" s="15" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="B135" s="1">
-        <v>3102</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>270</v>
+        <v>3100</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>426</v>
       </c>
       <c r="D135" s="1">
         <v>4</v>
@@ -7181,13 +7473,13 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" s="15" t="s">
-        <v>209</v>
+        <v>365</v>
       </c>
       <c r="B136" s="1">
-        <v>3103</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>209</v>
+        <v>3101</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>202</v>
       </c>
       <c r="D136" s="1">
         <v>4</v>
@@ -7219,13 +7511,13 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" s="15" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B137" s="1">
-        <v>3104</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>263</v>
+        <v>3102</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>268</v>
       </c>
       <c r="D137" s="1">
         <v>4</v>
@@ -7257,13 +7549,13 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="15" t="s">
-        <v>302</v>
+        <v>208</v>
       </c>
       <c r="B138" s="1">
-        <v>3105</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>302</v>
+        <v>3103</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>208</v>
       </c>
       <c r="D138" s="1">
         <v>4</v>
@@ -7295,13 +7587,13 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" s="15" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="B139" s="1">
-        <v>3106</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>303</v>
+        <v>3104</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>261</v>
       </c>
       <c r="D139" s="1">
         <v>4</v>
@@ -7333,13 +7625,13 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="15" t="s">
-        <v>207</v>
+        <v>300</v>
       </c>
       <c r="B140" s="1">
-        <v>3107</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>207</v>
+        <v>3105</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>300</v>
       </c>
       <c r="D140" s="1">
         <v>4</v>
@@ -7371,13 +7663,13 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="15" t="s">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="B141" s="1">
-        <v>3108</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>211</v>
+        <v>3106</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>301</v>
       </c>
       <c r="D141" s="1">
         <v>4</v>
@@ -7409,13 +7701,13 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" s="15" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="B142" s="1">
-        <v>3109</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>304</v>
+        <v>3107</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>206</v>
       </c>
       <c r="D142" s="1">
         <v>4</v>
@@ -7447,13 +7739,13 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="15" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B143" s="1">
-        <v>3110</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>205</v>
+        <v>3108</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>368</v>
       </c>
       <c r="D143" s="1">
         <v>4</v>
@@ -7485,13 +7777,13 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="15" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B144" s="1">
-        <v>3111</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>305</v>
+        <v>3109</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>302</v>
       </c>
       <c r="D144" s="1">
         <v>4</v>
@@ -7523,13 +7815,13 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="15" t="s">
-        <v>306</v>
+        <v>204</v>
       </c>
       <c r="B145" s="1">
-        <v>3112</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>306</v>
+        <v>3110</v>
+      </c>
+      <c r="C145" s="16" t="s">
+        <v>204</v>
       </c>
       <c r="D145" s="1">
         <v>4</v>
@@ -7561,13 +7853,13 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="15" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B146" s="1">
-        <v>3113</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>307</v>
+        <v>3111</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="D146" s="1">
         <v>4</v>
@@ -7599,13 +7891,13 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="15" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="B147" s="1">
-        <v>3114</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>227</v>
+        <v>3112</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>357</v>
       </c>
       <c r="D147" s="1">
         <v>4</v>
@@ -7637,13 +7929,13 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="15" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B148" s="1">
-        <v>3115</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>308</v>
+        <v>3113</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>369</v>
       </c>
       <c r="D148" s="1">
         <v>4</v>
@@ -7675,13 +7967,13 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="15" t="s">
-        <v>309</v>
+        <v>226</v>
       </c>
       <c r="B149" s="1">
-        <v>3116</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>309</v>
+        <v>3114</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>370</v>
       </c>
       <c r="D149" s="1">
         <v>4</v>
@@ -7713,13 +8005,13 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" s="15" t="s">
-        <v>225</v>
+        <v>305</v>
       </c>
       <c r="B150" s="1">
-        <v>3117</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>225</v>
+        <v>3115</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>305</v>
       </c>
       <c r="D150" s="1">
         <v>4</v>
@@ -7751,13 +8043,13 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="15" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B151" s="1">
-        <v>3118</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>310</v>
+        <v>3116</v>
+      </c>
+      <c r="C151" s="16" t="s">
+        <v>367</v>
       </c>
       <c r="D151" s="1">
         <v>4</v>
@@ -7789,13 +8081,13 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="15" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B152" s="1">
-        <v>3119</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>238</v>
+        <v>3117</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>371</v>
       </c>
       <c r="D152" s="1">
         <v>4</v>
@@ -7827,13 +8119,13 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="15" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B153" s="1">
-        <v>3120</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>311</v>
+        <v>3118</v>
+      </c>
+      <c r="C153" s="16" t="s">
+        <v>372</v>
       </c>
       <c r="D153" s="1">
         <v>4</v>
@@ -7865,13 +8157,13 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" s="15" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="B154" s="1">
-        <v>3121</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>273</v>
+        <v>3119</v>
+      </c>
+      <c r="C154" s="16" t="s">
+        <v>374</v>
       </c>
       <c r="D154" s="1">
         <v>4</v>
@@ -7903,13 +8195,13 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" s="15" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="B155" s="1">
-        <v>3122</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>220</v>
+        <v>3120</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>375</v>
       </c>
       <c r="D155" s="1">
         <v>4</v>
@@ -7941,13 +8233,13 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="15" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="B156" s="1">
-        <v>3123</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>245</v>
+        <v>3121</v>
+      </c>
+      <c r="C156" s="16" t="s">
+        <v>376</v>
       </c>
       <c r="D156" s="1">
         <v>4</v>
@@ -7979,13 +8271,13 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="15" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="B157" s="1">
-        <v>3124</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>249</v>
+        <v>3122</v>
+      </c>
+      <c r="C157" s="16" t="s">
+        <v>219</v>
       </c>
       <c r="D157" s="1">
         <v>4</v>
@@ -8017,13 +8309,13 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="15" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B158" s="1">
-        <v>3125</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>255</v>
+        <v>3123</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="D158" s="1">
         <v>4</v>
@@ -8055,13 +8347,13 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="15" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B159" s="1">
-        <v>3126</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>257</v>
+        <v>3124</v>
+      </c>
+      <c r="C159" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="D159" s="1">
         <v>4</v>
@@ -8093,13 +8385,13 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="15" t="s">
-        <v>312</v>
+        <v>253</v>
       </c>
       <c r="B160" s="1">
-        <v>3127</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>312</v>
+        <v>3125</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>253</v>
       </c>
       <c r="D160" s="1">
         <v>4</v>
@@ -8131,13 +8423,13 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="15" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="B161" s="1">
-        <v>3128</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>313</v>
+        <v>3126</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>255</v>
       </c>
       <c r="D161" s="1">
         <v>4</v>
@@ -8169,13 +8461,13 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" s="15" t="s">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="B162" s="1">
-        <v>3129</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>260</v>
+        <v>3127</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>373</v>
       </c>
       <c r="D162" s="1">
         <v>4</v>
@@ -8207,13 +8499,13 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="15" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B163" s="1">
-        <v>3130</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>315</v>
+        <v>3128</v>
+      </c>
+      <c r="C163" s="16" t="s">
+        <v>377</v>
       </c>
       <c r="D163" s="1">
         <v>4</v>
@@ -8245,13 +8537,13 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" s="15" t="s">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="B164" s="1">
-        <v>3131</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>316</v>
+        <v>3129</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>258</v>
       </c>
       <c r="D164" s="1">
         <v>4</v>
@@ -8283,13 +8575,13 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="15" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="B165" s="1">
-        <v>3132</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>266</v>
+        <v>3130</v>
+      </c>
+      <c r="C165" s="16" t="s">
+        <v>312</v>
       </c>
       <c r="D165" s="1">
         <v>4</v>
@@ -8321,13 +8613,13 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" s="15" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B166" s="1">
-        <v>3133</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>317</v>
+        <v>3131</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>378</v>
       </c>
       <c r="D166" s="1">
         <v>4</v>
@@ -8359,13 +8651,13 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" s="15" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="B167" s="1">
-        <v>3134</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>318</v>
+        <v>3132</v>
+      </c>
+      <c r="C167" s="16" t="s">
+        <v>379</v>
       </c>
       <c r="D167" s="1">
         <v>4</v>
@@ -8397,13 +8689,13 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="15" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B168" s="1">
-        <v>3135</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>319</v>
+        <v>3133</v>
+      </c>
+      <c r="C168" s="16" t="s">
+        <v>380</v>
       </c>
       <c r="D168" s="1">
         <v>4</v>
@@ -8435,13 +8727,13 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="15" t="s">
-        <v>224</v>
+        <v>315</v>
       </c>
       <c r="B169" s="1">
-        <v>3136</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>224</v>
+        <v>3134</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>381</v>
       </c>
       <c r="D169" s="1">
         <v>4</v>
@@ -8473,13 +8765,13 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" s="15" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B170" s="1">
-        <v>3137</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>320</v>
+        <v>3135</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>383</v>
       </c>
       <c r="D170" s="1">
         <v>4</v>
@@ -8511,13 +8803,13 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="15" t="s">
-        <v>321</v>
+        <v>223</v>
       </c>
       <c r="B171" s="1">
-        <v>3138</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>321</v>
+        <v>3136</v>
+      </c>
+      <c r="C171" s="16" t="s">
+        <v>384</v>
       </c>
       <c r="D171" s="1">
         <v>4</v>
@@ -8549,13 +8841,13 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" s="15" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B172" s="1">
-        <v>3139</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>322</v>
+        <v>3137</v>
+      </c>
+      <c r="C172" s="16" t="s">
+        <v>385</v>
       </c>
       <c r="D172" s="1">
         <v>4</v>
@@ -8587,13 +8879,13 @@
     </row>
     <row r="173" spans="1:12">
       <c r="A173" s="15" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B173" s="1">
-        <v>3140</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>323</v>
+        <v>3138</v>
+      </c>
+      <c r="C173" s="16" t="s">
+        <v>382</v>
       </c>
       <c r="D173" s="1">
         <v>4</v>
@@ -8625,13 +8917,13 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" s="15" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B174" s="1">
-        <v>3141</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>324</v>
+        <v>3139</v>
+      </c>
+      <c r="C174" s="16" t="s">
+        <v>386</v>
       </c>
       <c r="D174" s="1">
         <v>4</v>
@@ -8663,13 +8955,13 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="15" t="s">
-        <v>247</v>
+        <v>320</v>
       </c>
       <c r="B175" s="1">
-        <v>3142</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>247</v>
+        <v>3140</v>
+      </c>
+      <c r="C175" s="16" t="s">
+        <v>387</v>
       </c>
       <c r="D175" s="1">
         <v>4</v>
@@ -8701,13 +8993,13 @@
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="15" t="s">
-        <v>278</v>
+        <v>321</v>
       </c>
       <c r="B176" s="1">
-        <v>3143</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>278</v>
+        <v>3141</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>388</v>
       </c>
       <c r="D176" s="1">
         <v>4</v>
@@ -8716,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="F176" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -8739,13 +9031,13 @@
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="15" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B177" s="1">
-        <v>3144</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>240</v>
+        <v>3142</v>
+      </c>
+      <c r="C177" s="16" t="s">
+        <v>389</v>
       </c>
       <c r="D177" s="1">
         <v>4</v>
@@ -8777,13 +9069,13 @@
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="15" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="B178" s="1">
-        <v>3145</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>325</v>
+        <v>3143</v>
+      </c>
+      <c r="C178" s="16" t="s">
+        <v>390</v>
       </c>
       <c r="D178" s="1">
         <v>4</v>
@@ -8815,13 +9107,13 @@
     </row>
     <row r="179" spans="1:12">
       <c r="A179" s="15" t="s">
-        <v>326</v>
+        <v>239</v>
       </c>
       <c r="B179" s="1">
-        <v>3146</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>326</v>
+        <v>3144</v>
+      </c>
+      <c r="C179" s="16" t="s">
+        <v>391</v>
       </c>
       <c r="D179" s="1">
         <v>4</v>
@@ -8853,13 +9145,13 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" s="15" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B180" s="1">
-        <v>3147</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>327</v>
+        <v>3145</v>
+      </c>
+      <c r="C180" s="16" t="s">
+        <v>392</v>
       </c>
       <c r="D180" s="1">
         <v>4</v>
@@ -8891,13 +9183,13 @@
     </row>
     <row r="181" spans="1:12">
       <c r="A181" s="15" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B181" s="1">
-        <v>3148</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>328</v>
+        <v>3146</v>
+      </c>
+      <c r="C181" s="16" t="s">
+        <v>393</v>
       </c>
       <c r="D181" s="1">
         <v>4</v>
@@ -8929,13 +9221,13 @@
     </row>
     <row r="182" spans="1:12">
       <c r="A182" s="15" t="s">
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="B182" s="1">
-        <v>3149</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>251</v>
+        <v>3147</v>
+      </c>
+      <c r="C182" s="16" t="s">
+        <v>395</v>
       </c>
       <c r="D182" s="1">
         <v>4</v>
@@ -8944,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="F182" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" s="1">
         <v>0</v>
@@ -8967,13 +9259,13 @@
     </row>
     <row r="183" spans="1:12">
       <c r="A183" s="15" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B183" s="1">
-        <v>3150</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>329</v>
+        <v>3148</v>
+      </c>
+      <c r="C183" s="16" t="s">
+        <v>394</v>
       </c>
       <c r="D183" s="1">
         <v>4</v>
@@ -9005,13 +9297,13 @@
     </row>
     <row r="184" spans="1:12">
       <c r="A184" s="15" t="s">
-        <v>330</v>
+        <v>397</v>
       </c>
       <c r="B184" s="1">
-        <v>3151</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>330</v>
+        <v>3149</v>
+      </c>
+      <c r="C184" s="16" t="s">
+        <v>396</v>
       </c>
       <c r="D184" s="1">
         <v>4</v>
@@ -9043,13 +9335,13 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" s="15" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B185" s="1">
-        <v>3152</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>331</v>
+        <v>3150</v>
+      </c>
+      <c r="C185" s="16" t="s">
+        <v>398</v>
       </c>
       <c r="D185" s="1">
         <v>4</v>
@@ -9081,13 +9373,13 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" s="15" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B186" s="1">
-        <v>3153</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>332</v>
+        <v>3151</v>
+      </c>
+      <c r="C186" s="16" t="s">
+        <v>399</v>
       </c>
       <c r="D186" s="1">
         <v>4</v>
@@ -9119,13 +9411,13 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" s="15" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B187" s="1">
-        <v>3154</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>333</v>
+        <v>3152</v>
+      </c>
+      <c r="C187" s="16" t="s">
+        <v>400</v>
       </c>
       <c r="D187" s="1">
         <v>4</v>
@@ -9157,13 +9449,13 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" s="15" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B188" s="1">
-        <v>3155</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>334</v>
+        <v>3153</v>
+      </c>
+      <c r="C188" s="16" t="s">
+        <v>401</v>
       </c>
       <c r="D188" s="1">
         <v>4</v>
@@ -9195,13 +9487,13 @@
     </row>
     <row r="189" spans="1:12">
       <c r="A189" s="15" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B189" s="1">
-        <v>3156</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>335</v>
+        <v>3154</v>
+      </c>
+      <c r="C189" s="16" t="s">
+        <v>402</v>
       </c>
       <c r="D189" s="1">
         <v>4</v>
@@ -9233,13 +9525,13 @@
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="15" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B190" s="1">
-        <v>3157</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>336</v>
+        <v>3155</v>
+      </c>
+      <c r="C190" s="16" t="s">
+        <v>403</v>
       </c>
       <c r="D190" s="1">
         <v>4</v>
@@ -9271,13 +9563,13 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" s="15" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B191" s="1">
-        <v>3158</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>337</v>
+        <v>3156</v>
+      </c>
+      <c r="C191" s="16" t="s">
+        <v>404</v>
       </c>
       <c r="D191" s="1">
         <v>4</v>
@@ -9309,13 +9601,13 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" s="15" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B192" s="1">
-        <v>3159</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>338</v>
+        <v>3157</v>
+      </c>
+      <c r="C192" s="16" t="s">
+        <v>405</v>
       </c>
       <c r="D192" s="1">
         <v>4</v>
@@ -9347,13 +9639,13 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" s="15" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B193" s="1">
-        <v>3160</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>339</v>
+        <v>3158</v>
+      </c>
+      <c r="C193" s="16" t="s">
+        <v>406</v>
       </c>
       <c r="D193" s="1">
         <v>4</v>
@@ -9385,13 +9677,13 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" s="15" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B194" s="1">
-        <v>3161</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>340</v>
+        <v>3159</v>
+      </c>
+      <c r="C194" s="16" t="s">
+        <v>407</v>
       </c>
       <c r="D194" s="1">
         <v>4</v>
@@ -9423,13 +9715,13 @@
     </row>
     <row r="195" spans="1:12">
       <c r="A195" s="15" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B195" s="1">
-        <v>3162</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>341</v>
+        <v>3160</v>
+      </c>
+      <c r="C195" s="16" t="s">
+        <v>408</v>
       </c>
       <c r="D195" s="1">
         <v>4</v>
@@ -9461,13 +9753,13 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" s="15" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B196" s="1">
-        <v>3163</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>342</v>
+        <v>3161</v>
+      </c>
+      <c r="C196" s="16" t="s">
+        <v>409</v>
       </c>
       <c r="D196" s="1">
         <v>4</v>
@@ -9499,13 +9791,13 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" s="15" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B197" s="1">
-        <v>3164</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>343</v>
+        <v>3162</v>
+      </c>
+      <c r="C197" s="16" t="s">
+        <v>410</v>
       </c>
       <c r="D197" s="1">
         <v>4</v>
@@ -9537,13 +9829,13 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" s="15" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B198" s="1">
-        <v>3165</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>344</v>
+        <v>3163</v>
+      </c>
+      <c r="C198" s="16" t="s">
+        <v>411</v>
       </c>
       <c r="D198" s="1">
         <v>4</v>
@@ -9575,13 +9867,13 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" s="15" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B199" s="1">
-        <v>3166</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>345</v>
+        <v>3164</v>
+      </c>
+      <c r="C199" s="16" t="s">
+        <v>412</v>
       </c>
       <c r="D199" s="1">
         <v>4</v>
@@ -9613,13 +9905,13 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" s="15" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B200" s="1">
-        <v>3167</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>346</v>
+        <v>3165</v>
+      </c>
+      <c r="C200" s="16" t="s">
+        <v>413</v>
       </c>
       <c r="D200" s="1">
         <v>4</v>
@@ -9651,13 +9943,13 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" s="15" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B201" s="1">
-        <v>3168</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>347</v>
+        <v>3166</v>
+      </c>
+      <c r="C201" s="16" t="s">
+        <v>414</v>
       </c>
       <c r="D201" s="1">
         <v>4</v>
@@ -9689,13 +9981,13 @@
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="15" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B202" s="1">
-        <v>3169</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>348</v>
+        <v>3167</v>
+      </c>
+      <c r="C202" s="16" t="s">
+        <v>415</v>
       </c>
       <c r="D202" s="1">
         <v>4</v>
@@ -9727,13 +10019,13 @@
     </row>
     <row r="203" spans="1:12">
       <c r="A203" s="15" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B203" s="1">
-        <v>3170</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>349</v>
+        <v>3168</v>
+      </c>
+      <c r="C203" s="16" t="s">
+        <v>416</v>
       </c>
       <c r="D203" s="1">
         <v>4</v>
@@ -9765,13 +10057,13 @@
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="15" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B204" s="1">
-        <v>3171</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>350</v>
+        <v>3169</v>
+      </c>
+      <c r="C204" s="16" t="s">
+        <v>427</v>
       </c>
       <c r="D204" s="1">
         <v>4</v>
@@ -9803,13 +10095,13 @@
     </row>
     <row r="205" spans="1:12">
       <c r="A205" s="15" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B205" s="1">
-        <v>3172</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>351</v>
+        <v>3170</v>
+      </c>
+      <c r="C205" s="16" t="s">
+        <v>417</v>
       </c>
       <c r="D205" s="1">
         <v>4</v>
@@ -9841,13 +10133,13 @@
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="15" t="s">
-        <v>352</v>
+        <v>419</v>
       </c>
       <c r="B206" s="1">
-        <v>3173</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>352</v>
+        <v>3171</v>
+      </c>
+      <c r="C206" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="D206" s="1">
         <v>4</v>
@@ -9879,13 +10171,13 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" s="15" t="s">
-        <v>353</v>
+        <v>418</v>
       </c>
       <c r="B207" s="1">
-        <v>3174</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>353</v>
+        <v>3172</v>
+      </c>
+      <c r="C207" s="16" t="s">
+        <v>348</v>
       </c>
       <c r="D207" s="1">
         <v>4</v>
@@ -9917,13 +10209,13 @@
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="15" t="s">
-        <v>354</v>
+        <v>420</v>
       </c>
       <c r="B208" s="1">
-        <v>3175</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>354</v>
+        <v>3173</v>
+      </c>
+      <c r="C208" s="16" t="s">
+        <v>349</v>
       </c>
       <c r="D208" s="1">
         <v>4</v>
@@ -9955,13 +10247,13 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="15" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B209" s="1">
-        <v>3176</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>355</v>
+        <v>3174</v>
+      </c>
+      <c r="C209" s="16" t="s">
+        <v>421</v>
       </c>
       <c r="D209" s="1">
         <v>4</v>
@@ -9993,13 +10285,13 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="15" t="s">
-        <v>356</v>
+        <v>422</v>
       </c>
       <c r="B210" s="1">
-        <v>3177</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>356</v>
+        <v>3175</v>
+      </c>
+      <c r="C210" s="16" t="s">
+        <v>351</v>
       </c>
       <c r="D210" s="1">
         <v>4</v>
@@ -10031,13 +10323,13 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" s="15" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B211" s="1">
-        <v>3178</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>357</v>
+        <v>3176</v>
+      </c>
+      <c r="C211" s="16" t="s">
+        <v>423</v>
       </c>
       <c r="D211" s="1">
         <v>4</v>
@@ -10064,6 +10356,82 @@
         <v>100</v>
       </c>
       <c r="L211" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12">
+      <c r="A212" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="B212" s="1">
+        <v>3177</v>
+      </c>
+      <c r="C212" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="D212" s="1">
+        <v>4</v>
+      </c>
+      <c r="E212" s="1">
+        <v>0</v>
+      </c>
+      <c r="F212" s="1">
+        <v>1</v>
+      </c>
+      <c r="G212" s="1">
+        <v>0</v>
+      </c>
+      <c r="H212" s="1">
+        <v>0</v>
+      </c>
+      <c r="I212" s="1">
+        <v>1</v>
+      </c>
+      <c r="J212" s="1">
+        <v>1</v>
+      </c>
+      <c r="K212" s="1">
+        <v>100</v>
+      </c>
+      <c r="L212" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12">
+      <c r="A213" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="B213" s="1">
+        <v>3178</v>
+      </c>
+      <c r="C213" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="D213" s="1">
+        <v>4</v>
+      </c>
+      <c r="E213" s="1">
+        <v>0</v>
+      </c>
+      <c r="F213" s="1">
+        <v>1</v>
+      </c>
+      <c r="G213" s="1">
+        <v>0</v>
+      </c>
+      <c r="H213" s="1">
+        <v>0</v>
+      </c>
+      <c r="I213" s="1">
+        <v>1</v>
+      </c>
+      <c r="J213" s="1">
+        <v>1</v>
+      </c>
+      <c r="K213" s="1">
+        <v>100</v>
+      </c>
+      <c r="L213" s="1">
         <v>100</v>
       </c>
     </row>
@@ -10088,106 +10456,106 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="B3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="B6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -10195,59 +10563,59 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D27" t="s">
         <v>269</v>
       </c>
-      <c r="D27" t="s">
-        <v>271</v>
-      </c>
       <c r="E27" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -10255,7 +10623,7 @@
         <v>44</v>
       </c>
       <c r="G28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -10263,132 +10631,132 @@
         <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I30" t="s">
         <v>214</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="I30" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I31" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>218</v>
-      </c>
       <c r="G32" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I33" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F35" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.5">
       <c r="A36" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" t="s">
         <v>229</v>
-      </c>
-      <c r="G37" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
         <v>231</v>
       </c>
-      <c r="E38" t="s">
+      <c r="I38" t="s">
         <v>232</v>
-      </c>
-      <c r="I38" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.5">
       <c r="A39" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G40" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J41" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -10396,75 +10764,75 @@
         <v>24</v>
       </c>
       <c r="I43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I44" t="s">
+        <v>249</v>
+      </c>
+      <c r="J44" t="s">
         <v>250</v>
-      </c>
-      <c r="J44" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I46" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G48" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I49" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="B54" t="s">
+        <v>279</v>
+      </c>
+      <c r="C54" t="s">
         <v>281</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>283</v>
       </c>
-      <c r="D54" t="s">
-        <v>285</v>
-      </c>
       <c r="F54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -10472,38 +10840,42 @@
         <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s">
-        <v>210</v>
+        <v>209</v>
+      </c>
+      <c r="H59">
+        <f>32*4</f>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B61" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -10511,7 +10883,7 @@
         <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -10521,85 +10893,85 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B65" t="s">
         <v>272</v>
-      </c>
-      <c r="B65" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B70" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="16.5">
       <c r="A73" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B73" s="11" t="s">
         <v>234</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -10607,64 +10979,64 @@
         <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G77" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G78" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G79" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B80" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B81" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B82" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G83" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="438">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1614,6 +1614,13 @@
   </si>
   <si>
     <t>斧头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>干草</t>
+  </si>
+  <si>
+    <t>干草</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2100,7 +2107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q221"/>
+  <dimension ref="A2:Q222"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -2756,25 +2763,24 @@
         <v>433</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="3" customFormat="1">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3">
-        <v>1001</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>A17&amp;"_01"</f>
-        <v>芜菁_01</v>
+    <row r="17" spans="1:17">
+      <c r="A17" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="B17" s="1">
+        <v>105</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>437</v>
       </c>
       <c r="D17" s="1">
         <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -2782,34 +2788,32 @@
       <c r="H17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="3">
-        <v>29</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1</v>
+      <c r="I17" s="1">
+        <v>39</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>100</v>
-      </c>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f t="shared" ref="C18:C44" si="0">A18&amp;"_01"</f>
-        <v>卷心菜_01</v>
+        <f>A18&amp;"_01"</f>
+        <v>芜菁_01</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -2844,1054 +2848,1059 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="5"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" s="3" customFormat="1">
       <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f t="shared" ref="C19:C45" si="0">A19&amp;"_01"</f>
+        <v>卷心菜_01</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>29</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>100</v>
+      </c>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>1003</v>
       </c>
-      <c r="C19" s="3" t="str">
+      <c r="C20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>葱_01</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>5</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>29</v>
       </c>
-      <c r="J19" s="3">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="5" t="s">
+      <c r="J20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B21" s="3">
         <v>1004</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>萝卜_01</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>5</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>29</v>
       </c>
-      <c r="J20" s="3">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" s="5" t="s">
+      <c r="J21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B22" s="3">
         <v>1005</v>
       </c>
-      <c r="C21" s="3" t="str">
+      <c r="C22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>紫甘蓝_01</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>29</v>
       </c>
-      <c r="J21" s="3">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="A22" s="5" t="s">
+      <c r="J22" s="3">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B23" s="3">
         <v>1006</v>
       </c>
-      <c r="C22" s="3" t="str">
+      <c r="C23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>黄瓜_01</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D23" s="1">
         <v>5</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>29</v>
       </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23" s="5" t="s">
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B24" s="3">
         <v>1007</v>
       </c>
-      <c r="C23" s="3" t="str">
+      <c r="C24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西兰花_01</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>29</v>
       </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-      <c r="L23" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="5"/>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" s="5" t="s">
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B25" s="3">
         <v>1008</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>番茄_01</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25" s="1">
         <v>5</v>
       </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
         <v>29</v>
       </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q24" s="5"/>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="5" t="s">
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B26" s="3">
         <v>1009</v>
       </c>
-      <c r="C25" s="3" t="str">
+      <c r="C26" s="3" t="str">
         <f t="shared" si="0"/>
         <v>胡萝卜_01</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26" s="1">
         <v>5</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>29</v>
       </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q25" s="5"/>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="5" t="s">
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="5"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B27" s="3">
         <v>1010</v>
       </c>
-      <c r="C26" s="3" t="str">
+      <c r="C27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>西瓜_01</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>5</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>29</v>
       </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>100</v>
-      </c>
-      <c r="L26" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q26" s="5"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="5" t="s">
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>1011</v>
       </c>
-      <c r="C27" s="3" t="str">
+      <c r="C28" s="3" t="str">
         <f t="shared" si="0"/>
         <v>辣椒_01</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28" s="1">
         <v>5</v>
       </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
         <v>29</v>
       </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>100</v>
-      </c>
-      <c r="L27" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q27" s="5"/>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="5" t="s">
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q28" s="5"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>1012</v>
       </c>
-      <c r="C28" s="3" t="str">
+      <c r="C29" s="3" t="str">
         <f t="shared" si="0"/>
         <v>奇异果_01</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D29" s="1">
         <v>5</v>
       </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>29</v>
       </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>100</v>
-      </c>
-      <c r="L28" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q28" s="5"/>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" s="5" t="s">
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q29" s="5"/>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>1013</v>
       </c>
-      <c r="C29" s="3" t="str">
+      <c r="C30" s="3" t="str">
         <f t="shared" si="0"/>
         <v>茄子_01</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30" s="1">
         <v>5</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
         <v>29</v>
       </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>100</v>
-      </c>
-      <c r="L29" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q29" s="5"/>
-    </row>
-    <row r="30" spans="1:17">
-      <c r="A30" s="5" t="s">
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <v>1014</v>
       </c>
-      <c r="C30" s="3" t="str">
+      <c r="C31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>豌豆_01</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="1">
         <v>5</v>
       </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
         <v>29</v>
       </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>100</v>
-      </c>
-      <c r="L30" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q30" s="5"/>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="5" t="s">
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q31" s="5"/>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <v>1015</v>
       </c>
-      <c r="C31" s="3" t="str">
+      <c r="C32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>土豆_01</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>5</v>
       </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>29</v>
       </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>100</v>
-      </c>
-      <c r="L31" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q31" s="5"/>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" s="5" t="s">
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="5"/>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <v>1016</v>
       </c>
-      <c r="C32" s="3" t="str">
+      <c r="C33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>大蒜_01</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D33" s="1">
         <v>5</v>
       </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>29</v>
       </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>100</v>
-      </c>
-      <c r="L32" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="5"/>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="5" t="s">
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="5"/>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B34" s="3">
         <v>1017</v>
       </c>
-      <c r="C33" s="3" t="str">
+      <c r="C34" s="3" t="str">
         <f t="shared" si="0"/>
         <v>芦笋_01</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
         <v>29</v>
       </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>100</v>
-      </c>
-      <c r="L33" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q33" s="5"/>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="5" t="s">
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q34" s="5"/>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B35" s="3">
         <v>1018</v>
       </c>
-      <c r="C34" s="3" t="str">
+      <c r="C35" s="3" t="str">
         <f t="shared" si="0"/>
         <v>南瓜_01</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>29</v>
       </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>100</v>
-      </c>
-      <c r="L34" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="5" t="s">
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B36" s="3">
         <v>1019</v>
       </c>
-      <c r="C35" s="3" t="str">
+      <c r="C36" s="3" t="str">
         <f t="shared" si="0"/>
         <v>玉米_01</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D36" s="1">
         <v>5</v>
       </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
         <v>29</v>
       </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>100</v>
-      </c>
-      <c r="L35" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="5" t="s">
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B37" s="3">
         <v>1020</v>
       </c>
-      <c r="C36" s="3" t="str">
+      <c r="C37" s="3" t="str">
         <f t="shared" si="0"/>
         <v>小麦_01</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D37" s="1">
         <v>5</v>
       </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3">
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
         <v>29</v>
       </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>100</v>
-      </c>
-      <c r="L36" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="5" t="s">
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B38" s="3">
         <v>1021</v>
       </c>
-      <c r="C37" s="3" t="str">
+      <c r="C38" s="3" t="str">
         <f t="shared" si="0"/>
         <v>啤酒花_01</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D38" s="1">
         <v>5</v>
       </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="3">
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
         <v>29</v>
       </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>100</v>
-      </c>
-      <c r="L37" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" s="5" t="s">
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B39" s="3">
         <v>1022</v>
       </c>
-      <c r="C38" s="3" t="str">
+      <c r="C39" s="3" t="str">
         <f t="shared" si="0"/>
         <v>葡萄_01</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D39" s="1">
         <v>5</v>
       </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3">
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
         <v>29</v>
       </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>100</v>
-      </c>
-      <c r="L38" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17">
-      <c r="A39" s="5" t="s">
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B40" s="3">
         <v>1023</v>
       </c>
-      <c r="C39" s="3" t="str">
+      <c r="C40" s="3" t="str">
         <f t="shared" si="0"/>
         <v>菠萝_01</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D40" s="1">
         <v>5</v>
       </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3">
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
         <v>29</v>
       </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>100</v>
-      </c>
-      <c r="L39" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="A40" s="5" t="s">
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B41" s="3">
         <v>1024</v>
       </c>
-      <c r="C40" s="3" t="str">
+      <c r="C41" s="3" t="str">
         <f t="shared" si="0"/>
         <v>咖啡_01</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D41" s="1">
         <v>5</v>
       </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>29</v>
       </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>100</v>
-      </c>
-      <c r="L40" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="A41" s="5" t="s">
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B42" s="3">
         <v>1025</v>
       </c>
-      <c r="C41" s="3" t="str">
+      <c r="C42" s="3" t="str">
         <f t="shared" si="0"/>
         <v>草莓_01</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D42" s="1">
         <v>5</v>
       </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>29</v>
       </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17">
-      <c r="A42" s="5" t="s">
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B43" s="3">
         <v>1026</v>
       </c>
-      <c r="C42" s="3" t="str">
+      <c r="C43" s="3" t="str">
         <f t="shared" si="0"/>
         <v>蓝莓_01</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D43" s="1">
         <v>5</v>
       </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>29</v>
       </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>100</v>
-      </c>
-      <c r="L42" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17">
-      <c r="A43" s="5" t="s">
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B44" s="3">
         <v>1027</v>
       </c>
-      <c r="C43" s="3" t="str">
+      <c r="C44" s="3" t="str">
         <f t="shared" si="0"/>
         <v>红薯_01</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D44" s="1">
         <v>5</v>
       </c>
-      <c r="E43" s="1">
-        <v>1</v>
-      </c>
-      <c r="F43" s="1">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
         <v>29</v>
       </c>
-      <c r="J43" s="1">
-        <v>1</v>
-      </c>
-      <c r="K43" s="1">
-        <v>100</v>
-      </c>
-      <c r="L43" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17">
-      <c r="A44" s="5" t="s">
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B45" s="3">
         <v>1028</v>
       </c>
-      <c r="C44" s="3" t="str">
+      <c r="C45" s="3" t="str">
         <f t="shared" si="0"/>
         <v>甜菜_01</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D45" s="1">
         <v>5</v>
       </c>
-      <c r="E44" s="1">
-        <v>1</v>
-      </c>
-      <c r="F44" s="1">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>29</v>
-      </c>
-      <c r="J44" s="1">
-        <v>1</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17">
-      <c r="A45" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45" s="3">
-        <f>B17+100</f>
-        <v>1101</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
       <c r="E45" s="1">
-        <v>8001</v>
+        <v>1</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -3913,21 +3922,21 @@
       </c>
     </row>
     <row r="46" spans="1:17">
-      <c r="A46" s="9" t="s">
-        <v>61</v>
+      <c r="A46" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="B46" s="3">
-        <f t="shared" ref="B46:B72" si="1">B18+100</f>
-        <v>1102</v>
+        <f>B18+100</f>
+        <v>1101</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3952,1047 +3961,1048 @@
       </c>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="3">
+        <f t="shared" ref="B47:B73" si="1">B19+100</f>
+        <v>1102</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>8002</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>29</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+      <c r="L47" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B48" s="3">
         <f t="shared" si="1"/>
         <v>1103</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
         <v>8003</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
         <v>29</v>
       </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>100</v>
-      </c>
-      <c r="L47" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="9" t="s">
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+      <c r="L48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B49" s="3">
         <f t="shared" si="1"/>
         <v>1104</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
         <v>8004</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>29</v>
       </c>
-      <c r="J48" s="1">
-        <v>1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>100</v>
-      </c>
-      <c r="L48" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="5" t="s">
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B50" s="3">
         <f t="shared" si="1"/>
         <v>1105</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
         <v>8005</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
         <v>29</v>
       </c>
-      <c r="J49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1">
-        <v>100</v>
-      </c>
-      <c r="L49" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="9" t="s">
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B51" s="3">
         <f t="shared" si="1"/>
         <v>1106</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
         <v>8006</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3">
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
         <v>29</v>
       </c>
-      <c r="J50" s="1">
-        <v>1</v>
-      </c>
-      <c r="K50" s="1">
-        <v>100</v>
-      </c>
-      <c r="L50" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="9" t="s">
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+      <c r="L51" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B52" s="3">
         <f t="shared" si="1"/>
         <v>1107</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
         <v>8007</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3">
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>29</v>
       </c>
-      <c r="J51" s="1">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>100</v>
-      </c>
-      <c r="L51" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="9" t="s">
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>100</v>
+      </c>
+      <c r="L52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B53" s="3">
         <f t="shared" si="1"/>
         <v>1108</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
         <v>8008</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
         <v>29</v>
       </c>
-      <c r="J52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>100</v>
-      </c>
-      <c r="L52" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="9" t="s">
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1">
+        <v>100</v>
+      </c>
+      <c r="L53" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B54" s="3">
         <f t="shared" si="1"/>
         <v>1109</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
         <v>8009</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3">
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
         <v>29</v>
       </c>
-      <c r="J53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1">
-        <v>100</v>
-      </c>
-      <c r="L53" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="9" t="s">
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>100</v>
+      </c>
+      <c r="L54" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B55" s="3">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
         <v>8010</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
         <v>29</v>
       </c>
-      <c r="J54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>100</v>
-      </c>
-      <c r="L54" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" s="9" t="s">
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>100</v>
+      </c>
+      <c r="L55" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B56" s="3">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
         <v>8011</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3">
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
         <v>29</v>
       </c>
-      <c r="J55" s="1">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1">
-        <v>100</v>
-      </c>
-      <c r="L55" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12">
-      <c r="A56" s="5" t="s">
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="1">
+        <v>100</v>
+      </c>
+      <c r="L56" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B57" s="3">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
         <v>8012</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="3">
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>29</v>
       </c>
-      <c r="J56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>100</v>
-      </c>
-      <c r="L56" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12">
-      <c r="A57" s="9" t="s">
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="1">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B58" s="3">
         <f t="shared" si="1"/>
         <v>1113</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
         <v>8013</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>29</v>
       </c>
-      <c r="J57" s="1">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1">
-        <v>100</v>
-      </c>
-      <c r="L57" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="A58" s="5" t="s">
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B59" s="3">
         <f t="shared" si="1"/>
         <v>1114</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
         <v>8014</v>
       </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>29</v>
       </c>
-      <c r="J58" s="1">
-        <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>100</v>
-      </c>
-      <c r="L58" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
-      <c r="A59" s="9" t="s">
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B60" s="3">
         <f t="shared" si="1"/>
         <v>1115</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
         <v>8015</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
         <v>29</v>
       </c>
-      <c r="J59" s="1">
-        <v>1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>100</v>
-      </c>
-      <c r="L59" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" s="9" t="s">
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="1">
+        <v>100</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B61" s="3">
         <f t="shared" si="1"/>
         <v>1116</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
         <v>8016</v>
       </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>29</v>
       </c>
-      <c r="J60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1">
-        <v>100</v>
-      </c>
-      <c r="L60" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
-      <c r="A61" s="5" t="s">
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="1">
+        <v>100</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B62" s="3">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
         <v>8017</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>29</v>
       </c>
-      <c r="J61" s="1">
-        <v>1</v>
-      </c>
-      <c r="K61" s="1">
-        <v>100</v>
-      </c>
-      <c r="L61" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" s="9" t="s">
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="1">
+        <v>100</v>
+      </c>
+      <c r="L62" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B63" s="3">
         <f t="shared" si="1"/>
         <v>1118</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D62" s="1">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1">
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
         <v>8018</v>
       </c>
-      <c r="F62" s="1">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0</v>
-      </c>
-      <c r="H62" s="1">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
         <v>29</v>
       </c>
-      <c r="J62" s="1">
-        <v>1</v>
-      </c>
-      <c r="K62" s="1">
-        <v>100</v>
-      </c>
-      <c r="L62" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" s="9" t="s">
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="1">
+        <v>100</v>
+      </c>
+      <c r="L63" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B64" s="3">
         <f t="shared" si="1"/>
         <v>1119</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
         <v>8019</v>
       </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0</v>
-      </c>
-      <c r="H63" s="1">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3">
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3">
         <v>29</v>
       </c>
-      <c r="J63" s="1">
-        <v>1</v>
-      </c>
-      <c r="K63" s="1">
-        <v>100</v>
-      </c>
-      <c r="L63" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="9" t="s">
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="1">
+        <v>100</v>
+      </c>
+      <c r="L64" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
+      <c r="A65" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B65" s="3">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="1">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1">
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
         <v>8020</v>
       </c>
-      <c r="F64" s="1">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1">
-        <v>0</v>
-      </c>
-      <c r="I64" s="3">
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3">
         <v>29</v>
       </c>
-      <c r="J64" s="1">
-        <v>1</v>
-      </c>
-      <c r="K64" s="1">
-        <v>100</v>
-      </c>
-      <c r="L64" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17">
-      <c r="A65" s="5" t="s">
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="1">
+        <v>100</v>
+      </c>
+      <c r="L65" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
+      <c r="A66" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B66" s="3">
         <f t="shared" si="1"/>
         <v>1121</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1">
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
         <v>8021</v>
       </c>
-      <c r="F65" s="1">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-      <c r="I65" s="3">
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
         <v>29</v>
       </c>
-      <c r="J65" s="1">
-        <v>1</v>
-      </c>
-      <c r="K65" s="1">
-        <v>100</v>
-      </c>
-      <c r="L65" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17">
-      <c r="A66" s="9" t="s">
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1">
+        <v>100</v>
+      </c>
+      <c r="L66" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
+      <c r="A67" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B67" s="3">
         <f t="shared" si="1"/>
         <v>1122</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="1">
-        <v>0</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
         <v>8022</v>
       </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3">
         <v>29</v>
       </c>
-      <c r="J66" s="1">
-        <v>1</v>
-      </c>
-      <c r="K66" s="1">
-        <v>100</v>
-      </c>
-      <c r="L66" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17">
-      <c r="A67" s="5" t="s">
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="1">
+        <v>100</v>
+      </c>
+      <c r="L67" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
+      <c r="A68" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B68" s="3">
         <f t="shared" si="1"/>
         <v>1123</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D67" s="1">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1">
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
         <v>8023</v>
       </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
-      <c r="I67" s="3">
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3">
         <v>29</v>
       </c>
-      <c r="J67" s="1">
-        <v>1</v>
-      </c>
-      <c r="K67" s="1">
-        <v>100</v>
-      </c>
-      <c r="L67" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17">
-      <c r="A68" s="5" t="s">
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="1">
+        <v>100</v>
+      </c>
+      <c r="L68" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
+      <c r="A69" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B69" s="3">
         <f t="shared" si="1"/>
         <v>1124</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1">
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
         <v>8024</v>
       </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0</v>
-      </c>
-      <c r="I68" s="3">
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3">
         <v>29</v>
       </c>
-      <c r="J68" s="1">
-        <v>1</v>
-      </c>
-      <c r="K68" s="1">
-        <v>100</v>
-      </c>
-      <c r="L68" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17">
-      <c r="A69" s="9" t="s">
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+      <c r="K69" s="1">
+        <v>100</v>
+      </c>
+      <c r="L69" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
+      <c r="A70" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B70" s="3">
         <f t="shared" si="1"/>
         <v>1125</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="1">
-        <v>0</v>
-      </c>
-      <c r="E69" s="1">
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
         <v>8025</v>
       </c>
-      <c r="F69" s="1">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0</v>
-      </c>
-      <c r="I69" s="3">
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>29</v>
       </c>
-      <c r="J69" s="1">
-        <v>1</v>
-      </c>
-      <c r="K69" s="1">
-        <v>100</v>
-      </c>
-      <c r="L69" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17">
-      <c r="A70" s="9" t="s">
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>100</v>
+      </c>
+      <c r="L70" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
+      <c r="A71" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B71" s="3">
         <f t="shared" si="1"/>
         <v>1126</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="1">
-        <v>0</v>
-      </c>
-      <c r="E70" s="1">
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
         <v>8026</v>
       </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
-      </c>
-      <c r="H70" s="1">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3">
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3">
         <v>29</v>
       </c>
-      <c r="J70" s="1">
-        <v>1</v>
-      </c>
-      <c r="K70" s="1">
-        <v>100</v>
-      </c>
-      <c r="L70" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17">
-      <c r="A71" s="9" t="s">
+      <c r="J71" s="1">
+        <v>1</v>
+      </c>
+      <c r="K71" s="1">
+        <v>100</v>
+      </c>
+      <c r="L71" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17">
+      <c r="A72" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B72" s="3">
         <f t="shared" si="1"/>
         <v>1127</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D71" s="1">
-        <v>0</v>
-      </c>
-      <c r="E71" s="1">
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
         <v>8027</v>
       </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3">
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3">
         <v>29</v>
       </c>
-      <c r="J71" s="1">
-        <v>1</v>
-      </c>
-      <c r="K71" s="1">
-        <v>100</v>
-      </c>
-      <c r="L71" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17">
-      <c r="A72" s="9" t="s">
+      <c r="J72" s="1">
+        <v>1</v>
+      </c>
+      <c r="K72" s="1">
+        <v>100</v>
+      </c>
+      <c r="L72" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B73" s="3">
         <f t="shared" si="1"/>
         <v>1128</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D72" s="1">
-        <v>0</v>
-      </c>
-      <c r="E72" s="1">
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
         <v>8028</v>
       </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
-      </c>
-      <c r="H72" s="1">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3">
         <v>29</v>
       </c>
-      <c r="J72" s="1">
-        <v>1</v>
-      </c>
-      <c r="K72" s="1">
-        <v>100</v>
-      </c>
-      <c r="L72" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17">
-      <c r="A73" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B73" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D73" s="1">
-        <v>6</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0</v>
-      </c>
-      <c r="H73" s="1">
-        <v>0</v>
-      </c>
-      <c r="I73" s="1">
-        <v>1</v>
-      </c>
       <c r="J73" s="1">
         <v>1</v>
       </c>
@@ -5001,20 +5011,17 @@
       </c>
       <c r="L73" s="1">
         <v>100</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:17">
       <c r="A74" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B74" s="1">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D74" s="1">
         <v>6</v>
@@ -5026,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -5044,18 +5051,18 @@
         <v>100</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:17">
       <c r="A75" s="1" t="s">
-        <v>435</v>
+        <v>28</v>
       </c>
       <c r="B75" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>434</v>
+        <v>35</v>
       </c>
       <c r="D75" s="1">
         <v>6</v>
@@ -5067,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -5085,18 +5092,18 @@
         <v>100</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:17">
       <c r="A76" s="1" t="s">
-        <v>29</v>
+        <v>435</v>
       </c>
       <c r="B76" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>36</v>
+        <v>434</v>
       </c>
       <c r="D76" s="1">
         <v>6</v>
@@ -5126,18 +5133,18 @@
         <v>100</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:17">
       <c r="A77" s="1" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="B77" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="D77" s="1">
         <v>6</v>
@@ -5167,24 +5174,24 @@
         <v>100</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>178</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:17">
       <c r="A78" s="1" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="B78" s="1">
-        <v>2100</v>
+        <v>2004</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="D78" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E78" s="1">
-        <v>2100</v>
+        <v>1</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -5208,24 +5215,24 @@
         <v>100</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
     </row>
     <row r="79" spans="1:17">
       <c r="A79" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B79" s="1">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D79" s="1">
         <v>10</v>
       </c>
       <c r="E79" s="1">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -5249,24 +5256,24 @@
         <v>100</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:17">
       <c r="A80" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B80" s="1">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D80" s="1">
         <v>10</v>
       </c>
       <c r="E80" s="1">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -5290,24 +5297,24 @@
         <v>100</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:17">
       <c r="A81" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B81" s="1">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D81" s="1">
         <v>10</v>
       </c>
       <c r="E81" s="1">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -5331,24 +5338,24 @@
         <v>100</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:17">
       <c r="A82" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B82" s="1">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D82" s="1">
         <v>10</v>
       </c>
       <c r="E82" s="1">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -5372,24 +5379,24 @@
         <v>100</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:17">
       <c r="A83" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B83" s="1">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D83" s="1">
         <v>10</v>
       </c>
       <c r="E83" s="1">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -5413,24 +5420,24 @@
         <v>100</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:17">
       <c r="A84" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B84" s="1">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D84" s="1">
         <v>10</v>
       </c>
       <c r="E84" s="1">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -5454,24 +5461,24 @@
         <v>100</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="1:17">
       <c r="A85" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B85" s="1">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D85" s="1">
         <v>10</v>
       </c>
       <c r="E85" s="1">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -5495,24 +5502,24 @@
         <v>100</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:17">
       <c r="A86" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B86" s="1">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D86" s="1">
         <v>10</v>
       </c>
       <c r="E86" s="1">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -5536,24 +5543,24 @@
         <v>100</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87" spans="1:17">
       <c r="A87" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B87" s="1">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D87" s="1">
         <v>10</v>
       </c>
       <c r="E87" s="1">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -5577,24 +5584,24 @@
         <v>100</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:17">
       <c r="A88" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B88" s="1">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D88" s="1">
         <v>10</v>
       </c>
       <c r="E88" s="1">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -5618,24 +5625,24 @@
         <v>100</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:17">
       <c r="A89" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B89" s="1">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D89" s="1">
         <v>10</v>
       </c>
       <c r="E89" s="1">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5659,24 +5666,24 @@
         <v>100</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:17">
       <c r="A90" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" s="1">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D90" s="1">
         <v>10</v>
       </c>
       <c r="E90" s="1">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5700,106 +5707,106 @@
         <v>100</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:17">
       <c r="A91" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B91" s="1">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D91" s="1">
         <v>10</v>
       </c>
       <c r="E91" s="1">
+        <v>2112</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1">
+        <v>1</v>
+      </c>
+      <c r="J91" s="1">
+        <v>1</v>
+      </c>
+      <c r="K91" s="1">
+        <v>100</v>
+      </c>
+      <c r="L91" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17">
+      <c r="A92" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B92" s="1">
         <v>2113</v>
       </c>
-      <c r="F91" s="1">
-        <v>0</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0</v>
-      </c>
-      <c r="H91" s="1">
-        <v>0</v>
-      </c>
-      <c r="I91" s="1">
-        <v>1</v>
-      </c>
-      <c r="J91" s="1">
-        <v>1</v>
-      </c>
-      <c r="K91" s="1">
-        <v>100</v>
-      </c>
-      <c r="L91" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q91" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A92" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B92" s="1">
-        <v>2200</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D92" s="1">
         <v>10</v>
       </c>
       <c r="E92" s="1">
+        <v>2113</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1</v>
+      </c>
+      <c r="J92" s="1">
+        <v>1</v>
+      </c>
+      <c r="K92" s="1">
+        <v>100</v>
+      </c>
+      <c r="L92" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="12.75" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" s="1">
         <v>2200</v>
       </c>
-      <c r="F92" s="1">
-        <v>0</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1">
-        <v>0</v>
-      </c>
-      <c r="I92" s="1">
-        <v>1</v>
-      </c>
-      <c r="J92" s="1">
-        <v>1</v>
-      </c>
-      <c r="K92" s="1">
-        <v>100</v>
-      </c>
-      <c r="L92" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q92" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17">
-      <c r="A93" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B93" s="1">
-        <v>2201</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D93" s="1">
         <v>10</v>
       </c>
       <c r="E93" s="1">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5823,106 +5830,106 @@
         <v>100</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:17">
       <c r="A94" s="1" t="s">
-        <v>358</v>
+        <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>357</v>
+        <v>94</v>
       </c>
       <c r="D94" s="1">
         <v>10</v>
       </c>
       <c r="E94" s="1">
+        <v>2201</v>
+      </c>
+      <c r="F94" s="1">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1">
+        <v>1</v>
+      </c>
+      <c r="J94" s="1">
+        <v>1</v>
+      </c>
+      <c r="K94" s="1">
+        <v>100</v>
+      </c>
+      <c r="L94" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17">
+      <c r="A95" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B95" s="1">
         <v>2202</v>
       </c>
-      <c r="F94" s="1">
-        <v>0</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0</v>
-      </c>
-      <c r="H94" s="1">
-        <v>0</v>
-      </c>
-      <c r="I94" s="1">
-        <v>1</v>
-      </c>
-      <c r="J94" s="1">
-        <v>1</v>
-      </c>
-      <c r="K94" s="1">
-        <v>100</v>
-      </c>
-      <c r="L94" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q94" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D95" s="1">
+        <v>10</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2202</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>1</v>
+      </c>
+      <c r="J95" s="1">
+        <v>1</v>
+      </c>
+      <c r="K95" s="1">
+        <v>100</v>
+      </c>
+      <c r="L95" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q95" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15">
-      <c r="A95" s="12" t="s">
+    <row r="96" spans="1:17" ht="15">
+      <c r="A96" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B96" s="1">
         <v>4000</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C96" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="D95" s="1">
-        <v>3</v>
-      </c>
-      <c r="E95" s="7">
-        <v>1000</v>
-      </c>
-      <c r="F95" s="1">
-        <v>1</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0</v>
-      </c>
-      <c r="H95" s="1">
-        <v>0</v>
-      </c>
-      <c r="I95" s="1">
-        <v>9</v>
-      </c>
-      <c r="J95" s="1">
-        <v>1</v>
-      </c>
-      <c r="K95" s="1">
-        <v>100</v>
-      </c>
-      <c r="L95" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q95" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17">
-      <c r="A96" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B96" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>138</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96" s="7">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F96" s="1">
         <v>1</v>
@@ -5945,25 +5952,25 @@
       <c r="L96" s="1">
         <v>100</v>
       </c>
-      <c r="Q96" s="7" t="s">
-        <v>138</v>
+      <c r="Q96" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:17">
       <c r="A97" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B97" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
       </c>
       <c r="E97" s="7">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
@@ -5987,24 +5994,24 @@
         <v>100</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="98" spans="1:17">
       <c r="A98" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B98" s="1">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D98" s="1">
         <v>3</v>
       </c>
       <c r="E98" s="7">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="F98" s="1">
         <v>1</v>
@@ -6028,24 +6035,24 @@
         <v>100</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="99" spans="1:17">
       <c r="A99" s="7" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B99" s="1">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="D99" s="1">
         <v>3</v>
       </c>
       <c r="E99" s="7">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
@@ -6069,24 +6076,24 @@
         <v>100</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:17">
-      <c r="A100" s="8" t="s">
-        <v>141</v>
+      <c r="A100" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="B100" s="1">
-        <v>4008</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>141</v>
+        <v>4007</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="D100" s="1">
         <v>3</v>
       </c>
       <c r="E100" s="7">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -6109,25 +6116,25 @@
       <c r="L100" s="1">
         <v>100</v>
       </c>
-      <c r="Q100" s="8" t="s">
+      <c r="Q100" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17">
+      <c r="A101" s="8" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="101" spans="1:17">
-      <c r="A101" s="7" t="s">
-        <v>142</v>
-      </c>
       <c r="B101" s="1">
-        <v>4009</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>142</v>
+        <v>4008</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="D101" s="1">
         <v>3</v>
       </c>
       <c r="E101" s="7">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
@@ -6150,25 +6157,25 @@
       <c r="L101" s="1">
         <v>100</v>
       </c>
-      <c r="Q101" s="7" t="s">
+      <c r="Q101" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17">
+      <c r="A102" s="7" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="102" spans="1:17">
-      <c r="A102" s="8" t="s">
-        <v>143</v>
-      </c>
       <c r="B102" s="1">
-        <v>4010</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>143</v>
+        <v>4009</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="D102" s="1">
         <v>3</v>
       </c>
       <c r="E102" s="7">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
@@ -6191,25 +6198,25 @@
       <c r="L102" s="1">
         <v>100</v>
       </c>
-      <c r="Q102" s="8" t="s">
+      <c r="Q102" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17">
+      <c r="A103" s="8" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="103" spans="1:17">
-      <c r="A103" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="B103" s="1">
-        <v>4011</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>144</v>
+        <v>4010</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="D103" s="1">
         <v>3</v>
       </c>
       <c r="E103" s="7">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
@@ -6232,25 +6239,25 @@
       <c r="L103" s="1">
         <v>100</v>
       </c>
-      <c r="Q103" s="7" t="s">
-        <v>144</v>
+      <c r="Q103" s="8" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:17">
       <c r="A104" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B104" s="1">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D104" s="1">
         <v>3</v>
       </c>
       <c r="E104" s="7">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -6274,24 +6281,24 @@
         <v>100</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="105" spans="1:17">
       <c r="A105" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B105" s="1">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D105" s="1">
         <v>3</v>
       </c>
       <c r="E105" s="7">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -6315,24 +6322,24 @@
         <v>100</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:17">
       <c r="A106" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B106" s="1">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D106" s="1">
         <v>3</v>
       </c>
       <c r="E106" s="7">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
@@ -6356,24 +6363,24 @@
         <v>100</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:17">
       <c r="A107" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B107" s="1">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D107" s="1">
         <v>3</v>
       </c>
       <c r="E107" s="7">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -6397,24 +6404,24 @@
         <v>100</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:17">
       <c r="A108" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B108" s="1">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D108" s="1">
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
@@ -6438,24 +6445,24 @@
         <v>100</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:17">
       <c r="A109" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B109" s="1">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F109" s="1">
         <v>1</v>
@@ -6479,24 +6486,24 @@
         <v>100</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:17">
       <c r="A110" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B110" s="1">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -6520,24 +6527,24 @@
         <v>100</v>
       </c>
       <c r="Q110" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17">
+      <c r="A111" s="7" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="111" spans="1:17">
-      <c r="A111" s="8" t="s">
-        <v>152</v>
-      </c>
       <c r="B111" s="1">
-        <v>4020</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>152</v>
+        <v>4018</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>151</v>
       </c>
       <c r="D111" s="1">
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
@@ -6560,25 +6567,25 @@
       <c r="L111" s="1">
         <v>100</v>
       </c>
-      <c r="Q111" s="8" t="s">
+      <c r="Q111" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17">
+      <c r="A112" s="8" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="112" spans="1:17">
-      <c r="A112" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="B112" s="1">
-        <v>4021</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>153</v>
+        <v>4020</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="D112" s="1">
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
@@ -6601,25 +6608,25 @@
       <c r="L112" s="1">
         <v>100</v>
       </c>
-      <c r="Q112" s="7" t="s">
-        <v>153</v>
+      <c r="Q112" s="8" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:17">
       <c r="A113" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B113" s="1">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F113" s="1">
         <v>1</v>
@@ -6643,24 +6650,24 @@
         <v>100</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="114" spans="1:17">
       <c r="A114" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B114" s="1">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
       </c>
       <c r="E114" s="7">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
@@ -6684,24 +6691,24 @@
         <v>100</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="115" spans="1:17">
       <c r="A115" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B115" s="1">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D115" s="1">
         <v>3</v>
       </c>
       <c r="E115" s="7">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
@@ -6725,24 +6732,24 @@
         <v>100</v>
       </c>
       <c r="Q115" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17">
+      <c r="A116" s="7" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="116" spans="1:17">
-      <c r="A116" s="8" t="s">
-        <v>157</v>
-      </c>
       <c r="B116" s="1">
-        <v>4100</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>157</v>
+        <v>4024</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
       </c>
       <c r="E116" s="7">
-        <v>1100</v>
+        <v>1024</v>
       </c>
       <c r="F116" s="1">
         <v>1</v>
@@ -6765,25 +6772,25 @@
       <c r="L116" s="1">
         <v>100</v>
       </c>
-      <c r="Q116" s="8" t="s">
-        <v>157</v>
+      <c r="Q116" s="7" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="117" spans="1:17">
       <c r="A117" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B117" s="1">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D117" s="1">
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
@@ -6807,24 +6814,24 @@
         <v>100</v>
       </c>
       <c r="Q117" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" spans="1:17">
       <c r="A118" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B118" s="1">
-        <v>4103</v>
+        <v>4101</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D118" s="1">
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F118" s="1">
         <v>1</v>
@@ -6848,24 +6855,24 @@
         <v>100</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:17">
       <c r="A119" s="8" t="s">
-        <v>293</v>
+        <v>159</v>
       </c>
       <c r="B119" s="1">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>293</v>
+        <v>159</v>
       </c>
       <c r="D119" s="1">
         <v>3</v>
       </c>
       <c r="E119" s="7">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F119" s="1">
         <v>1</v>
@@ -6889,24 +6896,24 @@
         <v>100</v>
       </c>
       <c r="Q119" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120" spans="1:17">
       <c r="A120" s="8" t="s">
-        <v>161</v>
+        <v>293</v>
       </c>
       <c r="B120" s="1">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>161</v>
+        <v>293</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
       </c>
       <c r="E120" s="7">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -6930,24 +6937,24 @@
         <v>100</v>
       </c>
       <c r="Q120" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="121" spans="1:17">
       <c r="A121" s="8" t="s">
-        <v>356</v>
+        <v>161</v>
       </c>
       <c r="B121" s="1">
-        <v>4109</v>
+        <v>4106</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D121" s="1">
         <v>3</v>
       </c>
       <c r="E121" s="7">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
@@ -6971,24 +6978,24 @@
         <v>100</v>
       </c>
       <c r="Q121" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="122" spans="1:17">
       <c r="A122" s="8" t="s">
-        <v>291</v>
+        <v>356</v>
       </c>
       <c r="B122" s="1">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D122" s="1">
         <v>3</v>
       </c>
       <c r="E122" s="7">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F122" s="1">
         <v>1</v>
@@ -7012,24 +7019,24 @@
         <v>100</v>
       </c>
       <c r="Q122" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123" spans="1:17">
       <c r="A123" s="8" t="s">
-        <v>164</v>
+        <v>291</v>
       </c>
       <c r="B123" s="1">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D123" s="1">
         <v>3</v>
       </c>
       <c r="E123" s="7">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
@@ -7053,24 +7060,24 @@
         <v>100</v>
       </c>
       <c r="Q123" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="124" spans="1:17">
       <c r="A124" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B124" s="1">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D124" s="1">
         <v>3</v>
       </c>
       <c r="E124" s="7">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F124" s="1">
         <v>1</v>
@@ -7094,24 +7101,24 @@
         <v>100</v>
       </c>
       <c r="Q124" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="125" spans="1:17">
       <c r="A125" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B125" s="1">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D125" s="1">
         <v>3</v>
       </c>
       <c r="E125" s="7">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
@@ -7135,24 +7142,24 @@
         <v>100</v>
       </c>
       <c r="Q125" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:17">
       <c r="A126" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B126" s="1">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D126" s="1">
         <v>3</v>
       </c>
       <c r="E126" s="7">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
@@ -7176,24 +7183,24 @@
         <v>100</v>
       </c>
       <c r="Q126" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127" spans="1:17">
       <c r="A127" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B127" s="1">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D127" s="1">
         <v>3</v>
       </c>
       <c r="E127" s="7">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -7217,24 +7224,24 @@
         <v>100</v>
       </c>
       <c r="Q127" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="128" spans="1:17">
       <c r="A128" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B128" s="1">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D128" s="1">
         <v>3</v>
       </c>
       <c r="E128" s="7">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
@@ -7258,24 +7265,24 @@
         <v>100</v>
       </c>
       <c r="Q128" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="129" spans="1:17">
       <c r="A129" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B129" s="1">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D129" s="1">
         <v>3</v>
       </c>
       <c r="E129" s="7">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="F129" s="1">
         <v>1</v>
@@ -7299,24 +7306,24 @@
         <v>100</v>
       </c>
       <c r="Q129" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17">
+      <c r="A130" s="8" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="130" spans="1:17">
-      <c r="A130" s="13" t="s">
-        <v>275</v>
-      </c>
       <c r="B130" s="1">
-        <v>3000</v>
-      </c>
-      <c r="C130" s="16" t="s">
-        <v>275</v>
+        <v>4117</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>170</v>
       </c>
       <c r="D130" s="1">
         <v>3</v>
       </c>
-      <c r="E130" s="1">
-        <v>0</v>
+      <c r="E130" s="7">
+        <v>1117</v>
       </c>
       <c r="F130" s="1">
         <v>1</v>
@@ -7339,16 +7346,19 @@
       <c r="L130" s="1">
         <v>100</v>
       </c>
+      <c r="Q130" s="8" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="131" spans="1:17">
       <c r="A131" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B131" s="1">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D131" s="1">
         <v>3</v>
@@ -7357,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
@@ -7366,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="1">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J131" s="1">
         <v>1</v>
@@ -7380,13 +7390,13 @@
     </row>
     <row r="132" spans="1:17">
       <c r="A132" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B132" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D132" s="1">
         <v>3</v>
@@ -7418,13 +7428,13 @@
     </row>
     <row r="133" spans="1:17">
       <c r="A133" s="13" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="B133" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>363</v>
+        <v>279</v>
       </c>
       <c r="D133" s="1">
         <v>3</v>
@@ -7456,13 +7466,13 @@
     </row>
     <row r="134" spans="1:17">
       <c r="A134" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B134" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="D134" s="1">
         <v>3</v>
@@ -7493,14 +7503,14 @@
       </c>
     </row>
     <row r="135" spans="1:17">
-      <c r="A135" s="14" t="s">
-        <v>296</v>
+      <c r="A135" s="13" t="s">
+        <v>295</v>
       </c>
       <c r="B135" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D135" s="1">
         <v>3</v>
@@ -7532,13 +7542,13 @@
     </row>
     <row r="136" spans="1:17">
       <c r="A136" s="14" t="s">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="B136" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="D136" s="1">
         <v>3</v>
@@ -7547,7 +7557,7 @@
         <v>0</v>
       </c>
       <c r="F136" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="1">
         <v>0</v>
@@ -7570,13 +7580,13 @@
     </row>
     <row r="137" spans="1:17">
       <c r="A137" s="14" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B137" s="1">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D137" s="1">
         <v>3</v>
@@ -7594,7 +7604,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J137" s="1">
         <v>1</v>
@@ -7608,13 +7618,13 @@
     </row>
     <row r="138" spans="1:17">
       <c r="A138" s="14" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B138" s="1">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D138" s="1">
         <v>3</v>
@@ -7645,14 +7655,14 @@
       </c>
     </row>
     <row r="139" spans="1:17">
-      <c r="A139" s="1" t="s">
-        <v>239</v>
+      <c r="A139" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="B139" s="1">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="D139" s="1">
         <v>3</v>
@@ -7661,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="F139" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" s="1">
         <v>0</v>
@@ -7670,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="1">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J139" s="1">
         <v>1</v>
@@ -7684,13 +7694,13 @@
     </row>
     <row r="140" spans="1:17">
       <c r="A140" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B140" s="1">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D140" s="1">
         <v>3</v>
@@ -7722,13 +7732,13 @@
     </row>
     <row r="141" spans="1:17">
       <c r="A141" s="1" t="s">
-        <v>360</v>
+        <v>248</v>
       </c>
       <c r="B141" s="1">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>355</v>
+        <v>248</v>
       </c>
       <c r="D141" s="1">
         <v>3</v>
@@ -7759,14 +7769,14 @@
       </c>
     </row>
     <row r="142" spans="1:17">
-      <c r="A142" s="15" t="s">
-        <v>352</v>
+      <c r="A142" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="B142" s="1">
         <v>3011</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="D142" s="1">
         <v>3</v>
@@ -7775,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="F142" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" s="1">
         <v>0</v>
@@ -7798,16 +7808,16 @@
     </row>
     <row r="143" spans="1:17">
       <c r="A143" s="15" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B143" s="1">
-        <v>3100</v>
+        <v>3011</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="D143" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E143" s="1">
         <v>0</v>
@@ -7822,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="I143" s="1">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J143" s="1">
         <v>1</v>
@@ -7836,13 +7846,13 @@
     </row>
     <row r="144" spans="1:17">
       <c r="A144" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B144" s="1">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="C144" s="16" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="D144" s="1">
         <v>4</v>
@@ -7874,13 +7884,13 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="15" t="s">
-        <v>265</v>
+        <v>362</v>
       </c>
       <c r="B145" s="1">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="D145" s="1">
         <v>4</v>
@@ -7912,13 +7922,13 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="15" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="B146" s="1">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="D146" s="1">
         <v>4</v>
@@ -7950,13 +7960,13 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="15" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="B147" s="1">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="D147" s="1">
         <v>4</v>
@@ -7988,13 +7998,13 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="15" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="B148" s="1">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="D148" s="1">
         <v>4</v>
@@ -8026,13 +8036,13 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B149" s="1">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C149" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D149" s="1">
         <v>4</v>
@@ -8064,13 +8074,13 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" s="15" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="B150" s="1">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="D150" s="1">
         <v>4</v>
@@ -8102,13 +8112,13 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="15" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B151" s="1">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>365</v>
+        <v>203</v>
       </c>
       <c r="D151" s="1">
         <v>4</v>
@@ -8140,13 +8150,13 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="15" t="s">
-        <v>299</v>
+        <v>207</v>
       </c>
       <c r="B152" s="1">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="C152" s="16" t="s">
-        <v>299</v>
+        <v>365</v>
       </c>
       <c r="D152" s="1">
         <v>4</v>
@@ -8178,13 +8188,13 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="15" t="s">
-        <v>201</v>
+        <v>299</v>
       </c>
       <c r="B153" s="1">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>201</v>
+        <v>299</v>
       </c>
       <c r="D153" s="1">
         <v>4</v>
@@ -8216,13 +8226,13 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" s="15" t="s">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="B154" s="1">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="C154" s="16" t="s">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D154" s="1">
         <v>4</v>
@@ -8254,13 +8264,13 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" s="15" t="s">
-        <v>354</v>
+        <v>300</v>
       </c>
       <c r="B155" s="1">
-        <v>3112</v>
-      </c>
-      <c r="C155" s="17" t="s">
-        <v>354</v>
+        <v>3111</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>300</v>
       </c>
       <c r="D155" s="1">
         <v>4</v>
@@ -8292,13 +8302,13 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="15" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="B156" s="1">
-        <v>3113</v>
-      </c>
-      <c r="C156" s="16" t="s">
-        <v>366</v>
+        <v>3112</v>
+      </c>
+      <c r="C156" s="17" t="s">
+        <v>354</v>
       </c>
       <c r="D156" s="1">
         <v>4</v>
@@ -8330,13 +8340,13 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="15" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="B157" s="1">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="C157" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D157" s="1">
         <v>4</v>
@@ -8368,13 +8378,13 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="15" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="B158" s="1">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="C158" s="16" t="s">
-        <v>302</v>
+        <v>367</v>
       </c>
       <c r="D158" s="1">
         <v>4</v>
@@ -8406,13 +8416,13 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B159" s="1">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="D159" s="1">
         <v>4</v>
@@ -8444,13 +8454,13 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="15" t="s">
-        <v>221</v>
+        <v>303</v>
       </c>
       <c r="B160" s="1">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="C160" s="16" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D160" s="1">
         <v>4</v>
@@ -8482,13 +8492,13 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="15" t="s">
-        <v>304</v>
+        <v>221</v>
       </c>
       <c r="B161" s="1">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="C161" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D161" s="1">
         <v>4</v>
@@ -8520,13 +8530,13 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" s="15" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="B162" s="1">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="C162" s="16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D162" s="1">
         <v>4</v>
@@ -8558,13 +8568,13 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="15" t="s">
-        <v>305</v>
+        <v>234</v>
       </c>
       <c r="B163" s="1">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="C163" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D163" s="1">
         <v>4</v>
@@ -8596,13 +8606,13 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" s="15" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="B164" s="1">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="C164" s="16" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D164" s="1">
         <v>4</v>
@@ -8634,13 +8644,13 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="15" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="B165" s="1">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>216</v>
+        <v>373</v>
       </c>
       <c r="D165" s="1">
         <v>4</v>
@@ -8672,13 +8682,13 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" s="15" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="B166" s="1">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="C166" s="16" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="D166" s="1">
         <v>4</v>
@@ -8710,13 +8720,13 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" s="15" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B167" s="1">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="C167" s="16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D167" s="1">
         <v>4</v>
@@ -8748,13 +8758,13 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="15" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B168" s="1">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="C168" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D168" s="1">
         <v>4</v>
@@ -8786,13 +8796,13 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B169" s="1">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="C169" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D169" s="1">
         <v>4</v>
@@ -8824,13 +8834,13 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" s="15" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="B170" s="1">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="C170" s="16" t="s">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="D170" s="1">
         <v>4</v>
@@ -8862,13 +8872,13 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B171" s="1">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="C171" s="16" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D171" s="1">
         <v>4</v>
@@ -8900,13 +8910,13 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" s="15" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="B172" s="1">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="C172" s="16" t="s">
-        <v>255</v>
+        <v>374</v>
       </c>
       <c r="D172" s="1">
         <v>4</v>
@@ -8938,13 +8948,13 @@
     </row>
     <row r="173" spans="1:12">
       <c r="A173" s="15" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="B173" s="1">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="C173" s="16" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="D173" s="1">
         <v>4</v>
@@ -8976,13 +8986,13 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B174" s="1">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="C174" s="16" t="s">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="D174" s="1">
         <v>4</v>
@@ -9014,13 +9024,13 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="15" t="s">
-        <v>261</v>
+        <v>310</v>
       </c>
       <c r="B175" s="1">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="C175" s="16" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D175" s="1">
         <v>4</v>
@@ -9052,13 +9062,13 @@
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="15" t="s">
-        <v>311</v>
+        <v>261</v>
       </c>
       <c r="B176" s="1">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="C176" s="16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D176" s="1">
         <v>4</v>
@@ -9090,13 +9100,13 @@
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B177" s="1">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="C177" s="16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D177" s="1">
         <v>4</v>
@@ -9128,13 +9138,13 @@
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B178" s="1">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="C178" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D178" s="1">
         <v>4</v>
@@ -9166,13 +9176,13 @@
     </row>
     <row r="179" spans="1:12">
       <c r="A179" s="15" t="s">
-        <v>220</v>
+        <v>313</v>
       </c>
       <c r="B179" s="1">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="C179" s="16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D179" s="1">
         <v>4</v>
@@ -9204,13 +9214,13 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" s="15" t="s">
-        <v>314</v>
+        <v>220</v>
       </c>
       <c r="B180" s="1">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="C180" s="16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D180" s="1">
         <v>4</v>
@@ -9242,13 +9252,13 @@
     </row>
     <row r="181" spans="1:12">
       <c r="A181" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B181" s="1">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="C181" s="16" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D181" s="1">
         <v>4</v>
@@ -9280,13 +9290,13 @@
     </row>
     <row r="182" spans="1:12">
       <c r="A182" s="15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B182" s="1">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="C182" s="16" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D182" s="1">
         <v>4</v>
@@ -9318,13 +9328,13 @@
     </row>
     <row r="183" spans="1:12">
       <c r="A183" s="15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B183" s="1">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="C183" s="16" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D183" s="1">
         <v>4</v>
@@ -9356,13 +9366,13 @@
     </row>
     <row r="184" spans="1:12">
       <c r="A184" s="15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B184" s="1">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="C184" s="16" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D184" s="1">
         <v>4</v>
@@ -9394,13 +9404,13 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" s="15" t="s">
-        <v>243</v>
+        <v>318</v>
       </c>
       <c r="B185" s="1">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="C185" s="16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D185" s="1">
         <v>4</v>
@@ -9432,13 +9442,13 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" s="15" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="B186" s="1">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C186" s="16" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D186" s="1">
         <v>4</v>
@@ -9447,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="F186" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G186" s="1">
         <v>0</v>
@@ -9470,13 +9480,13 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" s="15" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="B187" s="1">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="C187" s="16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D187" s="1">
         <v>4</v>
@@ -9485,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="F187" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187" s="1">
         <v>0</v>
@@ -9508,13 +9518,13 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" s="15" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="B188" s="1">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="C188" s="16" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D188" s="1">
         <v>4</v>
@@ -9523,7 +9533,7 @@
         <v>0</v>
       </c>
       <c r="F188" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" s="1">
         <v>0</v>
@@ -9546,13 +9556,13 @@
     </row>
     <row r="189" spans="1:12">
       <c r="A189" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B189" s="1">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="C189" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D189" s="1">
         <v>4</v>
@@ -9561,7 +9571,7 @@
         <v>0</v>
       </c>
       <c r="F189" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189" s="1">
         <v>0</v>
@@ -9584,13 +9594,13 @@
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B190" s="1">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="C190" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D190" s="1">
         <v>4</v>
@@ -9599,7 +9609,7 @@
         <v>0</v>
       </c>
       <c r="F190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" s="1">
         <v>0</v>
@@ -9622,13 +9632,13 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B191" s="1">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="C191" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D191" s="1">
         <v>4</v>
@@ -9637,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="F191" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" s="1">
         <v>0</v>
@@ -9660,13 +9670,13 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" s="15" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="B192" s="1">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="C192" s="16" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D192" s="1">
         <v>4</v>
@@ -9698,13 +9708,13 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" s="15" t="s">
-        <v>323</v>
+        <v>394</v>
       </c>
       <c r="B193" s="1">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="C193" s="16" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D193" s="1">
         <v>4</v>
@@ -9736,13 +9746,13 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B194" s="1">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="C194" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D194" s="1">
         <v>4</v>
@@ -9774,13 +9784,13 @@
     </row>
     <row r="195" spans="1:12">
       <c r="A195" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B195" s="1">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="C195" s="16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D195" s="1">
         <v>4</v>
@@ -9812,13 +9822,13 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B196" s="1">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="C196" s="16" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D196" s="1">
         <v>4</v>
@@ -9850,13 +9860,13 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B197" s="1">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="C197" s="16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D197" s="1">
         <v>4</v>
@@ -9888,13 +9898,13 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" s="15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B198" s="1">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="C198" s="16" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D198" s="1">
         <v>4</v>
@@ -9926,13 +9936,13 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B199" s="1">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="C199" s="16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D199" s="1">
         <v>4</v>
@@ -9964,13 +9974,13 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B200" s="1">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C200" s="16" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D200" s="1">
         <v>4</v>
@@ -10002,13 +10012,13 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B201" s="1">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="C201" s="16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D201" s="1">
         <v>4</v>
@@ -10040,13 +10050,13 @@
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B202" s="1">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="C202" s="16" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D202" s="1">
         <v>4</v>
@@ -10078,13 +10088,13 @@
     </row>
     <row r="203" spans="1:12">
       <c r="A203" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B203" s="1">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="C203" s="16" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D203" s="1">
         <v>4</v>
@@ -10116,13 +10126,13 @@
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B204" s="1">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="C204" s="16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D204" s="1">
         <v>4</v>
@@ -10154,13 +10164,13 @@
     </row>
     <row r="205" spans="1:12">
       <c r="A205" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B205" s="1">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="C205" s="16" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D205" s="1">
         <v>4</v>
@@ -10192,13 +10202,13 @@
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B206" s="1">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="C206" s="16" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D206" s="1">
         <v>4</v>
@@ -10230,13 +10240,13 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B207" s="1">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="C207" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D207" s="1">
         <v>4</v>
@@ -10268,13 +10278,13 @@
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B208" s="1">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="C208" s="16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D208" s="1">
         <v>4</v>
@@ -10306,13 +10316,13 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B209" s="1">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="C209" s="16" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D209" s="1">
         <v>4</v>
@@ -10344,13 +10354,13 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B210" s="1">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="C210" s="16" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D210" s="1">
         <v>4</v>
@@ -10382,13 +10392,13 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B211" s="1">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="C211" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D211" s="1">
         <v>4</v>
@@ -10420,13 +10430,13 @@
     </row>
     <row r="212" spans="1:12">
       <c r="A212" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B212" s="1">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="C212" s="16" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="D212" s="1">
         <v>4</v>
@@ -10458,13 +10468,13 @@
     </row>
     <row r="213" spans="1:12">
       <c r="A213" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B213" s="1">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="C213" s="16" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D213" s="1">
         <v>4</v>
@@ -10496,13 +10506,13 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" s="15" t="s">
-        <v>416</v>
+        <v>343</v>
       </c>
       <c r="B214" s="1">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="C214" s="16" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="D214" s="1">
         <v>4</v>
@@ -10534,13 +10544,13 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B215" s="1">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="C215" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D215" s="1">
         <v>4</v>
@@ -10572,13 +10582,13 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" s="15" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B216" s="1">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="C216" s="16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D216" s="1">
         <v>4</v>
@@ -10610,13 +10620,13 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" s="15" t="s">
-        <v>347</v>
+        <v>417</v>
       </c>
       <c r="B217" s="1">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="C217" s="16" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
       <c r="D217" s="1">
         <v>4</v>
@@ -10648,13 +10658,13 @@
     </row>
     <row r="218" spans="1:12">
       <c r="A218" s="15" t="s">
-        <v>419</v>
+        <v>347</v>
       </c>
       <c r="B218" s="1">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="C218" s="16" t="s">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="D218" s="1">
         <v>4</v>
@@ -10686,13 +10696,13 @@
     </row>
     <row r="219" spans="1:12">
       <c r="A219" s="15" t="s">
-        <v>349</v>
+        <v>419</v>
       </c>
       <c r="B219" s="1">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="C219" s="16" t="s">
-        <v>420</v>
+        <v>348</v>
       </c>
       <c r="D219" s="1">
         <v>4</v>
@@ -10724,13 +10734,13 @@
     </row>
     <row r="220" spans="1:12">
       <c r="A220" s="15" t="s">
-        <v>421</v>
+        <v>349</v>
       </c>
       <c r="B220" s="1">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="C220" s="16" t="s">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="D220" s="1">
         <v>4</v>
@@ -10762,13 +10772,13 @@
     </row>
     <row r="221" spans="1:12">
       <c r="A221" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B221" s="1">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="C221" s="16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D221" s="1">
         <v>4</v>
@@ -10795,6 +10805,44 @@
         <v>100</v>
       </c>
       <c r="L221" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12">
+      <c r="A222" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="B222" s="1">
+        <v>3178</v>
+      </c>
+      <c r="C222" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="D222" s="1">
+        <v>4</v>
+      </c>
+      <c r="E222" s="1">
+        <v>0</v>
+      </c>
+      <c r="F222" s="1">
+        <v>1</v>
+      </c>
+      <c r="G222" s="1">
+        <v>0</v>
+      </c>
+      <c r="H222" s="1">
+        <v>0</v>
+      </c>
+      <c r="I222" s="1">
+        <v>1</v>
+      </c>
+      <c r="J222" s="1">
+        <v>1</v>
+      </c>
+      <c r="K222" s="1">
+        <v>100</v>
+      </c>
+      <c r="L222" s="1">
         <v>100</v>
       </c>
     </row>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -13730,7 +13730,7 @@
         <v>367</v>
       </c>
       <c r="D192" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E192" s="1">
         <v>0</v>
@@ -13768,7 +13768,7 @@
         <v>365</v>
       </c>
       <c r="D193" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E193" s="1">
         <v>0</v>
@@ -13806,7 +13806,7 @@
         <v>410</v>
       </c>
       <c r="D194" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E194" s="1">
         <v>0</v>
@@ -13844,7 +13844,7 @@
         <v>411</v>
       </c>
       <c r="D195" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E195" s="1">
         <v>0</v>
@@ -13882,7 +13882,7 @@
         <v>369</v>
       </c>
       <c r="D196" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E196" s="1">
         <v>0</v>
@@ -13920,7 +13920,7 @@
         <v>412</v>
       </c>
       <c r="D197" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E197" s="1">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>710</v>
       </c>
       <c r="D198" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E198" s="1">
         <v>0</v>
@@ -13996,7 +13996,7 @@
         <v>371</v>
       </c>
       <c r="D199" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E199" s="1">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>413</v>
       </c>
       <c r="D200" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E200" s="1">
         <v>0</v>
@@ -14072,7 +14072,7 @@
         <v>414</v>
       </c>
       <c r="D201" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E201" s="1">
         <v>0</v>
@@ -14110,7 +14110,7 @@
         <v>415</v>
       </c>
       <c r="D202" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E202" s="1">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>416</v>
       </c>
       <c r="D203" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E203" s="1">
         <v>0</v>
@@ -14186,7 +14186,7 @@
         <v>417</v>
       </c>
       <c r="D204" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E204" s="1">
         <v>0</v>
@@ -14224,7 +14224,7 @@
         <v>418</v>
       </c>
       <c r="D205" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E205" s="1">
         <v>0</v>
@@ -14262,7 +14262,7 @@
         <v>419</v>
       </c>
       <c r="D206" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E206" s="1">
         <v>0</v>
@@ -14300,7 +14300,7 @@
         <v>406</v>
       </c>
       <c r="D207" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E207" s="1">
         <v>0</v>
@@ -14338,7 +14338,7 @@
         <v>642</v>
       </c>
       <c r="D208" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E208" s="1">
         <v>0</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -21245,7 +21245,7 @@
         <v>443</v>
       </c>
       <c r="D209" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E209" s="1">
         <v>0</v>
@@ -21299,7 +21299,7 @@
         <v>0</v>
       </c>
       <c r="Z209" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AA209" s="1">
         <v>0</v>
@@ -21316,7 +21316,7 @@
         <v>440</v>
       </c>
       <c r="D210" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E210" s="1">
         <v>0</v>
@@ -21370,7 +21370,7 @@
         <v>0</v>
       </c>
       <c r="Z210" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AA210" s="1">
         <v>0</v>
@@ -21387,7 +21387,7 @@
         <v>441</v>
       </c>
       <c r="D211" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
@@ -21441,7 +21441,7 @@
         <v>0</v>
       </c>
       <c r="Z211" s="1">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="AA211" s="1">
         <v>0</v>
@@ -21458,7 +21458,7 @@
         <v>442</v>
       </c>
       <c r="D212" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E212" s="1">
         <v>0</v>
@@ -21529,7 +21529,7 @@
         <v>445</v>
       </c>
       <c r="D213" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E213" s="1">
         <v>0</v>
@@ -21600,7 +21600,7 @@
         <v>449</v>
       </c>
       <c r="D214" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E214" s="1">
         <v>0</v>
@@ -21671,7 +21671,7 @@
         <v>448</v>
       </c>
       <c r="D215" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E215" s="1">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>447</v>
       </c>
       <c r="D216" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E216" s="1">
         <v>0</v>
@@ -21813,7 +21813,7 @@
         <v>451</v>
       </c>
       <c r="D217" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E217" s="1">
         <v>0</v>
@@ -21884,7 +21884,7 @@
         <v>446</v>
       </c>
       <c r="D218" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E218" s="1">
         <v>0</v>
@@ -21955,7 +21955,7 @@
         <v>643</v>
       </c>
       <c r="D219" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E219" s="1">
         <v>0</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -14,12 +14,10 @@
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$G$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$G$96:$G$145</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -65,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="736">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2439,23 +2437,54 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>粘土</t>
+    <t>幻影水晶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>布片</t>
+    <t>绘写</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>蛛丝</t>
+    <t>加工</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>皮革</t>
+    <t>铁矿</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>蛇皮</t>
+    <t>盐矿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空白卷轴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰的结晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萤火树汁</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2463,113 +2492,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>琥珀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔力之土</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水晶石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彩色的布</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彩色羽毛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防水皮革</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>狼牙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鳞片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔族之血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暮光结晶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亡者之土</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夜之幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>植物的藤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幻影水晶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绘写</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加工</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁矿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>盐矿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>盐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁龟铠</t>
-  </si>
-  <si>
-    <t>铁龟铠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁龟铠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>空白卷轴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>传送卷轴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰的结晶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>萤火树汁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>风晶石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>纯净水</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2642,6 +2564,70 @@
   </si>
   <si>
     <t>otherType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇迹斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骑士冲击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙卷风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻影突刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔幻影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王之春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺颈鞭挞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷暴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽冥黑洞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧毒风暴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒猎杀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血腥囚笼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地刺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2786,7 +2772,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2855,6 +2841,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2933,3050 +2922,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="6"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="8"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="9"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="10"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="11"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="12"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="13"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="14"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="15"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="16"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="17"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="18"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="19"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="20"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="21"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="22"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="23"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="24"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="25"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="26"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="27"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="28"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="29"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="30"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="31"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="32"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="33"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="34"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="35"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="36"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="37"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="38"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="39"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="40"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="41"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="42"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="43"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000057-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="44"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000059-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="45"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000005B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="46"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000005D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="47"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000005F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="48"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000061-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="49"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000063-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="50"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000065-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="51"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000067-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="52"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000069-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="53"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000006B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="54"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000006D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="55"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000006F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="56"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000071-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="57"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000073-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="58"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000075-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="59"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000077-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="60"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000079-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="61"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000007B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="62"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000007D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="63"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000007F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="64"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000081-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="65"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000083-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="66"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000085-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="67"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000087-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="68"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000089-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="69"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000008B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="70"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000008D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="71"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000008F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="72"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000091-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="73"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000093-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="74"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000095-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="75"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000097-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="76"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000099-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="77"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000009B-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="78"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000009D-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="79"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000009F-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="80"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{000000A1-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="81"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{000000A3-62F2-479B-ABF8-C2B5F1379349}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$G$2:$G$80</c:f>
-              <c:strCache>
-                <c:ptCount val="79"/>
-                <c:pt idx="0">
-                  <c:v>铁块</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>刀刃</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>粘液</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>蛛丝</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>焦炭</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>鹿角</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>布片</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>马尾</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>毛线</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>皮革</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>蛇皮</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>木棒</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>石英砂</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>兽角</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>风晶石</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>琥珀</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>魔力之土</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>水晶石</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>羊毛</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>彩色的布</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>彩色羽毛</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>防水皮革</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>龟壳</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>寒冰气息</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>狼牙</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>鳞片</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>魔族之血</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>暮光结晶</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>亡者之土</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>象牙</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>夜之幕</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>幽魂</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>植物的藤</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>白磷粉末</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>冰的结晶</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>冰晶石</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>电偶瓶</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>毒淤泥</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>蜂刺</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>贵族徽章</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>火晶石</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>尖刺</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>金块</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>魔兽皮毛</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>奇美拉之翼</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>骑士之证</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>人狼之证</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>珊瑚</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>石化之眼</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>土晶石</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>贤者晶石</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>雪球</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>妖精粉</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>遗骨</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>银块</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>月之光华</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>脏绷带</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>珍珠</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>咒术药水</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>诅咒宝珠</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>暗夜之露</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>草药茶</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>恶魔花瓣</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>寒冰火种</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>幻影水晶</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>雷鸣宝珠</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>力量果实</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>魅惑药水</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>迷幻孢子</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>神奇泥浆</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>水晶球</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>图腾号角</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>武道精华</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>仙人掌</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>星的眼泪</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>眼球</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>萤火树汁</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>远古的硬币</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>粘土</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$H$2:$H$80</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="79"/>
-                <c:pt idx="0">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-843E-4A0B-B2B8-8CC07A4C3E6C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6335,37 +3280,37 @@
         <v>11</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>1</v>
@@ -6388,7 +3333,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>16</v>
@@ -6424,37 +3369,37 @@
         <v>9</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>6</v>
@@ -6930,7 +3875,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>717</v>
+        <v>698</v>
       </c>
       <c r="D10" s="1">
         <v>4</v>
@@ -7007,7 +3952,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -7084,7 +4029,7 @@
         <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
@@ -7774,13 +4719,13 @@
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
       <c r="B21" s="1">
         <v>200</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
       <c r="D21" s="1">
         <v>5</v>
@@ -8749,7 +5694,7 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A34" s="12" t="s">
-        <v>705</v>
+        <v>686</v>
       </c>
       <c r="B34" s="1">
         <v>215</v>
@@ -8824,7 +5769,7 @@
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A35" s="12" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="B35" s="1">
         <v>216</v>
@@ -14449,7 +11394,7 @@
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A110" s="12" t="s">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="B110" s="1">
         <v>295</v>
@@ -19357,7 +16302,7 @@
         <v>1</v>
       </c>
       <c r="E175" s="1">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F175" s="1">
         <v>1</v>
@@ -21047,13 +17992,13 @@
     </row>
     <row r="198" spans="1:28" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="B198" s="3">
         <v>1656</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>710</v>
+        <v>691</v>
       </c>
       <c r="D198" s="1">
         <v>2</v>
@@ -23060,13 +20005,13 @@
     </row>
     <row r="225" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A225" s="1" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="B225" s="1">
         <v>2100</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="D225" s="1">
         <v>10</v>
@@ -23132,7 +20077,7 @@
         <v>0</v>
       </c>
       <c r="AC225" s="1" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
     </row>
     <row r="226" spans="1:29" x14ac:dyDescent="0.15">
@@ -23291,13 +20236,13 @@
     </row>
     <row r="228" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A228" s="1" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="B228" s="1">
         <v>2103</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c r="D228" s="1">
         <v>10</v>
@@ -23363,7 +20308,7 @@
         <v>0</v>
       </c>
       <c r="AC228" s="1" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
     </row>
     <row r="229" spans="1:29" x14ac:dyDescent="0.15">
@@ -24138,13 +21083,13 @@
     </row>
     <row r="239" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A239" s="1" t="s">
-        <v>725</v>
+        <v>706</v>
       </c>
       <c r="B239" s="1">
         <v>2114</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>725</v>
+        <v>706</v>
       </c>
       <c r="D239" s="1">
         <v>10</v>
@@ -27135,7 +24080,7 @@
     </row>
     <row r="278" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A278" s="11" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="B278" s="1">
         <v>3002</v>
@@ -34632,7 +31577,9 @@
       <c r="F7" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>733</v>
+      </c>
       <c r="H7" s="14" t="s">
         <v>399</v>
       </c>
@@ -34676,7 +31623,9 @@
       <c r="F8" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="24" t="s">
+        <v>720</v>
+      </c>
       <c r="H8" s="17" t="s">
         <v>389</v>
       </c>
@@ -34726,7 +31675,9 @@
       <c r="F9" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>735</v>
+      </c>
       <c r="H9" s="14" t="s">
         <v>401</v>
       </c>
@@ -34773,7 +31724,9 @@
       <c r="F10" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="24" t="s">
+        <v>721</v>
+      </c>
       <c r="H10" s="14" t="s">
         <v>398</v>
       </c>
@@ -34861,7 +31814,9 @@
       <c r="F12" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>734</v>
+      </c>
       <c r="H12" s="14" t="s">
         <v>427</v>
       </c>
@@ -34909,7 +31864,9 @@
       <c r="F13" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="24" t="s">
+        <v>723</v>
+      </c>
       <c r="H13" s="14" t="s">
         <v>633</v>
       </c>
@@ -34950,7 +31907,9 @@
       <c r="F14" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="18" t="s">
+        <v>724</v>
+      </c>
       <c r="H14" s="14" t="s">
         <v>351</v>
       </c>
@@ -34997,7 +31956,9 @@
       <c r="F15" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="24" t="s">
+        <v>722</v>
+      </c>
       <c r="H15" s="9" t="s">
         <v>563</v>
       </c>
@@ -35044,7 +32005,9 @@
       <c r="F16" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="24" t="s">
+        <v>725</v>
+      </c>
       <c r="H16" s="9" t="s">
         <v>564</v>
       </c>
@@ -35058,7 +32021,7 @@
         <v>616</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>715</v>
+        <v>696</v>
       </c>
       <c r="N16" s="12">
         <f>VLOOKUP(J16,ItemData!$A$4:$B$377,2,FALSE)</f>
@@ -35132,7 +32095,9 @@
       <c r="F18" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>732</v>
+      </c>
       <c r="H18" s="14" t="s">
         <v>404</v>
       </c>
@@ -35173,7 +32138,9 @@
       <c r="F19" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="24" t="s">
+        <v>726</v>
+      </c>
       <c r="H19" s="14" t="s">
         <v>403</v>
       </c>
@@ -35220,7 +32187,9 @@
       <c r="F20" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G20" s="3"/>
+      <c r="G20" s="24" t="s">
+        <v>731</v>
+      </c>
       <c r="H20" s="14" t="s">
         <v>402</v>
       </c>
@@ -35349,7 +32318,9 @@
       <c r="F23" s="12" t="s">
         <v>544</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="24" t="s">
+        <v>727</v>
+      </c>
       <c r="H23" s="14" t="s">
         <v>618</v>
       </c>
@@ -35390,7 +32361,9 @@
       <c r="F24" s="12" t="s">
         <v>544</v>
       </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="24" t="s">
+        <v>728</v>
+      </c>
       <c r="H24" s="14" t="s">
         <v>617</v>
       </c>
@@ -35431,7 +32404,9 @@
       <c r="F25" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G25" s="3"/>
+      <c r="G25" s="24" t="s">
+        <v>729</v>
+      </c>
       <c r="H25" s="9" t="s">
         <v>567</v>
       </c>
@@ -35478,7 +32453,9 @@
       <c r="F26" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G26" s="3"/>
+      <c r="G26" s="24" t="s">
+        <v>730</v>
+      </c>
       <c r="H26" s="9" t="s">
         <v>566</v>
       </c>
@@ -35525,7 +32502,7 @@
       <c r="F27" t="s">
         <v>544</v>
       </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="24"/>
       <c r="H27" s="17" t="s">
         <v>627</v>
       </c>
@@ -35767,14 +32744,14 @@
         <v>1656</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>450</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="17" t="s">
-        <v>709</v>
+        <v>690</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>462</v>
@@ -36766,7 +33743,7 @@
         <v>547</v>
       </c>
       <c r="F62" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="H62" t="s">
         <v>432</v>
@@ -36781,7 +33758,7 @@
         <v>532</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="H63" t="s">
         <v>429</v>
@@ -36796,7 +33773,7 @@
         <v>528</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="H64" t="s">
         <v>434</v>
@@ -36876,7 +33853,7 @@
         <v>521</v>
       </c>
       <c r="F69" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H69" s="23" t="s">
         <v>513</v>
@@ -36913,7 +33890,7 @@
         <v>568</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H70" s="23" t="s">
         <v>516</v>
@@ -36950,7 +33927,7 @@
         <v>554</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H71" s="23" t="s">
         <v>558</v>
@@ -36987,7 +33964,7 @@
         <v>630</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H72" s="23" t="s">
         <v>556</v>
@@ -37024,7 +34001,7 @@
         <v>553</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H73" s="23" t="s">
         <v>514</v>
@@ -37033,7 +34010,7 @@
         <v>502</v>
       </c>
       <c r="K73" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="L73" s="19" t="s">
         <v>508</v>
@@ -37061,7 +34038,7 @@
         <v>592</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H74" s="23" t="s">
         <v>515</v>
@@ -37070,7 +34047,7 @@
         <v>600</v>
       </c>
       <c r="K74" s="12" t="s">
-        <v>714</v>
+        <v>695</v>
       </c>
       <c r="L74" s="19" t="s">
         <v>508</v>
@@ -37096,7 +34073,7 @@
     <row r="75" spans="4:19" x14ac:dyDescent="0.15">
       <c r="D75" s="20"/>
       <c r="F75" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H75" s="23" t="s">
         <v>557</v>
@@ -37130,10 +34107,10 @@
     </row>
     <row r="76" spans="4:19" x14ac:dyDescent="0.15">
       <c r="D76" s="22" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H76" s="23" t="s">
         <v>560</v>
@@ -37170,7 +34147,7 @@
         <v>552</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H77" s="23" t="s">
         <v>561</v>
@@ -37207,7 +34184,7 @@
         <v>615</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H78" s="23" t="s">
         <v>562</v>
@@ -37244,7 +34221,7 @@
         <v>555</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H79" s="23" t="s">
         <v>559</v>
@@ -37278,7 +34255,7 @@
     </row>
     <row r="80" spans="4:19" x14ac:dyDescent="0.15">
       <c r="H80" s="23" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>385</v>
@@ -37622,1033 +34599,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="E1:L80"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="7:12" s="12" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G2" t="s">
-        <v>541</v>
-      </c>
-      <c r="H2">
-        <v>25</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-    </row>
-    <row r="3" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G3" t="s">
-        <v>372</v>
-      </c>
-      <c r="H3">
-        <v>16</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-    </row>
-    <row r="4" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G4" t="s">
-        <v>545</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-    </row>
-    <row r="5" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G5" t="s">
-        <v>685</v>
-      </c>
-      <c r="H5">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G6" t="s">
-        <v>571</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-    </row>
-    <row r="7" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G7" t="s">
-        <v>475</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-    </row>
-    <row r="8" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G8" t="s">
-        <v>684</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-    </row>
-    <row r="9" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G9" t="s">
-        <v>375</v>
-      </c>
-      <c r="H9">
-        <v>7</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G10" t="s">
-        <v>601</v>
-      </c>
-      <c r="H10">
-        <v>7</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-    </row>
-    <row r="11" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G11" t="s">
-        <v>686</v>
-      </c>
-      <c r="H11">
-        <v>9</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-    </row>
-    <row r="12" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G12" t="s">
-        <v>687</v>
-      </c>
-      <c r="H12">
-        <v>6</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G13" t="s">
-        <v>363</v>
-      </c>
-      <c r="H13">
-        <v>5</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-    </row>
-    <row r="14" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G14" t="s">
-        <v>463</v>
-      </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-    </row>
-    <row r="15" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G15" t="s">
-        <v>379</v>
-      </c>
-      <c r="H15">
-        <v>5</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-    </row>
-    <row r="16" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G16" t="s">
-        <v>688</v>
-      </c>
-      <c r="H16">
-        <v>4</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-    </row>
-    <row r="17" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G17" t="s">
-        <v>689</v>
-      </c>
-      <c r="H17">
-        <v>4</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-    </row>
-    <row r="18" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G18" t="s">
-        <v>690</v>
-      </c>
-      <c r="H18">
-        <v>4</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-    </row>
-    <row r="19" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G19" t="s">
-        <v>691</v>
-      </c>
-      <c r="H19">
-        <v>4</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-    </row>
-    <row r="20" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G20" t="s">
-        <v>374</v>
-      </c>
-      <c r="H20">
-        <v>4</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-    </row>
-    <row r="21" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G21" t="s">
-        <v>692</v>
-      </c>
-      <c r="H21">
-        <v>3</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-    </row>
-    <row r="22" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G22" t="s">
-        <v>693</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-    </row>
-    <row r="23" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G23" t="s">
-        <v>694</v>
-      </c>
-      <c r="H23">
-        <v>3</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-    </row>
-    <row r="24" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G24" t="s">
-        <v>462</v>
-      </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-    </row>
-    <row r="25" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G25" t="s">
-        <v>502</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G26" t="s">
-        <v>695</v>
-      </c>
-      <c r="H26">
-        <v>3</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-    </row>
-    <row r="27" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G27" t="s">
-        <v>696</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-    </row>
-    <row r="28" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G28" t="s">
-        <v>697</v>
-      </c>
-      <c r="H28">
-        <v>3</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G29" t="s">
-        <v>698</v>
-      </c>
-      <c r="H29">
-        <v>3</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-    </row>
-    <row r="30" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G30" t="s">
-        <v>699</v>
-      </c>
-      <c r="H30">
-        <v>3</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-    </row>
-    <row r="31" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G31" t="s">
-        <v>485</v>
-      </c>
-      <c r="H31">
-        <v>3</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-    </row>
-    <row r="32" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G32" t="s">
-        <v>700</v>
-      </c>
-      <c r="H32">
-        <v>3</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-    </row>
-    <row r="33" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G33" t="s">
-        <v>387</v>
-      </c>
-      <c r="H33">
-        <v>3</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-    </row>
-    <row r="34" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G34" t="s">
-        <v>701</v>
-      </c>
-      <c r="H34">
-        <v>3</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-    </row>
-    <row r="35" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G35" t="s">
-        <v>525</v>
-      </c>
-      <c r="H35">
-        <v>2</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-    </row>
-    <row r="36" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G36" t="s">
-        <v>498</v>
-      </c>
-      <c r="H36">
-        <v>2</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-    </row>
-    <row r="37" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G37" t="s">
-        <v>497</v>
-      </c>
-      <c r="H37">
-        <v>2</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-    </row>
-    <row r="38" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G38" t="s">
-        <v>476</v>
-      </c>
-      <c r="H38">
-        <v>2</v>
-      </c>
-      <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-    </row>
-    <row r="39" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G39" t="s">
-        <v>492</v>
-      </c>
-      <c r="H39">
-        <v>2</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-    </row>
-    <row r="40" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G40" t="s">
-        <v>383</v>
-      </c>
-      <c r="H40">
-        <v>2</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-    </row>
-    <row r="41" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G41" t="s">
-        <v>520</v>
-      </c>
-      <c r="H41">
-        <v>2</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
-    </row>
-    <row r="42" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G42" t="s">
-        <v>478</v>
-      </c>
-      <c r="H42">
-        <v>2</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-    </row>
-    <row r="43" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G43" t="s">
-        <v>468</v>
-      </c>
-      <c r="H43">
-        <v>2</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-    </row>
-    <row r="44" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G44" t="s">
-        <v>388</v>
-      </c>
-      <c r="H44">
-        <v>2</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-    </row>
-    <row r="45" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G45" t="s">
-        <v>364</v>
-      </c>
-      <c r="H45">
-        <v>2</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-    </row>
-    <row r="46" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G46" t="s">
-        <v>385</v>
-      </c>
-      <c r="H46">
-        <v>2</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-    </row>
-    <row r="47" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G47" t="s">
-        <v>518</v>
-      </c>
-      <c r="H47">
-        <v>2</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="K47" s="12"/>
-      <c r="L47" s="12"/>
-    </row>
-    <row r="48" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G48" t="s">
-        <v>496</v>
-      </c>
-      <c r="H48">
-        <v>2</v>
-      </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-    </row>
-    <row r="49" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G49" t="s">
-        <v>378</v>
-      </c>
-      <c r="H49">
-        <v>2</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="K49" s="12"/>
-      <c r="L49" s="12"/>
-    </row>
-    <row r="50" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G50" t="s">
-        <v>384</v>
-      </c>
-      <c r="H50">
-        <v>2</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-    </row>
-    <row r="51" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G51" t="s">
-        <v>472</v>
-      </c>
-      <c r="H51">
-        <v>2</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-    </row>
-    <row r="52" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G52" t="s">
-        <v>524</v>
-      </c>
-      <c r="H52">
-        <v>2</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
-      </c>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-    </row>
-    <row r="53" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G53" t="s">
-        <v>380</v>
-      </c>
-      <c r="H53">
-        <v>2</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="K53" s="12"/>
-      <c r="L53" s="12"/>
-    </row>
-    <row r="54" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G54" t="s">
-        <v>491</v>
-      </c>
-      <c r="H54">
-        <v>2</v>
-      </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-    </row>
-    <row r="55" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G55" t="s">
-        <v>490</v>
-      </c>
-      <c r="H55">
-        <v>2</v>
-      </c>
-      <c r="I55">
-        <v>1</v>
-      </c>
-      <c r="K55" s="12"/>
-      <c r="L55" s="12"/>
-    </row>
-    <row r="56" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G56" t="s">
-        <v>484</v>
-      </c>
-      <c r="H56">
-        <v>2</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-    </row>
-    <row r="57" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="E57" s="12"/>
-      <c r="G57" t="s">
-        <v>575</v>
-      </c>
-      <c r="H57">
-        <v>2</v>
-      </c>
-      <c r="I57">
-        <v>1</v>
-      </c>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
-    </row>
-    <row r="58" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="E58" s="12"/>
-      <c r="G58" t="s">
-        <v>487</v>
-      </c>
-      <c r="H58">
-        <v>2</v>
-      </c>
-      <c r="I58">
-        <v>1</v>
-      </c>
-      <c r="K58" s="12"/>
-      <c r="L58" s="12"/>
-    </row>
-    <row r="59" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="E59" s="12"/>
-      <c r="G59" t="s">
-        <v>481</v>
-      </c>
-      <c r="H59">
-        <v>2</v>
-      </c>
-      <c r="I59">
-        <v>1</v>
-      </c>
-      <c r="K59" s="12"/>
-      <c r="L59" s="12"/>
-    </row>
-    <row r="60" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="E60" s="12"/>
-      <c r="G60" t="s">
-        <v>494</v>
-      </c>
-      <c r="H60">
-        <v>2</v>
-      </c>
-      <c r="I60">
-        <v>1</v>
-      </c>
-      <c r="L60" s="12"/>
-    </row>
-    <row r="61" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="E61" s="12"/>
-      <c r="G61" t="s">
-        <v>495</v>
-      </c>
-      <c r="H61">
-        <v>2</v>
-      </c>
-      <c r="I61">
-        <v>1</v>
-      </c>
-      <c r="L61" s="12"/>
-    </row>
-    <row r="62" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="E62" s="12"/>
-      <c r="G62" t="s">
-        <v>577</v>
-      </c>
-      <c r="H62">
-        <v>1</v>
-      </c>
-      <c r="I62">
-        <v>1</v>
-      </c>
-      <c r="L62" s="12"/>
-    </row>
-    <row r="63" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G63" t="s">
-        <v>464</v>
-      </c>
-      <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="L63" s="12"/>
-    </row>
-    <row r="64" spans="5:12" x14ac:dyDescent="0.15">
-      <c r="G64" t="s">
-        <v>527</v>
-      </c>
-      <c r="H64">
-        <v>1</v>
-      </c>
-      <c r="I64">
-        <v>1</v>
-      </c>
-      <c r="L64" s="12"/>
-    </row>
-    <row r="65" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G65" t="s">
-        <v>503</v>
-      </c>
-      <c r="H65">
-        <v>1</v>
-      </c>
-      <c r="I65">
-        <v>1</v>
-      </c>
-      <c r="L65" s="12"/>
-    </row>
-    <row r="66" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G66" t="s">
-        <v>529</v>
-      </c>
-      <c r="H66">
-        <v>1</v>
-      </c>
-      <c r="I66">
-        <v>1</v>
-      </c>
-      <c r="L66" s="12"/>
-    </row>
-    <row r="67" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G67" t="s">
-        <v>526</v>
-      </c>
-      <c r="H67">
-        <v>1</v>
-      </c>
-      <c r="I67">
-        <v>1</v>
-      </c>
-      <c r="L67" s="12"/>
-    </row>
-    <row r="68" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G68" t="s">
-        <v>531</v>
-      </c>
-      <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68">
-        <v>1</v>
-      </c>
-      <c r="L68" s="12"/>
-    </row>
-    <row r="69" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G69" t="s">
-        <v>530</v>
-      </c>
-      <c r="H69">
-        <v>1</v>
-      </c>
-      <c r="I69">
-        <v>1</v>
-      </c>
-      <c r="L69" s="12"/>
-    </row>
-    <row r="70" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G70" t="s">
-        <v>572</v>
-      </c>
-      <c r="H70">
-        <v>1</v>
-      </c>
-      <c r="I70">
-        <v>1</v>
-      </c>
-      <c r="L70" s="12"/>
-    </row>
-    <row r="71" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G71" t="s">
-        <v>483</v>
-      </c>
-      <c r="H71">
-        <v>1</v>
-      </c>
-      <c r="I71">
-        <v>1</v>
-      </c>
-      <c r="L71" s="12"/>
-    </row>
-    <row r="72" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G72" t="s">
-        <v>381</v>
-      </c>
-      <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
-      <c r="L72" s="12"/>
-    </row>
-    <row r="73" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G73" t="s">
-        <v>534</v>
-      </c>
-      <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="I73">
-        <v>1</v>
-      </c>
-      <c r="L73" s="12"/>
-    </row>
-    <row r="74" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G74" t="s">
-        <v>507</v>
-      </c>
-      <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="I74">
-        <v>1</v>
-      </c>
-      <c r="L74" s="12"/>
-    </row>
-    <row r="75" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G75" t="s">
-        <v>486</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75">
-        <v>1</v>
-      </c>
-      <c r="L75" s="12"/>
-    </row>
-    <row r="76" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G76" t="s">
-        <v>500</v>
-      </c>
-      <c r="H76">
-        <v>1</v>
-      </c>
-      <c r="I76">
-        <v>1</v>
-      </c>
-      <c r="L76" s="12"/>
-    </row>
-    <row r="77" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G77" t="s">
-        <v>376</v>
-      </c>
-      <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G78" t="s">
-        <v>509</v>
-      </c>
-      <c r="H78">
-        <v>1</v>
-      </c>
-      <c r="I78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G79" t="s">
-        <v>488</v>
-      </c>
-      <c r="H79">
-        <v>1</v>
-      </c>
-      <c r="I79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="7:12" x14ac:dyDescent="0.15">
-      <c r="G80" t="s">
-        <v>683</v>
-      </c>
-      <c r="H80">
-        <v>1</v>
-      </c>
-      <c r="I80">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="G1:I1">
-    <sortState ref="G2:I87">
-      <sortCondition descending="1" ref="H1"/>
-    </sortState>
-  </autoFilter>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E4:Z73"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -26559,7 +26559,7 @@
         <v>4</v>
       </c>
       <c r="E299" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F299" s="1">
         <v>0</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet3" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$AD$394</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$B$5:$S$54</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -2939,7 +2939,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3000,6 +3000,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3030,7 +3048,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3114,6 +3132,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3491,7 +3524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1" filterMode="1"/>
   <dimension ref="A2:AD394"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -3691,7 +3724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>119</v>
       </c>
@@ -3771,7 +3804,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>332</v>
       </c>
@@ -3851,7 +3884,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>333</v>
       </c>
@@ -3931,7 +3964,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>334</v>
       </c>
@@ -4011,7 +4044,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>335</v>
       </c>
@@ -4091,7 +4124,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>336</v>
       </c>
@@ -4171,7 +4204,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>631</v>
       </c>
@@ -4251,7 +4284,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>629</v>
       </c>
@@ -4331,7 +4364,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>632</v>
       </c>
@@ -4411,7 +4444,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>794</v>
       </c>
@@ -4494,7 +4527,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
@@ -4574,7 +4607,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>790</v>
       </c>
@@ -4651,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>791</v>
       </c>
@@ -4728,7 +4761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>792</v>
       </c>
@@ -4805,7 +4838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>793</v>
       </c>
@@ -4882,7 +4915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>787</v>
       </c>
@@ -4959,7 +4992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="27" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:30" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>123</v>
       </c>
@@ -5039,7 +5072,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
         <v>337</v>
       </c>
@@ -5119,7 +5152,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" s="12" t="s">
         <v>338</v>
       </c>
@@ -5199,7 +5232,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A23" s="12" t="s">
         <v>339</v>
       </c>
@@ -5279,7 +5312,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A24" s="12" t="s">
         <v>340</v>
       </c>
@@ -5359,7 +5392,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A25" s="12" t="s">
         <v>344</v>
       </c>
@@ -5439,7 +5472,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" s="12" t="s">
         <v>692</v>
       </c>
@@ -5517,7 +5550,7 @@
       </c>
       <c r="AD26" s="12"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A27" s="12" t="s">
         <v>460</v>
       </c>
@@ -5595,7 +5628,7 @@
       </c>
       <c r="AD27" s="12"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12" t="s">
         <v>461</v>
       </c>
@@ -5673,7 +5706,7 @@
       </c>
       <c r="AD28" s="12"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A29" s="12" t="s">
         <v>361</v>
       </c>
@@ -5751,7 +5784,7 @@
       </c>
       <c r="AD29" s="12"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" s="12" t="s">
         <v>367</v>
       </c>
@@ -5829,7 +5862,7 @@
       </c>
       <c r="AD30" s="12"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" s="12" t="s">
         <v>462</v>
       </c>
@@ -5907,7 +5940,7 @@
       </c>
       <c r="AD31" s="12"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" s="12" t="s">
         <v>463</v>
       </c>
@@ -5985,7 +6018,7 @@
       </c>
       <c r="AD32" s="12"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" s="12" t="s">
         <v>464</v>
       </c>
@@ -6063,7 +6096,7 @@
       </c>
       <c r="AD33" s="12"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" s="12" t="s">
         <v>465</v>
       </c>
@@ -6141,7 +6174,7 @@
       </c>
       <c r="AD34" s="12"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" s="12" t="s">
         <v>385</v>
       </c>
@@ -6219,7 +6252,7 @@
       </c>
       <c r="AD35" s="12"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" s="12" t="s">
         <v>466</v>
       </c>
@@ -6297,7 +6330,7 @@
       </c>
       <c r="AD36" s="12"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" s="12" t="s">
         <v>467</v>
       </c>
@@ -6375,7 +6408,7 @@
       </c>
       <c r="AD37" s="12"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A38" s="12" t="s">
         <v>372</v>
       </c>
@@ -6453,7 +6486,7 @@
       </c>
       <c r="AD38" s="12"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" s="12" t="s">
         <v>681</v>
       </c>
@@ -6531,7 +6564,7 @@
       </c>
       <c r="AD39" s="12"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" s="12" t="s">
         <v>682</v>
       </c>
@@ -6609,7 +6642,7 @@
       </c>
       <c r="AD40" s="12"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" s="12" t="s">
         <v>470</v>
       </c>
@@ -6687,7 +6720,7 @@
       </c>
       <c r="AD41" s="12"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" s="12" t="s">
         <v>471</v>
       </c>
@@ -6765,7 +6798,7 @@
       </c>
       <c r="AD42" s="12"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" s="12" t="s">
         <v>472</v>
       </c>
@@ -6843,7 +6876,7 @@
       </c>
       <c r="AD43" s="12"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" s="12" t="s">
         <v>375</v>
       </c>
@@ -6921,7 +6954,7 @@
       </c>
       <c r="AD44" s="12"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" s="12" t="s">
         <v>473</v>
       </c>
@@ -6999,7 +7032,7 @@
       </c>
       <c r="AD45" s="12"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" s="12" t="s">
         <v>474</v>
       </c>
@@ -7077,7 +7110,7 @@
       </c>
       <c r="AD46" s="12"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" s="12" t="s">
         <v>363</v>
       </c>
@@ -7155,7 +7188,7 @@
       </c>
       <c r="AD47" s="12"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" s="12" t="s">
         <v>384</v>
       </c>
@@ -7233,7 +7266,7 @@
       </c>
       <c r="AD48" s="12"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" s="12" t="s">
         <v>475</v>
       </c>
@@ -7311,7 +7344,7 @@
       </c>
       <c r="AD49" s="12"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" s="12" t="s">
         <v>476</v>
       </c>
@@ -7389,7 +7422,7 @@
       </c>
       <c r="AD50" s="12"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A51" s="12" t="s">
         <v>377</v>
       </c>
@@ -7467,7 +7500,7 @@
       </c>
       <c r="AD51" s="12"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" s="12" t="s">
         <v>376</v>
       </c>
@@ -7545,7 +7578,7 @@
       </c>
       <c r="AD52" s="12"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A53" s="12" t="s">
         <v>477</v>
       </c>
@@ -7623,7 +7656,7 @@
       </c>
       <c r="AD53" s="12"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" s="12" t="s">
         <v>478</v>
       </c>
@@ -7701,7 +7734,7 @@
       </c>
       <c r="AD54" s="12"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" s="12" t="s">
         <v>479</v>
       </c>
@@ -7779,7 +7812,7 @@
       </c>
       <c r="AD55" s="12"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" s="12" t="s">
         <v>480</v>
       </c>
@@ -7857,7 +7890,7 @@
       </c>
       <c r="AD56" s="12"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" s="12" t="s">
         <v>743</v>
       </c>
@@ -7935,7 +7968,7 @@
       </c>
       <c r="AD57" s="12"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" s="12" t="s">
         <v>482</v>
       </c>
@@ -8013,7 +8046,7 @@
       </c>
       <c r="AD58" s="12"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" s="12" t="s">
         <v>483</v>
       </c>
@@ -8091,7 +8124,7 @@
       </c>
       <c r="AD59" s="12"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A60" s="12" t="s">
         <v>365</v>
       </c>
@@ -8169,7 +8202,7 @@
       </c>
       <c r="AD60" s="12"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" s="12" t="s">
         <v>382</v>
       </c>
@@ -8247,7 +8280,7 @@
       </c>
       <c r="AD61" s="12"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" s="12" t="s">
         <v>484</v>
       </c>
@@ -8325,7 +8358,7 @@
       </c>
       <c r="AD62" s="12"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" s="12" t="s">
         <v>378</v>
       </c>
@@ -8403,7 +8436,7 @@
       </c>
       <c r="AD63" s="12"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" s="12" t="s">
         <v>504</v>
       </c>
@@ -8481,7 +8514,7 @@
       </c>
       <c r="AD64" s="12"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" s="12" t="s">
         <v>503</v>
       </c>
@@ -8559,7 +8592,7 @@
       </c>
       <c r="AD65" s="12"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" s="12" t="s">
         <v>485</v>
       </c>
@@ -8637,7 +8670,7 @@
       </c>
       <c r="AD66" s="12"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" s="12" t="s">
         <v>486</v>
       </c>
@@ -8715,7 +8748,7 @@
       </c>
       <c r="AD67" s="12"/>
     </row>
-    <row r="68" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:30" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="12" t="s">
         <v>386</v>
       </c>
@@ -8793,7 +8826,7 @@
       </c>
       <c r="AD68" s="12"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" s="12" t="s">
         <v>387</v>
       </c>
@@ -8871,7 +8904,7 @@
       </c>
       <c r="AD69" s="12"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" s="12" t="s">
         <v>487</v>
       </c>
@@ -8949,7 +8982,7 @@
       </c>
       <c r="AD70" s="12"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" s="12" t="s">
         <v>488</v>
       </c>
@@ -9027,7 +9060,7 @@
       </c>
       <c r="AD71" s="12"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" s="12" t="s">
         <v>489</v>
       </c>
@@ -9105,7 +9138,7 @@
       </c>
       <c r="AD72" s="12"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" s="12" t="s">
         <v>490</v>
       </c>
@@ -9183,7 +9216,7 @@
       </c>
       <c r="AD73" s="12"/>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" s="12" t="s">
         <v>379</v>
       </c>
@@ -9261,7 +9294,7 @@
       </c>
       <c r="AD74" s="12"/>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" s="12" t="s">
         <v>491</v>
       </c>
@@ -9339,7 +9372,7 @@
       </c>
       <c r="AD75" s="12"/>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" s="12" t="s">
         <v>492</v>
       </c>
@@ -9417,7 +9450,7 @@
       </c>
       <c r="AD76" s="12"/>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" s="12" t="s">
         <v>493</v>
       </c>
@@ -9495,7 +9528,7 @@
       </c>
       <c r="AD77" s="12"/>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" s="12" t="s">
         <v>494</v>
       </c>
@@ -9573,7 +9606,7 @@
       </c>
       <c r="AD78" s="12"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" s="12" t="s">
         <v>495</v>
       </c>
@@ -9651,7 +9684,7 @@
       </c>
       <c r="AD79" s="12"/>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" s="12" t="s">
         <v>381</v>
       </c>
@@ -9729,7 +9762,7 @@
       </c>
       <c r="AD80" s="12"/>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" s="12" t="s">
         <v>496</v>
       </c>
@@ -9807,7 +9840,7 @@
       </c>
       <c r="AD81" s="12"/>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" s="12" t="s">
         <v>497</v>
       </c>
@@ -9885,7 +9918,7 @@
       </c>
       <c r="AD82" s="12"/>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A83" s="12" t="s">
         <v>383</v>
       </c>
@@ -9963,7 +9996,7 @@
       </c>
       <c r="AD83" s="12"/>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A84" s="12" t="s">
         <v>498</v>
       </c>
@@ -10041,7 +10074,7 @@
       </c>
       <c r="AD84" s="12"/>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A85" s="12" t="s">
         <v>499</v>
       </c>
@@ -10119,7 +10152,7 @@
       </c>
       <c r="AD85" s="12"/>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A86" s="12" t="s">
         <v>500</v>
       </c>
@@ -10197,7 +10230,7 @@
       </c>
       <c r="AD86" s="12"/>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" s="12" t="s">
         <v>501</v>
       </c>
@@ -10275,7 +10308,7 @@
       </c>
       <c r="AD87" s="12"/>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" s="12" t="s">
         <v>502</v>
       </c>
@@ -10353,7 +10386,7 @@
       </c>
       <c r="AD88" s="12"/>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A89" s="12" t="s">
         <v>528</v>
       </c>
@@ -10431,7 +10464,7 @@
       </c>
       <c r="AD89" s="12"/>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A90" s="12" t="s">
         <v>525</v>
       </c>
@@ -10509,7 +10542,7 @@
       </c>
       <c r="AD90" s="12"/>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" s="12" t="s">
         <v>457</v>
       </c>
@@ -10587,7 +10620,7 @@
       </c>
       <c r="AD91" s="12"/>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" s="12" t="s">
         <v>572</v>
       </c>
@@ -10665,7 +10698,7 @@
       </c>
       <c r="AD92" s="12"/>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" s="12" t="s">
         <v>533</v>
       </c>
@@ -10743,7 +10776,7 @@
       </c>
       <c r="AD93" s="12"/>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" s="12" t="s">
         <v>371</v>
       </c>
@@ -10821,7 +10854,7 @@
       </c>
       <c r="AD94" s="12"/>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" s="12" t="s">
         <v>517</v>
       </c>
@@ -10899,7 +10932,7 @@
       </c>
       <c r="AD95" s="12"/>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A96" s="12" t="s">
         <v>374</v>
       </c>
@@ -10977,7 +11010,7 @@
       </c>
       <c r="AD96" s="12"/>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" s="12" t="s">
         <v>598</v>
       </c>
@@ -11055,7 +11088,7 @@
       </c>
       <c r="AD97" s="12"/>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" s="12" t="s">
         <v>543</v>
       </c>
@@ -11133,7 +11166,7 @@
       </c>
       <c r="AD98" s="12"/>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A99" s="12" t="s">
         <v>519</v>
       </c>
@@ -11211,7 +11244,7 @@
       </c>
       <c r="AD99" s="12"/>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A100" s="12" t="s">
         <v>506</v>
       </c>
@@ -11289,7 +11322,7 @@
       </c>
       <c r="AD100" s="12"/>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A101" s="12" t="s">
         <v>523</v>
       </c>
@@ -11367,7 +11400,7 @@
       </c>
       <c r="AD101" s="12"/>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A102" s="12" t="s">
         <v>571</v>
       </c>
@@ -11445,7 +11478,7 @@
       </c>
       <c r="AD102" s="12"/>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A103" s="12" t="s">
         <v>373</v>
       </c>
@@ -11523,7 +11556,7 @@
       </c>
       <c r="AD103" s="12"/>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A104" s="12" t="s">
         <v>524</v>
       </c>
@@ -11601,7 +11634,7 @@
       </c>
       <c r="AD104" s="12"/>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" s="12" t="s">
         <v>576</v>
       </c>
@@ -11679,7 +11712,7 @@
       </c>
       <c r="AD105" s="12"/>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A106" s="12" t="s">
         <v>574</v>
       </c>
@@ -11757,7 +11790,7 @@
       </c>
       <c r="AD106" s="12"/>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A107" s="12" t="s">
         <v>570</v>
       </c>
@@ -11835,7 +11868,7 @@
       </c>
       <c r="AD107" s="12"/>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A108" s="12" t="s">
         <v>530</v>
       </c>
@@ -11913,7 +11946,7 @@
       </c>
       <c r="AD108" s="12"/>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" s="12" t="s">
         <v>526</v>
       </c>
@@ -11991,7 +12024,7 @@
       </c>
       <c r="AD109" s="12"/>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" s="12" t="s">
         <v>573</v>
       </c>
@@ -12069,7 +12102,7 @@
       </c>
       <c r="AD110" s="12"/>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" s="12" t="s">
         <v>508</v>
       </c>
@@ -12147,7 +12180,7 @@
       </c>
       <c r="AD111" s="12"/>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A112" s="12" t="s">
         <v>575</v>
       </c>
@@ -12225,7 +12258,7 @@
       </c>
       <c r="AD112" s="12"/>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A113" s="12" t="s">
         <v>529</v>
       </c>
@@ -12303,7 +12336,7 @@
       </c>
       <c r="AD113" s="12"/>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" s="12" t="s">
         <v>532</v>
       </c>
@@ -12381,7 +12414,7 @@
       </c>
       <c r="AD114" s="12"/>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" s="12" t="s">
         <v>687</v>
       </c>
@@ -12459,7 +12492,7 @@
       </c>
       <c r="AD115" s="12"/>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" s="12" t="s">
         <v>639</v>
       </c>
@@ -12537,7 +12570,7 @@
       </c>
       <c r="AD116" s="12"/>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" s="12" t="s">
         <v>569</v>
       </c>
@@ -12615,7 +12648,7 @@
       </c>
       <c r="AD117" s="12"/>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A118" s="16" t="s">
         <v>539</v>
       </c>
@@ -12693,7 +12726,7 @@
       </c>
       <c r="AD118" s="12"/>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" s="16" t="s">
         <v>369</v>
       </c>
@@ -12771,7 +12804,7 @@
       </c>
       <c r="AD119" s="12"/>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" s="16" t="s">
         <v>733</v>
       </c>
@@ -12849,7 +12882,7 @@
       </c>
       <c r="AD120" s="12"/>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" s="16" t="s">
         <v>735</v>
       </c>
@@ -12927,7 +12960,7 @@
       </c>
       <c r="AD121" s="12"/>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A122" s="16" t="s">
         <v>782</v>
       </c>
@@ -13005,7 +13038,7 @@
       </c>
       <c r="AD122" s="12"/>
     </row>
-    <row r="123" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:30" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
         <v>38</v>
       </c>
@@ -13088,7 +13121,7 @@
       </c>
       <c r="AD123" s="5"/>
     </row>
-    <row r="124" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:30" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5" t="s">
         <v>39</v>
       </c>
@@ -13171,7 +13204,7 @@
       </c>
       <c r="AD124" s="5"/>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5" t="s">
         <v>164</v>
       </c>
@@ -13250,7 +13283,7 @@
       </c>
       <c r="AD125" s="5"/>
     </row>
-    <row r="126" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5" t="s">
         <v>40</v>
       </c>
@@ -13329,7 +13362,7 @@
       </c>
       <c r="AD126" s="5"/>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5" t="s">
         <v>41</v>
       </c>
@@ -13408,7 +13441,7 @@
       </c>
       <c r="AD127" s="5"/>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5" t="s">
         <v>42</v>
       </c>
@@ -13487,7 +13520,7 @@
       </c>
       <c r="AD128" s="5"/>
     </row>
-    <row r="129" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A129" s="5" t="s">
         <v>43</v>
       </c>
@@ -13566,7 +13599,7 @@
       </c>
       <c r="AD129" s="5"/>
     </row>
-    <row r="130" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A130" s="5" t="s">
         <v>44</v>
       </c>
@@ -13645,7 +13678,7 @@
       </c>
       <c r="AD130" s="5"/>
     </row>
-    <row r="131" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A131" s="5" t="s">
         <v>23</v>
       </c>
@@ -13724,7 +13757,7 @@
       </c>
       <c r="AD131" s="5"/>
     </row>
-    <row r="132" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A132" s="5" t="s">
         <v>45</v>
       </c>
@@ -13803,7 +13836,7 @@
       </c>
       <c r="AD132" s="5"/>
     </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5" t="s">
         <v>46</v>
       </c>
@@ -13882,7 +13915,7 @@
       </c>
       <c r="AD133" s="5"/>
     </row>
-    <row r="134" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A134" s="5" t="s">
         <v>47</v>
       </c>
@@ -13961,7 +13994,7 @@
       </c>
       <c r="AD134" s="5"/>
     </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A135" s="5" t="s">
         <v>58</v>
       </c>
@@ -14040,7 +14073,7 @@
       </c>
       <c r="AD135" s="5"/>
     </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A136" s="5" t="s">
         <v>59</v>
       </c>
@@ -14119,7 +14152,7 @@
       </c>
       <c r="AD136" s="5"/>
     </row>
-    <row r="137" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A137" s="5" t="s">
         <v>49</v>
       </c>
@@ -14198,7 +14231,7 @@
       </c>
       <c r="AD137" s="5"/>
     </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A138" s="5" t="s">
         <v>25</v>
       </c>
@@ -14277,7 +14310,7 @@
       </c>
       <c r="AD138" s="5"/>
     </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A139" s="5" t="s">
         <v>50</v>
       </c>
@@ -14356,7 +14389,7 @@
       </c>
       <c r="AD139" s="5"/>
     </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A140" s="5" t="s">
         <v>22</v>
       </c>
@@ -14434,7 +14467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" s="5" t="s">
         <v>48</v>
       </c>
@@ -14512,7 +14545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A142" s="5" t="s">
         <v>262</v>
       </c>
@@ -14590,7 +14623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A143" s="5" t="s">
         <v>55</v>
       </c>
@@ -14668,7 +14701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A144" s="5" t="s">
         <v>24</v>
       </c>
@@ -14746,7 +14779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A145" s="5" t="s">
         <v>56</v>
       </c>
@@ -14824,7 +14857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A146" s="5" t="s">
         <v>57</v>
       </c>
@@ -14902,7 +14935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A147" s="5" t="s">
         <v>51</v>
       </c>
@@ -14980,7 +15013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A148" s="5" t="s">
         <v>52</v>
       </c>
@@ -15058,7 +15091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A149" s="5" t="s">
         <v>53</v>
       </c>
@@ -15136,7 +15169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A150" s="5" t="s">
         <v>54</v>
       </c>
@@ -15214,7 +15247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A151" s="5" t="s">
         <v>60</v>
       </c>
@@ -15292,7 +15325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A152" s="9" t="s">
         <v>61</v>
       </c>
@@ -15370,7 +15403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A153" s="5" t="s">
         <v>163</v>
       </c>
@@ -15448,7 +15481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" s="9" t="s">
         <v>62</v>
       </c>
@@ -15526,7 +15559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A155" s="5" t="s">
         <v>63</v>
       </c>
@@ -15604,7 +15637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A156" s="9" t="s">
         <v>64</v>
       </c>
@@ -15682,7 +15715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A157" s="9" t="s">
         <v>65</v>
       </c>
@@ -15760,7 +15793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A158" s="9" t="s">
         <v>66</v>
       </c>
@@ -15838,7 +15871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A159" s="9" t="s">
         <v>67</v>
       </c>
@@ -15916,7 +15949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A160" s="9" t="s">
         <v>68</v>
       </c>
@@ -15994,7 +16027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A161" s="9" t="s">
         <v>69</v>
       </c>
@@ -16072,7 +16105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A162" s="5" t="s">
         <v>70</v>
       </c>
@@ -16150,7 +16183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A163" s="9" t="s">
         <v>71</v>
       </c>
@@ -16228,7 +16261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A164" s="5" t="s">
         <v>72</v>
       </c>
@@ -16306,7 +16339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A165" s="9" t="s">
         <v>73</v>
       </c>
@@ -16384,7 +16417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A166" s="9" t="s">
         <v>74</v>
       </c>
@@ -16462,7 +16495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A167" s="5" t="s">
         <v>75</v>
       </c>
@@ -16540,7 +16573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A168" s="9" t="s">
         <v>76</v>
       </c>
@@ -16618,7 +16651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A169" s="9" t="s">
         <v>77</v>
       </c>
@@ -16696,7 +16729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A170" s="9" t="s">
         <v>78</v>
       </c>
@@ -16774,7 +16807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A171" s="5" t="s">
         <v>79</v>
       </c>
@@ -16852,7 +16885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A172" s="9" t="s">
         <v>80</v>
       </c>
@@ -16930,7 +16963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A173" s="5" t="s">
         <v>81</v>
       </c>
@@ -17008,7 +17041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A174" s="5" t="s">
         <v>82</v>
       </c>
@@ -17086,7 +17119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A175" s="9" t="s">
         <v>83</v>
       </c>
@@ -17164,7 +17197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A176" s="9" t="s">
         <v>84</v>
       </c>
@@ -17242,7 +17275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A177" s="9" t="s">
         <v>85</v>
       </c>
@@ -17320,7 +17353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A178" s="9" t="s">
         <v>86</v>
       </c>
@@ -17405,7 +17438,7 @@
       <c r="B179" s="3">
         <v>1600</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="C179" s="29" t="s">
         <v>345</v>
       </c>
       <c r="D179" s="1">
@@ -17489,7 +17522,7 @@
         <v>1</v>
       </c>
       <c r="E180" s="1">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="F180" s="1">
         <v>1</v>
@@ -17559,14 +17592,14 @@
       <c r="B181" s="3">
         <v>1602</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="C181" s="31" t="s">
         <v>406</v>
       </c>
       <c r="D181" s="1">
         <v>1</v>
       </c>
       <c r="E181" s="1">
-        <v>0</v>
+        <v>1191</v>
       </c>
       <c r="F181" s="1">
         <v>1</v>
@@ -17578,7 +17611,7 @@
         <v>0</v>
       </c>
       <c r="I181" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J181" s="1">
         <v>0</v>
@@ -17636,14 +17669,14 @@
       <c r="B182" s="3">
         <v>1603</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="C182" s="32" t="s">
         <v>347</v>
       </c>
       <c r="D182" s="1">
         <v>1</v>
       </c>
       <c r="E182" s="1">
-        <v>0</v>
+        <v>1282</v>
       </c>
       <c r="F182" s="1">
         <v>1</v>
@@ -17655,7 +17688,7 @@
         <v>0</v>
       </c>
       <c r="I182" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J182" s="1">
         <v>0</v>
@@ -17713,7 +17746,7 @@
       <c r="B183" s="3">
         <v>1604</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="C183" s="30" t="s">
         <v>407</v>
       </c>
       <c r="D183" s="1">
@@ -17732,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="I183" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J183" s="1">
         <v>0</v>
@@ -17874,7 +17907,7 @@
         <v>1</v>
       </c>
       <c r="E185" s="1">
-        <v>0</v>
+        <v>1555</v>
       </c>
       <c r="F185" s="1">
         <v>2</v>
@@ -17944,14 +17977,14 @@
       <c r="B186" s="3">
         <v>1607</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="C186" s="32" t="s">
         <v>419</v>
       </c>
       <c r="D186" s="1">
         <v>1</v>
       </c>
       <c r="E186" s="1">
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="F186" s="1">
         <v>2</v>
@@ -17963,7 +17996,7 @@
         <v>0</v>
       </c>
       <c r="I186" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J186" s="1">
         <v>0</v>
@@ -18021,14 +18054,14 @@
       <c r="B187" s="3">
         <v>1608</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="C187" s="33" t="s">
         <v>350</v>
       </c>
       <c r="D187" s="1">
         <v>1</v>
       </c>
       <c r="E187" s="1">
-        <v>0</v>
+        <v>1646</v>
       </c>
       <c r="F187" s="1">
         <v>2</v>
@@ -18040,7 +18073,7 @@
         <v>0</v>
       </c>
       <c r="I187" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187" s="1">
         <v>0</v>
@@ -18175,14 +18208,14 @@
       <c r="B189" s="3">
         <v>1610</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="C189" s="33" t="s">
         <v>352</v>
       </c>
       <c r="D189" s="1">
         <v>1</v>
       </c>
       <c r="E189" s="1">
-        <v>0</v>
+        <v>1919</v>
       </c>
       <c r="F189" s="1">
         <v>3</v>
@@ -18194,7 +18227,7 @@
         <v>0</v>
       </c>
       <c r="I189" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" s="1">
         <v>0</v>
@@ -18252,14 +18285,14 @@
       <c r="B190" s="3">
         <v>1611</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="C190" s="32" t="s">
         <v>353</v>
       </c>
       <c r="D190" s="1">
         <v>1</v>
       </c>
       <c r="E190" s="1">
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="F190" s="1">
         <v>3</v>
@@ -18271,7 +18304,7 @@
         <v>0</v>
       </c>
       <c r="I190" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J190" s="1">
         <v>0</v>
@@ -18483,14 +18516,14 @@
       <c r="B193" s="3">
         <v>1614</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="C193" s="14" t="s">
         <v>408</v>
       </c>
       <c r="D193" s="1">
         <v>1</v>
       </c>
       <c r="E193" s="1">
-        <v>0</v>
+        <v>2192</v>
       </c>
       <c r="F193" s="1">
         <v>6</v>
@@ -18502,7 +18535,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J193" s="1">
         <v>0</v>
@@ -18560,14 +18593,14 @@
       <c r="B194" s="3">
         <v>1615</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="C194" s="31" t="s">
         <v>356</v>
       </c>
       <c r="D194" s="1">
         <v>1</v>
       </c>
       <c r="E194" s="1">
-        <v>0</v>
+        <v>2283</v>
       </c>
       <c r="F194" s="1">
         <v>6</v>
@@ -18579,7 +18612,7 @@
         <v>0</v>
       </c>
       <c r="I194" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J194" s="1">
         <v>0</v>
@@ -18637,14 +18670,14 @@
       <c r="B195" s="3">
         <v>1616</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="C195" s="30" t="s">
         <v>357</v>
       </c>
       <c r="D195" s="1">
         <v>1</v>
       </c>
       <c r="E195" s="1">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="F195" s="1">
         <v>3</v>
@@ -18656,7 +18689,7 @@
         <v>0</v>
       </c>
       <c r="I195" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J195" s="1">
         <v>0</v>
@@ -18721,7 +18754,7 @@
         <v>1</v>
       </c>
       <c r="E196" s="1">
-        <v>0</v>
+        <v>1373</v>
       </c>
       <c r="F196" s="1">
         <v>1</v>
@@ -18791,14 +18824,14 @@
       <c r="B197" s="3">
         <v>1618</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="C197" s="14" t="s">
         <v>634</v>
       </c>
       <c r="D197" s="1">
         <v>1</v>
       </c>
       <c r="E197" s="1">
-        <v>0</v>
+        <v>1828</v>
       </c>
       <c r="F197" s="1">
         <v>2</v>
@@ -18810,7 +18843,7 @@
         <v>0</v>
       </c>
       <c r="I197" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J197" s="1">
         <v>0</v>
@@ -18868,14 +18901,14 @@
       <c r="B198" s="3">
         <v>1619</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="C198" s="14" t="s">
         <v>635</v>
       </c>
       <c r="D198" s="1">
         <v>1</v>
       </c>
       <c r="E198" s="1">
-        <v>0</v>
+        <v>2374</v>
       </c>
       <c r="F198" s="1">
         <v>6</v>
@@ -18887,7 +18920,7 @@
         <v>0</v>
       </c>
       <c r="I198" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J198" s="1">
         <v>0</v>
@@ -18945,14 +18978,14 @@
       <c r="B199" s="3">
         <v>1620</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="C199" s="30" t="s">
         <v>636</v>
       </c>
       <c r="D199" s="1">
         <v>1</v>
       </c>
       <c r="E199" s="1">
-        <v>0</v>
+        <v>2465</v>
       </c>
       <c r="F199" s="1">
         <v>6</v>
@@ -18964,7 +18997,7 @@
         <v>0</v>
       </c>
       <c r="I199" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J199" s="1">
         <v>0</v>
@@ -21864,7 +21897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A237" s="1" t="s">
         <v>27</v>
       </c>
@@ -21944,7 +21977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="238" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A238" s="1" t="s">
         <v>28</v>
       </c>
@@ -22024,7 +22057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="239" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A239" s="1" t="s">
         <v>342</v>
       </c>
@@ -22104,7 +22137,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A240" s="1" t="s">
         <v>29</v>
       </c>
@@ -22184,7 +22217,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="241" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A241" s="1" t="s">
         <v>167</v>
       </c>
@@ -22264,7 +22297,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="242" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A242" s="1" t="s">
         <v>696</v>
       </c>
@@ -22344,7 +22377,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="243" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A243" s="1" t="s">
         <v>87</v>
       </c>
@@ -22424,7 +22457,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="244" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A244" s="1" t="s">
         <v>105</v>
       </c>
@@ -22504,7 +22537,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="245" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A245" s="1" t="s">
         <v>699</v>
       </c>
@@ -22584,7 +22617,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="246" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A246" s="1" t="s">
         <v>88</v>
       </c>
@@ -22664,7 +22697,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="247" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A247" s="1" t="s">
         <v>89</v>
       </c>
@@ -22744,7 +22777,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="248" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A248" s="1" t="s">
         <v>90</v>
       </c>
@@ -22824,7 +22857,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="249" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A249" s="1" t="s">
         <v>91</v>
       </c>
@@ -22904,7 +22937,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="250" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A250" s="1" t="s">
         <v>95</v>
       </c>
@@ -22984,7 +23017,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="251" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A251" s="1" t="s">
         <v>96</v>
       </c>
@@ -23064,7 +23097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="252" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A252" s="1" t="s">
         <v>97</v>
       </c>
@@ -23144,7 +23177,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="253" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A253" s="1" t="s">
         <v>94</v>
       </c>
@@ -23224,7 +23257,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="254" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A254" s="1" t="s">
         <v>102</v>
       </c>
@@ -23304,7 +23337,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="255" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:30" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="1" t="s">
         <v>92</v>
       </c>
@@ -23384,7 +23417,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="256" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
         <v>701</v>
       </c>
@@ -23464,7 +23497,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="257" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
         <v>93</v>
       </c>
@@ -23544,7 +23577,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="258" spans="1:30" ht="15" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:30" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="10" t="s">
         <v>203</v>
       </c>
@@ -23624,7 +23657,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="259" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A259" s="7" t="s">
         <v>130</v>
       </c>
@@ -23704,7 +23737,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="260" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A260" s="7" t="s">
         <v>129</v>
       </c>
@@ -23784,7 +23817,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="261" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A261" s="7" t="s">
         <v>131</v>
       </c>
@@ -23864,7 +23897,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="262" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A262" s="7" t="s">
         <v>165</v>
       </c>
@@ -23944,7 +23977,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="263" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A263" s="8" t="s">
         <v>133</v>
       </c>
@@ -24024,7 +24057,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="264" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A264" s="7" t="s">
         <v>134</v>
       </c>
@@ -24104,7 +24137,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="265" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A265" s="8" t="s">
         <v>135</v>
       </c>
@@ -24184,7 +24217,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="266" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A266" s="7" t="s">
         <v>136</v>
       </c>
@@ -24264,7 +24297,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="267" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A267" s="7" t="s">
         <v>137</v>
       </c>
@@ -24344,7 +24377,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="268" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A268" s="7" t="s">
         <v>138</v>
       </c>
@@ -24424,7 +24457,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="269" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A269" s="7" t="s">
         <v>139</v>
       </c>
@@ -24504,7 +24537,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="270" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A270" s="7" t="s">
         <v>140</v>
       </c>
@@ -24584,7 +24617,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="271" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A271" s="7" t="s">
         <v>141</v>
       </c>
@@ -24664,7 +24697,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="272" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A272" s="7" t="s">
         <v>142</v>
       </c>
@@ -24744,7 +24777,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="273" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A273" s="7" t="s">
         <v>143</v>
       </c>
@@ -24824,7 +24857,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="274" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A274" s="8" t="s">
         <v>144</v>
       </c>
@@ -24904,7 +24937,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="275" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A275" s="7" t="s">
         <v>145</v>
       </c>
@@ -24984,7 +25017,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="276" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A276" s="7" t="s">
         <v>146</v>
       </c>
@@ -25064,7 +25097,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="277" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A277" s="7" t="s">
         <v>147</v>
       </c>
@@ -25144,7 +25177,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="278" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A278" s="7" t="s">
         <v>148</v>
       </c>
@@ -25224,7 +25257,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="279" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A279" s="8" t="s">
         <v>149</v>
       </c>
@@ -25304,7 +25337,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="280" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A280" s="8" t="s">
         <v>150</v>
       </c>
@@ -25384,7 +25417,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="281" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A281" s="8" t="s">
         <v>151</v>
       </c>
@@ -25464,7 +25497,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="282" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A282" s="8" t="s">
         <v>204</v>
       </c>
@@ -25544,7 +25577,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="283" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A283" s="8" t="s">
         <v>153</v>
       </c>
@@ -25624,7 +25657,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="284" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A284" s="8" t="s">
         <v>265</v>
       </c>
@@ -25704,7 +25737,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="285" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A285" s="8" t="s">
         <v>202</v>
       </c>
@@ -25784,7 +25817,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="286" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A286" s="8" t="s">
         <v>156</v>
       </c>
@@ -25864,7 +25897,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="287" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A287" s="8" t="s">
         <v>157</v>
       </c>
@@ -25944,7 +25977,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="288" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A288" s="8" t="s">
         <v>158</v>
       </c>
@@ -26024,7 +26057,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="289" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A289" s="8" t="s">
         <v>159</v>
       </c>
@@ -26104,7 +26137,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="290" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A290" s="8" t="s">
         <v>160</v>
       </c>
@@ -26184,7 +26217,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="291" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A291" s="8" t="s">
         <v>161</v>
       </c>
@@ -26264,7 +26297,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="292" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A292" s="8" t="s">
         <v>162</v>
       </c>
@@ -26344,7 +26377,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="293" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A293" s="11" t="s">
         <v>199</v>
       </c>
@@ -26421,7 +26454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A294" s="11" t="s">
         <v>200</v>
       </c>
@@ -26498,7 +26531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A295" s="11" t="s">
         <v>683</v>
       </c>
@@ -26575,7 +26608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A296" s="11" t="s">
         <v>458</v>
       </c>
@@ -26652,7 +26685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A297" s="12" t="s">
         <v>459</v>
       </c>
@@ -26729,7 +26762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A298" s="12" t="s">
         <v>174</v>
       </c>
@@ -26806,7 +26839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A299" s="12" t="s">
         <v>171</v>
       </c>
@@ -26883,7 +26916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A300" s="12" t="s">
         <v>173</v>
       </c>
@@ -26960,7 +26993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A301" s="1" t="s">
         <v>186</v>
       </c>
@@ -27037,7 +27070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A302" s="1" t="s">
         <v>190</v>
       </c>
@@ -27114,7 +27147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A303" s="1" t="s">
         <v>267</v>
       </c>
@@ -27191,7 +27224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:30" hidden="1" x14ac:dyDescent="0.15">
       <c r="A304" s="13" t="s">
         <v>261</v>
       </c>
@@ -27268,7 +27301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A305" s="13" t="s">
         <v>268</v>
       </c>
@@ -27345,7 +27378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A306" s="13" t="s">
         <v>269</v>
       </c>
@@ -27422,7 +27455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A307" s="13" t="s">
         <v>196</v>
       </c>
@@ -27499,7 +27532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A308" s="13" t="s">
         <v>178</v>
       </c>
@@ -27576,7 +27609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A309" s="13" t="s">
         <v>194</v>
       </c>
@@ -27653,7 +27686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A310" s="13" t="s">
         <v>206</v>
       </c>
@@ -27730,7 +27763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A311" s="13" t="s">
         <v>207</v>
       </c>
@@ -27807,7 +27840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A312" s="13" t="s">
         <v>177</v>
       </c>
@@ -27884,7 +27917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A313" s="13" t="s">
         <v>179</v>
       </c>
@@ -27961,7 +27994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A314" s="13" t="s">
         <v>208</v>
       </c>
@@ -28038,7 +28071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A315" s="13" t="s">
         <v>176</v>
       </c>
@@ -28115,7 +28148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A316" s="13" t="s">
         <v>209</v>
       </c>
@@ -28192,7 +28225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A317" s="13" t="s">
         <v>263</v>
       </c>
@@ -28269,7 +28302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A318" s="13" t="s">
         <v>210</v>
       </c>
@@ -28346,7 +28379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A319" s="13" t="s">
         <v>183</v>
       </c>
@@ -28423,7 +28456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A320" s="13" t="s">
         <v>211</v>
       </c>
@@ -28500,7 +28533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A321" s="13" t="s">
         <v>212</v>
       </c>
@@ -28577,7 +28610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A322" s="13" t="s">
         <v>182</v>
       </c>
@@ -28654,7 +28687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A323" s="13" t="s">
         <v>213</v>
       </c>
@@ -28731,7 +28764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A324" s="13" t="s">
         <v>184</v>
       </c>
@@ -28808,7 +28841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A325" s="13" t="s">
         <v>214</v>
       </c>
@@ -28885,7 +28918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A326" s="13" t="s">
         <v>197</v>
       </c>
@@ -28962,7 +28995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A327" s="13" t="s">
         <v>180</v>
       </c>
@@ -29039,7 +29072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A328" s="13" t="s">
         <v>187</v>
       </c>
@@ -29116,7 +29149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A329" s="13" t="s">
         <v>189</v>
       </c>
@@ -29193,7 +29226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A330" s="13" t="s">
         <v>191</v>
       </c>
@@ -29270,7 +29303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A331" s="13" t="s">
         <v>192</v>
       </c>
@@ -29347,7 +29380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A332" s="13" t="s">
         <v>215</v>
       </c>
@@ -29424,7 +29457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A333" s="13" t="s">
         <v>216</v>
       </c>
@@ -29501,7 +29534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A334" s="13" t="s">
         <v>193</v>
       </c>
@@ -29578,7 +29611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A335" s="13" t="s">
         <v>218</v>
       </c>
@@ -29655,7 +29688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A336" s="13" t="s">
         <v>219</v>
       </c>
@@ -29732,7 +29765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A337" s="13" t="s">
         <v>195</v>
       </c>
@@ -29809,7 +29842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A338" s="13" t="s">
         <v>220</v>
       </c>
@@ -29886,7 +29919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A339" s="13" t="s">
         <v>221</v>
       </c>
@@ -29963,7 +29996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A340" s="13" t="s">
         <v>222</v>
       </c>
@@ -30040,7 +30073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A341" s="13" t="s">
         <v>181</v>
       </c>
@@ -30117,7 +30150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A342" s="13" t="s">
         <v>223</v>
       </c>
@@ -30194,7 +30227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A343" s="13" t="s">
         <v>224</v>
       </c>
@@ -30271,7 +30304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A344" s="13" t="s">
         <v>225</v>
       </c>
@@ -30348,7 +30381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A345" s="13" t="s">
         <v>226</v>
       </c>
@@ -30425,7 +30458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A346" s="13" t="s">
         <v>227</v>
       </c>
@@ -30502,7 +30535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A347" s="13" t="s">
         <v>188</v>
       </c>
@@ -30579,7 +30612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A348" s="13" t="s">
         <v>198</v>
       </c>
@@ -30656,7 +30689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A349" s="13" t="s">
         <v>185</v>
       </c>
@@ -30733,7 +30766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A350" s="13" t="s">
         <v>228</v>
       </c>
@@ -30810,7 +30843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A351" s="13" t="s">
         <v>229</v>
       </c>
@@ -30887,7 +30920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A352" s="13" t="s">
         <v>230</v>
       </c>
@@ -30964,7 +30997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A353" s="13" t="s">
         <v>231</v>
       </c>
@@ -31041,7 +31074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A354" s="13" t="s">
         <v>301</v>
       </c>
@@ -31118,7 +31151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A355" s="13" t="s">
         <v>232</v>
       </c>
@@ -31195,7 +31228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A356" s="13" t="s">
         <v>233</v>
       </c>
@@ -31272,7 +31305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A357" s="13" t="s">
         <v>234</v>
       </c>
@@ -31349,7 +31382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A358" s="13" t="s">
         <v>235</v>
       </c>
@@ -31426,7 +31459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A359" s="13" t="s">
         <v>236</v>
       </c>
@@ -31503,7 +31536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A360" s="13" t="s">
         <v>237</v>
       </c>
@@ -31580,7 +31613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A361" s="13" t="s">
         <v>238</v>
       </c>
@@ -31657,7 +31690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A362" s="13" t="s">
         <v>239</v>
       </c>
@@ -31734,7 +31767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A363" s="13" t="s">
         <v>240</v>
       </c>
@@ -31811,7 +31844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A364" s="13" t="s">
         <v>241</v>
       </c>
@@ -31888,7 +31921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A365" s="13" t="s">
         <v>242</v>
       </c>
@@ -31965,7 +31998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A366" s="13" t="s">
         <v>243</v>
       </c>
@@ -32042,7 +32075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A367" s="13" t="s">
         <v>244</v>
       </c>
@@ -32119,7 +32152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A368" s="13" t="s">
         <v>245</v>
       </c>
@@ -32196,7 +32229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A369" s="13" t="s">
         <v>246</v>
       </c>
@@ -32273,7 +32306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A370" s="13" t="s">
         <v>247</v>
       </c>
@@ -32350,7 +32383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A371" s="13" t="s">
         <v>248</v>
       </c>
@@ -32427,7 +32460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A372" s="13" t="s">
         <v>249</v>
       </c>
@@ -32504,7 +32537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A373" s="13" t="s">
         <v>250</v>
       </c>
@@ -32581,7 +32614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A374" s="13" t="s">
         <v>251</v>
       </c>
@@ -32658,7 +32691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A375" s="13" t="s">
         <v>252</v>
       </c>
@@ -32735,7 +32768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A376" s="13" t="s">
         <v>323</v>
       </c>
@@ -32812,7 +32845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A377" s="13" t="s">
         <v>322</v>
       </c>
@@ -32889,7 +32922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A378" s="13" t="s">
         <v>324</v>
       </c>
@@ -32966,7 +32999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A379" s="13" t="s">
         <v>256</v>
       </c>
@@ -33043,7 +33076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A380" s="13" t="s">
         <v>326</v>
       </c>
@@ -33120,7 +33153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A381" s="13" t="s">
         <v>258</v>
       </c>
@@ -33197,7 +33230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A382" s="13" t="s">
         <v>328</v>
       </c>
@@ -33274,7 +33307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A383" s="13" t="s">
         <v>329</v>
       </c>
@@ -33351,7 +33384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A384" s="12" t="s">
         <v>640</v>
       </c>
@@ -33428,7 +33461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A385" s="12" t="s">
         <v>641</v>
       </c>
@@ -33505,7 +33538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A386" s="12" t="s">
         <v>642</v>
       </c>
@@ -33582,7 +33615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A387" s="12" t="s">
         <v>643</v>
       </c>
@@ -33659,7 +33692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A388" s="12" t="s">
         <v>644</v>
       </c>
@@ -33736,7 +33769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A389" s="12" t="s">
         <v>645</v>
       </c>
@@ -33813,7 +33846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A390" s="12" t="s">
         <v>646</v>
       </c>
@@ -33890,7 +33923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A391" s="12" t="s">
         <v>647</v>
       </c>
@@ -33967,7 +34000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A392" s="12" t="s">
         <v>648</v>
       </c>
@@ -34044,7 +34077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A393" s="12" t="s">
         <v>649</v>
       </c>
@@ -34121,7 +34154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.15">
       <c r="A394" s="12" t="s">
         <v>650</v>
       </c>
@@ -34199,10 +34232,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C3">
-    <sortState ref="A4:K127">
-      <sortCondition ref="B3:B127"/>
-    </sortState>
+  <autoFilter ref="A3:AD394">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="1"/>
+        <filter val="2"/>
+        <filter val="7"/>
+        <filter val="8"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A66:A1048576 A1:A64">

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -3064,7 +3064,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3163,6 +3163,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19140,7 +19143,7 @@
         <v>0</v>
       </c>
       <c r="Z200" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA200" s="1">
         <v>0</v>
@@ -19217,7 +19220,7 @@
         <v>0</v>
       </c>
       <c r="Z201" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA201" s="1">
         <v>0</v>
@@ -19294,13 +19297,13 @@
         <v>0</v>
       </c>
       <c r="Z202" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA202" s="1">
         <v>0</v>
       </c>
       <c r="AB202" s="1">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AC202" s="1">
         <v>0</v>
@@ -19371,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="Z203" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA203" s="1">
         <v>0</v>
@@ -19448,13 +19451,13 @@
         <v>0</v>
       </c>
       <c r="Z204" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA204" s="1">
         <v>0</v>
       </c>
       <c r="AB204" s="1">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AC204" s="1">
         <v>0</v>
@@ -19522,16 +19525,16 @@
         <v>0</v>
       </c>
       <c r="Y205" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z205" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA205" s="1">
         <v>0</v>
       </c>
       <c r="AB205" s="1">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AC205" s="1">
         <v>0</v>
@@ -19602,13 +19605,13 @@
         <v>0</v>
       </c>
       <c r="Z206" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA206" s="1">
         <v>0</v>
       </c>
       <c r="AB206" s="1">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AC206" s="1">
         <v>0</v>
@@ -19679,13 +19682,13 @@
         <v>0</v>
       </c>
       <c r="Z207" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA207" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB207" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC207" s="1">
         <v>0</v>
@@ -19756,13 +19759,13 @@
         <v>0</v>
       </c>
       <c r="Z208" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA208" s="1">
         <v>0</v>
       </c>
       <c r="AB208" s="1">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AC208" s="1">
         <v>0</v>
@@ -19824,7 +19827,7 @@
         <v>0</v>
       </c>
       <c r="W209" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X209" s="1">
         <v>0</v>
@@ -19833,13 +19836,13 @@
         <v>0</v>
       </c>
       <c r="Z209" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA209" s="1">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AB209" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC209" s="1">
         <v>0</v>
@@ -19910,13 +19913,13 @@
         <v>0</v>
       </c>
       <c r="Z210" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA210" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB210" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC210" s="1">
         <v>0</v>
@@ -19978,7 +19981,7 @@
         <v>0</v>
       </c>
       <c r="W211" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X211" s="1">
         <v>0</v>
@@ -19987,13 +19990,13 @@
         <v>0</v>
       </c>
       <c r="Z211" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA211" s="1">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AB211" s="1">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AC211" s="1">
         <v>0</v>
@@ -20061,16 +20064,16 @@
         <v>0</v>
       </c>
       <c r="Y212" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z212" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA212" s="1">
         <v>0</v>
       </c>
       <c r="AB212" s="1">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AC212" s="1">
         <v>0</v>
@@ -20132,7 +20135,7 @@
         <v>0</v>
       </c>
       <c r="W213" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X213" s="1">
         <v>0</v>
@@ -20141,13 +20144,13 @@
         <v>0</v>
       </c>
       <c r="Z213" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA213" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB213" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC213" s="1">
         <v>0</v>
@@ -20209,7 +20212,7 @@
         <v>0</v>
       </c>
       <c r="W214" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="X214" s="1">
         <v>0</v>
@@ -20218,13 +20221,13 @@
         <v>0</v>
       </c>
       <c r="Z214" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA214" s="1">
         <v>0</v>
       </c>
       <c r="AB214" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC214" s="1">
         <v>0</v>
@@ -20286,7 +20289,7 @@
         <v>0</v>
       </c>
       <c r="W215" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X215" s="1">
         <v>0</v>
@@ -20295,10 +20298,10 @@
         <v>0</v>
       </c>
       <c r="Z215" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA215" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB215" s="1">
         <v>0</v>
@@ -20372,10 +20375,10 @@
         <v>0</v>
       </c>
       <c r="Z216" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA216" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB216" s="1">
         <v>0</v>
@@ -20384,850 +20387,894 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A217" s="1" t="s">
+    <row r="217" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A217" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="B217" s="3">
+      <c r="B217" s="24">
         <v>1700</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="C217" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="D217" s="1">
+      <c r="D217" s="9">
         <v>7</v>
       </c>
-      <c r="E217" s="1">
-        <v>0</v>
-      </c>
-      <c r="F217" s="1">
-        <v>0</v>
-      </c>
-      <c r="G217" s="1">
-        <v>0</v>
-      </c>
-      <c r="H217" s="1">
-        <v>0</v>
-      </c>
-      <c r="I217" s="1">
-        <v>0</v>
-      </c>
-      <c r="J217" s="1">
-        <v>0</v>
-      </c>
-      <c r="K217" s="3">
-        <v>1</v>
-      </c>
-      <c r="L217" s="1">
-        <v>1</v>
-      </c>
-      <c r="M217" s="1">
-        <v>100</v>
-      </c>
-      <c r="N217" s="1">
-        <v>100</v>
-      </c>
-      <c r="S217" s="1">
-        <v>0</v>
-      </c>
-      <c r="T217" s="1">
-        <v>0</v>
-      </c>
-      <c r="U217" s="1">
-        <v>0</v>
-      </c>
-      <c r="V217" s="1">
-        <v>0</v>
-      </c>
-      <c r="W217" s="1">
-        <v>0</v>
-      </c>
-      <c r="X217" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y217" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z217" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA217" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB217" s="1">
+      <c r="E217" s="9">
+        <v>0</v>
+      </c>
+      <c r="F217" s="9">
+        <v>0</v>
+      </c>
+      <c r="G217" s="9">
+        <v>0</v>
+      </c>
+      <c r="H217" s="9">
+        <v>0</v>
+      </c>
+      <c r="I217" s="9">
+        <v>0</v>
+      </c>
+      <c r="J217" s="9">
+        <v>0</v>
+      </c>
+      <c r="K217" s="24">
+        <v>1</v>
+      </c>
+      <c r="L217" s="9">
+        <v>1</v>
+      </c>
+      <c r="M217" s="9">
+        <v>100</v>
+      </c>
+      <c r="N217" s="9">
+        <v>100</v>
+      </c>
+      <c r="O217" s="34"/>
+      <c r="P217" s="34"/>
+      <c r="Q217" s="34"/>
+      <c r="R217" s="34"/>
+      <c r="S217" s="9">
+        <v>0</v>
+      </c>
+      <c r="T217" s="9">
+        <v>0</v>
+      </c>
+      <c r="U217" s="9">
+        <v>0</v>
+      </c>
+      <c r="V217" s="9">
+        <v>0</v>
+      </c>
+      <c r="W217" s="9">
+        <v>0</v>
+      </c>
+      <c r="X217" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y217" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA217" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB217" s="9">
+        <v>20</v>
+      </c>
+      <c r="AC217" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A218" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="B218" s="24">
+        <v>1701</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="D218" s="9">
+        <v>7</v>
+      </c>
+      <c r="E218" s="9">
+        <v>0</v>
+      </c>
+      <c r="F218" s="9">
+        <v>0</v>
+      </c>
+      <c r="G218" s="9">
+        <v>0</v>
+      </c>
+      <c r="H218" s="9">
+        <v>0</v>
+      </c>
+      <c r="I218" s="9">
+        <v>0</v>
+      </c>
+      <c r="J218" s="9">
+        <v>0</v>
+      </c>
+      <c r="K218" s="24">
+        <v>1</v>
+      </c>
+      <c r="L218" s="9">
+        <v>1</v>
+      </c>
+      <c r="M218" s="9">
+        <v>100</v>
+      </c>
+      <c r="N218" s="9">
+        <v>100</v>
+      </c>
+      <c r="O218" s="34"/>
+      <c r="P218" s="34"/>
+      <c r="Q218" s="34"/>
+      <c r="R218" s="34"/>
+      <c r="S218" s="9">
+        <v>0</v>
+      </c>
+      <c r="T218" s="9">
+        <v>0</v>
+      </c>
+      <c r="U218" s="9">
+        <v>0</v>
+      </c>
+      <c r="V218" s="9">
+        <v>0</v>
+      </c>
+      <c r="W218" s="9">
+        <v>0</v>
+      </c>
+      <c r="X218" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y218" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z218" s="9">
+        <v>10</v>
+      </c>
+      <c r="AA218" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB218" s="9">
+        <v>10</v>
+      </c>
+      <c r="AC218" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A219" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="B219" s="24">
+        <v>1702</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="D219" s="9">
+        <v>7</v>
+      </c>
+      <c r="E219" s="9">
+        <v>0</v>
+      </c>
+      <c r="F219" s="9">
+        <v>0</v>
+      </c>
+      <c r="G219" s="9">
+        <v>0</v>
+      </c>
+      <c r="H219" s="9">
+        <v>0</v>
+      </c>
+      <c r="I219" s="9">
+        <v>0</v>
+      </c>
+      <c r="J219" s="9">
+        <v>0</v>
+      </c>
+      <c r="K219" s="24">
+        <v>1</v>
+      </c>
+      <c r="L219" s="9">
+        <v>1</v>
+      </c>
+      <c r="M219" s="9">
+        <v>100</v>
+      </c>
+      <c r="N219" s="9">
+        <v>100</v>
+      </c>
+      <c r="O219" s="34"/>
+      <c r="P219" s="34"/>
+      <c r="Q219" s="34"/>
+      <c r="R219" s="34"/>
+      <c r="S219" s="9">
+        <v>0</v>
+      </c>
+      <c r="T219" s="9">
+        <v>0</v>
+      </c>
+      <c r="U219" s="9">
+        <v>0</v>
+      </c>
+      <c r="V219" s="9">
+        <v>0</v>
+      </c>
+      <c r="W219" s="9">
+        <v>0</v>
+      </c>
+      <c r="X219" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y219" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z219" s="9">
+        <v>15</v>
+      </c>
+      <c r="AA219" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB219" s="9">
+        <v>20</v>
+      </c>
+      <c r="AC219" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A220" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B220" s="24">
+        <v>1703</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D220" s="9">
+        <v>7</v>
+      </c>
+      <c r="E220" s="9">
+        <v>0</v>
+      </c>
+      <c r="F220" s="9">
+        <v>0</v>
+      </c>
+      <c r="G220" s="9">
+        <v>0</v>
+      </c>
+      <c r="H220" s="9">
+        <v>0</v>
+      </c>
+      <c r="I220" s="9">
+        <v>0</v>
+      </c>
+      <c r="J220" s="9">
+        <v>0</v>
+      </c>
+      <c r="K220" s="24">
+        <v>1</v>
+      </c>
+      <c r="L220" s="9">
+        <v>1</v>
+      </c>
+      <c r="M220" s="9">
+        <v>100</v>
+      </c>
+      <c r="N220" s="9">
+        <v>100</v>
+      </c>
+      <c r="O220" s="34"/>
+      <c r="P220" s="34"/>
+      <c r="Q220" s="34"/>
+      <c r="R220" s="34"/>
+      <c r="S220" s="9">
+        <v>0</v>
+      </c>
+      <c r="T220" s="9">
+        <v>0</v>
+      </c>
+      <c r="U220" s="9">
+        <v>0</v>
+      </c>
+      <c r="V220" s="9">
+        <v>0</v>
+      </c>
+      <c r="W220" s="9">
+        <v>0</v>
+      </c>
+      <c r="X220" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y220" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z220" s="9">
+        <v>5</v>
+      </c>
+      <c r="AA220" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB220" s="9">
+        <v>30</v>
+      </c>
+      <c r="AC220" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A221" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="B221" s="24">
+        <v>1704</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="D221" s="9">
+        <v>7</v>
+      </c>
+      <c r="E221" s="9">
+        <v>0</v>
+      </c>
+      <c r="F221" s="9">
+        <v>0</v>
+      </c>
+      <c r="G221" s="9">
+        <v>0</v>
+      </c>
+      <c r="H221" s="9">
+        <v>0</v>
+      </c>
+      <c r="I221" s="9">
+        <v>0</v>
+      </c>
+      <c r="J221" s="9">
+        <v>0</v>
+      </c>
+      <c r="K221" s="24">
+        <v>1</v>
+      </c>
+      <c r="L221" s="9">
+        <v>1</v>
+      </c>
+      <c r="M221" s="9">
+        <v>100</v>
+      </c>
+      <c r="N221" s="9">
+        <v>100</v>
+      </c>
+      <c r="O221" s="34"/>
+      <c r="P221" s="34"/>
+      <c r="Q221" s="34"/>
+      <c r="R221" s="34"/>
+      <c r="S221" s="9">
+        <v>0</v>
+      </c>
+      <c r="T221" s="9">
+        <v>0</v>
+      </c>
+      <c r="U221" s="9">
+        <v>0</v>
+      </c>
+      <c r="V221" s="9">
+        <v>0</v>
+      </c>
+      <c r="W221" s="9">
+        <v>0</v>
+      </c>
+      <c r="X221" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y221" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z221" s="9">
+        <v>10</v>
+      </c>
+      <c r="AA221" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB221" s="9">
         <v>50</v>
       </c>
-      <c r="AC217" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A218" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="B218" s="3">
-        <v>1701</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D218" s="1">
+      <c r="AC221" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A222" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B222" s="24">
+        <v>1705</v>
+      </c>
+      <c r="C222" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="D222" s="9">
         <v>7</v>
       </c>
-      <c r="E218" s="1">
-        <v>0</v>
-      </c>
-      <c r="F218" s="1">
-        <v>0</v>
-      </c>
-      <c r="G218" s="1">
-        <v>0</v>
-      </c>
-      <c r="H218" s="1">
-        <v>0</v>
-      </c>
-      <c r="I218" s="1">
-        <v>0</v>
-      </c>
-      <c r="J218" s="1">
-        <v>0</v>
-      </c>
-      <c r="K218" s="3">
-        <v>1</v>
-      </c>
-      <c r="L218" s="1">
-        <v>1</v>
-      </c>
-      <c r="M218" s="1">
-        <v>100</v>
-      </c>
-      <c r="N218" s="1">
-        <v>100</v>
-      </c>
-      <c r="S218" s="1">
-        <v>0</v>
-      </c>
-      <c r="T218" s="1">
-        <v>0</v>
-      </c>
-      <c r="U218" s="1">
-        <v>0</v>
-      </c>
-      <c r="V218" s="1">
-        <v>0</v>
-      </c>
-      <c r="W218" s="1">
-        <v>0</v>
-      </c>
-      <c r="X218" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y218" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z218" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA218" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB218" s="1">
-        <v>100</v>
-      </c>
-      <c r="AC218" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A219" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B219" s="3">
-        <v>1702</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="D219" s="1">
+      <c r="E222" s="9">
+        <v>0</v>
+      </c>
+      <c r="F222" s="9">
+        <v>0</v>
+      </c>
+      <c r="G222" s="9">
+        <v>0</v>
+      </c>
+      <c r="H222" s="9">
+        <v>0</v>
+      </c>
+      <c r="I222" s="9">
+        <v>0</v>
+      </c>
+      <c r="J222" s="9">
+        <v>0</v>
+      </c>
+      <c r="K222" s="24">
+        <v>1</v>
+      </c>
+      <c r="L222" s="9">
+        <v>1</v>
+      </c>
+      <c r="M222" s="9">
+        <v>100</v>
+      </c>
+      <c r="N222" s="9">
+        <v>100</v>
+      </c>
+      <c r="O222" s="34"/>
+      <c r="P222" s="34"/>
+      <c r="Q222" s="34"/>
+      <c r="R222" s="34"/>
+      <c r="S222" s="9">
+        <v>0</v>
+      </c>
+      <c r="T222" s="9">
+        <v>0</v>
+      </c>
+      <c r="U222" s="9">
+        <v>0</v>
+      </c>
+      <c r="V222" s="9">
+        <v>0</v>
+      </c>
+      <c r="W222" s="9">
+        <v>0</v>
+      </c>
+      <c r="X222" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y222" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z222" s="9">
+        <v>20</v>
+      </c>
+      <c r="AA222" s="9">
+        <v>10</v>
+      </c>
+      <c r="AB222" s="9">
+        <v>30</v>
+      </c>
+      <c r="AC222" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A223" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="B223" s="24">
+        <v>1706</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="D223" s="9">
         <v>7</v>
       </c>
-      <c r="E219" s="1">
-        <v>0</v>
-      </c>
-      <c r="F219" s="1">
-        <v>0</v>
-      </c>
-      <c r="G219" s="1">
-        <v>0</v>
-      </c>
-      <c r="H219" s="1">
-        <v>0</v>
-      </c>
-      <c r="I219" s="1">
-        <v>0</v>
-      </c>
-      <c r="J219" s="1">
-        <v>0</v>
-      </c>
-      <c r="K219" s="3">
-        <v>1</v>
-      </c>
-      <c r="L219" s="1">
-        <v>1</v>
-      </c>
-      <c r="M219" s="1">
-        <v>100</v>
-      </c>
-      <c r="N219" s="1">
-        <v>100</v>
-      </c>
-      <c r="S219" s="1">
-        <v>0</v>
-      </c>
-      <c r="T219" s="1">
-        <v>0</v>
-      </c>
-      <c r="U219" s="1">
-        <v>0</v>
-      </c>
-      <c r="V219" s="1">
-        <v>0</v>
-      </c>
-      <c r="W219" s="1">
-        <v>0</v>
-      </c>
-      <c r="X219" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y219" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z219" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA219" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB219" s="1">
+      <c r="E223" s="9">
+        <v>0</v>
+      </c>
+      <c r="F223" s="9">
+        <v>0</v>
+      </c>
+      <c r="G223" s="9">
+        <v>0</v>
+      </c>
+      <c r="H223" s="9">
+        <v>0</v>
+      </c>
+      <c r="I223" s="9">
+        <v>0</v>
+      </c>
+      <c r="J223" s="9">
+        <v>0</v>
+      </c>
+      <c r="K223" s="24">
+        <v>1</v>
+      </c>
+      <c r="L223" s="9">
+        <v>1</v>
+      </c>
+      <c r="M223" s="9">
+        <v>100</v>
+      </c>
+      <c r="N223" s="9">
+        <v>100</v>
+      </c>
+      <c r="O223" s="34"/>
+      <c r="P223" s="34"/>
+      <c r="Q223" s="34"/>
+      <c r="R223" s="34"/>
+      <c r="S223" s="9">
+        <v>0</v>
+      </c>
+      <c r="T223" s="9">
+        <v>0</v>
+      </c>
+      <c r="U223" s="9">
+        <v>0</v>
+      </c>
+      <c r="V223" s="9">
+        <v>0</v>
+      </c>
+      <c r="W223" s="9">
+        <v>0</v>
+      </c>
+      <c r="X223" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y223" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA223" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB223" s="9">
+        <v>100</v>
+      </c>
+      <c r="AC223" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:29" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A224" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="B224" s="24">
+        <v>1707</v>
+      </c>
+      <c r="C224" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="D224" s="9">
+        <v>7</v>
+      </c>
+      <c r="E224" s="9">
+        <v>0</v>
+      </c>
+      <c r="F224" s="9">
+        <v>0</v>
+      </c>
+      <c r="G224" s="9">
+        <v>0</v>
+      </c>
+      <c r="H224" s="9">
+        <v>0</v>
+      </c>
+      <c r="I224" s="9">
+        <v>0</v>
+      </c>
+      <c r="J224" s="9">
+        <v>0</v>
+      </c>
+      <c r="K224" s="24">
+        <v>1</v>
+      </c>
+      <c r="L224" s="9">
+        <v>1</v>
+      </c>
+      <c r="M224" s="9">
+        <v>100</v>
+      </c>
+      <c r="N224" s="9">
+        <v>100</v>
+      </c>
+      <c r="O224" s="34"/>
+      <c r="P224" s="34"/>
+      <c r="Q224" s="34"/>
+      <c r="R224" s="34"/>
+      <c r="S224" s="9">
+        <v>0</v>
+      </c>
+      <c r="T224" s="9">
+        <v>0</v>
+      </c>
+      <c r="U224" s="9">
+        <v>0</v>
+      </c>
+      <c r="V224" s="9">
+        <v>0</v>
+      </c>
+      <c r="W224" s="9">
+        <v>0</v>
+      </c>
+      <c r="X224" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y224" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z224" s="9">
+        <v>30</v>
+      </c>
+      <c r="AA224" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB224" s="9">
+        <v>80</v>
+      </c>
+      <c r="AC224" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:30" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A225" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B225" s="24">
+        <v>1708</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="D225" s="9">
+        <v>7</v>
+      </c>
+      <c r="E225" s="9">
+        <v>0</v>
+      </c>
+      <c r="F225" s="9">
+        <v>0</v>
+      </c>
+      <c r="G225" s="9">
+        <v>0</v>
+      </c>
+      <c r="H225" s="9">
+        <v>0</v>
+      </c>
+      <c r="I225" s="9">
+        <v>0</v>
+      </c>
+      <c r="J225" s="9">
+        <v>0</v>
+      </c>
+      <c r="K225" s="24">
+        <v>1</v>
+      </c>
+      <c r="L225" s="9">
+        <v>1</v>
+      </c>
+      <c r="M225" s="9">
+        <v>100</v>
+      </c>
+      <c r="N225" s="9">
+        <v>100</v>
+      </c>
+      <c r="O225" s="34"/>
+      <c r="P225" s="34"/>
+      <c r="Q225" s="34"/>
+      <c r="R225" s="34"/>
+      <c r="S225" s="9">
+        <v>0</v>
+      </c>
+      <c r="T225" s="9">
+        <v>0</v>
+      </c>
+      <c r="U225" s="9">
+        <v>0</v>
+      </c>
+      <c r="V225" s="9">
+        <v>0</v>
+      </c>
+      <c r="W225" s="9">
+        <v>0</v>
+      </c>
+      <c r="X225" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y225" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z225" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA225" s="9">
+        <v>20</v>
+      </c>
+      <c r="AB225" s="9">
+        <v>150</v>
+      </c>
+      <c r="AC225" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:30" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A226" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B226" s="24">
+        <v>1709</v>
+      </c>
+      <c r="C226" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D226" s="9">
+        <v>7</v>
+      </c>
+      <c r="E226" s="9">
+        <v>0</v>
+      </c>
+      <c r="F226" s="9">
+        <v>0</v>
+      </c>
+      <c r="G226" s="9">
+        <v>0</v>
+      </c>
+      <c r="H226" s="9">
+        <v>0</v>
+      </c>
+      <c r="I226" s="9">
+        <v>0</v>
+      </c>
+      <c r="J226" s="9">
+        <v>0</v>
+      </c>
+      <c r="K226" s="24">
+        <v>1</v>
+      </c>
+      <c r="L226" s="9">
+        <v>1</v>
+      </c>
+      <c r="M226" s="9">
+        <v>100</v>
+      </c>
+      <c r="N226" s="9">
+        <v>100</v>
+      </c>
+      <c r="O226" s="34"/>
+      <c r="P226" s="34"/>
+      <c r="Q226" s="34"/>
+      <c r="R226" s="34"/>
+      <c r="S226" s="9">
+        <v>0</v>
+      </c>
+      <c r="T226" s="9">
+        <v>0</v>
+      </c>
+      <c r="U226" s="9">
+        <v>0</v>
+      </c>
+      <c r="V226" s="9">
+        <v>0</v>
+      </c>
+      <c r="W226" s="9">
+        <v>0</v>
+      </c>
+      <c r="X226" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y226" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z226" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA226" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB226" s="9">
         <v>200</v>
       </c>
-      <c r="AC219" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A220" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B220" s="3">
-        <v>1703</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="D220" s="1">
+      <c r="AC226" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:30" s="9" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A227" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="B227" s="24">
+        <v>1710</v>
+      </c>
+      <c r="C227" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="D227" s="9">
         <v>7</v>
       </c>
-      <c r="E220" s="1">
-        <v>0</v>
-      </c>
-      <c r="F220" s="1">
-        <v>0</v>
-      </c>
-      <c r="G220" s="1">
-        <v>0</v>
-      </c>
-      <c r="H220" s="1">
-        <v>0</v>
-      </c>
-      <c r="I220" s="1">
-        <v>0</v>
-      </c>
-      <c r="J220" s="1">
-        <v>0</v>
-      </c>
-      <c r="K220" s="3">
-        <v>1</v>
-      </c>
-      <c r="L220" s="1">
-        <v>1</v>
-      </c>
-      <c r="M220" s="1">
-        <v>100</v>
-      </c>
-      <c r="N220" s="1">
-        <v>100</v>
-      </c>
-      <c r="S220" s="1">
-        <v>0</v>
-      </c>
-      <c r="T220" s="1">
-        <v>0</v>
-      </c>
-      <c r="U220" s="1">
-        <v>0</v>
-      </c>
-      <c r="V220" s="1">
-        <v>0</v>
-      </c>
-      <c r="W220" s="1">
-        <v>0</v>
-      </c>
-      <c r="X220" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y220" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z220" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA220" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB220" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC220" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A221" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="B221" s="3">
-        <v>1704</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D221" s="1">
-        <v>7</v>
-      </c>
-      <c r="E221" s="1">
-        <v>0</v>
-      </c>
-      <c r="F221" s="1">
-        <v>0</v>
-      </c>
-      <c r="G221" s="1">
-        <v>0</v>
-      </c>
-      <c r="H221" s="1">
-        <v>0</v>
-      </c>
-      <c r="I221" s="1">
-        <v>0</v>
-      </c>
-      <c r="J221" s="1">
-        <v>0</v>
-      </c>
-      <c r="K221" s="3">
-        <v>1</v>
-      </c>
-      <c r="L221" s="1">
-        <v>1</v>
-      </c>
-      <c r="M221" s="1">
-        <v>100</v>
-      </c>
-      <c r="N221" s="1">
-        <v>100</v>
-      </c>
-      <c r="S221" s="1">
-        <v>0</v>
-      </c>
-      <c r="T221" s="1">
-        <v>0</v>
-      </c>
-      <c r="U221" s="1">
-        <v>0</v>
-      </c>
-      <c r="V221" s="1">
-        <v>0</v>
-      </c>
-      <c r="W221" s="1">
-        <v>0</v>
-      </c>
-      <c r="X221" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y221" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z221" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA221" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB221" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC221" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A222" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="B222" s="3">
-        <v>1705</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="D222" s="1">
-        <v>7</v>
-      </c>
-      <c r="E222" s="1">
-        <v>0</v>
-      </c>
-      <c r="F222" s="1">
-        <v>0</v>
-      </c>
-      <c r="G222" s="1">
-        <v>0</v>
-      </c>
-      <c r="H222" s="1">
-        <v>0</v>
-      </c>
-      <c r="I222" s="1">
-        <v>0</v>
-      </c>
-      <c r="J222" s="1">
-        <v>0</v>
-      </c>
-      <c r="K222" s="3">
-        <v>1</v>
-      </c>
-      <c r="L222" s="1">
-        <v>1</v>
-      </c>
-      <c r="M222" s="1">
-        <v>100</v>
-      </c>
-      <c r="N222" s="1">
-        <v>100</v>
-      </c>
-      <c r="S222" s="1">
-        <v>0</v>
-      </c>
-      <c r="T222" s="1">
-        <v>0</v>
-      </c>
-      <c r="U222" s="1">
-        <v>0</v>
-      </c>
-      <c r="V222" s="1">
-        <v>0</v>
-      </c>
-      <c r="W222" s="1">
-        <v>0</v>
-      </c>
-      <c r="X222" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y222" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z222" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA222" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB222" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC222" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A223" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B223" s="3">
-        <v>1706</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D223" s="1">
-        <v>7</v>
-      </c>
-      <c r="E223" s="1">
-        <v>0</v>
-      </c>
-      <c r="F223" s="1">
-        <v>0</v>
-      </c>
-      <c r="G223" s="1">
-        <v>0</v>
-      </c>
-      <c r="H223" s="1">
-        <v>0</v>
-      </c>
-      <c r="I223" s="1">
-        <v>0</v>
-      </c>
-      <c r="J223" s="1">
-        <v>0</v>
-      </c>
-      <c r="K223" s="3">
-        <v>1</v>
-      </c>
-      <c r="L223" s="1">
-        <v>1</v>
-      </c>
-      <c r="M223" s="1">
-        <v>100</v>
-      </c>
-      <c r="N223" s="1">
-        <v>100</v>
-      </c>
-      <c r="S223" s="1">
-        <v>0</v>
-      </c>
-      <c r="T223" s="1">
-        <v>0</v>
-      </c>
-      <c r="U223" s="1">
-        <v>0</v>
-      </c>
-      <c r="V223" s="1">
-        <v>0</v>
-      </c>
-      <c r="W223" s="1">
-        <v>0</v>
-      </c>
-      <c r="X223" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y223" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z223" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA223" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB223" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC223" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A224" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="B224" s="3">
-        <v>1707</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D224" s="1">
-        <v>7</v>
-      </c>
-      <c r="E224" s="1">
-        <v>0</v>
-      </c>
-      <c r="F224" s="1">
-        <v>0</v>
-      </c>
-      <c r="G224" s="1">
-        <v>0</v>
-      </c>
-      <c r="H224" s="1">
-        <v>0</v>
-      </c>
-      <c r="I224" s="1">
-        <v>0</v>
-      </c>
-      <c r="J224" s="1">
-        <v>0</v>
-      </c>
-      <c r="K224" s="3">
-        <v>1</v>
-      </c>
-      <c r="L224" s="1">
-        <v>1</v>
-      </c>
-      <c r="M224" s="1">
-        <v>100</v>
-      </c>
-      <c r="N224" s="1">
-        <v>100</v>
-      </c>
-      <c r="S224" s="1">
-        <v>0</v>
-      </c>
-      <c r="T224" s="1">
-        <v>0</v>
-      </c>
-      <c r="U224" s="1">
-        <v>0</v>
-      </c>
-      <c r="V224" s="1">
-        <v>0</v>
-      </c>
-      <c r="W224" s="1">
-        <v>0</v>
-      </c>
-      <c r="X224" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y224" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z224" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA224" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB224" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC224" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A225" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="B225" s="3">
-        <v>1708</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D225" s="1">
-        <v>7</v>
-      </c>
-      <c r="E225" s="1">
-        <v>0</v>
-      </c>
-      <c r="F225" s="1">
-        <v>0</v>
-      </c>
-      <c r="G225" s="1">
-        <v>0</v>
-      </c>
-      <c r="H225" s="1">
-        <v>0</v>
-      </c>
-      <c r="I225" s="1">
-        <v>0</v>
-      </c>
-      <c r="J225" s="1">
-        <v>0</v>
-      </c>
-      <c r="K225" s="3">
-        <v>1</v>
-      </c>
-      <c r="L225" s="1">
-        <v>1</v>
-      </c>
-      <c r="M225" s="1">
-        <v>100</v>
-      </c>
-      <c r="N225" s="1">
-        <v>100</v>
-      </c>
-      <c r="S225" s="1">
-        <v>0</v>
-      </c>
-      <c r="T225" s="1">
-        <v>0</v>
-      </c>
-      <c r="U225" s="1">
-        <v>0</v>
-      </c>
-      <c r="V225" s="1">
-        <v>0</v>
-      </c>
-      <c r="W225" s="1">
-        <v>0</v>
-      </c>
-      <c r="X225" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y225" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z225" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA225" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB225" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC225" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A226" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="B226" s="3">
-        <v>1709</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D226" s="1">
-        <v>7</v>
-      </c>
-      <c r="E226" s="1">
-        <v>0</v>
-      </c>
-      <c r="F226" s="1">
-        <v>0</v>
-      </c>
-      <c r="G226" s="1">
-        <v>0</v>
-      </c>
-      <c r="H226" s="1">
-        <v>0</v>
-      </c>
-      <c r="I226" s="1">
-        <v>0</v>
-      </c>
-      <c r="J226" s="1">
-        <v>0</v>
-      </c>
-      <c r="K226" s="3">
-        <v>1</v>
-      </c>
-      <c r="L226" s="1">
-        <v>1</v>
-      </c>
-      <c r="M226" s="1">
-        <v>100</v>
-      </c>
-      <c r="N226" s="1">
-        <v>100</v>
-      </c>
-      <c r="S226" s="1">
-        <v>0</v>
-      </c>
-      <c r="T226" s="1">
-        <v>0</v>
-      </c>
-      <c r="U226" s="1">
-        <v>0</v>
-      </c>
-      <c r="V226" s="1">
-        <v>0</v>
-      </c>
-      <c r="W226" s="1">
-        <v>0</v>
-      </c>
-      <c r="X226" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y226" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z226" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA226" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB226" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC226" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A227" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="B227" s="3">
-        <v>1710</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="D227" s="1">
-        <v>7</v>
-      </c>
-      <c r="E227" s="1">
-        <v>0</v>
-      </c>
-      <c r="F227" s="1">
-        <v>0</v>
-      </c>
-      <c r="G227" s="1">
-        <v>0</v>
-      </c>
-      <c r="H227" s="1">
-        <v>0</v>
-      </c>
-      <c r="I227" s="1">
-        <v>0</v>
-      </c>
-      <c r="J227" s="1">
-        <v>0</v>
-      </c>
-      <c r="K227" s="3">
-        <v>1</v>
-      </c>
-      <c r="L227" s="1">
-        <v>1</v>
-      </c>
-      <c r="M227" s="1">
-        <v>100</v>
-      </c>
-      <c r="N227" s="1">
-        <v>100</v>
-      </c>
-      <c r="S227" s="1">
-        <v>0</v>
-      </c>
-      <c r="T227" s="1">
-        <v>0</v>
-      </c>
-      <c r="U227" s="1">
-        <v>0</v>
-      </c>
-      <c r="V227" s="1">
-        <v>0</v>
-      </c>
-      <c r="W227" s="1">
-        <v>0</v>
-      </c>
-      <c r="X227" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y227" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z227" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA227" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB227" s="1">
-        <v>10</v>
-      </c>
-      <c r="AC227" s="1">
+      <c r="E227" s="9">
+        <v>0</v>
+      </c>
+      <c r="F227" s="9">
+        <v>0</v>
+      </c>
+      <c r="G227" s="9">
+        <v>0</v>
+      </c>
+      <c r="H227" s="9">
+        <v>0</v>
+      </c>
+      <c r="I227" s="9">
+        <v>0</v>
+      </c>
+      <c r="J227" s="9">
+        <v>0</v>
+      </c>
+      <c r="K227" s="24">
+        <v>1</v>
+      </c>
+      <c r="L227" s="9">
+        <v>1</v>
+      </c>
+      <c r="M227" s="9">
+        <v>100</v>
+      </c>
+      <c r="N227" s="9">
+        <v>100</v>
+      </c>
+      <c r="O227" s="34"/>
+      <c r="P227" s="34"/>
+      <c r="Q227" s="34"/>
+      <c r="R227" s="34"/>
+      <c r="S227" s="9">
+        <v>0</v>
+      </c>
+      <c r="T227" s="9">
+        <v>0</v>
+      </c>
+      <c r="U227" s="9">
+        <v>0</v>
+      </c>
+      <c r="V227" s="9">
+        <v>0</v>
+      </c>
+      <c r="W227" s="9">
+        <v>0</v>
+      </c>
+      <c r="X227" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y227" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z227" s="9">
+        <v>20</v>
+      </c>
+      <c r="AA227" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB227" s="9">
+        <v>150</v>
+      </c>
+      <c r="AC227" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21287,7 +21334,7 @@
         <v>0</v>
       </c>
       <c r="W228" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X228" s="1">
         <v>0</v>
@@ -21364,10 +21411,10 @@
         <v>0</v>
       </c>
       <c r="W229" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X229" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y229" s="1">
         <v>0</v>
@@ -21441,7 +21488,7 @@
         <v>0</v>
       </c>
       <c r="W230" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X230" s="1">
         <v>0</v>
@@ -21518,16 +21565,16 @@
         <v>0</v>
       </c>
       <c r="W231" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="X231" s="1">
         <v>0</v>
       </c>
       <c r="Y231" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z231" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA231" s="1">
         <v>0</v>
@@ -21595,13 +21642,13 @@
         <v>0</v>
       </c>
       <c r="W232" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X232" s="1">
         <v>0</v>
       </c>
       <c r="Y232" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z232" s="1">
         <v>0</v>
@@ -21672,7 +21719,7 @@
         <v>0</v>
       </c>
       <c r="W233" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X233" s="1">
         <v>0</v>
@@ -21684,7 +21731,7 @@
         <v>0</v>
       </c>
       <c r="AA233" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB233" s="1">
         <v>0</v>
@@ -21749,7 +21796,7 @@
         <v>0</v>
       </c>
       <c r="W234" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="X234" s="1">
         <v>0</v>
@@ -21826,7 +21873,7 @@
         <v>0</v>
       </c>
       <c r="W235" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="X235" s="1">
         <v>0</v>
@@ -21903,16 +21950,16 @@
         <v>0</v>
       </c>
       <c r="W236" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X236" s="1">
         <v>0</v>
       </c>
       <c r="Y236" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z236" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA236" s="1">
         <v>0</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -3560,10 +3560,9 @@
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.75" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.875" style="1" customWidth="1"/>
-    <col min="6" max="10" width="8.875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="14" width="11.875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="18" width="11" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="10" width="8.875" style="1" customWidth="1"/>
+    <col min="11" max="14" width="11.875" style="1" customWidth="1"/>
+    <col min="15" max="18" width="11" style="2" customWidth="1"/>
     <col min="19" max="19" width="8.375" style="1" customWidth="1"/>
     <col min="20" max="29" width="7.75" style="1"/>
     <col min="30" max="30" width="26.125" style="1" customWidth="1"/>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -31155,7 +31155,7 @@
         <v>815</v>
       </c>
       <c r="S305" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U305" s="2" t="s">
         <v>802</v>
@@ -31251,7 +31251,7 @@
         <v>815</v>
       </c>
       <c r="S306" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U306" s="2" t="s">
         <v>802</v>
@@ -31347,7 +31347,7 @@
         <v>815</v>
       </c>
       <c r="S307" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U307" s="2" t="s">
         <v>802</v>
@@ -31443,7 +31443,7 @@
         <v>815</v>
       </c>
       <c r="S308" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U308" s="2" t="s">
         <v>802</v>
@@ -31539,7 +31539,7 @@
         <v>815</v>
       </c>
       <c r="S309" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U309" s="2" t="s">
         <v>802</v>
@@ -31635,7 +31635,7 @@
         <v>815</v>
       </c>
       <c r="S310" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U310" s="2" t="s">
         <v>802</v>
@@ -31731,7 +31731,7 @@
         <v>815</v>
       </c>
       <c r="S311" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U311" s="2" t="s">
         <v>802</v>
@@ -31827,7 +31827,7 @@
         <v>815</v>
       </c>
       <c r="S312" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U312" s="2" t="s">
         <v>802</v>
@@ -31923,7 +31923,7 @@
         <v>815</v>
       </c>
       <c r="S313" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U313" s="2" t="s">
         <v>802</v>
@@ -32019,7 +32019,7 @@
         <v>815</v>
       </c>
       <c r="S314" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U314" s="2" t="s">
         <v>802</v>
@@ -32211,7 +32211,7 @@
         <v>815</v>
       </c>
       <c r="S316" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U316" s="2" t="s">
         <v>802</v>
@@ -32307,7 +32307,7 @@
         <v>815</v>
       </c>
       <c r="S317" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U317" s="2" t="s">
         <v>802</v>
@@ -32595,7 +32595,7 @@
         <v>815</v>
       </c>
       <c r="S320" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U320" s="2" t="s">
         <v>802</v>
@@ -32691,7 +32691,7 @@
         <v>815</v>
       </c>
       <c r="S321" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U321" s="2" t="s">
         <v>802</v>
@@ -32787,7 +32787,7 @@
         <v>815</v>
       </c>
       <c r="S322" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U322" s="2" t="s">
         <v>802</v>
@@ -32883,7 +32883,7 @@
         <v>815</v>
       </c>
       <c r="S323" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U323" s="2" t="s">
         <v>802</v>
@@ -32979,7 +32979,7 @@
         <v>815</v>
       </c>
       <c r="S324" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U324" s="2" t="s">
         <v>802</v>
@@ -33843,7 +33843,7 @@
         <v>815</v>
       </c>
       <c r="S333" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U333" s="2" t="s">
         <v>802</v>
@@ -34131,7 +34131,7 @@
         <v>815</v>
       </c>
       <c r="S336" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U336" s="2" t="s">
         <v>802</v>
@@ -34227,7 +34227,7 @@
         <v>815</v>
       </c>
       <c r="S337" s="37">
-        <v>1000</v>
+        <v>904</v>
       </c>
       <c r="U337" s="2" t="s">
         <v>802</v>
@@ -34323,7 +34323,7 @@
         <v>815</v>
       </c>
       <c r="S338" s="37">
-        <v>1000</v>
+        <v>903</v>
       </c>
       <c r="U338" s="2" t="s">
         <v>802</v>
@@ -34419,7 +34419,7 @@
         <v>815</v>
       </c>
       <c r="S339" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U339" s="2" t="s">
         <v>802</v>
@@ -34515,7 +34515,7 @@
         <v>815</v>
       </c>
       <c r="S340" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U340" s="2" t="s">
         <v>802</v>
@@ -34611,7 +34611,7 @@
         <v>815</v>
       </c>
       <c r="S341" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U341" s="2" t="s">
         <v>802</v>
@@ -34707,7 +34707,7 @@
         <v>815</v>
       </c>
       <c r="S342" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U342" s="2" t="s">
         <v>802</v>
@@ -34899,7 +34899,7 @@
         <v>815</v>
       </c>
       <c r="S344" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U344" s="2" t="s">
         <v>802</v>
@@ -34995,7 +34995,7 @@
         <v>815</v>
       </c>
       <c r="S345" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U345" s="2" t="s">
         <v>802</v>
@@ -36243,7 +36243,7 @@
         <v>815</v>
       </c>
       <c r="S358" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U358" s="2" t="s">
         <v>802</v>
@@ -36531,7 +36531,7 @@
         <v>815</v>
       </c>
       <c r="S361" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U361" s="2" t="s">
         <v>802</v>
@@ -36627,7 +36627,7 @@
         <v>815</v>
       </c>
       <c r="S362" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U362" s="2" t="s">
         <v>802</v>
@@ -36723,7 +36723,7 @@
         <v>815</v>
       </c>
       <c r="S363" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U363" s="2" t="s">
         <v>802</v>
@@ -36819,7 +36819,7 @@
         <v>815</v>
       </c>
       <c r="S364" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U364" s="2" t="s">
         <v>802</v>
@@ -36915,7 +36915,7 @@
         <v>815</v>
       </c>
       <c r="S365" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U365" s="2" t="s">
         <v>802</v>
@@ -37011,7 +37011,7 @@
         <v>815</v>
       </c>
       <c r="S366" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U366" s="2" t="s">
         <v>802</v>
@@ -37107,7 +37107,7 @@
         <v>815</v>
       </c>
       <c r="S367" s="37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U367" s="2" t="s">
         <v>802</v>
@@ -37491,7 +37491,7 @@
         <v>815</v>
       </c>
       <c r="S371" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U371" s="2" t="s">
         <v>802</v>
@@ -37587,7 +37587,7 @@
         <v>815</v>
       </c>
       <c r="S372" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U372" s="2" t="s">
         <v>802</v>
@@ -37683,7 +37683,7 @@
         <v>815</v>
       </c>
       <c r="S373" s="37">
-        <v>1000</v>
+        <v>902</v>
       </c>
       <c r="U373" s="2" t="s">
         <v>802</v>
@@ -37779,7 +37779,7 @@
         <v>815</v>
       </c>
       <c r="S374" s="37">
-        <v>1000</v>
+        <v>903</v>
       </c>
       <c r="U374" s="2" t="s">
         <v>802</v>
@@ -38163,7 +38163,7 @@
         <v>815</v>
       </c>
       <c r="S378" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U378" s="2" t="s">
         <v>802</v>
@@ -38451,7 +38451,7 @@
         <v>815</v>
       </c>
       <c r="S381" s="37">
-        <v>1000</v>
+        <v>903</v>
       </c>
       <c r="U381" s="2" t="s">
         <v>802</v>
@@ -38643,7 +38643,7 @@
         <v>815</v>
       </c>
       <c r="S383" s="37">
-        <v>1000</v>
+        <v>901</v>
       </c>
       <c r="U383" s="2" t="s">
         <v>802</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -31198,7 +31198,7 @@
         <v>0</v>
       </c>
       <c r="AF305" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306" spans="1:32" x14ac:dyDescent="0.15">
@@ -31294,7 +31294,7 @@
         <v>0</v>
       </c>
       <c r="AF306" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:32" x14ac:dyDescent="0.15">
@@ -31390,7 +31390,7 @@
         <v>7</v>
       </c>
       <c r="AF307" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:32" x14ac:dyDescent="0.15">
@@ -31486,7 +31486,7 @@
         <v>0</v>
       </c>
       <c r="AF308" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:32" x14ac:dyDescent="0.15">
@@ -31582,7 +31582,7 @@
         <v>0</v>
       </c>
       <c r="AF309" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:32" x14ac:dyDescent="0.15">
@@ -31678,7 +31678,7 @@
         <v>0</v>
       </c>
       <c r="AF310" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:32" x14ac:dyDescent="0.15">
@@ -31774,7 +31774,7 @@
         <v>0</v>
       </c>
       <c r="AF311" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:32" x14ac:dyDescent="0.15">
@@ -31870,7 +31870,7 @@
         <v>0</v>
       </c>
       <c r="AF312" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:32" x14ac:dyDescent="0.15">
@@ -31966,7 +31966,7 @@
         <v>0</v>
       </c>
       <c r="AF313" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:32" x14ac:dyDescent="0.15">
@@ -32062,7 +32062,7 @@
         <v>0</v>
       </c>
       <c r="AF314" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:32" x14ac:dyDescent="0.15">
@@ -32158,7 +32158,7 @@
         <v>0</v>
       </c>
       <c r="AF315" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:32" x14ac:dyDescent="0.15">
@@ -32254,7 +32254,7 @@
         <v>0</v>
       </c>
       <c r="AF316" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:32" x14ac:dyDescent="0.15">
@@ -32350,7 +32350,7 @@
         <v>0</v>
       </c>
       <c r="AF317" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:32" x14ac:dyDescent="0.15">
@@ -32446,7 +32446,7 @@
         <v>10</v>
       </c>
       <c r="AF318" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:32" x14ac:dyDescent="0.15">
@@ -32542,7 +32542,7 @@
         <v>0</v>
       </c>
       <c r="AF319" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:32" x14ac:dyDescent="0.15">
@@ -32638,7 +32638,7 @@
         <v>0</v>
       </c>
       <c r="AF320" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:32" x14ac:dyDescent="0.15">
@@ -32734,7 +32734,7 @@
         <v>0</v>
       </c>
       <c r="AF321" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322" spans="1:32" x14ac:dyDescent="0.15">
@@ -32830,7 +32830,7 @@
         <v>0</v>
       </c>
       <c r="AF322" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:32" x14ac:dyDescent="0.15">
@@ -32926,7 +32926,7 @@
         <v>0</v>
       </c>
       <c r="AF323" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:32" x14ac:dyDescent="0.15">
@@ -33022,7 +33022,7 @@
         <v>0</v>
       </c>
       <c r="AF324" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:32" x14ac:dyDescent="0.15">
@@ -33118,7 +33118,7 @@
         <v>15</v>
       </c>
       <c r="AF325" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:32" x14ac:dyDescent="0.15">
@@ -33214,7 +33214,7 @@
         <v>0</v>
       </c>
       <c r="AF326" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:32" x14ac:dyDescent="0.15">
@@ -33310,7 +33310,7 @@
         <v>0</v>
       </c>
       <c r="AF327" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:32" x14ac:dyDescent="0.15">
@@ -33406,7 +33406,7 @@
         <v>0</v>
       </c>
       <c r="AF328" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:32" x14ac:dyDescent="0.15">
@@ -33502,7 +33502,7 @@
         <v>0</v>
       </c>
       <c r="AF329" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:32" x14ac:dyDescent="0.15">
@@ -33598,7 +33598,7 @@
         <v>0</v>
       </c>
       <c r="AF330" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:32" x14ac:dyDescent="0.15">
@@ -33694,7 +33694,7 @@
         <v>0</v>
       </c>
       <c r="AF331" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:32" x14ac:dyDescent="0.15">
@@ -33790,7 +33790,7 @@
         <v>15</v>
       </c>
       <c r="AF332" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:32" x14ac:dyDescent="0.15">
@@ -33886,7 +33886,7 @@
         <v>0</v>
       </c>
       <c r="AF333" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:32" x14ac:dyDescent="0.15">
@@ -33982,7 +33982,7 @@
         <v>20</v>
       </c>
       <c r="AF334" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:32" x14ac:dyDescent="0.15">
@@ -34078,7 +34078,7 @@
         <v>0</v>
       </c>
       <c r="AF335" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:32" x14ac:dyDescent="0.15">
@@ -34174,7 +34174,7 @@
         <v>0</v>
       </c>
       <c r="AF336" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:32" x14ac:dyDescent="0.15">
@@ -34270,7 +34270,7 @@
         <v>0</v>
       </c>
       <c r="AF337" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:32" x14ac:dyDescent="0.15">
@@ -34366,7 +34366,7 @@
         <v>0</v>
       </c>
       <c r="AF338" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:32" x14ac:dyDescent="0.15">
@@ -34462,7 +34462,7 @@
         <v>0</v>
       </c>
       <c r="AF339" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:32" x14ac:dyDescent="0.15">
@@ -34558,7 +34558,7 @@
         <v>0</v>
       </c>
       <c r="AF340" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:32" x14ac:dyDescent="0.15">
@@ -34654,7 +34654,7 @@
         <v>0</v>
       </c>
       <c r="AF341" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:32" x14ac:dyDescent="0.15">
@@ -34750,7 +34750,7 @@
         <v>0</v>
       </c>
       <c r="AF342" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:32" x14ac:dyDescent="0.15">
@@ -34846,7 +34846,7 @@
         <v>20</v>
       </c>
       <c r="AF343" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:32" x14ac:dyDescent="0.15">
@@ -34942,7 +34942,7 @@
         <v>0</v>
       </c>
       <c r="AF344" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:32" x14ac:dyDescent="0.15">
@@ -35038,7 +35038,7 @@
         <v>0</v>
       </c>
       <c r="AF345" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:32" x14ac:dyDescent="0.15">
@@ -35134,7 +35134,7 @@
         <v>30</v>
       </c>
       <c r="AF346" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:32" x14ac:dyDescent="0.15">
@@ -35230,7 +35230,7 @@
         <v>0</v>
       </c>
       <c r="AF347" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:32" x14ac:dyDescent="0.15">
@@ -35326,7 +35326,7 @@
         <v>0</v>
       </c>
       <c r="AF348" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:32" x14ac:dyDescent="0.15">
@@ -35422,7 +35422,7 @@
         <v>0</v>
       </c>
       <c r="AF349" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:32" x14ac:dyDescent="0.15">
@@ -35518,7 +35518,7 @@
         <v>0</v>
       </c>
       <c r="AF350" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:32" x14ac:dyDescent="0.15">
@@ -35614,7 +35614,7 @@
         <v>0</v>
       </c>
       <c r="AF351" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:32" x14ac:dyDescent="0.15">
@@ -35710,7 +35710,7 @@
         <v>0</v>
       </c>
       <c r="AF352" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:32" x14ac:dyDescent="0.15">
@@ -35806,7 +35806,7 @@
         <v>0</v>
       </c>
       <c r="AF353" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:32" x14ac:dyDescent="0.15">
@@ -35902,7 +35902,7 @@
         <v>0</v>
       </c>
       <c r="AF354" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:32" x14ac:dyDescent="0.15">
@@ -35998,7 +35998,7 @@
         <v>0</v>
       </c>
       <c r="AF355" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:32" x14ac:dyDescent="0.15">
@@ -36094,7 +36094,7 @@
         <v>0</v>
       </c>
       <c r="AF356" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:32" x14ac:dyDescent="0.15">
@@ -36190,7 +36190,7 @@
         <v>0</v>
       </c>
       <c r="AF357" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:32" x14ac:dyDescent="0.15">
@@ -36286,7 +36286,7 @@
         <v>0</v>
       </c>
       <c r="AF358" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:32" x14ac:dyDescent="0.15">
@@ -36382,7 +36382,7 @@
         <v>0</v>
       </c>
       <c r="AF359" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:32" x14ac:dyDescent="0.15">
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="AF360" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:32" x14ac:dyDescent="0.15">
@@ -36574,7 +36574,7 @@
         <v>0</v>
       </c>
       <c r="AF361" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:32" x14ac:dyDescent="0.15">
@@ -36670,7 +36670,7 @@
         <v>0</v>
       </c>
       <c r="AF362" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:32" x14ac:dyDescent="0.15">
@@ -36766,7 +36766,7 @@
         <v>0</v>
       </c>
       <c r="AF363" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:32" x14ac:dyDescent="0.15">
@@ -36862,7 +36862,7 @@
         <v>0</v>
       </c>
       <c r="AF364" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:32" x14ac:dyDescent="0.15">
@@ -36958,7 +36958,7 @@
         <v>0</v>
       </c>
       <c r="AF365" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366" spans="1:32" x14ac:dyDescent="0.15">
@@ -37054,7 +37054,7 @@
         <v>0</v>
       </c>
       <c r="AF366" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:32" x14ac:dyDescent="0.15">
@@ -37150,7 +37150,7 @@
         <v>0</v>
       </c>
       <c r="AF367" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:32" x14ac:dyDescent="0.15">
@@ -37246,7 +37246,7 @@
         <v>0</v>
       </c>
       <c r="AF368" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:32" x14ac:dyDescent="0.15">
@@ -37342,7 +37342,7 @@
         <v>0</v>
       </c>
       <c r="AF369" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:32" x14ac:dyDescent="0.15">
@@ -37438,7 +37438,7 @@
         <v>0</v>
       </c>
       <c r="AF370" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:32" x14ac:dyDescent="0.15">
@@ -37534,7 +37534,7 @@
         <v>0</v>
       </c>
       <c r="AF371" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:32" x14ac:dyDescent="0.15">
@@ -37630,7 +37630,7 @@
         <v>0</v>
       </c>
       <c r="AF372" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:32" x14ac:dyDescent="0.15">
@@ -37726,7 +37726,7 @@
         <v>0</v>
       </c>
       <c r="AF373" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="374" spans="1:32" x14ac:dyDescent="0.15">
@@ -37822,7 +37822,7 @@
         <v>0</v>
       </c>
       <c r="AF374" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:32" x14ac:dyDescent="0.15">
@@ -37918,7 +37918,7 @@
         <v>0</v>
       </c>
       <c r="AF375" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:32" x14ac:dyDescent="0.15">
@@ -38014,7 +38014,7 @@
         <v>32</v>
       </c>
       <c r="AF376" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:32" x14ac:dyDescent="0.15">
@@ -38110,7 +38110,7 @@
         <v>0</v>
       </c>
       <c r="AF377" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:32" x14ac:dyDescent="0.15">
@@ -38206,7 +38206,7 @@
         <v>0</v>
       </c>
       <c r="AF378" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379" spans="1:32" x14ac:dyDescent="0.15">
@@ -38302,7 +38302,7 @@
         <v>35</v>
       </c>
       <c r="AF379" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:32" x14ac:dyDescent="0.15">
@@ -38398,7 +38398,7 @@
         <v>40</v>
       </c>
       <c r="AF380" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:32" x14ac:dyDescent="0.15">
@@ -38494,7 +38494,7 @@
         <v>0</v>
       </c>
       <c r="AF381" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382" spans="1:32" x14ac:dyDescent="0.15">
@@ -38590,7 +38590,7 @@
         <v>45</v>
       </c>
       <c r="AF382" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:32" x14ac:dyDescent="0.15">
@@ -38686,7 +38686,7 @@
         <v>0</v>
       </c>
       <c r="AF383" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384" spans="1:32" x14ac:dyDescent="0.15">

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -27,7 +27,7 @@
     <sheet name="鱼" sheetId="15" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$AG$403</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$AG$410</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet13!$Q$47:$Q$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet2!$B$5:$X$54</definedName>
   </definedNames>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5652" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="1580">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5522,6 +5522,74 @@
   </si>
   <si>
     <t>线鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的禽类，可以产出[鸡蛋]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的禽类，可以产出[鸭绒]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的兽类，可以产出[兔子脚]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的兽类，可以产出[羊毛]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的兽类，可以产出[鸡蛋]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的兽类，可以产出[牛奶]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的兽类，可以产出[猪肉]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8366,7 +8434,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:AG403"/>
+  <dimension ref="A2:AG410"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -45515,20 +45583,20 @@
       </c>
     </row>
     <row r="393" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A393" s="12" t="s">
-        <v>629</v>
+      <c r="A393" s="1" t="s">
+        <v>1564</v>
       </c>
       <c r="B393" s="1">
-        <v>4000</v>
-      </c>
-      <c r="C393" s="12" t="s">
-        <v>629</v>
+        <v>3500</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>1563</v>
       </c>
       <c r="D393" s="1">
-        <v>5</v>
-      </c>
-      <c r="E393" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E393" s="7">
+        <v>3000</v>
       </c>
       <c r="F393" s="1">
         <v>0</v>
@@ -45552,13 +45620,14 @@
         <v>1</v>
       </c>
       <c r="M393" s="39">
-        <v>100</v>
+        <f>N393*2</f>
+        <v>254</v>
       </c>
       <c r="N393" s="39">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="Q393" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R393" s="36">
         <v>0</v>
@@ -45602,25 +45671,25 @@
       <c r="AF393" s="1">
         <v>0</v>
       </c>
-      <c r="AG393" s="1" t="s">
-        <v>1517</v>
+      <c r="AG393" s="34" t="s">
+        <v>1573</v>
       </c>
     </row>
     <row r="394" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A394" s="12" t="s">
-        <v>630</v>
+      <c r="A394" s="1" t="s">
+        <v>1565</v>
       </c>
       <c r="B394" s="1">
-        <v>4001</v>
-      </c>
-      <c r="C394" s="12" t="s">
-        <v>630</v>
+        <v>3501</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>1571</v>
       </c>
       <c r="D394" s="1">
-        <v>5</v>
-      </c>
-      <c r="E394" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E394" s="7">
+        <v>3002</v>
       </c>
       <c r="F394" s="1">
         <v>0</v>
@@ -45644,13 +45713,14 @@
         <v>1</v>
       </c>
       <c r="M394" s="39">
-        <v>100</v>
+        <f t="shared" ref="M394:M399" si="14">N394*2</f>
+        <v>574</v>
       </c>
       <c r="N394" s="39">
-        <v>100</v>
+        <v>287</v>
       </c>
       <c r="Q394" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R394" s="36">
         <v>0</v>
@@ -45694,25 +45764,25 @@
       <c r="AF394" s="1">
         <v>0</v>
       </c>
-      <c r="AG394" s="1" t="s">
-        <v>1519</v>
+      <c r="AG394" s="34" t="s">
+        <v>1574</v>
       </c>
     </row>
     <row r="395" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A395" s="12" t="s">
-        <v>631</v>
+      <c r="A395" s="1" t="s">
+        <v>1566</v>
       </c>
       <c r="B395" s="1">
-        <v>4002</v>
-      </c>
-      <c r="C395" s="12" t="s">
-        <v>631</v>
+        <v>3502</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>1572</v>
       </c>
       <c r="D395" s="1">
-        <v>5</v>
-      </c>
-      <c r="E395" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E395" s="7">
+        <v>3004</v>
       </c>
       <c r="F395" s="1">
         <v>0</v>
@@ -45736,13 +45806,14 @@
         <v>1</v>
       </c>
       <c r="M395" s="39">
-        <v>100</v>
+        <f t="shared" si="14"/>
+        <v>818</v>
       </c>
       <c r="N395" s="39">
-        <v>100</v>
+        <v>409</v>
       </c>
       <c r="Q395" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R395" s="36">
         <v>0</v>
@@ -45786,25 +45857,25 @@
       <c r="AF395" s="1">
         <v>0</v>
       </c>
-      <c r="AG395" s="1" t="s">
-        <v>1521</v>
+      <c r="AG395" s="34" t="s">
+        <v>1575</v>
       </c>
     </row>
     <row r="396" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A396" s="12" t="s">
-        <v>632</v>
+      <c r="A396" s="1" t="s">
+        <v>1567</v>
       </c>
       <c r="B396" s="1">
-        <v>4003</v>
-      </c>
-      <c r="C396" s="12" t="s">
-        <v>632</v>
+        <v>3503</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>1567</v>
       </c>
       <c r="D396" s="1">
-        <v>5</v>
-      </c>
-      <c r="E396" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E396" s="7">
+        <v>3006</v>
       </c>
       <c r="F396" s="1">
         <v>0</v>
@@ -45828,13 +45899,14 @@
         <v>1</v>
       </c>
       <c r="M396" s="39">
-        <v>100</v>
+        <f t="shared" si="14"/>
+        <v>1132</v>
       </c>
       <c r="N396" s="39">
-        <v>100</v>
+        <v>566</v>
       </c>
       <c r="Q396" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R396" s="36">
         <v>0</v>
@@ -45878,25 +45950,25 @@
       <c r="AF396" s="1">
         <v>0</v>
       </c>
-      <c r="AG396" s="1" t="s">
-        <v>1523</v>
+      <c r="AG396" s="34" t="s">
+        <v>1576</v>
       </c>
     </row>
     <row r="397" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A397" s="12" t="s">
-        <v>633</v>
+      <c r="A397" s="1" t="s">
+        <v>1568</v>
       </c>
       <c r="B397" s="1">
-        <v>4004</v>
-      </c>
-      <c r="C397" s="12" t="s">
-        <v>633</v>
+        <v>3504</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>1568</v>
       </c>
       <c r="D397" s="1">
-        <v>5</v>
-      </c>
-      <c r="E397" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E397" s="7">
+        <v>3010</v>
       </c>
       <c r="F397" s="1">
         <v>0</v>
@@ -45920,13 +45992,14 @@
         <v>1</v>
       </c>
       <c r="M397" s="39">
-        <v>100</v>
+        <f t="shared" si="14"/>
+        <v>1524</v>
       </c>
       <c r="N397" s="39">
-        <v>100</v>
+        <v>762</v>
       </c>
       <c r="Q397" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R397" s="36">
         <v>0</v>
@@ -45970,25 +46043,25 @@
       <c r="AF397" s="1">
         <v>0</v>
       </c>
-      <c r="AG397" s="1" t="s">
-        <v>1525</v>
+      <c r="AG397" s="34" t="s">
+        <v>1578</v>
       </c>
     </row>
     <row r="398" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A398" s="12" t="s">
-        <v>634</v>
+      <c r="A398" s="1" t="s">
+        <v>1570</v>
       </c>
       <c r="B398" s="1">
-        <v>4005</v>
-      </c>
-      <c r="C398" s="12" t="s">
-        <v>634</v>
+        <v>3505</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>1570</v>
       </c>
       <c r="D398" s="1">
-        <v>5</v>
-      </c>
-      <c r="E398" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E398" s="7">
+        <v>3008</v>
       </c>
       <c r="F398" s="1">
         <v>0</v>
@@ -46012,13 +46085,14 @@
         <v>1</v>
       </c>
       <c r="M398" s="39">
-        <v>100</v>
+        <f t="shared" si="14"/>
+        <v>1970</v>
       </c>
       <c r="N398" s="39">
-        <v>100</v>
+        <v>985</v>
       </c>
       <c r="Q398" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R398" s="36">
         <v>0</v>
@@ -46062,25 +46136,25 @@
       <c r="AF398" s="1">
         <v>0</v>
       </c>
-      <c r="AG398" s="1" t="s">
-        <v>1527</v>
+      <c r="AG398" s="34" t="s">
+        <v>1579</v>
       </c>
     </row>
     <row r="399" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A399" s="12" t="s">
-        <v>635</v>
+      <c r="A399" s="1" t="s">
+        <v>1569</v>
       </c>
       <c r="B399" s="1">
-        <v>4006</v>
-      </c>
-      <c r="C399" s="12" t="s">
-        <v>635</v>
+        <v>3506</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>1569</v>
       </c>
       <c r="D399" s="1">
-        <v>5</v>
-      </c>
-      <c r="E399" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E399" s="7">
+        <v>3012</v>
       </c>
       <c r="F399" s="1">
         <v>0</v>
@@ -46104,13 +46178,14 @@
         <v>1</v>
       </c>
       <c r="M399" s="39">
-        <v>100</v>
+        <f t="shared" si="14"/>
+        <v>3040</v>
       </c>
       <c r="N399" s="39">
-        <v>100</v>
+        <v>1520</v>
       </c>
       <c r="Q399" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R399" s="36">
         <v>0</v>
@@ -46154,19 +46229,19 @@
       <c r="AF399" s="1">
         <v>0</v>
       </c>
-      <c r="AG399" s="1" t="s">
-        <v>1529</v>
+      <c r="AG399" s="34" t="s">
+        <v>1577</v>
       </c>
     </row>
     <row r="400" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A400" s="12" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="B400" s="1">
-        <v>4007</v>
+        <v>4000</v>
       </c>
       <c r="C400" s="12" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="D400" s="1">
         <v>5</v>
@@ -46247,18 +46322,18 @@
         <v>0</v>
       </c>
       <c r="AG400" s="1" t="s">
-        <v>1531</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="401" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A401" s="12" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="B401" s="1">
-        <v>4008</v>
+        <v>4001</v>
       </c>
       <c r="C401" s="12" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D401" s="1">
         <v>5</v>
@@ -46339,18 +46414,18 @@
         <v>0</v>
       </c>
       <c r="AG401" s="1" t="s">
-        <v>1533</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="402" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A402" s="12" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B402" s="1">
-        <v>4009</v>
+        <v>4002</v>
       </c>
       <c r="C402" s="12" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D402" s="1">
         <v>5</v>
@@ -46431,18 +46506,18 @@
         <v>0</v>
       </c>
       <c r="AG402" s="1" t="s">
-        <v>1535</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="403" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A403" s="12" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B403" s="1">
-        <v>4010</v>
+        <v>4003</v>
       </c>
       <c r="C403" s="12" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="D403" s="1">
         <v>5</v>
@@ -46523,13 +46598,657 @@
         <v>0</v>
       </c>
       <c r="AG403" s="1" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="404" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A404" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B404" s="1">
+        <v>4004</v>
+      </c>
+      <c r="C404" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="D404" s="1">
+        <v>5</v>
+      </c>
+      <c r="E404" s="1">
+        <v>0</v>
+      </c>
+      <c r="F404" s="1">
+        <v>0</v>
+      </c>
+      <c r="G404" s="1">
+        <v>1</v>
+      </c>
+      <c r="H404" s="1">
+        <v>0</v>
+      </c>
+      <c r="I404" s="1">
+        <v>0</v>
+      </c>
+      <c r="J404" s="1">
+        <v>0</v>
+      </c>
+      <c r="K404" s="1">
+        <v>1</v>
+      </c>
+      <c r="L404" s="1">
+        <v>1</v>
+      </c>
+      <c r="M404" s="39">
+        <v>100</v>
+      </c>
+      <c r="N404" s="39">
+        <v>100</v>
+      </c>
+      <c r="Q404" s="36">
+        <v>1</v>
+      </c>
+      <c r="R404" s="36">
+        <v>0</v>
+      </c>
+      <c r="S404" s="36">
+        <v>0</v>
+      </c>
+      <c r="U404" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="V404" s="1">
+        <v>0</v>
+      </c>
+      <c r="W404" s="1">
+        <v>0</v>
+      </c>
+      <c r="X404" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y404" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z404" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA404" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB404" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC404" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD404" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE404" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF404" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG404" s="1" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="405" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A405" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="B405" s="1">
+        <v>4005</v>
+      </c>
+      <c r="C405" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="D405" s="1">
+        <v>5</v>
+      </c>
+      <c r="E405" s="1">
+        <v>0</v>
+      </c>
+      <c r="F405" s="1">
+        <v>0</v>
+      </c>
+      <c r="G405" s="1">
+        <v>1</v>
+      </c>
+      <c r="H405" s="1">
+        <v>0</v>
+      </c>
+      <c r="I405" s="1">
+        <v>0</v>
+      </c>
+      <c r="J405" s="1">
+        <v>0</v>
+      </c>
+      <c r="K405" s="1">
+        <v>1</v>
+      </c>
+      <c r="L405" s="1">
+        <v>1</v>
+      </c>
+      <c r="M405" s="39">
+        <v>100</v>
+      </c>
+      <c r="N405" s="39">
+        <v>100</v>
+      </c>
+      <c r="Q405" s="36">
+        <v>1</v>
+      </c>
+      <c r="R405" s="36">
+        <v>0</v>
+      </c>
+      <c r="S405" s="36">
+        <v>0</v>
+      </c>
+      <c r="U405" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="V405" s="1">
+        <v>0</v>
+      </c>
+      <c r="W405" s="1">
+        <v>0</v>
+      </c>
+      <c r="X405" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y405" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z405" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA405" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB405" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC405" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD405" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE405" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF405" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG405" s="1" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="406" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A406" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="B406" s="1">
+        <v>4006</v>
+      </c>
+      <c r="C406" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="D406" s="1">
+        <v>5</v>
+      </c>
+      <c r="E406" s="1">
+        <v>0</v>
+      </c>
+      <c r="F406" s="1">
+        <v>0</v>
+      </c>
+      <c r="G406" s="1">
+        <v>1</v>
+      </c>
+      <c r="H406" s="1">
+        <v>0</v>
+      </c>
+      <c r="I406" s="1">
+        <v>0</v>
+      </c>
+      <c r="J406" s="1">
+        <v>0</v>
+      </c>
+      <c r="K406" s="1">
+        <v>1</v>
+      </c>
+      <c r="L406" s="1">
+        <v>1</v>
+      </c>
+      <c r="M406" s="39">
+        <v>100</v>
+      </c>
+      <c r="N406" s="39">
+        <v>100</v>
+      </c>
+      <c r="Q406" s="36">
+        <v>1</v>
+      </c>
+      <c r="R406" s="36">
+        <v>0</v>
+      </c>
+      <c r="S406" s="36">
+        <v>0</v>
+      </c>
+      <c r="U406" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="V406" s="1">
+        <v>0</v>
+      </c>
+      <c r="W406" s="1">
+        <v>0</v>
+      </c>
+      <c r="X406" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y406" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z406" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA406" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB406" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC406" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD406" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE406" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF406" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG406" s="1" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="407" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A407" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="B407" s="1">
+        <v>4007</v>
+      </c>
+      <c r="C407" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="D407" s="1">
+        <v>5</v>
+      </c>
+      <c r="E407" s="1">
+        <v>0</v>
+      </c>
+      <c r="F407" s="1">
+        <v>0</v>
+      </c>
+      <c r="G407" s="1">
+        <v>1</v>
+      </c>
+      <c r="H407" s="1">
+        <v>0</v>
+      </c>
+      <c r="I407" s="1">
+        <v>0</v>
+      </c>
+      <c r="J407" s="1">
+        <v>0</v>
+      </c>
+      <c r="K407" s="1">
+        <v>1</v>
+      </c>
+      <c r="L407" s="1">
+        <v>1</v>
+      </c>
+      <c r="M407" s="39">
+        <v>100</v>
+      </c>
+      <c r="N407" s="39">
+        <v>100</v>
+      </c>
+      <c r="Q407" s="36">
+        <v>1</v>
+      </c>
+      <c r="R407" s="36">
+        <v>0</v>
+      </c>
+      <c r="S407" s="36">
+        <v>0</v>
+      </c>
+      <c r="U407" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="V407" s="1">
+        <v>0</v>
+      </c>
+      <c r="W407" s="1">
+        <v>0</v>
+      </c>
+      <c r="X407" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y407" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z407" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA407" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB407" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC407" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD407" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE407" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF407" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG407" s="1" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="408" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A408" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="B408" s="1">
+        <v>4008</v>
+      </c>
+      <c r="C408" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="D408" s="1">
+        <v>5</v>
+      </c>
+      <c r="E408" s="1">
+        <v>0</v>
+      </c>
+      <c r="F408" s="1">
+        <v>0</v>
+      </c>
+      <c r="G408" s="1">
+        <v>1</v>
+      </c>
+      <c r="H408" s="1">
+        <v>0</v>
+      </c>
+      <c r="I408" s="1">
+        <v>0</v>
+      </c>
+      <c r="J408" s="1">
+        <v>0</v>
+      </c>
+      <c r="K408" s="1">
+        <v>1</v>
+      </c>
+      <c r="L408" s="1">
+        <v>1</v>
+      </c>
+      <c r="M408" s="39">
+        <v>100</v>
+      </c>
+      <c r="N408" s="39">
+        <v>100</v>
+      </c>
+      <c r="Q408" s="36">
+        <v>1</v>
+      </c>
+      <c r="R408" s="36">
+        <v>0</v>
+      </c>
+      <c r="S408" s="36">
+        <v>0</v>
+      </c>
+      <c r="U408" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="V408" s="1">
+        <v>0</v>
+      </c>
+      <c r="W408" s="1">
+        <v>0</v>
+      </c>
+      <c r="X408" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y408" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z408" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA408" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB408" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC408" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD408" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE408" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF408" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG408" s="1" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="409" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A409" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="B409" s="1">
+        <v>4009</v>
+      </c>
+      <c r="C409" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="D409" s="1">
+        <v>5</v>
+      </c>
+      <c r="E409" s="1">
+        <v>0</v>
+      </c>
+      <c r="F409" s="1">
+        <v>0</v>
+      </c>
+      <c r="G409" s="1">
+        <v>1</v>
+      </c>
+      <c r="H409" s="1">
+        <v>0</v>
+      </c>
+      <c r="I409" s="1">
+        <v>0</v>
+      </c>
+      <c r="J409" s="1">
+        <v>0</v>
+      </c>
+      <c r="K409" s="1">
+        <v>1</v>
+      </c>
+      <c r="L409" s="1">
+        <v>1</v>
+      </c>
+      <c r="M409" s="39">
+        <v>100</v>
+      </c>
+      <c r="N409" s="39">
+        <v>100</v>
+      </c>
+      <c r="Q409" s="36">
+        <v>1</v>
+      </c>
+      <c r="R409" s="36">
+        <v>0</v>
+      </c>
+      <c r="S409" s="36">
+        <v>0</v>
+      </c>
+      <c r="U409" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="V409" s="1">
+        <v>0</v>
+      </c>
+      <c r="W409" s="1">
+        <v>0</v>
+      </c>
+      <c r="X409" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y409" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z409" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA409" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB409" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC409" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD409" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE409" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF409" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG409" s="1" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="410" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A410" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="B410" s="1">
+        <v>4010</v>
+      </c>
+      <c r="C410" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="D410" s="1">
+        <v>5</v>
+      </c>
+      <c r="E410" s="1">
+        <v>0</v>
+      </c>
+      <c r="F410" s="1">
+        <v>0</v>
+      </c>
+      <c r="G410" s="1">
+        <v>1</v>
+      </c>
+      <c r="H410" s="1">
+        <v>0</v>
+      </c>
+      <c r="I410" s="1">
+        <v>0</v>
+      </c>
+      <c r="J410" s="1">
+        <v>0</v>
+      </c>
+      <c r="K410" s="1">
+        <v>1</v>
+      </c>
+      <c r="L410" s="1">
+        <v>1</v>
+      </c>
+      <c r="M410" s="39">
+        <v>100</v>
+      </c>
+      <c r="N410" s="39">
+        <v>100</v>
+      </c>
+      <c r="Q410" s="36">
+        <v>1</v>
+      </c>
+      <c r="R410" s="36">
+        <v>0</v>
+      </c>
+      <c r="S410" s="36">
+        <v>0</v>
+      </c>
+      <c r="U410" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="V410" s="1">
+        <v>0</v>
+      </c>
+      <c r="W410" s="1">
+        <v>0</v>
+      </c>
+      <c r="X410" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y410" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z410" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA410" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB410" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC410" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD410" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE410" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF410" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG410" s="1" t="s">
         <v>1537</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AG403"/>
+  <autoFilter ref="A3:AG410"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A64 A66:A1048576">
+  <conditionalFormatting sqref="A1:A64 A66:A392 A400:A1048576">
     <cfRule type="duplicateValues" dxfId="32" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65">
@@ -46538,7 +47257,7 @@
   <conditionalFormatting sqref="C10:C12">
     <cfRule type="duplicateValues" dxfId="30" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C393:C403">
+  <conditionalFormatting sqref="C400:C410">
     <cfRule type="duplicateValues" dxfId="29" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C88:C121">
@@ -60251,11 +60970,11 @@
         <v>3.75</v>
       </c>
       <c r="S6" s="12">
-        <f>VLOOKUP(K6,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K6,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="T6" s="12">
-        <f>VLOOKUP(M6,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M6,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U6" s="12"/>
@@ -60313,15 +61032,15 @@
         <v>8</v>
       </c>
       <c r="S7" s="12">
-        <f>VLOOKUP(K7,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K7,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T7" s="12">
-        <f>VLOOKUP(M7,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M7,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>220</v>
       </c>
       <c r="U7" s="12">
-        <f>VLOOKUP(O7,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O7,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>257</v>
       </c>
       <c r="V7" s="12"/>
@@ -60385,19 +61104,19 @@
         <v>0</v>
       </c>
       <c r="S8" s="12">
-        <f>VLOOKUP(K8,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K8,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T8" s="12">
-        <f>VLOOKUP(M8,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M8,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>229</v>
       </c>
       <c r="U8" s="12">
-        <f>VLOOKUP(O8,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O8,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>205</v>
       </c>
       <c r="V8" s="12">
-        <f>VLOOKUP(Q8,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q8,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>284</v>
       </c>
       <c r="X8" s="12" t="str">
@@ -60460,19 +61179,19 @@
         <v>0</v>
       </c>
       <c r="S9" s="12">
-        <f>VLOOKUP(K9,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K9,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T9" s="12">
-        <f>VLOOKUP(M9,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M9,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>218</v>
       </c>
       <c r="U9" s="12">
-        <f>VLOOKUP(O9,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O9,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V9" s="12">
-        <f>VLOOKUP(Q9,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q9,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>212</v>
       </c>
       <c r="X9" s="12" t="str">
@@ -60532,19 +61251,19 @@
         <v>0</v>
       </c>
       <c r="S10" s="12">
-        <f>VLOOKUP(K10,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K10,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T10" s="12">
-        <f>VLOOKUP(M10,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M10,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>260</v>
       </c>
       <c r="U10" s="12">
-        <f>VLOOKUP(O10,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O10,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>261</v>
       </c>
       <c r="V10" s="12">
-        <f>VLOOKUP(Q10,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q10,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>253</v>
       </c>
       <c r="X10" s="12" t="str">
@@ -60595,15 +61314,15 @@
         <v>3.75</v>
       </c>
       <c r="S11" s="12">
-        <f>VLOOKUP(K11,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K11,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>104</v>
       </c>
       <c r="T11" s="12">
-        <f>VLOOKUP(M11,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M11,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>222</v>
       </c>
       <c r="U11" s="12">
-        <f>VLOOKUP(O11,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O11,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="V11" s="12"/>
@@ -60665,19 +61384,19 @@
         <v>0</v>
       </c>
       <c r="S12" s="12">
-        <f>VLOOKUP(K12,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K12,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="T12" s="12">
-        <f>VLOOKUP(M12,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M12,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>259</v>
       </c>
       <c r="U12" s="12">
-        <f>VLOOKUP(O12,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O12,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>237</v>
       </c>
       <c r="V12" s="12">
-        <f>VLOOKUP(Q12,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q12,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>239</v>
       </c>
       <c r="X12" s="12" t="str">
@@ -60730,15 +61449,15 @@
         <v>5</v>
       </c>
       <c r="S13" s="12">
-        <f>VLOOKUP(K13,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K13,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="T13" s="12">
-        <f>VLOOKUP(M13,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M13,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>275</v>
       </c>
       <c r="U13" s="12">
-        <f>VLOOKUP(O13,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O13,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V13" s="12"/>
@@ -60799,19 +61518,19 @@
         <v>0</v>
       </c>
       <c r="S14" s="12">
-        <f>VLOOKUP(K14,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K14,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="T14" s="12">
-        <f>VLOOKUP(M14,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M14,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>227</v>
       </c>
       <c r="U14" s="12">
-        <f>VLOOKUP(O14,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O14,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>240</v>
       </c>
       <c r="V14" s="12">
-        <f>VLOOKUP(Q14,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q14,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="X14" s="12" t="str">
@@ -60871,19 +61590,19 @@
         <v>0</v>
       </c>
       <c r="S15" s="12">
-        <f>VLOOKUP(K15,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K15,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>237</v>
       </c>
       <c r="T15" s="12">
-        <f>VLOOKUP(M15,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M15,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U15" s="12">
-        <f>VLOOKUP(O15,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O15,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>256</v>
       </c>
       <c r="V15" s="12">
-        <f>VLOOKUP(Q15,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q15,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>285</v>
       </c>
       <c r="X15" s="12" t="str">
@@ -60943,19 +61662,19 @@
         <v>0</v>
       </c>
       <c r="S16" s="12">
-        <f>VLOOKUP(K16,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K16,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>269</v>
       </c>
       <c r="T16" s="12">
-        <f>VLOOKUP(M16,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M16,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="U16" s="12">
-        <f>VLOOKUP(O16,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O16,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>264</v>
       </c>
       <c r="V16" s="12">
-        <f>VLOOKUP(Q16,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q16,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>208</v>
       </c>
       <c r="X16" s="12" t="str">
@@ -61006,15 +61725,15 @@
         <v>0</v>
       </c>
       <c r="S17" s="12">
-        <f>VLOOKUP(K17,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K17,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="T17" s="12">
-        <f>VLOOKUP(M17,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M17,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U17" s="12">
-        <f>VLOOKUP(O17,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O17,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>241</v>
       </c>
       <c r="V17" s="12"/>
@@ -61068,15 +61787,15 @@
         <v>0</v>
       </c>
       <c r="S18" s="12">
-        <f>VLOOKUP(K18,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K18,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1609</v>
       </c>
       <c r="T18" s="12">
-        <f>VLOOKUP(M18,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M18,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>254</v>
       </c>
       <c r="U18" s="12">
-        <f>VLOOKUP(O18,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O18,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>211</v>
       </c>
       <c r="V18" s="12"/>
@@ -61137,19 +61856,19 @@
         <v>0</v>
       </c>
       <c r="S19" s="12">
-        <f>VLOOKUP(K19,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K19,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1609</v>
       </c>
       <c r="T19" s="12">
-        <f>VLOOKUP(M19,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M19,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>259</v>
       </c>
       <c r="U19" s="12">
-        <f>VLOOKUP(O19,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O19,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>258</v>
       </c>
       <c r="V19" s="12">
-        <f>VLOOKUP(Q19,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q19,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>263</v>
       </c>
       <c r="X19" s="12" t="str">
@@ -61209,19 +61928,19 @@
         <v>0</v>
       </c>
       <c r="S20" s="12">
-        <f>VLOOKUP(K20,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K20,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1609</v>
       </c>
       <c r="T20" s="12">
-        <f>VLOOKUP(M20,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M20,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>253</v>
       </c>
       <c r="U20" s="12">
-        <f>VLOOKUP(O20,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O20,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>260</v>
       </c>
       <c r="V20" s="12">
-        <f>VLOOKUP(Q20,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q20,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>267</v>
       </c>
       <c r="X20" s="12" t="str">
@@ -61272,15 +61991,15 @@
         <v>0</v>
       </c>
       <c r="S21" s="12">
-        <f>VLOOKUP(K21,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K21,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>238</v>
       </c>
       <c r="T21" s="12">
-        <f>VLOOKUP(M21,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M21,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>276</v>
       </c>
       <c r="U21" s="12">
-        <f>VLOOKUP(O21,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O21,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="V21" s="12"/>
@@ -61332,15 +62051,15 @@
         <v>0</v>
       </c>
       <c r="S22" s="12">
-        <f>VLOOKUP(K22,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K22,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>221</v>
       </c>
       <c r="T22" s="12">
-        <f>VLOOKUP(M22,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M22,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>276</v>
       </c>
       <c r="U22" s="12">
-        <f>VLOOKUP(O22,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O22,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="V22" s="12"/>
@@ -61394,15 +62113,15 @@
         <v>0</v>
       </c>
       <c r="S23" s="34">
-        <f>VLOOKUP(K23,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K23,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1613</v>
       </c>
       <c r="T23" s="12">
-        <f>VLOOKUP(M23,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M23,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>213</v>
       </c>
       <c r="U23" s="12">
-        <f>VLOOKUP(O23,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O23,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>246</v>
       </c>
       <c r="V23" s="12"/>
@@ -61456,15 +62175,15 @@
         <v>16.5</v>
       </c>
       <c r="S24" s="34">
-        <f>VLOOKUP(K24,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K24,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1612</v>
       </c>
       <c r="T24" s="12">
-        <f>VLOOKUP(M24,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M24,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>211</v>
       </c>
       <c r="U24" s="12">
-        <f>VLOOKUP(O24,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O24,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1612</v>
       </c>
       <c r="V24" s="12"/>
@@ -61525,19 +62244,19 @@
         <v>49.5</v>
       </c>
       <c r="S25" s="12">
-        <f>VLOOKUP(K25,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K25,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>270</v>
       </c>
       <c r="T25" s="12">
-        <f>VLOOKUP(M25,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M25,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>225</v>
       </c>
       <c r="U25" s="12">
-        <f>VLOOKUP(O25,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O25,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>239</v>
       </c>
       <c r="V25" s="12">
-        <f>VLOOKUP(Q25,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q25,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1614</v>
       </c>
       <c r="X25" s="12" t="str">
@@ -61597,19 +62316,19 @@
         <v>43.5</v>
       </c>
       <c r="S26" s="12">
-        <f>VLOOKUP(K26,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K26,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>245</v>
       </c>
       <c r="T26" s="12">
-        <f>VLOOKUP(M26,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M26,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>255</v>
       </c>
       <c r="U26" s="12">
-        <f>VLOOKUP(O26,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O26,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>268</v>
       </c>
       <c r="V26" s="12">
-        <f>VLOOKUP(Q26,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q26,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1615</v>
       </c>
       <c r="X26" s="12" t="str">
@@ -61653,11 +62372,11 @@
         <v>2</v>
       </c>
       <c r="S27" s="12">
-        <f>VLOOKUP(K27,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K27,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T27" s="12">
-        <f>VLOOKUP(M27,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M27,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>277</v>
       </c>
       <c r="U27" s="12"/>
@@ -61710,15 +62429,15 @@
         <v>0</v>
       </c>
       <c r="S28" s="12">
-        <f>VLOOKUP(K28,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K28,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="T28" s="12">
-        <f>VLOOKUP(M28,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M28,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="U28" s="12">
-        <f>VLOOKUP(O28,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O28,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="V28" s="12"/>
@@ -61770,15 +62489,15 @@
         <v>5</v>
       </c>
       <c r="S29" s="12">
-        <f>VLOOKUP(K29,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K29,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1651</v>
       </c>
       <c r="T29" s="12">
-        <f>VLOOKUP(M29,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M29,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>227</v>
       </c>
       <c r="U29" s="12">
-        <f>VLOOKUP(O29,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O29,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V29" s="12"/>
@@ -61830,15 +62549,15 @@
         <v>0</v>
       </c>
       <c r="S30" s="12">
-        <f>VLOOKUP(K30,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K30,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1651</v>
       </c>
       <c r="T30" s="12">
-        <f>VLOOKUP(M30,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M30,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>223</v>
       </c>
       <c r="U30" s="12">
-        <f>VLOOKUP(O30,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O30,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>301</v>
       </c>
       <c r="V30" s="12"/>
@@ -61883,11 +62602,11 @@
         <v>0</v>
       </c>
       <c r="S31" s="12">
-        <f>VLOOKUP(K31,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K31,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="T31" s="12">
-        <f>VLOOKUP(M31,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M31,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>205</v>
       </c>
       <c r="U31" s="12"/>
@@ -61947,19 +62666,19 @@
         <v>0</v>
       </c>
       <c r="S32" s="12">
-        <f>VLOOKUP(K32,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K32,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1654</v>
       </c>
       <c r="T32" s="12">
-        <f>VLOOKUP(M32,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M32,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>250</v>
       </c>
       <c r="U32" s="12">
-        <f>VLOOKUP(O32,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O32,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>229</v>
       </c>
       <c r="V32" s="12">
-        <f>VLOOKUP(Q32,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q32,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="X32" s="12" t="str">
@@ -62012,15 +62731,15 @@
       <c r="Q33" s="16"/>
       <c r="R33" s="34"/>
       <c r="S33" s="12">
-        <f>VLOOKUP(K33,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K33,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>202</v>
       </c>
       <c r="T33" s="12">
-        <f>VLOOKUP(M33,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M33,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1654</v>
       </c>
       <c r="U33" s="12">
-        <f>VLOOKUP(O33,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O33,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>210</v>
       </c>
       <c r="X33" s="12" t="str">
@@ -62078,15 +62797,15 @@
         <v>0</v>
       </c>
       <c r="S34" s="12">
-        <f>VLOOKUP(K34,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K34,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="T34" s="12">
-        <f>VLOOKUP(M34,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M34,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>228</v>
       </c>
       <c r="U34" s="12">
-        <f>VLOOKUP(O34,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O34,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>277</v>
       </c>
       <c r="V34" s="12"/>
@@ -62138,15 +62857,15 @@
         <v>0</v>
       </c>
       <c r="S35" s="12">
-        <f>VLOOKUP(K35,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K35,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>273</v>
       </c>
       <c r="T35" s="12">
-        <f>VLOOKUP(M35,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M35,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="U35" s="12">
-        <f>VLOOKUP(O35,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O35,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="V35" s="12"/>
@@ -62205,19 +62924,19 @@
         <v>0</v>
       </c>
       <c r="S36" s="12">
-        <f>VLOOKUP(K36,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K36,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>264</v>
       </c>
       <c r="T36" s="12">
-        <f>VLOOKUP(M36,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M36,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>277</v>
       </c>
       <c r="U36" s="12">
-        <f>VLOOKUP(O36,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O36,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>255</v>
       </c>
       <c r="V36" s="12">
-        <f>VLOOKUP(Q36,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q36,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>246</v>
       </c>
       <c r="X36" s="12" t="str">
@@ -62268,15 +62987,15 @@
         <v>0</v>
       </c>
       <c r="S37" s="12">
-        <f>VLOOKUP(K37,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K37,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1650</v>
       </c>
       <c r="T37" s="12">
-        <f>VLOOKUP(M37,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M37,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>208</v>
       </c>
       <c r="U37" s="12">
-        <f>VLOOKUP(O37,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O37,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="W37" s="12"/>
@@ -62335,19 +63054,19 @@
         <v>0</v>
       </c>
       <c r="S38" s="12">
-        <f>VLOOKUP(K38,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K38,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1651</v>
       </c>
       <c r="T38" s="12">
-        <f>VLOOKUP(M38,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M38,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>242</v>
       </c>
       <c r="U38" s="12">
-        <f>VLOOKUP(O38,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O38,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>247</v>
       </c>
       <c r="V38" s="12">
-        <f>VLOOKUP(Q38,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q38,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>241</v>
       </c>
       <c r="X38" s="12" t="str">
@@ -62405,19 +63124,19 @@
         <v>0</v>
       </c>
       <c r="S39" s="12">
-        <f>VLOOKUP(K39,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K39,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1654</v>
       </c>
       <c r="T39" s="12">
-        <f>VLOOKUP(M39,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M39,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U39" s="12">
-        <f>VLOOKUP(O39,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O39,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V39" s="12">
-        <f>VLOOKUP(Q39,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q39,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>218</v>
       </c>
       <c r="X39" s="12" t="str">
@@ -62468,15 +63187,15 @@
         <v>0</v>
       </c>
       <c r="S40" s="12">
-        <f>VLOOKUP(K40,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K40,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T40" s="12">
-        <f>VLOOKUP(M40,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M40,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="U40" s="12">
-        <f>VLOOKUP(O40,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O40,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>228</v>
       </c>
       <c r="W40" s="12"/>
@@ -62528,15 +63247,15 @@
         <v>0</v>
       </c>
       <c r="S41" s="12">
-        <f>VLOOKUP(K41,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K41,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1650</v>
       </c>
       <c r="T41" s="12">
-        <f>VLOOKUP(M41,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M41,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="U41" s="12">
-        <f>VLOOKUP(O41,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O41,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>282</v>
       </c>
       <c r="W41" s="12"/>
@@ -62595,19 +63314,19 @@
         <v>0</v>
       </c>
       <c r="S42" s="12">
-        <f>VLOOKUP(K42,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K42,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1657</v>
       </c>
       <c r="T42" s="12">
-        <f>VLOOKUP(M42,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M42,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>279</v>
       </c>
       <c r="U42" s="12">
-        <f>VLOOKUP(O42,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O42,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>234</v>
       </c>
       <c r="V42" s="12">
-        <f>VLOOKUP(Q42,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q42,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>247</v>
       </c>
       <c r="X42" s="12" t="str">
@@ -62665,19 +63384,19 @@
         <v>0</v>
       </c>
       <c r="S43" s="12">
-        <f>VLOOKUP(K43,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K43,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>248</v>
       </c>
       <c r="T43" s="12">
-        <f>VLOOKUP(M43,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M43,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1650</v>
       </c>
       <c r="U43" s="12">
-        <f>VLOOKUP(O43,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O43,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>245</v>
       </c>
       <c r="V43" s="12">
-        <f>VLOOKUP(Q43,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q43,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>285</v>
       </c>
       <c r="X43" s="12" t="str">
@@ -62728,15 +63447,15 @@
         <v>1.75</v>
       </c>
       <c r="S44" s="12">
-        <f>VLOOKUP(K44,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K44,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T44" s="12">
-        <f>VLOOKUP(M44,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M44,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>302</v>
       </c>
       <c r="U44" s="12">
-        <f>VLOOKUP(O44,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O44,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="W44" s="12"/>
@@ -62788,15 +63507,15 @@
         <v>1.75</v>
       </c>
       <c r="S45" s="12">
-        <f>VLOOKUP(K45,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K45,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="T45" s="12">
-        <f>VLOOKUP(M45,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M45,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>222</v>
       </c>
       <c r="U45" s="12">
-        <f>VLOOKUP(O45,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O45,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="W45" s="12"/>
@@ -62848,15 +63567,15 @@
         <v>0</v>
       </c>
       <c r="S46" s="12">
-        <f>VLOOKUP(K46,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K46,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="T46" s="12">
-        <f>VLOOKUP(M46,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M46,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>210</v>
       </c>
       <c r="U46" s="12">
-        <f>VLOOKUP(O46,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O46,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>202</v>
       </c>
       <c r="W46" s="12"/>
@@ -62915,15 +63634,15 @@
         <v>0</v>
       </c>
       <c r="S47" s="12">
-        <f>VLOOKUP(K47,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K47,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1701</v>
       </c>
       <c r="T47" s="12">
-        <f>VLOOKUP(M47,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M47,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>273</v>
       </c>
       <c r="U47" s="12">
-        <f>VLOOKUP(O47,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O47,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>238</v>
       </c>
       <c r="W47" s="12"/>
@@ -62975,15 +63694,15 @@
         <v>0</v>
       </c>
       <c r="S48" s="12">
-        <f>VLOOKUP(K48,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K48,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1700</v>
       </c>
       <c r="T48" s="12">
-        <f>VLOOKUP(M48,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M48,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>301</v>
       </c>
       <c r="U48" s="12">
-        <f>VLOOKUP(O48,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O48,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="W48" s="12"/>
@@ -63042,19 +63761,19 @@
         <v>0</v>
       </c>
       <c r="S49" s="12">
-        <f>VLOOKUP(K49,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K49,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1701</v>
       </c>
       <c r="T49" s="12">
-        <f>VLOOKUP(M49,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M49,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>234</v>
       </c>
       <c r="U49" s="12">
-        <f>VLOOKUP(O49,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O49,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>223</v>
       </c>
       <c r="V49" s="12">
-        <f>VLOOKUP(Q49,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q49,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>279</v>
       </c>
       <c r="X49" s="12" t="str">
@@ -63112,19 +63831,19 @@
         <v>0</v>
       </c>
       <c r="S50" s="12">
-        <f>VLOOKUP(K50,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K50,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1700</v>
       </c>
       <c r="T50" s="12">
-        <f>VLOOKUP(M50,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M50,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>280</v>
       </c>
       <c r="U50" s="12">
-        <f>VLOOKUP(O50,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O50,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="V50" s="12">
-        <f>VLOOKUP(Q50,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q50,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="X50" s="12" t="str">
@@ -63182,19 +63901,19 @@
         <v>5</v>
       </c>
       <c r="S51" s="12">
-        <f>VLOOKUP(K51,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K51,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1702</v>
       </c>
       <c r="T51" s="12">
-        <f>VLOOKUP(M51,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M51,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>275</v>
       </c>
       <c r="U51" s="12">
-        <f>VLOOKUP(O51,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O51,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>240</v>
       </c>
       <c r="V51" s="12">
-        <f>VLOOKUP(Q51,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q51,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="X51" s="12" t="str">
@@ -63252,19 +63971,19 @@
         <v>0</v>
       </c>
       <c r="S52" s="12">
-        <f>VLOOKUP(K52,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K52,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1700</v>
       </c>
       <c r="T52" s="12">
-        <f>VLOOKUP(M52,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M52,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>281</v>
       </c>
       <c r="U52" s="12">
-        <f>VLOOKUP(O52,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O52,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>251</v>
       </c>
       <c r="V52" s="12">
-        <f>VLOOKUP(Q52,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q52,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>282</v>
       </c>
       <c r="X52" s="12" t="str">
@@ -63322,19 +64041,19 @@
         <v>0</v>
       </c>
       <c r="S53" s="12">
-        <f>VLOOKUP(K53,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K53,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="T53" s="12">
-        <f>VLOOKUP(M53,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M53,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1704</v>
       </c>
       <c r="U53" s="12">
-        <f>VLOOKUP(O53,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O53,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>264</v>
       </c>
       <c r="V53" s="12">
-        <f>VLOOKUP(Q53,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q53,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>258</v>
       </c>
       <c r="X53" s="12" t="str">
@@ -63391,19 +64110,19 @@
         <v>0</v>
       </c>
       <c r="S54" s="12">
-        <f>VLOOKUP(K54,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K54,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1703</v>
       </c>
       <c r="T54" s="12">
-        <f>VLOOKUP(M54,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M54,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>282</v>
       </c>
       <c r="U54" s="12">
-        <f>VLOOKUP(O54,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(O54,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="V54" s="12">
-        <f>VLOOKUP(Q54,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(Q54,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>267</v>
       </c>
       <c r="X54" s="12" t="str">
@@ -63610,15 +64329,15 @@
         <v>474</v>
       </c>
       <c r="Q69" s="16">
-        <f>VLOOKUP(J69,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J69,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>290</v>
       </c>
       <c r="S69" s="12">
-        <f>VLOOKUP(K69,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K69,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>292</v>
       </c>
       <c r="T69" s="12">
-        <f>VLOOKUP(M69,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M69,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>244</v>
       </c>
       <c r="V69" t="str">
@@ -63647,15 +64366,15 @@
         <v>452</v>
       </c>
       <c r="Q70" s="16">
-        <f>VLOOKUP(J70,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J70,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>294</v>
       </c>
       <c r="S70" s="12">
-        <f>VLOOKUP(K70,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K70,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>265</v>
       </c>
       <c r="T70" s="12">
-        <f>VLOOKUP(M70,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M70,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>207</v>
       </c>
       <c r="V70" s="12" t="str">
@@ -63684,15 +64403,15 @@
         <v>483</v>
       </c>
       <c r="Q71" s="16">
-        <f>VLOOKUP(J71,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J71,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>251</v>
       </c>
       <c r="S71" s="12">
-        <f>VLOOKUP(K71,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K71,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>287</v>
       </c>
       <c r="T71" s="12">
-        <f>VLOOKUP(M71,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M71,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>257</v>
       </c>
       <c r="V71" s="12" t="str">
@@ -63721,15 +64440,15 @@
         <v>496</v>
       </c>
       <c r="Q72" s="16">
-        <f>VLOOKUP(J72,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J72,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>290</v>
       </c>
       <c r="S72" s="12">
-        <f>VLOOKUP(K72,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K72,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>225</v>
       </c>
       <c r="T72" s="12">
-        <f>VLOOKUP(M72,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M72,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="V72" s="12" t="str">
@@ -63758,15 +64477,15 @@
         <v>496</v>
       </c>
       <c r="Q73" s="16">
-        <f>VLOOKUP(J73,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J73,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>267</v>
       </c>
       <c r="S73" s="12">
-        <f>VLOOKUP(K73,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K73,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>261</v>
       </c>
       <c r="T73" s="12">
-        <f>VLOOKUP(M73,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M73,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="V73" s="12" t="str">
@@ -63795,15 +64514,15 @@
         <v>496</v>
       </c>
       <c r="Q74" s="16">
-        <f>VLOOKUP(J74,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J74,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>284</v>
       </c>
       <c r="S74" s="12">
-        <f>VLOOKUP(K74,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K74,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>291</v>
       </c>
       <c r="T74" s="12">
-        <f>VLOOKUP(M74,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M74,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="V74" s="12" t="str">
@@ -63830,15 +64549,15 @@
         <v>454</v>
       </c>
       <c r="Q75" s="16">
-        <f>VLOOKUP(J75,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J75,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>263</v>
       </c>
       <c r="S75" s="12">
-        <f>VLOOKUP(K75,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K75,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>255</v>
       </c>
       <c r="T75" s="12">
-        <f>VLOOKUP(M75,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M75,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>210</v>
       </c>
       <c r="V75" s="12" t="str">
@@ -63867,15 +64586,15 @@
         <v>478</v>
       </c>
       <c r="Q76" s="16">
-        <f>VLOOKUP(J76,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J76,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>236</v>
       </c>
       <c r="S76" s="12">
-        <f>VLOOKUP(K76,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K76,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>259</v>
       </c>
       <c r="T76" s="12">
-        <f>VLOOKUP(M76,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M76,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>250</v>
       </c>
       <c r="V76" s="12" t="str">
@@ -63904,15 +64623,15 @@
         <v>512</v>
       </c>
       <c r="Q77" s="16">
-        <f>VLOOKUP(J77,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J77,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>208</v>
       </c>
       <c r="S77" s="12">
-        <f>VLOOKUP(K77,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K77,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="T77" s="12">
-        <f>VLOOKUP(M77,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M77,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>281</v>
       </c>
       <c r="V77" s="12" t="str">
@@ -63941,15 +64660,15 @@
         <v>473</v>
       </c>
       <c r="Q78" s="16">
-        <f>VLOOKUP(J78,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J78,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>288</v>
       </c>
       <c r="S78" s="12">
-        <f>VLOOKUP(K78,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K78,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>256</v>
       </c>
       <c r="T78" s="12">
-        <f>VLOOKUP(M78,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M78,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>240</v>
       </c>
       <c r="V78" s="12" t="str">
@@ -63978,15 +64697,15 @@
         <v>480</v>
       </c>
       <c r="Q79" s="16">
-        <f>VLOOKUP(J79,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J79,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>293</v>
       </c>
       <c r="S79" s="12">
-        <f>VLOOKUP(K79,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K79,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>289</v>
       </c>
       <c r="T79" s="12">
-        <f>VLOOKUP(M79,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M79,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>254</v>
       </c>
       <c r="V79" s="12" t="str">
@@ -64009,15 +64728,15 @@
         <v>497</v>
       </c>
       <c r="Q80" s="16">
-        <f>VLOOKUP(J80,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J80,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="S80" s="12">
-        <f>VLOOKUP(K80,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K80,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>269</v>
       </c>
       <c r="T80" s="12">
-        <f>VLOOKUP(M80,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M80,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>291</v>
       </c>
       <c r="U80" s="12"/>
@@ -64055,11 +64774,11 @@
         <v>726</v>
       </c>
       <c r="Q83" s="16">
-        <f>VLOOKUP(J83,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J83,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>105</v>
       </c>
       <c r="S83" s="12">
-        <f>VLOOKUP(K83,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K83,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T83" s="12"/>
@@ -64087,11 +64806,11 @@
         <v>729</v>
       </c>
       <c r="Q84" s="16">
-        <f>VLOOKUP(J84,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J84,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1800</v>
       </c>
       <c r="S84" s="12">
-        <f>VLOOKUP(K84,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K84,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>285</v>
       </c>
       <c r="T84" s="12"/>
@@ -64121,15 +64840,15 @@
         <v>482</v>
       </c>
       <c r="Q85" s="16">
-        <f>VLOOKUP(J85,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J85,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="S85" s="12">
-        <f>VLOOKUP(K85,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K85,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="T85" s="12">
-        <f>VLOOKUP(M85,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M85,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>256</v>
       </c>
       <c r="W85" s="12" t="str">
@@ -64155,11 +64874,11 @@
         <v>747</v>
       </c>
       <c r="Q86" s="16">
-        <f>VLOOKUP(J86,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J86,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="S86" s="12">
-        <f>VLOOKUP(K86,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K86,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="T86" s="12"/>
@@ -64189,15 +64908,15 @@
         <v>456</v>
       </c>
       <c r="Q87" s="16">
-        <f>VLOOKUP(J87,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J87,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1803</v>
       </c>
       <c r="S87" s="12">
-        <f>VLOOKUP(K87,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K87,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>241</v>
       </c>
       <c r="T87" s="12">
-        <f>VLOOKUP(M87,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M87,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>213</v>
       </c>
       <c r="W87" s="12" t="str">
@@ -64226,15 +64945,15 @@
         <v>375</v>
       </c>
       <c r="Q88" s="16">
-        <f>VLOOKUP(J88,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J88,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="S88" s="12">
-        <f>VLOOKUP(K88,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K88,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>248</v>
       </c>
       <c r="T88" s="12">
-        <f>VLOOKUP(M88,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M88,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="W88" s="12" t="str">
@@ -64263,15 +64982,15 @@
         <v>479</v>
       </c>
       <c r="Q89" s="16">
-        <f>VLOOKUP(J89,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J89,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="S89" s="12">
-        <f>VLOOKUP(K89,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K89,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>228</v>
       </c>
       <c r="T89" s="12">
-        <f>VLOOKUP(M89,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M89,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>251</v>
       </c>
       <c r="W89" s="12" t="str">
@@ -64300,15 +65019,15 @@
         <v>469</v>
       </c>
       <c r="Q90" s="16">
-        <f>VLOOKUP(J90,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J90,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="S90" s="12">
-        <f>VLOOKUP(K90,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K90,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>279</v>
       </c>
       <c r="T90" s="12">
-        <f>VLOOKUP(M90,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M90,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>234</v>
       </c>
       <c r="W90" s="12" t="str">
@@ -64337,15 +65056,15 @@
         <v>378</v>
       </c>
       <c r="Q91" s="16">
-        <f>VLOOKUP(J91,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(J91,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>1804</v>
       </c>
       <c r="S91" s="12">
-        <f>VLOOKUP(K91,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(K91,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>288</v>
       </c>
       <c r="T91" s="12">
-        <f>VLOOKUP(M91,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(M91,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>247</v>
       </c>
       <c r="W91" s="12" t="str">
@@ -70636,7 +71355,7 @@
         <v>180</v>
       </c>
       <c r="S63" s="38">
-        <f>VLOOKUP(D63,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D63,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>301</v>
       </c>
     </row>
@@ -70698,7 +71417,7 @@
         <v>180</v>
       </c>
       <c r="S64" s="38">
-        <f>VLOOKUP(D64,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D64,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>3007</v>
       </c>
     </row>
@@ -70760,7 +71479,7 @@
         <v>405</v>
       </c>
       <c r="S65" s="38">
-        <f>VLOOKUP(D65,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D65,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>302</v>
       </c>
     </row>
@@ -70822,7 +71541,7 @@
         <v>154.28571428571428</v>
       </c>
       <c r="S66" s="38">
-        <f>VLOOKUP(D66,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D66,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>283</v>
       </c>
     </row>
@@ -70884,7 +71603,7 @@
         <v>405</v>
       </c>
       <c r="S67" s="38">
-        <f>VLOOKUP(D67,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D67,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>3008</v>
       </c>
     </row>
@@ -70946,7 +71665,7 @@
         <v>360</v>
       </c>
       <c r="S68" s="38">
-        <f>VLOOKUP(D68,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D68,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>3006</v>
       </c>
     </row>
@@ -71008,7 +71727,7 @@
         <v>480</v>
       </c>
       <c r="S69" s="38">
-        <f>VLOOKUP(D69,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D69,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>276</v>
       </c>
     </row>
@@ -71070,7 +71789,7 @@
         <v>360</v>
       </c>
       <c r="S70" s="38">
-        <f>VLOOKUP(D70,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D70,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>235</v>
       </c>
     </row>
@@ -71132,7 +71851,7 @@
         <v>405</v>
       </c>
       <c r="S71" s="38">
-        <f>VLOOKUP(D71,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D71,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>302</v>
       </c>
     </row>
@@ -71194,7 +71913,7 @@
         <v>90</v>
       </c>
       <c r="S72" s="38">
-        <f>VLOOKUP(D72,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D72,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>297</v>
       </c>
     </row>
@@ -71256,7 +71975,7 @@
         <v>180</v>
       </c>
       <c r="S73" s="38">
-        <f>VLOOKUP(D73,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D73,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>222</v>
       </c>
     </row>
@@ -71318,7 +72037,7 @@
         <v>270</v>
       </c>
       <c r="S74" s="38">
-        <f>VLOOKUP(D74,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D74,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>213</v>
       </c>
     </row>
@@ -71380,7 +72099,7 @@
         <v>900</v>
       </c>
       <c r="S75" s="38">
-        <f>VLOOKUP(D75,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D75,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>240</v>
       </c>
     </row>
@@ -71442,7 +72161,7 @@
         <v>1350</v>
       </c>
       <c r="S76" s="38">
-        <f>VLOOKUP(D76,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D76,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>260</v>
       </c>
     </row>
@@ -71504,7 +72223,7 @@
         <v>225</v>
       </c>
       <c r="S77" s="38">
-        <f>VLOOKUP(D77,ItemData!$A$4:$B$403,2,FALSE)</f>
+        <f>VLOOKUP(D77,ItemData!$A$4:$B$410,2,FALSE)</f>
         <v>203</v>
       </c>
     </row>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5692" uniqueCount="1586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5792" uniqueCount="1628">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5614,6 +5614,155 @@
   </si>
   <si>
     <t>Waterpot2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP恢复15</t>
+  </si>
+  <si>
+    <t>HP恢复50</t>
+  </si>
+  <si>
+    <t>HP恢复20</t>
+  </si>
+  <si>
+    <t>HP恢复25</t>
+  </si>
+  <si>
+    <t>HP恢复35</t>
+  </si>
+  <si>
+    <t>HP恢复80</t>
+  </si>
+  <si>
+    <t>HP恢复100</t>
+  </si>
+  <si>
+    <t>HP恢复140</t>
+  </si>
+  <si>
+    <t>HP恢复90</t>
+  </si>
+  <si>
+    <t>HP恢复80,MP恢复30,体力恢复80</t>
+  </si>
+  <si>
+    <t>HP恢复140,MP恢复80</t>
+  </si>
+  <si>
+    <t>HP恢复40</t>
+  </si>
+  <si>
+    <t>,MP恢复70</t>
+  </si>
+  <si>
+    <t>HP恢复70</t>
+  </si>
+  <si>
+    <t>HP恢复60</t>
+  </si>
+  <si>
+    <t>HP恢复120</t>
+  </si>
+  <si>
+    <t>HP恢复180</t>
+  </si>
+  <si>
+    <t>HP恢复120,MP恢复40</t>
+  </si>
+  <si>
+    <t>HP恢复160,MP恢复100</t>
+  </si>
+  <si>
+    <t>MP恢复200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力恢复100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useInfo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8478,7 +8627,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:AG412"/>
+  <dimension ref="A2:AH412"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -8493,10 +8642,11 @@
     <col min="22" max="22" width="8.375" style="1" customWidth="1"/>
     <col min="23" max="32" width="7.75" style="1" customWidth="1"/>
     <col min="33" max="33" width="50.125" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="7.75" style="1"/>
+    <col min="34" max="34" width="17.75" style="1" customWidth="1"/>
+    <col min="35" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8596,8 +8746,11 @@
       <c r="AG2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" ht="27" x14ac:dyDescent="0.15">
+      <c r="AH2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8697,8 +8850,11 @@
       <c r="AG3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH3" s="1" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>115</v>
       </c>
@@ -8790,7 +8946,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>321</v>
       </c>
@@ -8882,7 +9038,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>322</v>
       </c>
@@ -8974,7 +9130,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>323</v>
       </c>
@@ -9066,7 +9222,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>324</v>
       </c>
@@ -9158,7 +9314,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>325</v>
       </c>
@@ -9250,7 +9406,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>618</v>
       </c>
@@ -9342,7 +9498,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>616</v>
       </c>
@@ -9434,7 +9590,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>619</v>
       </c>
@@ -9526,7 +9682,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>775</v>
       </c>
@@ -9619,7 +9775,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>159</v>
       </c>
@@ -9712,7 +9868,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>772</v>
       </c>
@@ -9805,7 +9961,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>773</v>
       </c>
@@ -36892,7 +37048,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="305" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A305" s="11" t="s">
         <v>670</v>
       </c>
@@ -36984,7 +37140,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="306" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A306" s="11" t="s">
         <v>445</v>
       </c>
@@ -37076,7 +37232,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="307" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A307" s="12" t="s">
         <v>446</v>
       </c>
@@ -37168,7 +37324,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="308" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A308" s="12" t="s">
         <v>165</v>
       </c>
@@ -37260,7 +37416,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="309" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A309" s="12" t="s">
         <v>162</v>
       </c>
@@ -37352,7 +37508,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="310" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A310" s="12" t="s">
         <v>164</v>
       </c>
@@ -37444,7 +37600,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="311" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A311" s="1" t="s">
         <v>177</v>
       </c>
@@ -37536,7 +37692,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="312" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A312" s="1" t="s">
         <v>181</v>
       </c>
@@ -37628,7 +37784,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="313" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A313" s="1" t="s">
         <v>256</v>
       </c>
@@ -37720,7 +37876,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="314" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A314" s="13" t="s">
         <v>970</v>
       </c>
@@ -37812,7 +37968,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="315" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A315" s="13" t="s">
         <v>257</v>
       </c>
@@ -37911,8 +38067,11 @@
       <c r="AG315" s="34" t="s">
         <v>1424</v>
       </c>
-    </row>
-    <row r="316" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH315" s="1" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="316" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A316" s="13" t="s">
         <v>258</v>
       </c>
@@ -38011,8 +38170,11 @@
       <c r="AG316" s="34" t="s">
         <v>1425</v>
       </c>
-    </row>
-    <row r="317" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH316" s="1" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="317" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A317" s="13" t="s">
         <v>187</v>
       </c>
@@ -38111,8 +38273,11 @@
       <c r="AG317" s="34" t="s">
         <v>1426</v>
       </c>
-    </row>
-    <row r="318" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH317" s="1" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="318" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A318" s="13" t="s">
         <v>169</v>
       </c>
@@ -38211,8 +38376,11 @@
       <c r="AG318" s="34" t="s">
         <v>1427</v>
       </c>
-    </row>
-    <row r="319" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH318" s="1" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="319" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A319" s="13" t="s">
         <v>185</v>
       </c>
@@ -38311,8 +38479,11 @@
       <c r="AG319" s="34" t="s">
         <v>1428</v>
       </c>
-    </row>
-    <row r="320" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH319" s="1" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="320" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A320" s="13" t="s">
         <v>197</v>
       </c>
@@ -38411,8 +38582,11 @@
       <c r="AG320" s="34" t="s">
         <v>1429</v>
       </c>
-    </row>
-    <row r="321" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH320" s="1" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="321" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A321" s="13" t="s">
         <v>198</v>
       </c>
@@ -38511,8 +38685,11 @@
       <c r="AG321" s="34" t="s">
         <v>1430</v>
       </c>
-    </row>
-    <row r="322" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH321" s="1" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="322" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A322" s="13" t="s">
         <v>168</v>
       </c>
@@ -38611,8 +38788,11 @@
       <c r="AG322" s="34" t="s">
         <v>1431</v>
       </c>
-    </row>
-    <row r="323" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH322" s="1" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="323" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A323" s="13" t="s">
         <v>170</v>
       </c>
@@ -38711,8 +38891,11 @@
       <c r="AG323" s="34" t="s">
         <v>1432</v>
       </c>
-    </row>
-    <row r="324" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH323" s="1" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="324" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A324" s="13" t="s">
         <v>199</v>
       </c>
@@ -38811,8 +38994,11 @@
       <c r="AG324" s="34" t="s">
         <v>1433</v>
       </c>
-    </row>
-    <row r="325" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH324" s="1" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="325" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A325" s="13" t="s">
         <v>167</v>
       </c>
@@ -38911,8 +39097,11 @@
       <c r="AG325" s="34" t="s">
         <v>1434</v>
       </c>
-    </row>
-    <row r="326" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH325" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="326" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A326" s="13" t="s">
         <v>200</v>
       </c>
@@ -39011,8 +39200,11 @@
       <c r="AG326" s="34" t="s">
         <v>1435</v>
       </c>
-    </row>
-    <row r="327" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH326" s="1" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="327" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A327" s="13" t="s">
         <v>252</v>
       </c>
@@ -39111,8 +39303,11 @@
       <c r="AG327" s="34" t="s">
         <v>1436</v>
       </c>
-    </row>
-    <row r="328" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH327" s="1" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="328" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A328" s="13" t="s">
         <v>201</v>
       </c>
@@ -39211,8 +39406,11 @@
       <c r="AG328" s="34" t="s">
         <v>1437</v>
       </c>
-    </row>
-    <row r="329" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH328" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="329" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A329" s="13" t="s">
         <v>174</v>
       </c>
@@ -39311,8 +39509,11 @@
       <c r="AG329" s="34" t="s">
         <v>1438</v>
       </c>
-    </row>
-    <row r="330" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH329" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="330" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A330" s="13" t="s">
         <v>202</v>
       </c>
@@ -39411,8 +39612,11 @@
       <c r="AG330" s="34" t="s">
         <v>1439</v>
       </c>
-    </row>
-    <row r="331" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH330" s="1" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="331" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A331" s="13" t="s">
         <v>203</v>
       </c>
@@ -39511,8 +39715,11 @@
       <c r="AG331" s="34" t="s">
         <v>1440</v>
       </c>
-    </row>
-    <row r="332" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH331" s="1" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="332" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A332" s="13" t="s">
         <v>173</v>
       </c>
@@ -39611,8 +39818,11 @@
       <c r="AG332" s="34" t="s">
         <v>1441</v>
       </c>
-    </row>
-    <row r="333" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH332" s="1" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="333" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A333" s="13" t="s">
         <v>204</v>
       </c>
@@ -39711,8 +39921,11 @@
       <c r="AG333" s="34" t="s">
         <v>1442</v>
       </c>
-    </row>
-    <row r="334" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH333" s="1" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="334" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A334" s="13" t="s">
         <v>175</v>
       </c>
@@ -39811,8 +40024,11 @@
       <c r="AG334" s="34" t="s">
         <v>1443</v>
       </c>
-    </row>
-    <row r="335" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH334" s="1" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="335" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A335" s="13" t="s">
         <v>205</v>
       </c>
@@ -39911,8 +40127,11 @@
       <c r="AG335" s="34" t="s">
         <v>1444</v>
       </c>
-    </row>
-    <row r="336" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH335" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="336" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A336" s="13" t="s">
         <v>188</v>
       </c>
@@ -40011,8 +40230,11 @@
       <c r="AG336" s="34" t="s">
         <v>1445</v>
       </c>
-    </row>
-    <row r="337" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH336" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="337" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A337" s="13" t="s">
         <v>171</v>
       </c>
@@ -40111,8 +40333,11 @@
       <c r="AG337" s="34" t="s">
         <v>1446</v>
       </c>
-    </row>
-    <row r="338" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH337" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="338" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A338" s="13" t="s">
         <v>178</v>
       </c>
@@ -40211,8 +40436,11 @@
       <c r="AG338" s="34" t="s">
         <v>1447</v>
       </c>
-    </row>
-    <row r="339" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH338" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="339" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A339" s="13" t="s">
         <v>180</v>
       </c>
@@ -40311,8 +40539,11 @@
       <c r="AG339" s="34" t="s">
         <v>1448</v>
       </c>
-    </row>
-    <row r="340" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH339" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="340" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A340" s="13" t="s">
         <v>182</v>
       </c>
@@ -40411,8 +40642,11 @@
       <c r="AG340" s="34" t="s">
         <v>1449</v>
       </c>
-    </row>
-    <row r="341" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH340" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="341" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A341" s="13" t="s">
         <v>183</v>
       </c>
@@ -40511,8 +40745,11 @@
       <c r="AG341" s="34" t="s">
         <v>1450</v>
       </c>
-    </row>
-    <row r="342" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH341" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="342" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A342" s="13" t="s">
         <v>206</v>
       </c>
@@ -40611,8 +40848,11 @@
       <c r="AG342" s="34" t="s">
         <v>1451</v>
       </c>
-    </row>
-    <row r="343" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH342" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="343" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A343" s="13" t="s">
         <v>207</v>
       </c>
@@ -40711,8 +40951,11 @@
       <c r="AG343" s="34" t="s">
         <v>1452</v>
       </c>
-    </row>
-    <row r="344" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH343" s="1" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="344" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A344" s="13" t="s">
         <v>184</v>
       </c>
@@ -40811,8 +41054,11 @@
       <c r="AG344" s="34" t="s">
         <v>1453</v>
       </c>
-    </row>
-    <row r="345" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH344" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="345" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A345" s="13" t="s">
         <v>209</v>
       </c>
@@ -40911,8 +41157,11 @@
       <c r="AG345" s="34" t="s">
         <v>1454</v>
       </c>
-    </row>
-    <row r="346" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH345" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="346" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A346" s="13" t="s">
         <v>210</v>
       </c>
@@ -41011,8 +41260,11 @@
       <c r="AG346" s="34" t="s">
         <v>1455</v>
       </c>
-    </row>
-    <row r="347" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH346" s="1" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="347" spans="1:34" ht="27" x14ac:dyDescent="0.15">
       <c r="A347" s="13" t="s">
         <v>186</v>
       </c>
@@ -41111,8 +41363,11 @@
       <c r="AG347" s="34" t="s">
         <v>1456</v>
       </c>
-    </row>
-    <row r="348" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH347" s="1" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="348" spans="1:34" ht="27" x14ac:dyDescent="0.15">
       <c r="A348" s="13" t="s">
         <v>211</v>
       </c>
@@ -41211,8 +41466,11 @@
       <c r="AG348" s="34" t="s">
         <v>1457</v>
       </c>
-    </row>
-    <row r="349" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH348" s="1" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="349" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A349" s="13" t="s">
         <v>212</v>
       </c>
@@ -41311,8 +41569,11 @@
       <c r="AG349" s="34" t="s">
         <v>1458</v>
       </c>
-    </row>
-    <row r="350" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH349" s="1" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="350" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A350" s="13" t="s">
         <v>213</v>
       </c>
@@ -41411,8 +41672,11 @@
       <c r="AG350" s="34" t="s">
         <v>1459</v>
       </c>
-    </row>
-    <row r="351" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH350" s="1" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="351" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A351" s="13" t="s">
         <v>172</v>
       </c>
@@ -41511,8 +41775,11 @@
       <c r="AG351" s="34" t="s">
         <v>1460</v>
       </c>
-    </row>
-    <row r="352" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH351" s="1" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="352" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A352" s="13" t="s">
         <v>214</v>
       </c>
@@ -41611,8 +41878,11 @@
       <c r="AG352" s="34" t="s">
         <v>1461</v>
       </c>
-    </row>
-    <row r="353" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH352" s="1" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="353" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A353" s="13" t="s">
         <v>215</v>
       </c>
@@ -41711,8 +41981,11 @@
       <c r="AG353" s="34" t="s">
         <v>1462</v>
       </c>
-    </row>
-    <row r="354" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH353" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="354" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A354" s="13" t="s">
         <v>216</v>
       </c>
@@ -41811,8 +42084,11 @@
       <c r="AG354" s="34" t="s">
         <v>1463</v>
       </c>
-    </row>
-    <row r="355" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH354" s="1" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="355" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A355" s="13" t="s">
         <v>217</v>
       </c>
@@ -41911,8 +42187,11 @@
       <c r="AG355" s="34" t="s">
         <v>1464</v>
       </c>
-    </row>
-    <row r="356" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH355" s="1" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="356" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A356" s="13" t="s">
         <v>218</v>
       </c>
@@ -42011,8 +42290,11 @@
       <c r="AG356" s="34" t="s">
         <v>1465</v>
       </c>
-    </row>
-    <row r="357" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH356" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="357" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A357" s="13" t="s">
         <v>179</v>
       </c>
@@ -42111,8 +42393,11 @@
       <c r="AG357" s="34" t="s">
         <v>1466</v>
       </c>
-    </row>
-    <row r="358" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH357" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="358" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A358" s="13" t="s">
         <v>189</v>
       </c>
@@ -42211,8 +42496,11 @@
       <c r="AG358" s="34" t="s">
         <v>1467</v>
       </c>
-    </row>
-    <row r="359" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH358" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="359" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A359" s="13" t="s">
         <v>176</v>
       </c>
@@ -42311,8 +42599,11 @@
       <c r="AG359" s="34" t="s">
         <v>1468</v>
       </c>
-    </row>
-    <row r="360" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH359" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="360" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A360" s="13" t="s">
         <v>219</v>
       </c>
@@ -42411,8 +42702,11 @@
       <c r="AG360" s="34" t="s">
         <v>1469</v>
       </c>
-    </row>
-    <row r="361" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH360" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="361" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A361" s="13" t="s">
         <v>220</v>
       </c>
@@ -42511,8 +42805,11 @@
       <c r="AG361" s="34" t="s">
         <v>1470</v>
       </c>
-    </row>
-    <row r="362" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH361" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="362" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A362" s="13" t="s">
         <v>221</v>
       </c>
@@ -42611,8 +42908,11 @@
       <c r="AG362" s="34" t="s">
         <v>1471</v>
       </c>
-    </row>
-    <row r="363" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH362" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="363" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A363" s="13" t="s">
         <v>222</v>
       </c>
@@ -42711,8 +43011,11 @@
       <c r="AG363" s="34" t="s">
         <v>1472</v>
       </c>
-    </row>
-    <row r="364" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH363" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="364" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A364" s="13" t="s">
         <v>290</v>
       </c>
@@ -42811,8 +43114,11 @@
       <c r="AG364" s="34" t="s">
         <v>1473</v>
       </c>
-    </row>
-    <row r="365" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH364" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="365" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A365" s="13" t="s">
         <v>223</v>
       </c>
@@ -42911,8 +43217,11 @@
       <c r="AG365" s="34" t="s">
         <v>1474</v>
       </c>
-    </row>
-    <row r="366" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH365" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="366" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A366" s="13" t="s">
         <v>224</v>
       </c>
@@ -43011,8 +43320,11 @@
       <c r="AG366" s="34" t="s">
         <v>1475</v>
       </c>
-    </row>
-    <row r="367" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH366" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="367" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A367" s="13" t="s">
         <v>225</v>
       </c>
@@ -43111,8 +43423,11 @@
       <c r="AG367" s="34" t="s">
         <v>1476</v>
       </c>
-    </row>
-    <row r="368" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH367" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="368" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A368" s="13" t="s">
         <v>226</v>
       </c>
@@ -43211,8 +43526,11 @@
       <c r="AG368" s="34" t="s">
         <v>1477</v>
       </c>
-    </row>
-    <row r="369" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH368" s="1" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="369" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A369" s="13" t="s">
         <v>227</v>
       </c>
@@ -43311,8 +43629,11 @@
       <c r="AG369" s="34" t="s">
         <v>1478</v>
       </c>
-    </row>
-    <row r="370" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH369" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="370" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A370" s="13" t="s">
         <v>228</v>
       </c>
@@ -43411,8 +43732,11 @@
       <c r="AG370" s="34" t="s">
         <v>1479</v>
       </c>
-    </row>
-    <row r="371" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH370" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="371" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A371" s="13" t="s">
         <v>229</v>
       </c>
@@ -43511,8 +43835,11 @@
       <c r="AG371" s="34" t="s">
         <v>1480</v>
       </c>
-    </row>
-    <row r="372" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH371" s="1" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="372" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A372" s="13" t="s">
         <v>230</v>
       </c>
@@ -43611,8 +43938,11 @@
       <c r="AG372" s="34" t="s">
         <v>1481</v>
       </c>
-    </row>
-    <row r="373" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH372" s="1" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="373" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A373" s="13" t="s">
         <v>231</v>
       </c>
@@ -43711,8 +44041,11 @@
       <c r="AG373" s="34" t="s">
         <v>1482</v>
       </c>
-    </row>
-    <row r="374" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH373" s="1" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="374" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A374" s="13" t="s">
         <v>232</v>
       </c>
@@ -43811,8 +44144,11 @@
       <c r="AG374" s="34" t="s">
         <v>1483</v>
       </c>
-    </row>
-    <row r="375" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH374" s="1" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="375" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A375" s="13" t="s">
         <v>233</v>
       </c>
@@ -43911,8 +44247,11 @@
       <c r="AG375" s="34" t="s">
         <v>1484</v>
       </c>
-    </row>
-    <row r="376" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH375" s="1" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="376" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A376" s="13" t="s">
         <v>234</v>
       </c>
@@ -44011,8 +44350,11 @@
       <c r="AG376" s="34" t="s">
         <v>1485</v>
       </c>
-    </row>
-    <row r="377" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH376" s="1" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="377" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A377" s="13" t="s">
         <v>235</v>
       </c>
@@ -44111,8 +44453,11 @@
       <c r="AG377" s="34" t="s">
         <v>1486</v>
       </c>
-    </row>
-    <row r="378" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH377" s="1" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="378" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A378" s="13" t="s">
         <v>236</v>
       </c>
@@ -44211,8 +44556,11 @@
       <c r="AG378" s="34" t="s">
         <v>1487</v>
       </c>
-    </row>
-    <row r="379" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH378" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="379" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A379" s="13" t="s">
         <v>237</v>
       </c>
@@ -44311,8 +44659,11 @@
       <c r="AG379" s="34" t="s">
         <v>1488</v>
       </c>
-    </row>
-    <row r="380" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH379" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="380" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A380" s="13" t="s">
         <v>238</v>
       </c>
@@ -44411,8 +44762,11 @@
       <c r="AG380" s="34" t="s">
         <v>1489</v>
       </c>
-    </row>
-    <row r="381" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH380" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="381" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A381" s="13" t="s">
         <v>239</v>
       </c>
@@ -44511,8 +44865,11 @@
       <c r="AG381" s="34" t="s">
         <v>1490</v>
       </c>
-    </row>
-    <row r="382" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH381" s="1" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="382" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A382" s="13" t="s">
         <v>240</v>
       </c>
@@ -44611,8 +44968,11 @@
       <c r="AG382" s="34" t="s">
         <v>1491</v>
       </c>
-    </row>
-    <row r="383" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH382" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="383" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A383" s="13" t="s">
         <v>241</v>
       </c>
@@ -44711,8 +45071,11 @@
       <c r="AG383" s="34" t="s">
         <v>1492</v>
       </c>
-    </row>
-    <row r="384" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH383" s="1" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="384" spans="1:34" ht="27" x14ac:dyDescent="0.15">
       <c r="A384" s="13" t="s">
         <v>242</v>
       </c>
@@ -44811,8 +45174,11 @@
       <c r="AG384" s="34" t="s">
         <v>1493</v>
       </c>
-    </row>
-    <row r="385" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH384" s="1" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="385" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A385" s="13" t="s">
         <v>243</v>
       </c>
@@ -44911,8 +45277,11 @@
       <c r="AG385" s="34" t="s">
         <v>1494</v>
       </c>
-    </row>
-    <row r="386" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH385" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="386" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A386" s="13" t="s">
         <v>312</v>
       </c>
@@ -45011,8 +45380,11 @@
       <c r="AG386" s="34" t="s">
         <v>1495</v>
       </c>
-    </row>
-    <row r="387" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH386" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="387" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A387" s="13" t="s">
         <v>311</v>
       </c>
@@ -45111,8 +45483,11 @@
       <c r="AG387" s="34" t="s">
         <v>1496</v>
       </c>
-    </row>
-    <row r="388" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH387" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="388" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A388" s="13" t="s">
         <v>313</v>
       </c>
@@ -45211,8 +45586,11 @@
       <c r="AG388" s="34" t="s">
         <v>1497</v>
       </c>
-    </row>
-    <row r="389" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH388" s="1" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="389" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A389" s="13" t="s">
         <v>247</v>
       </c>
@@ -45311,8 +45689,11 @@
       <c r="AG389" s="34" t="s">
         <v>1498</v>
       </c>
-    </row>
-    <row r="390" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH389" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="390" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A390" s="13" t="s">
         <v>315</v>
       </c>
@@ -45411,8 +45792,11 @@
       <c r="AG390" s="34" t="s">
         <v>1499</v>
       </c>
-    </row>
-    <row r="391" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH390" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="391" spans="1:34" ht="27" x14ac:dyDescent="0.15">
       <c r="A391" s="13" t="s">
         <v>249</v>
       </c>
@@ -45511,8 +45895,11 @@
       <c r="AG391" s="34" t="s">
         <v>1500</v>
       </c>
-    </row>
-    <row r="392" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH391" s="1" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="392" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A392" s="13" t="s">
         <v>317</v>
       </c>
@@ -45611,8 +45998,11 @@
       <c r="AG392" s="34" t="s">
         <v>1501</v>
       </c>
-    </row>
-    <row r="393" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH392" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="393" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A393" s="13" t="s">
         <v>318</v>
       </c>
@@ -45711,8 +46101,11 @@
       <c r="AG393" s="34" t="s">
         <v>1502</v>
       </c>
-    </row>
-    <row r="394" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH393" s="1" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="394" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A394" s="48" t="s">
         <v>969</v>
       </c>
@@ -45811,8 +46204,11 @@
       <c r="AG394" s="34" t="s">
         <v>1503</v>
       </c>
-    </row>
-    <row r="395" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH394" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="395" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A395" s="1" t="s">
         <v>1562</v>
       </c>
@@ -45904,8 +46300,11 @@
       <c r="AG395" s="34" t="s">
         <v>1571</v>
       </c>
-    </row>
-    <row r="396" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH395" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="396" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A396" s="1" t="s">
         <v>1563</v>
       </c>
@@ -45997,8 +46396,11 @@
       <c r="AG396" s="34" t="s">
         <v>1572</v>
       </c>
-    </row>
-    <row r="397" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH396" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="397" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A397" s="1" t="s">
         <v>1564</v>
       </c>
@@ -46090,8 +46492,11 @@
       <c r="AG397" s="34" t="s">
         <v>1573</v>
       </c>
-    </row>
-    <row r="398" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH397" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="398" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A398" s="1" t="s">
         <v>1565</v>
       </c>
@@ -46183,8 +46588,11 @@
       <c r="AG398" s="34" t="s">
         <v>1574</v>
       </c>
-    </row>
-    <row r="399" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH398" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="399" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A399" s="1" t="s">
         <v>1566</v>
       </c>
@@ -46276,8 +46684,11 @@
       <c r="AG399" s="34" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="400" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH399" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="400" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A400" s="1" t="s">
         <v>1568</v>
       </c>
@@ -46369,8 +46780,11 @@
       <c r="AG400" s="34" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="401" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH400" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="401" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A401" s="1" t="s">
         <v>1567</v>
       </c>
@@ -46462,8 +46876,11 @@
       <c r="AG401" s="34" t="s">
         <v>1575</v>
       </c>
-    </row>
-    <row r="402" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH401" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="402" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A402" s="12" t="s">
         <v>627</v>
       </c>
@@ -46554,8 +46971,11 @@
       <c r="AG402" s="1" t="s">
         <v>1515</v>
       </c>
-    </row>
-    <row r="403" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH402" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="403" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A403" s="12" t="s">
         <v>628</v>
       </c>
@@ -46646,8 +47066,11 @@
       <c r="AG403" s="1" t="s">
         <v>1517</v>
       </c>
-    </row>
-    <row r="404" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH403" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="404" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A404" s="12" t="s">
         <v>629</v>
       </c>
@@ -46738,8 +47161,11 @@
       <c r="AG404" s="1" t="s">
         <v>1519</v>
       </c>
-    </row>
-    <row r="405" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH404" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="405" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A405" s="12" t="s">
         <v>630</v>
       </c>
@@ -46830,8 +47256,11 @@
       <c r="AG405" s="1" t="s">
         <v>1521</v>
       </c>
-    </row>
-    <row r="406" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH405" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="406" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A406" s="12" t="s">
         <v>631</v>
       </c>
@@ -46922,8 +47351,11 @@
       <c r="AG406" s="1" t="s">
         <v>1523</v>
       </c>
-    </row>
-    <row r="407" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH406" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="407" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A407" s="12" t="s">
         <v>632</v>
       </c>
@@ -47014,8 +47446,11 @@
       <c r="AG407" s="1" t="s">
         <v>1525</v>
       </c>
-    </row>
-    <row r="408" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH407" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="408" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A408" s="12" t="s">
         <v>633</v>
       </c>
@@ -47106,8 +47541,11 @@
       <c r="AG408" s="1" t="s">
         <v>1527</v>
       </c>
-    </row>
-    <row r="409" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH408" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="409" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A409" s="12" t="s">
         <v>634</v>
       </c>
@@ -47198,8 +47636,11 @@
       <c r="AG409" s="1" t="s">
         <v>1529</v>
       </c>
-    </row>
-    <row r="410" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH409" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="410" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A410" s="12" t="s">
         <v>635</v>
       </c>
@@ -47290,8 +47731,11 @@
       <c r="AG410" s="1" t="s">
         <v>1531</v>
       </c>
-    </row>
-    <row r="411" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH410" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="411" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A411" s="12" t="s">
         <v>636</v>
       </c>
@@ -47382,8 +47826,11 @@
       <c r="AG411" s="1" t="s">
         <v>1533</v>
       </c>
-    </row>
-    <row r="412" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH411" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="412" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A412" s="12" t="s">
         <v>637</v>
       </c>
@@ -47473,6 +47920,9 @@
       </c>
       <c r="AG412" s="1" t="s">
         <v>1535</v>
+      </c>
+      <c r="AH412" s="1" t="s">
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -5638,9 +5638,6 @@
     <t>HP恢复40</t>
   </si>
   <si>
-    <t>,MP恢复70</t>
-  </si>
-  <si>
     <t>HP恢复70</t>
   </si>
   <si>
@@ -5864,6 +5861,10 @@
   </si>
   <si>
     <t>金枪鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP恢复70</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8952,7 +8953,7 @@
         <v>6</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.15">
@@ -10995,7 +10996,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="12" t="s">
         <v>675</v>
       </c>
@@ -30840,7 +30841,7 @@
         <v>2000</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D237" s="1">
         <v>6</v>
@@ -30933,7 +30934,7 @@
         <v>2001</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D238" s="1">
         <v>6</v>
@@ -31026,7 +31027,7 @@
         <v>2002</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D239" s="1">
         <v>6</v>
@@ -31119,7 +31120,7 @@
         <v>2003</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D240" s="1">
         <v>6</v>
@@ -33723,7 +33724,7 @@
         <v>4000</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D268" s="1">
         <v>3</v>
@@ -33816,7 +33817,7 @@
         <v>4003</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D269" s="1">
         <v>3</v>
@@ -33908,7 +33909,7 @@
         <v>4004</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D270" s="1">
         <v>3</v>
@@ -34000,7 +34001,7 @@
         <v>4006</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D271" s="1">
         <v>3</v>
@@ -34093,7 +34094,7 @@
         <v>4007</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="D272" s="1">
         <v>3</v>
@@ -34186,7 +34187,7 @@
         <v>4008</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="D273" s="1">
         <v>3</v>
@@ -34371,7 +34372,7 @@
         <v>4010</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D275" s="1">
         <v>3</v>
@@ -34557,7 +34558,7 @@
         <v>4012</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D277" s="1">
         <v>3</v>
@@ -34649,7 +34650,7 @@
         <v>4013</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="D278" s="1">
         <v>3</v>
@@ -34742,7 +34743,7 @@
         <v>4014</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D279" s="1">
         <v>3</v>
@@ -34835,7 +34836,7 @@
         <v>4015</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D280" s="1">
         <v>3</v>
@@ -35021,7 +35022,7 @@
         <v>4017</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D282" s="1">
         <v>3</v>
@@ -35114,7 +35115,7 @@
         <v>4018</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="D283" s="1">
         <v>3</v>
@@ -35300,7 +35301,7 @@
         <v>4021</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D285" s="1">
         <v>3</v>
@@ -35672,7 +35673,7 @@
         <v>4100</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="D289" s="1">
         <v>3</v>
@@ -35858,7 +35859,7 @@
         <v>4103</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
@@ -35951,7 +35952,7 @@
         <v>4105</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
@@ -36044,7 +36045,7 @@
         <v>4106</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
@@ -36137,7 +36138,7 @@
         <v>4109</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -36229,7 +36230,7 @@
         <v>4110</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -36322,7 +36323,7 @@
         <v>4111</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -36415,7 +36416,7 @@
         <v>4112</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -36508,7 +36509,7 @@
         <v>4113</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -36694,7 +36695,7 @@
         <v>4115</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -36787,7 +36788,7 @@
         <v>4116</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -38375,7 +38376,7 @@
         <v>1422</v>
       </c>
       <c r="AH317" s="1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="318" spans="1:34" x14ac:dyDescent="0.15">
@@ -38581,7 +38582,7 @@
         <v>1424</v>
       </c>
       <c r="AH319" s="1" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="320" spans="1:34" x14ac:dyDescent="0.15">
@@ -38684,7 +38685,7 @@
         <v>1425</v>
       </c>
       <c r="AH320" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="321" spans="1:34" x14ac:dyDescent="0.15">
@@ -38787,7 +38788,7 @@
         <v>1426</v>
       </c>
       <c r="AH321" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="322" spans="1:34" x14ac:dyDescent="0.15">
@@ -39096,7 +39097,7 @@
         <v>1429</v>
       </c>
       <c r="AH324" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="325" spans="1:34" x14ac:dyDescent="0.15">
@@ -39302,7 +39303,7 @@
         <v>1431</v>
       </c>
       <c r="AH326" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="327" spans="1:34" x14ac:dyDescent="0.15">
@@ -39405,7 +39406,7 @@
         <v>1432</v>
       </c>
       <c r="AH327" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="328" spans="1:34" x14ac:dyDescent="0.15">
@@ -39714,7 +39715,7 @@
         <v>1435</v>
       </c>
       <c r="AH330" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="331" spans="1:34" x14ac:dyDescent="0.15">
@@ -39817,7 +39818,7 @@
         <v>1436</v>
       </c>
       <c r="AH331" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="332" spans="1:34" x14ac:dyDescent="0.15">
@@ -40023,7 +40024,7 @@
         <v>1438</v>
       </c>
       <c r="AH333" s="1" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="334" spans="1:34" x14ac:dyDescent="0.15">
@@ -41774,7 +41775,7 @@
         <v>1455</v>
       </c>
       <c r="AH350" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="351" spans="1:34" x14ac:dyDescent="0.15">
@@ -41877,7 +41878,7 @@
         <v>1456</v>
       </c>
       <c r="AH351" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="352" spans="1:34" x14ac:dyDescent="0.15">
@@ -41980,7 +41981,7 @@
         <v>1457</v>
       </c>
       <c r="AH352" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="353" spans="1:34" x14ac:dyDescent="0.15">
@@ -42186,7 +42187,7 @@
         <v>1459</v>
       </c>
       <c r="AH354" s="1" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="355" spans="1:34" x14ac:dyDescent="0.15">
@@ -42289,7 +42290,7 @@
         <v>1460</v>
       </c>
       <c r="AH355" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="356" spans="1:34" x14ac:dyDescent="0.15">
@@ -43628,7 +43629,7 @@
         <v>1473</v>
       </c>
       <c r="AH368" s="1" t="s">
-        <v>1594</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="369" spans="1:34" x14ac:dyDescent="0.15">
@@ -43937,7 +43938,7 @@
         <v>1476</v>
       </c>
       <c r="AH371" s="1" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="372" spans="1:34" x14ac:dyDescent="0.15">
@@ -44040,7 +44041,7 @@
         <v>1477</v>
       </c>
       <c r="AH372" s="1" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="373" spans="1:34" x14ac:dyDescent="0.15">
@@ -44143,7 +44144,7 @@
         <v>1478</v>
       </c>
       <c r="AH373" s="1" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="374" spans="1:34" x14ac:dyDescent="0.15">
@@ -44246,7 +44247,7 @@
         <v>1479</v>
       </c>
       <c r="AH374" s="1" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="375" spans="1:34" x14ac:dyDescent="0.15">
@@ -44349,7 +44350,7 @@
         <v>1480</v>
       </c>
       <c r="AH375" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="376" spans="1:34" x14ac:dyDescent="0.15">
@@ -44452,7 +44453,7 @@
         <v>1481</v>
       </c>
       <c r="AH376" s="1" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="377" spans="1:34" x14ac:dyDescent="0.15">
@@ -44555,7 +44556,7 @@
         <v>1482</v>
       </c>
       <c r="AH377" s="1" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="378" spans="1:34" x14ac:dyDescent="0.15">
@@ -44967,7 +44968,7 @@
         <v>1486</v>
       </c>
       <c r="AH381" s="1" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="382" spans="1:34" x14ac:dyDescent="0.15">
@@ -45070,7 +45071,7 @@
         <v>1487</v>
       </c>
       <c r="AH382" s="1" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="383" spans="1:34" x14ac:dyDescent="0.15">
@@ -45173,7 +45174,7 @@
         <v>1488</v>
       </c>
       <c r="AH383" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="384" spans="1:34" ht="27" x14ac:dyDescent="0.15">
@@ -45276,7 +45277,7 @@
         <v>1489</v>
       </c>
       <c r="AH384" s="1" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="385" spans="1:34" x14ac:dyDescent="0.15">
@@ -45688,7 +45689,7 @@
         <v>1493</v>
       </c>
       <c r="AH388" s="1" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="389" spans="1:34" x14ac:dyDescent="0.15">
@@ -45997,7 +45998,7 @@
         <v>1496</v>
       </c>
       <c r="AH391" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="392" spans="1:34" x14ac:dyDescent="0.15">
@@ -46203,7 +46204,7 @@
         <v>1498</v>
       </c>
       <c r="AH393" s="1" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="394" spans="1:34" x14ac:dyDescent="0.15">

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -4909,9 +4909,6 @@
     <t>味道鲜美独特，是危险与美味并存的精灵。</t>
   </si>
   <si>
-    <t>母在海洋表层漂浮，姿态轻盈，是海洋里的透明仙子。</t>
-  </si>
-  <si>
     <t>在近岸礁石区域游，外形硬朗，游姿沉稳，味道鲜美。</t>
   </si>
   <si>
@@ -5865,6 +5862,10 @@
   </si>
   <si>
     <t>MP恢复70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在海洋表层漂浮，姿态轻盈，是海洋里的透明仙子。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8953,7 +8954,7 @@
         <v>6</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.15">
@@ -10251,7 +10252,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B18" s="1">
         <v>23</v>
@@ -17119,7 +17120,7 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A91" s="12" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B91" s="1">
         <v>271</v>
@@ -30841,7 +30842,7 @@
         <v>2000</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D237" s="1">
         <v>6</v>
@@ -30928,13 +30929,13 @@
     </row>
     <row r="238" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A238" s="1" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B238" s="1">
         <v>2001</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D238" s="1">
         <v>6</v>
@@ -31016,7 +31017,7 @@
         <v>100</v>
       </c>
       <c r="AG238" s="1" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="239" spans="1:33" x14ac:dyDescent="0.15">
@@ -31027,7 +31028,7 @@
         <v>2002</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D239" s="1">
         <v>6</v>
@@ -31120,7 +31121,7 @@
         <v>2003</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D240" s="1">
         <v>6</v>
@@ -32602,13 +32603,13 @@
     </row>
     <row r="256" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B256" s="1">
         <v>2115</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D256" s="1">
         <v>6</v>
@@ -32690,18 +32691,18 @@
         <v>300</v>
       </c>
       <c r="AG256" s="1" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="257" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B257" s="1">
         <v>2116</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="D257" s="1">
         <v>6</v>
@@ -32783,7 +32784,7 @@
         <v>600</v>
       </c>
       <c r="AG257" s="1" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="258" spans="1:33" x14ac:dyDescent="0.15">
@@ -32881,13 +32882,13 @@
     </row>
     <row r="259" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B259" s="1">
         <v>2201</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D259" s="1">
         <v>10</v>
@@ -32969,18 +32970,18 @@
         <v>0</v>
       </c>
       <c r="AG259" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="260" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A260" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B260" s="1">
         <v>2202</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D260" s="1">
         <v>10</v>
@@ -33062,18 +33063,18 @@
         <v>0</v>
       </c>
       <c r="AG260" s="3" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="261" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A261" s="8" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B261" s="1">
         <v>2203</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D261" s="1">
         <v>10</v>
@@ -33155,18 +33156,18 @@
         <v>0</v>
       </c>
       <c r="AG261" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="262" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A262" s="8" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B262" s="1">
         <v>2204</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D262" s="1">
         <v>10</v>
@@ -33248,18 +33249,18 @@
         <v>0</v>
       </c>
       <c r="AG262" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="263" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A263" s="8" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B263" s="1">
         <v>2205</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D263" s="1">
         <v>10</v>
@@ -33341,18 +33342,18 @@
         <v>0</v>
       </c>
       <c r="AG263" s="8" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="264" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A264" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B264" s="1">
         <v>2206</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D264" s="1">
         <v>10</v>
@@ -33434,18 +33435,18 @@
         <v>0</v>
       </c>
       <c r="AG264" s="8" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="265" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A265" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B265" s="1">
         <v>2207</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D265" s="1">
         <v>10</v>
@@ -33527,18 +33528,18 @@
         <v>0</v>
       </c>
       <c r="AG265" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="266" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A266" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B266" s="1">
         <v>2208</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D266" s="1">
         <v>10</v>
@@ -33620,18 +33621,18 @@
         <v>0</v>
       </c>
       <c r="AG266" s="8" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="267" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A267" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B267" s="1">
         <v>2209</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D267" s="1">
         <v>10</v>
@@ -33713,7 +33714,7 @@
         <v>0</v>
       </c>
       <c r="AG267" s="8" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="268" spans="1:33" ht="14.25" x14ac:dyDescent="0.15">
@@ -33724,7 +33725,7 @@
         <v>4000</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D268" s="1">
         <v>3</v>
@@ -33817,7 +33818,7 @@
         <v>4003</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D269" s="1">
         <v>3</v>
@@ -33909,7 +33910,7 @@
         <v>4004</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D270" s="1">
         <v>3</v>
@@ -34001,7 +34002,7 @@
         <v>4006</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D271" s="1">
         <v>3</v>
@@ -34088,13 +34089,13 @@
     </row>
     <row r="272" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A272" s="7" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B272" s="1">
         <v>4007</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D272" s="1">
         <v>3</v>
@@ -34187,7 +34188,7 @@
         <v>4008</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="D273" s="1">
         <v>3</v>
@@ -34372,7 +34373,7 @@
         <v>4010</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="D275" s="1">
         <v>3</v>
@@ -34459,13 +34460,13 @@
     </row>
     <row r="276" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A276" s="7" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B276" s="1">
         <v>4011</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D276" s="1">
         <v>3</v>
@@ -34558,7 +34559,7 @@
         <v>4012</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D277" s="1">
         <v>3</v>
@@ -34650,7 +34651,7 @@
         <v>4013</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D278" s="1">
         <v>3</v>
@@ -34743,7 +34744,7 @@
         <v>4014</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="D279" s="1">
         <v>3</v>
@@ -34836,7 +34837,7 @@
         <v>4015</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D280" s="1">
         <v>3</v>
@@ -35022,7 +35023,7 @@
         <v>4017</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D282" s="1">
         <v>3</v>
@@ -35115,7 +35116,7 @@
         <v>4018</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D283" s="1">
         <v>3</v>
@@ -35301,7 +35302,7 @@
         <v>4021</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="D285" s="1">
         <v>3</v>
@@ -35673,7 +35674,7 @@
         <v>4100</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D289" s="1">
         <v>3</v>
@@ -35859,7 +35860,7 @@
         <v>4103</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
@@ -35952,7 +35953,7 @@
         <v>4105</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
@@ -36045,7 +36046,7 @@
         <v>4106</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
@@ -36138,7 +36139,7 @@
         <v>4109</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -36230,7 +36231,7 @@
         <v>4110</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -36312,7 +36313,7 @@
         <v>0</v>
       </c>
       <c r="AG295" s="8" t="s">
-        <v>1400</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="296" spans="1:33" x14ac:dyDescent="0.15">
@@ -36323,7 +36324,7 @@
         <v>4111</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -36405,7 +36406,7 @@
         <v>0</v>
       </c>
       <c r="AG296" s="8" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="297" spans="1:33" x14ac:dyDescent="0.15">
@@ -36416,7 +36417,7 @@
         <v>4112</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -36498,7 +36499,7 @@
         <v>0</v>
       </c>
       <c r="AG297" s="8" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="298" spans="1:33" x14ac:dyDescent="0.15">
@@ -36509,7 +36510,7 @@
         <v>4113</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -36591,7 +36592,7 @@
         <v>0</v>
       </c>
       <c r="AG298" s="8" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="299" spans="1:33" x14ac:dyDescent="0.15">
@@ -36684,7 +36685,7 @@
         <v>0</v>
       </c>
       <c r="AG299" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="300" spans="1:33" x14ac:dyDescent="0.15">
@@ -36695,7 +36696,7 @@
         <v>4115</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -36777,7 +36778,7 @@
         <v>0</v>
       </c>
       <c r="AG300" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="301" spans="1:33" x14ac:dyDescent="0.15">
@@ -36788,7 +36789,7 @@
         <v>4116</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -36870,7 +36871,7 @@
         <v>0</v>
       </c>
       <c r="AG301" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="302" spans="1:33" x14ac:dyDescent="0.15">
@@ -36963,7 +36964,7 @@
         <v>0</v>
       </c>
       <c r="AG302" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="303" spans="1:33" x14ac:dyDescent="0.15">
@@ -37055,7 +37056,7 @@
         <v>0</v>
       </c>
       <c r="AG303" s="34" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="304" spans="1:33" x14ac:dyDescent="0.15">
@@ -37147,7 +37148,7 @@
         <v>0</v>
       </c>
       <c r="AG304" s="34" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="305" spans="1:34" x14ac:dyDescent="0.15">
@@ -37239,7 +37240,7 @@
         <v>0</v>
       </c>
       <c r="AG305" s="34" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="306" spans="1:34" x14ac:dyDescent="0.15">
@@ -37331,7 +37332,7 @@
         <v>0</v>
       </c>
       <c r="AG306" s="34" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="307" spans="1:34" x14ac:dyDescent="0.15">
@@ -37423,7 +37424,7 @@
         <v>0</v>
       </c>
       <c r="AG307" s="34" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="308" spans="1:34" x14ac:dyDescent="0.15">
@@ -37515,7 +37516,7 @@
         <v>0</v>
       </c>
       <c r="AG308" s="34" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="309" spans="1:34" x14ac:dyDescent="0.15">
@@ -37607,7 +37608,7 @@
         <v>0</v>
       </c>
       <c r="AG309" s="34" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="310" spans="1:34" x14ac:dyDescent="0.15">
@@ -37699,7 +37700,7 @@
         <v>0</v>
       </c>
       <c r="AG310" s="34" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="311" spans="1:34" x14ac:dyDescent="0.15">
@@ -37791,7 +37792,7 @@
         <v>0</v>
       </c>
       <c r="AG311" s="34" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="312" spans="1:34" x14ac:dyDescent="0.15">
@@ -37883,7 +37884,7 @@
         <v>0</v>
       </c>
       <c r="AG312" s="34" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="313" spans="1:34" x14ac:dyDescent="0.15">
@@ -37975,7 +37976,7 @@
         <v>0</v>
       </c>
       <c r="AG313" s="34" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="314" spans="1:34" x14ac:dyDescent="0.15">
@@ -38067,7 +38068,7 @@
         <v>0</v>
       </c>
       <c r="AG314" s="34" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="315" spans="1:34" x14ac:dyDescent="0.15">
@@ -38167,10 +38168,10 @@
         <v>0</v>
       </c>
       <c r="AG315" s="34" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="AH315" s="1" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="316" spans="1:34" x14ac:dyDescent="0.15">
@@ -38270,10 +38271,10 @@
         <v>0</v>
       </c>
       <c r="AG316" s="34" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="AH316" s="1" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="317" spans="1:34" x14ac:dyDescent="0.15">
@@ -38373,10 +38374,10 @@
         <v>8</v>
       </c>
       <c r="AG317" s="34" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="AH317" s="1" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="318" spans="1:34" x14ac:dyDescent="0.15">
@@ -38476,10 +38477,10 @@
         <v>0</v>
       </c>
       <c r="AG318" s="34" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="AH318" s="1" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="319" spans="1:34" x14ac:dyDescent="0.15">
@@ -38579,10 +38580,10 @@
         <v>0</v>
       </c>
       <c r="AG319" s="34" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="AH319" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="320" spans="1:34" x14ac:dyDescent="0.15">
@@ -38682,10 +38683,10 @@
         <v>0</v>
       </c>
       <c r="AG320" s="34" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="AH320" s="1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="321" spans="1:34" x14ac:dyDescent="0.15">
@@ -38785,10 +38786,10 @@
         <v>0</v>
       </c>
       <c r="AG321" s="34" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="AH321" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="322" spans="1:34" x14ac:dyDescent="0.15">
@@ -38888,10 +38889,10 @@
         <v>0</v>
       </c>
       <c r="AG322" s="34" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="AH322" s="1" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="323" spans="1:34" x14ac:dyDescent="0.15">
@@ -38991,10 +38992,10 @@
         <v>0</v>
       </c>
       <c r="AG323" s="34" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="AH323" s="1" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="324" spans="1:34" x14ac:dyDescent="0.15">
@@ -39094,10 +39095,10 @@
         <v>0</v>
       </c>
       <c r="AG324" s="34" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="AH324" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="325" spans="1:34" x14ac:dyDescent="0.15">
@@ -39197,7 +39198,7 @@
         <v>8</v>
       </c>
       <c r="AG325" s="34" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="AH325" s="1" t="s">
         <v>636</v>
@@ -39300,10 +39301,10 @@
         <v>0</v>
       </c>
       <c r="AG326" s="34" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="AH326" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="327" spans="1:34" x14ac:dyDescent="0.15">
@@ -39403,10 +39404,10 @@
         <v>0</v>
       </c>
       <c r="AG327" s="34" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="AH327" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="328" spans="1:34" x14ac:dyDescent="0.15">
@@ -39506,7 +39507,7 @@
         <v>8</v>
       </c>
       <c r="AG328" s="34" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="AH328" s="1" t="s">
         <v>636</v>
@@ -39609,7 +39610,7 @@
         <v>8</v>
       </c>
       <c r="AG329" s="34" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="AH329" s="1" t="s">
         <v>636</v>
@@ -39712,10 +39713,10 @@
         <v>0</v>
       </c>
       <c r="AG330" s="34" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="AH330" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="331" spans="1:34" x14ac:dyDescent="0.15">
@@ -39815,10 +39816,10 @@
         <v>0</v>
       </c>
       <c r="AG331" s="34" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="AH331" s="1" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="332" spans="1:34" x14ac:dyDescent="0.15">
@@ -39918,10 +39919,10 @@
         <v>0</v>
       </c>
       <c r="AG332" s="34" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="AH332" s="1" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="333" spans="1:34" x14ac:dyDescent="0.15">
@@ -40021,10 +40022,10 @@
         <v>0</v>
       </c>
       <c r="AG333" s="34" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="AH333" s="1" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="334" spans="1:34" x14ac:dyDescent="0.15">
@@ -40124,10 +40125,10 @@
         <v>0</v>
       </c>
       <c r="AG334" s="34" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="AH334" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="335" spans="1:34" x14ac:dyDescent="0.15">
@@ -40227,7 +40228,7 @@
         <v>8</v>
       </c>
       <c r="AG335" s="34" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AH335" s="1" t="s">
         <v>636</v>
@@ -40330,7 +40331,7 @@
         <v>8</v>
       </c>
       <c r="AG336" s="34" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AH336" s="1" t="s">
         <v>636</v>
@@ -40433,7 +40434,7 @@
         <v>8</v>
       </c>
       <c r="AG337" s="34" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="AH337" s="1" t="s">
         <v>636</v>
@@ -40536,7 +40537,7 @@
         <v>8</v>
       </c>
       <c r="AG338" s="34" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="AH338" s="1" t="s">
         <v>636</v>
@@ -40639,7 +40640,7 @@
         <v>8</v>
       </c>
       <c r="AG339" s="34" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="AH339" s="1" t="s">
         <v>636</v>
@@ -40742,7 +40743,7 @@
         <v>8</v>
       </c>
       <c r="AG340" s="34" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="AH340" s="1" t="s">
         <v>636</v>
@@ -40845,7 +40846,7 @@
         <v>8</v>
       </c>
       <c r="AG341" s="34" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="AH341" s="1" t="s">
         <v>636</v>
@@ -40948,7 +40949,7 @@
         <v>8</v>
       </c>
       <c r="AG342" s="34" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="AH342" s="1" t="s">
         <v>636</v>
@@ -41051,10 +41052,10 @@
         <v>0</v>
       </c>
       <c r="AG343" s="34" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="AH343" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="344" spans="1:34" x14ac:dyDescent="0.15">
@@ -41154,7 +41155,7 @@
         <v>8</v>
       </c>
       <c r="AG344" s="34" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="AH344" s="1" t="s">
         <v>636</v>
@@ -41257,7 +41258,7 @@
         <v>0</v>
       </c>
       <c r="AG345" s="34" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="AH345" s="1" t="s">
         <v>636</v>
@@ -41360,10 +41361,10 @@
         <v>0</v>
       </c>
       <c r="AG346" s="34" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="AH346" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="347" spans="1:34" ht="27" x14ac:dyDescent="0.15">
@@ -41463,10 +41464,10 @@
         <v>0</v>
       </c>
       <c r="AG347" s="34" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="AH347" s="1" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="348" spans="1:34" ht="27" x14ac:dyDescent="0.15">
@@ -41566,10 +41567,10 @@
         <v>0</v>
       </c>
       <c r="AG348" s="34" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="AH348" s="1" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="349" spans="1:34" x14ac:dyDescent="0.15">
@@ -41669,10 +41670,10 @@
         <v>0</v>
       </c>
       <c r="AG349" s="34" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="AH349" s="1" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="350" spans="1:34" x14ac:dyDescent="0.15">
@@ -41772,10 +41773,10 @@
         <v>0</v>
       </c>
       <c r="AG350" s="34" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="AH350" s="1" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="351" spans="1:34" x14ac:dyDescent="0.15">
@@ -41875,10 +41876,10 @@
         <v>0</v>
       </c>
       <c r="AG351" s="34" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="AH351" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="352" spans="1:34" x14ac:dyDescent="0.15">
@@ -41978,10 +41979,10 @@
         <v>8</v>
       </c>
       <c r="AG352" s="34" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="AH352" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="353" spans="1:34" x14ac:dyDescent="0.15">
@@ -42081,7 +42082,7 @@
         <v>8</v>
       </c>
       <c r="AG353" s="34" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="AH353" s="1" t="s">
         <v>636</v>
@@ -42184,10 +42185,10 @@
         <v>0</v>
       </c>
       <c r="AG354" s="34" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="AH354" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="355" spans="1:34" x14ac:dyDescent="0.15">
@@ -42287,10 +42288,10 @@
         <v>8</v>
       </c>
       <c r="AG355" s="34" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="AH355" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="356" spans="1:34" x14ac:dyDescent="0.15">
@@ -42390,7 +42391,7 @@
         <v>8</v>
       </c>
       <c r="AG356" s="34" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="AH356" s="1" t="s">
         <v>636</v>
@@ -42493,7 +42494,7 @@
         <v>8</v>
       </c>
       <c r="AG357" s="34" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="AH357" s="1" t="s">
         <v>636</v>
@@ -42596,7 +42597,7 @@
         <v>8</v>
       </c>
       <c r="AG358" s="34" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="AH358" s="1" t="s">
         <v>636</v>
@@ -42699,7 +42700,7 @@
         <v>8</v>
       </c>
       <c r="AG359" s="34" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="AH359" s="1" t="s">
         <v>636</v>
@@ -42802,7 +42803,7 @@
         <v>8</v>
       </c>
       <c r="AG360" s="34" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="AH360" s="1" t="s">
         <v>636</v>
@@ -42905,7 +42906,7 @@
         <v>8</v>
       </c>
       <c r="AG361" s="34" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="AH361" s="1" t="s">
         <v>636</v>
@@ -43008,7 +43009,7 @@
         <v>8</v>
       </c>
       <c r="AG362" s="34" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="AH362" s="1" t="s">
         <v>636</v>
@@ -43111,7 +43112,7 @@
         <v>8</v>
       </c>
       <c r="AG363" s="34" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="AH363" s="1" t="s">
         <v>636</v>
@@ -43214,7 +43215,7 @@
         <v>8</v>
       </c>
       <c r="AG364" s="34" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="AH364" s="1" t="s">
         <v>636</v>
@@ -43317,7 +43318,7 @@
         <v>8</v>
       </c>
       <c r="AG365" s="34" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="AH365" s="1" t="s">
         <v>636</v>
@@ -43420,7 +43421,7 @@
         <v>8</v>
       </c>
       <c r="AG366" s="34" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="AH366" s="1" t="s">
         <v>636</v>
@@ -43523,7 +43524,7 @@
         <v>8</v>
       </c>
       <c r="AG367" s="34" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="AH367" s="1" t="s">
         <v>636</v>
@@ -43626,10 +43627,10 @@
         <v>0</v>
       </c>
       <c r="AG368" s="34" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="AH368" s="1" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="369" spans="1:34" x14ac:dyDescent="0.15">
@@ -43729,7 +43730,7 @@
         <v>8</v>
       </c>
       <c r="AG369" s="34" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="AH369" s="1" t="s">
         <v>636</v>
@@ -43832,7 +43833,7 @@
         <v>8</v>
       </c>
       <c r="AG370" s="34" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="AH370" s="1" t="s">
         <v>636</v>
@@ -43935,10 +43936,10 @@
         <v>0</v>
       </c>
       <c r="AG371" s="34" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="AH371" s="1" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="372" spans="1:34" x14ac:dyDescent="0.15">
@@ -44038,10 +44039,10 @@
         <v>0</v>
       </c>
       <c r="AG372" s="34" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="AH372" s="1" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="373" spans="1:34" x14ac:dyDescent="0.15">
@@ -44141,10 +44142,10 @@
         <v>0</v>
       </c>
       <c r="AG373" s="34" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="AH373" s="1" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="374" spans="1:34" x14ac:dyDescent="0.15">
@@ -44244,10 +44245,10 @@
         <v>0</v>
       </c>
       <c r="AG374" s="34" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="AH374" s="1" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="375" spans="1:34" x14ac:dyDescent="0.15">
@@ -44347,10 +44348,10 @@
         <v>0</v>
       </c>
       <c r="AG375" s="34" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="AH375" s="1" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="376" spans="1:34" x14ac:dyDescent="0.15">
@@ -44450,10 +44451,10 @@
         <v>0</v>
       </c>
       <c r="AG376" s="34" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="AH376" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="377" spans="1:34" x14ac:dyDescent="0.15">
@@ -44553,10 +44554,10 @@
         <v>0</v>
       </c>
       <c r="AG377" s="34" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AH377" s="1" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="378" spans="1:34" x14ac:dyDescent="0.15">
@@ -44656,7 +44657,7 @@
         <v>8</v>
       </c>
       <c r="AG378" s="34" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="AH378" s="1" t="s">
         <v>636</v>
@@ -44759,7 +44760,7 @@
         <v>8</v>
       </c>
       <c r="AG379" s="34" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="AH379" s="1" t="s">
         <v>636</v>
@@ -44862,7 +44863,7 @@
         <v>8</v>
       </c>
       <c r="AG380" s="34" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="AH380" s="1" t="s">
         <v>636</v>
@@ -44965,10 +44966,10 @@
         <v>8</v>
       </c>
       <c r="AG381" s="34" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="AH381" s="1" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="382" spans="1:34" x14ac:dyDescent="0.15">
@@ -45068,10 +45069,10 @@
         <v>0</v>
       </c>
       <c r="AG382" s="34" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="AH382" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="383" spans="1:34" x14ac:dyDescent="0.15">
@@ -45171,10 +45172,10 @@
         <v>8</v>
       </c>
       <c r="AG383" s="34" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="AH383" s="1" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="384" spans="1:34" ht="27" x14ac:dyDescent="0.15">
@@ -45274,10 +45275,10 @@
         <v>0</v>
       </c>
       <c r="AG384" s="34" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="AH384" s="1" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="385" spans="1:34" x14ac:dyDescent="0.15">
@@ -45377,7 +45378,7 @@
         <v>8</v>
       </c>
       <c r="AG385" s="34" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="AH385" s="1" t="s">
         <v>636</v>
@@ -45480,7 +45481,7 @@
         <v>8</v>
       </c>
       <c r="AG386" s="34" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="AH386" s="1" t="s">
         <v>636</v>
@@ -45583,7 +45584,7 @@
         <v>8</v>
       </c>
       <c r="AG387" s="34" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="AH387" s="1" t="s">
         <v>636</v>
@@ -45686,10 +45687,10 @@
         <v>0</v>
       </c>
       <c r="AG388" s="34" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="AH388" s="1" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="389" spans="1:34" x14ac:dyDescent="0.15">
@@ -45789,7 +45790,7 @@
         <v>8</v>
       </c>
       <c r="AG389" s="34" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="AH389" s="1" t="s">
         <v>636</v>
@@ -45892,7 +45893,7 @@
         <v>8</v>
       </c>
       <c r="AG390" s="34" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="AH390" s="1" t="s">
         <v>636</v>
@@ -45995,10 +45996,10 @@
         <v>0</v>
       </c>
       <c r="AG391" s="34" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="AH391" s="1" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="392" spans="1:34" x14ac:dyDescent="0.15">
@@ -46098,7 +46099,7 @@
         <v>8</v>
       </c>
       <c r="AG392" s="34" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AH392" s="1" t="s">
         <v>636</v>
@@ -46201,10 +46202,10 @@
         <v>0</v>
       </c>
       <c r="AG393" s="34" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="AH393" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="394" spans="1:34" x14ac:dyDescent="0.15">
@@ -46304,7 +46305,7 @@
         <v>8</v>
       </c>
       <c r="AG394" s="34" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="AH394" s="1" t="s">
         <v>636</v>
@@ -46312,13 +46313,13 @@
     </row>
     <row r="395" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A395" s="1" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B395" s="1">
         <v>3500</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D395" s="1">
         <v>11</v>
@@ -46400,7 +46401,7 @@
         <v>0</v>
       </c>
       <c r="AG395" s="34" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="AH395" s="1" t="s">
         <v>636</v>
@@ -46408,13 +46409,13 @@
     </row>
     <row r="396" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A396" s="1" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B396" s="1">
         <v>3501</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D396" s="1">
         <v>11</v>
@@ -46496,7 +46497,7 @@
         <v>0</v>
       </c>
       <c r="AG396" s="34" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="AH396" s="1" t="s">
         <v>636</v>
@@ -46504,13 +46505,13 @@
     </row>
     <row r="397" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A397" s="1" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B397" s="1">
         <v>3502</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D397" s="1">
         <v>11</v>
@@ -46592,7 +46593,7 @@
         <v>0</v>
       </c>
       <c r="AG397" s="34" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="AH397" s="1" t="s">
         <v>636</v>
@@ -46600,13 +46601,13 @@
     </row>
     <row r="398" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A398" s="1" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B398" s="1">
         <v>3503</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D398" s="1">
         <v>11</v>
@@ -46688,7 +46689,7 @@
         <v>0</v>
       </c>
       <c r="AG398" s="34" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="AH398" s="1" t="s">
         <v>636</v>
@@ -46696,13 +46697,13 @@
     </row>
     <row r="399" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A399" s="1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B399" s="1">
         <v>3504</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D399" s="1">
         <v>11</v>
@@ -46784,7 +46785,7 @@
         <v>0</v>
       </c>
       <c r="AG399" s="34" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="AH399" s="1" t="s">
         <v>636</v>
@@ -46792,13 +46793,13 @@
     </row>
     <row r="400" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A400" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B400" s="1">
         <v>3505</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D400" s="1">
         <v>11</v>
@@ -46880,7 +46881,7 @@
         <v>0</v>
       </c>
       <c r="AG400" s="34" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AH400" s="1" t="s">
         <v>636</v>
@@ -46888,13 +46889,13 @@
     </row>
     <row r="401" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A401" s="1" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B401" s="1">
         <v>3506</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D401" s="1">
         <v>11</v>
@@ -46976,7 +46977,7 @@
         <v>0</v>
       </c>
       <c r="AG401" s="34" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="AH401" s="1" t="s">
         <v>636</v>
@@ -47071,7 +47072,7 @@
         <v>0</v>
       </c>
       <c r="AG402" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="AH402" s="1" t="s">
         <v>636</v>
@@ -47166,7 +47167,7 @@
         <v>0</v>
       </c>
       <c r="AG403" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="AH403" s="1" t="s">
         <v>636</v>
@@ -47261,7 +47262,7 @@
         <v>0</v>
       </c>
       <c r="AG404" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="AH404" s="1" t="s">
         <v>636</v>
@@ -47356,7 +47357,7 @@
         <v>0</v>
       </c>
       <c r="AG405" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="AH405" s="1" t="s">
         <v>636</v>
@@ -47451,7 +47452,7 @@
         <v>0</v>
       </c>
       <c r="AG406" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="AH406" s="1" t="s">
         <v>636</v>
@@ -47546,7 +47547,7 @@
         <v>0</v>
       </c>
       <c r="AG407" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="AH407" s="1" t="s">
         <v>636</v>
@@ -47641,7 +47642,7 @@
         <v>0</v>
       </c>
       <c r="AG408" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="AH408" s="1" t="s">
         <v>636</v>
@@ -47736,7 +47737,7 @@
         <v>0</v>
       </c>
       <c r="AG409" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="AH409" s="1" t="s">
         <v>636</v>
@@ -47831,7 +47832,7 @@
         <v>0</v>
       </c>
       <c r="AG410" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="AH410" s="1" t="s">
         <v>636</v>
@@ -47926,7 +47927,7 @@
         <v>0</v>
       </c>
       <c r="AG411" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="AH411" s="1" t="s">
         <v>636</v>
@@ -48021,7 +48022,7 @@
         <v>0</v>
       </c>
       <c r="AG412" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="AH412" s="1" t="s">
         <v>636</v>
@@ -60162,7 +60163,7 @@
     </row>
     <row r="4" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G4" s="7" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="I4" s="34">
         <v>3</v>
@@ -60183,7 +60184,7 @@
         <v>4</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="K5" s="38">
         <f t="shared" si="0"/>
@@ -60207,7 +60208,7 @@
     </row>
     <row r="7" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G7" s="7" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="I7" s="34">
         <v>6</v>
@@ -60273,7 +60274,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="K11" s="38">
         <f t="shared" si="0"/>
@@ -60788,7 +60789,7 @@
         <v>623</v>
       </c>
       <c r="S32" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="33" spans="9:19" x14ac:dyDescent="0.15">
@@ -60799,7 +60800,7 @@
         <v>624</v>
       </c>
       <c r="S33" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="34" spans="9:19" x14ac:dyDescent="0.15">
@@ -60810,7 +60811,7 @@
         <v>625</v>
       </c>
       <c r="S34" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="35" spans="9:19" x14ac:dyDescent="0.15">
@@ -60818,7 +60819,7 @@
         <v>626</v>
       </c>
       <c r="S35" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="36" spans="9:19" x14ac:dyDescent="0.15">
@@ -60826,7 +60827,7 @@
         <v>627</v>
       </c>
       <c r="S36" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="37" spans="9:19" x14ac:dyDescent="0.15">
@@ -60834,7 +60835,7 @@
         <v>628</v>
       </c>
       <c r="S37" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="38" spans="9:19" x14ac:dyDescent="0.15">
@@ -60842,7 +60843,7 @@
         <v>629</v>
       </c>
       <c r="S38" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" spans="9:19" x14ac:dyDescent="0.15">
@@ -60850,7 +60851,7 @@
         <v>630</v>
       </c>
       <c r="S39" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="40" spans="9:19" x14ac:dyDescent="0.15">
@@ -60858,7 +60859,7 @@
         <v>631</v>
       </c>
       <c r="S40" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="41" spans="9:19" x14ac:dyDescent="0.15">
@@ -60866,7 +60867,7 @@
         <v>632</v>
       </c>
       <c r="S41" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="42" spans="9:19" x14ac:dyDescent="0.15">
@@ -60874,7 +60875,7 @@
         <v>633</v>
       </c>
       <c r="S42" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="47" spans="9:19" x14ac:dyDescent="0.15">
@@ -60882,7 +60883,7 @@
         <v>623</v>
       </c>
       <c r="R47" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="48" spans="9:19" ht="17.25" x14ac:dyDescent="0.15">
@@ -60890,13 +60891,13 @@
         <v>187</v>
       </c>
       <c r="J48" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="Q48" t="s">
         <v>624</v>
       </c>
       <c r="R48" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="49" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -60904,13 +60905,13 @@
         <v>188</v>
       </c>
       <c r="J49" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="Q49" t="s">
         <v>625</v>
       </c>
       <c r="R49" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="50" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -60918,13 +60919,13 @@
         <v>189</v>
       </c>
       <c r="J50" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="Q50" t="s">
         <v>626</v>
       </c>
       <c r="R50" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="51" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -60932,13 +60933,13 @@
         <v>858</v>
       </c>
       <c r="J51" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="Q51" t="s">
         <v>627</v>
       </c>
       <c r="R51" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="52" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -60946,13 +60947,13 @@
         <v>193</v>
       </c>
       <c r="J52" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="Q52" t="s">
         <v>628</v>
       </c>
       <c r="R52" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="53" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -60960,13 +60961,13 @@
         <v>162</v>
       </c>
       <c r="J53" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="Q53" t="s">
         <v>629</v>
       </c>
       <c r="R53" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="54" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -60974,13 +60975,13 @@
         <v>159</v>
       </c>
       <c r="J54" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="Q54" t="s">
         <v>630</v>
       </c>
       <c r="R54" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="55" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -60988,13 +60989,13 @@
         <v>161</v>
       </c>
       <c r="J55" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="Q55" t="s">
         <v>631</v>
       </c>
       <c r="R55" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="56" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61002,13 +61003,13 @@
         <v>174</v>
       </c>
       <c r="J56" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="Q56" t="s">
         <v>632</v>
       </c>
       <c r="R56" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="57" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61016,13 +61017,13 @@
         <v>178</v>
       </c>
       <c r="J57" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="Q57" t="s">
         <v>633</v>
       </c>
       <c r="R57" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="58" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61030,7 +61031,7 @@
         <v>250</v>
       </c>
       <c r="J58" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="59" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61038,7 +61039,7 @@
         <v>205</v>
       </c>
       <c r="J59" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="60" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61046,7 +61047,7 @@
         <v>795</v>
       </c>
       <c r="J60" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="61" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61054,7 +61055,7 @@
         <v>163</v>
       </c>
       <c r="J61" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="62" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61062,7 +61063,7 @@
         <v>184</v>
       </c>
       <c r="J62" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="63" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61070,7 +61071,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="64" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -61078,7 +61079,7 @@
         <v>182</v>
       </c>
       <c r="J64" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="65" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61086,7 +61087,7 @@
         <v>194</v>
       </c>
       <c r="J65" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="66" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61094,7 +61095,7 @@
         <v>195</v>
       </c>
       <c r="J66" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="67" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61102,7 +61103,7 @@
         <v>165</v>
       </c>
       <c r="J67" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="68" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61110,7 +61111,7 @@
         <v>167</v>
       </c>
       <c r="J68" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="69" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61118,7 +61119,7 @@
         <v>196</v>
       </c>
       <c r="J69" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="70" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61126,7 +61127,7 @@
         <v>164</v>
       </c>
       <c r="J70" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="71" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61134,7 +61135,7 @@
         <v>197</v>
       </c>
       <c r="J71" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="72" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61142,7 +61143,7 @@
         <v>796</v>
       </c>
       <c r="J72" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="73" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61150,7 +61151,7 @@
         <v>198</v>
       </c>
       <c r="J73" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="74" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61158,7 +61159,7 @@
         <v>171</v>
       </c>
       <c r="J74" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="75" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61166,7 +61167,7 @@
         <v>199</v>
       </c>
       <c r="J75" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="76" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61174,7 +61175,7 @@
         <v>200</v>
       </c>
       <c r="J76" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="77" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61182,7 +61183,7 @@
         <v>170</v>
       </c>
       <c r="J77" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="78" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61190,7 +61191,7 @@
         <v>201</v>
       </c>
       <c r="J78" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="79" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61198,7 +61199,7 @@
         <v>172</v>
       </c>
       <c r="J79" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="80" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61206,7 +61207,7 @@
         <v>202</v>
       </c>
       <c r="J80" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="81" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61214,7 +61215,7 @@
         <v>185</v>
       </c>
       <c r="J81" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="82" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61222,7 +61223,7 @@
         <v>168</v>
       </c>
       <c r="J82" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="83" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61230,7 +61231,7 @@
         <v>175</v>
       </c>
       <c r="J83" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="84" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61238,7 +61239,7 @@
         <v>177</v>
       </c>
       <c r="J84" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="85" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61246,7 +61247,7 @@
         <v>179</v>
       </c>
       <c r="J85" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="86" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61254,7 +61255,7 @@
         <v>180</v>
       </c>
       <c r="J86" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="87" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61262,7 +61263,7 @@
         <v>203</v>
       </c>
       <c r="J87" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="88" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61270,7 +61271,7 @@
         <v>204</v>
       </c>
       <c r="J88" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="89" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61278,7 +61279,7 @@
         <v>181</v>
       </c>
       <c r="J89" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="90" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61286,7 +61287,7 @@
         <v>206</v>
       </c>
       <c r="J90" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="91" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61294,7 +61295,7 @@
         <v>207</v>
       </c>
       <c r="J91" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="92" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61302,7 +61303,7 @@
         <v>183</v>
       </c>
       <c r="J92" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="93" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61310,7 +61311,7 @@
         <v>208</v>
       </c>
       <c r="J93" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="94" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61318,7 +61319,7 @@
         <v>209</v>
       </c>
       <c r="J94" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="95" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61326,7 +61327,7 @@
         <v>210</v>
       </c>
       <c r="J95" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="96" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61334,7 +61335,7 @@
         <v>169</v>
       </c>
       <c r="J96" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="97" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61342,7 +61343,7 @@
         <v>211</v>
       </c>
       <c r="J97" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="98" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61350,7 +61351,7 @@
         <v>212</v>
       </c>
       <c r="J98" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="99" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61358,7 +61359,7 @@
         <v>213</v>
       </c>
       <c r="J99" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="100" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61366,7 +61367,7 @@
         <v>214</v>
       </c>
       <c r="J100" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="101" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61374,7 +61375,7 @@
         <v>215</v>
       </c>
       <c r="J101" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="102" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61382,7 +61383,7 @@
         <v>176</v>
       </c>
       <c r="J102" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="103" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61390,7 +61391,7 @@
         <v>186</v>
       </c>
       <c r="J103" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="104" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61398,7 +61399,7 @@
         <v>173</v>
       </c>
       <c r="J104" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="105" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61406,7 +61407,7 @@
         <v>216</v>
       </c>
       <c r="J105" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="106" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61414,7 +61415,7 @@
         <v>217</v>
       </c>
       <c r="J106" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="107" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61422,7 +61423,7 @@
         <v>218</v>
       </c>
       <c r="J107" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="108" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61430,7 +61431,7 @@
         <v>219</v>
       </c>
       <c r="J108" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="109" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61438,7 +61439,7 @@
         <v>797</v>
       </c>
       <c r="J109" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="110" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61446,7 +61447,7 @@
         <v>220</v>
       </c>
       <c r="J110" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="111" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61454,7 +61455,7 @@
         <v>221</v>
       </c>
       <c r="J111" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="112" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61462,7 +61463,7 @@
         <v>222</v>
       </c>
       <c r="J112" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="113" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61470,7 +61471,7 @@
         <v>223</v>
       </c>
       <c r="J113" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="114" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61478,7 +61479,7 @@
         <v>224</v>
       </c>
       <c r="J114" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="115" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61486,7 +61487,7 @@
         <v>225</v>
       </c>
       <c r="J115" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="116" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61494,7 +61495,7 @@
         <v>226</v>
       </c>
       <c r="J116" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="117" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61502,7 +61503,7 @@
         <v>227</v>
       </c>
       <c r="J117" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="118" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61510,7 +61511,7 @@
         <v>228</v>
       </c>
       <c r="J118" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="119" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61518,7 +61519,7 @@
         <v>229</v>
       </c>
       <c r="J119" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="120" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61526,7 +61527,7 @@
         <v>230</v>
       </c>
       <c r="J120" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="121" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61534,7 +61535,7 @@
         <v>231</v>
       </c>
       <c r="J121" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="122" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61542,7 +61543,7 @@
         <v>232</v>
       </c>
       <c r="J122" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="123" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61550,7 +61551,7 @@
         <v>233</v>
       </c>
       <c r="J123" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="124" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61558,7 +61559,7 @@
         <v>234</v>
       </c>
       <c r="J124" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="125" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61566,7 +61567,7 @@
         <v>235</v>
       </c>
       <c r="J125" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="126" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61574,7 +61575,7 @@
         <v>236</v>
       </c>
       <c r="J126" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="127" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61582,7 +61583,7 @@
         <v>237</v>
       </c>
       <c r="J127" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="128" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61590,7 +61591,7 @@
         <v>238</v>
       </c>
       <c r="J128" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="129" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61598,7 +61599,7 @@
         <v>239</v>
       </c>
       <c r="J129" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="130" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61606,7 +61607,7 @@
         <v>240</v>
       </c>
       <c r="J130" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="131" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61614,7 +61615,7 @@
         <v>241</v>
       </c>
       <c r="J131" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="132" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61622,7 +61623,7 @@
         <v>242</v>
       </c>
       <c r="J132" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="133" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61630,7 +61631,7 @@
         <v>243</v>
       </c>
       <c r="J133" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="134" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61638,7 +61639,7 @@
         <v>244</v>
       </c>
       <c r="J134" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="135" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61646,7 +61647,7 @@
         <v>245</v>
       </c>
       <c r="J135" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="136" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61654,7 +61655,7 @@
         <v>246</v>
       </c>
       <c r="J136" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="137" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61662,7 +61663,7 @@
         <v>247</v>
       </c>
       <c r="J137" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="138" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61670,7 +61671,7 @@
         <v>248</v>
       </c>
       <c r="J138" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="139" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -61678,7 +61679,7 @@
         <v>798</v>
       </c>
       <c r="J139" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
   </sheetData>
@@ -70517,7 +70518,7 @@
         <v>813</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="L32" s="38" t="s">
         <v>814</v>
@@ -72217,7 +72218,7 @@
         <v>930</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="E65" s="38">
         <v>2</v>
@@ -72589,7 +72590,7 @@
         <v>936</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="E71" s="38">
         <v>2</v>
@@ -72899,7 +72900,7 @@
         <v>941</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="E76" s="38">
         <v>2</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6721" uniqueCount="1812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6721" uniqueCount="1829">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4881,55 +4881,28 @@
     <t>活跃于湖泊池塘，其肉口感筋道，有淡淡水草香。</t>
   </si>
   <si>
-    <t>在南方水域自在游，肉嫩且味醇，纯净而悠长。</t>
-  </si>
-  <si>
-    <t>隐匿于淡水中，蟹肉鲜甜，如风轻拂味蕾，带来清爽与润泽。</t>
-  </si>
-  <si>
     <t>栖息在水底暗处，体表黏滑，味道浓郁厚重。</t>
   </si>
   <si>
-    <t>梭于溪流河湾，味道清新自然，像溪流中的灵动音符。</t>
-  </si>
-  <si>
     <t>在池水中嬉戏，色彩缤纷，游时如彩锦流动。</t>
   </si>
   <si>
     <t>于清澈溪流疾行，身形纤细，游姿灵动如箭。</t>
   </si>
   <si>
-    <t>称霸于较深淡水，身形矫健，游时虎虎生威，鱼肉非常鲜嫩。</t>
-  </si>
-  <si>
     <t>体态圆润，行动迟缓呆萌，如水中滚动的可爱肉球。</t>
   </si>
   <si>
-    <t>生活于溪流，肉色粉嫩，味道像春日樱落溪流的一抹甜香。</t>
-  </si>
-  <si>
-    <t>在清澈山涧活跃，肉质紧实爽脆，似山涧清泉流淌的鲜活滋味。</t>
-  </si>
-  <si>
     <t>在近海岩礁附近巡游，鱼肉甜美仿佛大海温柔的抚摸。</t>
   </si>
   <si>
-    <t>在冷水水域闪亮，身披金光，似金色阳光融入水中的精华。</t>
-  </si>
-  <si>
     <t>色彩绚丽，群游如星芒闪烁，是水中梦幻的霓虹派对。</t>
   </si>
   <si>
-    <t>在清澈溪流中欢畅，色泽若桃，游态宛如溪边桃花飘落的精灵。</t>
-  </si>
-  <si>
     <t>在海洋中奋力洄游，身姿强壮，其味鲜美浓郁。</t>
   </si>
   <si>
     <t>尾巴似扇，游姿婀娜多姿，如穿着华服走秀的模特。</t>
-  </si>
-  <si>
-    <t>岩穴暗影栖息，动作轻柔，似幽暗中的神秘舞者，悄然无声。</t>
   </si>
   <si>
     <t>身形修长，游时气势磅礴，仿若银色蛟龙驰骋沧海。</t>
@@ -6393,6 +6366,110 @@
   </si>
   <si>
     <t>1,1</t>
+  </si>
+  <si>
+    <t>层层叠叠，大口咬下，多种口感在舌尖碰撞。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>口感清脆，酸辣开胃，是佐餐小菜中的经典之选。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肉质细腻，外皮香脆，内部软嫩，保留鲷鱼的优雅风味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身披红甲，虾肉紧实，烤香四溢，奢华的海鲜烧烤美味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼的肥嫩经盐烤激发，咸香与鲜嫩融合，回味无穷。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原汁原味，轻轻一剥，鲜嫩洁白的蟹肉展露无遗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤制使肉质紧实，散发别样的海味鲜香。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一面贴底烤出金黄，鱼肉鲜嫩，口感独具魅力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇聚各类海鲜，鲜香浓郁，尽显海洋风味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦类的粉末，可成为各种形状，承载丰富口感。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咸酸适度，爽脆开胃，为餐桌增添一份独特的风味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新鲜脆爽，多种蔬菜汇聚，健康与美味并存。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肉香四溢，香料加持，感受热辣鲜香的诱惑。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辣味刺激，蟹肉鲜美，带来独特热辣的风味体验。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浓郁果香，口感醇厚，将整串葡萄的精华浓缩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>称霸于较深淡水，游时虎虎生威，鱼肉非常鲜嫩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梭于溪流河湾，像溪流中的灵动音符。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活于溪流，味道像春日樱落溪流的一抹甜香。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在清澈山涧活跃，似山涧清泉流淌的鲜活滋味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在冷水水域闪亮，似金色阳光融入水中的精华。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在清澈溪流中欢畅，游态宛如溪边桃花飘落的精灵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩穴暗影栖息，动作轻柔，似幽暗中的神秘舞者。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表皮盐香，鱼肉鲜嫩，简单烤制，锁住鲮鱼的原始鲜美。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐匿于淡水中，蟹肉鲜甜，如风轻拂味蕾。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在南方水域自在游，肉嫩且味醇，纯净而悠长。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼身闪彩，盐烤之下，肉质紧实，散发独特的咸鲜风味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6595,7 +6672,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6741,6 +6818,10 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9270,7 +9351,7 @@
     <col min="21" max="22" width="11" style="2" customWidth="1"/>
     <col min="23" max="23" width="8.375" style="1" customWidth="1"/>
     <col min="24" max="33" width="7.75" style="1" customWidth="1"/>
-    <col min="34" max="34" width="50.125" style="1" customWidth="1"/>
+    <col min="34" max="34" width="92.125" style="1" customWidth="1"/>
     <col min="35" max="35" width="17.75" style="1" customWidth="1"/>
     <col min="36" max="16384" width="7.75" style="1"/>
   </cols>
@@ -9402,7 +9483,7 @@
         <v>695</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1799</v>
+        <v>1790</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>16</v>
@@ -9486,7 +9567,7 @@
         <v>6</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>1621</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.15">
@@ -10826,7 +10907,7 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>1537</v>
+        <v>1528</v>
       </c>
       <c r="B18" s="1">
         <v>23</v>
@@ -11036,7 +11117,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1723</v>
+        <v>1714</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -11132,7 +11213,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1724</v>
+        <v>1715</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -11228,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1724</v>
+        <v>1715</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -11325,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1725</v>
+        <v>1716</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -11421,7 +11502,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1726</v>
+        <v>1717</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -11518,7 +11599,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1723</v>
+        <v>1714</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -11615,7 +11696,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1727</v>
+        <v>1718</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -11711,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1724</v>
+        <v>1715</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -11808,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1728</v>
+        <v>1719</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -11905,7 +11986,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1729</v>
+        <v>1720</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -12003,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1730</v>
+        <v>1721</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -12101,7 +12182,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1731</v>
+        <v>1722</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -12198,7 +12279,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1732</v>
+        <v>1723</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -12295,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -12392,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1734</v>
+        <v>1725</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -12489,7 +12570,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -12587,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1736</v>
+        <v>1727</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -12684,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1692</v>
+        <v>1683</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -12781,7 +12862,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1737</v>
+        <v>1728</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -12879,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1738</v>
+        <v>1729</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -12975,7 +13056,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1739</v>
+        <v>1730</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -13072,7 +13153,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1740</v>
+        <v>1731</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -13168,7 +13249,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -13265,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1741</v>
+        <v>1732</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -13361,7 +13442,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1742</v>
+        <v>1733</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -13459,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1743</v>
+        <v>1734</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -13556,7 +13637,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1744</v>
+        <v>1735</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -13653,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1745</v>
+        <v>1736</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -13751,7 +13832,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1746</v>
+        <v>1737</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -13849,7 +13930,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1747</v>
+        <v>1738</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -13946,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1748</v>
+        <v>1739</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -14042,7 +14123,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1749</v>
+        <v>1740</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -14140,7 +14221,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1750</v>
+        <v>1741</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -14238,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -14335,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1751</v>
+        <v>1742</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -14432,7 +14513,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -14529,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1752</v>
+        <v>1743</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -14626,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1753</v>
+        <v>1744</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -14722,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1754</v>
+        <v>1745</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -14819,7 +14900,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1755</v>
+        <v>1746</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -14917,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1745</v>
+        <v>1736</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -15015,7 +15096,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1756</v>
+        <v>1747</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
@@ -15113,7 +15194,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1757</v>
+        <v>1748</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -15210,7 +15291,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1744</v>
+        <v>1735</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -15308,7 +15389,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1758</v>
+        <v>1749</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -15405,7 +15486,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -15502,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1759</v>
+        <v>1750</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -15599,7 +15680,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1760</v>
+        <v>1751</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -15696,7 +15777,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1761</v>
+        <v>1752</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -15794,7 +15875,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1755</v>
+        <v>1746</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -15892,7 +15973,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1762</v>
+        <v>1753</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -15989,7 +16070,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1763</v>
+        <v>1754</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -16085,7 +16166,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1764</v>
+        <v>1755</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -16182,7 +16263,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1765</v>
+        <v>1756</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -16279,7 +16360,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1749</v>
+        <v>1740</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -16377,7 +16458,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1754</v>
+        <v>1745</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -16474,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1766</v>
+        <v>1757</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -16572,7 +16653,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1767</v>
+        <v>1758</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -16669,7 +16750,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1768</v>
+        <v>1759</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
@@ -16766,7 +16847,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1769</v>
+        <v>1760</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -16863,7 +16944,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1766</v>
+        <v>1757</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -16961,7 +17042,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -17058,7 +17139,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1770</v>
+        <v>1761</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -17155,7 +17236,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>1690</v>
+        <v>1681</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
@@ -17253,7 +17334,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>1771</v>
+        <v>1762</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
@@ -17350,7 +17431,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1772</v>
+        <v>1763</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -17447,7 +17528,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1773</v>
+        <v>1764</v>
       </c>
       <c r="H86" s="1">
         <v>0</v>
@@ -17543,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1774</v>
+        <v>1765</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -17640,7 +17721,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1774</v>
+        <v>1765</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -17737,7 +17818,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -17834,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1775</v>
+        <v>1766</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -17913,7 +17994,7 @@
     </row>
     <row r="91" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A91" s="12" t="s">
-        <v>1538</v>
+        <v>1529</v>
       </c>
       <c r="B91" s="1">
         <v>271</v>
@@ -17931,7 +18012,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1776</v>
+        <v>1767</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -18027,7 +18108,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>1777</v>
+        <v>1768</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -18124,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
@@ -18221,7 +18302,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1778</v>
+        <v>1769</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -18319,7 +18400,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1779</v>
+        <v>1770</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -18416,7 +18497,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1780</v>
+        <v>1771</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -18513,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1781</v>
+        <v>1772</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -18609,7 +18690,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1782</v>
+        <v>1773</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -18688,7 +18769,7 @@
     </row>
     <row r="99" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A99" s="12" t="s">
-        <v>1653</v>
+        <v>1644</v>
       </c>
       <c r="B99" s="1">
         <v>279</v>
@@ -18706,7 +18787,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1762</v>
+        <v>1753</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -18803,7 +18884,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1783</v>
+        <v>1774</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -18900,7 +18981,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1784</v>
+        <v>1775</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -18997,7 +19078,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1785</v>
+        <v>1776</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -19094,7 +19175,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>1786</v>
+        <v>1777</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -19191,7 +19272,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>1787</v>
+        <v>1778</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -19288,7 +19369,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -19385,7 +19466,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>1788</v>
+        <v>1779</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -19482,7 +19563,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1741</v>
+        <v>1732</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -19579,7 +19660,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1789</v>
+        <v>1780</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -19676,7 +19757,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>1790</v>
+        <v>1781</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -19773,7 +19854,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>1791</v>
+        <v>1782</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -19870,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>1792</v>
+        <v>1783</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -19967,7 +20048,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>1774</v>
+        <v>1765</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -20064,7 +20145,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>1767</v>
+        <v>1758</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -20161,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -20258,7 +20339,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1793</v>
+        <v>1784</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -20354,7 +20435,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>1738</v>
+        <v>1729</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -20452,7 +20533,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1794</v>
+        <v>1785</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -20549,7 +20630,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1763</v>
+        <v>1754</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -20645,7 +20726,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>1763</v>
+        <v>1754</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -20742,7 +20823,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>1795</v>
+        <v>1786</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -20838,7 +20919,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>1786</v>
+        <v>1777</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -20934,7 +21015,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>1796</v>
+        <v>1787</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -21031,7 +21112,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H123" s="1">
         <v>1</v>
@@ -21233,7 +21314,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H125" s="1">
         <v>1</v>
@@ -21330,7 +21411,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H126" s="1">
         <v>1</v>
@@ -21428,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H127" s="1">
         <v>1</v>
@@ -21526,7 +21607,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H128" s="1">
         <v>1</v>
@@ -21624,7 +21705,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H129" s="1">
         <v>1</v>
@@ -21721,7 +21802,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H130" s="1">
         <v>1</v>
@@ -21819,7 +21900,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H131" s="1">
         <v>1</v>
@@ -21917,7 +21998,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
       <c r="H132" s="1">
         <v>1</v>
@@ -22014,7 +22095,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H133" s="1">
         <v>1</v>
@@ -22112,7 +22193,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
       <c r="H134" s="1">
         <v>1</v>
@@ -22209,7 +22290,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H135" s="1">
         <v>1</v>
@@ -22307,7 +22388,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H136" s="1">
         <v>1</v>
@@ -22404,7 +22485,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H137" s="1">
         <v>1</v>
@@ -22501,7 +22582,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H138" s="1">
         <v>1</v>
@@ -22599,7 +22680,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H139" s="1">
         <v>1</v>
@@ -22696,7 +22777,7 @@
         <v>0</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H140" s="1">
         <v>1</v>
@@ -22794,7 +22875,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H141" s="1">
         <v>1</v>
@@ -22891,7 +22972,7 @@
         <v>0</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H142" s="1">
         <v>1</v>
@@ -22988,7 +23069,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H143" s="1">
         <v>1</v>
@@ -23085,7 +23166,7 @@
         <v>0</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
       <c r="H144" s="1">
         <v>1</v>
@@ -23183,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
       <c r="H145" s="1">
         <v>1</v>
@@ -23280,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
       <c r="H146" s="1">
         <v>1</v>
@@ -23377,7 +23458,7 @@
         <v>0</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
       <c r="H147" s="1">
         <v>1</v>
@@ -23475,7 +23556,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
       <c r="H148" s="1">
         <v>1</v>
@@ -23573,7 +23654,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1789</v>
+        <v>1780</v>
       </c>
       <c r="H149" s="1">
         <v>1</v>
@@ -23670,7 +23751,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="H150" s="1">
         <v>1</v>
@@ -26482,7 +26563,7 @@
         <v>1</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
@@ -26579,7 +26660,7 @@
         <v>1</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1685</v>
+        <v>1676</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -26675,7 +26756,7 @@
         <v>1</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -26771,7 +26852,7 @@
         <v>1</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -26867,7 +26948,7 @@
         <v>1</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -26963,7 +27044,7 @@
         <v>2</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -27060,7 +27141,7 @@
         <v>2</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -27156,7 +27237,7 @@
         <v>2</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1685</v>
+        <v>1676</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -27252,7 +27333,7 @@
         <v>2</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
@@ -27348,7 +27429,7 @@
         <v>3</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
@@ -27444,7 +27525,7 @@
         <v>3</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1689</v>
+        <v>1680</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
@@ -27540,7 +27621,7 @@
         <v>3</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1690</v>
+        <v>1681</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -27636,7 +27717,7 @@
         <v>6</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>1691</v>
+        <v>1682</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -27732,7 +27813,7 @@
         <v>6</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>1692</v>
+        <v>1683</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -27828,7 +27909,7 @@
         <v>6</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
@@ -27924,7 +28005,7 @@
         <v>6</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>1693</v>
+        <v>1684</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
@@ -28020,7 +28101,7 @@
         <v>3</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
@@ -28116,7 +28197,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -28212,7 +28293,7 @@
         <v>2</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
@@ -28308,7 +28389,7 @@
         <v>6</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -28404,7 +28485,7 @@
         <v>6</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>1694</v>
+        <v>1685</v>
       </c>
       <c r="H199" s="1">
         <v>0</v>
@@ -28500,7 +28581,7 @@
         <v>0</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>1695</v>
+        <v>1686</v>
       </c>
       <c r="H200" s="1">
         <v>0</v>
@@ -28596,7 +28677,7 @@
         <v>0</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>1696</v>
+        <v>1687</v>
       </c>
       <c r="H201" s="1">
         <v>0</v>
@@ -28692,7 +28773,7 @@
         <v>0</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
@@ -28788,7 +28869,7 @@
         <v>0</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1698</v>
+        <v>1689</v>
       </c>
       <c r="H203" s="1">
         <v>0</v>
@@ -28884,7 +28965,7 @@
         <v>0</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -28980,7 +29061,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>1699</v>
+        <v>1690</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -29076,7 +29157,7 @@
         <v>0</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
@@ -29172,7 +29253,7 @@
         <v>0</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -29268,7 +29349,7 @@
         <v>0</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1698</v>
+        <v>1689</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -29364,7 +29445,7 @@
         <v>0</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1701</v>
+        <v>1692</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
@@ -29460,7 +29541,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1695</v>
+        <v>1686</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
@@ -29556,7 +29637,7 @@
         <v>0</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1702</v>
+        <v>1693</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -29652,7 +29733,7 @@
         <v>0</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
@@ -29748,7 +29829,7 @@
         <v>0</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -29844,7 +29925,7 @@
         <v>0</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1703</v>
+        <v>1694</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -29940,7 +30021,7 @@
         <v>0</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -30036,7 +30117,7 @@
         <v>0</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1704</v>
+        <v>1695</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -30132,7 +30213,7 @@
         <v>0</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1705</v>
+        <v>1696</v>
       </c>
       <c r="H217" s="9">
         <v>0</v>
@@ -30231,7 +30312,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1706</v>
+        <v>1697</v>
       </c>
       <c r="H218" s="9">
         <v>0</v>
@@ -30330,7 +30411,7 @@
         <v>0</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1707</v>
+        <v>1698</v>
       </c>
       <c r="H219" s="9">
         <v>0</v>
@@ -30429,7 +30510,7 @@
         <v>0</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1708</v>
+        <v>1699</v>
       </c>
       <c r="H220" s="9">
         <v>0</v>
@@ -30528,7 +30609,7 @@
         <v>0</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1709</v>
+        <v>1700</v>
       </c>
       <c r="H221" s="9">
         <v>0</v>
@@ -30627,7 +30708,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1710</v>
+        <v>1701</v>
       </c>
       <c r="H222" s="9">
         <v>0</v>
@@ -30726,7 +30807,7 @@
         <v>0</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1711</v>
+        <v>1702</v>
       </c>
       <c r="H223" s="9">
         <v>0</v>
@@ -30825,7 +30906,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1712</v>
+        <v>1703</v>
       </c>
       <c r="H224" s="9">
         <v>0</v>
@@ -30924,7 +31005,7 @@
         <v>0</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1713</v>
+        <v>1704</v>
       </c>
       <c r="H225" s="9">
         <v>0</v>
@@ -31023,7 +31104,7 @@
         <v>0</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1714</v>
+        <v>1705</v>
       </c>
       <c r="H226" s="9">
         <v>0</v>
@@ -31122,7 +31203,7 @@
         <v>0</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1714</v>
+        <v>1705</v>
       </c>
       <c r="H227" s="9">
         <v>0</v>
@@ -31221,7 +31302,7 @@
         <v>0</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1715</v>
+        <v>1706</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -31317,7 +31398,7 @@
         <v>0</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1715</v>
+        <v>1706</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -31413,7 +31494,7 @@
         <v>0</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1716</v>
+        <v>1707</v>
       </c>
       <c r="H230" s="1">
         <v>0</v>
@@ -31509,7 +31590,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1717</v>
+        <v>1708</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -31605,7 +31686,7 @@
         <v>0</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1718</v>
+        <v>1709</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -31701,7 +31782,7 @@
         <v>0</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1719</v>
+        <v>1710</v>
       </c>
       <c r="H233" s="1">
         <v>0</v>
@@ -31797,7 +31878,7 @@
         <v>0</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1720</v>
+        <v>1711</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
@@ -31893,7 +31974,7 @@
         <v>0</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1720</v>
+        <v>1711</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -31989,7 +32070,7 @@
         <v>0</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1717</v>
+        <v>1708</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -32073,7 +32154,7 @@
         <v>2000</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="D237" s="1">
         <v>6</v>
@@ -32085,7 +32166,7 @@
         <v>0</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -32163,13 +32244,13 @@
     </row>
     <row r="238" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A238" s="1" t="s">
-        <v>1573</v>
+        <v>1564</v>
       </c>
       <c r="B238" s="1">
         <v>2001</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1623</v>
+        <v>1614</v>
       </c>
       <c r="D238" s="1">
         <v>6</v>
@@ -32181,7 +32262,7 @@
         <v>0</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -32254,7 +32335,7 @@
         <v>100</v>
       </c>
       <c r="AH238" s="1" t="s">
-        <v>1576</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="239" spans="1:34" x14ac:dyDescent="0.15">
@@ -32265,7 +32346,7 @@
         <v>2002</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="D239" s="1">
         <v>6</v>
@@ -32277,7 +32358,7 @@
         <v>0</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1722</v>
+        <v>1713</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
@@ -32361,7 +32442,7 @@
         <v>2003</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="D240" s="1">
         <v>6</v>
@@ -32373,7 +32454,7 @@
         <v>0</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1722</v>
+        <v>1713</v>
       </c>
       <c r="H240" s="1">
         <v>0</v>
@@ -32469,7 +32550,7 @@
         <v>0</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
       <c r="H241" s="1">
         <v>0</v>
@@ -33891,13 +33972,13 @@
     </row>
     <row r="256" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
-        <v>1574</v>
+        <v>1565</v>
       </c>
       <c r="B256" s="1">
         <v>2115</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1579</v>
+        <v>1570</v>
       </c>
       <c r="D256" s="1">
         <v>6</v>
@@ -33982,18 +34063,18 @@
         <v>300</v>
       </c>
       <c r="AH256" s="1" t="s">
-        <v>1577</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="257" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
-        <v>1575</v>
+        <v>1566</v>
       </c>
       <c r="B257" s="1">
         <v>2116</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1580</v>
+        <v>1571</v>
       </c>
       <c r="D257" s="1">
         <v>6</v>
@@ -34078,7 +34159,7 @@
         <v>600</v>
       </c>
       <c r="AH257" s="1" t="s">
-        <v>1578</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="258" spans="1:34" x14ac:dyDescent="0.15">
@@ -34179,13 +34260,13 @@
     </row>
     <row r="259" spans="1:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="1" t="s">
-        <v>1539</v>
+        <v>1530</v>
       </c>
       <c r="B259" s="1">
         <v>2201</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1541</v>
+        <v>1532</v>
       </c>
       <c r="D259" s="1">
         <v>10</v>
@@ -34270,18 +34351,18 @@
         <v>0</v>
       </c>
       <c r="AH259" s="3" t="s">
-        <v>1549</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="260" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A260" s="1" t="s">
-        <v>1540</v>
+        <v>1531</v>
       </c>
       <c r="B260" s="1">
         <v>2202</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1540</v>
+        <v>1531</v>
       </c>
       <c r="D260" s="1">
         <v>10</v>
@@ -34366,18 +34447,18 @@
         <v>0</v>
       </c>
       <c r="AH260" s="3" t="s">
-        <v>1550</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="261" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A261" s="8" t="s">
-        <v>1542</v>
+        <v>1533</v>
       </c>
       <c r="B261" s="1">
         <v>2203</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>1542</v>
+        <v>1533</v>
       </c>
       <c r="D261" s="1">
         <v>10</v>
@@ -34462,18 +34543,18 @@
         <v>0</v>
       </c>
       <c r="AH261" s="8" t="s">
-        <v>1551</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="262" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A262" s="8" t="s">
-        <v>1543</v>
+        <v>1534</v>
       </c>
       <c r="B262" s="1">
         <v>2204</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>1543</v>
+        <v>1534</v>
       </c>
       <c r="D262" s="1">
         <v>10</v>
@@ -34558,18 +34639,18 @@
         <v>0</v>
       </c>
       <c r="AH262" s="8" t="s">
-        <v>1551</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="263" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A263" s="8" t="s">
-        <v>1544</v>
+        <v>1535</v>
       </c>
       <c r="B263" s="1">
         <v>2205</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>1544</v>
+        <v>1535</v>
       </c>
       <c r="D263" s="1">
         <v>10</v>
@@ -34654,18 +34735,18 @@
         <v>0</v>
       </c>
       <c r="AH263" s="8" t="s">
-        <v>1552</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="264" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A264" s="8" t="s">
-        <v>1545</v>
+        <v>1536</v>
       </c>
       <c r="B264" s="1">
         <v>2206</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>1545</v>
+        <v>1536</v>
       </c>
       <c r="D264" s="1">
         <v>10</v>
@@ -34750,18 +34831,18 @@
         <v>0</v>
       </c>
       <c r="AH264" s="8" t="s">
-        <v>1553</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="265" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A265" s="8" t="s">
-        <v>1546</v>
+        <v>1537</v>
       </c>
       <c r="B265" s="1">
         <v>2207</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>1546</v>
+        <v>1537</v>
       </c>
       <c r="D265" s="1">
         <v>10</v>
@@ -34846,18 +34927,18 @@
         <v>0</v>
       </c>
       <c r="AH265" s="8" t="s">
-        <v>1551</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="266" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A266" s="8" t="s">
-        <v>1547</v>
+        <v>1538</v>
       </c>
       <c r="B266" s="1">
         <v>2208</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>1547</v>
+        <v>1538</v>
       </c>
       <c r="D266" s="1">
         <v>10</v>
@@ -34942,18 +35023,18 @@
         <v>0</v>
       </c>
       <c r="AH266" s="8" t="s">
-        <v>1552</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="267" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A267" s="8" t="s">
-        <v>1548</v>
+        <v>1539</v>
       </c>
       <c r="B267" s="1">
         <v>2209</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>1548</v>
+        <v>1539</v>
       </c>
       <c r="D267" s="1">
         <v>10</v>
@@ -35038,7 +35119,7 @@
         <v>0</v>
       </c>
       <c r="AH267" s="8" t="s">
-        <v>1554</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="268" spans="1:34" ht="14.25" x14ac:dyDescent="0.15">
@@ -35049,7 +35130,7 @@
         <v>4000</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>1626</v>
+        <v>1617</v>
       </c>
       <c r="D268" s="1">
         <v>3</v>
@@ -35061,7 +35142,7 @@
         <v>0</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H268" s="1">
         <v>1</v>
@@ -35145,7 +35226,7 @@
         <v>4003</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>1627</v>
+        <v>1618</v>
       </c>
       <c r="D269" s="1">
         <v>3</v>
@@ -35157,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H269" s="1">
         <v>1</v>
@@ -35240,7 +35321,7 @@
         <v>4004</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>1628</v>
+        <v>1619</v>
       </c>
       <c r="D270" s="1">
         <v>3</v>
@@ -35252,7 +35333,7 @@
         <v>0</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H270" s="1">
         <v>1</v>
@@ -35335,7 +35416,7 @@
         <v>4006</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>1629</v>
+        <v>1620</v>
       </c>
       <c r="D271" s="1">
         <v>3</v>
@@ -35347,7 +35428,7 @@
         <v>0</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H271" s="1">
         <v>1</v>
@@ -35420,18 +35501,18 @@
         <v>0</v>
       </c>
       <c r="AH271" s="7" t="s">
-        <v>1376</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="272" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A272" s="7" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
       <c r="B272" s="1">
         <v>4007</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>1630</v>
+        <v>1621</v>
       </c>
       <c r="D272" s="1">
         <v>3</v>
@@ -35443,7 +35524,7 @@
         <v>0</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H272" s="1">
         <v>1</v>
@@ -35515,8 +35596,8 @@
       <c r="AG272" s="1">
         <v>0</v>
       </c>
-      <c r="AH272" s="7" t="s">
-        <v>1377</v>
+      <c r="AH272" s="50" t="s">
+        <v>1826</v>
       </c>
     </row>
     <row r="273" spans="1:34" x14ac:dyDescent="0.15">
@@ -35527,7 +35608,7 @@
         <v>4008</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="D273" s="1">
         <v>3</v>
@@ -35539,7 +35620,7 @@
         <v>0</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H273" s="1">
         <v>1</v>
@@ -35611,7 +35692,7 @@
         <v>0</v>
       </c>
       <c r="AH273" s="8" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="274" spans="1:34" x14ac:dyDescent="0.15">
@@ -35634,7 +35715,7 @@
         <v>0</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H274" s="1">
         <v>1</v>
@@ -35706,8 +35787,8 @@
       <c r="AG274" s="1">
         <v>0</v>
       </c>
-      <c r="AH274" s="7" t="s">
-        <v>1379</v>
+      <c r="AH274" s="50" t="s">
+        <v>1819</v>
       </c>
     </row>
     <row r="275" spans="1:34" x14ac:dyDescent="0.15">
@@ -35718,7 +35799,7 @@
         <v>4010</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>1632</v>
+        <v>1623</v>
       </c>
       <c r="D275" s="1">
         <v>3</v>
@@ -35730,7 +35811,7 @@
         <v>0</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H275" s="1">
         <v>1</v>
@@ -35803,18 +35884,18 @@
         <v>0</v>
       </c>
       <c r="AH275" s="8" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="276" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A276" s="7" t="s">
-        <v>1536</v>
+        <v>1527</v>
       </c>
       <c r="B276" s="1">
         <v>4011</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>1555</v>
+        <v>1546</v>
       </c>
       <c r="D276" s="1">
         <v>3</v>
@@ -35826,7 +35907,7 @@
         <v>0</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H276" s="1">
         <v>1</v>
@@ -35899,7 +35980,7 @@
         <v>0</v>
       </c>
       <c r="AH276" s="7" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="277" spans="1:34" x14ac:dyDescent="0.15">
@@ -35910,7 +35991,7 @@
         <v>4012</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>1633</v>
+        <v>1624</v>
       </c>
       <c r="D277" s="1">
         <v>3</v>
@@ -35922,7 +36003,7 @@
         <v>0</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H277" s="1">
         <v>1</v>
@@ -35993,8 +36074,8 @@
       <c r="AG277" s="1">
         <v>0</v>
       </c>
-      <c r="AH277" s="7" t="s">
-        <v>1382</v>
+      <c r="AH277" s="50" t="s">
+        <v>1818</v>
       </c>
     </row>
     <row r="278" spans="1:34" x14ac:dyDescent="0.15">
@@ -36005,7 +36086,7 @@
         <v>4013</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>1634</v>
+        <v>1625</v>
       </c>
       <c r="D278" s="1">
         <v>3</v>
@@ -36017,7 +36098,7 @@
         <v>0</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H278" s="1">
         <v>1</v>
@@ -36090,7 +36171,7 @@
         <v>0</v>
       </c>
       <c r="AH278" s="7" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="279" spans="1:34" x14ac:dyDescent="0.15">
@@ -36101,7 +36182,7 @@
         <v>4014</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
       <c r="D279" s="1">
         <v>3</v>
@@ -36113,7 +36194,7 @@
         <v>0</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H279" s="1">
         <v>1</v>
@@ -36185,8 +36266,8 @@
       <c r="AG279" s="1">
         <v>0</v>
       </c>
-      <c r="AH279" s="7" t="s">
-        <v>1384</v>
+      <c r="AH279" s="50" t="s">
+        <v>1820</v>
       </c>
     </row>
     <row r="280" spans="1:34" x14ac:dyDescent="0.15">
@@ -36197,7 +36278,7 @@
         <v>4015</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>1636</v>
+        <v>1627</v>
       </c>
       <c r="D280" s="1">
         <v>3</v>
@@ -36209,7 +36290,7 @@
         <v>0</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H280" s="1">
         <v>1</v>
@@ -36281,8 +36362,8 @@
       <c r="AG280" s="1">
         <v>0</v>
       </c>
-      <c r="AH280" s="7" t="s">
-        <v>1385</v>
+      <c r="AH280" s="50" t="s">
+        <v>1821</v>
       </c>
     </row>
     <row r="281" spans="1:34" x14ac:dyDescent="0.15">
@@ -36305,7 +36386,7 @@
         <v>0</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H281" s="1">
         <v>1</v>
@@ -36378,7 +36459,7 @@
         <v>0</v>
       </c>
       <c r="AH281" s="7" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="282" spans="1:34" x14ac:dyDescent="0.15">
@@ -36389,7 +36470,7 @@
         <v>4017</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>1637</v>
+        <v>1628</v>
       </c>
       <c r="D282" s="1">
         <v>3</v>
@@ -36401,7 +36482,7 @@
         <v>0</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H282" s="1">
         <v>1</v>
@@ -36473,8 +36554,8 @@
       <c r="AG282" s="1">
         <v>0</v>
       </c>
-      <c r="AH282" s="7" t="s">
-        <v>1387</v>
+      <c r="AH282" s="50" t="s">
+        <v>1822</v>
       </c>
     </row>
     <row r="283" spans="1:34" x14ac:dyDescent="0.15">
@@ -36485,7 +36566,7 @@
         <v>4018</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>1638</v>
+        <v>1629</v>
       </c>
       <c r="D283" s="1">
         <v>3</v>
@@ -36497,7 +36578,7 @@
         <v>0</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H283" s="1">
         <v>1</v>
@@ -36570,10 +36651,10 @@
         <v>0</v>
       </c>
       <c r="AH283" s="7" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="284" spans="1:34" ht="27" x14ac:dyDescent="0.15">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="284" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A284" s="8" t="s">
         <v>135</v>
       </c>
@@ -36593,7 +36674,7 @@
         <v>0</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H284" s="1">
         <v>1</v>
@@ -36665,8 +36746,8 @@
       <c r="AG284" s="1">
         <v>0</v>
       </c>
-      <c r="AH284" s="8" t="s">
-        <v>1389</v>
+      <c r="AH284" s="51" t="s">
+        <v>1823</v>
       </c>
     </row>
     <row r="285" spans="1:34" x14ac:dyDescent="0.15">
@@ -36677,7 +36758,7 @@
         <v>4021</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>1639</v>
+        <v>1630</v>
       </c>
       <c r="D285" s="1">
         <v>3</v>
@@ -36689,7 +36770,7 @@
         <v>0</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H285" s="1">
         <v>1</v>
@@ -36762,7 +36843,7 @@
         <v>0</v>
       </c>
       <c r="AH285" s="7" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="286" spans="1:34" x14ac:dyDescent="0.15">
@@ -36785,7 +36866,7 @@
         <v>0</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H286" s="1">
         <v>1</v>
@@ -36858,7 +36939,7 @@
         <v>0</v>
       </c>
       <c r="AH286" s="7" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="287" spans="1:34" x14ac:dyDescent="0.15">
@@ -36881,7 +36962,7 @@
         <v>0</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H287" s="1">
         <v>1</v>
@@ -36954,7 +37035,7 @@
         <v>0</v>
       </c>
       <c r="AH287" s="7" t="s">
-        <v>1393</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="288" spans="1:34" x14ac:dyDescent="0.15">
@@ -36977,7 +37058,7 @@
         <v>0</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H288" s="1">
         <v>1</v>
@@ -37049,8 +37130,8 @@
       <c r="AG288" s="1">
         <v>0</v>
       </c>
-      <c r="AH288" s="7" t="s">
-        <v>1392</v>
+      <c r="AH288" s="50" t="s">
+        <v>1824</v>
       </c>
     </row>
     <row r="289" spans="1:34" x14ac:dyDescent="0.15">
@@ -37061,7 +37142,7 @@
         <v>4100</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>1640</v>
+        <v>1631</v>
       </c>
       <c r="D289" s="1">
         <v>3</v>
@@ -37073,7 +37154,7 @@
         <v>0</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H289" s="1">
         <v>1</v>
@@ -37146,7 +37227,7 @@
         <v>0</v>
       </c>
       <c r="AH289" s="8" t="s">
-        <v>1394</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="290" spans="1:34" x14ac:dyDescent="0.15">
@@ -37169,7 +37250,7 @@
         <v>0</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H290" s="1">
         <v>1</v>
@@ -37242,7 +37323,7 @@
         <v>0</v>
       </c>
       <c r="AH290" s="8" t="s">
-        <v>1395</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="291" spans="1:34" x14ac:dyDescent="0.15">
@@ -37253,7 +37334,7 @@
         <v>4103</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>1641</v>
+        <v>1632</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
@@ -37265,7 +37346,7 @@
         <v>0</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H291" s="1">
         <v>1</v>
@@ -37338,7 +37419,7 @@
         <v>0</v>
       </c>
       <c r="AH291" s="8" t="s">
-        <v>1396</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="292" spans="1:34" x14ac:dyDescent="0.15">
@@ -37349,7 +37430,7 @@
         <v>4105</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>1642</v>
+        <v>1633</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
@@ -37361,7 +37442,7 @@
         <v>0</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H292" s="1">
         <v>1</v>
@@ -37434,7 +37515,7 @@
         <v>0</v>
       </c>
       <c r="AH292" s="8" t="s">
-        <v>1397</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="293" spans="1:34" x14ac:dyDescent="0.15">
@@ -37445,7 +37526,7 @@
         <v>4106</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>1643</v>
+        <v>1634</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
@@ -37457,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H293" s="1">
         <v>1</v>
@@ -37530,7 +37611,7 @@
         <v>0</v>
       </c>
       <c r="AH293" s="8" t="s">
-        <v>1398</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="294" spans="1:34" x14ac:dyDescent="0.15">
@@ -37541,7 +37622,7 @@
         <v>4109</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>1644</v>
+        <v>1635</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -37553,7 +37634,7 @@
         <v>0</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H294" s="1">
         <v>1</v>
@@ -37625,7 +37706,7 @@
         <v>0</v>
       </c>
       <c r="AH294" s="8" t="s">
-        <v>1399</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="295" spans="1:34" x14ac:dyDescent="0.15">
@@ -37636,7 +37717,7 @@
         <v>4110</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>1645</v>
+        <v>1636</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -37648,7 +37729,7 @@
         <v>0</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H295" s="1">
         <v>1</v>
@@ -37721,7 +37802,7 @@
         <v>0</v>
       </c>
       <c r="AH295" s="8" t="s">
-        <v>1652</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="296" spans="1:34" x14ac:dyDescent="0.15">
@@ -37732,7 +37813,7 @@
         <v>4111</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>1646</v>
+        <v>1637</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -37744,7 +37825,7 @@
         <v>0</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H296" s="1">
         <v>1</v>
@@ -37817,7 +37898,7 @@
         <v>0</v>
       </c>
       <c r="AH296" s="8" t="s">
-        <v>1400</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="297" spans="1:34" x14ac:dyDescent="0.15">
@@ -37828,7 +37909,7 @@
         <v>4112</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>1647</v>
+        <v>1638</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -37840,7 +37921,7 @@
         <v>0</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H297" s="1">
         <v>1</v>
@@ -37913,7 +37994,7 @@
         <v>0</v>
       </c>
       <c r="AH297" s="8" t="s">
-        <v>1401</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="298" spans="1:34" x14ac:dyDescent="0.15">
@@ -37924,7 +38005,7 @@
         <v>4113</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>1648</v>
+        <v>1639</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -37936,7 +38017,7 @@
         <v>0</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H298" s="1">
         <v>1</v>
@@ -38009,7 +38090,7 @@
         <v>0</v>
       </c>
       <c r="AH298" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="299" spans="1:34" x14ac:dyDescent="0.15">
@@ -38032,7 +38113,7 @@
         <v>0</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H299" s="1">
         <v>1</v>
@@ -38105,7 +38186,7 @@
         <v>0</v>
       </c>
       <c r="AH299" s="8" t="s">
-        <v>1403</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="300" spans="1:34" x14ac:dyDescent="0.15">
@@ -38116,7 +38197,7 @@
         <v>4115</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>1649</v>
+        <v>1640</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -38128,7 +38209,7 @@
         <v>0</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H300" s="1">
         <v>1</v>
@@ -38201,7 +38282,7 @@
         <v>0</v>
       </c>
       <c r="AH300" s="8" t="s">
-        <v>1404</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="301" spans="1:34" x14ac:dyDescent="0.15">
@@ -38212,7 +38293,7 @@
         <v>4116</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>1650</v>
+        <v>1641</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -38224,7 +38305,7 @@
         <v>0</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="H301" s="1">
         <v>1</v>
@@ -38297,7 +38378,7 @@
         <v>0</v>
       </c>
       <c r="AH301" s="8" t="s">
-        <v>1405</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="302" spans="1:34" x14ac:dyDescent="0.15">
@@ -38320,7 +38401,7 @@
         <v>0</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="H302" s="1">
         <v>1</v>
@@ -38393,7 +38474,7 @@
         <v>0</v>
       </c>
       <c r="AH302" s="8" t="s">
-        <v>1406</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="303" spans="1:34" x14ac:dyDescent="0.15">
@@ -38416,7 +38497,7 @@
         <v>0</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H303" s="1">
         <v>1</v>
@@ -38488,7 +38569,7 @@
         <v>0</v>
       </c>
       <c r="AH303" s="34" t="s">
-        <v>1407</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="304" spans="1:34" x14ac:dyDescent="0.15">
@@ -38511,7 +38592,7 @@
         <v>0</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -38583,7 +38664,7 @@
         <v>0</v>
       </c>
       <c r="AH304" s="34" t="s">
-        <v>1408</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="305" spans="1:35" x14ac:dyDescent="0.15">
@@ -38606,7 +38687,7 @@
         <v>0</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
@@ -38678,7 +38759,7 @@
         <v>0</v>
       </c>
       <c r="AH305" s="34" t="s">
-        <v>1409</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="306" spans="1:35" x14ac:dyDescent="0.15">
@@ -38701,7 +38782,7 @@
         <v>0</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -38773,7 +38854,7 @@
         <v>0</v>
       </c>
       <c r="AH306" s="34" t="s">
-        <v>1410</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="307" spans="1:35" x14ac:dyDescent="0.15">
@@ -38796,7 +38877,7 @@
         <v>0</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1667</v>
+        <v>1658</v>
       </c>
       <c r="H307" s="1">
         <v>0</v>
@@ -38868,7 +38949,7 @@
         <v>0</v>
       </c>
       <c r="AH307" s="34" t="s">
-        <v>1411</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="308" spans="1:35" x14ac:dyDescent="0.15">
@@ -38891,7 +38972,7 @@
         <v>0</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H308" s="1">
         <v>1</v>
@@ -38963,7 +39044,7 @@
         <v>0</v>
       </c>
       <c r="AH308" s="34" t="s">
-        <v>1412</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="309" spans="1:35" x14ac:dyDescent="0.15">
@@ -38986,7 +39067,7 @@
         <v>0</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
       <c r="H309" s="1">
         <v>1</v>
@@ -39058,7 +39139,7 @@
         <v>0</v>
       </c>
       <c r="AH309" s="34" t="s">
-        <v>1413</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="310" spans="1:35" x14ac:dyDescent="0.15">
@@ -39081,7 +39162,7 @@
         <v>0</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
       <c r="H310" s="1">
         <v>1</v>
@@ -39153,7 +39234,7 @@
         <v>0</v>
       </c>
       <c r="AH310" s="34" t="s">
-        <v>1414</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="311" spans="1:35" x14ac:dyDescent="0.15">
@@ -39176,7 +39257,7 @@
         <v>0</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H311" s="1">
         <v>0</v>
@@ -39247,8 +39328,8 @@
       <c r="AG311" s="1">
         <v>0</v>
       </c>
-      <c r="AH311" s="34" t="s">
-        <v>1415</v>
+      <c r="AH311" s="35" t="s">
+        <v>1812</v>
       </c>
     </row>
     <row r="312" spans="1:35" x14ac:dyDescent="0.15">
@@ -39271,7 +39352,7 @@
         <v>0</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>1667</v>
+        <v>1658</v>
       </c>
       <c r="H312" s="1">
         <v>0</v>
@@ -39343,7 +39424,7 @@
         <v>0</v>
       </c>
       <c r="AH312" s="34" t="s">
-        <v>1416</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="313" spans="1:35" x14ac:dyDescent="0.15">
@@ -39366,7 +39447,7 @@
         <v>0</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="H313" s="1">
         <v>0</v>
@@ -39438,7 +39519,7 @@
         <v>0</v>
       </c>
       <c r="AH313" s="34" t="s">
-        <v>1417</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="314" spans="1:35" x14ac:dyDescent="0.15">
@@ -39461,7 +39542,7 @@
         <v>0</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
       <c r="H314" s="1">
         <v>1</v>
@@ -39533,7 +39614,7 @@
         <v>0</v>
       </c>
       <c r="AH314" s="34" t="s">
-        <v>1418</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="315" spans="1:35" x14ac:dyDescent="0.15">
@@ -39556,7 +39637,7 @@
         <v>0</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H315" s="1">
         <v>1</v>
@@ -39635,11 +39716,11 @@
       <c r="AG315" s="1">
         <v>0</v>
       </c>
-      <c r="AH315" s="34" t="s">
-        <v>1419</v>
+      <c r="AH315" s="35" t="s">
+        <v>1813</v>
       </c>
       <c r="AI315" s="1" t="s">
-        <v>1581</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="316" spans="1:35" x14ac:dyDescent="0.15">
@@ -39662,7 +39743,7 @@
         <v>0</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H316" s="1">
         <v>1</v>
@@ -39741,11 +39822,11 @@
       <c r="AG316" s="1">
         <v>0</v>
       </c>
-      <c r="AH316" s="34" t="s">
-        <v>1420</v>
+      <c r="AH316" s="35" t="s">
+        <v>1814</v>
       </c>
       <c r="AI316" s="1" t="s">
-        <v>1582</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="317" spans="1:35" x14ac:dyDescent="0.15">
@@ -39768,7 +39849,7 @@
         <v>0</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1804</v>
+        <v>1795</v>
       </c>
       <c r="H317" s="1">
         <v>1</v>
@@ -39848,10 +39929,10 @@
         <v>8</v>
       </c>
       <c r="AH317" s="34" t="s">
-        <v>1421</v>
+        <v>1412</v>
       </c>
       <c r="AI317" s="1" t="s">
-        <v>1619</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="318" spans="1:35" x14ac:dyDescent="0.15">
@@ -39874,7 +39955,7 @@
         <v>0</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H318" s="1">
         <v>1</v>
@@ -39953,11 +40034,11 @@
       <c r="AG318" s="1">
         <v>0</v>
       </c>
-      <c r="AH318" s="34" t="s">
-        <v>1422</v>
+      <c r="AH318" s="35" t="s">
+        <v>1804</v>
       </c>
       <c r="AI318" s="1" t="s">
-        <v>1583</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="319" spans="1:35" x14ac:dyDescent="0.15">
@@ -39980,7 +40061,7 @@
         <v>0</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1804</v>
+        <v>1795</v>
       </c>
       <c r="H319" s="1">
         <v>1</v>
@@ -40060,10 +40141,10 @@
         <v>0</v>
       </c>
       <c r="AH319" s="34" t="s">
-        <v>1423</v>
+        <v>1414</v>
       </c>
       <c r="AI319" s="1" t="s">
-        <v>1618</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="320" spans="1:35" x14ac:dyDescent="0.15">
@@ -40086,7 +40167,7 @@
         <v>0</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1805</v>
+        <v>1796</v>
       </c>
       <c r="H320" s="1">
         <v>1</v>
@@ -40166,10 +40247,10 @@
         <v>0</v>
       </c>
       <c r="AH320" s="34" t="s">
-        <v>1424</v>
+        <v>1415</v>
       </c>
       <c r="AI320" s="1" t="s">
-        <v>1620</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="321" spans="1:35" x14ac:dyDescent="0.15">
@@ -40192,7 +40273,7 @@
         <v>0</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1804</v>
+        <v>1795</v>
       </c>
       <c r="H321" s="1">
         <v>1</v>
@@ -40272,10 +40353,10 @@
         <v>0</v>
       </c>
       <c r="AH321" s="34" t="s">
-        <v>1425</v>
+        <v>1416</v>
       </c>
       <c r="AI321" s="1" t="s">
-        <v>1617</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="322" spans="1:35" x14ac:dyDescent="0.15">
@@ -40298,7 +40379,7 @@
         <v>0</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H322" s="1">
         <v>1</v>
@@ -40378,10 +40459,10 @@
         <v>0</v>
       </c>
       <c r="AH322" s="34" t="s">
-        <v>1426</v>
+        <v>1417</v>
       </c>
       <c r="AI322" s="1" t="s">
-        <v>1584</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="323" spans="1:35" x14ac:dyDescent="0.15">
@@ -40484,10 +40565,10 @@
         <v>0</v>
       </c>
       <c r="AH323" s="34" t="s">
-        <v>1427</v>
+        <v>1418</v>
       </c>
       <c r="AI323" s="1" t="s">
-        <v>1585</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="324" spans="1:35" x14ac:dyDescent="0.15">
@@ -40510,7 +40591,7 @@
         <v>0</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1806</v>
+        <v>1797</v>
       </c>
       <c r="H324" s="1">
         <v>1</v>
@@ -40590,10 +40671,10 @@
         <v>0</v>
       </c>
       <c r="AH324" s="34" t="s">
-        <v>1428</v>
+        <v>1419</v>
       </c>
       <c r="AI324" s="1" t="s">
-        <v>1616</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="325" spans="1:35" x14ac:dyDescent="0.15">
@@ -40695,8 +40776,8 @@
       <c r="AG325" s="1">
         <v>8</v>
       </c>
-      <c r="AH325" s="34" t="s">
-        <v>1429</v>
+      <c r="AH325" s="35" t="s">
+        <v>1815</v>
       </c>
       <c r="AI325" s="1" t="s">
         <v>636</v>
@@ -40722,7 +40803,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1804</v>
+        <v>1795</v>
       </c>
       <c r="H326" s="1">
         <v>1</v>
@@ -40802,10 +40883,10 @@
         <v>0</v>
       </c>
       <c r="AH326" s="34" t="s">
-        <v>1430</v>
+        <v>1421</v>
       </c>
       <c r="AI326" s="1" t="s">
-        <v>1615</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="327" spans="1:35" x14ac:dyDescent="0.15">
@@ -40828,7 +40909,7 @@
         <v>0</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1804</v>
+        <v>1795</v>
       </c>
       <c r="H327" s="1">
         <v>1</v>
@@ -40908,10 +40989,10 @@
         <v>0</v>
       </c>
       <c r="AH327" s="34" t="s">
-        <v>1431</v>
+        <v>1422</v>
       </c>
       <c r="AI327" s="1" t="s">
-        <v>1614</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="328" spans="1:35" x14ac:dyDescent="0.15">
@@ -41014,7 +41095,7 @@
         <v>8</v>
       </c>
       <c r="AH328" s="34" t="s">
-        <v>1432</v>
+        <v>1423</v>
       </c>
       <c r="AI328" s="1" t="s">
         <v>636</v>
@@ -41120,7 +41201,7 @@
         <v>8</v>
       </c>
       <c r="AH329" s="34" t="s">
-        <v>1433</v>
+        <v>1424</v>
       </c>
       <c r="AI329" s="1" t="s">
         <v>636</v>
@@ -41146,7 +41227,7 @@
         <v>0</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1804</v>
+        <v>1795</v>
       </c>
       <c r="H330" s="1">
         <v>1</v>
@@ -41225,11 +41306,11 @@
       <c r="AG330" s="1">
         <v>0</v>
       </c>
-      <c r="AH330" s="34" t="s">
-        <v>1434</v>
+      <c r="AH330" s="35" t="s">
+        <v>1803</v>
       </c>
       <c r="AI330" s="1" t="s">
-        <v>1613</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="331" spans="1:35" x14ac:dyDescent="0.15">
@@ -41252,7 +41333,7 @@
         <v>0</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H331" s="1">
         <v>1</v>
@@ -41331,11 +41412,11 @@
       <c r="AG331" s="1">
         <v>0</v>
       </c>
-      <c r="AH331" s="34" t="s">
-        <v>1435</v>
+      <c r="AH331" s="35" t="s">
+        <v>1816</v>
       </c>
       <c r="AI331" s="1" t="s">
-        <v>1612</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="332" spans="1:35" x14ac:dyDescent="0.15">
@@ -41358,7 +41439,7 @@
         <v>0</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H332" s="1">
         <v>1</v>
@@ -41438,10 +41519,10 @@
         <v>0</v>
       </c>
       <c r="AH332" s="34" t="s">
-        <v>1436</v>
+        <v>1427</v>
       </c>
       <c r="AI332" s="1" t="s">
-        <v>1586</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="333" spans="1:35" x14ac:dyDescent="0.15">
@@ -41464,7 +41545,7 @@
         <v>0</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H333" s="1">
         <v>1</v>
@@ -41543,11 +41624,11 @@
       <c r="AG333" s="1">
         <v>0</v>
       </c>
-      <c r="AH333" s="34" t="s">
-        <v>1437</v>
+      <c r="AH333" s="35" t="s">
+        <v>1811</v>
       </c>
       <c r="AI333" s="1" t="s">
-        <v>1611</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="334" spans="1:35" x14ac:dyDescent="0.15">
@@ -41650,10 +41731,10 @@
         <v>0</v>
       </c>
       <c r="AH334" s="34" t="s">
-        <v>1438</v>
+        <v>1429</v>
       </c>
       <c r="AI334" s="1" t="s">
-        <v>1587</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="335" spans="1:35" x14ac:dyDescent="0.15">
@@ -41676,7 +41757,7 @@
         <v>0</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>1808</v>
+        <v>1799</v>
       </c>
       <c r="H335" s="1">
         <v>1</v>
@@ -41756,7 +41837,7 @@
         <v>8</v>
       </c>
       <c r="AH335" s="34" t="s">
-        <v>1439</v>
+        <v>1430</v>
       </c>
       <c r="AI335" s="1" t="s">
         <v>636</v>
@@ -41782,7 +41863,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>1809</v>
+        <v>1800</v>
       </c>
       <c r="H336" s="1">
         <v>1</v>
@@ -41862,7 +41943,7 @@
         <v>8</v>
       </c>
       <c r="AH336" s="34" t="s">
-        <v>1440</v>
+        <v>1431</v>
       </c>
       <c r="AI336" s="1" t="s">
         <v>636</v>
@@ -41888,7 +41969,7 @@
         <v>0</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>1809</v>
+        <v>1800</v>
       </c>
       <c r="H337" s="1">
         <v>1</v>
@@ -41968,7 +42049,7 @@
         <v>8</v>
       </c>
       <c r="AH337" s="34" t="s">
-        <v>1441</v>
+        <v>1432</v>
       </c>
       <c r="AI337" s="1" t="s">
         <v>636</v>
@@ -41994,7 +42075,7 @@
         <v>0</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1809</v>
+        <v>1800</v>
       </c>
       <c r="H338" s="1">
         <v>1</v>
@@ -42073,8 +42154,8 @@
       <c r="AG338" s="1">
         <v>8</v>
       </c>
-      <c r="AH338" s="34" t="s">
-        <v>1442</v>
+      <c r="AH338" s="35" t="s">
+        <v>1817</v>
       </c>
       <c r="AI338" s="1" t="s">
         <v>636</v>
@@ -42100,7 +42181,7 @@
         <v>0</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>1809</v>
+        <v>1800</v>
       </c>
       <c r="H339" s="1">
         <v>1</v>
@@ -42180,7 +42261,7 @@
         <v>8</v>
       </c>
       <c r="AH339" s="34" t="s">
-        <v>1443</v>
+        <v>1434</v>
       </c>
       <c r="AI339" s="1" t="s">
         <v>636</v>
@@ -42206,7 +42287,7 @@
         <v>0</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>1809</v>
+        <v>1800</v>
       </c>
       <c r="H340" s="1">
         <v>1</v>
@@ -42286,7 +42367,7 @@
         <v>8</v>
       </c>
       <c r="AH340" s="34" t="s">
-        <v>1444</v>
+        <v>1435</v>
       </c>
       <c r="AI340" s="1" t="s">
         <v>636</v>
@@ -42312,7 +42393,7 @@
         <v>0</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1809</v>
+        <v>1800</v>
       </c>
       <c r="H341" s="1">
         <v>1</v>
@@ -42392,7 +42473,7 @@
         <v>8</v>
       </c>
       <c r="AH341" s="34" t="s">
-        <v>1445</v>
+        <v>1436</v>
       </c>
       <c r="AI341" s="1" t="s">
         <v>636</v>
@@ -42418,7 +42499,7 @@
         <v>0</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1808</v>
+        <v>1799</v>
       </c>
       <c r="H342" s="1">
         <v>1</v>
@@ -42498,7 +42579,7 @@
         <v>8</v>
       </c>
       <c r="AH342" s="34" t="s">
-        <v>1446</v>
+        <v>1437</v>
       </c>
       <c r="AI342" s="1" t="s">
         <v>636</v>
@@ -42604,10 +42685,10 @@
         <v>0</v>
       </c>
       <c r="AH343" s="34" t="s">
-        <v>1447</v>
+        <v>1438</v>
       </c>
       <c r="AI343" s="1" t="s">
-        <v>1588</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="344" spans="1:35" x14ac:dyDescent="0.15">
@@ -42630,7 +42711,7 @@
         <v>0</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>1808</v>
+        <v>1799</v>
       </c>
       <c r="H344" s="1">
         <v>1</v>
@@ -42710,7 +42791,7 @@
         <v>8</v>
       </c>
       <c r="AH344" s="34" t="s">
-        <v>1448</v>
+        <v>1439</v>
       </c>
       <c r="AI344" s="1" t="s">
         <v>636</v>
@@ -42736,7 +42817,7 @@
         <v>0</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1806</v>
+        <v>1797</v>
       </c>
       <c r="H345" s="1">
         <v>1</v>
@@ -42816,7 +42897,7 @@
         <v>0</v>
       </c>
       <c r="AH345" s="34" t="s">
-        <v>1449</v>
+        <v>1440</v>
       </c>
       <c r="AI345" s="1" t="s">
         <v>636</v>
@@ -42922,10 +43003,10 @@
         <v>0</v>
       </c>
       <c r="AH346" s="34" t="s">
-        <v>1450</v>
+        <v>1441</v>
       </c>
       <c r="AI346" s="1" t="s">
-        <v>1589</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="347" spans="1:35" ht="27" x14ac:dyDescent="0.15">
@@ -42948,7 +43029,7 @@
         <v>0</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>1804</v>
+        <v>1795</v>
       </c>
       <c r="H347" s="1">
         <v>1</v>
@@ -43028,10 +43109,10 @@
         <v>0</v>
       </c>
       <c r="AH347" s="34" t="s">
-        <v>1451</v>
+        <v>1442</v>
       </c>
       <c r="AI347" s="1" t="s">
-        <v>1590</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="348" spans="1:35" ht="27" x14ac:dyDescent="0.15">
@@ -43054,7 +43135,7 @@
         <v>0</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H348" s="1">
         <v>1</v>
@@ -43134,10 +43215,10 @@
         <v>0</v>
       </c>
       <c r="AH348" s="34" t="s">
-        <v>1452</v>
+        <v>1443</v>
       </c>
       <c r="AI348" s="1" t="s">
-        <v>1591</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="349" spans="1:35" x14ac:dyDescent="0.15">
@@ -43240,10 +43321,10 @@
         <v>0</v>
       </c>
       <c r="AH349" s="34" t="s">
-        <v>1453</v>
+        <v>1444</v>
       </c>
       <c r="AI349" s="1" t="s">
-        <v>1592</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="350" spans="1:35" x14ac:dyDescent="0.15">
@@ -43266,7 +43347,7 @@
         <v>0</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H350" s="1">
         <v>1</v>
@@ -43346,10 +43427,10 @@
         <v>0</v>
       </c>
       <c r="AH350" s="34" t="s">
-        <v>1454</v>
+        <v>1445</v>
       </c>
       <c r="AI350" s="1" t="s">
-        <v>1607</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="351" spans="1:35" x14ac:dyDescent="0.15">
@@ -43372,7 +43453,7 @@
         <v>0</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H351" s="1">
         <v>1</v>
@@ -43452,10 +43533,10 @@
         <v>0</v>
       </c>
       <c r="AH351" s="34" t="s">
-        <v>1455</v>
+        <v>1446</v>
       </c>
       <c r="AI351" s="1" t="s">
-        <v>1608</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="352" spans="1:35" x14ac:dyDescent="0.15">
@@ -43478,7 +43559,7 @@
         <v>0</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="H352" s="1">
         <v>1</v>
@@ -43558,10 +43639,10 @@
         <v>8</v>
       </c>
       <c r="AH352" s="34" t="s">
-        <v>1456</v>
+        <v>1447</v>
       </c>
       <c r="AI352" s="1" t="s">
-        <v>1609</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="353" spans="1:35" x14ac:dyDescent="0.15">
@@ -43584,7 +43665,7 @@
         <v>0</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>1677</v>
+        <v>1668</v>
       </c>
       <c r="H353" s="1">
         <v>1</v>
@@ -43664,7 +43745,7 @@
         <v>8</v>
       </c>
       <c r="AH353" s="34" t="s">
-        <v>1457</v>
+        <v>1448</v>
       </c>
       <c r="AI353" s="1" t="s">
         <v>636</v>
@@ -43690,7 +43771,7 @@
         <v>0</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
       <c r="H354" s="1">
         <v>1</v>
@@ -43770,10 +43851,10 @@
         <v>0</v>
       </c>
       <c r="AH354" s="34" t="s">
-        <v>1458</v>
+        <v>1449</v>
       </c>
       <c r="AI354" s="1" t="s">
-        <v>1610</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="355" spans="1:35" x14ac:dyDescent="0.15">
@@ -43796,7 +43877,7 @@
         <v>0</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>1802</v>
+        <v>1793</v>
       </c>
       <c r="H355" s="1">
         <v>1</v>
@@ -43876,10 +43957,10 @@
         <v>8</v>
       </c>
       <c r="AH355" s="34" t="s">
-        <v>1459</v>
+        <v>1450</v>
       </c>
       <c r="AI355" s="1" t="s">
-        <v>1608</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="356" spans="1:35" x14ac:dyDescent="0.15">
@@ -43902,7 +43983,7 @@
         <v>0</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>1801</v>
+        <v>1792</v>
       </c>
       <c r="H356" s="1">
         <v>1</v>
@@ -43982,7 +44063,7 @@
         <v>8</v>
       </c>
       <c r="AH356" s="34" t="s">
-        <v>1460</v>
+        <v>1451</v>
       </c>
       <c r="AI356" s="1" t="s">
         <v>636</v>
@@ -44088,7 +44169,7 @@
         <v>8</v>
       </c>
       <c r="AH357" s="34" t="s">
-        <v>1461</v>
+        <v>1452</v>
       </c>
       <c r="AI357" s="1" t="s">
         <v>636</v>
@@ -44194,7 +44275,7 @@
         <v>8</v>
       </c>
       <c r="AH358" s="34" t="s">
-        <v>1462</v>
+        <v>1453</v>
       </c>
       <c r="AI358" s="1" t="s">
         <v>636</v>
@@ -44300,7 +44381,7 @@
         <v>8</v>
       </c>
       <c r="AH359" s="34" t="s">
-        <v>1463</v>
+        <v>1454</v>
       </c>
       <c r="AI359" s="1" t="s">
         <v>636</v>
@@ -44406,7 +44487,7 @@
         <v>8</v>
       </c>
       <c r="AH360" s="34" t="s">
-        <v>1464</v>
+        <v>1455</v>
       </c>
       <c r="AI360" s="1" t="s">
         <v>636</v>
@@ -44512,7 +44593,7 @@
         <v>8</v>
       </c>
       <c r="AH361" s="34" t="s">
-        <v>1465</v>
+        <v>1456</v>
       </c>
       <c r="AI361" s="1" t="s">
         <v>636</v>
@@ -44618,7 +44699,7 @@
         <v>8</v>
       </c>
       <c r="AH362" s="34" t="s">
-        <v>1466</v>
+        <v>1457</v>
       </c>
       <c r="AI362" s="1" t="s">
         <v>636</v>
@@ -44724,7 +44805,7 @@
         <v>8</v>
       </c>
       <c r="AH363" s="34" t="s">
-        <v>1467</v>
+        <v>1458</v>
       </c>
       <c r="AI363" s="1" t="s">
         <v>636</v>
@@ -44830,7 +44911,7 @@
         <v>8</v>
       </c>
       <c r="AH364" s="34" t="s">
-        <v>1468</v>
+        <v>1459</v>
       </c>
       <c r="AI364" s="1" t="s">
         <v>636</v>
@@ -44936,7 +45017,7 @@
         <v>8</v>
       </c>
       <c r="AH365" s="34" t="s">
-        <v>1469</v>
+        <v>1825</v>
       </c>
       <c r="AI365" s="1" t="s">
         <v>636</v>
@@ -45042,7 +45123,7 @@
         <v>8</v>
       </c>
       <c r="AH366" s="34" t="s">
-        <v>1470</v>
+        <v>1461</v>
       </c>
       <c r="AI366" s="1" t="s">
         <v>636</v>
@@ -45148,7 +45229,7 @@
         <v>8</v>
       </c>
       <c r="AH367" s="34" t="s">
-        <v>1471</v>
+        <v>1828</v>
       </c>
       <c r="AI367" s="1" t="s">
         <v>636</v>
@@ -45253,11 +45334,11 @@
       <c r="AG368" s="1">
         <v>0</v>
       </c>
-      <c r="AH368" s="34" t="s">
-        <v>1472</v>
+      <c r="AH368" s="35" t="s">
+        <v>1805</v>
       </c>
       <c r="AI368" s="1" t="s">
-        <v>1651</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="369" spans="1:35" x14ac:dyDescent="0.15">
@@ -45360,7 +45441,7 @@
         <v>8</v>
       </c>
       <c r="AH369" s="34" t="s">
-        <v>1473</v>
+        <v>1464</v>
       </c>
       <c r="AI369" s="1" t="s">
         <v>636</v>
@@ -45465,8 +45546,8 @@
       <c r="AG370" s="1">
         <v>8</v>
       </c>
-      <c r="AH370" s="34" t="s">
-        <v>1474</v>
+      <c r="AH370" s="35" t="s">
+        <v>1807</v>
       </c>
       <c r="AI370" s="1" t="s">
         <v>636</v>
@@ -45572,10 +45653,10 @@
         <v>0</v>
       </c>
       <c r="AH371" s="34" t="s">
-        <v>1475</v>
+        <v>1466</v>
       </c>
       <c r="AI371" s="1" t="s">
-        <v>1606</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="372" spans="1:35" x14ac:dyDescent="0.15">
@@ -45678,10 +45759,10 @@
         <v>0</v>
       </c>
       <c r="AH372" s="34" t="s">
-        <v>1476</v>
+        <v>1467</v>
       </c>
       <c r="AI372" s="1" t="s">
-        <v>1605</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="373" spans="1:35" x14ac:dyDescent="0.15">
@@ -45784,10 +45865,10 @@
         <v>0</v>
       </c>
       <c r="AH373" s="34" t="s">
-        <v>1477</v>
+        <v>1468</v>
       </c>
       <c r="AI373" s="1" t="s">
-        <v>1604</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="374" spans="1:35" x14ac:dyDescent="0.15">
@@ -45889,11 +45970,11 @@
       <c r="AG374" s="1">
         <v>0</v>
       </c>
-      <c r="AH374" s="34" t="s">
-        <v>1478</v>
+      <c r="AH374" s="35" t="s">
+        <v>1810</v>
       </c>
       <c r="AI374" s="1" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="375" spans="1:35" x14ac:dyDescent="0.15">
@@ -45996,10 +46077,10 @@
         <v>0</v>
       </c>
       <c r="AH375" s="34" t="s">
-        <v>1479</v>
+        <v>1470</v>
       </c>
       <c r="AI375" s="1" t="s">
-        <v>1594</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="376" spans="1:35" x14ac:dyDescent="0.15">
@@ -46101,11 +46182,11 @@
       <c r="AG376" s="1">
         <v>0</v>
       </c>
-      <c r="AH376" s="34" t="s">
-        <v>1480</v>
+      <c r="AH376" s="35" t="s">
+        <v>1809</v>
       </c>
       <c r="AI376" s="1" t="s">
-        <v>1595</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="377" spans="1:35" x14ac:dyDescent="0.15">
@@ -46208,10 +46289,10 @@
         <v>0</v>
       </c>
       <c r="AH377" s="34" t="s">
-        <v>1481</v>
+        <v>1472</v>
       </c>
       <c r="AI377" s="1" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="378" spans="1:35" x14ac:dyDescent="0.15">
@@ -46314,7 +46395,7 @@
         <v>8</v>
       </c>
       <c r="AH378" s="34" t="s">
-        <v>1482</v>
+        <v>1473</v>
       </c>
       <c r="AI378" s="1" t="s">
         <v>636</v>
@@ -46419,8 +46500,8 @@
       <c r="AG379" s="1">
         <v>8</v>
       </c>
-      <c r="AH379" s="34" t="s">
-        <v>1483</v>
+      <c r="AH379" s="35" t="s">
+        <v>1806</v>
       </c>
       <c r="AI379" s="1" t="s">
         <v>636</v>
@@ -46526,7 +46607,7 @@
         <v>8</v>
       </c>
       <c r="AH380" s="34" t="s">
-        <v>1484</v>
+        <v>1475</v>
       </c>
       <c r="AI380" s="1" t="s">
         <v>636</v>
@@ -46552,7 +46633,7 @@
         <v>0</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>1810</v>
+        <v>1801</v>
       </c>
       <c r="H381" s="1">
         <v>1</v>
@@ -46631,11 +46712,11 @@
       <c r="AG381" s="1">
         <v>8</v>
       </c>
-      <c r="AH381" s="34" t="s">
-        <v>1485</v>
+      <c r="AH381" s="35" t="s">
+        <v>1808</v>
       </c>
       <c r="AI381" s="1" t="s">
-        <v>1603</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="382" spans="1:35" x14ac:dyDescent="0.15">
@@ -46658,7 +46739,7 @@
         <v>0</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H382" s="1">
         <v>1</v>
@@ -46738,10 +46819,10 @@
         <v>0</v>
       </c>
       <c r="AH382" s="34" t="s">
-        <v>1486</v>
+        <v>1477</v>
       </c>
       <c r="AI382" s="1" t="s">
-        <v>1602</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="383" spans="1:35" x14ac:dyDescent="0.15">
@@ -46764,7 +46845,7 @@
         <v>0</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H383" s="1">
         <v>1</v>
@@ -46844,10 +46925,10 @@
         <v>8</v>
       </c>
       <c r="AH383" s="34" t="s">
-        <v>1487</v>
+        <v>1478</v>
       </c>
       <c r="AI383" s="1" t="s">
-        <v>1601</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="384" spans="1:35" ht="27" x14ac:dyDescent="0.15">
@@ -46870,7 +46951,7 @@
         <v>0</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H384" s="1">
         <v>1</v>
@@ -46950,10 +47031,10 @@
         <v>0</v>
       </c>
       <c r="AH384" s="34" t="s">
-        <v>1488</v>
+        <v>1479</v>
       </c>
       <c r="AI384" s="1" t="s">
-        <v>1597</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="385" spans="1:35" x14ac:dyDescent="0.15">
@@ -46976,7 +47057,7 @@
         <v>0</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H385" s="1">
         <v>1</v>
@@ -47056,7 +47137,7 @@
         <v>8</v>
       </c>
       <c r="AH385" s="34" t="s">
-        <v>1489</v>
+        <v>1480</v>
       </c>
       <c r="AI385" s="1" t="s">
         <v>636</v>
@@ -47082,7 +47163,7 @@
         <v>0</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>1811</v>
+        <v>1802</v>
       </c>
       <c r="H386" s="1">
         <v>1</v>
@@ -47162,7 +47243,7 @@
         <v>8</v>
       </c>
       <c r="AH386" s="34" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="AI386" s="1" t="s">
         <v>636</v>
@@ -47188,7 +47269,7 @@
         <v>0</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H387" s="1">
         <v>1</v>
@@ -47268,7 +47349,7 @@
         <v>8</v>
       </c>
       <c r="AH387" s="34" t="s">
-        <v>1491</v>
+        <v>1482</v>
       </c>
       <c r="AI387" s="1" t="s">
         <v>636</v>
@@ -47294,7 +47375,7 @@
         <v>0</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H388" s="1">
         <v>1</v>
@@ -47374,10 +47455,10 @@
         <v>0</v>
       </c>
       <c r="AH388" s="34" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
       <c r="AI388" s="1" t="s">
-        <v>1600</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="389" spans="1:35" x14ac:dyDescent="0.15">
@@ -47400,7 +47481,7 @@
         <v>0</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>1811</v>
+        <v>1802</v>
       </c>
       <c r="H389" s="1">
         <v>1</v>
@@ -47480,7 +47561,7 @@
         <v>8</v>
       </c>
       <c r="AH389" s="34" t="s">
-        <v>1493</v>
+        <v>1484</v>
       </c>
       <c r="AI389" s="1" t="s">
         <v>636</v>
@@ -47506,7 +47587,7 @@
         <v>0</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>1811</v>
+        <v>1802</v>
       </c>
       <c r="H390" s="1">
         <v>1</v>
@@ -47586,7 +47667,7 @@
         <v>8</v>
       </c>
       <c r="AH390" s="34" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="AI390" s="1" t="s">
         <v>636</v>
@@ -47612,7 +47693,7 @@
         <v>0</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>1807</v>
+        <v>1798</v>
       </c>
       <c r="H391" s="1">
         <v>1</v>
@@ -47692,10 +47773,10 @@
         <v>0</v>
       </c>
       <c r="AH391" s="34" t="s">
-        <v>1495</v>
+        <v>1486</v>
       </c>
       <c r="AI391" s="1" t="s">
-        <v>1598</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="392" spans="1:35" x14ac:dyDescent="0.15">
@@ -47718,7 +47799,7 @@
         <v>0</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>1811</v>
+        <v>1802</v>
       </c>
       <c r="H392" s="1">
         <v>1</v>
@@ -47798,7 +47879,7 @@
         <v>8</v>
       </c>
       <c r="AH392" s="34" t="s">
-        <v>1496</v>
+        <v>1487</v>
       </c>
       <c r="AI392" s="1" t="s">
         <v>636</v>
@@ -47904,10 +47985,10 @@
         <v>0</v>
       </c>
       <c r="AH393" s="34" t="s">
-        <v>1497</v>
+        <v>1488</v>
       </c>
       <c r="AI393" s="1" t="s">
-        <v>1599</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="394" spans="1:35" x14ac:dyDescent="0.15">
@@ -47930,7 +48011,7 @@
         <v>0</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>1800</v>
+        <v>1791</v>
       </c>
       <c r="H394" s="1">
         <v>1</v>
@@ -48010,7 +48091,7 @@
         <v>8</v>
       </c>
       <c r="AH394" s="34" t="s">
-        <v>1498</v>
+        <v>1489</v>
       </c>
       <c r="AI394" s="1" t="s">
         <v>636</v>
@@ -48018,13 +48099,13 @@
     </row>
     <row r="395" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A395" s="1" t="s">
-        <v>1557</v>
+        <v>1548</v>
       </c>
       <c r="B395" s="1">
         <v>3500</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>1556</v>
+        <v>1547</v>
       </c>
       <c r="D395" s="1">
         <v>11</v>
@@ -48109,7 +48190,7 @@
         <v>0</v>
       </c>
       <c r="AH395" s="34" t="s">
-        <v>1566</v>
+        <v>1557</v>
       </c>
       <c r="AI395" s="1" t="s">
         <v>636</v>
@@ -48117,13 +48198,13 @@
     </row>
     <row r="396" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A396" s="1" t="s">
-        <v>1558</v>
+        <v>1549</v>
       </c>
       <c r="B396" s="1">
         <v>3501</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>1564</v>
+        <v>1555</v>
       </c>
       <c r="D396" s="1">
         <v>11</v>
@@ -48208,7 +48289,7 @@
         <v>0</v>
       </c>
       <c r="AH396" s="34" t="s">
-        <v>1567</v>
+        <v>1558</v>
       </c>
       <c r="AI396" s="1" t="s">
         <v>636</v>
@@ -48216,13 +48297,13 @@
     </row>
     <row r="397" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A397" s="1" t="s">
-        <v>1559</v>
+        <v>1550</v>
       </c>
       <c r="B397" s="1">
         <v>3502</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>1565</v>
+        <v>1556</v>
       </c>
       <c r="D397" s="1">
         <v>11</v>
@@ -48307,7 +48388,7 @@
         <v>0</v>
       </c>
       <c r="AH397" s="34" t="s">
-        <v>1568</v>
+        <v>1559</v>
       </c>
       <c r="AI397" s="1" t="s">
         <v>636</v>
@@ -48315,13 +48396,13 @@
     </row>
     <row r="398" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A398" s="1" t="s">
-        <v>1560</v>
+        <v>1551</v>
       </c>
       <c r="B398" s="1">
         <v>3503</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>1560</v>
+        <v>1551</v>
       </c>
       <c r="D398" s="1">
         <v>11</v>
@@ -48406,7 +48487,7 @@
         <v>0</v>
       </c>
       <c r="AH398" s="34" t="s">
-        <v>1569</v>
+        <v>1560</v>
       </c>
       <c r="AI398" s="1" t="s">
         <v>636</v>
@@ -48414,13 +48495,13 @@
     </row>
     <row r="399" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A399" s="1" t="s">
-        <v>1561</v>
+        <v>1552</v>
       </c>
       <c r="B399" s="1">
         <v>3504</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>1561</v>
+        <v>1552</v>
       </c>
       <c r="D399" s="1">
         <v>11</v>
@@ -48505,7 +48586,7 @@
         <v>0</v>
       </c>
       <c r="AH399" s="34" t="s">
-        <v>1571</v>
+        <v>1562</v>
       </c>
       <c r="AI399" s="1" t="s">
         <v>636</v>
@@ -48513,13 +48594,13 @@
     </row>
     <row r="400" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A400" s="1" t="s">
-        <v>1563</v>
+        <v>1554</v>
       </c>
       <c r="B400" s="1">
         <v>3505</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>1563</v>
+        <v>1554</v>
       </c>
       <c r="D400" s="1">
         <v>11</v>
@@ -48604,7 +48685,7 @@
         <v>0</v>
       </c>
       <c r="AH400" s="34" t="s">
-        <v>1572</v>
+        <v>1563</v>
       </c>
       <c r="AI400" s="1" t="s">
         <v>636</v>
@@ -48612,13 +48693,13 @@
     </row>
     <row r="401" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A401" s="1" t="s">
-        <v>1562</v>
+        <v>1553</v>
       </c>
       <c r="B401" s="1">
         <v>3506</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>1562</v>
+        <v>1553</v>
       </c>
       <c r="D401" s="1">
         <v>11</v>
@@ -48703,7 +48784,7 @@
         <v>0</v>
       </c>
       <c r="AH401" s="34" t="s">
-        <v>1570</v>
+        <v>1561</v>
       </c>
       <c r="AI401" s="1" t="s">
         <v>636</v>
@@ -48801,7 +48882,7 @@
         <v>0</v>
       </c>
       <c r="AH402" s="1" t="s">
-        <v>1510</v>
+        <v>1501</v>
       </c>
       <c r="AI402" s="1" t="s">
         <v>636</v>
@@ -48899,7 +48980,7 @@
         <v>0</v>
       </c>
       <c r="AH403" s="1" t="s">
-        <v>1512</v>
+        <v>1503</v>
       </c>
       <c r="AI403" s="1" t="s">
         <v>636</v>
@@ -48997,7 +49078,7 @@
         <v>0</v>
       </c>
       <c r="AH404" s="1" t="s">
-        <v>1514</v>
+        <v>1505</v>
       </c>
       <c r="AI404" s="1" t="s">
         <v>636</v>
@@ -49095,7 +49176,7 @@
         <v>0</v>
       </c>
       <c r="AH405" s="1" t="s">
-        <v>1516</v>
+        <v>1507</v>
       </c>
       <c r="AI405" s="1" t="s">
         <v>636</v>
@@ -49193,7 +49274,7 @@
         <v>0</v>
       </c>
       <c r="AH406" s="1" t="s">
-        <v>1518</v>
+        <v>1509</v>
       </c>
       <c r="AI406" s="1" t="s">
         <v>636</v>
@@ -49291,7 +49372,7 @@
         <v>0</v>
       </c>
       <c r="AH407" s="1" t="s">
-        <v>1520</v>
+        <v>1511</v>
       </c>
       <c r="AI407" s="1" t="s">
         <v>636</v>
@@ -49389,7 +49470,7 @@
         <v>0</v>
       </c>
       <c r="AH408" s="1" t="s">
-        <v>1522</v>
+        <v>1513</v>
       </c>
       <c r="AI408" s="1" t="s">
         <v>636</v>
@@ -49487,7 +49568,7 @@
         <v>0</v>
       </c>
       <c r="AH409" s="1" t="s">
-        <v>1524</v>
+        <v>1515</v>
       </c>
       <c r="AI409" s="1" t="s">
         <v>636</v>
@@ -49585,7 +49666,7 @@
         <v>0</v>
       </c>
       <c r="AH410" s="1" t="s">
-        <v>1526</v>
+        <v>1517</v>
       </c>
       <c r="AI410" s="1" t="s">
         <v>636</v>
@@ -49683,7 +49764,7 @@
         <v>0</v>
       </c>
       <c r="AH411" s="1" t="s">
-        <v>1528</v>
+        <v>1519</v>
       </c>
       <c r="AI411" s="1" t="s">
         <v>636</v>
@@ -49781,7 +49862,7 @@
         <v>0</v>
       </c>
       <c r="AH412" s="1" t="s">
-        <v>1530</v>
+        <v>1521</v>
       </c>
       <c r="AI412" s="1" t="s">
         <v>636</v>
@@ -64757,7 +64838,7 @@
     </row>
     <row r="4" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G4" s="7" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
       <c r="I4" s="34">
         <v>3</v>
@@ -64778,7 +64859,7 @@
         <v>4</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
       <c r="K5" s="38">
         <f t="shared" si="0"/>
@@ -64802,7 +64883,7 @@
     </row>
     <row r="7" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G7" s="7" t="s">
-        <v>1536</v>
+        <v>1527</v>
       </c>
       <c r="I7" s="34">
         <v>6</v>
@@ -64868,7 +64949,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>1536</v>
+        <v>1527</v>
       </c>
       <c r="K11" s="38">
         <f t="shared" si="0"/>
@@ -65225,7 +65306,7 @@
         <v>139</v>
       </c>
       <c r="I1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="2" spans="8:9" x14ac:dyDescent="0.15">
@@ -65233,7 +65314,7 @@
         <v>140</v>
       </c>
       <c r="I2" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="3" spans="8:9" x14ac:dyDescent="0.15">
@@ -65241,7 +65322,7 @@
         <v>141</v>
       </c>
       <c r="I3" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="4" spans="8:9" x14ac:dyDescent="0.15">
@@ -65249,7 +65330,7 @@
         <v>142</v>
       </c>
       <c r="I4" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="5" spans="8:9" x14ac:dyDescent="0.15">
@@ -65257,7 +65338,7 @@
         <v>192</v>
       </c>
       <c r="I5" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="6" spans="8:9" x14ac:dyDescent="0.15">
@@ -65265,7 +65346,7 @@
         <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7" spans="8:9" x14ac:dyDescent="0.15">
@@ -65273,7 +65354,7 @@
         <v>922</v>
       </c>
       <c r="I7" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="8" spans="8:9" x14ac:dyDescent="0.15">
@@ -65281,7 +65362,7 @@
         <v>958</v>
       </c>
       <c r="I8" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="9" spans="8:9" x14ac:dyDescent="0.15">
@@ -65289,7 +65370,7 @@
         <v>146</v>
       </c>
       <c r="I9" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="10" spans="8:9" x14ac:dyDescent="0.15">
@@ -65297,7 +65378,7 @@
         <v>147</v>
       </c>
       <c r="I10" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="11" spans="8:9" x14ac:dyDescent="0.15">
@@ -65305,7 +65386,7 @@
         <v>148</v>
       </c>
       <c r="I11" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="12" spans="8:9" x14ac:dyDescent="0.15">
@@ -65313,7 +65394,7 @@
         <v>149</v>
       </c>
       <c r="I12" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="13" spans="8:9" x14ac:dyDescent="0.15">
@@ -65321,7 +65402,7 @@
         <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="14" spans="8:9" x14ac:dyDescent="0.15">
@@ -65329,7 +65410,7 @@
         <v>151</v>
       </c>
       <c r="I14" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="15" spans="8:9" x14ac:dyDescent="0.15">
@@ -65337,7 +65418,7 @@
         <v>152</v>
       </c>
       <c r="I15" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="16" spans="8:9" x14ac:dyDescent="0.15">
@@ -65345,7 +65426,7 @@
         <v>187</v>
       </c>
       <c r="I16" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.15">
@@ -65353,7 +65434,7 @@
         <v>188</v>
       </c>
       <c r="I17" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.15">
@@ -65361,7 +65442,7 @@
         <v>189</v>
       </c>
       <c r="I18" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="19" spans="8:9" x14ac:dyDescent="0.15">
@@ -65369,7 +65450,7 @@
         <v>858</v>
       </c>
       <c r="I19" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="20" spans="8:9" x14ac:dyDescent="0.15">
@@ -65377,7 +65458,7 @@
         <v>193</v>
       </c>
       <c r="I20" t="s">
-        <v>1667</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="21" spans="8:9" x14ac:dyDescent="0.15">
@@ -65385,7 +65466,7 @@
         <v>162</v>
       </c>
       <c r="I21" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="22" spans="8:9" x14ac:dyDescent="0.15">
@@ -65393,7 +65474,7 @@
         <v>159</v>
       </c>
       <c r="I22" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="23" spans="8:9" x14ac:dyDescent="0.15">
@@ -65401,7 +65482,7 @@
         <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="24" spans="8:9" x14ac:dyDescent="0.15">
@@ -65409,7 +65490,7 @@
         <v>174</v>
       </c>
       <c r="I24" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="25" spans="8:9" x14ac:dyDescent="0.15">
@@ -65417,7 +65498,7 @@
         <v>178</v>
       </c>
       <c r="I25" t="s">
-        <v>1667</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="26" spans="8:9" x14ac:dyDescent="0.15">
@@ -65425,7 +65506,7 @@
         <v>250</v>
       </c>
       <c r="I26" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="27" spans="8:9" x14ac:dyDescent="0.15">
@@ -65433,7 +65514,7 @@
         <v>205</v>
       </c>
       <c r="I27" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="28" spans="8:9" x14ac:dyDescent="0.15">
@@ -65441,7 +65522,7 @@
         <v>795</v>
       </c>
       <c r="I28" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="29" spans="8:9" x14ac:dyDescent="0.15">
@@ -65449,7 +65530,7 @@
         <v>163</v>
       </c>
       <c r="I29" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="30" spans="8:9" x14ac:dyDescent="0.15">
@@ -65457,7 +65538,7 @@
         <v>184</v>
       </c>
       <c r="I30" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="31" spans="8:9" x14ac:dyDescent="0.15">
@@ -65465,7 +65546,7 @@
         <v>166</v>
       </c>
       <c r="I31" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="32" spans="8:9" x14ac:dyDescent="0.15">
@@ -65473,7 +65554,7 @@
         <v>182</v>
       </c>
       <c r="I32" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="33" spans="8:9" x14ac:dyDescent="0.15">
@@ -65481,7 +65562,7 @@
         <v>194</v>
       </c>
       <c r="I33" t="s">
-        <v>1667</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="34" spans="8:9" x14ac:dyDescent="0.15">
@@ -65489,7 +65570,7 @@
         <v>195</v>
       </c>
       <c r="I34" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="35" spans="8:9" x14ac:dyDescent="0.15">
@@ -65497,7 +65578,7 @@
         <v>165</v>
       </c>
       <c r="I35" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="36" spans="8:9" x14ac:dyDescent="0.15">
@@ -65505,7 +65586,7 @@
         <v>167</v>
       </c>
       <c r="I36" t="s">
-        <v>1671</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="37" spans="8:9" x14ac:dyDescent="0.15">
@@ -65513,7 +65594,7 @@
         <v>196</v>
       </c>
       <c r="I37" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="38" spans="8:9" x14ac:dyDescent="0.15">
@@ -65521,7 +65602,7 @@
         <v>164</v>
       </c>
       <c r="I38" t="s">
-        <v>1672</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="39" spans="8:9" x14ac:dyDescent="0.15">
@@ -65529,7 +65610,7 @@
         <v>197</v>
       </c>
       <c r="I39" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="40" spans="8:9" x14ac:dyDescent="0.15">
@@ -65537,7 +65618,7 @@
         <v>796</v>
       </c>
       <c r="I40" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="41" spans="8:9" x14ac:dyDescent="0.15">
@@ -65545,7 +65626,7 @@
         <v>198</v>
       </c>
       <c r="I41" t="s">
-        <v>1672</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="42" spans="8:9" x14ac:dyDescent="0.15">
@@ -65553,7 +65634,7 @@
         <v>171</v>
       </c>
       <c r="I42" t="s">
-        <v>1672</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="43" spans="8:9" x14ac:dyDescent="0.15">
@@ -65561,7 +65642,7 @@
         <v>199</v>
       </c>
       <c r="I43" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="44" spans="8:9" x14ac:dyDescent="0.15">
@@ -65569,7 +65650,7 @@
         <v>200</v>
       </c>
       <c r="I44" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="45" spans="8:9" x14ac:dyDescent="0.15">
@@ -65577,7 +65658,7 @@
         <v>170</v>
       </c>
       <c r="I45" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="46" spans="8:9" x14ac:dyDescent="0.15">
@@ -65585,7 +65666,7 @@
         <v>201</v>
       </c>
       <c r="I46" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="47" spans="8:9" x14ac:dyDescent="0.15">
@@ -65593,7 +65674,7 @@
         <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>1671</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="48" spans="8:9" x14ac:dyDescent="0.15">
@@ -65601,7 +65682,7 @@
         <v>202</v>
       </c>
       <c r="I48" t="s">
-        <v>1674</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="49" spans="8:9" x14ac:dyDescent="0.15">
@@ -65609,7 +65690,7 @@
         <v>185</v>
       </c>
       <c r="I49" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="50" spans="8:9" x14ac:dyDescent="0.15">
@@ -65617,7 +65698,7 @@
         <v>168</v>
       </c>
       <c r="I50" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="51" spans="8:9" x14ac:dyDescent="0.15">
@@ -65625,7 +65706,7 @@
         <v>175</v>
       </c>
       <c r="I51" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="52" spans="8:9" x14ac:dyDescent="0.15">
@@ -65633,7 +65714,7 @@
         <v>177</v>
       </c>
       <c r="I52" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="53" spans="8:9" x14ac:dyDescent="0.15">
@@ -65641,7 +65722,7 @@
         <v>179</v>
       </c>
       <c r="I53" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="54" spans="8:9" x14ac:dyDescent="0.15">
@@ -65649,7 +65730,7 @@
         <v>180</v>
       </c>
       <c r="I54" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="55" spans="8:9" x14ac:dyDescent="0.15">
@@ -65657,7 +65738,7 @@
         <v>203</v>
       </c>
       <c r="I55" t="s">
-        <v>1674</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="56" spans="8:9" x14ac:dyDescent="0.15">
@@ -65665,7 +65746,7 @@
         <v>204</v>
       </c>
       <c r="I56" t="s">
-        <v>1671</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="57" spans="8:9" x14ac:dyDescent="0.15">
@@ -65673,7 +65754,7 @@
         <v>181</v>
       </c>
       <c r="I57" t="s">
-        <v>1674</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="58" spans="8:9" x14ac:dyDescent="0.15">
@@ -65681,7 +65762,7 @@
         <v>206</v>
       </c>
       <c r="I58" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="59" spans="8:9" x14ac:dyDescent="0.15">
@@ -65689,7 +65770,7 @@
         <v>207</v>
       </c>
       <c r="I59" t="s">
-        <v>1671</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="60" spans="8:9" x14ac:dyDescent="0.15">
@@ -65697,7 +65778,7 @@
         <v>183</v>
       </c>
       <c r="I60" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="61" spans="8:9" x14ac:dyDescent="0.15">
@@ -65705,7 +65786,7 @@
         <v>208</v>
       </c>
       <c r="I61" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="62" spans="8:9" x14ac:dyDescent="0.15">
@@ -65713,7 +65794,7 @@
         <v>209</v>
       </c>
       <c r="I62" t="s">
-        <v>1671</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="63" spans="8:9" x14ac:dyDescent="0.15">
@@ -65721,7 +65802,7 @@
         <v>210</v>
       </c>
       <c r="I63" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="64" spans="8:9" x14ac:dyDescent="0.15">
@@ -65729,7 +65810,7 @@
         <v>169</v>
       </c>
       <c r="I64" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="65" spans="8:9" x14ac:dyDescent="0.15">
@@ -65737,7 +65818,7 @@
         <v>211</v>
       </c>
       <c r="I65" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="66" spans="8:9" x14ac:dyDescent="0.15">
@@ -65745,7 +65826,7 @@
         <v>212</v>
       </c>
       <c r="I66" t="s">
-        <v>1677</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="67" spans="8:9" x14ac:dyDescent="0.15">
@@ -65753,7 +65834,7 @@
         <v>213</v>
       </c>
       <c r="I67" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="68" spans="8:9" x14ac:dyDescent="0.15">
@@ -65761,7 +65842,7 @@
         <v>214</v>
       </c>
       <c r="I68" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="69" spans="8:9" x14ac:dyDescent="0.15">
@@ -65769,7 +65850,7 @@
         <v>215</v>
       </c>
       <c r="I69" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="70" spans="8:9" x14ac:dyDescent="0.15">
@@ -65777,7 +65858,7 @@
         <v>176</v>
       </c>
       <c r="I70" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="71" spans="8:9" x14ac:dyDescent="0.15">
@@ -65785,7 +65866,7 @@
         <v>186</v>
       </c>
       <c r="I71" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="72" spans="8:9" x14ac:dyDescent="0.15">
@@ -65793,7 +65874,7 @@
         <v>173</v>
       </c>
       <c r="I72" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="73" spans="8:9" x14ac:dyDescent="0.15">
@@ -65801,7 +65882,7 @@
         <v>216</v>
       </c>
       <c r="I73" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="74" spans="8:9" x14ac:dyDescent="0.15">
@@ -65809,7 +65890,7 @@
         <v>217</v>
       </c>
       <c r="I74" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="75" spans="8:9" x14ac:dyDescent="0.15">
@@ -65817,7 +65898,7 @@
         <v>218</v>
       </c>
       <c r="I75" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="76" spans="8:9" x14ac:dyDescent="0.15">
@@ -65825,7 +65906,7 @@
         <v>219</v>
       </c>
       <c r="I76" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="77" spans="8:9" x14ac:dyDescent="0.15">
@@ -65833,7 +65914,7 @@
         <v>797</v>
       </c>
       <c r="I77" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="78" spans="8:9" x14ac:dyDescent="0.15">
@@ -65841,7 +65922,7 @@
         <v>220</v>
       </c>
       <c r="I78" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="79" spans="8:9" x14ac:dyDescent="0.15">
@@ -65849,7 +65930,7 @@
         <v>221</v>
       </c>
       <c r="I79" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="80" spans="8:9" x14ac:dyDescent="0.15">
@@ -65857,7 +65938,7 @@
         <v>222</v>
       </c>
       <c r="I80" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="81" spans="8:9" x14ac:dyDescent="0.15">
@@ -65865,7 +65946,7 @@
         <v>223</v>
       </c>
       <c r="I81" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="82" spans="8:9" x14ac:dyDescent="0.15">
@@ -65873,7 +65954,7 @@
         <v>224</v>
       </c>
       <c r="I82" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="83" spans="8:9" x14ac:dyDescent="0.15">
@@ -65881,7 +65962,7 @@
         <v>225</v>
       </c>
       <c r="I83" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="84" spans="8:9" x14ac:dyDescent="0.15">
@@ -65889,7 +65970,7 @@
         <v>226</v>
       </c>
       <c r="I84" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="85" spans="8:9" x14ac:dyDescent="0.15">
@@ -65897,7 +65978,7 @@
         <v>227</v>
       </c>
       <c r="I85" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="86" spans="8:9" x14ac:dyDescent="0.15">
@@ -65905,7 +65986,7 @@
         <v>228</v>
       </c>
       <c r="I86" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="87" spans="8:9" x14ac:dyDescent="0.15">
@@ -65913,7 +65994,7 @@
         <v>229</v>
       </c>
       <c r="I87" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="88" spans="8:9" x14ac:dyDescent="0.15">
@@ -65921,7 +66002,7 @@
         <v>230</v>
       </c>
       <c r="I88" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="89" spans="8:9" x14ac:dyDescent="0.15">
@@ -65929,7 +66010,7 @@
         <v>231</v>
       </c>
       <c r="I89" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="90" spans="8:9" x14ac:dyDescent="0.15">
@@ -65937,7 +66018,7 @@
         <v>232</v>
       </c>
       <c r="I90" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="91" spans="8:9" x14ac:dyDescent="0.15">
@@ -65945,7 +66026,7 @@
         <v>233</v>
       </c>
       <c r="I91" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="92" spans="8:9" x14ac:dyDescent="0.15">
@@ -65953,7 +66034,7 @@
         <v>234</v>
       </c>
       <c r="I92" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="93" spans="8:9" x14ac:dyDescent="0.15">
@@ -65961,7 +66042,7 @@
         <v>235</v>
       </c>
       <c r="I93" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="94" spans="8:9" x14ac:dyDescent="0.15">
@@ -65969,7 +66050,7 @@
         <v>236</v>
       </c>
       <c r="I94" t="s">
-        <v>1680</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="95" spans="8:9" x14ac:dyDescent="0.15">
@@ -65977,7 +66058,7 @@
         <v>237</v>
       </c>
       <c r="I95" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="96" spans="8:9" x14ac:dyDescent="0.15">
@@ -65985,7 +66066,7 @@
         <v>238</v>
       </c>
       <c r="I96" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="97" spans="8:9" x14ac:dyDescent="0.15">
@@ -65993,7 +66074,7 @@
         <v>239</v>
       </c>
       <c r="I97" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="98" spans="8:9" x14ac:dyDescent="0.15">
@@ -66001,7 +66082,7 @@
         <v>240</v>
       </c>
       <c r="I98" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="99" spans="8:9" x14ac:dyDescent="0.15">
@@ -66009,7 +66090,7 @@
         <v>241</v>
       </c>
       <c r="I99" t="s">
-        <v>1681</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="100" spans="8:9" x14ac:dyDescent="0.15">
@@ -66017,7 +66098,7 @@
         <v>242</v>
       </c>
       <c r="I100" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="101" spans="8:9" x14ac:dyDescent="0.15">
@@ -66025,7 +66106,7 @@
         <v>243</v>
       </c>
       <c r="I101" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="102" spans="8:9" x14ac:dyDescent="0.15">
@@ -66033,7 +66114,7 @@
         <v>244</v>
       </c>
       <c r="I102" t="s">
-        <v>1681</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="103" spans="8:9" x14ac:dyDescent="0.15">
@@ -66041,7 +66122,7 @@
         <v>245</v>
       </c>
       <c r="I103" t="s">
-        <v>1681</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="104" spans="8:9" x14ac:dyDescent="0.15">
@@ -66049,7 +66130,7 @@
         <v>246</v>
       </c>
       <c r="I104" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="105" spans="8:9" x14ac:dyDescent="0.15">
@@ -66057,7 +66138,7 @@
         <v>247</v>
       </c>
       <c r="I105" t="s">
-        <v>1681</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="106" spans="8:9" x14ac:dyDescent="0.15">
@@ -66065,7 +66146,7 @@
         <v>248</v>
       </c>
       <c r="I106" t="s">
-        <v>1682</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="107" spans="8:9" x14ac:dyDescent="0.15">
@@ -66073,7 +66154,7 @@
         <v>798</v>
       </c>
       <c r="I107" t="s">
-        <v>1683</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="108" spans="8:9" x14ac:dyDescent="0.15">
@@ -66081,7 +66162,7 @@
         <v>330</v>
       </c>
       <c r="I108" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="109" spans="8:9" x14ac:dyDescent="0.15">
@@ -66089,7 +66170,7 @@
         <v>331</v>
       </c>
       <c r="I109" t="s">
-        <v>1685</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="110" spans="8:9" x14ac:dyDescent="0.15">
@@ -66097,7 +66178,7 @@
         <v>391</v>
       </c>
       <c r="I110" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="111" spans="8:9" x14ac:dyDescent="0.15">
@@ -66105,7 +66186,7 @@
         <v>332</v>
       </c>
       <c r="I111" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="112" spans="8:9" x14ac:dyDescent="0.15">
@@ -66113,7 +66194,7 @@
         <v>392</v>
       </c>
       <c r="I112" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="113" spans="8:9" x14ac:dyDescent="0.15">
@@ -66121,7 +66202,7 @@
         <v>333</v>
       </c>
       <c r="I113" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="114" spans="8:9" x14ac:dyDescent="0.15">
@@ -66129,7 +66210,7 @@
         <v>334</v>
       </c>
       <c r="I114" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="115" spans="8:9" x14ac:dyDescent="0.15">
@@ -66137,7 +66218,7 @@
         <v>827</v>
       </c>
       <c r="I115" t="s">
-        <v>1685</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="116" spans="8:9" x14ac:dyDescent="0.15">
@@ -66145,7 +66226,7 @@
         <v>335</v>
       </c>
       <c r="I116" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="117" spans="8:9" x14ac:dyDescent="0.15">
@@ -66153,7 +66234,7 @@
         <v>336</v>
       </c>
       <c r="I117" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="118" spans="8:9" x14ac:dyDescent="0.15">
@@ -66161,7 +66242,7 @@
         <v>337</v>
       </c>
       <c r="I118" t="s">
-        <v>1689</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="119" spans="8:9" x14ac:dyDescent="0.15">
@@ -66169,7 +66250,7 @@
         <v>338</v>
       </c>
       <c r="I119" t="s">
-        <v>1690</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="120" spans="8:9" x14ac:dyDescent="0.15">
@@ -66177,7 +66258,7 @@
         <v>339</v>
       </c>
       <c r="I120" t="s">
-        <v>1691</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="121" spans="8:9" x14ac:dyDescent="0.15">
@@ -66185,15 +66266,15 @@
         <v>773</v>
       </c>
       <c r="I121" t="s">
-        <v>1692</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="122" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H122" s="7" t="s">
-        <v>1654</v>
+        <v>1645</v>
       </c>
       <c r="I122" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="123" spans="8:9" x14ac:dyDescent="0.15">
@@ -66201,7 +66282,7 @@
         <v>341</v>
       </c>
       <c r="I123" t="s">
-        <v>1693</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="124" spans="8:9" x14ac:dyDescent="0.15">
@@ -66209,7 +66290,7 @@
         <v>342</v>
       </c>
       <c r="I124" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="125" spans="8:9" x14ac:dyDescent="0.15">
@@ -66217,7 +66298,7 @@
         <v>616</v>
       </c>
       <c r="I125" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="126" spans="8:9" x14ac:dyDescent="0.15">
@@ -66225,7 +66306,7 @@
         <v>617</v>
       </c>
       <c r="I126" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="127" spans="8:9" x14ac:dyDescent="0.15">
@@ -66233,7 +66314,7 @@
         <v>618</v>
       </c>
       <c r="I127" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="128" spans="8:9" x14ac:dyDescent="0.15">
@@ -66241,7 +66322,7 @@
         <v>619</v>
       </c>
       <c r="I128" t="s">
-        <v>1694</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="129" spans="8:9" x14ac:dyDescent="0.15">
@@ -66249,7 +66330,7 @@
         <v>351</v>
       </c>
       <c r="I129" t="s">
-        <v>1695</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="130" spans="8:9" x14ac:dyDescent="0.15">
@@ -66257,7 +66338,7 @@
         <v>349</v>
       </c>
       <c r="I130" t="s">
-        <v>1696</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="131" spans="8:9" x14ac:dyDescent="0.15">
@@ -66265,7 +66346,7 @@
         <v>394</v>
       </c>
       <c r="I131" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="132" spans="8:9" x14ac:dyDescent="0.15">
@@ -66273,7 +66354,7 @@
         <v>395</v>
       </c>
       <c r="I132" t="s">
-        <v>1698</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="133" spans="8:9" x14ac:dyDescent="0.15">
@@ -66281,7 +66362,7 @@
         <v>353</v>
       </c>
       <c r="I133" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="134" spans="8:9" x14ac:dyDescent="0.15">
@@ -66289,7 +66370,7 @@
         <v>396</v>
       </c>
       <c r="I134" t="s">
-        <v>1699</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="135" spans="8:9" x14ac:dyDescent="0.15">
@@ -66297,7 +66378,7 @@
         <v>667</v>
       </c>
       <c r="I135" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="136" spans="8:9" x14ac:dyDescent="0.15">
@@ -66305,7 +66386,7 @@
         <v>355</v>
       </c>
       <c r="I136" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="137" spans="8:9" x14ac:dyDescent="0.15">
@@ -66313,7 +66394,7 @@
         <v>397</v>
       </c>
       <c r="I137" t="s">
-        <v>1698</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="138" spans="8:9" x14ac:dyDescent="0.15">
@@ -66321,7 +66402,7 @@
         <v>398</v>
       </c>
       <c r="I138" t="s">
-        <v>1701</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="139" spans="8:9" x14ac:dyDescent="0.15">
@@ -66329,7 +66410,7 @@
         <v>399</v>
       </c>
       <c r="I139" t="s">
-        <v>1695</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="140" spans="8:9" x14ac:dyDescent="0.15">
@@ -66337,7 +66418,7 @@
         <v>400</v>
       </c>
       <c r="I140" t="s">
-        <v>1702</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="141" spans="8:9" x14ac:dyDescent="0.15">
@@ -66345,7 +66426,7 @@
         <v>401</v>
       </c>
       <c r="I141" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="142" spans="8:9" x14ac:dyDescent="0.15">
@@ -66353,7 +66434,7 @@
         <v>402</v>
       </c>
       <c r="I142" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="143" spans="8:9" x14ac:dyDescent="0.15">
@@ -66361,7 +66442,7 @@
         <v>403</v>
       </c>
       <c r="I143" t="s">
-        <v>1703</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="144" spans="8:9" x14ac:dyDescent="0.15">
@@ -66369,7 +66450,7 @@
         <v>390</v>
       </c>
       <c r="I144" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="145" spans="8:9" x14ac:dyDescent="0.15">
@@ -66377,7 +66458,7 @@
         <v>620</v>
       </c>
       <c r="I145" t="s">
-        <v>1704</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="146" spans="8:9" x14ac:dyDescent="0.15">
@@ -66385,7 +66466,7 @@
         <v>425</v>
       </c>
       <c r="I146" t="s">
-        <v>1705</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="147" spans="8:9" x14ac:dyDescent="0.15">
@@ -66393,7 +66474,7 @@
         <v>422</v>
       </c>
       <c r="I147" t="s">
-        <v>1706</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="148" spans="8:9" x14ac:dyDescent="0.15">
@@ -66401,7 +66482,7 @@
         <v>423</v>
       </c>
       <c r="I148" t="s">
-        <v>1707</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="149" spans="8:9" x14ac:dyDescent="0.15">
@@ -66409,7 +66490,7 @@
         <v>424</v>
       </c>
       <c r="I149" t="s">
-        <v>1708</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="150" spans="8:9" x14ac:dyDescent="0.15">
@@ -66417,7 +66498,7 @@
         <v>427</v>
       </c>
       <c r="I150" t="s">
-        <v>1709</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="151" spans="8:9" x14ac:dyDescent="0.15">
@@ -66425,7 +66506,7 @@
         <v>431</v>
       </c>
       <c r="I151" t="s">
-        <v>1710</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="152" spans="8:9" x14ac:dyDescent="0.15">
@@ -66433,7 +66514,7 @@
         <v>430</v>
       </c>
       <c r="I152" t="s">
-        <v>1711</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="153" spans="8:9" x14ac:dyDescent="0.15">
@@ -66441,7 +66522,7 @@
         <v>429</v>
       </c>
       <c r="I153" t="s">
-        <v>1712</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="154" spans="8:9" x14ac:dyDescent="0.15">
@@ -66449,7 +66530,7 @@
         <v>433</v>
       </c>
       <c r="I154" t="s">
-        <v>1713</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="155" spans="8:9" x14ac:dyDescent="0.15">
@@ -66457,7 +66538,7 @@
         <v>428</v>
       </c>
       <c r="I155" t="s">
-        <v>1714</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="156" spans="8:9" x14ac:dyDescent="0.15">
@@ -66465,7 +66546,7 @@
         <v>621</v>
       </c>
       <c r="I156" t="s">
-        <v>1714</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="157" spans="8:9" x14ac:dyDescent="0.15">
@@ -66473,7 +66554,7 @@
         <v>718</v>
       </c>
       <c r="I157" t="s">
-        <v>1715</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="158" spans="8:9" x14ac:dyDescent="0.15">
@@ -66481,7 +66562,7 @@
         <v>778</v>
       </c>
       <c r="I158" t="s">
-        <v>1715</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="159" spans="8:9" x14ac:dyDescent="0.15">
@@ -66489,7 +66570,7 @@
         <v>725</v>
       </c>
       <c r="I159" t="s">
-        <v>1716</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="160" spans="8:9" x14ac:dyDescent="0.15">
@@ -66497,7 +66578,7 @@
         <v>726</v>
       </c>
       <c r="I160" t="s">
-        <v>1717</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="161" spans="8:9" x14ac:dyDescent="0.15">
@@ -66505,7 +66586,7 @@
         <v>733</v>
       </c>
       <c r="I161" t="s">
-        <v>1718</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="162" spans="8:9" x14ac:dyDescent="0.15">
@@ -66513,7 +66594,7 @@
         <v>729</v>
       </c>
       <c r="I162" t="s">
-        <v>1719</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="163" spans="8:9" x14ac:dyDescent="0.15">
@@ -66521,7 +66602,7 @@
         <v>728</v>
       </c>
       <c r="I163" t="s">
-        <v>1720</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="164" spans="8:9" x14ac:dyDescent="0.15">
@@ -66529,7 +66610,7 @@
         <v>737</v>
       </c>
       <c r="I164" t="s">
-        <v>1720</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="165" spans="8:9" x14ac:dyDescent="0.15">
@@ -66537,47 +66618,47 @@
         <v>730</v>
       </c>
       <c r="I165" t="s">
-        <v>1717</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="166" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H166" s="7" t="s">
-        <v>1655</v>
+        <v>1646</v>
       </c>
       <c r="I166" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="167" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H167" s="7" t="s">
-        <v>1656</v>
+        <v>1647</v>
       </c>
       <c r="I167" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="168" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H168" s="7" t="s">
-        <v>1657</v>
+        <v>1648</v>
       </c>
       <c r="I168" t="s">
-        <v>1722</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="169" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H169" s="7" t="s">
-        <v>1658</v>
+        <v>1649</v>
       </c>
       <c r="I169" t="s">
-        <v>1722</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="170" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H170" s="7" t="s">
-        <v>1659</v>
+        <v>1650</v>
       </c>
       <c r="I170" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="171" spans="8:9" x14ac:dyDescent="0.15">
@@ -66585,7 +66666,7 @@
         <v>120</v>
       </c>
       <c r="I171" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="172" spans="8:9" x14ac:dyDescent="0.15">
@@ -66593,7 +66674,7 @@
         <v>122</v>
       </c>
       <c r="I172" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="173" spans="8:9" x14ac:dyDescent="0.15">
@@ -66601,7 +66682,7 @@
         <v>121</v>
       </c>
       <c r="I173" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="174" spans="8:9" x14ac:dyDescent="0.15">
@@ -66609,15 +66690,15 @@
         <v>123</v>
       </c>
       <c r="I174" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="175" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H175" s="7" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
       <c r="I175" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="176" spans="8:9" x14ac:dyDescent="0.15">
@@ -66625,7 +66706,7 @@
         <v>124</v>
       </c>
       <c r="I176" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="177" spans="8:9" x14ac:dyDescent="0.15">
@@ -66633,7 +66714,7 @@
         <v>125</v>
       </c>
       <c r="I177" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="178" spans="8:9" x14ac:dyDescent="0.15">
@@ -66641,15 +66722,15 @@
         <v>126</v>
       </c>
       <c r="I178" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="179" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H179" s="7" t="s">
-        <v>1536</v>
+        <v>1527</v>
       </c>
       <c r="I179" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="180" spans="8:9" x14ac:dyDescent="0.15">
@@ -66657,7 +66738,7 @@
         <v>128</v>
       </c>
       <c r="I180" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="181" spans="8:9" x14ac:dyDescent="0.15">
@@ -66665,7 +66746,7 @@
         <v>129</v>
       </c>
       <c r="I181" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="182" spans="8:9" x14ac:dyDescent="0.15">
@@ -66673,7 +66754,7 @@
         <v>130</v>
       </c>
       <c r="I182" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="183" spans="8:9" x14ac:dyDescent="0.15">
@@ -66681,7 +66762,7 @@
         <v>131</v>
       </c>
       <c r="I183" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="184" spans="8:9" x14ac:dyDescent="0.15">
@@ -66689,7 +66770,7 @@
         <v>132</v>
       </c>
       <c r="I184" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="185" spans="8:9" x14ac:dyDescent="0.15">
@@ -66697,7 +66778,7 @@
         <v>133</v>
       </c>
       <c r="I185" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="186" spans="8:9" x14ac:dyDescent="0.15">
@@ -66705,7 +66786,7 @@
         <v>134</v>
       </c>
       <c r="I186" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="187" spans="8:9" x14ac:dyDescent="0.15">
@@ -66713,7 +66794,7 @@
         <v>957</v>
       </c>
       <c r="I187" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="188" spans="8:9" x14ac:dyDescent="0.15">
@@ -66721,7 +66802,7 @@
         <v>136</v>
       </c>
       <c r="I188" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="189" spans="8:9" x14ac:dyDescent="0.15">
@@ -66729,7 +66810,7 @@
         <v>137</v>
       </c>
       <c r="I189" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="190" spans="8:9" x14ac:dyDescent="0.15">
@@ -66737,7 +66818,7 @@
         <v>138</v>
       </c>
       <c r="I190" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="191" spans="8:9" x14ac:dyDescent="0.15">
@@ -66745,15 +66826,15 @@
         <v>981</v>
       </c>
       <c r="I191" t="s">
-        <v>1723</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="192" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H192" s="7" t="s">
-        <v>1660</v>
+        <v>1651</v>
       </c>
       <c r="I192" t="s">
-        <v>1724</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="193" spans="8:9" x14ac:dyDescent="0.15">
@@ -66761,15 +66842,15 @@
         <v>862</v>
       </c>
       <c r="I193" t="s">
-        <v>1724</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="194" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H194" s="7" t="s">
-        <v>1661</v>
+        <v>1652</v>
       </c>
       <c r="I194" t="s">
-        <v>1725</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="195" spans="8:9" x14ac:dyDescent="0.15">
@@ -66777,7 +66858,7 @@
         <v>347</v>
       </c>
       <c r="I195" t="s">
-        <v>1726</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="196" spans="8:9" x14ac:dyDescent="0.15">
@@ -66785,7 +66866,7 @@
         <v>328</v>
       </c>
       <c r="I196" t="s">
-        <v>1723</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="197" spans="8:9" x14ac:dyDescent="0.15">
@@ -66793,7 +66874,7 @@
         <v>829</v>
       </c>
       <c r="I197" t="s">
-        <v>1727</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="198" spans="8:9" x14ac:dyDescent="0.15">
@@ -66801,7 +66882,7 @@
         <v>443</v>
       </c>
       <c r="I198" t="s">
-        <v>1724</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="199" spans="8:9" x14ac:dyDescent="0.15">
@@ -66809,7 +66890,7 @@
         <v>444</v>
       </c>
       <c r="I199" t="s">
-        <v>1728</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="200" spans="8:9" x14ac:dyDescent="0.15">
@@ -66817,7 +66898,7 @@
         <v>346</v>
       </c>
       <c r="I200" t="s">
-        <v>1729</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="201" spans="8:9" x14ac:dyDescent="0.15">
@@ -66825,7 +66906,7 @@
         <v>352</v>
       </c>
       <c r="I201" t="s">
-        <v>1730</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="202" spans="8:9" x14ac:dyDescent="0.15">
@@ -66833,7 +66914,7 @@
         <v>445</v>
       </c>
       <c r="I202" t="s">
-        <v>1731</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="203" spans="8:9" x14ac:dyDescent="0.15">
@@ -66841,7 +66922,7 @@
         <v>446</v>
       </c>
       <c r="I203" t="s">
-        <v>1732</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="204" spans="8:9" x14ac:dyDescent="0.15">
@@ -66849,7 +66930,7 @@
         <v>447</v>
       </c>
       <c r="I204" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="205" spans="8:9" x14ac:dyDescent="0.15">
@@ -66857,7 +66938,7 @@
         <v>448</v>
       </c>
       <c r="I205" t="s">
-        <v>1734</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="206" spans="8:9" x14ac:dyDescent="0.15">
@@ -66865,7 +66946,7 @@
         <v>370</v>
       </c>
       <c r="I206" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="207" spans="8:9" x14ac:dyDescent="0.15">
@@ -66873,7 +66954,7 @@
         <v>449</v>
       </c>
       <c r="I207" t="s">
-        <v>1736</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="208" spans="8:9" x14ac:dyDescent="0.15">
@@ -66881,7 +66962,7 @@
         <v>450</v>
       </c>
       <c r="I208" t="s">
-        <v>1692</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="209" spans="8:9" x14ac:dyDescent="0.15">
@@ -66889,7 +66970,7 @@
         <v>357</v>
       </c>
       <c r="I209" t="s">
-        <v>1737</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="210" spans="8:9" x14ac:dyDescent="0.15">
@@ -66897,7 +66978,7 @@
         <v>451</v>
       </c>
       <c r="I210" t="s">
-        <v>1738</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="211" spans="8:9" x14ac:dyDescent="0.15">
@@ -66905,7 +66986,7 @@
         <v>452</v>
       </c>
       <c r="I211" t="s">
-        <v>1739</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="212" spans="8:9" x14ac:dyDescent="0.15">
@@ -66913,7 +66994,7 @@
         <v>453</v>
       </c>
       <c r="I212" t="s">
-        <v>1740</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="213" spans="8:9" x14ac:dyDescent="0.15">
@@ -66921,7 +67002,7 @@
         <v>454</v>
       </c>
       <c r="I213" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="214" spans="8:9" x14ac:dyDescent="0.15">
@@ -66929,7 +67010,7 @@
         <v>455</v>
       </c>
       <c r="I214" t="s">
-        <v>1741</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="215" spans="8:9" x14ac:dyDescent="0.15">
@@ -66937,7 +67018,7 @@
         <v>360</v>
       </c>
       <c r="I215" t="s">
-        <v>1742</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="216" spans="8:9" x14ac:dyDescent="0.15">
@@ -66945,7 +67026,7 @@
         <v>456</v>
       </c>
       <c r="I216" t="s">
-        <v>1743</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="217" spans="8:9" x14ac:dyDescent="0.15">
@@ -66953,7 +67034,7 @@
         <v>457</v>
       </c>
       <c r="I217" t="s">
-        <v>1744</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="218" spans="8:9" x14ac:dyDescent="0.15">
@@ -66961,7 +67042,7 @@
         <v>348</v>
       </c>
       <c r="I218" t="s">
-        <v>1745</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="219" spans="8:9" x14ac:dyDescent="0.15">
@@ -66969,7 +67050,7 @@
         <v>369</v>
       </c>
       <c r="I219" t="s">
-        <v>1746</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="220" spans="8:9" x14ac:dyDescent="0.15">
@@ -66977,7 +67058,7 @@
         <v>458</v>
       </c>
       <c r="I220" t="s">
-        <v>1747</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="221" spans="8:9" x14ac:dyDescent="0.15">
@@ -66985,7 +67066,7 @@
         <v>459</v>
       </c>
       <c r="I221" t="s">
-        <v>1748</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="222" spans="8:9" x14ac:dyDescent="0.15">
@@ -66993,7 +67074,7 @@
         <v>362</v>
       </c>
       <c r="I222" t="s">
-        <v>1749</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="223" spans="8:9" x14ac:dyDescent="0.15">
@@ -67001,7 +67082,7 @@
         <v>361</v>
       </c>
       <c r="I223" t="s">
-        <v>1750</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="224" spans="8:9" x14ac:dyDescent="0.15">
@@ -67009,7 +67090,7 @@
         <v>460</v>
       </c>
       <c r="I224" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="225" spans="8:9" x14ac:dyDescent="0.15">
@@ -67017,7 +67098,7 @@
         <v>461</v>
       </c>
       <c r="I225" t="s">
-        <v>1751</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="226" spans="8:9" x14ac:dyDescent="0.15">
@@ -67025,7 +67106,7 @@
         <v>462</v>
       </c>
       <c r="I226" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="227" spans="8:9" x14ac:dyDescent="0.15">
@@ -67033,7 +67114,7 @@
         <v>463</v>
       </c>
       <c r="I227" t="s">
-        <v>1752</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="228" spans="8:9" x14ac:dyDescent="0.15">
@@ -67041,7 +67122,7 @@
         <v>464</v>
       </c>
       <c r="I228" t="s">
-        <v>1753</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="229" spans="8:9" x14ac:dyDescent="0.15">
@@ -67049,7 +67130,7 @@
         <v>465</v>
       </c>
       <c r="I229" t="s">
-        <v>1754</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="230" spans="8:9" x14ac:dyDescent="0.15">
@@ -67057,7 +67138,7 @@
         <v>466</v>
       </c>
       <c r="I230" t="s">
-        <v>1755</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="231" spans="8:9" x14ac:dyDescent="0.15">
@@ -67065,7 +67146,7 @@
         <v>350</v>
       </c>
       <c r="I231" t="s">
-        <v>1745</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="232" spans="8:9" x14ac:dyDescent="0.15">
@@ -67073,7 +67154,7 @@
         <v>367</v>
       </c>
       <c r="I232" t="s">
-        <v>1756</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="233" spans="8:9" x14ac:dyDescent="0.15">
@@ -67081,7 +67162,7 @@
         <v>467</v>
       </c>
       <c r="I233" t="s">
-        <v>1757</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="234" spans="8:9" x14ac:dyDescent="0.15">
@@ -67089,7 +67170,7 @@
         <v>363</v>
       </c>
       <c r="I234" t="s">
-        <v>1744</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="235" spans="8:9" x14ac:dyDescent="0.15">
@@ -67097,7 +67178,7 @@
         <v>365</v>
       </c>
       <c r="I235" t="s">
-        <v>1758</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="236" spans="8:9" x14ac:dyDescent="0.15">
@@ -67105,7 +67186,7 @@
         <v>486</v>
       </c>
       <c r="I236" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="237" spans="8:9" x14ac:dyDescent="0.15">
@@ -67113,7 +67194,7 @@
         <v>468</v>
       </c>
       <c r="I237" t="s">
-        <v>1759</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="238" spans="8:9" x14ac:dyDescent="0.15">
@@ -67121,7 +67202,7 @@
         <v>469</v>
       </c>
       <c r="I238" t="s">
-        <v>1760</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="239" spans="8:9" x14ac:dyDescent="0.15">
@@ -67129,7 +67210,7 @@
         <v>371</v>
       </c>
       <c r="I239" t="s">
-        <v>1761</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="240" spans="8:9" x14ac:dyDescent="0.15">
@@ -67137,7 +67218,7 @@
         <v>372</v>
       </c>
       <c r="I240" t="s">
-        <v>1755</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="241" spans="8:9" x14ac:dyDescent="0.15">
@@ -67145,7 +67226,7 @@
         <v>470</v>
       </c>
       <c r="I241" t="s">
-        <v>1762</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="242" spans="8:9" x14ac:dyDescent="0.15">
@@ -67153,7 +67234,7 @@
         <v>471</v>
       </c>
       <c r="I242" t="s">
-        <v>1763</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="243" spans="8:9" x14ac:dyDescent="0.15">
@@ -67161,7 +67242,7 @@
         <v>472</v>
       </c>
       <c r="I243" t="s">
-        <v>1764</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="244" spans="8:9" x14ac:dyDescent="0.15">
@@ -67169,7 +67250,7 @@
         <v>473</v>
       </c>
       <c r="I244" t="s">
-        <v>1765</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="245" spans="8:9" x14ac:dyDescent="0.15">
@@ -67177,7 +67258,7 @@
         <v>364</v>
       </c>
       <c r="I245" t="s">
-        <v>1749</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="246" spans="8:9" x14ac:dyDescent="0.15">
@@ -67185,7 +67266,7 @@
         <v>474</v>
       </c>
       <c r="I246" t="s">
-        <v>1754</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="247" spans="8:9" x14ac:dyDescent="0.15">
@@ -67193,7 +67274,7 @@
         <v>475</v>
       </c>
       <c r="I247" t="s">
-        <v>1766</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="248" spans="8:9" x14ac:dyDescent="0.15">
@@ -67201,7 +67282,7 @@
         <v>476</v>
       </c>
       <c r="I248" t="s">
-        <v>1767</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="249" spans="8:9" x14ac:dyDescent="0.15">
@@ -67209,7 +67290,7 @@
         <v>477</v>
       </c>
       <c r="I249" t="s">
-        <v>1768</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="250" spans="8:9" x14ac:dyDescent="0.15">
@@ -67217,7 +67298,7 @@
         <v>478</v>
       </c>
       <c r="I250" t="s">
-        <v>1769</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="251" spans="8:9" x14ac:dyDescent="0.15">
@@ -67225,7 +67306,7 @@
         <v>366</v>
       </c>
       <c r="I251" t="s">
-        <v>1766</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="252" spans="8:9" x14ac:dyDescent="0.15">
@@ -67233,7 +67314,7 @@
         <v>479</v>
       </c>
       <c r="I252" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="253" spans="8:9" x14ac:dyDescent="0.15">
@@ -67241,7 +67322,7 @@
         <v>480</v>
       </c>
       <c r="I253" t="s">
-        <v>1770</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="254" spans="8:9" x14ac:dyDescent="0.15">
@@ -67249,7 +67330,7 @@
         <v>368</v>
       </c>
       <c r="I254" t="s">
-        <v>1690</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="255" spans="8:9" x14ac:dyDescent="0.15">
@@ -67257,7 +67338,7 @@
         <v>481</v>
       </c>
       <c r="I255" t="s">
-        <v>1771</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="256" spans="8:9" x14ac:dyDescent="0.15">
@@ -67265,7 +67346,7 @@
         <v>482</v>
       </c>
       <c r="I256" t="s">
-        <v>1772</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="257" spans="8:9" x14ac:dyDescent="0.15">
@@ -67273,7 +67354,7 @@
         <v>483</v>
       </c>
       <c r="I257" t="s">
-        <v>1773</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="258" spans="8:9" x14ac:dyDescent="0.15">
@@ -67281,7 +67362,7 @@
         <v>484</v>
       </c>
       <c r="I258" t="s">
-        <v>1774</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="259" spans="8:9" x14ac:dyDescent="0.15">
@@ -67289,7 +67370,7 @@
         <v>485</v>
       </c>
       <c r="I259" t="s">
-        <v>1774</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="260" spans="8:9" x14ac:dyDescent="0.15">
@@ -67297,7 +67378,7 @@
         <v>511</v>
       </c>
       <c r="I260" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="261" spans="8:9" x14ac:dyDescent="0.15">
@@ -67305,7 +67386,7 @@
         <v>508</v>
       </c>
       <c r="I261" t="s">
-        <v>1775</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="262" spans="8:9" x14ac:dyDescent="0.15">
@@ -67313,7 +67394,7 @@
         <v>440</v>
       </c>
       <c r="I262" t="s">
-        <v>1776</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="263" spans="8:9" x14ac:dyDescent="0.15">
@@ -67321,7 +67402,7 @@
         <v>555</v>
       </c>
       <c r="I263" t="s">
-        <v>1777</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="264" spans="8:9" x14ac:dyDescent="0.15">
@@ -67329,7 +67410,7 @@
         <v>516</v>
       </c>
       <c r="I264" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="265" spans="8:9" x14ac:dyDescent="0.15">
@@ -67337,7 +67418,7 @@
         <v>356</v>
       </c>
       <c r="I265" t="s">
-        <v>1778</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="266" spans="8:9" x14ac:dyDescent="0.15">
@@ -67345,7 +67426,7 @@
         <v>500</v>
       </c>
       <c r="I266" t="s">
-        <v>1779</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="267" spans="8:9" x14ac:dyDescent="0.15">
@@ -67353,7 +67434,7 @@
         <v>359</v>
       </c>
       <c r="I267" t="s">
-        <v>1780</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="268" spans="8:9" x14ac:dyDescent="0.15">
@@ -67361,7 +67442,7 @@
         <v>581</v>
       </c>
       <c r="I268" t="s">
-        <v>1781</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="269" spans="8:9" x14ac:dyDescent="0.15">
@@ -67369,7 +67450,7 @@
         <v>526</v>
       </c>
       <c r="I269" t="s">
-        <v>1782</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="270" spans="8:9" x14ac:dyDescent="0.15">
@@ -67377,7 +67458,7 @@
         <v>502</v>
       </c>
       <c r="I270" t="s">
-        <v>1762</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="271" spans="8:9" x14ac:dyDescent="0.15">
@@ -67385,7 +67466,7 @@
         <v>489</v>
       </c>
       <c r="I271" t="s">
-        <v>1783</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="272" spans="8:9" x14ac:dyDescent="0.15">
@@ -67393,7 +67474,7 @@
         <v>506</v>
       </c>
       <c r="I272" t="s">
-        <v>1784</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="273" spans="8:9" x14ac:dyDescent="0.15">
@@ -67401,7 +67482,7 @@
         <v>554</v>
       </c>
       <c r="I273" t="s">
-        <v>1785</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="274" spans="8:9" x14ac:dyDescent="0.15">
@@ -67409,7 +67490,7 @@
         <v>358</v>
       </c>
       <c r="I274" t="s">
-        <v>1786</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="275" spans="8:9" x14ac:dyDescent="0.15">
@@ -67417,7 +67498,7 @@
         <v>507</v>
       </c>
       <c r="I275" t="s">
-        <v>1787</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="276" spans="8:9" x14ac:dyDescent="0.15">
@@ -67425,7 +67506,7 @@
         <v>559</v>
       </c>
       <c r="I276" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="277" spans="8:9" x14ac:dyDescent="0.15">
@@ -67433,7 +67514,7 @@
         <v>557</v>
       </c>
       <c r="I277" t="s">
-        <v>1788</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="278" spans="8:9" x14ac:dyDescent="0.15">
@@ -67441,7 +67522,7 @@
         <v>553</v>
       </c>
       <c r="I278" t="s">
-        <v>1741</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="279" spans="8:9" x14ac:dyDescent="0.15">
@@ -67449,7 +67530,7 @@
         <v>513</v>
       </c>
       <c r="I279" t="s">
-        <v>1789</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="280" spans="8:9" x14ac:dyDescent="0.15">
@@ -67457,7 +67538,7 @@
         <v>509</v>
       </c>
       <c r="I280" t="s">
-        <v>1790</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="281" spans="8:9" x14ac:dyDescent="0.15">
@@ -67465,7 +67546,7 @@
         <v>556</v>
       </c>
       <c r="I281" t="s">
-        <v>1791</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="282" spans="8:9" x14ac:dyDescent="0.15">
@@ -67473,7 +67554,7 @@
         <v>491</v>
       </c>
       <c r="I282" t="s">
-        <v>1792</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="283" spans="8:9" x14ac:dyDescent="0.15">
@@ -67481,7 +67562,7 @@
         <v>558</v>
       </c>
       <c r="I283" t="s">
-        <v>1774</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="284" spans="8:9" x14ac:dyDescent="0.15">
@@ -67489,7 +67570,7 @@
         <v>512</v>
       </c>
       <c r="I284" t="s">
-        <v>1767</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="285" spans="8:9" x14ac:dyDescent="0.15">
@@ -67497,7 +67578,7 @@
         <v>515</v>
       </c>
       <c r="I285" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="286" spans="8:9" x14ac:dyDescent="0.15">
@@ -67505,7 +67586,7 @@
         <v>634</v>
       </c>
       <c r="I286" t="s">
-        <v>1793</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="287" spans="8:9" x14ac:dyDescent="0.15">
@@ -67513,7 +67594,7 @@
         <v>622</v>
       </c>
       <c r="I287" t="s">
-        <v>1738</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="288" spans="8:9" x14ac:dyDescent="0.15">
@@ -67521,7 +67602,7 @@
         <v>552</v>
       </c>
       <c r="I288" t="s">
-        <v>1794</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="289" spans="8:9" x14ac:dyDescent="0.15">
@@ -67529,7 +67610,7 @@
         <v>522</v>
       </c>
       <c r="I289" t="s">
-        <v>1763</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="290" spans="8:9" x14ac:dyDescent="0.15">
@@ -67537,7 +67618,7 @@
         <v>354</v>
       </c>
       <c r="I290" t="s">
-        <v>1763</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="291" spans="8:9" x14ac:dyDescent="0.15">
@@ -67545,7 +67626,7 @@
         <v>714</v>
       </c>
       <c r="I291" t="s">
-        <v>1795</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="292" spans="8:9" x14ac:dyDescent="0.15">
@@ -67553,15 +67634,15 @@
         <v>715</v>
       </c>
       <c r="I292" t="s">
-        <v>1786</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="293" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H293" s="7" t="s">
-        <v>1662</v>
+        <v>1653</v>
       </c>
       <c r="I293" t="s">
-        <v>1796</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="294" spans="8:9" x14ac:dyDescent="0.15">
@@ -67569,7 +67650,7 @@
         <v>33</v>
       </c>
       <c r="I294" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="295" spans="8:9" x14ac:dyDescent="0.15">
@@ -67577,7 +67658,7 @@
         <v>921</v>
       </c>
       <c r="I295" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="296" spans="8:9" x14ac:dyDescent="0.15">
@@ -67585,7 +67666,7 @@
         <v>35</v>
       </c>
       <c r="I296" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="297" spans="8:9" x14ac:dyDescent="0.15">
@@ -67593,7 +67674,7 @@
         <v>36</v>
       </c>
       <c r="I297" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="298" spans="8:9" x14ac:dyDescent="0.15">
@@ -67601,7 +67682,7 @@
         <v>37</v>
       </c>
       <c r="I298" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="299" spans="8:9" x14ac:dyDescent="0.15">
@@ -67609,7 +67690,7 @@
         <v>38</v>
       </c>
       <c r="I299" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="300" spans="8:9" x14ac:dyDescent="0.15">
@@ -67617,7 +67698,7 @@
         <v>39</v>
       </c>
       <c r="I300" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="301" spans="8:9" x14ac:dyDescent="0.15">
@@ -67625,7 +67706,7 @@
         <v>23</v>
       </c>
       <c r="I301" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="302" spans="8:9" x14ac:dyDescent="0.15">
@@ -67633,7 +67714,7 @@
         <v>40</v>
       </c>
       <c r="I302" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="303" spans="8:9" x14ac:dyDescent="0.15">
@@ -67641,7 +67722,7 @@
         <v>41</v>
       </c>
       <c r="I303" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="304" spans="8:9" x14ac:dyDescent="0.15">
@@ -67649,7 +67730,7 @@
         <v>42</v>
       </c>
       <c r="I304" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="305" spans="8:9" x14ac:dyDescent="0.15">
@@ -67657,7 +67738,7 @@
         <v>53</v>
       </c>
       <c r="I305" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="306" spans="8:9" x14ac:dyDescent="0.15">
@@ -67665,7 +67746,7 @@
         <v>54</v>
       </c>
       <c r="I306" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="307" spans="8:9" x14ac:dyDescent="0.15">
@@ -67673,7 +67754,7 @@
         <v>44</v>
       </c>
       <c r="I307" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="308" spans="8:9" x14ac:dyDescent="0.15">
@@ -67681,7 +67762,7 @@
         <v>25</v>
       </c>
       <c r="I308" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="309" spans="8:9" x14ac:dyDescent="0.15">
@@ -67689,7 +67770,7 @@
         <v>45</v>
       </c>
       <c r="I309" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="310" spans="8:9" x14ac:dyDescent="0.15">
@@ -67697,7 +67778,7 @@
         <v>22</v>
       </c>
       <c r="I310" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="311" spans="8:9" x14ac:dyDescent="0.15">
@@ -67705,15 +67786,15 @@
         <v>43</v>
       </c>
       <c r="I311" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="312" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H312" s="7" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="I312" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="313" spans="8:9" x14ac:dyDescent="0.15">
@@ -67721,7 +67802,7 @@
         <v>50</v>
       </c>
       <c r="I313" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="314" spans="8:9" x14ac:dyDescent="0.15">
@@ -67729,7 +67810,7 @@
         <v>24</v>
       </c>
       <c r="I314" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="315" spans="8:9" x14ac:dyDescent="0.15">
@@ -67737,7 +67818,7 @@
         <v>51</v>
       </c>
       <c r="I315" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="316" spans="8:9" x14ac:dyDescent="0.15">
@@ -67745,7 +67826,7 @@
         <v>52</v>
       </c>
       <c r="I316" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="317" spans="8:9" x14ac:dyDescent="0.15">
@@ -67753,7 +67834,7 @@
         <v>46</v>
       </c>
       <c r="I317" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="318" spans="8:9" x14ac:dyDescent="0.15">
@@ -67761,7 +67842,7 @@
         <v>47</v>
       </c>
       <c r="I318" t="s">
-        <v>1798</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="319" spans="8:9" x14ac:dyDescent="0.15">
@@ -67769,7 +67850,7 @@
         <v>48</v>
       </c>
       <c r="I319" t="s">
-        <v>1789</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="320" spans="8:9" x14ac:dyDescent="0.15">
@@ -67777,7 +67858,7 @@
         <v>49</v>
       </c>
       <c r="I320" t="s">
-        <v>1797</v>
+        <v>1788</v>
       </c>
     </row>
   </sheetData>
@@ -67957,7 +68038,7 @@
         <v>623</v>
       </c>
       <c r="S32" t="s">
-        <v>1507</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="33" spans="9:19" x14ac:dyDescent="0.15">
@@ -67968,7 +68049,7 @@
         <v>624</v>
       </c>
       <c r="S33" t="s">
-        <v>1508</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="34" spans="9:19" x14ac:dyDescent="0.15">
@@ -67979,7 +68060,7 @@
         <v>625</v>
       </c>
       <c r="S34" t="s">
-        <v>1509</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="9:19" x14ac:dyDescent="0.15">
@@ -67987,7 +68068,7 @@
         <v>626</v>
       </c>
       <c r="S35" t="s">
-        <v>1499</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="36" spans="9:19" x14ac:dyDescent="0.15">
@@ -67995,7 +68076,7 @@
         <v>627</v>
       </c>
       <c r="S36" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="37" spans="9:19" x14ac:dyDescent="0.15">
@@ -68003,7 +68084,7 @@
         <v>628</v>
       </c>
       <c r="S37" t="s">
-        <v>1501</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="38" spans="9:19" x14ac:dyDescent="0.15">
@@ -68011,7 +68092,7 @@
         <v>629</v>
       </c>
       <c r="S38" t="s">
-        <v>1502</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="39" spans="9:19" x14ac:dyDescent="0.15">
@@ -68019,7 +68100,7 @@
         <v>630</v>
       </c>
       <c r="S39" t="s">
-        <v>1503</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="40" spans="9:19" x14ac:dyDescent="0.15">
@@ -68027,7 +68108,7 @@
         <v>631</v>
       </c>
       <c r="S40" t="s">
-        <v>1504</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="41" spans="9:19" x14ac:dyDescent="0.15">
@@ -68035,7 +68116,7 @@
         <v>632</v>
       </c>
       <c r="S41" t="s">
-        <v>1505</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="42" spans="9:19" x14ac:dyDescent="0.15">
@@ -68043,7 +68124,7 @@
         <v>633</v>
       </c>
       <c r="S42" t="s">
-        <v>1506</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="47" spans="9:19" x14ac:dyDescent="0.15">
@@ -68051,7 +68132,7 @@
         <v>623</v>
       </c>
       <c r="R47" t="s">
-        <v>1511</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="48" spans="9:19" ht="17.25" x14ac:dyDescent="0.15">
@@ -68059,13 +68140,13 @@
         <v>187</v>
       </c>
       <c r="J48" t="s">
-        <v>1407</v>
+        <v>1398</v>
       </c>
       <c r="Q48" t="s">
         <v>624</v>
       </c>
       <c r="R48" t="s">
-        <v>1513</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="49" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68073,13 +68154,13 @@
         <v>188</v>
       </c>
       <c r="J49" t="s">
-        <v>1408</v>
+        <v>1399</v>
       </c>
       <c r="Q49" t="s">
         <v>625</v>
       </c>
       <c r="R49" t="s">
-        <v>1515</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="50" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68087,13 +68168,13 @@
         <v>189</v>
       </c>
       <c r="J50" t="s">
-        <v>1409</v>
+        <v>1400</v>
       </c>
       <c r="Q50" t="s">
         <v>626</v>
       </c>
       <c r="R50" t="s">
-        <v>1517</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="51" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68101,13 +68182,13 @@
         <v>858</v>
       </c>
       <c r="J51" t="s">
-        <v>1410</v>
+        <v>1401</v>
       </c>
       <c r="Q51" t="s">
         <v>627</v>
       </c>
       <c r="R51" t="s">
-        <v>1519</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="52" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68115,13 +68196,13 @@
         <v>193</v>
       </c>
       <c r="J52" t="s">
-        <v>1411</v>
+        <v>1402</v>
       </c>
       <c r="Q52" t="s">
         <v>628</v>
       </c>
       <c r="R52" t="s">
-        <v>1521</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="53" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68129,13 +68210,13 @@
         <v>162</v>
       </c>
       <c r="J53" t="s">
-        <v>1412</v>
+        <v>1403</v>
       </c>
       <c r="Q53" t="s">
         <v>629</v>
       </c>
       <c r="R53" t="s">
-        <v>1523</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="54" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68143,13 +68224,13 @@
         <v>159</v>
       </c>
       <c r="J54" t="s">
-        <v>1413</v>
+        <v>1404</v>
       </c>
       <c r="Q54" t="s">
         <v>630</v>
       </c>
       <c r="R54" t="s">
-        <v>1525</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="55" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68157,13 +68238,13 @@
         <v>161</v>
       </c>
       <c r="J55" t="s">
-        <v>1414</v>
+        <v>1405</v>
       </c>
       <c r="Q55" t="s">
         <v>631</v>
       </c>
       <c r="R55" t="s">
-        <v>1527</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="56" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68171,13 +68252,13 @@
         <v>174</v>
       </c>
       <c r="J56" t="s">
-        <v>1415</v>
+        <v>1406</v>
       </c>
       <c r="Q56" t="s">
         <v>632</v>
       </c>
       <c r="R56" t="s">
-        <v>1529</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="57" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68185,13 +68266,13 @@
         <v>178</v>
       </c>
       <c r="J57" t="s">
-        <v>1416</v>
+        <v>1407</v>
       </c>
       <c r="Q57" t="s">
         <v>633</v>
       </c>
       <c r="R57" t="s">
-        <v>1531</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="58" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68199,7 +68280,7 @@
         <v>250</v>
       </c>
       <c r="J58" t="s">
-        <v>1417</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="59" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68207,7 +68288,7 @@
         <v>205</v>
       </c>
       <c r="J59" t="s">
-        <v>1418</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="60" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68215,7 +68296,7 @@
         <v>795</v>
       </c>
       <c r="J60" t="s">
-        <v>1419</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="61" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68223,7 +68304,7 @@
         <v>163</v>
       </c>
       <c r="J61" t="s">
-        <v>1420</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="62" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68231,7 +68312,7 @@
         <v>184</v>
       </c>
       <c r="J62" t="s">
-        <v>1421</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="63" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68239,7 +68320,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>1422</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="64" spans="9:18" ht="17.25" x14ac:dyDescent="0.15">
@@ -68247,7 +68328,7 @@
         <v>182</v>
       </c>
       <c r="J64" t="s">
-        <v>1423</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="65" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68255,7 +68336,7 @@
         <v>194</v>
       </c>
       <c r="J65" t="s">
-        <v>1424</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="66" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68263,7 +68344,7 @@
         <v>195</v>
       </c>
       <c r="J66" t="s">
-        <v>1425</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="67" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68271,7 +68352,7 @@
         <v>165</v>
       </c>
       <c r="J67" t="s">
-        <v>1426</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="68" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68279,7 +68360,7 @@
         <v>167</v>
       </c>
       <c r="J68" t="s">
-        <v>1427</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="69" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68287,7 +68368,7 @@
         <v>196</v>
       </c>
       <c r="J69" t="s">
-        <v>1428</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="70" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68295,7 +68376,7 @@
         <v>164</v>
       </c>
       <c r="J70" t="s">
-        <v>1429</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="71" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68303,7 +68384,7 @@
         <v>197</v>
       </c>
       <c r="J71" t="s">
-        <v>1430</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="72" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68311,7 +68392,7 @@
         <v>796</v>
       </c>
       <c r="J72" t="s">
-        <v>1431</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="73" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68319,7 +68400,7 @@
         <v>198</v>
       </c>
       <c r="J73" t="s">
-        <v>1432</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="74" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68327,7 +68408,7 @@
         <v>171</v>
       </c>
       <c r="J74" t="s">
-        <v>1433</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="75" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68335,7 +68416,7 @@
         <v>199</v>
       </c>
       <c r="J75" t="s">
-        <v>1434</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="76" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68343,7 +68424,7 @@
         <v>200</v>
       </c>
       <c r="J76" t="s">
-        <v>1435</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="77" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68351,7 +68432,7 @@
         <v>170</v>
       </c>
       <c r="J77" t="s">
-        <v>1436</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="78" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68359,7 +68440,7 @@
         <v>201</v>
       </c>
       <c r="J78" t="s">
-        <v>1437</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="79" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68367,7 +68448,7 @@
         <v>172</v>
       </c>
       <c r="J79" t="s">
-        <v>1438</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="80" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68375,7 +68456,7 @@
         <v>202</v>
       </c>
       <c r="J80" t="s">
-        <v>1439</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="81" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68383,7 +68464,7 @@
         <v>185</v>
       </c>
       <c r="J81" t="s">
-        <v>1440</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="82" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68391,7 +68472,7 @@
         <v>168</v>
       </c>
       <c r="J82" t="s">
-        <v>1441</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="83" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68399,7 +68480,7 @@
         <v>175</v>
       </c>
       <c r="J83" t="s">
-        <v>1442</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="84" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68407,7 +68488,7 @@
         <v>177</v>
       </c>
       <c r="J84" t="s">
-        <v>1443</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="85" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68415,7 +68496,7 @@
         <v>179</v>
       </c>
       <c r="J85" t="s">
-        <v>1444</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="86" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68423,7 +68504,7 @@
         <v>180</v>
       </c>
       <c r="J86" t="s">
-        <v>1445</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="87" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68431,7 +68512,7 @@
         <v>203</v>
       </c>
       <c r="J87" t="s">
-        <v>1446</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="88" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68439,7 +68520,7 @@
         <v>204</v>
       </c>
       <c r="J88" t="s">
-        <v>1447</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="89" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68447,7 +68528,7 @@
         <v>181</v>
       </c>
       <c r="J89" t="s">
-        <v>1448</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="90" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68455,7 +68536,7 @@
         <v>206</v>
       </c>
       <c r="J90" t="s">
-        <v>1449</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="91" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68463,7 +68544,7 @@
         <v>207</v>
       </c>
       <c r="J91" t="s">
-        <v>1450</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="92" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68471,7 +68552,7 @@
         <v>183</v>
       </c>
       <c r="J92" t="s">
-        <v>1451</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="93" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68479,7 +68560,7 @@
         <v>208</v>
       </c>
       <c r="J93" t="s">
-        <v>1452</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="94" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68487,7 +68568,7 @@
         <v>209</v>
       </c>
       <c r="J94" t="s">
-        <v>1453</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="95" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68495,7 +68576,7 @@
         <v>210</v>
       </c>
       <c r="J95" t="s">
-        <v>1454</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="96" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68503,7 +68584,7 @@
         <v>169</v>
       </c>
       <c r="J96" t="s">
-        <v>1455</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="97" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68511,7 +68592,7 @@
         <v>211</v>
       </c>
       <c r="J97" t="s">
-        <v>1456</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="98" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68519,7 +68600,7 @@
         <v>212</v>
       </c>
       <c r="J98" t="s">
-        <v>1457</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="99" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68527,7 +68608,7 @@
         <v>213</v>
       </c>
       <c r="J99" t="s">
-        <v>1458</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="100" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68535,7 +68616,7 @@
         <v>214</v>
       </c>
       <c r="J100" t="s">
-        <v>1459</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="101" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68543,7 +68624,7 @@
         <v>215</v>
       </c>
       <c r="J101" t="s">
-        <v>1460</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="102" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68551,7 +68632,7 @@
         <v>176</v>
       </c>
       <c r="J102" t="s">
-        <v>1461</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="103" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68559,7 +68640,7 @@
         <v>186</v>
       </c>
       <c r="J103" t="s">
-        <v>1462</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="104" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68567,7 +68648,7 @@
         <v>173</v>
       </c>
       <c r="J104" t="s">
-        <v>1463</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="105" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68575,7 +68656,7 @@
         <v>216</v>
       </c>
       <c r="J105" t="s">
-        <v>1464</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="106" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68583,7 +68664,7 @@
         <v>217</v>
       </c>
       <c r="J106" t="s">
-        <v>1465</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="107" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68591,7 +68672,7 @@
         <v>218</v>
       </c>
       <c r="J107" t="s">
-        <v>1466</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="108" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68599,7 +68680,7 @@
         <v>219</v>
       </c>
       <c r="J108" t="s">
-        <v>1467</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="109" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68607,7 +68688,7 @@
         <v>797</v>
       </c>
       <c r="J109" t="s">
-        <v>1468</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="110" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68615,7 +68696,7 @@
         <v>220</v>
       </c>
       <c r="J110" t="s">
-        <v>1469</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="111" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68623,7 +68704,7 @@
         <v>221</v>
       </c>
       <c r="J111" t="s">
-        <v>1470</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="112" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68631,7 +68712,7 @@
         <v>222</v>
       </c>
       <c r="J112" t="s">
-        <v>1471</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="113" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68639,7 +68720,7 @@
         <v>223</v>
       </c>
       <c r="J113" t="s">
-        <v>1472</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="114" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68647,7 +68728,7 @@
         <v>224</v>
       </c>
       <c r="J114" t="s">
-        <v>1473</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="115" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68655,7 +68736,7 @@
         <v>225</v>
       </c>
       <c r="J115" t="s">
-        <v>1474</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="116" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68663,7 +68744,7 @@
         <v>226</v>
       </c>
       <c r="J116" t="s">
-        <v>1475</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="117" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68671,7 +68752,7 @@
         <v>227</v>
       </c>
       <c r="J117" t="s">
-        <v>1476</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="118" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68679,7 +68760,7 @@
         <v>228</v>
       </c>
       <c r="J118" t="s">
-        <v>1477</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="119" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68687,7 +68768,7 @@
         <v>229</v>
       </c>
       <c r="J119" t="s">
-        <v>1478</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="120" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68695,7 +68776,7 @@
         <v>230</v>
       </c>
       <c r="J120" t="s">
-        <v>1479</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="121" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68703,7 +68784,7 @@
         <v>231</v>
       </c>
       <c r="J121" t="s">
-        <v>1480</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="122" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68711,7 +68792,7 @@
         <v>232</v>
       </c>
       <c r="J122" t="s">
-        <v>1481</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="123" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68719,7 +68800,7 @@
         <v>233</v>
       </c>
       <c r="J123" t="s">
-        <v>1482</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="124" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68727,7 +68808,7 @@
         <v>234</v>
       </c>
       <c r="J124" t="s">
-        <v>1483</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="125" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68735,7 +68816,7 @@
         <v>235</v>
       </c>
       <c r="J125" t="s">
-        <v>1484</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="126" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68743,7 +68824,7 @@
         <v>236</v>
       </c>
       <c r="J126" t="s">
-        <v>1485</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="127" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68751,7 +68832,7 @@
         <v>237</v>
       </c>
       <c r="J127" t="s">
-        <v>1486</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="128" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68759,7 +68840,7 @@
         <v>238</v>
       </c>
       <c r="J128" t="s">
-        <v>1487</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="129" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68767,7 +68848,7 @@
         <v>239</v>
       </c>
       <c r="J129" t="s">
-        <v>1488</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="130" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68775,7 +68856,7 @@
         <v>240</v>
       </c>
       <c r="J130" t="s">
-        <v>1489</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="131" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68783,7 +68864,7 @@
         <v>241</v>
       </c>
       <c r="J131" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="132" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68791,7 +68872,7 @@
         <v>242</v>
       </c>
       <c r="J132" t="s">
-        <v>1491</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="133" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68799,7 +68880,7 @@
         <v>243</v>
       </c>
       <c r="J133" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="134" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68807,7 +68888,7 @@
         <v>244</v>
       </c>
       <c r="J134" t="s">
-        <v>1493</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="135" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68815,7 +68896,7 @@
         <v>245</v>
       </c>
       <c r="J135" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="136" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68823,7 +68904,7 @@
         <v>246</v>
       </c>
       <c r="J136" t="s">
-        <v>1495</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="137" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68831,7 +68912,7 @@
         <v>247</v>
       </c>
       <c r="J137" t="s">
-        <v>1496</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="138" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68839,7 +68920,7 @@
         <v>248</v>
       </c>
       <c r="J138" t="s">
-        <v>1497</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="139" spans="9:10" ht="17.25" x14ac:dyDescent="0.15">
@@ -68847,7 +68928,7 @@
         <v>798</v>
       </c>
       <c r="J139" t="s">
-        <v>1498</v>
+        <v>1489</v>
       </c>
     </row>
   </sheetData>
@@ -77686,7 +77767,7 @@
         <v>813</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>1532</v>
+        <v>1523</v>
       </c>
       <c r="L32" s="38" t="s">
         <v>814</v>
@@ -79386,7 +79467,7 @@
         <v>930</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1533</v>
+        <v>1524</v>
       </c>
       <c r="E65" s="38">
         <v>2</v>
@@ -79758,7 +79839,7 @@
         <v>936</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1533</v>
+        <v>1524</v>
       </c>
       <c r="E71" s="38">
         <v>2</v>
@@ -80068,7 +80149,7 @@
         <v>941</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1534</v>
+        <v>1525</v>
       </c>
       <c r="E76" s="38">
         <v>2</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -48795,7 +48795,7 @@
         <v>623</v>
       </c>
       <c r="B402" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="C402" s="12" t="s">
         <v>623</v>
@@ -48893,7 +48893,7 @@
         <v>624</v>
       </c>
       <c r="B403" s="1">
-        <v>4001</v>
+        <v>5001</v>
       </c>
       <c r="C403" s="12" t="s">
         <v>624</v>
@@ -48991,7 +48991,7 @@
         <v>625</v>
       </c>
       <c r="B404" s="1">
-        <v>4002</v>
+        <v>5002</v>
       </c>
       <c r="C404" s="12" t="s">
         <v>625</v>
@@ -49089,7 +49089,7 @@
         <v>626</v>
       </c>
       <c r="B405" s="1">
-        <v>4003</v>
+        <v>5003</v>
       </c>
       <c r="C405" s="12" t="s">
         <v>626</v>
@@ -49187,7 +49187,7 @@
         <v>627</v>
       </c>
       <c r="B406" s="1">
-        <v>4004</v>
+        <v>5004</v>
       </c>
       <c r="C406" s="12" t="s">
         <v>627</v>
@@ -49285,7 +49285,7 @@
         <v>628</v>
       </c>
       <c r="B407" s="1">
-        <v>4005</v>
+        <v>5005</v>
       </c>
       <c r="C407" s="12" t="s">
         <v>628</v>
@@ -49383,7 +49383,7 @@
         <v>629</v>
       </c>
       <c r="B408" s="1">
-        <v>4006</v>
+        <v>5006</v>
       </c>
       <c r="C408" s="12" t="s">
         <v>629</v>
@@ -49481,7 +49481,7 @@
         <v>630</v>
       </c>
       <c r="B409" s="1">
-        <v>4007</v>
+        <v>5007</v>
       </c>
       <c r="C409" s="12" t="s">
         <v>630</v>
@@ -49579,7 +49579,7 @@
         <v>631</v>
       </c>
       <c r="B410" s="1">
-        <v>4008</v>
+        <v>5008</v>
       </c>
       <c r="C410" s="12" t="s">
         <v>631</v>
@@ -49677,7 +49677,7 @@
         <v>632</v>
       </c>
       <c r="B411" s="1">
-        <v>4009</v>
+        <v>5009</v>
       </c>
       <c r="C411" s="12" t="s">
         <v>632</v>
@@ -49775,7 +49775,7 @@
         <v>633</v>
       </c>
       <c r="B412" s="1">
-        <v>4010</v>
+        <v>5010</v>
       </c>
       <c r="C412" s="12" t="s">
         <v>633</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -5794,10 +5794,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>河蟹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鲶鱼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6469,6 +6465,10 @@
   </si>
   <si>
     <t>鱼身闪彩，盐烤之下，肉质紧实，散发独特的咸鲜风味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套蟹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9483,7 +9483,7 @@
         <v>695</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>16</v>
@@ -11117,7 +11117,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -11213,7 +11213,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -11309,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -11406,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -11502,7 +11502,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -11599,7 +11599,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -11696,7 +11696,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -11792,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -11889,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -11986,7 +11986,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -12182,7 +12182,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -12279,7 +12279,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -12376,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -12473,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -12570,7 +12570,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -12668,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -12765,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -12862,7 +12862,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -12960,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -13056,7 +13056,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -13153,7 +13153,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -13249,7 +13249,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -13346,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -13442,7 +13442,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -13540,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -13637,7 +13637,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -13734,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -13832,7 +13832,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -13930,7 +13930,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -14027,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -14123,7 +14123,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -14221,7 +14221,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -14319,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -14416,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -14513,7 +14513,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -14610,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -14803,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -14900,7 +14900,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -15096,7 +15096,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
@@ -15194,7 +15194,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -15291,7 +15291,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -15389,7 +15389,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -15486,7 +15486,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -15680,7 +15680,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -15777,7 +15777,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -15875,7 +15875,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -15973,7 +15973,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -16070,7 +16070,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -16166,7 +16166,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -16263,7 +16263,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -16360,7 +16360,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -16458,7 +16458,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -16653,7 +16653,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -16750,7 +16750,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
@@ -16847,7 +16847,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -16944,7 +16944,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -17042,7 +17042,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -17139,7 +17139,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -17236,7 +17236,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
@@ -17431,7 +17431,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -17528,7 +17528,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H86" s="1">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -17721,7 +17721,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -17818,7 +17818,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -18012,7 +18012,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -18108,7 +18108,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -18205,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
@@ -18302,7 +18302,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -18400,7 +18400,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -18497,7 +18497,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -18594,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -18690,7 +18690,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -18769,7 +18769,7 @@
     </row>
     <row r="99" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A99" s="12" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="B99" s="1">
         <v>279</v>
@@ -18787,7 +18787,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -18884,7 +18884,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -18981,7 +18981,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -19078,7 +19078,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -19175,7 +19175,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -19272,7 +19272,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -19369,7 +19369,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -19466,7 +19466,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -19563,7 +19563,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -19660,7 +19660,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -19757,7 +19757,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -19854,7 +19854,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -19951,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -20145,7 +20145,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -20339,7 +20339,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -20435,7 +20435,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -20533,7 +20533,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -20630,7 +20630,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -20726,7 +20726,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -20823,7 +20823,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -20919,7 +20919,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -21015,7 +21015,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -21112,7 +21112,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H123" s="1">
         <v>1</v>
@@ -21314,7 +21314,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H125" s="1">
         <v>1</v>
@@ -21411,7 +21411,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H126" s="1">
         <v>1</v>
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H127" s="1">
         <v>1</v>
@@ -21607,7 +21607,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H128" s="1">
         <v>1</v>
@@ -21705,7 +21705,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H129" s="1">
         <v>1</v>
@@ -21802,7 +21802,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H130" s="1">
         <v>1</v>
@@ -21900,7 +21900,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H131" s="1">
         <v>1</v>
@@ -21998,7 +21998,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H132" s="1">
         <v>1</v>
@@ -22095,7 +22095,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H133" s="1">
         <v>1</v>
@@ -22193,7 +22193,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H134" s="1">
         <v>1</v>
@@ -22290,7 +22290,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H135" s="1">
         <v>1</v>
@@ -22388,7 +22388,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H136" s="1">
         <v>1</v>
@@ -22485,7 +22485,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H137" s="1">
         <v>1</v>
@@ -22582,7 +22582,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H138" s="1">
         <v>1</v>
@@ -22680,7 +22680,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H139" s="1">
         <v>1</v>
@@ -22777,7 +22777,7 @@
         <v>0</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H140" s="1">
         <v>1</v>
@@ -22875,7 +22875,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H141" s="1">
         <v>1</v>
@@ -22972,7 +22972,7 @@
         <v>0</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H142" s="1">
         <v>1</v>
@@ -23069,7 +23069,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H143" s="1">
         <v>1</v>
@@ -23166,7 +23166,7 @@
         <v>0</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H144" s="1">
         <v>1</v>
@@ -23264,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H145" s="1">
         <v>1</v>
@@ -23361,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H146" s="1">
         <v>1</v>
@@ -23458,7 +23458,7 @@
         <v>0</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H147" s="1">
         <v>1</v>
@@ -23556,7 +23556,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H148" s="1">
         <v>1</v>
@@ -23654,7 +23654,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H149" s="1">
         <v>1</v>
@@ -23751,7 +23751,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H150" s="1">
         <v>1</v>
@@ -26563,7 +26563,7 @@
         <v>1</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
@@ -26660,7 +26660,7 @@
         <v>1</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -26756,7 +26756,7 @@
         <v>1</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -26852,7 +26852,7 @@
         <v>1</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -26948,7 +26948,7 @@
         <v>1</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -27044,7 +27044,7 @@
         <v>2</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -27141,7 +27141,7 @@
         <v>2</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -27237,7 +27237,7 @@
         <v>2</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -27333,7 +27333,7 @@
         <v>2</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
@@ -27429,7 +27429,7 @@
         <v>3</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
@@ -27525,7 +27525,7 @@
         <v>3</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
@@ -27621,7 +27621,7 @@
         <v>3</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -27717,7 +27717,7 @@
         <v>6</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -27813,7 +27813,7 @@
         <v>6</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -27909,7 +27909,7 @@
         <v>6</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
@@ -28005,7 +28005,7 @@
         <v>6</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
@@ -28101,7 +28101,7 @@
         <v>3</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
@@ -28197,7 +28197,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -28293,7 +28293,7 @@
         <v>2</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
@@ -28389,7 +28389,7 @@
         <v>6</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -28485,7 +28485,7 @@
         <v>6</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H199" s="1">
         <v>0</v>
@@ -28581,7 +28581,7 @@
         <v>0</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H200" s="1">
         <v>0</v>
@@ -28677,7 +28677,7 @@
         <v>0</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H201" s="1">
         <v>0</v>
@@ -28773,7 +28773,7 @@
         <v>0</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
@@ -28869,7 +28869,7 @@
         <v>0</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H203" s="1">
         <v>0</v>
@@ -28965,7 +28965,7 @@
         <v>0</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -29061,7 +29061,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -29157,7 +29157,7 @@
         <v>0</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
@@ -29253,7 +29253,7 @@
         <v>0</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -29349,7 +29349,7 @@
         <v>0</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -29445,7 +29445,7 @@
         <v>0</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
@@ -29541,7 +29541,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
@@ -29637,7 +29637,7 @@
         <v>0</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -29733,7 +29733,7 @@
         <v>0</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
@@ -29829,7 +29829,7 @@
         <v>0</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -29925,7 +29925,7 @@
         <v>0</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -30021,7 +30021,7 @@
         <v>0</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -30117,7 +30117,7 @@
         <v>0</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -30213,7 +30213,7 @@
         <v>0</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H217" s="9">
         <v>0</v>
@@ -30312,7 +30312,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H218" s="9">
         <v>0</v>
@@ -30411,7 +30411,7 @@
         <v>0</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H219" s="9">
         <v>0</v>
@@ -30510,7 +30510,7 @@
         <v>0</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H220" s="9">
         <v>0</v>
@@ -30609,7 +30609,7 @@
         <v>0</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H221" s="9">
         <v>0</v>
@@ -30708,7 +30708,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H222" s="9">
         <v>0</v>
@@ -30807,7 +30807,7 @@
         <v>0</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H223" s="9">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H224" s="9">
         <v>0</v>
@@ -31005,7 +31005,7 @@
         <v>0</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H225" s="9">
         <v>0</v>
@@ -31104,7 +31104,7 @@
         <v>0</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H226" s="9">
         <v>0</v>
@@ -31203,7 +31203,7 @@
         <v>0</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H227" s="9">
         <v>0</v>
@@ -31302,7 +31302,7 @@
         <v>0</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -31398,7 +31398,7 @@
         <v>0</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -31494,7 +31494,7 @@
         <v>0</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H230" s="1">
         <v>0</v>
@@ -31590,7 +31590,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -31686,7 +31686,7 @@
         <v>0</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -31782,7 +31782,7 @@
         <v>0</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H233" s="1">
         <v>0</v>
@@ -31878,7 +31878,7 @@
         <v>0</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
@@ -31974,7 +31974,7 @@
         <v>0</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -32070,7 +32070,7 @@
         <v>0</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -32166,7 +32166,7 @@
         <v>0</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -32262,7 +32262,7 @@
         <v>0</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -32358,7 +32358,7 @@
         <v>0</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
@@ -32454,7 +32454,7 @@
         <v>0</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H240" s="1">
         <v>0</v>
@@ -32550,7 +32550,7 @@
         <v>0</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H241" s="1">
         <v>0</v>
@@ -35142,7 +35142,7 @@
         <v>0</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H268" s="1">
         <v>1</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H269" s="1">
         <v>1</v>
@@ -35333,7 +35333,7 @@
         <v>0</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H270" s="1">
         <v>1</v>
@@ -35428,7 +35428,7 @@
         <v>0</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H271" s="1">
         <v>1</v>
@@ -35501,7 +35501,7 @@
         <v>0</v>
       </c>
       <c r="AH271" s="7" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="272" spans="1:34" x14ac:dyDescent="0.15">
@@ -35512,7 +35512,7 @@
         <v>4007</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>1621</v>
+        <v>1828</v>
       </c>
       <c r="D272" s="1">
         <v>3</v>
@@ -35524,7 +35524,7 @@
         <v>0</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H272" s="1">
         <v>1</v>
@@ -35597,7 +35597,7 @@
         <v>0</v>
       </c>
       <c r="AH272" s="50" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="273" spans="1:34" x14ac:dyDescent="0.15">
@@ -35608,7 +35608,7 @@
         <v>4008</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D273" s="1">
         <v>3</v>
@@ -35620,7 +35620,7 @@
         <v>0</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H273" s="1">
         <v>1</v>
@@ -35715,7 +35715,7 @@
         <v>0</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H274" s="1">
         <v>1</v>
@@ -35788,7 +35788,7 @@
         <v>0</v>
       </c>
       <c r="AH274" s="50" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="275" spans="1:34" x14ac:dyDescent="0.15">
@@ -35799,7 +35799,7 @@
         <v>4010</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D275" s="1">
         <v>3</v>
@@ -35811,7 +35811,7 @@
         <v>0</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H275" s="1">
         <v>1</v>
@@ -35907,7 +35907,7 @@
         <v>0</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H276" s="1">
         <v>1</v>
@@ -35991,7 +35991,7 @@
         <v>4012</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D277" s="1">
         <v>3</v>
@@ -36003,7 +36003,7 @@
         <v>0</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H277" s="1">
         <v>1</v>
@@ -36075,7 +36075,7 @@
         <v>0</v>
       </c>
       <c r="AH277" s="50" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="278" spans="1:34" x14ac:dyDescent="0.15">
@@ -36086,7 +36086,7 @@
         <v>4013</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D278" s="1">
         <v>3</v>
@@ -36098,7 +36098,7 @@
         <v>0</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H278" s="1">
         <v>1</v>
@@ -36182,7 +36182,7 @@
         <v>4014</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D279" s="1">
         <v>3</v>
@@ -36194,7 +36194,7 @@
         <v>0</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H279" s="1">
         <v>1</v>
@@ -36267,7 +36267,7 @@
         <v>0</v>
       </c>
       <c r="AH279" s="50" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="280" spans="1:34" x14ac:dyDescent="0.15">
@@ -36278,7 +36278,7 @@
         <v>4015</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D280" s="1">
         <v>3</v>
@@ -36290,7 +36290,7 @@
         <v>0</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H280" s="1">
         <v>1</v>
@@ -36363,7 +36363,7 @@
         <v>0</v>
       </c>
       <c r="AH280" s="50" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="281" spans="1:34" x14ac:dyDescent="0.15">
@@ -36386,7 +36386,7 @@
         <v>0</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H281" s="1">
         <v>1</v>
@@ -36470,7 +36470,7 @@
         <v>4017</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D282" s="1">
         <v>3</v>
@@ -36482,7 +36482,7 @@
         <v>0</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H282" s="1">
         <v>1</v>
@@ -36555,7 +36555,7 @@
         <v>0</v>
       </c>
       <c r="AH282" s="50" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="283" spans="1:34" x14ac:dyDescent="0.15">
@@ -36566,7 +36566,7 @@
         <v>4018</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D283" s="1">
         <v>3</v>
@@ -36578,7 +36578,7 @@
         <v>0</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H283" s="1">
         <v>1</v>
@@ -36674,7 +36674,7 @@
         <v>0</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H284" s="1">
         <v>1</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="AH284" s="51" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="285" spans="1:34" x14ac:dyDescent="0.15">
@@ -36758,7 +36758,7 @@
         <v>4021</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D285" s="1">
         <v>3</v>
@@ -36770,7 +36770,7 @@
         <v>0</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H285" s="1">
         <v>1</v>
@@ -36866,7 +36866,7 @@
         <v>0</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H286" s="1">
         <v>1</v>
@@ -36962,7 +36962,7 @@
         <v>0</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H287" s="1">
         <v>1</v>
@@ -37058,7 +37058,7 @@
         <v>0</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H288" s="1">
         <v>1</v>
@@ -37131,7 +37131,7 @@
         <v>0</v>
       </c>
       <c r="AH288" s="50" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="289" spans="1:34" x14ac:dyDescent="0.15">
@@ -37142,7 +37142,7 @@
         <v>4100</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D289" s="1">
         <v>3</v>
@@ -37154,7 +37154,7 @@
         <v>0</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H289" s="1">
         <v>1</v>
@@ -37250,7 +37250,7 @@
         <v>0</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H290" s="1">
         <v>1</v>
@@ -37334,7 +37334,7 @@
         <v>4103</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
@@ -37346,7 +37346,7 @@
         <v>0</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H291" s="1">
         <v>1</v>
@@ -37430,7 +37430,7 @@
         <v>4105</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
@@ -37442,7 +37442,7 @@
         <v>0</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H292" s="1">
         <v>1</v>
@@ -37526,7 +37526,7 @@
         <v>4106</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H293" s="1">
         <v>1</v>
@@ -37622,7 +37622,7 @@
         <v>4109</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -37634,7 +37634,7 @@
         <v>0</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H294" s="1">
         <v>1</v>
@@ -37717,7 +37717,7 @@
         <v>4110</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -37729,7 +37729,7 @@
         <v>0</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H295" s="1">
         <v>1</v>
@@ -37802,7 +37802,7 @@
         <v>0</v>
       </c>
       <c r="AH295" s="8" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="296" spans="1:34" x14ac:dyDescent="0.15">
@@ -37813,7 +37813,7 @@
         <v>4111</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -37825,7 +37825,7 @@
         <v>0</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H296" s="1">
         <v>1</v>
@@ -37909,7 +37909,7 @@
         <v>4112</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -37921,7 +37921,7 @@
         <v>0</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H297" s="1">
         <v>1</v>
@@ -38005,7 +38005,7 @@
         <v>4113</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -38017,7 +38017,7 @@
         <v>0</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H298" s="1">
         <v>1</v>
@@ -38113,7 +38113,7 @@
         <v>0</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H299" s="1">
         <v>1</v>
@@ -38197,7 +38197,7 @@
         <v>4115</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -38209,7 +38209,7 @@
         <v>0</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H300" s="1">
         <v>1</v>
@@ -38293,7 +38293,7 @@
         <v>4116</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -38305,7 +38305,7 @@
         <v>0</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H301" s="1">
         <v>1</v>
@@ -38401,7 +38401,7 @@
         <v>0</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H302" s="1">
         <v>1</v>
@@ -38497,7 +38497,7 @@
         <v>0</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H303" s="1">
         <v>1</v>
@@ -38592,7 +38592,7 @@
         <v>0</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -38687,7 +38687,7 @@
         <v>0</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
@@ -38782,7 +38782,7 @@
         <v>0</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -38877,7 +38877,7 @@
         <v>0</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H307" s="1">
         <v>0</v>
@@ -38972,7 +38972,7 @@
         <v>0</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H308" s="1">
         <v>1</v>
@@ -39067,7 +39067,7 @@
         <v>0</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H309" s="1">
         <v>1</v>
@@ -39162,7 +39162,7 @@
         <v>0</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H310" s="1">
         <v>1</v>
@@ -39257,7 +39257,7 @@
         <v>0</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H311" s="1">
         <v>0</v>
@@ -39329,7 +39329,7 @@
         <v>0</v>
       </c>
       <c r="AH311" s="35" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="312" spans="1:35" x14ac:dyDescent="0.15">
@@ -39352,7 +39352,7 @@
         <v>0</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H312" s="1">
         <v>0</v>
@@ -39447,7 +39447,7 @@
         <v>0</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H313" s="1">
         <v>0</v>
@@ -39542,7 +39542,7 @@
         <v>0</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H314" s="1">
         <v>1</v>
@@ -39637,7 +39637,7 @@
         <v>0</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H315" s="1">
         <v>1</v>
@@ -39717,7 +39717,7 @@
         <v>0</v>
       </c>
       <c r="AH315" s="35" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="AI315" s="1" t="s">
         <v>1572</v>
@@ -39743,7 +39743,7 @@
         <v>0</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H316" s="1">
         <v>1</v>
@@ -39823,7 +39823,7 @@
         <v>0</v>
       </c>
       <c r="AH316" s="35" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="AI316" s="1" t="s">
         <v>1573</v>
@@ -39849,7 +39849,7 @@
         <v>0</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H317" s="1">
         <v>1</v>
@@ -39955,7 +39955,7 @@
         <v>0</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H318" s="1">
         <v>1</v>
@@ -40035,7 +40035,7 @@
         <v>0</v>
       </c>
       <c r="AH318" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="AI318" s="1" t="s">
         <v>1574</v>
@@ -40061,7 +40061,7 @@
         <v>0</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H319" s="1">
         <v>1</v>
@@ -40167,7 +40167,7 @@
         <v>0</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H320" s="1">
         <v>1</v>
@@ -40273,7 +40273,7 @@
         <v>0</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H321" s="1">
         <v>1</v>
@@ -40379,7 +40379,7 @@
         <v>0</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H322" s="1">
         <v>1</v>
@@ -40591,7 +40591,7 @@
         <v>0</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H324" s="1">
         <v>1</v>
@@ -40777,7 +40777,7 @@
         <v>8</v>
       </c>
       <c r="AH325" s="35" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="AI325" s="1" t="s">
         <v>636</v>
@@ -40803,7 +40803,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H326" s="1">
         <v>1</v>
@@ -40909,7 +40909,7 @@
         <v>0</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H327" s="1">
         <v>1</v>
@@ -41227,7 +41227,7 @@
         <v>0</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H330" s="1">
         <v>1</v>
@@ -41307,7 +41307,7 @@
         <v>0</v>
       </c>
       <c r="AH330" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="AI330" s="1" t="s">
         <v>1604</v>
@@ -41333,7 +41333,7 @@
         <v>0</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H331" s="1">
         <v>1</v>
@@ -41413,7 +41413,7 @@
         <v>0</v>
       </c>
       <c r="AH331" s="35" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="AI331" s="1" t="s">
         <v>1603</v>
@@ -41439,7 +41439,7 @@
         <v>0</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H332" s="1">
         <v>1</v>
@@ -41545,7 +41545,7 @@
         <v>0</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H333" s="1">
         <v>1</v>
@@ -41625,7 +41625,7 @@
         <v>0</v>
       </c>
       <c r="AH333" s="35" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="AI333" s="1" t="s">
         <v>1602</v>
@@ -41757,7 +41757,7 @@
         <v>0</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H335" s="1">
         <v>1</v>
@@ -41863,7 +41863,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H336" s="1">
         <v>1</v>
@@ -41969,7 +41969,7 @@
         <v>0</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H337" s="1">
         <v>1</v>
@@ -42075,7 +42075,7 @@
         <v>0</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H338" s="1">
         <v>1</v>
@@ -42155,7 +42155,7 @@
         <v>8</v>
       </c>
       <c r="AH338" s="35" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="AI338" s="1" t="s">
         <v>636</v>
@@ -42181,7 +42181,7 @@
         <v>0</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H339" s="1">
         <v>1</v>
@@ -42287,7 +42287,7 @@
         <v>0</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H340" s="1">
         <v>1</v>
@@ -42393,7 +42393,7 @@
         <v>0</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H341" s="1">
         <v>1</v>
@@ -42499,7 +42499,7 @@
         <v>0</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H342" s="1">
         <v>1</v>
@@ -42711,7 +42711,7 @@
         <v>0</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H344" s="1">
         <v>1</v>
@@ -42817,7 +42817,7 @@
         <v>0</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H345" s="1">
         <v>1</v>
@@ -43029,7 +43029,7 @@
         <v>0</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H347" s="1">
         <v>1</v>
@@ -43135,7 +43135,7 @@
         <v>0</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H348" s="1">
         <v>1</v>
@@ -43347,7 +43347,7 @@
         <v>0</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H350" s="1">
         <v>1</v>
@@ -43453,7 +43453,7 @@
         <v>0</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H351" s="1">
         <v>1</v>
@@ -43559,7 +43559,7 @@
         <v>0</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H352" s="1">
         <v>1</v>
@@ -43665,7 +43665,7 @@
         <v>0</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H353" s="1">
         <v>1</v>
@@ -43771,7 +43771,7 @@
         <v>0</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H354" s="1">
         <v>1</v>
@@ -43877,7 +43877,7 @@
         <v>0</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H355" s="1">
         <v>1</v>
@@ -43983,7 +43983,7 @@
         <v>0</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H356" s="1">
         <v>1</v>
@@ -45017,7 +45017,7 @@
         <v>8</v>
       </c>
       <c r="AH365" s="34" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="AI365" s="1" t="s">
         <v>636</v>
@@ -45229,7 +45229,7 @@
         <v>8</v>
       </c>
       <c r="AH367" s="34" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="AI367" s="1" t="s">
         <v>636</v>
@@ -45335,10 +45335,10 @@
         <v>0</v>
       </c>
       <c r="AH368" s="35" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="AI368" s="1" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="369" spans="1:35" x14ac:dyDescent="0.15">
@@ -45547,7 +45547,7 @@
         <v>8</v>
       </c>
       <c r="AH370" s="35" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="AI370" s="1" t="s">
         <v>636</v>
@@ -45971,7 +45971,7 @@
         <v>0</v>
       </c>
       <c r="AH374" s="35" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="AI374" s="1" t="s">
         <v>1584</v>
@@ -46183,7 +46183,7 @@
         <v>0</v>
       </c>
       <c r="AH376" s="35" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="AI376" s="1" t="s">
         <v>1586</v>
@@ -46501,7 +46501,7 @@
         <v>8</v>
       </c>
       <c r="AH379" s="35" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="AI379" s="1" t="s">
         <v>636</v>
@@ -46633,7 +46633,7 @@
         <v>0</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H381" s="1">
         <v>1</v>
@@ -46713,7 +46713,7 @@
         <v>8</v>
       </c>
       <c r="AH381" s="35" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="AI381" s="1" t="s">
         <v>1594</v>
@@ -46739,7 +46739,7 @@
         <v>0</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H382" s="1">
         <v>1</v>
@@ -46845,7 +46845,7 @@
         <v>0</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H383" s="1">
         <v>1</v>
@@ -46951,7 +46951,7 @@
         <v>0</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H384" s="1">
         <v>1</v>
@@ -47057,7 +47057,7 @@
         <v>0</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H385" s="1">
         <v>1</v>
@@ -47163,7 +47163,7 @@
         <v>0</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H386" s="1">
         <v>1</v>
@@ -47269,7 +47269,7 @@
         <v>0</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H387" s="1">
         <v>1</v>
@@ -47375,7 +47375,7 @@
         <v>0</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H388" s="1">
         <v>1</v>
@@ -47481,7 +47481,7 @@
         <v>0</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H389" s="1">
         <v>1</v>
@@ -47587,7 +47587,7 @@
         <v>0</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H390" s="1">
         <v>1</v>
@@ -47693,7 +47693,7 @@
         <v>0</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H391" s="1">
         <v>1</v>
@@ -47799,7 +47799,7 @@
         <v>0</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H392" s="1">
         <v>1</v>
@@ -48011,7 +48011,7 @@
         <v>0</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H394" s="1">
         <v>1</v>
@@ -65306,7 +65306,7 @@
         <v>139</v>
       </c>
       <c r="I1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="2" spans="8:9" x14ac:dyDescent="0.15">
@@ -65314,7 +65314,7 @@
         <v>140</v>
       </c>
       <c r="I2" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="3" spans="8:9" x14ac:dyDescent="0.15">
@@ -65322,7 +65322,7 @@
         <v>141</v>
       </c>
       <c r="I3" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="4" spans="8:9" x14ac:dyDescent="0.15">
@@ -65330,7 +65330,7 @@
         <v>142</v>
       </c>
       <c r="I4" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="5" spans="8:9" x14ac:dyDescent="0.15">
@@ -65338,7 +65338,7 @@
         <v>192</v>
       </c>
       <c r="I5" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="6" spans="8:9" x14ac:dyDescent="0.15">
@@ -65346,7 +65346,7 @@
         <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="7" spans="8:9" x14ac:dyDescent="0.15">
@@ -65354,7 +65354,7 @@
         <v>922</v>
       </c>
       <c r="I7" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="8" spans="8:9" x14ac:dyDescent="0.15">
@@ -65362,7 +65362,7 @@
         <v>958</v>
       </c>
       <c r="I8" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="9" spans="8:9" x14ac:dyDescent="0.15">
@@ -65370,7 +65370,7 @@
         <v>146</v>
       </c>
       <c r="I9" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="10" spans="8:9" x14ac:dyDescent="0.15">
@@ -65378,7 +65378,7 @@
         <v>147</v>
       </c>
       <c r="I10" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="11" spans="8:9" x14ac:dyDescent="0.15">
@@ -65386,7 +65386,7 @@
         <v>148</v>
       </c>
       <c r="I11" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="12" spans="8:9" x14ac:dyDescent="0.15">
@@ -65394,7 +65394,7 @@
         <v>149</v>
       </c>
       <c r="I12" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="13" spans="8:9" x14ac:dyDescent="0.15">
@@ -65402,7 +65402,7 @@
         <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="14" spans="8:9" x14ac:dyDescent="0.15">
@@ -65410,7 +65410,7 @@
         <v>151</v>
       </c>
       <c r="I14" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="15" spans="8:9" x14ac:dyDescent="0.15">
@@ -65418,7 +65418,7 @@
         <v>152</v>
       </c>
       <c r="I15" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="16" spans="8:9" x14ac:dyDescent="0.15">
@@ -65426,7 +65426,7 @@
         <v>187</v>
       </c>
       <c r="I16" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.15">
@@ -65434,7 +65434,7 @@
         <v>188</v>
       </c>
       <c r="I17" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.15">
@@ -65442,7 +65442,7 @@
         <v>189</v>
       </c>
       <c r="I18" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="19" spans="8:9" x14ac:dyDescent="0.15">
@@ -65450,7 +65450,7 @@
         <v>858</v>
       </c>
       <c r="I19" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="20" spans="8:9" x14ac:dyDescent="0.15">
@@ -65458,7 +65458,7 @@
         <v>193</v>
       </c>
       <c r="I20" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="21" spans="8:9" x14ac:dyDescent="0.15">
@@ -65466,7 +65466,7 @@
         <v>162</v>
       </c>
       <c r="I21" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="22" spans="8:9" x14ac:dyDescent="0.15">
@@ -65474,7 +65474,7 @@
         <v>159</v>
       </c>
       <c r="I22" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="23" spans="8:9" x14ac:dyDescent="0.15">
@@ -65482,7 +65482,7 @@
         <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="24" spans="8:9" x14ac:dyDescent="0.15">
@@ -65490,7 +65490,7 @@
         <v>174</v>
       </c>
       <c r="I24" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="25" spans="8:9" x14ac:dyDescent="0.15">
@@ -65498,7 +65498,7 @@
         <v>178</v>
       </c>
       <c r="I25" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="26" spans="8:9" x14ac:dyDescent="0.15">
@@ -65506,7 +65506,7 @@
         <v>250</v>
       </c>
       <c r="I26" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="27" spans="8:9" x14ac:dyDescent="0.15">
@@ -65514,7 +65514,7 @@
         <v>205</v>
       </c>
       <c r="I27" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="28" spans="8:9" x14ac:dyDescent="0.15">
@@ -65522,7 +65522,7 @@
         <v>795</v>
       </c>
       <c r="I28" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="29" spans="8:9" x14ac:dyDescent="0.15">
@@ -65530,7 +65530,7 @@
         <v>163</v>
       </c>
       <c r="I29" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="30" spans="8:9" x14ac:dyDescent="0.15">
@@ -65538,7 +65538,7 @@
         <v>184</v>
       </c>
       <c r="I30" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="31" spans="8:9" x14ac:dyDescent="0.15">
@@ -65546,7 +65546,7 @@
         <v>166</v>
       </c>
       <c r="I31" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="32" spans="8:9" x14ac:dyDescent="0.15">
@@ -65554,7 +65554,7 @@
         <v>182</v>
       </c>
       <c r="I32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="33" spans="8:9" x14ac:dyDescent="0.15">
@@ -65562,7 +65562,7 @@
         <v>194</v>
       </c>
       <c r="I33" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="34" spans="8:9" x14ac:dyDescent="0.15">
@@ -65570,7 +65570,7 @@
         <v>195</v>
       </c>
       <c r="I34" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="35" spans="8:9" x14ac:dyDescent="0.15">
@@ -65578,7 +65578,7 @@
         <v>165</v>
       </c>
       <c r="I35" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="36" spans="8:9" x14ac:dyDescent="0.15">
@@ -65586,7 +65586,7 @@
         <v>167</v>
       </c>
       <c r="I36" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="37" spans="8:9" x14ac:dyDescent="0.15">
@@ -65594,7 +65594,7 @@
         <v>196</v>
       </c>
       <c r="I37" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="38" spans="8:9" x14ac:dyDescent="0.15">
@@ -65602,7 +65602,7 @@
         <v>164</v>
       </c>
       <c r="I38" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="39" spans="8:9" x14ac:dyDescent="0.15">
@@ -65610,7 +65610,7 @@
         <v>197</v>
       </c>
       <c r="I39" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="40" spans="8:9" x14ac:dyDescent="0.15">
@@ -65618,7 +65618,7 @@
         <v>796</v>
       </c>
       <c r="I40" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="41" spans="8:9" x14ac:dyDescent="0.15">
@@ -65626,7 +65626,7 @@
         <v>198</v>
       </c>
       <c r="I41" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="42" spans="8:9" x14ac:dyDescent="0.15">
@@ -65634,7 +65634,7 @@
         <v>171</v>
       </c>
       <c r="I42" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="43" spans="8:9" x14ac:dyDescent="0.15">
@@ -65642,7 +65642,7 @@
         <v>199</v>
       </c>
       <c r="I43" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="44" spans="8:9" x14ac:dyDescent="0.15">
@@ -65650,7 +65650,7 @@
         <v>200</v>
       </c>
       <c r="I44" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="45" spans="8:9" x14ac:dyDescent="0.15">
@@ -65658,7 +65658,7 @@
         <v>170</v>
       </c>
       <c r="I45" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="46" spans="8:9" x14ac:dyDescent="0.15">
@@ -65666,7 +65666,7 @@
         <v>201</v>
       </c>
       <c r="I46" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="47" spans="8:9" x14ac:dyDescent="0.15">
@@ -65674,7 +65674,7 @@
         <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="48" spans="8:9" x14ac:dyDescent="0.15">
@@ -65682,7 +65682,7 @@
         <v>202</v>
       </c>
       <c r="I48" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="49" spans="8:9" x14ac:dyDescent="0.15">
@@ -65690,7 +65690,7 @@
         <v>185</v>
       </c>
       <c r="I49" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="50" spans="8:9" x14ac:dyDescent="0.15">
@@ -65698,7 +65698,7 @@
         <v>168</v>
       </c>
       <c r="I50" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="51" spans="8:9" x14ac:dyDescent="0.15">
@@ -65706,7 +65706,7 @@
         <v>175</v>
       </c>
       <c r="I51" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="52" spans="8:9" x14ac:dyDescent="0.15">
@@ -65714,7 +65714,7 @@
         <v>177</v>
       </c>
       <c r="I52" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="53" spans="8:9" x14ac:dyDescent="0.15">
@@ -65722,7 +65722,7 @@
         <v>179</v>
       </c>
       <c r="I53" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="54" spans="8:9" x14ac:dyDescent="0.15">
@@ -65730,7 +65730,7 @@
         <v>180</v>
       </c>
       <c r="I54" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="55" spans="8:9" x14ac:dyDescent="0.15">
@@ -65738,7 +65738,7 @@
         <v>203</v>
       </c>
       <c r="I55" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="56" spans="8:9" x14ac:dyDescent="0.15">
@@ -65746,7 +65746,7 @@
         <v>204</v>
       </c>
       <c r="I56" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="57" spans="8:9" x14ac:dyDescent="0.15">
@@ -65754,7 +65754,7 @@
         <v>181</v>
       </c>
       <c r="I57" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="58" spans="8:9" x14ac:dyDescent="0.15">
@@ -65762,7 +65762,7 @@
         <v>206</v>
       </c>
       <c r="I58" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="59" spans="8:9" x14ac:dyDescent="0.15">
@@ -65770,7 +65770,7 @@
         <v>207</v>
       </c>
       <c r="I59" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="60" spans="8:9" x14ac:dyDescent="0.15">
@@ -65778,7 +65778,7 @@
         <v>183</v>
       </c>
       <c r="I60" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="61" spans="8:9" x14ac:dyDescent="0.15">
@@ -65786,7 +65786,7 @@
         <v>208</v>
       </c>
       <c r="I61" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="62" spans="8:9" x14ac:dyDescent="0.15">
@@ -65794,7 +65794,7 @@
         <v>209</v>
       </c>
       <c r="I62" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="63" spans="8:9" x14ac:dyDescent="0.15">
@@ -65802,7 +65802,7 @@
         <v>210</v>
       </c>
       <c r="I63" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="64" spans="8:9" x14ac:dyDescent="0.15">
@@ -65810,7 +65810,7 @@
         <v>169</v>
       </c>
       <c r="I64" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="65" spans="8:9" x14ac:dyDescent="0.15">
@@ -65818,7 +65818,7 @@
         <v>211</v>
       </c>
       <c r="I65" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="66" spans="8:9" x14ac:dyDescent="0.15">
@@ -65826,7 +65826,7 @@
         <v>212</v>
       </c>
       <c r="I66" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="67" spans="8:9" x14ac:dyDescent="0.15">
@@ -65834,7 +65834,7 @@
         <v>213</v>
       </c>
       <c r="I67" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="68" spans="8:9" x14ac:dyDescent="0.15">
@@ -65842,7 +65842,7 @@
         <v>214</v>
       </c>
       <c r="I68" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="69" spans="8:9" x14ac:dyDescent="0.15">
@@ -65850,7 +65850,7 @@
         <v>215</v>
       </c>
       <c r="I69" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="70" spans="8:9" x14ac:dyDescent="0.15">
@@ -65858,7 +65858,7 @@
         <v>176</v>
       </c>
       <c r="I70" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="71" spans="8:9" x14ac:dyDescent="0.15">
@@ -65866,7 +65866,7 @@
         <v>186</v>
       </c>
       <c r="I71" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="72" spans="8:9" x14ac:dyDescent="0.15">
@@ -65874,7 +65874,7 @@
         <v>173</v>
       </c>
       <c r="I72" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="73" spans="8:9" x14ac:dyDescent="0.15">
@@ -65882,7 +65882,7 @@
         <v>216</v>
       </c>
       <c r="I73" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="74" spans="8:9" x14ac:dyDescent="0.15">
@@ -65890,7 +65890,7 @@
         <v>217</v>
       </c>
       <c r="I74" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="75" spans="8:9" x14ac:dyDescent="0.15">
@@ -65898,7 +65898,7 @@
         <v>218</v>
       </c>
       <c r="I75" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="76" spans="8:9" x14ac:dyDescent="0.15">
@@ -65906,7 +65906,7 @@
         <v>219</v>
       </c>
       <c r="I76" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="77" spans="8:9" x14ac:dyDescent="0.15">
@@ -65914,7 +65914,7 @@
         <v>797</v>
       </c>
       <c r="I77" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="78" spans="8:9" x14ac:dyDescent="0.15">
@@ -65922,7 +65922,7 @@
         <v>220</v>
       </c>
       <c r="I78" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="79" spans="8:9" x14ac:dyDescent="0.15">
@@ -65930,7 +65930,7 @@
         <v>221</v>
       </c>
       <c r="I79" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="80" spans="8:9" x14ac:dyDescent="0.15">
@@ -65938,7 +65938,7 @@
         <v>222</v>
       </c>
       <c r="I80" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="81" spans="8:9" x14ac:dyDescent="0.15">
@@ -65946,7 +65946,7 @@
         <v>223</v>
       </c>
       <c r="I81" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="82" spans="8:9" x14ac:dyDescent="0.15">
@@ -65954,7 +65954,7 @@
         <v>224</v>
       </c>
       <c r="I82" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="83" spans="8:9" x14ac:dyDescent="0.15">
@@ -65962,7 +65962,7 @@
         <v>225</v>
       </c>
       <c r="I83" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="84" spans="8:9" x14ac:dyDescent="0.15">
@@ -65970,7 +65970,7 @@
         <v>226</v>
       </c>
       <c r="I84" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="85" spans="8:9" x14ac:dyDescent="0.15">
@@ -65978,7 +65978,7 @@
         <v>227</v>
       </c>
       <c r="I85" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="86" spans="8:9" x14ac:dyDescent="0.15">
@@ -65986,7 +65986,7 @@
         <v>228</v>
       </c>
       <c r="I86" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="87" spans="8:9" x14ac:dyDescent="0.15">
@@ -65994,7 +65994,7 @@
         <v>229</v>
       </c>
       <c r="I87" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="88" spans="8:9" x14ac:dyDescent="0.15">
@@ -66002,7 +66002,7 @@
         <v>230</v>
       </c>
       <c r="I88" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="89" spans="8:9" x14ac:dyDescent="0.15">
@@ -66010,7 +66010,7 @@
         <v>231</v>
       </c>
       <c r="I89" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="90" spans="8:9" x14ac:dyDescent="0.15">
@@ -66018,7 +66018,7 @@
         <v>232</v>
       </c>
       <c r="I90" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="91" spans="8:9" x14ac:dyDescent="0.15">
@@ -66026,7 +66026,7 @@
         <v>233</v>
       </c>
       <c r="I91" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="92" spans="8:9" x14ac:dyDescent="0.15">
@@ -66034,7 +66034,7 @@
         <v>234</v>
       </c>
       <c r="I92" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="93" spans="8:9" x14ac:dyDescent="0.15">
@@ -66042,7 +66042,7 @@
         <v>235</v>
       </c>
       <c r="I93" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="94" spans="8:9" x14ac:dyDescent="0.15">
@@ -66050,7 +66050,7 @@
         <v>236</v>
       </c>
       <c r="I94" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="95" spans="8:9" x14ac:dyDescent="0.15">
@@ -66058,7 +66058,7 @@
         <v>237</v>
       </c>
       <c r="I95" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="96" spans="8:9" x14ac:dyDescent="0.15">
@@ -66066,7 +66066,7 @@
         <v>238</v>
       </c>
       <c r="I96" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="97" spans="8:9" x14ac:dyDescent="0.15">
@@ -66074,7 +66074,7 @@
         <v>239</v>
       </c>
       <c r="I97" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="98" spans="8:9" x14ac:dyDescent="0.15">
@@ -66082,7 +66082,7 @@
         <v>240</v>
       </c>
       <c r="I98" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="99" spans="8:9" x14ac:dyDescent="0.15">
@@ -66090,7 +66090,7 @@
         <v>241</v>
       </c>
       <c r="I99" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="100" spans="8:9" x14ac:dyDescent="0.15">
@@ -66098,7 +66098,7 @@
         <v>242</v>
       </c>
       <c r="I100" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="101" spans="8:9" x14ac:dyDescent="0.15">
@@ -66106,7 +66106,7 @@
         <v>243</v>
       </c>
       <c r="I101" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="102" spans="8:9" x14ac:dyDescent="0.15">
@@ -66114,7 +66114,7 @@
         <v>244</v>
       </c>
       <c r="I102" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="103" spans="8:9" x14ac:dyDescent="0.15">
@@ -66122,7 +66122,7 @@
         <v>245</v>
       </c>
       <c r="I103" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="104" spans="8:9" x14ac:dyDescent="0.15">
@@ -66130,7 +66130,7 @@
         <v>246</v>
       </c>
       <c r="I104" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="105" spans="8:9" x14ac:dyDescent="0.15">
@@ -66138,7 +66138,7 @@
         <v>247</v>
       </c>
       <c r="I105" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="106" spans="8:9" x14ac:dyDescent="0.15">
@@ -66146,7 +66146,7 @@
         <v>248</v>
       </c>
       <c r="I106" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="107" spans="8:9" x14ac:dyDescent="0.15">
@@ -66154,7 +66154,7 @@
         <v>798</v>
       </c>
       <c r="I107" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="108" spans="8:9" x14ac:dyDescent="0.15">
@@ -66162,7 +66162,7 @@
         <v>330</v>
       </c>
       <c r="I108" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="109" spans="8:9" x14ac:dyDescent="0.15">
@@ -66170,7 +66170,7 @@
         <v>331</v>
       </c>
       <c r="I109" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="110" spans="8:9" x14ac:dyDescent="0.15">
@@ -66178,7 +66178,7 @@
         <v>391</v>
       </c>
       <c r="I110" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="111" spans="8:9" x14ac:dyDescent="0.15">
@@ -66186,7 +66186,7 @@
         <v>332</v>
       </c>
       <c r="I111" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="112" spans="8:9" x14ac:dyDescent="0.15">
@@ -66194,7 +66194,7 @@
         <v>392</v>
       </c>
       <c r="I112" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="113" spans="8:9" x14ac:dyDescent="0.15">
@@ -66202,7 +66202,7 @@
         <v>333</v>
       </c>
       <c r="I113" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="114" spans="8:9" x14ac:dyDescent="0.15">
@@ -66210,7 +66210,7 @@
         <v>334</v>
       </c>
       <c r="I114" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="115" spans="8:9" x14ac:dyDescent="0.15">
@@ -66218,7 +66218,7 @@
         <v>827</v>
       </c>
       <c r="I115" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="116" spans="8:9" x14ac:dyDescent="0.15">
@@ -66226,7 +66226,7 @@
         <v>335</v>
       </c>
       <c r="I116" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="117" spans="8:9" x14ac:dyDescent="0.15">
@@ -66234,7 +66234,7 @@
         <v>336</v>
       </c>
       <c r="I117" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="118" spans="8:9" x14ac:dyDescent="0.15">
@@ -66242,7 +66242,7 @@
         <v>337</v>
       </c>
       <c r="I118" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="119" spans="8:9" x14ac:dyDescent="0.15">
@@ -66250,7 +66250,7 @@
         <v>338</v>
       </c>
       <c r="I119" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="120" spans="8:9" x14ac:dyDescent="0.15">
@@ -66258,7 +66258,7 @@
         <v>339</v>
       </c>
       <c r="I120" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="121" spans="8:9" x14ac:dyDescent="0.15">
@@ -66266,15 +66266,15 @@
         <v>773</v>
       </c>
       <c r="I121" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="122" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H122" s="7" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="I122" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="123" spans="8:9" x14ac:dyDescent="0.15">
@@ -66282,7 +66282,7 @@
         <v>341</v>
       </c>
       <c r="I123" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="124" spans="8:9" x14ac:dyDescent="0.15">
@@ -66290,7 +66290,7 @@
         <v>342</v>
       </c>
       <c r="I124" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="125" spans="8:9" x14ac:dyDescent="0.15">
@@ -66298,7 +66298,7 @@
         <v>616</v>
       </c>
       <c r="I125" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="126" spans="8:9" x14ac:dyDescent="0.15">
@@ -66306,7 +66306,7 @@
         <v>617</v>
       </c>
       <c r="I126" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="127" spans="8:9" x14ac:dyDescent="0.15">
@@ -66314,7 +66314,7 @@
         <v>618</v>
       </c>
       <c r="I127" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="128" spans="8:9" x14ac:dyDescent="0.15">
@@ -66322,7 +66322,7 @@
         <v>619</v>
       </c>
       <c r="I128" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="129" spans="8:9" x14ac:dyDescent="0.15">
@@ -66330,7 +66330,7 @@
         <v>351</v>
       </c>
       <c r="I129" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="130" spans="8:9" x14ac:dyDescent="0.15">
@@ -66338,7 +66338,7 @@
         <v>349</v>
       </c>
       <c r="I130" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="131" spans="8:9" x14ac:dyDescent="0.15">
@@ -66346,7 +66346,7 @@
         <v>394</v>
       </c>
       <c r="I131" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="132" spans="8:9" x14ac:dyDescent="0.15">
@@ -66354,7 +66354,7 @@
         <v>395</v>
       </c>
       <c r="I132" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="133" spans="8:9" x14ac:dyDescent="0.15">
@@ -66362,7 +66362,7 @@
         <v>353</v>
       </c>
       <c r="I133" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="134" spans="8:9" x14ac:dyDescent="0.15">
@@ -66370,7 +66370,7 @@
         <v>396</v>
       </c>
       <c r="I134" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="135" spans="8:9" x14ac:dyDescent="0.15">
@@ -66378,7 +66378,7 @@
         <v>667</v>
       </c>
       <c r="I135" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="136" spans="8:9" x14ac:dyDescent="0.15">
@@ -66386,7 +66386,7 @@
         <v>355</v>
       </c>
       <c r="I136" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="137" spans="8:9" x14ac:dyDescent="0.15">
@@ -66394,7 +66394,7 @@
         <v>397</v>
       </c>
       <c r="I137" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="138" spans="8:9" x14ac:dyDescent="0.15">
@@ -66402,7 +66402,7 @@
         <v>398</v>
       </c>
       <c r="I138" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="139" spans="8:9" x14ac:dyDescent="0.15">
@@ -66410,7 +66410,7 @@
         <v>399</v>
       </c>
       <c r="I139" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="140" spans="8:9" x14ac:dyDescent="0.15">
@@ -66418,7 +66418,7 @@
         <v>400</v>
       </c>
       <c r="I140" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="141" spans="8:9" x14ac:dyDescent="0.15">
@@ -66426,7 +66426,7 @@
         <v>401</v>
       </c>
       <c r="I141" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="142" spans="8:9" x14ac:dyDescent="0.15">
@@ -66434,7 +66434,7 @@
         <v>402</v>
       </c>
       <c r="I142" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="143" spans="8:9" x14ac:dyDescent="0.15">
@@ -66442,7 +66442,7 @@
         <v>403</v>
       </c>
       <c r="I143" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="144" spans="8:9" x14ac:dyDescent="0.15">
@@ -66450,7 +66450,7 @@
         <v>390</v>
       </c>
       <c r="I144" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="145" spans="8:9" x14ac:dyDescent="0.15">
@@ -66458,7 +66458,7 @@
         <v>620</v>
       </c>
       <c r="I145" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="146" spans="8:9" x14ac:dyDescent="0.15">
@@ -66466,7 +66466,7 @@
         <v>425</v>
       </c>
       <c r="I146" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="147" spans="8:9" x14ac:dyDescent="0.15">
@@ -66474,7 +66474,7 @@
         <v>422</v>
       </c>
       <c r="I147" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="148" spans="8:9" x14ac:dyDescent="0.15">
@@ -66482,7 +66482,7 @@
         <v>423</v>
       </c>
       <c r="I148" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="149" spans="8:9" x14ac:dyDescent="0.15">
@@ -66490,7 +66490,7 @@
         <v>424</v>
       </c>
       <c r="I149" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="150" spans="8:9" x14ac:dyDescent="0.15">
@@ -66498,7 +66498,7 @@
         <v>427</v>
       </c>
       <c r="I150" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="151" spans="8:9" x14ac:dyDescent="0.15">
@@ -66506,7 +66506,7 @@
         <v>431</v>
       </c>
       <c r="I151" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="152" spans="8:9" x14ac:dyDescent="0.15">
@@ -66514,7 +66514,7 @@
         <v>430</v>
       </c>
       <c r="I152" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="153" spans="8:9" x14ac:dyDescent="0.15">
@@ -66522,7 +66522,7 @@
         <v>429</v>
       </c>
       <c r="I153" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="154" spans="8:9" x14ac:dyDescent="0.15">
@@ -66530,7 +66530,7 @@
         <v>433</v>
       </c>
       <c r="I154" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="155" spans="8:9" x14ac:dyDescent="0.15">
@@ -66538,7 +66538,7 @@
         <v>428</v>
       </c>
       <c r="I155" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="156" spans="8:9" x14ac:dyDescent="0.15">
@@ -66546,7 +66546,7 @@
         <v>621</v>
       </c>
       <c r="I156" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="157" spans="8:9" x14ac:dyDescent="0.15">
@@ -66554,7 +66554,7 @@
         <v>718</v>
       </c>
       <c r="I157" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="158" spans="8:9" x14ac:dyDescent="0.15">
@@ -66562,7 +66562,7 @@
         <v>778</v>
       </c>
       <c r="I158" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="159" spans="8:9" x14ac:dyDescent="0.15">
@@ -66570,7 +66570,7 @@
         <v>725</v>
       </c>
       <c r="I159" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="160" spans="8:9" x14ac:dyDescent="0.15">
@@ -66578,7 +66578,7 @@
         <v>726</v>
       </c>
       <c r="I160" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="161" spans="8:9" x14ac:dyDescent="0.15">
@@ -66586,7 +66586,7 @@
         <v>733</v>
       </c>
       <c r="I161" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="162" spans="8:9" x14ac:dyDescent="0.15">
@@ -66594,7 +66594,7 @@
         <v>729</v>
       </c>
       <c r="I162" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="163" spans="8:9" x14ac:dyDescent="0.15">
@@ -66602,7 +66602,7 @@
         <v>728</v>
       </c>
       <c r="I163" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="164" spans="8:9" x14ac:dyDescent="0.15">
@@ -66610,7 +66610,7 @@
         <v>737</v>
       </c>
       <c r="I164" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="165" spans="8:9" x14ac:dyDescent="0.15">
@@ -66618,47 +66618,47 @@
         <v>730</v>
       </c>
       <c r="I165" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="166" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H166" s="7" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="I166" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="167" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H167" s="7" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="I167" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="168" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H168" s="7" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="I168" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="169" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H169" s="7" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="I169" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="170" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H170" s="7" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="I170" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="171" spans="8:9" x14ac:dyDescent="0.15">
@@ -66666,7 +66666,7 @@
         <v>120</v>
       </c>
       <c r="I171" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="172" spans="8:9" x14ac:dyDescent="0.15">
@@ -66674,7 +66674,7 @@
         <v>122</v>
       </c>
       <c r="I172" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="173" spans="8:9" x14ac:dyDescent="0.15">
@@ -66682,7 +66682,7 @@
         <v>121</v>
       </c>
       <c r="I173" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="174" spans="8:9" x14ac:dyDescent="0.15">
@@ -66690,7 +66690,7 @@
         <v>123</v>
       </c>
       <c r="I174" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="175" spans="8:9" x14ac:dyDescent="0.15">
@@ -66698,7 +66698,7 @@
         <v>1526</v>
       </c>
       <c r="I175" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="176" spans="8:9" x14ac:dyDescent="0.15">
@@ -66706,7 +66706,7 @@
         <v>124</v>
       </c>
       <c r="I176" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="177" spans="8:9" x14ac:dyDescent="0.15">
@@ -66714,7 +66714,7 @@
         <v>125</v>
       </c>
       <c r="I177" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="178" spans="8:9" x14ac:dyDescent="0.15">
@@ -66722,7 +66722,7 @@
         <v>126</v>
       </c>
       <c r="I178" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="179" spans="8:9" x14ac:dyDescent="0.15">
@@ -66730,7 +66730,7 @@
         <v>1527</v>
       </c>
       <c r="I179" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="180" spans="8:9" x14ac:dyDescent="0.15">
@@ -66738,7 +66738,7 @@
         <v>128</v>
       </c>
       <c r="I180" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="181" spans="8:9" x14ac:dyDescent="0.15">
@@ -66746,7 +66746,7 @@
         <v>129</v>
       </c>
       <c r="I181" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="182" spans="8:9" x14ac:dyDescent="0.15">
@@ -66754,7 +66754,7 @@
         <v>130</v>
       </c>
       <c r="I182" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="183" spans="8:9" x14ac:dyDescent="0.15">
@@ -66762,7 +66762,7 @@
         <v>131</v>
       </c>
       <c r="I183" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="184" spans="8:9" x14ac:dyDescent="0.15">
@@ -66770,7 +66770,7 @@
         <v>132</v>
       </c>
       <c r="I184" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="185" spans="8:9" x14ac:dyDescent="0.15">
@@ -66778,7 +66778,7 @@
         <v>133</v>
       </c>
       <c r="I185" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="186" spans="8:9" x14ac:dyDescent="0.15">
@@ -66786,7 +66786,7 @@
         <v>134</v>
       </c>
       <c r="I186" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="187" spans="8:9" x14ac:dyDescent="0.15">
@@ -66794,7 +66794,7 @@
         <v>957</v>
       </c>
       <c r="I187" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="188" spans="8:9" x14ac:dyDescent="0.15">
@@ -66802,7 +66802,7 @@
         <v>136</v>
       </c>
       <c r="I188" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="189" spans="8:9" x14ac:dyDescent="0.15">
@@ -66810,7 +66810,7 @@
         <v>137</v>
       </c>
       <c r="I189" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="190" spans="8:9" x14ac:dyDescent="0.15">
@@ -66818,7 +66818,7 @@
         <v>138</v>
       </c>
       <c r="I190" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="191" spans="8:9" x14ac:dyDescent="0.15">
@@ -66826,15 +66826,15 @@
         <v>981</v>
       </c>
       <c r="I191" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="192" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H192" s="7" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="I192" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="193" spans="8:9" x14ac:dyDescent="0.15">
@@ -66842,15 +66842,15 @@
         <v>862</v>
       </c>
       <c r="I193" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="194" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H194" s="7" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="I194" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="195" spans="8:9" x14ac:dyDescent="0.15">
@@ -66858,7 +66858,7 @@
         <v>347</v>
       </c>
       <c r="I195" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="196" spans="8:9" x14ac:dyDescent="0.15">
@@ -66866,7 +66866,7 @@
         <v>328</v>
       </c>
       <c r="I196" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="197" spans="8:9" x14ac:dyDescent="0.15">
@@ -66874,7 +66874,7 @@
         <v>829</v>
       </c>
       <c r="I197" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="198" spans="8:9" x14ac:dyDescent="0.15">
@@ -66882,7 +66882,7 @@
         <v>443</v>
       </c>
       <c r="I198" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="199" spans="8:9" x14ac:dyDescent="0.15">
@@ -66890,7 +66890,7 @@
         <v>444</v>
       </c>
       <c r="I199" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="200" spans="8:9" x14ac:dyDescent="0.15">
@@ -66898,7 +66898,7 @@
         <v>346</v>
       </c>
       <c r="I200" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="201" spans="8:9" x14ac:dyDescent="0.15">
@@ -66906,7 +66906,7 @@
         <v>352</v>
       </c>
       <c r="I201" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="202" spans="8:9" x14ac:dyDescent="0.15">
@@ -66914,7 +66914,7 @@
         <v>445</v>
       </c>
       <c r="I202" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="203" spans="8:9" x14ac:dyDescent="0.15">
@@ -66922,7 +66922,7 @@
         <v>446</v>
       </c>
       <c r="I203" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="204" spans="8:9" x14ac:dyDescent="0.15">
@@ -66930,7 +66930,7 @@
         <v>447</v>
       </c>
       <c r="I204" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="205" spans="8:9" x14ac:dyDescent="0.15">
@@ -66938,7 +66938,7 @@
         <v>448</v>
       </c>
       <c r="I205" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="206" spans="8:9" x14ac:dyDescent="0.15">
@@ -66946,7 +66946,7 @@
         <v>370</v>
       </c>
       <c r="I206" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="207" spans="8:9" x14ac:dyDescent="0.15">
@@ -66954,7 +66954,7 @@
         <v>449</v>
       </c>
       <c r="I207" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="208" spans="8:9" x14ac:dyDescent="0.15">
@@ -66962,7 +66962,7 @@
         <v>450</v>
       </c>
       <c r="I208" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="209" spans="8:9" x14ac:dyDescent="0.15">
@@ -66970,7 +66970,7 @@
         <v>357</v>
       </c>
       <c r="I209" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="210" spans="8:9" x14ac:dyDescent="0.15">
@@ -66978,7 +66978,7 @@
         <v>451</v>
       </c>
       <c r="I210" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="211" spans="8:9" x14ac:dyDescent="0.15">
@@ -66986,7 +66986,7 @@
         <v>452</v>
       </c>
       <c r="I211" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="212" spans="8:9" x14ac:dyDescent="0.15">
@@ -66994,7 +66994,7 @@
         <v>453</v>
       </c>
       <c r="I212" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="213" spans="8:9" x14ac:dyDescent="0.15">
@@ -67002,7 +67002,7 @@
         <v>454</v>
       </c>
       <c r="I213" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="214" spans="8:9" x14ac:dyDescent="0.15">
@@ -67010,7 +67010,7 @@
         <v>455</v>
       </c>
       <c r="I214" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="215" spans="8:9" x14ac:dyDescent="0.15">
@@ -67018,7 +67018,7 @@
         <v>360</v>
       </c>
       <c r="I215" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="216" spans="8:9" x14ac:dyDescent="0.15">
@@ -67026,7 +67026,7 @@
         <v>456</v>
       </c>
       <c r="I216" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="217" spans="8:9" x14ac:dyDescent="0.15">
@@ -67034,7 +67034,7 @@
         <v>457</v>
       </c>
       <c r="I217" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="218" spans="8:9" x14ac:dyDescent="0.15">
@@ -67042,7 +67042,7 @@
         <v>348</v>
       </c>
       <c r="I218" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="219" spans="8:9" x14ac:dyDescent="0.15">
@@ -67050,7 +67050,7 @@
         <v>369</v>
       </c>
       <c r="I219" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="220" spans="8:9" x14ac:dyDescent="0.15">
@@ -67058,7 +67058,7 @@
         <v>458</v>
       </c>
       <c r="I220" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="221" spans="8:9" x14ac:dyDescent="0.15">
@@ -67066,7 +67066,7 @@
         <v>459</v>
       </c>
       <c r="I221" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="222" spans="8:9" x14ac:dyDescent="0.15">
@@ -67074,7 +67074,7 @@
         <v>362</v>
       </c>
       <c r="I222" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="223" spans="8:9" x14ac:dyDescent="0.15">
@@ -67082,7 +67082,7 @@
         <v>361</v>
       </c>
       <c r="I223" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="224" spans="8:9" x14ac:dyDescent="0.15">
@@ -67090,7 +67090,7 @@
         <v>460</v>
       </c>
       <c r="I224" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="225" spans="8:9" x14ac:dyDescent="0.15">
@@ -67098,7 +67098,7 @@
         <v>461</v>
       </c>
       <c r="I225" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="226" spans="8:9" x14ac:dyDescent="0.15">
@@ -67106,7 +67106,7 @@
         <v>462</v>
       </c>
       <c r="I226" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="227" spans="8:9" x14ac:dyDescent="0.15">
@@ -67114,7 +67114,7 @@
         <v>463</v>
       </c>
       <c r="I227" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="228" spans="8:9" x14ac:dyDescent="0.15">
@@ -67122,7 +67122,7 @@
         <v>464</v>
       </c>
       <c r="I228" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="229" spans="8:9" x14ac:dyDescent="0.15">
@@ -67130,7 +67130,7 @@
         <v>465</v>
       </c>
       <c r="I229" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="230" spans="8:9" x14ac:dyDescent="0.15">
@@ -67138,7 +67138,7 @@
         <v>466</v>
       </c>
       <c r="I230" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="231" spans="8:9" x14ac:dyDescent="0.15">
@@ -67146,7 +67146,7 @@
         <v>350</v>
       </c>
       <c r="I231" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="232" spans="8:9" x14ac:dyDescent="0.15">
@@ -67154,7 +67154,7 @@
         <v>367</v>
       </c>
       <c r="I232" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="233" spans="8:9" x14ac:dyDescent="0.15">
@@ -67162,7 +67162,7 @@
         <v>467</v>
       </c>
       <c r="I233" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="234" spans="8:9" x14ac:dyDescent="0.15">
@@ -67170,7 +67170,7 @@
         <v>363</v>
       </c>
       <c r="I234" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="235" spans="8:9" x14ac:dyDescent="0.15">
@@ -67178,7 +67178,7 @@
         <v>365</v>
       </c>
       <c r="I235" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="236" spans="8:9" x14ac:dyDescent="0.15">
@@ -67186,7 +67186,7 @@
         <v>486</v>
       </c>
       <c r="I236" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="237" spans="8:9" x14ac:dyDescent="0.15">
@@ -67194,7 +67194,7 @@
         <v>468</v>
       </c>
       <c r="I237" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="238" spans="8:9" x14ac:dyDescent="0.15">
@@ -67202,7 +67202,7 @@
         <v>469</v>
       </c>
       <c r="I238" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="239" spans="8:9" x14ac:dyDescent="0.15">
@@ -67210,7 +67210,7 @@
         <v>371</v>
       </c>
       <c r="I239" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="240" spans="8:9" x14ac:dyDescent="0.15">
@@ -67218,7 +67218,7 @@
         <v>372</v>
       </c>
       <c r="I240" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="241" spans="8:9" x14ac:dyDescent="0.15">
@@ -67226,7 +67226,7 @@
         <v>470</v>
       </c>
       <c r="I241" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="242" spans="8:9" x14ac:dyDescent="0.15">
@@ -67234,7 +67234,7 @@
         <v>471</v>
       </c>
       <c r="I242" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="243" spans="8:9" x14ac:dyDescent="0.15">
@@ -67242,7 +67242,7 @@
         <v>472</v>
       </c>
       <c r="I243" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="244" spans="8:9" x14ac:dyDescent="0.15">
@@ -67250,7 +67250,7 @@
         <v>473</v>
       </c>
       <c r="I244" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="245" spans="8:9" x14ac:dyDescent="0.15">
@@ -67258,7 +67258,7 @@
         <v>364</v>
       </c>
       <c r="I245" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="246" spans="8:9" x14ac:dyDescent="0.15">
@@ -67266,7 +67266,7 @@
         <v>474</v>
       </c>
       <c r="I246" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="247" spans="8:9" x14ac:dyDescent="0.15">
@@ -67274,7 +67274,7 @@
         <v>475</v>
       </c>
       <c r="I247" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="248" spans="8:9" x14ac:dyDescent="0.15">
@@ -67282,7 +67282,7 @@
         <v>476</v>
       </c>
       <c r="I248" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="249" spans="8:9" x14ac:dyDescent="0.15">
@@ -67290,7 +67290,7 @@
         <v>477</v>
       </c>
       <c r="I249" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="250" spans="8:9" x14ac:dyDescent="0.15">
@@ -67298,7 +67298,7 @@
         <v>478</v>
       </c>
       <c r="I250" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="251" spans="8:9" x14ac:dyDescent="0.15">
@@ -67306,7 +67306,7 @@
         <v>366</v>
       </c>
       <c r="I251" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="252" spans="8:9" x14ac:dyDescent="0.15">
@@ -67314,7 +67314,7 @@
         <v>479</v>
       </c>
       <c r="I252" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="253" spans="8:9" x14ac:dyDescent="0.15">
@@ -67322,7 +67322,7 @@
         <v>480</v>
       </c>
       <c r="I253" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="254" spans="8:9" x14ac:dyDescent="0.15">
@@ -67330,7 +67330,7 @@
         <v>368</v>
       </c>
       <c r="I254" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="255" spans="8:9" x14ac:dyDescent="0.15">
@@ -67338,7 +67338,7 @@
         <v>481</v>
       </c>
       <c r="I255" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="256" spans="8:9" x14ac:dyDescent="0.15">
@@ -67346,7 +67346,7 @@
         <v>482</v>
       </c>
       <c r="I256" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="257" spans="8:9" x14ac:dyDescent="0.15">
@@ -67354,7 +67354,7 @@
         <v>483</v>
       </c>
       <c r="I257" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="258" spans="8:9" x14ac:dyDescent="0.15">
@@ -67362,7 +67362,7 @@
         <v>484</v>
       </c>
       <c r="I258" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="259" spans="8:9" x14ac:dyDescent="0.15">
@@ -67370,7 +67370,7 @@
         <v>485</v>
       </c>
       <c r="I259" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="260" spans="8:9" x14ac:dyDescent="0.15">
@@ -67378,7 +67378,7 @@
         <v>511</v>
       </c>
       <c r="I260" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="261" spans="8:9" x14ac:dyDescent="0.15">
@@ -67386,7 +67386,7 @@
         <v>508</v>
       </c>
       <c r="I261" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="262" spans="8:9" x14ac:dyDescent="0.15">
@@ -67394,7 +67394,7 @@
         <v>440</v>
       </c>
       <c r="I262" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="263" spans="8:9" x14ac:dyDescent="0.15">
@@ -67402,7 +67402,7 @@
         <v>555</v>
       </c>
       <c r="I263" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="264" spans="8:9" x14ac:dyDescent="0.15">
@@ -67410,7 +67410,7 @@
         <v>516</v>
       </c>
       <c r="I264" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="265" spans="8:9" x14ac:dyDescent="0.15">
@@ -67418,7 +67418,7 @@
         <v>356</v>
       </c>
       <c r="I265" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="266" spans="8:9" x14ac:dyDescent="0.15">
@@ -67426,7 +67426,7 @@
         <v>500</v>
       </c>
       <c r="I266" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="267" spans="8:9" x14ac:dyDescent="0.15">
@@ -67434,7 +67434,7 @@
         <v>359</v>
       </c>
       <c r="I267" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="268" spans="8:9" x14ac:dyDescent="0.15">
@@ -67442,7 +67442,7 @@
         <v>581</v>
       </c>
       <c r="I268" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="269" spans="8:9" x14ac:dyDescent="0.15">
@@ -67450,7 +67450,7 @@
         <v>526</v>
       </c>
       <c r="I269" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="270" spans="8:9" x14ac:dyDescent="0.15">
@@ -67458,7 +67458,7 @@
         <v>502</v>
       </c>
       <c r="I270" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="271" spans="8:9" x14ac:dyDescent="0.15">
@@ -67466,7 +67466,7 @@
         <v>489</v>
       </c>
       <c r="I271" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="272" spans="8:9" x14ac:dyDescent="0.15">
@@ -67474,7 +67474,7 @@
         <v>506</v>
       </c>
       <c r="I272" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="273" spans="8:9" x14ac:dyDescent="0.15">
@@ -67482,7 +67482,7 @@
         <v>554</v>
       </c>
       <c r="I273" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="274" spans="8:9" x14ac:dyDescent="0.15">
@@ -67490,7 +67490,7 @@
         <v>358</v>
       </c>
       <c r="I274" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="275" spans="8:9" x14ac:dyDescent="0.15">
@@ -67498,7 +67498,7 @@
         <v>507</v>
       </c>
       <c r="I275" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="276" spans="8:9" x14ac:dyDescent="0.15">
@@ -67506,7 +67506,7 @@
         <v>559</v>
       </c>
       <c r="I276" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="277" spans="8:9" x14ac:dyDescent="0.15">
@@ -67514,7 +67514,7 @@
         <v>557</v>
       </c>
       <c r="I277" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="278" spans="8:9" x14ac:dyDescent="0.15">
@@ -67522,7 +67522,7 @@
         <v>553</v>
       </c>
       <c r="I278" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="279" spans="8:9" x14ac:dyDescent="0.15">
@@ -67530,7 +67530,7 @@
         <v>513</v>
       </c>
       <c r="I279" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="280" spans="8:9" x14ac:dyDescent="0.15">
@@ -67538,7 +67538,7 @@
         <v>509</v>
       </c>
       <c r="I280" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="281" spans="8:9" x14ac:dyDescent="0.15">
@@ -67546,7 +67546,7 @@
         <v>556</v>
       </c>
       <c r="I281" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="282" spans="8:9" x14ac:dyDescent="0.15">
@@ -67554,7 +67554,7 @@
         <v>491</v>
       </c>
       <c r="I282" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="283" spans="8:9" x14ac:dyDescent="0.15">
@@ -67562,7 +67562,7 @@
         <v>558</v>
       </c>
       <c r="I283" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="284" spans="8:9" x14ac:dyDescent="0.15">
@@ -67570,7 +67570,7 @@
         <v>512</v>
       </c>
       <c r="I284" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="285" spans="8:9" x14ac:dyDescent="0.15">
@@ -67578,7 +67578,7 @@
         <v>515</v>
       </c>
       <c r="I285" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="286" spans="8:9" x14ac:dyDescent="0.15">
@@ -67586,7 +67586,7 @@
         <v>634</v>
       </c>
       <c r="I286" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="287" spans="8:9" x14ac:dyDescent="0.15">
@@ -67594,7 +67594,7 @@
         <v>622</v>
       </c>
       <c r="I287" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="288" spans="8:9" x14ac:dyDescent="0.15">
@@ -67602,7 +67602,7 @@
         <v>552</v>
       </c>
       <c r="I288" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="289" spans="8:9" x14ac:dyDescent="0.15">
@@ -67610,7 +67610,7 @@
         <v>522</v>
       </c>
       <c r="I289" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="290" spans="8:9" x14ac:dyDescent="0.15">
@@ -67618,7 +67618,7 @@
         <v>354</v>
       </c>
       <c r="I290" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="291" spans="8:9" x14ac:dyDescent="0.15">
@@ -67626,7 +67626,7 @@
         <v>714</v>
       </c>
       <c r="I291" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="292" spans="8:9" x14ac:dyDescent="0.15">
@@ -67634,15 +67634,15 @@
         <v>715</v>
       </c>
       <c r="I292" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="293" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H293" s="7" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="I293" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="294" spans="8:9" x14ac:dyDescent="0.15">
@@ -67650,7 +67650,7 @@
         <v>33</v>
       </c>
       <c r="I294" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="295" spans="8:9" x14ac:dyDescent="0.15">
@@ -67658,7 +67658,7 @@
         <v>921</v>
       </c>
       <c r="I295" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="296" spans="8:9" x14ac:dyDescent="0.15">
@@ -67666,7 +67666,7 @@
         <v>35</v>
       </c>
       <c r="I296" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="297" spans="8:9" x14ac:dyDescent="0.15">
@@ -67674,7 +67674,7 @@
         <v>36</v>
       </c>
       <c r="I297" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="298" spans="8:9" x14ac:dyDescent="0.15">
@@ -67682,7 +67682,7 @@
         <v>37</v>
       </c>
       <c r="I298" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="299" spans="8:9" x14ac:dyDescent="0.15">
@@ -67690,7 +67690,7 @@
         <v>38</v>
       </c>
       <c r="I299" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="300" spans="8:9" x14ac:dyDescent="0.15">
@@ -67698,7 +67698,7 @@
         <v>39</v>
       </c>
       <c r="I300" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="301" spans="8:9" x14ac:dyDescent="0.15">
@@ -67706,7 +67706,7 @@
         <v>23</v>
       </c>
       <c r="I301" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="302" spans="8:9" x14ac:dyDescent="0.15">
@@ -67714,7 +67714,7 @@
         <v>40</v>
       </c>
       <c r="I302" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="303" spans="8:9" x14ac:dyDescent="0.15">
@@ -67722,7 +67722,7 @@
         <v>41</v>
       </c>
       <c r="I303" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="304" spans="8:9" x14ac:dyDescent="0.15">
@@ -67730,7 +67730,7 @@
         <v>42</v>
       </c>
       <c r="I304" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="305" spans="8:9" x14ac:dyDescent="0.15">
@@ -67738,7 +67738,7 @@
         <v>53</v>
       </c>
       <c r="I305" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="306" spans="8:9" x14ac:dyDescent="0.15">
@@ -67746,7 +67746,7 @@
         <v>54</v>
       </c>
       <c r="I306" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="307" spans="8:9" x14ac:dyDescent="0.15">
@@ -67754,7 +67754,7 @@
         <v>44</v>
       </c>
       <c r="I307" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="308" spans="8:9" x14ac:dyDescent="0.15">
@@ -67762,7 +67762,7 @@
         <v>25</v>
       </c>
       <c r="I308" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="309" spans="8:9" x14ac:dyDescent="0.15">
@@ -67770,7 +67770,7 @@
         <v>45</v>
       </c>
       <c r="I309" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="310" spans="8:9" x14ac:dyDescent="0.15">
@@ -67778,7 +67778,7 @@
         <v>22</v>
       </c>
       <c r="I310" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="311" spans="8:9" x14ac:dyDescent="0.15">
@@ -67786,15 +67786,15 @@
         <v>43</v>
       </c>
       <c r="I311" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="312" spans="8:9" x14ac:dyDescent="0.15">
       <c r="H312" s="7" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="I312" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="313" spans="8:9" x14ac:dyDescent="0.15">
@@ -67802,7 +67802,7 @@
         <v>50</v>
       </c>
       <c r="I313" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="314" spans="8:9" x14ac:dyDescent="0.15">
@@ -67810,7 +67810,7 @@
         <v>24</v>
       </c>
       <c r="I314" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="315" spans="8:9" x14ac:dyDescent="0.15">
@@ -67818,7 +67818,7 @@
         <v>51</v>
       </c>
       <c r="I315" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="316" spans="8:9" x14ac:dyDescent="0.15">
@@ -67826,7 +67826,7 @@
         <v>52</v>
       </c>
       <c r="I316" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="317" spans="8:9" x14ac:dyDescent="0.15">
@@ -67834,7 +67834,7 @@
         <v>46</v>
       </c>
       <c r="I317" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="318" spans="8:9" x14ac:dyDescent="0.15">
@@ -67842,7 +67842,7 @@
         <v>47</v>
       </c>
       <c r="I318" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="319" spans="8:9" x14ac:dyDescent="0.15">
@@ -67850,7 +67850,7 @@
         <v>48</v>
       </c>
       <c r="I319" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="320" spans="8:9" x14ac:dyDescent="0.15">
@@ -67858,7 +67858,7 @@
         <v>49</v>
       </c>
       <c r="I320" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6721" uniqueCount="1829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6716" uniqueCount="1829">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -10631,7 +10631,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -10667,8 +10667,8 @@
       <c r="R15" s="36" t="s">
         <v>801</v>
       </c>
-      <c r="S15" s="36" t="s">
-        <v>803</v>
+      <c r="S15" s="36">
+        <v>50</v>
       </c>
       <c r="T15" s="36">
         <v>0</v>
@@ -10727,7 +10727,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -10763,8 +10763,8 @@
       <c r="R16" s="36" t="s">
         <v>801</v>
       </c>
-      <c r="S16" s="36" t="s">
-        <v>803</v>
+      <c r="S16" s="36">
+        <v>50</v>
       </c>
       <c r="T16" s="36">
         <v>0</v>
@@ -10823,7 +10823,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -10859,8 +10859,8 @@
       <c r="R17" s="36" t="s">
         <v>801</v>
       </c>
-      <c r="S17" s="36" t="s">
-        <v>803</v>
+      <c r="S17" s="36">
+        <v>50</v>
       </c>
       <c r="T17" s="36">
         <v>0</v>
@@ -10919,7 +10919,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -10955,8 +10955,8 @@
       <c r="R18" s="36" t="s">
         <v>801</v>
       </c>
-      <c r="S18" s="36" t="s">
-        <v>803</v>
+      <c r="S18" s="36">
+        <v>50</v>
       </c>
       <c r="T18" s="36">
         <v>0</v>
@@ -11015,7 +11015,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -11051,8 +11051,8 @@
       <c r="R19" s="36" t="s">
         <v>801</v>
       </c>
-      <c r="S19" s="36" t="s">
-        <v>803</v>
+      <c r="S19" s="36">
+        <v>50</v>
       </c>
       <c r="T19" s="36">
         <v>0</v>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -28,7 +28,7 @@
     <sheet name="鱼" sheetId="15" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$AH$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$AH$420</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet13!$Q$47:$Q$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet2!$B$5:$X$54</definedName>
   </definedNames>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6716" uniqueCount="1829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6748" uniqueCount="1829">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9337,7 +9337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:AI412"/>
+  <dimension ref="A2:AI420"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
@@ -48148,7 +48148,7 @@
         <v>0</v>
       </c>
       <c r="S395" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T395" s="36">
         <v>0</v>
@@ -48247,7 +48247,7 @@
         <v>0</v>
       </c>
       <c r="S396" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T396" s="36">
         <v>0</v>
@@ -48346,7 +48346,7 @@
         <v>0</v>
       </c>
       <c r="S397" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T397" s="36">
         <v>0</v>
@@ -48445,7 +48445,7 @@
         <v>0</v>
       </c>
       <c r="S398" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T398" s="36">
         <v>0</v>
@@ -48544,7 +48544,7 @@
         <v>0</v>
       </c>
       <c r="S399" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T399" s="36">
         <v>0</v>
@@ -48643,7 +48643,7 @@
         <v>0</v>
       </c>
       <c r="S400" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T400" s="36">
         <v>0</v>
@@ -48742,7 +48742,7 @@
         <v>0</v>
       </c>
       <c r="S401" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T401" s="36">
         <v>0</v>
@@ -48791,20 +48791,20 @@
       </c>
     </row>
     <row r="402" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A402" s="12" t="s">
-        <v>623</v>
+      <c r="A402" s="1" t="s">
+        <v>935</v>
       </c>
       <c r="B402" s="1">
-        <v>5000</v>
-      </c>
-      <c r="C402" s="12" t="s">
-        <v>623</v>
+        <v>3507</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>935</v>
       </c>
       <c r="D402" s="1">
-        <v>5</v>
-      </c>
-      <c r="E402" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E402" s="7">
+        <v>3100</v>
       </c>
       <c r="F402" s="1">
         <v>0</v>
@@ -48831,16 +48831,17 @@
         <v>1</v>
       </c>
       <c r="N402" s="39">
-        <v>100</v>
+        <f t="shared" ref="N402:N409" si="17">O402*2</f>
+        <v>4110</v>
       </c>
       <c r="O402" s="39">
-        <v>100</v>
+        <v>2055</v>
       </c>
       <c r="R402" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S402" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T402" s="36">
         <v>0</v>
@@ -48882,27 +48883,24 @@
         <v>0</v>
       </c>
       <c r="AH402" s="1" t="s">
-        <v>1501</v>
-      </c>
-      <c r="AI402" s="1" t="s">
-        <v>636</v>
+        <v>935</v>
       </c>
     </row>
     <row r="403" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A403" s="12" t="s">
-        <v>624</v>
+      <c r="A403" s="1" t="s">
+        <v>936</v>
       </c>
       <c r="B403" s="1">
-        <v>5001</v>
-      </c>
-      <c r="C403" s="12" t="s">
-        <v>624</v>
+        <v>3508</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>936</v>
       </c>
       <c r="D403" s="1">
-        <v>5</v>
-      </c>
-      <c r="E403" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E403" s="7">
+        <v>3102</v>
       </c>
       <c r="F403" s="1">
         <v>0</v>
@@ -48929,16 +48927,17 @@
         <v>1</v>
       </c>
       <c r="N403" s="39">
-        <v>100</v>
+        <f t="shared" si="17"/>
+        <v>5180</v>
       </c>
       <c r="O403" s="39">
-        <v>100</v>
+        <v>2590</v>
       </c>
       <c r="R403" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S403" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T403" s="36">
         <v>0</v>
@@ -48980,27 +48979,24 @@
         <v>0</v>
       </c>
       <c r="AH403" s="1" t="s">
-        <v>1503</v>
-      </c>
-      <c r="AI403" s="1" t="s">
-        <v>636</v>
+        <v>936</v>
       </c>
     </row>
     <row r="404" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A404" s="12" t="s">
-        <v>625</v>
+      <c r="A404" s="1" t="s">
+        <v>937</v>
       </c>
       <c r="B404" s="1">
-        <v>5002</v>
-      </c>
-      <c r="C404" s="12" t="s">
-        <v>625</v>
+        <v>3509</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>937</v>
       </c>
       <c r="D404" s="1">
-        <v>5</v>
-      </c>
-      <c r="E404" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E404" s="7">
+        <v>3104</v>
       </c>
       <c r="F404" s="1">
         <v>0</v>
@@ -49027,16 +49023,17 @@
         <v>1</v>
       </c>
       <c r="N404" s="39">
-        <v>100</v>
+        <f t="shared" si="17"/>
+        <v>6250</v>
       </c>
       <c r="O404" s="39">
-        <v>100</v>
+        <v>3125</v>
       </c>
       <c r="R404" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S404" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T404" s="36">
         <v>0</v>
@@ -49078,27 +49075,24 @@
         <v>0</v>
       </c>
       <c r="AH404" s="1" t="s">
-        <v>1505</v>
-      </c>
-      <c r="AI404" s="1" t="s">
-        <v>636</v>
+        <v>937</v>
       </c>
     </row>
     <row r="405" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A405" s="12" t="s">
-        <v>626</v>
+      <c r="A405" s="1" t="s">
+        <v>938</v>
       </c>
       <c r="B405" s="1">
-        <v>5003</v>
-      </c>
-      <c r="C405" s="12" t="s">
-        <v>626</v>
+        <v>3510</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>938</v>
       </c>
       <c r="D405" s="1">
-        <v>5</v>
-      </c>
-      <c r="E405" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E405" s="7">
+        <v>3106</v>
       </c>
       <c r="F405" s="1">
         <v>0</v>
@@ -49125,16 +49119,17 @@
         <v>1</v>
       </c>
       <c r="N405" s="39">
-        <v>100</v>
+        <f t="shared" si="17"/>
+        <v>7320</v>
       </c>
       <c r="O405" s="39">
-        <v>100</v>
+        <v>3660</v>
       </c>
       <c r="R405" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S405" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T405" s="36">
         <v>0</v>
@@ -49176,27 +49171,24 @@
         <v>0</v>
       </c>
       <c r="AH405" s="1" t="s">
-        <v>1507</v>
-      </c>
-      <c r="AI405" s="1" t="s">
-        <v>636</v>
+        <v>938</v>
       </c>
     </row>
     <row r="406" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A406" s="12" t="s">
-        <v>627</v>
+      <c r="A406" s="1" t="s">
+        <v>939</v>
       </c>
       <c r="B406" s="1">
-        <v>5004</v>
-      </c>
-      <c r="C406" s="12" t="s">
-        <v>627</v>
+        <v>3511</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>939</v>
       </c>
       <c r="D406" s="1">
-        <v>5</v>
-      </c>
-      <c r="E406" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E406" s="7">
+        <v>3108</v>
       </c>
       <c r="F406" s="1">
         <v>0</v>
@@ -49223,16 +49215,17 @@
         <v>1</v>
       </c>
       <c r="N406" s="39">
-        <v>100</v>
+        <f t="shared" si="17"/>
+        <v>8390</v>
       </c>
       <c r="O406" s="39">
-        <v>100</v>
+        <v>4195</v>
       </c>
       <c r="R406" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S406" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T406" s="36">
         <v>0</v>
@@ -49274,27 +49267,24 @@
         <v>0</v>
       </c>
       <c r="AH406" s="1" t="s">
-        <v>1509</v>
-      </c>
-      <c r="AI406" s="1" t="s">
-        <v>636</v>
+        <v>939</v>
       </c>
     </row>
     <row r="407" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A407" s="12" t="s">
-        <v>628</v>
+      <c r="A407" s="1" t="s">
+        <v>940</v>
       </c>
       <c r="B407" s="1">
-        <v>5005</v>
-      </c>
-      <c r="C407" s="12" t="s">
-        <v>628</v>
+        <v>3512</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>940</v>
       </c>
       <c r="D407" s="1">
-        <v>5</v>
-      </c>
-      <c r="E407" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E407" s="7">
+        <v>3110</v>
       </c>
       <c r="F407" s="1">
         <v>0</v>
@@ -49321,16 +49311,17 @@
         <v>1</v>
       </c>
       <c r="N407" s="39">
-        <v>100</v>
+        <f t="shared" si="17"/>
+        <v>9460</v>
       </c>
       <c r="O407" s="39">
-        <v>100</v>
+        <v>4730</v>
       </c>
       <c r="R407" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S407" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T407" s="36">
         <v>0</v>
@@ -49372,27 +49363,24 @@
         <v>0</v>
       </c>
       <c r="AH407" s="1" t="s">
-        <v>1511</v>
-      </c>
-      <c r="AI407" s="1" t="s">
-        <v>636</v>
+        <v>940</v>
       </c>
     </row>
     <row r="408" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A408" s="12" t="s">
-        <v>629</v>
+      <c r="A408" s="1" t="s">
+        <v>941</v>
       </c>
       <c r="B408" s="1">
-        <v>5006</v>
-      </c>
-      <c r="C408" s="12" t="s">
-        <v>629</v>
+        <v>3513</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>941</v>
       </c>
       <c r="D408" s="1">
-        <v>5</v>
-      </c>
-      <c r="E408" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E408" s="7">
+        <v>3112</v>
       </c>
       <c r="F408" s="1">
         <v>0</v>
@@ -49419,16 +49407,17 @@
         <v>1</v>
       </c>
       <c r="N408" s="39">
-        <v>100</v>
+        <f t="shared" si="17"/>
+        <v>10530</v>
       </c>
       <c r="O408" s="39">
-        <v>100</v>
+        <v>5265</v>
       </c>
       <c r="R408" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S408" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T408" s="36">
         <v>0</v>
@@ -49470,27 +49459,24 @@
         <v>0</v>
       </c>
       <c r="AH408" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="AI408" s="1" t="s">
-        <v>636</v>
+        <v>941</v>
       </c>
     </row>
     <row r="409" spans="1:35" x14ac:dyDescent="0.15">
-      <c r="A409" s="12" t="s">
-        <v>630</v>
+      <c r="A409" s="1" t="s">
+        <v>942</v>
       </c>
       <c r="B409" s="1">
-        <v>5007</v>
-      </c>
-      <c r="C409" s="12" t="s">
-        <v>630</v>
+        <v>3514</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>942</v>
       </c>
       <c r="D409" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E409" s="1">
-        <v>0</v>
+        <v>3114</v>
       </c>
       <c r="F409" s="1">
         <v>0</v>
@@ -49517,16 +49503,17 @@
         <v>1</v>
       </c>
       <c r="N409" s="39">
-        <v>100</v>
+        <f t="shared" si="17"/>
+        <v>11600</v>
       </c>
       <c r="O409" s="39">
-        <v>100</v>
+        <v>5800</v>
       </c>
       <c r="R409" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S409" s="36">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T409" s="36">
         <v>0</v>
@@ -49568,21 +49555,18 @@
         <v>0</v>
       </c>
       <c r="AH409" s="1" t="s">
-        <v>1515</v>
-      </c>
-      <c r="AI409" s="1" t="s">
-        <v>636</v>
+        <v>942</v>
       </c>
     </row>
     <row r="410" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A410" s="12" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B410" s="1">
-        <v>5008</v>
+        <v>5000</v>
       </c>
       <c r="C410" s="12" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="D410" s="1">
         <v>5</v>
@@ -49666,7 +49650,7 @@
         <v>0</v>
       </c>
       <c r="AH410" s="1" t="s">
-        <v>1517</v>
+        <v>1501</v>
       </c>
       <c r="AI410" s="1" t="s">
         <v>636</v>
@@ -49674,13 +49658,13 @@
     </row>
     <row r="411" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A411" s="12" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B411" s="1">
-        <v>5009</v>
+        <v>5001</v>
       </c>
       <c r="C411" s="12" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="D411" s="1">
         <v>5</v>
@@ -49764,7 +49748,7 @@
         <v>0</v>
       </c>
       <c r="AH411" s="1" t="s">
-        <v>1519</v>
+        <v>1503</v>
       </c>
       <c r="AI411" s="1" t="s">
         <v>636</v>
@@ -49772,13 +49756,13 @@
     </row>
     <row r="412" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A412" s="12" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B412" s="1">
-        <v>5010</v>
+        <v>5002</v>
       </c>
       <c r="C412" s="12" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="D412" s="1">
         <v>5</v>
@@ -49862,16 +49846,800 @@
         <v>0</v>
       </c>
       <c r="AH412" s="1" t="s">
-        <v>1521</v>
+        <v>1505</v>
       </c>
       <c r="AI412" s="1" t="s">
         <v>636</v>
       </c>
     </row>
+    <row r="413" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A413" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="B413" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C413" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="D413" s="1">
+        <v>5</v>
+      </c>
+      <c r="E413" s="1">
+        <v>0</v>
+      </c>
+      <c r="F413" s="1">
+        <v>0</v>
+      </c>
+      <c r="G413" s="1">
+        <v>0</v>
+      </c>
+      <c r="H413" s="1">
+        <v>1</v>
+      </c>
+      <c r="I413" s="1">
+        <v>0</v>
+      </c>
+      <c r="J413" s="1">
+        <v>0</v>
+      </c>
+      <c r="K413" s="1">
+        <v>0</v>
+      </c>
+      <c r="L413" s="1">
+        <v>1</v>
+      </c>
+      <c r="M413" s="1">
+        <v>1</v>
+      </c>
+      <c r="N413" s="39">
+        <v>100</v>
+      </c>
+      <c r="O413" s="39">
+        <v>100</v>
+      </c>
+      <c r="R413" s="36">
+        <v>1</v>
+      </c>
+      <c r="S413" s="36">
+        <v>0</v>
+      </c>
+      <c r="T413" s="36">
+        <v>0</v>
+      </c>
+      <c r="V413" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W413" s="1">
+        <v>0</v>
+      </c>
+      <c r="X413" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y413" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG413" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH413" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="AI413" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="414" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A414" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="B414" s="1">
+        <v>5004</v>
+      </c>
+      <c r="C414" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="D414" s="1">
+        <v>5</v>
+      </c>
+      <c r="E414" s="1">
+        <v>0</v>
+      </c>
+      <c r="F414" s="1">
+        <v>0</v>
+      </c>
+      <c r="G414" s="1">
+        <v>0</v>
+      </c>
+      <c r="H414" s="1">
+        <v>1</v>
+      </c>
+      <c r="I414" s="1">
+        <v>0</v>
+      </c>
+      <c r="J414" s="1">
+        <v>0</v>
+      </c>
+      <c r="K414" s="1">
+        <v>0</v>
+      </c>
+      <c r="L414" s="1">
+        <v>1</v>
+      </c>
+      <c r="M414" s="1">
+        <v>1</v>
+      </c>
+      <c r="N414" s="39">
+        <v>100</v>
+      </c>
+      <c r="O414" s="39">
+        <v>100</v>
+      </c>
+      <c r="R414" s="36">
+        <v>1</v>
+      </c>
+      <c r="S414" s="36">
+        <v>0</v>
+      </c>
+      <c r="T414" s="36">
+        <v>0</v>
+      </c>
+      <c r="V414" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W414" s="1">
+        <v>0</v>
+      </c>
+      <c r="X414" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y414" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG414" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH414" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="AI414" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="415" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A415" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B415" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C415" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="D415" s="1">
+        <v>5</v>
+      </c>
+      <c r="E415" s="1">
+        <v>0</v>
+      </c>
+      <c r="F415" s="1">
+        <v>0</v>
+      </c>
+      <c r="G415" s="1">
+        <v>0</v>
+      </c>
+      <c r="H415" s="1">
+        <v>1</v>
+      </c>
+      <c r="I415" s="1">
+        <v>0</v>
+      </c>
+      <c r="J415" s="1">
+        <v>0</v>
+      </c>
+      <c r="K415" s="1">
+        <v>0</v>
+      </c>
+      <c r="L415" s="1">
+        <v>1</v>
+      </c>
+      <c r="M415" s="1">
+        <v>1</v>
+      </c>
+      <c r="N415" s="39">
+        <v>100</v>
+      </c>
+      <c r="O415" s="39">
+        <v>100</v>
+      </c>
+      <c r="R415" s="36">
+        <v>1</v>
+      </c>
+      <c r="S415" s="36">
+        <v>0</v>
+      </c>
+      <c r="T415" s="36">
+        <v>0</v>
+      </c>
+      <c r="V415" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W415" s="1">
+        <v>0</v>
+      </c>
+      <c r="X415" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y415" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG415" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH415" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="AI415" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="416" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A416" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="B416" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C416" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="D416" s="1">
+        <v>5</v>
+      </c>
+      <c r="E416" s="1">
+        <v>0</v>
+      </c>
+      <c r="F416" s="1">
+        <v>0</v>
+      </c>
+      <c r="G416" s="1">
+        <v>0</v>
+      </c>
+      <c r="H416" s="1">
+        <v>1</v>
+      </c>
+      <c r="I416" s="1">
+        <v>0</v>
+      </c>
+      <c r="J416" s="1">
+        <v>0</v>
+      </c>
+      <c r="K416" s="1">
+        <v>0</v>
+      </c>
+      <c r="L416" s="1">
+        <v>1</v>
+      </c>
+      <c r="M416" s="1">
+        <v>1</v>
+      </c>
+      <c r="N416" s="39">
+        <v>100</v>
+      </c>
+      <c r="O416" s="39">
+        <v>100</v>
+      </c>
+      <c r="R416" s="36">
+        <v>1</v>
+      </c>
+      <c r="S416" s="36">
+        <v>0</v>
+      </c>
+      <c r="T416" s="36">
+        <v>0</v>
+      </c>
+      <c r="V416" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W416" s="1">
+        <v>0</v>
+      </c>
+      <c r="X416" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y416" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG416" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH416" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="AI416" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="417" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A417" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="B417" s="1">
+        <v>5007</v>
+      </c>
+      <c r="C417" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="D417" s="1">
+        <v>5</v>
+      </c>
+      <c r="E417" s="1">
+        <v>0</v>
+      </c>
+      <c r="F417" s="1">
+        <v>0</v>
+      </c>
+      <c r="G417" s="1">
+        <v>0</v>
+      </c>
+      <c r="H417" s="1">
+        <v>1</v>
+      </c>
+      <c r="I417" s="1">
+        <v>0</v>
+      </c>
+      <c r="J417" s="1">
+        <v>0</v>
+      </c>
+      <c r="K417" s="1">
+        <v>0</v>
+      </c>
+      <c r="L417" s="1">
+        <v>1</v>
+      </c>
+      <c r="M417" s="1">
+        <v>1</v>
+      </c>
+      <c r="N417" s="39">
+        <v>100</v>
+      </c>
+      <c r="O417" s="39">
+        <v>100</v>
+      </c>
+      <c r="R417" s="36">
+        <v>1</v>
+      </c>
+      <c r="S417" s="36">
+        <v>0</v>
+      </c>
+      <c r="T417" s="36">
+        <v>0</v>
+      </c>
+      <c r="V417" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W417" s="1">
+        <v>0</v>
+      </c>
+      <c r="X417" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y417" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG417" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH417" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="AI417" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="418" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A418" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="B418" s="1">
+        <v>5008</v>
+      </c>
+      <c r="C418" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="D418" s="1">
+        <v>5</v>
+      </c>
+      <c r="E418" s="1">
+        <v>0</v>
+      </c>
+      <c r="F418" s="1">
+        <v>0</v>
+      </c>
+      <c r="G418" s="1">
+        <v>0</v>
+      </c>
+      <c r="H418" s="1">
+        <v>1</v>
+      </c>
+      <c r="I418" s="1">
+        <v>0</v>
+      </c>
+      <c r="J418" s="1">
+        <v>0</v>
+      </c>
+      <c r="K418" s="1">
+        <v>0</v>
+      </c>
+      <c r="L418" s="1">
+        <v>1</v>
+      </c>
+      <c r="M418" s="1">
+        <v>1</v>
+      </c>
+      <c r="N418" s="39">
+        <v>100</v>
+      </c>
+      <c r="O418" s="39">
+        <v>100</v>
+      </c>
+      <c r="R418" s="36">
+        <v>1</v>
+      </c>
+      <c r="S418" s="36">
+        <v>0</v>
+      </c>
+      <c r="T418" s="36">
+        <v>0</v>
+      </c>
+      <c r="V418" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W418" s="1">
+        <v>0</v>
+      </c>
+      <c r="X418" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y418" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG418" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH418" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="AI418" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="419" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A419" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="B419" s="1">
+        <v>5009</v>
+      </c>
+      <c r="C419" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="D419" s="1">
+        <v>5</v>
+      </c>
+      <c r="E419" s="1">
+        <v>0</v>
+      </c>
+      <c r="F419" s="1">
+        <v>0</v>
+      </c>
+      <c r="G419" s="1">
+        <v>0</v>
+      </c>
+      <c r="H419" s="1">
+        <v>1</v>
+      </c>
+      <c r="I419" s="1">
+        <v>0</v>
+      </c>
+      <c r="J419" s="1">
+        <v>0</v>
+      </c>
+      <c r="K419" s="1">
+        <v>0</v>
+      </c>
+      <c r="L419" s="1">
+        <v>1</v>
+      </c>
+      <c r="M419" s="1">
+        <v>1</v>
+      </c>
+      <c r="N419" s="39">
+        <v>100</v>
+      </c>
+      <c r="O419" s="39">
+        <v>100</v>
+      </c>
+      <c r="R419" s="36">
+        <v>1</v>
+      </c>
+      <c r="S419" s="36">
+        <v>0</v>
+      </c>
+      <c r="T419" s="36">
+        <v>0</v>
+      </c>
+      <c r="V419" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W419" s="1">
+        <v>0</v>
+      </c>
+      <c r="X419" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y419" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG419" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH419" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AI419" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="420" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="A420" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B420" s="1">
+        <v>5010</v>
+      </c>
+      <c r="C420" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="D420" s="1">
+        <v>5</v>
+      </c>
+      <c r="E420" s="1">
+        <v>0</v>
+      </c>
+      <c r="F420" s="1">
+        <v>0</v>
+      </c>
+      <c r="G420" s="1">
+        <v>0</v>
+      </c>
+      <c r="H420" s="1">
+        <v>1</v>
+      </c>
+      <c r="I420" s="1">
+        <v>0</v>
+      </c>
+      <c r="J420" s="1">
+        <v>0</v>
+      </c>
+      <c r="K420" s="1">
+        <v>0</v>
+      </c>
+      <c r="L420" s="1">
+        <v>1</v>
+      </c>
+      <c r="M420" s="1">
+        <v>1</v>
+      </c>
+      <c r="N420" s="39">
+        <v>100</v>
+      </c>
+      <c r="O420" s="39">
+        <v>100</v>
+      </c>
+      <c r="R420" s="36">
+        <v>1</v>
+      </c>
+      <c r="S420" s="36">
+        <v>0</v>
+      </c>
+      <c r="T420" s="36">
+        <v>0</v>
+      </c>
+      <c r="V420" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="W420" s="1">
+        <v>0</v>
+      </c>
+      <c r="X420" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y420" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG420" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH420" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="AI420" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:AH412"/>
+  <autoFilter ref="A3:AH420"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A402:A1048576 A1:A64 A66:A255 A258:A394">
+  <conditionalFormatting sqref="A410:A1048576 A1:A64 A66:A255 A258:A394">
     <cfRule type="duplicateValues" dxfId="34" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65">
@@ -49880,7 +50648,7 @@
   <conditionalFormatting sqref="C10:C12">
     <cfRule type="duplicateValues" dxfId="32" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C402:C412">
+  <conditionalFormatting sqref="C410:C420">
     <cfRule type="duplicateValues" dxfId="31" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C88:C121">
@@ -69008,11 +69776,11 @@
         <v>3.75</v>
       </c>
       <c r="S6" s="12">
-        <f>VLOOKUP(K6,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K6,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="T6" s="12">
-        <f>VLOOKUP(M6,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M6,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U6" s="12"/>
@@ -69070,15 +69838,15 @@
         <v>8</v>
       </c>
       <c r="S7" s="12">
-        <f>VLOOKUP(K7,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K7,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T7" s="12">
-        <f>VLOOKUP(M7,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M7,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>220</v>
       </c>
       <c r="U7" s="12">
-        <f>VLOOKUP(O7,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O7,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>257</v>
       </c>
       <c r="V7" s="12"/>
@@ -69142,19 +69910,19 @@
         <v>0</v>
       </c>
       <c r="S8" s="12">
-        <f>VLOOKUP(K8,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K8,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T8" s="12">
-        <f>VLOOKUP(M8,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M8,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>229</v>
       </c>
       <c r="U8" s="12">
-        <f>VLOOKUP(O8,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O8,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>205</v>
       </c>
       <c r="V8" s="12">
-        <f>VLOOKUP(Q8,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q8,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>284</v>
       </c>
       <c r="X8" s="12" t="str">
@@ -69217,19 +69985,19 @@
         <v>0</v>
       </c>
       <c r="S9" s="12">
-        <f>VLOOKUP(K9,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K9,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T9" s="12">
-        <f>VLOOKUP(M9,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M9,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>218</v>
       </c>
       <c r="U9" s="12">
-        <f>VLOOKUP(O9,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O9,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V9" s="12">
-        <f>VLOOKUP(Q9,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q9,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>212</v>
       </c>
       <c r="X9" s="12" t="str">
@@ -69289,19 +70057,19 @@
         <v>0</v>
       </c>
       <c r="S10" s="12">
-        <f>VLOOKUP(K10,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K10,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1600</v>
       </c>
       <c r="T10" s="12">
-        <f>VLOOKUP(M10,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M10,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>260</v>
       </c>
       <c r="U10" s="12">
-        <f>VLOOKUP(O10,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O10,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>261</v>
       </c>
       <c r="V10" s="12">
-        <f>VLOOKUP(Q10,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q10,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>253</v>
       </c>
       <c r="X10" s="12" t="str">
@@ -69352,15 +70120,15 @@
         <v>3.75</v>
       </c>
       <c r="S11" s="12">
-        <f>VLOOKUP(K11,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K11,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>104</v>
       </c>
       <c r="T11" s="12">
-        <f>VLOOKUP(M11,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M11,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>222</v>
       </c>
       <c r="U11" s="12">
-        <f>VLOOKUP(O11,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O11,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="V11" s="12"/>
@@ -69422,19 +70190,19 @@
         <v>0</v>
       </c>
       <c r="S12" s="12">
-        <f>VLOOKUP(K12,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K12,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="T12" s="12">
-        <f>VLOOKUP(M12,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M12,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>259</v>
       </c>
       <c r="U12" s="12">
-        <f>VLOOKUP(O12,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O12,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>237</v>
       </c>
       <c r="V12" s="12">
-        <f>VLOOKUP(Q12,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q12,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>239</v>
       </c>
       <c r="X12" s="12" t="str">
@@ -69487,15 +70255,15 @@
         <v>5</v>
       </c>
       <c r="S13" s="12">
-        <f>VLOOKUP(K13,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K13,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="T13" s="12">
-        <f>VLOOKUP(M13,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M13,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>275</v>
       </c>
       <c r="U13" s="12">
-        <f>VLOOKUP(O13,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O13,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V13" s="12"/>
@@ -69556,19 +70324,19 @@
         <v>0</v>
       </c>
       <c r="S14" s="12">
-        <f>VLOOKUP(K14,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K14,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="T14" s="12">
-        <f>VLOOKUP(M14,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M14,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>227</v>
       </c>
       <c r="U14" s="12">
-        <f>VLOOKUP(O14,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O14,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>240</v>
       </c>
       <c r="V14" s="12">
-        <f>VLOOKUP(Q14,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q14,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="X14" s="12" t="str">
@@ -69628,19 +70396,19 @@
         <v>0</v>
       </c>
       <c r="S15" s="12">
-        <f>VLOOKUP(K15,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K15,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>237</v>
       </c>
       <c r="T15" s="12">
-        <f>VLOOKUP(M15,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M15,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U15" s="12">
-        <f>VLOOKUP(O15,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O15,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>256</v>
       </c>
       <c r="V15" s="12">
-        <f>VLOOKUP(Q15,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q15,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>285</v>
       </c>
       <c r="X15" s="12" t="str">
@@ -69700,19 +70468,19 @@
         <v>0</v>
       </c>
       <c r="S16" s="12">
-        <f>VLOOKUP(K16,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K16,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>269</v>
       </c>
       <c r="T16" s="12">
-        <f>VLOOKUP(M16,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M16,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1605</v>
       </c>
       <c r="U16" s="12">
-        <f>VLOOKUP(O16,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O16,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>264</v>
       </c>
       <c r="V16" s="12">
-        <f>VLOOKUP(Q16,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q16,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>208</v>
       </c>
       <c r="X16" s="12" t="str">
@@ -69763,15 +70531,15 @@
         <v>0</v>
       </c>
       <c r="S17" s="12">
-        <f>VLOOKUP(K17,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K17,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="T17" s="12">
-        <f>VLOOKUP(M17,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M17,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U17" s="12">
-        <f>VLOOKUP(O17,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O17,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>241</v>
       </c>
       <c r="V17" s="12"/>
@@ -69825,15 +70593,15 @@
         <v>0</v>
       </c>
       <c r="S18" s="12">
-        <f>VLOOKUP(K18,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K18,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1609</v>
       </c>
       <c r="T18" s="12">
-        <f>VLOOKUP(M18,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M18,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>254</v>
       </c>
       <c r="U18" s="12">
-        <f>VLOOKUP(O18,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O18,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>211</v>
       </c>
       <c r="V18" s="12"/>
@@ -69894,19 +70662,19 @@
         <v>0</v>
       </c>
       <c r="S19" s="12">
-        <f>VLOOKUP(K19,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K19,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1609</v>
       </c>
       <c r="T19" s="12">
-        <f>VLOOKUP(M19,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M19,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>259</v>
       </c>
       <c r="U19" s="12">
-        <f>VLOOKUP(O19,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O19,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>258</v>
       </c>
       <c r="V19" s="12">
-        <f>VLOOKUP(Q19,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q19,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>263</v>
       </c>
       <c r="X19" s="12" t="str">
@@ -69966,19 +70734,19 @@
         <v>0</v>
       </c>
       <c r="S20" s="12">
-        <f>VLOOKUP(K20,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K20,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1609</v>
       </c>
       <c r="T20" s="12">
-        <f>VLOOKUP(M20,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M20,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>253</v>
       </c>
       <c r="U20" s="12">
-        <f>VLOOKUP(O20,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O20,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>260</v>
       </c>
       <c r="V20" s="12">
-        <f>VLOOKUP(Q20,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q20,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>267</v>
       </c>
       <c r="X20" s="12" t="str">
@@ -70029,15 +70797,15 @@
         <v>0</v>
       </c>
       <c r="S21" s="12">
-        <f>VLOOKUP(K21,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K21,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>238</v>
       </c>
       <c r="T21" s="12">
-        <f>VLOOKUP(M21,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M21,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>276</v>
       </c>
       <c r="U21" s="12">
-        <f>VLOOKUP(O21,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O21,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="V21" s="12"/>
@@ -70089,15 +70857,15 @@
         <v>0</v>
       </c>
       <c r="S22" s="12">
-        <f>VLOOKUP(K22,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K22,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>221</v>
       </c>
       <c r="T22" s="12">
-        <f>VLOOKUP(M22,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M22,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>276</v>
       </c>
       <c r="U22" s="12">
-        <f>VLOOKUP(O22,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O22,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="V22" s="12"/>
@@ -70151,15 +70919,15 @@
         <v>0</v>
       </c>
       <c r="S23" s="34">
-        <f>VLOOKUP(K23,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K23,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1613</v>
       </c>
       <c r="T23" s="12">
-        <f>VLOOKUP(M23,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M23,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>213</v>
       </c>
       <c r="U23" s="12">
-        <f>VLOOKUP(O23,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O23,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>246</v>
       </c>
       <c r="V23" s="12"/>
@@ -70213,15 +70981,15 @@
         <v>16.5</v>
       </c>
       <c r="S24" s="34">
-        <f>VLOOKUP(K24,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K24,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1612</v>
       </c>
       <c r="T24" s="12">
-        <f>VLOOKUP(M24,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M24,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>211</v>
       </c>
       <c r="U24" s="12">
-        <f>VLOOKUP(O24,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O24,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1612</v>
       </c>
       <c r="V24" s="12"/>
@@ -70282,19 +71050,19 @@
         <v>49.5</v>
       </c>
       <c r="S25" s="12">
-        <f>VLOOKUP(K25,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K25,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>270</v>
       </c>
       <c r="T25" s="12">
-        <f>VLOOKUP(M25,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M25,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>225</v>
       </c>
       <c r="U25" s="12">
-        <f>VLOOKUP(O25,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O25,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>239</v>
       </c>
       <c r="V25" s="12">
-        <f>VLOOKUP(Q25,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q25,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1614</v>
       </c>
       <c r="X25" s="12" t="str">
@@ -70354,19 +71122,19 @@
         <v>43.5</v>
       </c>
       <c r="S26" s="12">
-        <f>VLOOKUP(K26,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K26,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>245</v>
       </c>
       <c r="T26" s="12">
-        <f>VLOOKUP(M26,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M26,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>255</v>
       </c>
       <c r="U26" s="12">
-        <f>VLOOKUP(O26,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O26,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>268</v>
       </c>
       <c r="V26" s="12">
-        <f>VLOOKUP(Q26,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q26,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1615</v>
       </c>
       <c r="X26" s="12" t="str">
@@ -70410,11 +71178,11 @@
         <v>2</v>
       </c>
       <c r="S27" s="12">
-        <f>VLOOKUP(K27,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K27,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T27" s="12">
-        <f>VLOOKUP(M27,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M27,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>277</v>
       </c>
       <c r="U27" s="12"/>
@@ -70467,15 +71235,15 @@
         <v>0</v>
       </c>
       <c r="S28" s="12">
-        <f>VLOOKUP(K28,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K28,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="T28" s="12">
-        <f>VLOOKUP(M28,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M28,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="U28" s="12">
-        <f>VLOOKUP(O28,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O28,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="V28" s="12"/>
@@ -70527,15 +71295,15 @@
         <v>5</v>
       </c>
       <c r="S29" s="12">
-        <f>VLOOKUP(K29,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K29,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1651</v>
       </c>
       <c r="T29" s="12">
-        <f>VLOOKUP(M29,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M29,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>227</v>
       </c>
       <c r="U29" s="12">
-        <f>VLOOKUP(O29,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O29,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V29" s="12"/>
@@ -70587,15 +71355,15 @@
         <v>0</v>
       </c>
       <c r="S30" s="12">
-        <f>VLOOKUP(K30,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K30,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1651</v>
       </c>
       <c r="T30" s="12">
-        <f>VLOOKUP(M30,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M30,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>223</v>
       </c>
       <c r="U30" s="12">
-        <f>VLOOKUP(O30,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O30,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>301</v>
       </c>
       <c r="V30" s="12"/>
@@ -70640,11 +71408,11 @@
         <v>0</v>
       </c>
       <c r="S31" s="12">
-        <f>VLOOKUP(K31,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K31,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="T31" s="12">
-        <f>VLOOKUP(M31,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M31,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>205</v>
       </c>
       <c r="U31" s="12"/>
@@ -70704,19 +71472,19 @@
         <v>0</v>
       </c>
       <c r="S32" s="12">
-        <f>VLOOKUP(K32,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K32,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1654</v>
       </c>
       <c r="T32" s="12">
-        <f>VLOOKUP(M32,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M32,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>250</v>
       </c>
       <c r="U32" s="12">
-        <f>VLOOKUP(O32,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O32,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>229</v>
       </c>
       <c r="V32" s="12">
-        <f>VLOOKUP(Q32,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q32,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="X32" s="12" t="str">
@@ -70769,15 +71537,15 @@
       <c r="Q33" s="16"/>
       <c r="R33" s="34"/>
       <c r="S33" s="12">
-        <f>VLOOKUP(K33,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K33,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>202</v>
       </c>
       <c r="T33" s="12">
-        <f>VLOOKUP(M33,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M33,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1654</v>
       </c>
       <c r="U33" s="12">
-        <f>VLOOKUP(O33,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O33,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>210</v>
       </c>
       <c r="X33" s="12" t="str">
@@ -70835,15 +71603,15 @@
         <v>0</v>
       </c>
       <c r="S34" s="12">
-        <f>VLOOKUP(K34,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K34,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="T34" s="12">
-        <f>VLOOKUP(M34,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M34,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>228</v>
       </c>
       <c r="U34" s="12">
-        <f>VLOOKUP(O34,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O34,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>277</v>
       </c>
       <c r="V34" s="12"/>
@@ -70895,15 +71663,15 @@
         <v>0</v>
       </c>
       <c r="S35" s="12">
-        <f>VLOOKUP(K35,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K35,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>273</v>
       </c>
       <c r="T35" s="12">
-        <f>VLOOKUP(M35,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M35,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="U35" s="12">
-        <f>VLOOKUP(O35,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O35,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="V35" s="12"/>
@@ -70962,19 +71730,19 @@
         <v>0</v>
       </c>
       <c r="S36" s="12">
-        <f>VLOOKUP(K36,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K36,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>264</v>
       </c>
       <c r="T36" s="12">
-        <f>VLOOKUP(M36,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M36,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>277</v>
       </c>
       <c r="U36" s="12">
-        <f>VLOOKUP(O36,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O36,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>255</v>
       </c>
       <c r="V36" s="12">
-        <f>VLOOKUP(Q36,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q36,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>246</v>
       </c>
       <c r="X36" s="12" t="str">
@@ -71025,15 +71793,15 @@
         <v>0</v>
       </c>
       <c r="S37" s="12">
-        <f>VLOOKUP(K37,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K37,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1650</v>
       </c>
       <c r="T37" s="12">
-        <f>VLOOKUP(M37,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M37,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>208</v>
       </c>
       <c r="U37" s="12">
-        <f>VLOOKUP(O37,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O37,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="W37" s="12"/>
@@ -71092,19 +71860,19 @@
         <v>0</v>
       </c>
       <c r="S38" s="12">
-        <f>VLOOKUP(K38,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K38,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1651</v>
       </c>
       <c r="T38" s="12">
-        <f>VLOOKUP(M38,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M38,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>242</v>
       </c>
       <c r="U38" s="12">
-        <f>VLOOKUP(O38,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O38,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>247</v>
       </c>
       <c r="V38" s="12">
-        <f>VLOOKUP(Q38,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q38,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>241</v>
       </c>
       <c r="X38" s="12" t="str">
@@ -71162,19 +71930,19 @@
         <v>0</v>
       </c>
       <c r="S39" s="12">
-        <f>VLOOKUP(K39,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K39,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1654</v>
       </c>
       <c r="T39" s="12">
-        <f>VLOOKUP(M39,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M39,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="U39" s="12">
-        <f>VLOOKUP(O39,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O39,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="V39" s="12">
-        <f>VLOOKUP(Q39,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q39,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>218</v>
       </c>
       <c r="X39" s="12" t="str">
@@ -71225,15 +71993,15 @@
         <v>0</v>
       </c>
       <c r="S40" s="12">
-        <f>VLOOKUP(K40,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K40,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T40" s="12">
-        <f>VLOOKUP(M40,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M40,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="U40" s="12">
-        <f>VLOOKUP(O40,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O40,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>228</v>
       </c>
       <c r="W40" s="12"/>
@@ -71285,15 +72053,15 @@
         <v>0</v>
       </c>
       <c r="S41" s="12">
-        <f>VLOOKUP(K41,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K41,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1650</v>
       </c>
       <c r="T41" s="12">
-        <f>VLOOKUP(M41,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M41,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="U41" s="12">
-        <f>VLOOKUP(O41,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O41,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>282</v>
       </c>
       <c r="W41" s="12"/>
@@ -71352,19 +72120,19 @@
         <v>0</v>
       </c>
       <c r="S42" s="12">
-        <f>VLOOKUP(K42,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K42,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1657</v>
       </c>
       <c r="T42" s="12">
-        <f>VLOOKUP(M42,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M42,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>279</v>
       </c>
       <c r="U42" s="12">
-        <f>VLOOKUP(O42,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O42,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>234</v>
       </c>
       <c r="V42" s="12">
-        <f>VLOOKUP(Q42,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q42,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>247</v>
       </c>
       <c r="X42" s="12" t="str">
@@ -71422,19 +72190,19 @@
         <v>0</v>
       </c>
       <c r="S43" s="12">
-        <f>VLOOKUP(K43,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K43,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>248</v>
       </c>
       <c r="T43" s="12">
-        <f>VLOOKUP(M43,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M43,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1650</v>
       </c>
       <c r="U43" s="12">
-        <f>VLOOKUP(O43,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O43,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>245</v>
       </c>
       <c r="V43" s="12">
-        <f>VLOOKUP(Q43,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q43,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>285</v>
       </c>
       <c r="X43" s="12" t="str">
@@ -71485,15 +72253,15 @@
         <v>1.75</v>
       </c>
       <c r="S44" s="12">
-        <f>VLOOKUP(K44,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K44,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T44" s="12">
-        <f>VLOOKUP(M44,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M44,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>302</v>
       </c>
       <c r="U44" s="12">
-        <f>VLOOKUP(O44,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O44,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="W44" s="12"/>
@@ -71545,15 +72313,15 @@
         <v>1.75</v>
       </c>
       <c r="S45" s="12">
-        <f>VLOOKUP(K45,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K45,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="T45" s="12">
-        <f>VLOOKUP(M45,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M45,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>222</v>
       </c>
       <c r="U45" s="12">
-        <f>VLOOKUP(O45,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O45,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="W45" s="12"/>
@@ -71605,15 +72373,15 @@
         <v>0</v>
       </c>
       <c r="S46" s="12">
-        <f>VLOOKUP(K46,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K46,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="T46" s="12">
-        <f>VLOOKUP(M46,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M46,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>210</v>
       </c>
       <c r="U46" s="12">
-        <f>VLOOKUP(O46,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O46,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>202</v>
       </c>
       <c r="W46" s="12"/>
@@ -71672,15 +72440,15 @@
         <v>0</v>
       </c>
       <c r="S47" s="12">
-        <f>VLOOKUP(K47,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K47,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1701</v>
       </c>
       <c r="T47" s="12">
-        <f>VLOOKUP(M47,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M47,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>273</v>
       </c>
       <c r="U47" s="12">
-        <f>VLOOKUP(O47,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O47,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>238</v>
       </c>
       <c r="W47" s="12"/>
@@ -71732,15 +72500,15 @@
         <v>0</v>
       </c>
       <c r="S48" s="12">
-        <f>VLOOKUP(K48,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K48,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1700</v>
       </c>
       <c r="T48" s="12">
-        <f>VLOOKUP(M48,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M48,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>301</v>
       </c>
       <c r="U48" s="12">
-        <f>VLOOKUP(O48,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O48,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>214</v>
       </c>
       <c r="W48" s="12"/>
@@ -71799,19 +72567,19 @@
         <v>0</v>
       </c>
       <c r="S49" s="12">
-        <f>VLOOKUP(K49,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K49,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1701</v>
       </c>
       <c r="T49" s="12">
-        <f>VLOOKUP(M49,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M49,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>234</v>
       </c>
       <c r="U49" s="12">
-        <f>VLOOKUP(O49,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O49,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>223</v>
       </c>
       <c r="V49" s="12">
-        <f>VLOOKUP(Q49,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q49,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>279</v>
       </c>
       <c r="X49" s="12" t="str">
@@ -71869,19 +72637,19 @@
         <v>0</v>
       </c>
       <c r="S50" s="12">
-        <f>VLOOKUP(K50,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K50,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1700</v>
       </c>
       <c r="T50" s="12">
-        <f>VLOOKUP(M50,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M50,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>280</v>
       </c>
       <c r="U50" s="12">
-        <f>VLOOKUP(O50,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O50,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="V50" s="12">
-        <f>VLOOKUP(Q50,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q50,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="X50" s="12" t="str">
@@ -71939,19 +72707,19 @@
         <v>5</v>
       </c>
       <c r="S51" s="12">
-        <f>VLOOKUP(K51,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K51,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1702</v>
       </c>
       <c r="T51" s="12">
-        <f>VLOOKUP(M51,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M51,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>275</v>
       </c>
       <c r="U51" s="12">
-        <f>VLOOKUP(O51,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O51,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>240</v>
       </c>
       <c r="V51" s="12">
-        <f>VLOOKUP(Q51,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q51,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>299</v>
       </c>
       <c r="X51" s="12" t="str">
@@ -72009,19 +72777,19 @@
         <v>0</v>
       </c>
       <c r="S52" s="12">
-        <f>VLOOKUP(K52,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K52,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1700</v>
       </c>
       <c r="T52" s="12">
-        <f>VLOOKUP(M52,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M52,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>281</v>
       </c>
       <c r="U52" s="12">
-        <f>VLOOKUP(O52,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O52,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>251</v>
       </c>
       <c r="V52" s="12">
-        <f>VLOOKUP(Q52,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q52,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>282</v>
       </c>
       <c r="X52" s="12" t="str">
@@ -72079,19 +72847,19 @@
         <v>0</v>
       </c>
       <c r="S53" s="12">
-        <f>VLOOKUP(K53,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K53,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="T53" s="12">
-        <f>VLOOKUP(M53,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M53,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1704</v>
       </c>
       <c r="U53" s="12">
-        <f>VLOOKUP(O53,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O53,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>264</v>
       </c>
       <c r="V53" s="12">
-        <f>VLOOKUP(Q53,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q53,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>258</v>
       </c>
       <c r="X53" s="12" t="str">
@@ -72148,19 +72916,19 @@
         <v>0</v>
       </c>
       <c r="S54" s="12">
-        <f>VLOOKUP(K54,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K54,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1703</v>
       </c>
       <c r="T54" s="12">
-        <f>VLOOKUP(M54,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M54,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>282</v>
       </c>
       <c r="U54" s="12">
-        <f>VLOOKUP(O54,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(O54,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>232</v>
       </c>
       <c r="V54" s="12">
-        <f>VLOOKUP(Q54,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(Q54,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>267</v>
       </c>
       <c r="X54" s="12" t="str">
@@ -72367,15 +73135,15 @@
         <v>468</v>
       </c>
       <c r="Q69" s="16">
-        <f>VLOOKUP(J69,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J69,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>290</v>
       </c>
       <c r="S69" s="12">
-        <f>VLOOKUP(K69,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K69,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>292</v>
       </c>
       <c r="T69" s="12">
-        <f>VLOOKUP(M69,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M69,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>244</v>
       </c>
       <c r="V69" t="str">
@@ -72404,15 +73172,15 @@
         <v>446</v>
       </c>
       <c r="Q70" s="16">
-        <f>VLOOKUP(J70,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J70,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>294</v>
       </c>
       <c r="S70" s="12">
-        <f>VLOOKUP(K70,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K70,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>265</v>
       </c>
       <c r="T70" s="12">
-        <f>VLOOKUP(M70,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M70,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>207</v>
       </c>
       <c r="V70" s="12" t="str">
@@ -72441,15 +73209,15 @@
         <v>477</v>
       </c>
       <c r="Q71" s="16">
-        <f>VLOOKUP(J71,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J71,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>251</v>
       </c>
       <c r="S71" s="12">
-        <f>VLOOKUP(K71,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K71,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>287</v>
       </c>
       <c r="T71" s="12">
-        <f>VLOOKUP(M71,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M71,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>257</v>
       </c>
       <c r="V71" s="12" t="str">
@@ -72478,15 +73246,15 @@
         <v>490</v>
       </c>
       <c r="Q72" s="16">
-        <f>VLOOKUP(J72,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J72,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>290</v>
       </c>
       <c r="S72" s="12">
-        <f>VLOOKUP(K72,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K72,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>225</v>
       </c>
       <c r="T72" s="12">
-        <f>VLOOKUP(M72,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M72,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="V72" s="12" t="str">
@@ -72515,15 +73283,15 @@
         <v>490</v>
       </c>
       <c r="Q73" s="16">
-        <f>VLOOKUP(J73,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J73,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>267</v>
       </c>
       <c r="S73" s="12">
-        <f>VLOOKUP(K73,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K73,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>261</v>
       </c>
       <c r="T73" s="12">
-        <f>VLOOKUP(M73,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M73,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="V73" s="12" t="str">
@@ -72552,15 +73320,15 @@
         <v>490</v>
       </c>
       <c r="Q74" s="16">
-        <f>VLOOKUP(J74,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J74,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>284</v>
       </c>
       <c r="S74" s="12">
-        <f>VLOOKUP(K74,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K74,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>291</v>
       </c>
       <c r="T74" s="12">
-        <f>VLOOKUP(M74,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M74,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="V74" s="12" t="str">
@@ -72587,15 +73355,15 @@
         <v>448</v>
       </c>
       <c r="Q75" s="16">
-        <f>VLOOKUP(J75,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J75,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>263</v>
       </c>
       <c r="S75" s="12">
-        <f>VLOOKUP(K75,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K75,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>255</v>
       </c>
       <c r="T75" s="12">
-        <f>VLOOKUP(M75,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M75,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>210</v>
       </c>
       <c r="V75" s="12" t="str">
@@ -72624,15 +73392,15 @@
         <v>472</v>
       </c>
       <c r="Q76" s="16">
-        <f>VLOOKUP(J76,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J76,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>236</v>
       </c>
       <c r="S76" s="12">
-        <f>VLOOKUP(K76,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K76,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>259</v>
       </c>
       <c r="T76" s="12">
-        <f>VLOOKUP(M76,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M76,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>250</v>
       </c>
       <c r="V76" s="12" t="str">
@@ -72661,15 +73429,15 @@
         <v>506</v>
       </c>
       <c r="Q77" s="16">
-        <f>VLOOKUP(J77,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J77,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>208</v>
       </c>
       <c r="S77" s="12">
-        <f>VLOOKUP(K77,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K77,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>278</v>
       </c>
       <c r="T77" s="12">
-        <f>VLOOKUP(M77,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M77,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>281</v>
       </c>
       <c r="V77" s="12" t="str">
@@ -72698,15 +73466,15 @@
         <v>467</v>
       </c>
       <c r="Q78" s="16">
-        <f>VLOOKUP(J78,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J78,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>288</v>
       </c>
       <c r="S78" s="12">
-        <f>VLOOKUP(K78,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K78,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>256</v>
       </c>
       <c r="T78" s="12">
-        <f>VLOOKUP(M78,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M78,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>240</v>
       </c>
       <c r="V78" s="12" t="str">
@@ -72735,15 +73503,15 @@
         <v>474</v>
       </c>
       <c r="Q79" s="16">
-        <f>VLOOKUP(J79,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J79,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>293</v>
       </c>
       <c r="S79" s="12">
-        <f>VLOOKUP(K79,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K79,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>289</v>
       </c>
       <c r="T79" s="12">
-        <f>VLOOKUP(M79,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M79,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>254</v>
       </c>
       <c r="V79" s="12" t="str">
@@ -72766,15 +73534,15 @@
         <v>491</v>
       </c>
       <c r="Q80" s="16">
-        <f>VLOOKUP(J80,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J80,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="S80" s="12">
-        <f>VLOOKUP(K80,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K80,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>269</v>
       </c>
       <c r="T80" s="12">
-        <f>VLOOKUP(M80,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M80,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>291</v>
       </c>
       <c r="U80" s="12"/>
@@ -72812,11 +73580,11 @@
         <v>720</v>
       </c>
       <c r="Q83" s="16">
-        <f>VLOOKUP(J83,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J83,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>105</v>
       </c>
       <c r="S83" s="12">
-        <f>VLOOKUP(K83,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K83,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="T83" s="12"/>
@@ -72844,11 +73612,11 @@
         <v>723</v>
       </c>
       <c r="Q84" s="16">
-        <f>VLOOKUP(J84,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J84,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1800</v>
       </c>
       <c r="S84" s="12">
-        <f>VLOOKUP(K84,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K84,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>285</v>
       </c>
       <c r="T84" s="12"/>
@@ -72878,15 +73646,15 @@
         <v>476</v>
       </c>
       <c r="Q85" s="16">
-        <f>VLOOKUP(J85,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J85,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>204</v>
       </c>
       <c r="S85" s="12">
-        <f>VLOOKUP(K85,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K85,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>286</v>
       </c>
       <c r="T85" s="12">
-        <f>VLOOKUP(M85,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M85,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>256</v>
       </c>
       <c r="W85" s="12" t="str">
@@ -72912,11 +73680,11 @@
         <v>741</v>
       </c>
       <c r="Q86" s="16">
-        <f>VLOOKUP(J86,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J86,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>298</v>
       </c>
       <c r="S86" s="12">
-        <f>VLOOKUP(K86,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K86,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>271</v>
       </c>
       <c r="T86" s="12"/>
@@ -72946,15 +73714,15 @@
         <v>450</v>
       </c>
       <c r="Q87" s="16">
-        <f>VLOOKUP(J87,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J87,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1803</v>
       </c>
       <c r="S87" s="12">
-        <f>VLOOKUP(K87,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K87,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>241</v>
       </c>
       <c r="T87" s="12">
-        <f>VLOOKUP(M87,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M87,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>213</v>
       </c>
       <c r="W87" s="12" t="str">
@@ -72983,15 +73751,15 @@
         <v>369</v>
       </c>
       <c r="Q88" s="16">
-        <f>VLOOKUP(J88,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J88,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="S88" s="12">
-        <f>VLOOKUP(K88,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K88,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>248</v>
       </c>
       <c r="T88" s="12">
-        <f>VLOOKUP(M88,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M88,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>224</v>
       </c>
       <c r="W88" s="12" t="str">
@@ -73020,15 +73788,15 @@
         <v>473</v>
       </c>
       <c r="Q89" s="16">
-        <f>VLOOKUP(J89,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J89,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="S89" s="12">
-        <f>VLOOKUP(K89,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K89,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>228</v>
       </c>
       <c r="T89" s="12">
-        <f>VLOOKUP(M89,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M89,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>251</v>
       </c>
       <c r="W89" s="12" t="str">
@@ -73057,15 +73825,15 @@
         <v>463</v>
       </c>
       <c r="Q90" s="16">
-        <f>VLOOKUP(J90,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J90,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>272</v>
       </c>
       <c r="S90" s="12">
-        <f>VLOOKUP(K90,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K90,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>279</v>
       </c>
       <c r="T90" s="12">
-        <f>VLOOKUP(M90,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M90,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>234</v>
       </c>
       <c r="W90" s="12" t="str">
@@ -73094,15 +73862,15 @@
         <v>372</v>
       </c>
       <c r="Q91" s="16">
-        <f>VLOOKUP(J91,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(J91,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>1804</v>
       </c>
       <c r="S91" s="12">
-        <f>VLOOKUP(K91,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(K91,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>288</v>
       </c>
       <c r="T91" s="12">
-        <f>VLOOKUP(M91,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(M91,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>247</v>
       </c>
       <c r="W91" s="12" t="str">
@@ -79393,7 +80161,7 @@
         <v>180</v>
       </c>
       <c r="S63" s="38">
-        <f>VLOOKUP(D63,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D63,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>301</v>
       </c>
     </row>
@@ -79455,7 +80223,7 @@
         <v>180</v>
       </c>
       <c r="S64" s="38">
-        <f>VLOOKUP(D64,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D64,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>3007</v>
       </c>
     </row>
@@ -79517,7 +80285,7 @@
         <v>405</v>
       </c>
       <c r="S65" s="38">
-        <f>VLOOKUP(D65,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D65,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>302</v>
       </c>
     </row>
@@ -79579,7 +80347,7 @@
         <v>154.28571428571428</v>
       </c>
       <c r="S66" s="38">
-        <f>VLOOKUP(D66,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D66,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>283</v>
       </c>
     </row>
@@ -79641,7 +80409,7 @@
         <v>405</v>
       </c>
       <c r="S67" s="38">
-        <f>VLOOKUP(D67,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D67,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>3008</v>
       </c>
     </row>
@@ -79703,7 +80471,7 @@
         <v>360</v>
       </c>
       <c r="S68" s="38">
-        <f>VLOOKUP(D68,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D68,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>3006</v>
       </c>
     </row>
@@ -79765,7 +80533,7 @@
         <v>480</v>
       </c>
       <c r="S69" s="38">
-        <f>VLOOKUP(D69,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D69,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>276</v>
       </c>
     </row>
@@ -79827,7 +80595,7 @@
         <v>360</v>
       </c>
       <c r="S70" s="38">
-        <f>VLOOKUP(D70,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D70,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>235</v>
       </c>
     </row>
@@ -79889,7 +80657,7 @@
         <v>405</v>
       </c>
       <c r="S71" s="38">
-        <f>VLOOKUP(D71,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D71,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>302</v>
       </c>
     </row>
@@ -79951,7 +80719,7 @@
         <v>90</v>
       </c>
       <c r="S72" s="38">
-        <f>VLOOKUP(D72,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D72,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>297</v>
       </c>
     </row>
@@ -80013,7 +80781,7 @@
         <v>180</v>
       </c>
       <c r="S73" s="38">
-        <f>VLOOKUP(D73,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D73,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>222</v>
       </c>
     </row>
@@ -80075,7 +80843,7 @@
         <v>270</v>
       </c>
       <c r="S74" s="38">
-        <f>VLOOKUP(D74,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D74,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>213</v>
       </c>
     </row>
@@ -80137,7 +80905,7 @@
         <v>900</v>
       </c>
       <c r="S75" s="38">
-        <f>VLOOKUP(D75,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D75,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>240</v>
       </c>
     </row>
@@ -80199,7 +80967,7 @@
         <v>1350</v>
       </c>
       <c r="S76" s="38">
-        <f>VLOOKUP(D76,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D76,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>260</v>
       </c>
     </row>
@@ -80261,7 +81029,7 @@
         <v>225</v>
       </c>
       <c r="S77" s="38">
-        <f>VLOOKUP(D77,ItemData!$A$4:$B$412,2,FALSE)</f>
+        <f>VLOOKUP(D77,ItemData!$A$4:$B$420,2,FALSE)</f>
         <v>203</v>
       </c>
     </row>

--- a/Datas/ItemData.xlsx
+++ b/Datas/ItemData.xlsx
@@ -13,24 +13,25 @@
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="17" r:id="rId2"/>
-    <sheet name="Sheet13" sheetId="16" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="8" r:id="rId7"/>
-    <sheet name="植物" sheetId="7" r:id="rId8"/>
-    <sheet name="动物" sheetId="14" r:id="rId9"/>
-    <sheet name="装备" sheetId="9" r:id="rId10"/>
-    <sheet name="Sheet8" sheetId="11" r:id="rId11"/>
-    <sheet name="材料" sheetId="12" r:id="rId12"/>
-    <sheet name="食物" sheetId="13" r:id="rId13"/>
-    <sheet name="鱼" sheetId="15" r:id="rId14"/>
+    <sheet name="Sheet6" sheetId="18" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="17" r:id="rId3"/>
+    <sheet name="Sheet13" sheetId="16" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="8" r:id="rId8"/>
+    <sheet name="植物" sheetId="7" r:id="rId9"/>
+    <sheet name="动物" sheetId="14" r:id="rId10"/>
+    <sheet name="装备" sheetId="9" r:id="rId11"/>
+    <sheet name="Sheet8" sheetId="11" r:id="rId12"/>
+    <sheet name="材料" sheetId="12" r:id="rId13"/>
+    <sheet name="食物" sheetId="13" r:id="rId14"/>
+    <sheet name="鱼" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemData!$A$3:$AI$420</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet13!$Q$47:$Q$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet2!$B$5:$X$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet13!$Q$47:$Q$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet2!$B$5:$X$54</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -159,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6755" uniqueCount="1832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6805" uniqueCount="1857">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6482,6 +6483,81 @@
   <si>
     <t>int2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芜菁根圆润饱满，是腌菜好原料，简单加工后，带着质朴清甜，能为日常餐桌添独特风味。</t>
+  </si>
+  <si>
+    <t>卷心菜叶片层层紧裹，形成紧实叶球，颜色翠绿，口感脆嫩，是餐桌上常见的蔬菜。</t>
+  </si>
+  <si>
+    <t>葱身姿纤细修长，有着独特且浓郁的香气，轻轻一嗅，便能提神醒脑，是调味的好帮手。</t>
+  </si>
+  <si>
+    <t>萝卜形态多样，有长有圆，口感更是一绝，咬下瞬间，清甜汁水率先散开，随后一丝辛辣巧妙涌上舌尖，丰富口感令人难忘。</t>
+  </si>
+  <si>
+    <t>紫甘蓝有着深紫色外衣，神秘又迷人，它富含花青素，营养满满，好看又好吃。</t>
+  </si>
+  <si>
+    <t>黄瓜浑身带刺，表皮翠绿，内里果肉水润脆嫩，直接咬上一口，清甜汁水在口中迸发，满是清爽。</t>
+  </si>
+  <si>
+    <t>西兰花的花球紧密排列，像精心雕琢的艺术品，色泽翠绿，营养丰富，口感鲜嫩。</t>
+  </si>
+  <si>
+    <t>番茄果实圆润可爱，颜色鲜艳，无论是红番茄的酸甜，还是黄番茄的清甜，都十分诱人。</t>
+  </si>
+  <si>
+    <t>胡萝卜拥有细长橙红的根，富含胡萝卜素等营养成分，是健康饮食的好选择。</t>
+  </si>
+  <si>
+    <t>西瓜个头较大，表皮有条纹，切开后，红瓤黑籽，汁水四溢，清甜可口，是夏日消暑的明星水果。</t>
+  </si>
+  <si>
+    <t>辣椒形态各异，辣度从温和到火爆，颜色丰富，为食物增添别样风味，是重要的调味食材。</t>
+  </si>
+  <si>
+    <t>奇异果外表毛茸茸，剥开后，翠绿果肉搭配密密麻麻的黑籽，酸甜汁水丰富，让人欲罢不能。</t>
+  </si>
+  <si>
+    <t>茄子颜色多样，有深紫、浅紫等，形状或修长或圆润，口感软糯，深受人们喜爱。</t>
+  </si>
+  <si>
+    <t>豌豆荚饱满，里面的豆粒圆润可爱，或青或黄，口感清甜，十分美味。</t>
+  </si>
+  <si>
+    <t>土豆块茎呈椭圆形，表皮颜色多样，有黄、白等，富含淀粉，是提供能量的好食材。</t>
+  </si>
+  <si>
+    <t>大蒜由多瓣组成，气味浓烈，具有杀菌作用，是常见的调味佐料。</t>
+  </si>
+  <si>
+    <t>芦笋嫩芽细长，顶端微微弯曲，口感鲜嫩爽滑，带有自然的清香。</t>
+  </si>
+  <si>
+    <t>南瓜果实形态各异，有圆有扁，果肉金黄，香甜软糯，是秋季丰收的象征。</t>
+  </si>
+  <si>
+    <t>玉米棒饱满，玉米粒排列整齐，颜色金黄，颗粒饱满，香甜可口，是常见的粮食作物。</t>
+  </si>
+  <si>
+    <t>大麦麦粒饱满，用途广泛，可用于酿造，也可作为饲料。</t>
+  </si>
+  <si>
+    <t>啤酒花有独特的香气和苦味，是酿造啤酒时赋予啤酒独特风味的关键。</t>
+  </si>
+  <si>
+    <t>草莓小巧玲珑，心形果实十分可爱，色泽鲜艳，酸甜多汁，果香浓郁。</t>
+  </si>
+  <si>
+    <t>蓝莓果实小巧，呈深蓝色，表面有一层白霜，富含花青素，营养丰富。</t>
+  </si>
+  <si>
+    <t>红薯块根形状多样，表皮或红或紫，果肉香甜，产量高，是常见的食物。</t>
+  </si>
+  <si>
+    <t>甜菜根粗壮厚实，富含糖分，既可以直接食用，也是制糖的重要原料。</t>
   </si>
 </sst>
 </file>
@@ -50764,6 +50840,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:R157"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -53597,7 +53683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O261"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -56438,7 +56524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H2:R218"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -61032,7 +61118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="D1:Y92"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -65650,7 +65736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="G2:O32"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -66147,6 +66233,267 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="J4:J102"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="4" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J6" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="8" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J10" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="12" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J12" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="14" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J14" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="16" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J18" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="20" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J22" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="24" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J26" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="28" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J30" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="32" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J34" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="36" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J38" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="40" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J42" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="44" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J46" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="48" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J50" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="52" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J54" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="56" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J58" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="60" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J60" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J62" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="64" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J66" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="68" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J68" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J70" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="72" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J72" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J74" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="76" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J78" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="80" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J80" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="82" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J82" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="84" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J84" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J86" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="88" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J88" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J90" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="92" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J92" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="94" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J94" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="96" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J96" t="s">
+        <v>48</v>
+      </